--- a/data/SAB.MI.xlsx
+++ b/data/SAB.MI.xlsx
@@ -38,118 +38,118 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5656795501709</t>
+    <t xml:space="preserve">8.56568050384521</t>
   </si>
   <si>
     <t xml:space="preserve">SAB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61823177337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48310375213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33296012878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37049293518066</t>
+    <t xml:space="preserve">8.61822986602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4831018447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33295822143555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37049388885498</t>
   </si>
   <si>
     <t xml:space="preserve">8.31794357299805</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25788688659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16029167175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88252782821655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52969169616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66481924057007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62728500366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61226987838745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73989152908325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75490617752075</t>
+    <t xml:space="preserve">8.257887840271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16029357910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88252830505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52969121932983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66482019424438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62728452682495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61227083206177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73989200592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75490665435791</t>
   </si>
   <si>
     <t xml:space="preserve">7.76992130279541</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89754390716553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61977624893188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79994964599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72487735748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65731334686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50716924667358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34201288223267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54470539093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39080858230591</t>
+    <t xml:space="preserve">7.89754343032837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61977767944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79994821548462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72487783432007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65731430053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50717067718506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34201145172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54470491409302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39080905914307</t>
   </si>
   <si>
     <t xml:space="preserve">7.58224105834961</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82247066497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0852222442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1152515411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95760059356689</t>
+    <t xml:space="preserve">7.82246971130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08522319793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11525058746338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95759916305542</t>
   </si>
   <si>
     <t xml:space="preserve">8.06270027160645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03267192840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9200644493103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77742719650269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86751461029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80745649337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98762798309326</t>
+    <t xml:space="preserve">8.03267288208008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92006397247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77742767333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86751365661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80745601654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98762893676758</t>
   </si>
   <si>
     <t xml:space="preserve">8.04017925262451</t>
@@ -161,34 +161,34 @@
     <t xml:space="preserve">7.96510696411133</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9050498008728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93507957458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89003562927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94258594512939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82997941970825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81496334075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73238515853882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64980602264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71737003326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67232894897461</t>
+    <t xml:space="preserve">7.90505027770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93507814407349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89003610610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94258499145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82997846603394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81496381759644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7323842048645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64980554580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71737098693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67232847213745</t>
   </si>
   <si>
     <t xml:space="preserve">7.63479232788086</t>
@@ -197,109 +197,109 @@
     <t xml:space="preserve">7.51467800140381</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64229917526245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56722784042358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70235538482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74739933013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46963214874268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69484949111938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4921555519104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47338771820068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43585157394409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50341606140137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48089408874512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59725570678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42834520339966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38705587387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37203979492188</t>
+    <t xml:space="preserve">7.64229965209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56722736358643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70235633850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.747398853302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46963405609131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69484901428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49215507507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47338628768921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43585205078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50341510772705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48089361190796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59725475311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4283447265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38705539703369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37203931808472</t>
   </si>
   <si>
     <t xml:space="preserve">7.31949090957642</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28195476531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52122068405151</t>
+    <t xml:space="preserve">7.28195428848267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52122116088867</t>
   </si>
   <si>
     <t xml:space="preserve">7.80533933639526</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75009346008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75798606872559</t>
+    <t xml:space="preserve">7.75009393692017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75798654556274</t>
   </si>
   <si>
     <t xml:space="preserve">7.81323099136353</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86058521270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69879484176636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58435821533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68695640563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5764684677124</t>
+    <t xml:space="preserve">7.8605842590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69879531860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58435916900635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68695735931396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57646656036377</t>
   </si>
   <si>
     <t xml:space="preserve">7.53700590133667</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49754476547241</t>
+    <t xml:space="preserve">7.49754524230957</t>
   </si>
   <si>
     <t xml:space="preserve">7.28445720672607</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92536354064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07926082611084</t>
+    <t xml:space="preserve">6.92536401748657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07926225662231</t>
   </si>
   <si>
     <t xml:space="preserve">7.22921228408813</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45808458328247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26078033447266</t>
+    <t xml:space="preserve">7.45808410644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26077938079834</t>
   </si>
   <si>
     <t xml:space="preserve">7.37127113342285</t>
@@ -308,64 +308,64 @@
     <t xml:space="preserve">7.26472663879395</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34759521484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46992254257202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3673243522644</t>
+    <t xml:space="preserve">7.34759569168091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46992301940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36732482910156</t>
   </si>
   <si>
     <t xml:space="preserve">7.37916326522827</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13450622558594</t>
+    <t xml:space="preserve">7.13450527191162</t>
   </si>
   <si>
     <t xml:space="preserve">7.18975162506104</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10293674468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15029191970825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10688304901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20553493499756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18185949325562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2213191986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19369697570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24894189834595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19764375686646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18580532073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22526597976685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20948219299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31602573394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21342754364014</t>
+    <t xml:space="preserve">7.10293865203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15029144287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10688447952271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20553636550903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18185997009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22131967544556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19369745254517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24894285202026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19764423370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18580484390259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22526502609253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20948123931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31602621078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21342802047729</t>
   </si>
   <si>
     <t xml:space="preserve">7.16607475280762</t>
@@ -377,25 +377,25 @@
     <t xml:space="preserve">7.13056087493896</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11082983016968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17791271209717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23315811157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27656602859497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30024242401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29234933853149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24104976654053</t>
+    <t xml:space="preserve">7.11082935333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17791318893433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23315858840942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27656507492065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30024194717407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29234981536865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24105072021484</t>
   </si>
   <si>
     <t xml:space="preserve">7.11872148513794</t>
@@ -404,16 +404,16 @@
     <t xml:space="preserve">7.095046043396</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00428581237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94509410858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93325614929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09899091720581</t>
+    <t xml:space="preserve">7.00428628921509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94509506225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93325567245483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09899187088013</t>
   </si>
   <si>
     <t xml:space="preserve">7.15423679351807</t>
@@ -422,49 +422,49 @@
     <t xml:space="preserve">7.13845252990723</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15818214416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05558490753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07136964797974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06742334365845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0240159034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04769325256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06347560882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08320665359497</t>
+    <t xml:space="preserve">7.15818166732788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05558443069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07136917114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06742286682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02401542663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04769277572632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06347703933716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08320760726929</t>
   </si>
   <si>
     <t xml:space="preserve">7.05163908004761</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04374599456787</t>
+    <t xml:space="preserve">7.04374551773071</t>
   </si>
   <si>
     <t xml:space="preserve">7.03190803527832</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05953025817871</t>
+    <t xml:space="preserve">7.05953073501587</t>
   </si>
   <si>
     <t xml:space="preserve">7.03585433959961</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17396640777588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9056339263916</t>
+    <t xml:space="preserve">7.17396688461304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90563440322876</t>
   </si>
   <si>
     <t xml:space="preserve">6.91352653503418</t>
@@ -479,16 +479,16 @@
     <t xml:space="preserve">6.94114828109741</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9687705039978</t>
+    <t xml:space="preserve">6.96877098083496</t>
   </si>
   <si>
     <t xml:space="preserve">7.14239883422852</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45019292831421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79350090026855</t>
+    <t xml:space="preserve">7.45019245147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7935004234314</t>
   </si>
   <si>
     <t xml:space="preserve">7.92372179031372</t>
@@ -503,118 +503,118 @@
     <t xml:space="preserve">8.16837882995605</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08945751190186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19994735717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06578159332275</t>
+    <t xml:space="preserve">8.08945655822754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19994640350342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06578063964844</t>
   </si>
   <si>
     <t xml:space="preserve">8.1289176940918</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17626953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32622146606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55509567260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56298542022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42881774902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35778903961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39725017547607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42092800140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44460391998291</t>
+    <t xml:space="preserve">8.17627048492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32622051239014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55509376525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56298637390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42881965637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35779190063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39725208282471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42092704772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44460487365723</t>
   </si>
   <si>
     <t xml:space="preserve">8.40514183044434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26308345794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18416309356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30254650115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22362327575684</t>
+    <t xml:space="preserve">8.26308536529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18416118621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30254554748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22362232208252</t>
   </si>
   <si>
     <t xml:space="preserve">8.2867603302002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25519180297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34989833831787</t>
+    <t xml:space="preserve">8.25519275665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34989738464355</t>
   </si>
   <si>
     <t xml:space="preserve">8.31043720245361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36568260192871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33411407470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34200668334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46038913726807</t>
+    <t xml:space="preserve">8.36568164825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33411312103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34200572967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46038818359375</t>
   </si>
   <si>
     <t xml:space="preserve">8.62612438201904</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74450492858887</t>
+    <t xml:space="preserve">8.74450588226318</t>
   </si>
   <si>
     <t xml:space="preserve">8.88656520843506</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00494575500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23381900787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30484771728516</t>
+    <t xml:space="preserve">9.0049467086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23381805419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30484867095947</t>
   </si>
   <si>
     <t xml:space="preserve">9.26538753509521</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1627893447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19435691833496</t>
+    <t xml:space="preserve">9.16278839111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19435787200928</t>
   </si>
   <si>
     <t xml:space="preserve">9.24960327148438</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29695510864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36798572540283</t>
+    <t xml:space="preserve">9.29695701599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36798667907715</t>
   </si>
   <si>
     <t xml:space="preserve">9.54950523376465</t>
@@ -629,13 +629,13 @@
     <t xml:space="preserve">10.2203378677368</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4807786941528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.457103729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2913684844971</t>
+    <t xml:space="preserve">10.4807796478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4571027755737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2913665771484</t>
   </si>
   <si>
     <t xml:space="preserve">10.2597980499268</t>
@@ -644,28 +644,28 @@
     <t xml:space="preserve">10.1493082046509</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0861721038818</t>
+    <t xml:space="preserve">10.0861711502075</t>
   </si>
   <si>
     <t xml:space="preserve">10.0151414871216</t>
   </si>
   <si>
-    <t xml:space="preserve">10.101957321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.165093421936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0546016693115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1808767318726</t>
+    <t xml:space="preserve">10.101954460144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1650943756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0546026229858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1808786392212</t>
   </si>
   <si>
     <t xml:space="preserve">10.1177387237549</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1887683868408</t>
+    <t xml:space="preserve">10.1887693405151</t>
   </si>
   <si>
     <t xml:space="preserve">10.070387840271</t>
@@ -677,46 +677,46 @@
     <t xml:space="preserve">10.0230340957642</t>
   </si>
   <si>
-    <t xml:space="preserve">10.496563911438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4176425933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3150434494019</t>
+    <t xml:space="preserve">10.4965620040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4176416397095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3150444030762</t>
   </si>
   <si>
     <t xml:space="preserve">10.7333278656006</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4492092132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5597009658813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6386222839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.591269493103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0095539093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8832788467407</t>
+    <t xml:space="preserve">10.4492120742798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5597019195557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6386213302612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5912685394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0095548629761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.883279800415</t>
   </si>
   <si>
     <t xml:space="preserve">11.3410234451294</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0592079162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9171495437622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0513181686401</t>
+    <t xml:space="preserve">12.0592098236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9171524047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0513191223145</t>
   </si>
   <si>
     <t xml:space="preserve">11.6882791519165</t>
@@ -728,10 +728,10 @@
     <t xml:space="preserve">12.2644052505493</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6274442672729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5406312942505</t>
+    <t xml:space="preserve">12.6274452209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5406303405762</t>
   </si>
   <si>
     <t xml:space="preserve">12.6747970581055</t>
@@ -743,43 +743,43 @@
     <t xml:space="preserve">12.4728555679321</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6518535614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8471240997314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8145790100098</t>
+    <t xml:space="preserve">12.6518526077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8471231460571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8145780563354</t>
   </si>
   <si>
     <t xml:space="preserve">12.9203481674194</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8715314865112</t>
+    <t xml:space="preserve">12.8715305328369</t>
   </si>
   <si>
     <t xml:space="preserve">12.9366207122803</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8064422607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6437158584595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.822714805603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5209159851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8463659286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7812757492065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9114561080933</t>
+    <t xml:space="preserve">12.8064403533936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6437168121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8227138519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5209150314331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8463649749756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7812738418579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9114551544189</t>
   </si>
   <si>
     <t xml:space="preserve">11.9277276992798</t>
@@ -788,7 +788,7 @@
     <t xml:space="preserve">11.9602727890015</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8056840896606</t>
+    <t xml:space="preserve">11.8056831359863</t>
   </si>
   <si>
     <t xml:space="preserve">12.1311330795288</t>
@@ -797,31 +797,31 @@
     <t xml:space="preserve">12.0009536743164</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9846820831299</t>
+    <t xml:space="preserve">11.9846811294556</t>
   </si>
   <si>
     <t xml:space="preserve">12.0416355133057</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0823173522949</t>
+    <t xml:space="preserve">12.0823163986206</t>
   </si>
   <si>
     <t xml:space="preserve">11.9765453338623</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8789100646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7161846160889</t>
+    <t xml:space="preserve">11.8789110183716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7161855697632</t>
   </si>
   <si>
     <t xml:space="preserve">11.4720993041992</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5534610748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5860061645508</t>
+    <t xml:space="preserve">11.5534601211548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5860052108765</t>
   </si>
   <si>
     <t xml:space="preserve">11.7975473403931</t>
@@ -833,13 +833,13 @@
     <t xml:space="preserve">12.0904521942139</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1636772155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.074179649353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2287683486938</t>
+    <t xml:space="preserve">12.1636791229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0741806030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2287673950195</t>
   </si>
   <si>
     <t xml:space="preserve">12.1392698287964</t>
@@ -848,205 +848,205 @@
     <t xml:space="preserve">12.2043600082397</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1880865097046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1474056243896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2531785964966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3670854568481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4077653884888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.448447227478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9447574615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7820320129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.895941734314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0098476409912</t>
+    <t xml:space="preserve">12.1880874633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.147406578064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2531757354736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3670845031738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4077663421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4484462738037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9447584152222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7820329666138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8959398269653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0098485946655</t>
   </si>
   <si>
     <t xml:space="preserve">12.9528942108154</t>
   </si>
   <si>
-    <t xml:space="preserve">12.855260848999</t>
+    <t xml:space="preserve">12.8552589416504</t>
   </si>
   <si>
     <t xml:space="preserve">12.7332162857056</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7738971710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9854383468628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2620706558228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6851568222046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9292421340942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9943323135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7502450942993</t>
+    <t xml:space="preserve">12.7738962173462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9854402542114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2620697021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.685154914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9292440414429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9943351745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7502460479736</t>
   </si>
   <si>
     <t xml:space="preserve">13.8153352737427</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8316078186035</t>
+    <t xml:space="preserve">13.8316068649292</t>
   </si>
   <si>
     <t xml:space="preserve">14.0187406539917</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0268774032593</t>
+    <t xml:space="preserve">14.0268783569336</t>
   </si>
   <si>
     <t xml:space="preserve">14.1814661026001</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1570587158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2302827835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.775411605835</t>
+    <t xml:space="preserve">14.1570568084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2302846908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7754125595093</t>
   </si>
   <si>
     <t xml:space="preserve">15.3205413818359</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2961330413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4588575363159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8249864578247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.792441368103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5076713562012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8493938446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8656673431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5158081054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0039844512939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2643451690674</t>
+    <t xml:space="preserve">15.2961301803589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.458854675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8249883651733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7924394607544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5076723098755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8493967056274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8656663894653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5158090591431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0039825439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2643413543701</t>
   </si>
   <si>
     <t xml:space="preserve">16.7769260406494</t>
   </si>
   <si>
-    <t xml:space="preserve">16.955924987793</t>
+    <t xml:space="preserve">16.9559230804443</t>
   </si>
   <si>
     <t xml:space="preserve">17.4115543365479</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0454235076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0787258148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6475048065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0217723846436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0543193817139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1275444030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2984046936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4123096466064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1682224273682</t>
+    <t xml:space="preserve">17.0454216003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0787239074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6475028991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0217704772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0543155670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1275424957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2984027862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4123115539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1682262420654</t>
   </si>
   <si>
     <t xml:space="preserve">18.1600856781006</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9160003662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.265100479126</t>
+    <t xml:space="preserve">17.9160022735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2650985717773</t>
   </si>
   <si>
     <t xml:space="preserve">17.0861034393311</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2976455688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0047416687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1267871856689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8745632171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0779685974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8664264678955</t>
+    <t xml:space="preserve">17.2976474761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0047397613525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1267833709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8745613098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0779666900635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8664245605469</t>
   </si>
   <si>
     <t xml:space="preserve">16.7850608825684</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9884662628174</t>
+    <t xml:space="preserve">16.988468170166</t>
   </si>
   <si>
     <t xml:space="preserve">16.5979290008545</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9152450561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8338813781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9640617370605</t>
+    <t xml:space="preserve">16.9152431488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8338794708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9640636444092</t>
   </si>
   <si>
     <t xml:space="preserve">16.8826999664307</t>
@@ -1055,28 +1055,28 @@
     <t xml:space="preserve">16.9233798980713</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1349201202393</t>
+    <t xml:space="preserve">17.1349239349365</t>
   </si>
   <si>
     <t xml:space="preserve">17.0698318481445</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1674671173096</t>
+    <t xml:space="preserve">17.1674633026123</t>
   </si>
   <si>
     <t xml:space="preserve">17.6637763977051</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2251777648926</t>
+    <t xml:space="preserve">18.2251796722412</t>
   </si>
   <si>
     <t xml:space="preserve">18.8598022460938</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0632133483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7052154541016</t>
+    <t xml:space="preserve">19.06321144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7052135467529</t>
   </si>
   <si>
     <t xml:space="preserve">18.6319885253906</t>
@@ -1085,10 +1085,10 @@
     <t xml:space="preserve">18.7377605438232</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7133483886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5913105010986</t>
+    <t xml:space="preserve">18.7133541107178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.59130859375</t>
   </si>
   <si>
     <t xml:space="preserve">18.3065414428711</t>
@@ -1100,16 +1100,16 @@
     <t xml:space="preserve">18.217041015625</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2089042663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4611301422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5417327880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9071063995361</t>
+    <t xml:space="preserve">18.2089080810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4611263275146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5417308807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9071083068848</t>
   </si>
   <si>
     <t xml:space="preserve">16.4758853912354</t>
@@ -1124,22 +1124,22 @@
     <t xml:space="preserve">16.3619785308838</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2806167602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3782482147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1992568969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2236652374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2724800109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.679292678833</t>
+    <t xml:space="preserve">16.2806186676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3782501220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1992530822754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2236633300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2724781036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6792907714844</t>
   </si>
   <si>
     <t xml:space="preserve">16.313159942627</t>
@@ -1148,166 +1148,166 @@
     <t xml:space="preserve">16.0934829711914</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9470300674438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1911163330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3538417816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.028392791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9144859313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1822233200073</t>
+    <t xml:space="preserve">15.9470319747925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1911182403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3538379669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0283966064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9144840240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.182225227356</t>
   </si>
   <si>
     <t xml:space="preserve">14.9706802368164</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1008625030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.873046875</t>
+    <t xml:space="preserve">15.1008605957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8730478286743</t>
   </si>
   <si>
     <t xml:space="preserve">14.222146987915</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8478803634644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8893175125122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1984968185425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3937673568726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5402202606201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9381351470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5964136123657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4011449813843</t>
+    <t xml:space="preserve">13.8478813171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8893194198608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1984958648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3937664031982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5402173995972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9381380081177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.59641456604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.40114402771</t>
   </si>
   <si>
     <t xml:space="preserve">14.2058744430542</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1082410812378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.059422492981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.912971496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0106039047241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3197813034058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6452302932739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7428693771362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7265958786011</t>
+    <t xml:space="preserve">14.1082391738892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0594244003296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9129705429077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0106048583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3197841644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6452331542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7428665161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7265939712524</t>
   </si>
   <si>
     <t xml:space="preserve">15.2147703170776</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8079566955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8567733764648</t>
+    <t xml:space="preserve">14.807957649231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8567743301392</t>
   </si>
   <si>
     <t xml:space="preserve">14.9544067382812</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7916831970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2709655761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.003228187561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4825067520142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9218635559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9055919647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0194988250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0520458221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2562084197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7354879379272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8168516159058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6215829849243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9307594299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6866722106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7192144393921</t>
+    <t xml:space="preserve">14.7916841506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2709646224976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0032262802124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4825057983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9218654632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.905592918396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0194978713989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0520439147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2562065124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7354898452759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8168506622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.62158203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9307565689087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6866703033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.719217300415</t>
   </si>
   <si>
     <t xml:space="preserve">15.7029418945312</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6703987121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6053094863892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5653495788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9956836700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0291938781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0627031326294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2470064163208</t>
+    <t xml:space="preserve">15.6703977584839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6053085327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5653505325317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9956827163696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0291929244995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0627021789551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2470083236694</t>
   </si>
   <si>
     <t xml:space="preserve">15.2302522659302</t>
@@ -1316,88 +1316,88 @@
     <t xml:space="preserve">15.5318412780762</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7161426544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8669424057007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5821084976196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4983320236206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.481575012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4145565032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1799898147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.07945728302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1129703521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3589944839478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.291974067688</t>
+    <t xml:space="preserve">15.7161464691162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8669404983521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.582106590271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4983310699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4815759658813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4145545959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1799879074097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0794591903687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1129655838013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3589935302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2919731140137</t>
   </si>
   <si>
     <t xml:space="preserve">14.2584657669067</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4595241546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4092597961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5600547790527</t>
+    <t xml:space="preserve">14.4595251083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4092607498169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5600528717041</t>
   </si>
   <si>
     <t xml:space="preserve">13.4039621353149</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4877376556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2364130020142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5380020141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4374732971191</t>
+    <t xml:space="preserve">13.487735748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2364120483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5380029678345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4374723434448</t>
   </si>
   <si>
     <t xml:space="preserve">14.191445350647</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5882663726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.688796043396</t>
+    <t xml:space="preserve">13.5882654190063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6887969970703</t>
   </si>
   <si>
     <t xml:space="preserve">13.4207181930542</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5212459564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5715112686157</t>
+    <t xml:space="preserve">13.5212469100952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5715131759644</t>
   </si>
   <si>
     <t xml:space="preserve">13.3201875686646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1526384353638</t>
+    <t xml:space="preserve">13.1526374816895</t>
   </si>
   <si>
     <t xml:space="preserve">13.186146736145</t>
@@ -1415,46 +1415,46 @@
     <t xml:space="preserve">12.6834993362427</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5662145614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9013137817383</t>
+    <t xml:space="preserve">12.5662155151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.901312828064</t>
   </si>
   <si>
     <t xml:space="preserve">12.8342933654785</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4824390411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1473398208618</t>
+    <t xml:space="preserve">12.482439994812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1473407745361</t>
   </si>
   <si>
     <t xml:space="preserve">12.0803213119507</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0635652542114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9797925949097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5609159469604</t>
+    <t xml:space="preserve">12.0635662078857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9797916412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5609178543091</t>
   </si>
   <si>
     <t xml:space="preserve">11.1923084259033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2258186340332</t>
+    <t xml:space="preserve">11.2258176803589</t>
   </si>
   <si>
     <t xml:space="preserve">12.4321746826172</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1191272735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2531681060791</t>
+    <t xml:space="preserve">13.1191291809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2531671524048</t>
   </si>
   <si>
     <t xml:space="preserve">13.2866773605347</t>
@@ -1463,10 +1463,10 @@
     <t xml:space="preserve">12.7672729492188</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3536968231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9850873947144</t>
+    <t xml:space="preserve">13.3536977767944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9850883483887</t>
   </si>
   <si>
     <t xml:space="preserve">12.8007841110229</t>
@@ -1478,7 +1478,7 @@
     <t xml:space="preserve">12.8678035736084</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8122434616089</t>
+    <t xml:space="preserve">11.8122425079346</t>
   </si>
   <si>
     <t xml:space="preserve">11.6279373168945</t>
@@ -1490,13 +1490,13 @@
     <t xml:space="preserve">11.7284669876099</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9630346298218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.896017074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6614465713501</t>
+    <t xml:space="preserve">11.9630355834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8960161209106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6614475250244</t>
   </si>
   <si>
     <t xml:space="preserve">11.075023651123</t>
@@ -1505,10 +1505,10 @@
     <t xml:space="preserve">11.0415134429932</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9577398300171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7566795349121</t>
+    <t xml:space="preserve">10.9577388763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7566804885864</t>
   </si>
   <si>
     <t xml:space="preserve">10.9242296218872</t>
@@ -1517,16 +1517,16 @@
     <t xml:space="preserve">10.9744939804077</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7117118835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3651552200317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4603891372681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1587982177734</t>
+    <t xml:space="preserve">11.7117109298706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3651542663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4603872299194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1587991714478</t>
   </si>
   <si>
     <t xml:space="preserve">11.1252889633179</t>
@@ -1535,34 +1535,34 @@
     <t xml:space="preserve">11.1755542755127</t>
   </si>
   <si>
-    <t xml:space="preserve">11.376612663269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2311153411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3986654281616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9295263290405</t>
+    <t xml:space="preserve">11.3766136169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2311172485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3986663818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9295253753662</t>
   </si>
   <si>
     <t xml:space="preserve">11.7954864501953</t>
   </si>
   <si>
-    <t xml:space="preserve">11.87926197052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.197606086731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2478704452515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0133018493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1305847167969</t>
+    <t xml:space="preserve">11.8792610168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1976051330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2478713989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0133008956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1305856704712</t>
   </si>
   <si>
     <t xml:space="preserve">12.1808500289917</t>
@@ -1574,58 +1574,58 @@
     <t xml:space="preserve">12.3316459655762</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4656858444214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5997247695923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7170095443726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8845586776733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9515781402588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9683332443237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.20290184021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7337646484375</t>
+    <t xml:space="preserve">12.4656848907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.599723815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7170104980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8845596313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9515790939331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.968334197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2029037475586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7337636947632</t>
   </si>
   <si>
     <t xml:space="preserve">12.8175392150879</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6499891281128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7002553939819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5159502029419</t>
+    <t xml:space="preserve">12.6499910354614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7002544403076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5159482955933</t>
   </si>
   <si>
     <t xml:space="preserve">12.784029006958</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0018424987793</t>
+    <t xml:space="preserve">13.0018434524536</t>
   </si>
   <si>
     <t xml:space="preserve">13.0353536605835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5494585037231</t>
+    <t xml:space="preserve">12.5494604110718</t>
   </si>
   <si>
     <t xml:space="preserve">12.9348230361938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9180698394775</t>
+    <t xml:space="preserve">12.9180679321289</t>
   </si>
   <si>
     <t xml:space="preserve">13.3872060775757</t>
@@ -1634,28 +1634,28 @@
     <t xml:space="preserve">13.6217775344849</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8228349685669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5044927597046</t>
+    <t xml:space="preserve">13.8228359222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5044918060303</t>
   </si>
   <si>
     <t xml:space="preserve">13.4542264938354</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6385326385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7223062515259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3704528808594</t>
+    <t xml:space="preserve">13.6385316848755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7223052978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3704538345337</t>
   </si>
   <si>
     <t xml:space="preserve">13.0521087646484</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0185995101929</t>
+    <t xml:space="preserve">13.0185976028442</t>
   </si>
   <si>
     <t xml:space="preserve">13.1693925857544</t>
@@ -1670,25 +1670,25 @@
     <t xml:space="preserve">12.7481775283813</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5740203857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3650350570679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2257099151611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2779588699341</t>
+    <t xml:space="preserve">12.5740213394165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3650341033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2257108688354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2779579162598</t>
   </si>
   <si>
     <t xml:space="preserve">12.3127889633179</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2953720092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3302040100098</t>
+    <t xml:space="preserve">12.295373916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3302030563354</t>
   </si>
   <si>
     <t xml:space="preserve">12.1212177276611</t>
@@ -1697,7 +1697,7 @@
     <t xml:space="preserve">12.5217752456665</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4869441986084</t>
+    <t xml:space="preserve">12.4869432449341</t>
   </si>
   <si>
     <t xml:space="preserve">12.4521131515503</t>
@@ -1712,31 +1712,31 @@
     <t xml:space="preserve">11.894814491272</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2082958221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8178396224976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7655916213989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.643684387207</t>
+    <t xml:space="preserve">12.2082948684692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8178386688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7655925750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6436834335327</t>
   </si>
   <si>
     <t xml:space="preserve">12.399866104126</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6262674331665</t>
+    <t xml:space="preserve">12.6262683868408</t>
   </si>
   <si>
     <t xml:space="preserve">12.5391902923584</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8700866699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9745779037476</t>
+    <t xml:space="preserve">12.8700857162476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9745788574219</t>
   </si>
   <si>
     <t xml:space="preserve">12.95716381073</t>
@@ -1748,16 +1748,16 @@
     <t xml:space="preserve">12.7830085754395</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6959295272827</t>
+    <t xml:space="preserve">12.695930480957</t>
   </si>
   <si>
     <t xml:space="preserve">12.800422668457</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8875007629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1560487747192</t>
+    <t xml:space="preserve">12.8875017166138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1560478210449</t>
   </si>
   <si>
     <t xml:space="preserve">12.0341396331787</t>
@@ -1766,10 +1766,10 @@
     <t xml:space="preserve">11.7206602096558</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2431259155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7554912567139</t>
+    <t xml:space="preserve">12.2431268692017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7554903030396</t>
   </si>
   <si>
     <t xml:space="preserve">11.6684131622314</t>
@@ -1781,7 +1781,7 @@
     <t xml:space="preserve">12.0689706802368</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1038007736206</t>
+    <t xml:space="preserve">12.1038017272949</t>
   </si>
   <si>
     <t xml:space="preserve">11.790322303772</t>
@@ -1790,25 +1790,25 @@
     <t xml:space="preserve">11.842568397522</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9470624923706</t>
+    <t xml:space="preserve">11.9470615386963</t>
   </si>
   <si>
     <t xml:space="preserve">11.8251533508301</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8599834442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7729063034058</t>
+    <t xml:space="preserve">11.8599853515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7729072570801</t>
   </si>
   <si>
     <t xml:space="preserve">11.8774003982544</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6509971618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5465049743652</t>
+    <t xml:space="preserve">11.6509981155396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5465059280396</t>
   </si>
   <si>
     <t xml:space="preserve">11.3201026916504</t>
@@ -1817,7 +1817,7 @@
     <t xml:space="preserve">11.2156095504761</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4071807861328</t>
+    <t xml:space="preserve">11.4071798324585</t>
   </si>
   <si>
     <t xml:space="preserve">11.3026857376099</t>
@@ -1826,16 +1826,16 @@
     <t xml:space="preserve">11.3549337387085</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3897638320923</t>
+    <t xml:space="preserve">11.3897647857666</t>
   </si>
   <si>
     <t xml:space="preserve">11.1981935501099</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9369602203369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0414543151855</t>
+    <t xml:space="preserve">10.9369611740112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0414533615112</t>
   </si>
   <si>
     <t xml:space="preserve">10.8847141265869</t>
@@ -1847,40 +1847,40 @@
     <t xml:space="preserve">10.9717922210693</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8324670791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6234817504883</t>
+    <t xml:space="preserve">10.832465171814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6234798431396</t>
   </si>
   <si>
     <t xml:space="preserve">10.6060657501221</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5886487960815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5189867019653</t>
+    <t xml:space="preserve">10.5886497497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5189876556396</t>
   </si>
   <si>
     <t xml:space="preserve">10.4493265151978</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6583118438721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7802200317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1633634567261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1111154556274</t>
+    <t xml:space="preserve">10.6583127975464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7802209854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1633615493774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1111173629761</t>
   </si>
   <si>
     <t xml:space="preserve">11.0588684082031</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9892072677612</t>
+    <t xml:space="preserve">10.9892063140869</t>
   </si>
   <si>
     <t xml:space="preserve">10.8498821258545</t>
@@ -1889,7 +1889,7 @@
     <t xml:space="preserve">11.0240383148193</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0066242218018</t>
+    <t xml:space="preserve">11.0066223144531</t>
   </si>
   <si>
     <t xml:space="preserve">10.7976360321045</t>
@@ -1898,22 +1898,22 @@
     <t xml:space="preserve">10.8150520324707</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9543752670288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0937004089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7032432556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9818925857544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9296464920044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9122323989868</t>
+    <t xml:space="preserve">10.9543762207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0937013626099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7032442092896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9818935394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9296455383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9122304916382</t>
   </si>
   <si>
     <t xml:space="preserve">11.8077383041382</t>
@@ -1925,19 +1925,19 @@
     <t xml:space="preserve">12.086386680603</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9644765853882</t>
+    <t xml:space="preserve">11.9644775390625</t>
   </si>
   <si>
     <t xml:space="preserve">11.529088973999</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4942579269409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5813360214233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.476842880249</t>
+    <t xml:space="preserve">11.4942569732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.581335067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4768419265747</t>
   </si>
   <si>
     <t xml:space="preserve">11.6858291625977</t>
@@ -1946,10 +1946,10 @@
     <t xml:space="preserve">12.1908798217773</t>
   </si>
   <si>
-    <t xml:space="preserve">12.347620010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5116720199585</t>
+    <t xml:space="preserve">12.3476190567017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5116729736328</t>
   </si>
   <si>
     <t xml:space="preserve">11.5987510681152</t>
@@ -1958,10 +1958,10 @@
     <t xml:space="preserve">10.7105588912964</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70045852661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49146938323975</t>
+    <t xml:space="preserve">9.70045757293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49147129058838</t>
   </si>
   <si>
     <t xml:space="preserve">9.03866672515869</t>
@@ -1979,70 +1979,70 @@
     <t xml:space="preserve">8.22884368896484</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45524501800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53361511230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49007701873779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31592178344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32462978363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16788864135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38558483123779</t>
+    <t xml:space="preserve">8.45524597167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.533616065979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49007606506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31592082977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32462882995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16788959503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38558387756348</t>
   </si>
   <si>
     <t xml:space="preserve">8.28979778289795</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41170692443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49878406524658</t>
+    <t xml:space="preserve">8.41170787811279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4987850189209</t>
   </si>
   <si>
     <t xml:space="preserve">8.63810920715332</t>
   </si>
   <si>
-    <t xml:space="preserve">8.690354347229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67294120788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79485034942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96900463104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75131034851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70777034759521</t>
+    <t xml:space="preserve">8.69035530090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67294025421143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79484844207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96900367736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75130844116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70777130126953</t>
   </si>
   <si>
     <t xml:space="preserve">8.83838748931885</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1866979598999</t>
+    <t xml:space="preserve">9.18669700622559</t>
   </si>
   <si>
     <t xml:space="preserve">9.05608177185059</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14315891265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23023700714111</t>
+    <t xml:space="preserve">9.14315986633301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2302360534668</t>
   </si>
   <si>
     <t xml:space="preserve">9.40439224243164</t>
@@ -2051,7 +2051,7 @@
     <t xml:space="preserve">9.66562557220459</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57854843139648</t>
+    <t xml:space="preserve">9.5785493850708</t>
   </si>
   <si>
     <t xml:space="preserve">9.31731510162354</t>
@@ -2066,10 +2066,10 @@
     <t xml:space="preserve">8.51620006561279</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60327911376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56844615936279</t>
+    <t xml:space="preserve">8.60327816009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56844711303711</t>
   </si>
   <si>
     <t xml:space="preserve">9.36085319519043</t>
@@ -2078,34 +2078,34 @@
     <t xml:space="preserve">9.83978176116943</t>
   </si>
   <si>
-    <t xml:space="preserve">10.01393699646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1010150909424</t>
+    <t xml:space="preserve">10.0139379501343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1010141372681</t>
   </si>
   <si>
     <t xml:space="preserve">9.92685890197754</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88332176208496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0574750900269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97039794921875</t>
+    <t xml:space="preserve">9.88332080841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0574760437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97039890289307</t>
   </si>
   <si>
     <t xml:space="preserve">9.70916366577148</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75270366668701</t>
+    <t xml:space="preserve">9.75270462036133</t>
   </si>
   <si>
     <t xml:space="preserve">9.6220874786377</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53500938415527</t>
+    <t xml:space="preserve">9.53501033782959</t>
   </si>
   <si>
     <t xml:space="preserve">9.79624271392822</t>
@@ -2114,31 +2114,31 @@
     <t xml:space="preserve">10.1880922317505</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2751693725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5364036560059</t>
+    <t xml:space="preserve">10.2751703262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5364027023315</t>
   </si>
   <si>
     <t xml:space="preserve">10.9282531738281</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0153284072876</t>
+    <t xml:space="preserve">11.0153293609619</t>
   </si>
   <si>
     <t xml:space="preserve">10.7540979385376</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4928636550903</t>
+    <t xml:space="preserve">10.4928646087646</t>
   </si>
   <si>
     <t xml:space="preserve">10.4057865142822</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3622465133667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3187084197998</t>
+    <t xml:space="preserve">10.362247467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3187093734741</t>
   </si>
   <si>
     <t xml:space="preserve">11.1894865036011</t>
@@ -2147,10 +2147,10 @@
     <t xml:space="preserve">11.2765636444092</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4507188796997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0167236328125</t>
+    <t xml:space="preserve">11.4507179260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0167245864868</t>
   </si>
   <si>
     <t xml:space="preserve">12.0602626800537</t>
@@ -2162,7 +2162,7 @@
     <t xml:space="preserve">12.0100746154785</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8314867019653</t>
+    <t xml:space="preserve">11.831485748291</t>
   </si>
   <si>
     <t xml:space="preserve">11.6975450515747</t>
@@ -2171,7 +2171,7 @@
     <t xml:space="preserve">11.4743099212646</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2064275741577</t>
+    <t xml:space="preserve">11.2064266204834</t>
   </si>
   <si>
     <t xml:space="preserve">11.4296617507935</t>
@@ -2180,19 +2180,19 @@
     <t xml:space="preserve">11.608250617981</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2510738372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5813665390015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5367193222046</t>
+    <t xml:space="preserve">11.2510747909546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5813674926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5367202758789</t>
   </si>
   <si>
     <t xml:space="preserve">11.0278387069702</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8938970565796</t>
+    <t xml:space="preserve">10.8938961029053</t>
   </si>
   <si>
     <t xml:space="preserve">11.1617794036865</t>
@@ -2201,22 +2201,22 @@
     <t xml:space="preserve">11.0724849700928</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9207820892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.188663482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2333106994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3226041793823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2779579162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8761339187622</t>
+    <t xml:space="preserve">11.9207801818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1886615753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2333097457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3226051330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2779569625854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8761329650879</t>
   </si>
   <si>
     <t xml:space="preserve">12.1440162658691</t>
@@ -2231,37 +2231,37 @@
     <t xml:space="preserve">13.4387826919556</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4834289550781</t>
+    <t xml:space="preserve">13.4834308624268</t>
   </si>
   <si>
     <t xml:space="preserve">13.9299011230469</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8406057357788</t>
+    <t xml:space="preserve">13.8406066894531</t>
   </si>
   <si>
     <t xml:space="preserve">14.0191946029663</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9030179977417</t>
+    <t xml:space="preserve">12.9030170440674</t>
   </si>
   <si>
     <t xml:space="preserve">13.0816059112549</t>
   </si>
   <si>
-    <t xml:space="preserve">13.036958694458</t>
+    <t xml:space="preserve">13.0369596481323</t>
   </si>
   <si>
     <t xml:space="preserve">13.7513122558594</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7959585189819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3941345214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9745473861694</t>
+    <t xml:space="preserve">13.7959594726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3941354751587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9745483398438</t>
   </si>
   <si>
     <t xml:space="preserve">13.2601947784424</t>
@@ -2270,16 +2270,16 @@
     <t xml:space="preserve">13.6620178222656</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6173715591431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.88525390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6442537307739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7781953811646</t>
+    <t xml:space="preserve">13.6173706054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8852529525757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6442546844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7781963348389</t>
   </si>
   <si>
     <t xml:space="preserve">14.9121379852295</t>
@@ -2288,7 +2288,7 @@
     <t xml:space="preserve">15.0907258987427</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7335481643677</t>
+    <t xml:space="preserve">14.733549118042</t>
   </si>
   <si>
     <t xml:space="preserve">14.4210195541382</t>
@@ -2297,22 +2297,22 @@
     <t xml:space="preserve">14.5103130340576</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1800203323364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8497285842896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8050813674927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.072961807251</t>
+    <t xml:space="preserve">15.1800193786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8497276306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.805079460144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0729637145996</t>
   </si>
   <si>
     <t xml:space="preserve">16.3854923248291</t>
   </si>
   <si>
-    <t xml:space="preserve">16.921257019043</t>
+    <t xml:space="preserve">16.9212589263916</t>
   </si>
   <si>
     <t xml:space="preserve">17.1891403198242</t>
@@ -2321,10 +2321,10 @@
     <t xml:space="preserve">16.7426700592041</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7249050140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7695541381836</t>
+    <t xml:space="preserve">17.7249069213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.769552230835</t>
   </si>
   <si>
     <t xml:space="preserve">17.8142013549805</t>
@@ -2333,31 +2333,31 @@
     <t xml:space="preserve">17.8588466644287</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0374374389648</t>
+    <t xml:space="preserve">18.0374355316162</t>
   </si>
   <si>
     <t xml:space="preserve">18.12672996521</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3946132659912</t>
+    <t xml:space="preserve">18.3946113586426</t>
   </si>
   <si>
     <t xml:space="preserve">18.5732002258301</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6980247497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3053188323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5909652709961</t>
+    <t xml:space="preserve">16.6980228424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3053169250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5909671783447</t>
   </si>
   <si>
     <t xml:space="preserve">18.2160243988037</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9481430053711</t>
+    <t xml:space="preserve">17.9481391906738</t>
   </si>
   <si>
     <t xml:space="preserve">19.0196723937988</t>
@@ -2366,46 +2366,46 @@
     <t xml:space="preserve">20.1804981231689</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5376739501953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6269683837891</t>
+    <t xml:space="preserve">20.5376758575439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6269702911377</t>
   </si>
   <si>
     <t xml:space="preserve">20.9841461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8055572509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0734386444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0912055969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0019092559814</t>
+    <t xml:space="preserve">20.8055553436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0734405517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0912036895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0019111633301</t>
   </si>
   <si>
     <t xml:space="preserve">19.8233203887939</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2697944641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1982612609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9126148223877</t>
+    <t xml:space="preserve">20.2697925567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1982593536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9126129150391</t>
   </si>
   <si>
     <t xml:space="preserve">19.5554389953613</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6447315216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9303779602051</t>
+    <t xml:space="preserve">19.6447334289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9303760528564</t>
   </si>
   <si>
     <t xml:space="preserve">20.7162628173828</t>
@@ -2414,7 +2414,7 @@
     <t xml:space="preserve">20.4483814239502</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4306163787842</t>
+    <t xml:space="preserve">21.4306182861328</t>
   </si>
   <si>
     <t xml:space="preserve">21.3413219451904</t>
@@ -2429,16 +2429,16 @@
     <t xml:space="preserve">22.0556774139404</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7877941131592</t>
+    <t xml:space="preserve">21.7877922058105</t>
   </si>
   <si>
     <t xml:space="preserve">22.7700309753418</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9147033691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4583892822266</t>
+    <t xml:space="preserve">24.914701461792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4583873748779</t>
   </si>
   <si>
     <t xml:space="preserve">24.0020771026611</t>
@@ -2447,22 +2447,22 @@
     <t xml:space="preserve">23.8195514678955</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5496520996094</t>
+    <t xml:space="preserve">24.549654006958</t>
   </si>
   <si>
     <t xml:space="preserve">25.4622783660889</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8234405517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0933380126953</t>
+    <t xml:space="preserve">24.8234424591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0933399200439</t>
   </si>
   <si>
     <t xml:space="preserve">24.732177734375</t>
   </si>
   <si>
-    <t xml:space="preserve">24.367130279541</t>
+    <t xml:space="preserve">24.3671283721924</t>
   </si>
   <si>
     <t xml:space="preserve">23.9108142852783</t>
@@ -2471,7 +2471,7 @@
     <t xml:space="preserve">23.2719764709473</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6370277404785</t>
+    <t xml:space="preserve">23.6370258331299</t>
   </si>
   <si>
     <t xml:space="preserve">23.5457630157471</t>
@@ -2483,22 +2483,22 @@
     <t xml:space="preserve">23.7282886505127</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1846027374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0059661865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3593482971191</t>
+    <t xml:space="preserve">24.1846008300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0059642791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3593502044678</t>
   </si>
   <si>
     <t xml:space="preserve">22.8156623840332</t>
   </si>
   <si>
-    <t xml:space="preserve">22.268087387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7243995666504</t>
+    <t xml:space="preserve">22.2680854797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7243976593018</t>
   </si>
   <si>
     <t xml:space="preserve">23.4545021057129</t>
@@ -2510,10 +2510,10 @@
     <t xml:space="preserve">23.1807117462158</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9069271087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1768245697021</t>
+    <t xml:space="preserve">22.906925201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1768226623535</t>
   </si>
   <si>
     <t xml:space="preserve">22.5418758392334</t>
@@ -2525,10 +2525,10 @@
     <t xml:space="preserve">22.0855617523193</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5379848480225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7205085754395</t>
+    <t xml:space="preserve">21.5379867553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7205104827881</t>
   </si>
   <si>
     <t xml:space="preserve">21.3554592132568</t>
@@ -2537,10 +2537,10 @@
     <t xml:space="preserve">21.8117733001709</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4467239379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8991470336914</t>
+    <t xml:space="preserve">21.4467220306396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8991451263428</t>
   </si>
   <si>
     <t xml:space="preserve">19.0738945007324</t>
@@ -2549,13 +2549,13 @@
     <t xml:space="preserve">19.8952560424805</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8039970397949</t>
+    <t xml:space="preserve">19.8039951324463</t>
   </si>
   <si>
     <t xml:space="preserve">19.6214694976807</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7127323150635</t>
+    <t xml:space="preserve">19.7127342224121</t>
   </si>
   <si>
     <t xml:space="preserve">21.081672668457</t>
@@ -2564,10 +2564,10 @@
     <t xml:space="preserve">24.6409149169922</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3710155487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.374906539917</t>
+    <t xml:space="preserve">25.3710174560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3749046325684</t>
   </si>
   <si>
     <t xml:space="preserve">25.6448059082031</t>
@@ -2594,22 +2594,22 @@
     <t xml:space="preserve">21.6292476654053</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9904079437256</t>
+    <t xml:space="preserve">20.9904098510742</t>
   </si>
   <si>
     <t xml:space="preserve">21.2641983032227</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1729354858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5340976715088</t>
+    <t xml:space="preserve">21.1729335784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5340957641602</t>
   </si>
   <si>
     <t xml:space="preserve">20.8078842163086</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4428329467773</t>
+    <t xml:space="preserve">20.442834854126</t>
   </si>
   <si>
     <t xml:space="preserve">21.9030361175537</t>
@@ -2624,19 +2624,19 @@
     <t xml:space="preserve">20.1690464019775</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3476810455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1651573181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2525291442871</t>
+    <t xml:space="preserve">19.3476829528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1651554107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2525310516357</t>
   </si>
   <si>
     <t xml:space="preserve">18.6175804138184</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1156349182129</t>
+    <t xml:space="preserve">18.1156368255615</t>
   </si>
   <si>
     <t xml:space="preserve">17.4311676025391</t>
@@ -2657,19 +2657,19 @@
     <t xml:space="preserve">16.7010650634766</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6593227386475</t>
+    <t xml:space="preserve">17.6593246459961</t>
   </si>
   <si>
     <t xml:space="preserve">17.2486400604248</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3437938690186</t>
+    <t xml:space="preserve">18.3437919616699</t>
   </si>
   <si>
     <t xml:space="preserve">18.800106048584</t>
   </si>
   <si>
-    <t xml:space="preserve">19.256420135498</t>
+    <t xml:space="preserve">19.2564182281494</t>
   </si>
   <si>
     <t xml:space="preserve">18.982629776001</t>
@@ -2690,7 +2690,7 @@
     <t xml:space="preserve">21.8574047088623</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3137168884277</t>
+    <t xml:space="preserve">22.3137187957764</t>
   </si>
   <si>
     <t xml:space="preserve">21.9486656188965</t>
@@ -2702,28 +2702,28 @@
     <t xml:space="preserve">21.4923534393311</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4049797058105</t>
+    <t xml:space="preserve">22.4049777984619</t>
   </si>
   <si>
     <t xml:space="preserve">22.678768157959</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5913944244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5001335144043</t>
+    <t xml:space="preserve">23.5913963317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5001316070557</t>
   </si>
   <si>
     <t xml:space="preserve">23.7337303161621</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8271713256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.387809753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2009315490723</t>
+    <t xml:space="preserve">23.827169418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3878116607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2009296417236</t>
   </si>
   <si>
     <t xml:space="preserve">24.6681289672852</t>
@@ -2732,28 +2732,28 @@
     <t xml:space="preserve">24.621410369873</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0607719421387</t>
+    <t xml:space="preserve">24.06077003479</t>
   </si>
   <si>
     <t xml:space="preserve">23.9673309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5001316070557</t>
+    <t xml:space="preserve">23.500129699707</t>
   </si>
   <si>
     <t xml:space="preserve">22.9394912719727</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7058925628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6591739654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5190124511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.425573348999</t>
+    <t xml:space="preserve">22.7058906555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6591720581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5190143585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4255714416504</t>
   </si>
   <si>
     <t xml:space="preserve">23.4534130096436</t>
@@ -2771,7 +2771,7 @@
     <t xml:space="preserve">22.0985317230225</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9116554260254</t>
+    <t xml:space="preserve">21.9116535186768</t>
   </si>
   <si>
     <t xml:space="preserve">21.6780548095703</t>
@@ -2783,7 +2783,7 @@
     <t xml:space="preserve">23.0329303741455</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9862117767334</t>
+    <t xml:space="preserve">22.986213684082</t>
   </si>
   <si>
     <t xml:space="preserve">21.8182144165039</t>
@@ -2792,7 +2792,7 @@
     <t xml:space="preserve">22.1919727325439</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7714939117432</t>
+    <t xml:space="preserve">21.7714920043945</t>
   </si>
   <si>
     <t xml:space="preserve">22.2386913299561</t>
@@ -2804,13 +2804,13 @@
     <t xml:space="preserve">23.31325340271</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7993335723877</t>
+    <t xml:space="preserve">22.7993316650391</t>
   </si>
   <si>
     <t xml:space="preserve">22.3321323394775</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5846138000488</t>
+    <t xml:space="preserve">21.5846157073975</t>
   </si>
   <si>
     <t xml:space="preserve">20.930534362793</t>
@@ -2822,7 +2822,7 @@
     <t xml:space="preserve">20.2764568328857</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9494152069092</t>
+    <t xml:space="preserve">19.9494171142578</t>
   </si>
   <si>
     <t xml:space="preserve">20.4166164398193</t>
@@ -2843,25 +2843,25 @@
     <t xml:space="preserve">19.9026947021484</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8092555999756</t>
+    <t xml:space="preserve">19.8092575073242</t>
   </si>
   <si>
     <t xml:space="preserve">19.5756568908691</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3420562744141</t>
+    <t xml:space="preserve">19.3420581817627</t>
   </si>
   <si>
     <t xml:space="preserve">19.2486171722412</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9215774536133</t>
+    <t xml:space="preserve">18.9215755462646</t>
   </si>
   <si>
     <t xml:space="preserve">18.8281364440918</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5758495330811</t>
+    <t xml:space="preserve">18.5758476257324</t>
   </si>
   <si>
     <t xml:space="preserve">18.5010967254639</t>
@@ -2873,7 +2873,7 @@
     <t xml:space="preserve">19.5289363861084</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5945377349854</t>
+    <t xml:space="preserve">18.5945358276367</t>
   </si>
   <si>
     <t xml:space="preserve">18.3702812194824</t>
@@ -2882,7 +2882,7 @@
     <t xml:space="preserve">18.0525856018066</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9217700958252</t>
+    <t xml:space="preserve">17.9217720031738</t>
   </si>
   <si>
     <t xml:space="preserve">17.7535781860352</t>
@@ -2894,10 +2894,10 @@
     <t xml:space="preserve">17.7348899841309</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4919452667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2303161621094</t>
+    <t xml:space="preserve">17.4919471740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2303142547607</t>
   </si>
   <si>
     <t xml:space="preserve">17.1742496490479</t>
@@ -2912,7 +2912,7 @@
     <t xml:space="preserve">16.4454212188721</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1277236938477</t>
+    <t xml:space="preserve">16.1277256011963</t>
   </si>
   <si>
     <t xml:space="preserve">16.5014839172363</t>
@@ -2924,13 +2924,13 @@
     <t xml:space="preserve">16.0342845916748</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8847808837891</t>
+    <t xml:space="preserve">15.8847818374634</t>
   </si>
   <si>
     <t xml:space="preserve">15.3241405487061</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6044616699219</t>
+    <t xml:space="preserve">15.6044607162476</t>
   </si>
   <si>
     <t xml:space="preserve">15.7352771759033</t>
@@ -2948,7 +2948,7 @@
     <t xml:space="preserve">16.7444267272949</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7257404327393</t>
+    <t xml:space="preserve">16.7257385253906</t>
   </si>
   <si>
     <t xml:space="preserve">16.9313087463379</t>
@@ -2960,7 +2960,7 @@
     <t xml:space="preserve">17.9965229034424</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2581558227539</t>
+    <t xml:space="preserve">18.2581539154053</t>
   </si>
   <si>
     <t xml:space="preserve">17.6601371765137</t>
@@ -2969,10 +2969,10 @@
     <t xml:space="preserve">17.5666980743408</t>
   </si>
   <si>
-    <t xml:space="preserve">17.641450881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3142166137695</t>
+    <t xml:space="preserve">17.6414489746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3142185211182</t>
   </si>
   <si>
     <t xml:space="preserve">18.0712738037109</t>
@@ -3011,7 +3011,7 @@
     <t xml:space="preserve">17.7162017822266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5293216705322</t>
+    <t xml:space="preserve">17.5293235778809</t>
   </si>
   <si>
     <t xml:space="preserve">16.9873714447021</t>
@@ -3023,10 +3023,10 @@
     <t xml:space="preserve">17.5480117797852</t>
   </si>
   <si>
-    <t xml:space="preserve">16.277229309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9221572875977</t>
+    <t xml:space="preserve">16.2772274017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.922158241272</t>
   </si>
   <si>
     <t xml:space="preserve">16.0155963897705</t>
@@ -3035,19 +3035,19 @@
     <t xml:space="preserve">15.9595327377319</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9782218933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0903472900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8287172317505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6231489181519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5857744216919</t>
+    <t xml:space="preserve">15.9782209396362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0903491973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8287162780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6231479644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5857725143433</t>
   </si>
   <si>
     <t xml:space="preserve">16.0716609954834</t>
@@ -3068,10 +3068,10 @@
     <t xml:space="preserve">16.6322994232178</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6136112213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5762348175049</t>
+    <t xml:space="preserve">16.6136131286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5762367248535</t>
   </si>
   <si>
     <t xml:space="preserve">16.3519802093506</t>
@@ -3080,13 +3080,13 @@
     <t xml:space="preserve">16.2024765014648</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7913408279419</t>
+    <t xml:space="preserve">15.7913398742676</t>
   </si>
   <si>
     <t xml:space="preserve">15.7726516723633</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6978998184204</t>
+    <t xml:space="preserve">15.6979007720947</t>
   </si>
   <si>
     <t xml:space="preserve">16.5201721191406</t>
@@ -3095,34 +3095,34 @@
     <t xml:space="preserve">16.1464138031006</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1650981903076</t>
+    <t xml:space="preserve">16.1651000976562</t>
   </si>
   <si>
     <t xml:space="preserve">16.109037399292</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8474044799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7539663314819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8660917282104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6792125701904</t>
+    <t xml:space="preserve">15.8474025726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7539653778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8660936355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6792144775391</t>
   </si>
   <si>
     <t xml:space="preserve">15.8100280761719</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5110206604004</t>
+    <t xml:space="preserve">15.5110216140747</t>
   </si>
   <si>
     <t xml:space="preserve">15.3802042007446</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0064449310303</t>
+    <t xml:space="preserve">15.0064458847046</t>
   </si>
   <si>
     <t xml:space="preserve">14.8008785247803</t>
@@ -3131,7 +3131,7 @@
     <t xml:space="preserve">14.6700620651245</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4271183013916</t>
+    <t xml:space="preserve">14.4271173477173</t>
   </si>
   <si>
     <t xml:space="preserve">14.5766229629517</t>
@@ -3161,13 +3161,13 @@
     <t xml:space="preserve">15.0811967849731</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5670852661133</t>
+    <t xml:space="preserve">15.567084312439</t>
   </si>
   <si>
     <t xml:space="preserve">15.716588973999</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6605253219604</t>
+    <t xml:space="preserve">15.6605262756348</t>
   </si>
   <si>
     <t xml:space="preserve">15.1933259963989</t>
@@ -3176,13 +3176,13 @@
     <t xml:space="preserve">15.3988933563232</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4175806045532</t>
+    <t xml:space="preserve">15.4175815582275</t>
   </si>
   <si>
     <t xml:space="preserve">15.4362697601318</t>
   </si>
   <si>
-    <t xml:space="preserve">15.137261390686</t>
+    <t xml:space="preserve">15.1372623443604</t>
   </si>
   <si>
     <t xml:space="preserve">15.0438222885132</t>
@@ -3194,7 +3194,7 @@
     <t xml:space="preserve">14.9877586364746</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7261257171631</t>
+    <t xml:space="preserve">14.7261266708374</t>
   </si>
   <si>
     <t xml:space="preserve">14.950382232666</t>
@@ -3209,22 +3209,22 @@
     <t xml:space="preserve">14.3149900436401</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5018701553345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4084310531616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1654872894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.202862739563</t>
+    <t xml:space="preserve">14.5018711090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4084300994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1654863357544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2028617858887</t>
   </si>
   <si>
     <t xml:space="preserve">14.2963027954102</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1281099319458</t>
+    <t xml:space="preserve">14.1281108856201</t>
   </si>
   <si>
     <t xml:space="preserve">13.8291034698486</t>
@@ -3239,19 +3239,19 @@
     <t xml:space="preserve">13.4179677963257</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5487833023071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6422233581543</t>
+    <t xml:space="preserve">13.5487842559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6422243118286</t>
   </si>
   <si>
     <t xml:space="preserve">13.45534324646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3992805480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3245277404785</t>
+    <t xml:space="preserve">13.3992795944214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3245286941528</t>
   </si>
   <si>
     <t xml:space="preserve">13.2497758865356</t>
@@ -3260,7 +3260,7 @@
     <t xml:space="preserve">13.0815839767456</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3432149887085</t>
+    <t xml:space="preserve">13.3432159423828</t>
   </si>
   <si>
     <t xml:space="preserve">13.1937122344971</t>
@@ -3269,7 +3269,7 @@
     <t xml:space="preserve">13.3058395385742</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2589263916016</t>
+    <t xml:space="preserve">14.2589273452759</t>
   </si>
   <si>
     <t xml:space="preserve">14.2776145935059</t>
@@ -3278,7 +3278,7 @@
     <t xml:space="preserve">14.7448139190674</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5575466156006</t>
+    <t xml:space="preserve">16.5575485229492</t>
   </si>
   <si>
     <t xml:space="preserve">16.4641094207764</t>
@@ -3287,13 +3287,13 @@
     <t xml:space="preserve">16.4267311096191</t>
   </si>
   <si>
-    <t xml:space="preserve">16.314603805542</t>
+    <t xml:space="preserve">16.3146018981934</t>
   </si>
   <si>
     <t xml:space="preserve">16.2585391998291</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2398529052734</t>
+    <t xml:space="preserve">16.2398509979248</t>
   </si>
   <si>
     <t xml:space="preserve">16.1837882995605</t>
@@ -3302,13 +3302,13 @@
     <t xml:space="preserve">14.8569412231445</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7074375152588</t>
+    <t xml:space="preserve">14.7074384689331</t>
   </si>
   <si>
     <t xml:space="preserve">14.6887502670288</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3897428512573</t>
+    <t xml:space="preserve">14.389741897583</t>
   </si>
   <si>
     <t xml:space="preserve">14.782190322876</t>
@@ -3329,19 +3329,19 @@
     <t xml:space="preserve">12.9881439208984</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5956964492798</t>
+    <t xml:space="preserve">12.5956954956055</t>
   </si>
   <si>
     <t xml:space="preserve">12.7078247070312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7452001571655</t>
+    <t xml:space="preserve">12.7452011108398</t>
   </si>
   <si>
     <t xml:space="preserve">12.4275054931641</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0442085266113</t>
+    <t xml:space="preserve">13.044207572937</t>
   </si>
   <si>
     <t xml:space="preserve">13.3805913925171</t>
@@ -3368,28 +3368,28 @@
     <t xml:space="preserve">13.9972944259644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0159826278687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6513748168945</t>
+    <t xml:space="preserve">14.015983581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6513738632202</t>
   </si>
   <si>
     <t xml:space="preserve">15.0251340866089</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4736442565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.903468132019</t>
+    <t xml:space="preserve">15.4736452102661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9034700393677</t>
   </si>
   <si>
     <t xml:space="preserve">16.482795715332</t>
   </si>
   <si>
-    <t xml:space="preserve">16.912618637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8565578460693</t>
+    <t xml:space="preserve">16.9126205444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8565559387207</t>
   </si>
   <si>
     <t xml:space="preserve">16.9499950408936</t>
@@ -3398,7 +3398,7 @@
     <t xml:space="preserve">16.8752422332764</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0434341430664</t>
+    <t xml:space="preserve">17.043436050415</t>
   </si>
   <si>
     <t xml:space="preserve">15.9969091415405</t>
@@ -3410,7 +3410,7 @@
     <t xml:space="preserve">15.5483961105347</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6418361663818</t>
+    <t xml:space="preserve">15.6418380737305</t>
   </si>
   <si>
     <t xml:space="preserve">16.4080429077148</t>
@@ -3422,13 +3422,13 @@
     <t xml:space="preserve">16.6790199279785</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5855808258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8002967834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7068576812744</t>
+    <t xml:space="preserve">16.585578918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8002986907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.706859588623</t>
   </si>
   <si>
     <t xml:space="preserve">16.211820602417</t>
@@ -3437,19 +3437,19 @@
     <t xml:space="preserve">15.3708620071411</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3052597045898</t>
+    <t xml:space="preserve">16.3052616119385</t>
   </si>
   <si>
     <t xml:space="preserve">16.0249404907227</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1273384094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9404582977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6134185791016</t>
+    <t xml:space="preserve">18.1273365020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9404602050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6134204864502</t>
   </si>
   <si>
     <t xml:space="preserve">17.7070121765137</t>
@@ -68894,7 +68894,7 @@
     </row>
     <row r="2491">
       <c r="A2491" s="1" t="n">
-        <v>45946.5759143519</v>
+        <v>45946.2916666667</v>
       </c>
       <c r="B2491" t="n">
         <v>300</v>
@@ -68915,6 +68915,32 @@
         <v>1267</v>
       </c>
       <c r="H2491" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2492">
+      <c r="A2492" s="1" t="n">
+        <v>45947.6493171296</v>
+      </c>
+      <c r="B2492" t="n">
+        <v>5483</v>
+      </c>
+      <c r="C2492" t="n">
+        <v>14</v>
+      </c>
+      <c r="D2492" t="n">
+        <v>13.8000001907349</v>
+      </c>
+      <c r="E2492" t="n">
+        <v>13.8500003814697</v>
+      </c>
+      <c r="F2492" t="n">
+        <v>14</v>
+      </c>
+      <c r="G2492" t="s">
+        <v>1262</v>
+      </c>
+      <c r="H2492" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SAB.MI.xlsx
+++ b/data/SAB.MI.xlsx
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5656795501709</t>
+    <t xml:space="preserve">8.56568145751953</t>
   </si>
   <si>
     <t xml:space="preserve">SAB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61823081970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48310279846191</t>
+    <t xml:space="preserve">8.61822986602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4831018447876</t>
   </si>
   <si>
     <t xml:space="preserve">8.33295917510986</t>
@@ -56,58 +56,58 @@
     <t xml:space="preserve">8.37049388885498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31794357299805</t>
+    <t xml:space="preserve">8.31794261932373</t>
   </si>
   <si>
     <t xml:space="preserve">8.25788593292236</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16029453277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88252782821655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52969074249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66482067108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62728548049927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61227130889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73989295959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75490760803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76992130279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89754247665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61977815628052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79994916915894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72487783432007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65731382369995</t>
+    <t xml:space="preserve">8.16029167175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88252878189087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52969121932983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66481971740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62728404998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61226940155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73989200592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75490617752075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76992082595825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89754343032837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61977767944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79995012283325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72487592697144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65731334686279</t>
   </si>
   <si>
     <t xml:space="preserve">7.50716972351074</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34201097488403</t>
+    <t xml:space="preserve">7.34201049804688</t>
   </si>
   <si>
     <t xml:space="preserve">7.54470539093018</t>
@@ -119,7 +119,7 @@
     <t xml:space="preserve">7.58224105834961</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8224720954895</t>
+    <t xml:space="preserve">7.82247066497803</t>
   </si>
   <si>
     <t xml:space="preserve">8.08522319793701</t>
@@ -131,109 +131,109 @@
     <t xml:space="preserve">7.95760154724121</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06269931793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03267192840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92006540298462</t>
+    <t xml:space="preserve">8.06269836425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03267097473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92006301879883</t>
   </si>
   <si>
     <t xml:space="preserve">7.77742767333984</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86751270294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80745553970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98762941360474</t>
+    <t xml:space="preserve">7.86751413345337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80745697021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98762989044189</t>
   </si>
   <si>
     <t xml:space="preserve">8.04017925262451</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99513673782349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96510696411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9050498008728</t>
+    <t xml:space="preserve">7.99513578414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96510744094849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90504932403564</t>
   </si>
   <si>
     <t xml:space="preserve">7.93507862091064</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8900351524353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94258499145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82997798919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81496381759644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7323842048645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64980602264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.717369556427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67232751846313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63479042053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51467657089233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64229917526245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56722784042358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70235681533813</t>
+    <t xml:space="preserve">7.89003562927246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94258546829224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82997846603394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81496477127075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73238468170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64980554580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71737146377563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67232894897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63479089736938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51467752456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64230012893677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56722688674927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70235633850098</t>
   </si>
   <si>
     <t xml:space="preserve">7.74739837646484</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46963310241699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69484949111938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49215602874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47338771820068</t>
+    <t xml:space="preserve">7.46963357925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69484996795654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4921555519104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47338628768921</t>
   </si>
   <si>
     <t xml:space="preserve">7.43585157394409</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50341558456421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48089504241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59725475311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4283447265625</t>
+    <t xml:space="preserve">7.50341606140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48089456558228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59725618362427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42834520339966</t>
   </si>
   <si>
     <t xml:space="preserve">7.38705492019653</t>
@@ -245,82 +245,82 @@
     <t xml:space="preserve">7.31949043273926</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28195476531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52122116088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80534029006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7500958442688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75798559188843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81323099136353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8605842590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69879484176636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58435869216919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68695688247681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57646560668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53700733184814</t>
+    <t xml:space="preserve">7.28195381164551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52122211456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80533933639526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75009441375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75798654556274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81323194503784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86058521270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69879579544067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58435821533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68695640563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57646799087524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53700685501099</t>
   </si>
   <si>
     <t xml:space="preserve">7.49754476547241</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28445720672607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92536354064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07926177978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22921228408813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45808458328247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26078128814697</t>
+    <t xml:space="preserve">7.28445672988892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92536401748657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.079261302948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22921133041382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45808362960815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26078033447266</t>
   </si>
   <si>
     <t xml:space="preserve">7.37127065658569</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26472663879395</t>
+    <t xml:space="preserve">7.26472759246826</t>
   </si>
   <si>
     <t xml:space="preserve">7.34759521484375</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46992254257202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36732482910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37916374206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13450574874878</t>
+    <t xml:space="preserve">7.46992301940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36732530593872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37916278839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13450622558594</t>
   </si>
   <si>
     <t xml:space="preserve">7.18975114822388</t>
@@ -329,19 +329,19 @@
     <t xml:space="preserve">7.10293769836426</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15029096603394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10688352584839</t>
+    <t xml:space="preserve">7.15029191970825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10688447952271</t>
   </si>
   <si>
     <t xml:space="preserve">7.20553541183472</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18185997009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2213191986084</t>
+    <t xml:space="preserve">7.18185949325562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22132015228271</t>
   </si>
   <si>
     <t xml:space="preserve">7.19369697570801</t>
@@ -350,67 +350,67 @@
     <t xml:space="preserve">7.24894285202026</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1976432800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1858057975769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22526502609253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20948219299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31602621078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21342849731445</t>
+    <t xml:space="preserve">7.19764375686646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18580484390259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22526597976685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20948123931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31602716445923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21342754364014</t>
   </si>
   <si>
     <t xml:space="preserve">7.16607427597046</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24499654769897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13055992126465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11082983016968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17791414260864</t>
+    <t xml:space="preserve">7.24499607086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13056087493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1108283996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17791318893433</t>
   </si>
   <si>
     <t xml:space="preserve">7.23315858840942</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2765645980835</t>
+    <t xml:space="preserve">7.27656507492065</t>
   </si>
   <si>
     <t xml:space="preserve">7.30024147033691</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29234886169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.241051197052</t>
+    <t xml:space="preserve">7.29234933853149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24105072021484</t>
   </si>
   <si>
     <t xml:space="preserve">7.11872243881226</t>
   </si>
   <si>
-    <t xml:space="preserve">7.095046043396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00428581237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94509506225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93325757980347</t>
+    <t xml:space="preserve">7.09504556655884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00428676605225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9450945854187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93325662612915</t>
   </si>
   <si>
     <t xml:space="preserve">7.09899187088013</t>
@@ -428,82 +428,82 @@
     <t xml:space="preserve">7.05558490753174</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07136917114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06742382049561</t>
+    <t xml:space="preserve">7.07136964797974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06742334365845</t>
   </si>
   <si>
     <t xml:space="preserve">7.02401494979858</t>
   </si>
   <si>
-    <t xml:space="preserve">7.047691822052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06347560882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08320808410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05163955688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04374694824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03190755844116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05953073501587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03585338592529</t>
+    <t xml:space="preserve">7.04769229888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0634765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08320713043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05163908004761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04374599456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03190851211548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05953025817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03585386276245</t>
   </si>
   <si>
     <t xml:space="preserve">7.17396783828735</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90563488006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91352558135986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93720197677612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92141819000244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9411473274231</t>
+    <t xml:space="preserve">6.90563344955444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91352701187134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93720293045044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9214186668396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94114780426025</t>
   </si>
   <si>
     <t xml:space="preserve">6.9687705039978</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14239883422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45019245147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79350185394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92372226715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0499963760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20783805847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16837882995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08945655822754</t>
+    <t xml:space="preserve">7.1423978805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45019149780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7935004234314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9237208366394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04999542236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.207839012146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16837787628174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08945751190186</t>
   </si>
   <si>
     <t xml:space="preserve">8.19994735717773</t>
@@ -518,10 +518,10 @@
     <t xml:space="preserve">8.17626953125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32622241973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55509376525879</t>
+    <t xml:space="preserve">8.32622051239014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55509471893311</t>
   </si>
   <si>
     <t xml:space="preserve">8.56298637390137</t>
@@ -530,43 +530,43 @@
     <t xml:space="preserve">8.42881870269775</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35778903961182</t>
+    <t xml:space="preserve">8.35778999328613</t>
   </si>
   <si>
     <t xml:space="preserve">8.39725112915039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42092704772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44460487365723</t>
+    <t xml:space="preserve">8.42092800140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44460391998291</t>
   </si>
   <si>
     <t xml:space="preserve">8.40514373779297</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26308536529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18416118621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30254554748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22362422943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28676128387451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25519275665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34989738464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3104362487793</t>
+    <t xml:space="preserve">8.26308441162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18416213989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30254650115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22362327575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2867603302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2551908493042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34989833831787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31043529510498</t>
   </si>
   <si>
     <t xml:space="preserve">8.36568260192871</t>
@@ -575,73 +575,73 @@
     <t xml:space="preserve">8.33411312103271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34200572967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46038913726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62612438201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74450492858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88656520843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0049467086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23381805419922</t>
+    <t xml:space="preserve">8.34200477600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46038722991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62612342834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74450397491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88656425476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00494575500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23381900787354</t>
   </si>
   <si>
     <t xml:space="preserve">9.30484771728516</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2653865814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16278839111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19435882568359</t>
+    <t xml:space="preserve">9.26538848876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1627893447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19435787200928</t>
   </si>
   <si>
     <t xml:space="preserve">9.24960327148438</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29695510864258</t>
+    <t xml:space="preserve">9.29695606231689</t>
   </si>
   <si>
     <t xml:space="preserve">9.36798572540283</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54950428009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67577934265137</t>
+    <t xml:space="preserve">9.54950618743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67578029632568</t>
   </si>
   <si>
     <t xml:space="preserve">9.7468090057373</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2203388214111</t>
+    <t xml:space="preserve">10.2203378677368</t>
   </si>
   <si>
     <t xml:space="preserve">10.4807786941528</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4571018218994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2913656234741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2597999572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1493072509766</t>
+    <t xml:space="preserve">10.4571027755737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2913665771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2597980499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1493082046509</t>
   </si>
   <si>
     <t xml:space="preserve">10.0861721038818</t>
@@ -650,22 +650,22 @@
     <t xml:space="preserve">10.0151414871216</t>
   </si>
   <si>
-    <t xml:space="preserve">10.101954460144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1650924682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0546035766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1808767318726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1177396774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1887702941895</t>
+    <t xml:space="preserve">10.1019554138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.165093421936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0546026229858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1808776855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1177387237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1887693405151</t>
   </si>
   <si>
     <t xml:space="preserve">10.070387840271</t>
@@ -674,19 +674,19 @@
     <t xml:space="preserve">10.1098480224609</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0230340957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.496563911438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4176425933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3150444030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7333278656006</t>
+    <t xml:space="preserve">10.0230331420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4965648651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4176416397095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3150434494019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7333288192749</t>
   </si>
   <si>
     <t xml:space="preserve">10.4492101669312</t>
@@ -695,7 +695,7 @@
     <t xml:space="preserve">10.5597009658813</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6386213302612</t>
+    <t xml:space="preserve">10.6386222839355</t>
   </si>
   <si>
     <t xml:space="preserve">10.591269493103</t>
@@ -707,22 +707,22 @@
     <t xml:space="preserve">10.883279800415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3410243988037</t>
+    <t xml:space="preserve">11.3410234451294</t>
   </si>
   <si>
     <t xml:space="preserve">12.0592098236084</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9171504974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0513191223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6882801055908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6803865432739</t>
+    <t xml:space="preserve">11.9171514511108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0513172149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6882781982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6803855895996</t>
   </si>
   <si>
     <t xml:space="preserve">12.2644052505493</t>
@@ -734,19 +734,19 @@
     <t xml:space="preserve">12.5406312942505</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6747961044312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7379350662231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4728546142578</t>
+    <t xml:space="preserve">12.6747970581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7379341125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4728565216064</t>
   </si>
   <si>
     <t xml:space="preserve">12.6518535614014</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8471221923828</t>
+    <t xml:space="preserve">12.8471231460571</t>
   </si>
   <si>
     <t xml:space="preserve">12.8145771026611</t>
@@ -767,22 +767,22 @@
     <t xml:space="preserve">12.6437168121338</t>
   </si>
   <si>
-    <t xml:space="preserve">12.822714805603</t>
+    <t xml:space="preserve">12.8227138519287</t>
   </si>
   <si>
     <t xml:space="preserve">11.5209150314331</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8463649749756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7812738418579</t>
+    <t xml:space="preserve">11.8463659286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7812747955322</t>
   </si>
   <si>
     <t xml:space="preserve">11.9114561080933</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9277267456055</t>
+    <t xml:space="preserve">11.9277276992798</t>
   </si>
   <si>
     <t xml:space="preserve">11.9602727890015</t>
@@ -791,37 +791,37 @@
     <t xml:space="preserve">11.8056840896606</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1311349868774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0009536743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9846801757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0416355133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0823163986206</t>
+    <t xml:space="preserve">12.1311330795288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0009546279907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9846820831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0416345596313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0823154449463</t>
   </si>
   <si>
     <t xml:space="preserve">11.9765453338623</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8789110183716</t>
+    <t xml:space="preserve">11.8789119720459</t>
   </si>
   <si>
     <t xml:space="preserve">11.7161855697632</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4720993041992</t>
+    <t xml:space="preserve">11.4720973968506</t>
   </si>
   <si>
     <t xml:space="preserve">11.5534591674805</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5860052108765</t>
+    <t xml:space="preserve">11.5860071182251</t>
   </si>
   <si>
     <t xml:space="preserve">11.7975482940674</t>
@@ -833,58 +833,58 @@
     <t xml:space="preserve">12.0904531478882</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1636791229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0741786956787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2287683486938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1392688751221</t>
+    <t xml:space="preserve">12.1636781692505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.074179649353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2287693023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1392707824707</t>
   </si>
   <si>
     <t xml:space="preserve">12.2043590545654</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1880874633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.147406578064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2531785964966</t>
+    <t xml:space="preserve">12.1880855560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1474075317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2531776428223</t>
   </si>
   <si>
     <t xml:space="preserve">12.3670845031738</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4077672958374</t>
+    <t xml:space="preserve">12.4077663421631</t>
   </si>
   <si>
     <t xml:space="preserve">12.448447227478</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9447584152222</t>
+    <t xml:space="preserve">12.9447574615479</t>
   </si>
   <si>
     <t xml:space="preserve">12.7820329666138</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8959398269653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0098466873169</t>
+    <t xml:space="preserve">12.8959407806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0098485946655</t>
   </si>
   <si>
     <t xml:space="preserve">12.9528942108154</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8552589416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7332143783569</t>
+    <t xml:space="preserve">12.8552598953247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7332153320312</t>
   </si>
   <si>
     <t xml:space="preserve">12.7738971710205</t>
@@ -893,34 +893,34 @@
     <t xml:space="preserve">12.9854393005371</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2620706558228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.685154914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9292430877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9943342208862</t>
+    <t xml:space="preserve">13.2620697021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6851558685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9292421340942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9943332672119</t>
   </si>
   <si>
     <t xml:space="preserve">13.7502460479736</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8153371810913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8316087722778</t>
+    <t xml:space="preserve">13.8153343200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8316078186035</t>
   </si>
   <si>
     <t xml:space="preserve">14.0187406539917</t>
   </si>
   <si>
-    <t xml:space="preserve">14.026876449585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.181468963623</t>
+    <t xml:space="preserve">14.0268783569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1814651489258</t>
   </si>
   <si>
     <t xml:space="preserve">14.157057762146</t>
@@ -929,34 +929,34 @@
     <t xml:space="preserve">14.2302837371826</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7754096984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3205394744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2961311340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4588556289673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.824987411499</t>
+    <t xml:space="preserve">14.7754106521606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.320538520813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2961301803589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.458854675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8249883651733</t>
   </si>
   <si>
     <t xml:space="preserve">15.7924423217773</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5076732635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8493957519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8656663894653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5158081054688</t>
+    <t xml:space="preserve">15.5076742172241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8493938446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8656692504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5158100128174</t>
   </si>
   <si>
     <t xml:space="preserve">16.0039844512939</t>
@@ -968,22 +968,22 @@
     <t xml:space="preserve">16.776927947998</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9559268951416</t>
+    <t xml:space="preserve">16.9559230804443</t>
   </si>
   <si>
     <t xml:space="preserve">17.4115543365479</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0454216003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0787258148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6475067138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0217704772949</t>
+    <t xml:space="preserve">17.0454254150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0787220001221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6475028991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0217723846436</t>
   </si>
   <si>
     <t xml:space="preserve">18.0543174743652</t>
@@ -992,7 +992,7 @@
     <t xml:space="preserve">18.1275444030762</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2984046936035</t>
+    <t xml:space="preserve">18.2984008789062</t>
   </si>
   <si>
     <t xml:space="preserve">18.4123115539551</t>
@@ -1001,34 +1001,34 @@
     <t xml:space="preserve">18.1682243347168</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1600875854492</t>
+    <t xml:space="preserve">18.1600914001465</t>
   </si>
   <si>
     <t xml:space="preserve">17.9160003662109</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2651023864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0861053466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2976455688477</t>
+    <t xml:space="preserve">17.265100479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0861034393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2976474761963</t>
   </si>
   <si>
     <t xml:space="preserve">17.0047397613525</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1267852783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8745594024658</t>
+    <t xml:space="preserve">17.1267833709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8745613098145</t>
   </si>
   <si>
     <t xml:space="preserve">17.0779666900635</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8664245605469</t>
+    <t xml:space="preserve">16.8664264678955</t>
   </si>
   <si>
     <t xml:space="preserve">16.785062789917</t>
@@ -1043,31 +1043,31 @@
     <t xml:space="preserve">16.9152431488037</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8338813781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9640617370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.882698059082</t>
+    <t xml:space="preserve">16.8338832855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9640598297119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8826999664307</t>
   </si>
   <si>
     <t xml:space="preserve">16.9233779907227</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1349201202393</t>
+    <t xml:space="preserve">17.1349182128906</t>
   </si>
   <si>
     <t xml:space="preserve">17.0698299407959</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1674671173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6637763977051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2251758575439</t>
+    <t xml:space="preserve">17.1674652099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6637744903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2251777648926</t>
   </si>
   <si>
     <t xml:space="preserve">18.859806060791</t>
@@ -1076,28 +1076,28 @@
     <t xml:space="preserve">19.06321144104</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7052135467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6319923400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7377643585205</t>
+    <t xml:space="preserve">18.7052154541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6319885253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7377605438232</t>
   </si>
   <si>
     <t xml:space="preserve">18.7133522033691</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5913066864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3065395355225</t>
+    <t xml:space="preserve">18.59130859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3065414428711</t>
   </si>
   <si>
     <t xml:space="preserve">18.6157169342041</t>
   </si>
   <si>
-    <t xml:space="preserve">18.217041015625</t>
+    <t xml:space="preserve">18.2170429229736</t>
   </si>
   <si>
     <t xml:space="preserve">18.2089023590088</t>
@@ -1106,88 +1106,88 @@
     <t xml:space="preserve">18.4611301422119</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5417346954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9071063995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4758834838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3945236206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1097526550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3619804382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2806167602539</t>
+    <t xml:space="preserve">17.5417327880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9071083068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4758853912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3945217132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1097564697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3619785308838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2806186676025</t>
   </si>
   <si>
     <t xml:space="preserve">16.3782501220703</t>
   </si>
   <si>
-    <t xml:space="preserve">16.199254989624</t>
+    <t xml:space="preserve">16.1992530822754</t>
   </si>
   <si>
     <t xml:space="preserve">16.2236633300781</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2724800109863</t>
+    <t xml:space="preserve">16.272481918335</t>
   </si>
   <si>
     <t xml:space="preserve">16.679292678833</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3131580352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.09348487854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9470329284668</t>
+    <t xml:space="preserve">16.3131618499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0934829711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9470281600952</t>
   </si>
   <si>
     <t xml:space="preserve">16.1911182403564</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3538417816162</t>
+    <t xml:space="preserve">16.3538436889648</t>
   </si>
   <si>
     <t xml:space="preserve">16.028392791748</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9144849777222</t>
+    <t xml:space="preserve">15.9144830703735</t>
   </si>
   <si>
     <t xml:space="preserve">15.182222366333</t>
   </si>
   <si>
-    <t xml:space="preserve">14.970682144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1008625030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.873046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2221460342407</t>
+    <t xml:space="preserve">14.9706802368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1008634567261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8730459213257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.222146987915</t>
   </si>
   <si>
     <t xml:space="preserve">13.8478803634644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8893175125122</t>
+    <t xml:space="preserve">14.8893194198608</t>
   </si>
   <si>
     <t xml:space="preserve">15.1984958648682</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3937654495239</t>
+    <t xml:space="preserve">15.3937664031982</t>
   </si>
   <si>
     <t xml:space="preserve">15.5402202606201</t>
@@ -1196,58 +1196,58 @@
     <t xml:space="preserve">14.938136100769</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5964155197144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4011449813843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2058725357056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1082420349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0594244003296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9129705429077</t>
+    <t xml:space="preserve">14.59641456604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4011468887329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2058744430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1082401275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.059422492981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9129695892334</t>
   </si>
   <si>
     <t xml:space="preserve">14.0106039047241</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3197832107544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6452331542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7428665161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7265958786011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2147703170776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8079566955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8567743301392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9544086456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7916851043701</t>
+    <t xml:space="preserve">14.3197822570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6452322006226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7428693771362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7265930175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.214768409729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.807957649231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8567733764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9544067382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7916860580444</t>
   </si>
   <si>
     <t xml:space="preserve">14.2709655761719</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0032253265381</t>
+    <t xml:space="preserve">15.0032262802124</t>
   </si>
   <si>
     <t xml:space="preserve">14.4825048446655</t>
@@ -1256,13 +1256,13 @@
     <t xml:space="preserve">14.9218654632568</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9055910110474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0194988250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0520448684692</t>
+    <t xml:space="preserve">14.905590057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0194978713989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0520439147949</t>
   </si>
   <si>
     <t xml:space="preserve">16.2562065124512</t>
@@ -1271,115 +1271,115 @@
     <t xml:space="preserve">15.7354879379272</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8168525695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6215791702271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.930757522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6866703033447</t>
+    <t xml:space="preserve">15.8168487548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6215829849243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.930760383606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.686674118042</t>
   </si>
   <si>
     <t xml:space="preserve">15.7192163467407</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7029418945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6703987121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6053113937378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5653486251831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9956817626953</t>
+    <t xml:space="preserve">15.7029399871826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6703968048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6053056716919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5653514862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.995680809021</t>
   </si>
   <si>
     <t xml:space="preserve">15.0291938781738</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0627021789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2470083236694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2302532196045</t>
+    <t xml:space="preserve">15.0627012252808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2470073699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2302522659302</t>
   </si>
   <si>
     <t xml:space="preserve">15.5318431854248</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7161474227905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8669414520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.582106590271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4983320236206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4815759658813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4145574569702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1799869537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0794591903687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1129674911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3589944839478</t>
+    <t xml:space="preserve">15.7161464691162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8669395446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5821075439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.498330116272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4815769195557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4145555496216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.179988861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.07945728302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1129684448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3589954376221</t>
   </si>
   <si>
     <t xml:space="preserve">14.291974067688</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2584638595581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4595260620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4092617034912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5600519180298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4039630889893</t>
+    <t xml:space="preserve">14.2584648132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4595241546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4092588424683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5600528717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4039611816406</t>
   </si>
   <si>
     <t xml:space="preserve">13.4877376556396</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2364120483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5380010604858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4374732971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.191445350647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5882663726807</t>
+    <t xml:space="preserve">13.2364139556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5380020141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4374723434448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1914443969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.588267326355</t>
   </si>
   <si>
     <t xml:space="preserve">13.6887969970703</t>
@@ -1388,19 +1388,19 @@
     <t xml:space="preserve">13.4207172393799</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5212469100952</t>
+    <t xml:space="preserve">13.5212459564209</t>
   </si>
   <si>
     <t xml:space="preserve">13.5715131759644</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3201866149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1526374816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1861486434937</t>
+    <t xml:space="preserve">13.3201875686646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1526384353638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1861476898193</t>
   </si>
   <si>
     <t xml:space="preserve">13.2196578979492</t>
@@ -1409,19 +1409,19 @@
     <t xml:space="preserve">13.3034324645996</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8510494232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6834983825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5662145614624</t>
+    <t xml:space="preserve">12.8510484695435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6834993362427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5662155151367</t>
   </si>
   <si>
     <t xml:space="preserve">12.901312828064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8342933654785</t>
+    <t xml:space="preserve">12.8342943191528</t>
   </si>
   <si>
     <t xml:space="preserve">12.4824390411377</t>
@@ -1442,55 +1442,55 @@
     <t xml:space="preserve">11.5609178543091</t>
   </si>
   <si>
-    <t xml:space="preserve">11.192307472229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2258186340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4321737289429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1191282272339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2531671524048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.286678314209</t>
+    <t xml:space="preserve">11.1923084259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2258176803589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4321746826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1191272735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2531681060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2866773605347</t>
   </si>
   <si>
     <t xml:space="preserve">12.7672739028931</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3536968231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9850873947144</t>
+    <t xml:space="preserve">13.3536977767944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9850883483887</t>
   </si>
   <si>
     <t xml:space="preserve">12.8007841110229</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6332349777222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8678035736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8122425079346</t>
+    <t xml:space="preserve">12.6332340240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8678026199341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8122415542603</t>
   </si>
   <si>
     <t xml:space="preserve">11.6279373168945</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6111831665039</t>
+    <t xml:space="preserve">11.6111812591553</t>
   </si>
   <si>
     <t xml:space="preserve">11.7284669876099</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9630346298218</t>
+    <t xml:space="preserve">11.9630365371704</t>
   </si>
   <si>
     <t xml:space="preserve">11.8960161209106</t>
@@ -1502,13 +1502,13 @@
     <t xml:space="preserve">11.075023651123</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0415134429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9577388763428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7566804885864</t>
+    <t xml:space="preserve">11.0415143966675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9577398300171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7566814422607</t>
   </si>
   <si>
     <t xml:space="preserve">10.9242286682129</t>
@@ -1523,73 +1523,73 @@
     <t xml:space="preserve">12.3651552200317</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4603881835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1587972640991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1252880096436</t>
+    <t xml:space="preserve">11.4603872299194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1587991714478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1252889633179</t>
   </si>
   <si>
     <t xml:space="preserve">11.1755542755127</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3766136169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2311153411865</t>
+    <t xml:space="preserve">11.3766117095947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2311162948608</t>
   </si>
   <si>
     <t xml:space="preserve">12.3986644744873</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9295263290405</t>
+    <t xml:space="preserve">11.9295272827148</t>
   </si>
   <si>
     <t xml:space="preserve">11.7954864501953</t>
   </si>
   <si>
-    <t xml:space="preserve">11.87926197052</t>
+    <t xml:space="preserve">11.8792610168457</t>
   </si>
   <si>
     <t xml:space="preserve">12.197606086731</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2478713989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0133018493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1305856704712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.180850982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3819103240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3316459655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4656848907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5997228622437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7170095443726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8845596313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9515781402588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.968334197998</t>
+    <t xml:space="preserve">12.2478704452515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0132999420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1305847167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1808519363403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3819093704224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3316450119019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4656858444214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5997247695923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7170104980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8845586776733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9515790939331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9683332443237</t>
   </si>
   <si>
     <t xml:space="preserve">13.2029027938843</t>
@@ -1601,31 +1601,31 @@
     <t xml:space="preserve">12.8175392150879</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6499900817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7002534866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5159482955933</t>
+    <t xml:space="preserve">12.6499891281128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7002544403076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5159502029419</t>
   </si>
   <si>
     <t xml:space="preserve">12.784029006958</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0018434524536</t>
+    <t xml:space="preserve">13.0018444061279</t>
   </si>
   <si>
     <t xml:space="preserve">13.0353536605835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5494604110718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9348239898682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9180688858032</t>
+    <t xml:space="preserve">12.5494585037231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9348230361938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9180679321289</t>
   </si>
   <si>
     <t xml:space="preserve">13.38720703125</t>
@@ -1634,28 +1634,28 @@
     <t xml:space="preserve">13.6217765808105</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8228368759155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5044937133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4542255401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6385307312012</t>
+    <t xml:space="preserve">13.8228359222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5044927597046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4542264938354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6385326385498</t>
   </si>
   <si>
     <t xml:space="preserve">13.7223052978516</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3704519271851</t>
+    <t xml:space="preserve">13.3704528808594</t>
   </si>
   <si>
     <t xml:space="preserve">13.0521087646484</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0185985565186</t>
+    <t xml:space="preserve">13.0185976028442</t>
   </si>
   <si>
     <t xml:space="preserve">13.1693925857544</t>
@@ -1667,10 +1667,10 @@
     <t xml:space="preserve">12.499195098877</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7481775283813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5740203857422</t>
+    <t xml:space="preserve">12.7481784820557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5740213394165</t>
   </si>
   <si>
     <t xml:space="preserve">12.3650341033936</t>
@@ -1679,91 +1679,91 @@
     <t xml:space="preserve">12.2257099151611</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2779579162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3127880096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2953729629517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3302030563354</t>
+    <t xml:space="preserve">12.2779569625854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3127889633179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2953720092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3302021026611</t>
   </si>
   <si>
     <t xml:space="preserve">12.1212177276611</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5217733383179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4869441986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4521131515503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1386318206787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0515565872192</t>
+    <t xml:space="preserve">12.5217742919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4869432449341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.452112197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1386337280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0515556335449</t>
   </si>
   <si>
     <t xml:space="preserve">11.8948154449463</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2082958221436</t>
+    <t xml:space="preserve">12.2082948684692</t>
   </si>
   <si>
     <t xml:space="preserve">12.8178396224976</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7655925750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.643684387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3998651504517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6262674331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5391912460327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8700857162476</t>
+    <t xml:space="preserve">12.7655916213989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6436834335327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.399866104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6262683868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5391902923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8700866699219</t>
   </si>
   <si>
     <t xml:space="preserve">12.9745779037476</t>
   </si>
   <si>
-    <t xml:space="preserve">12.95716381073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9397478103638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7830095291138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6959295272827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.800422668457</t>
+    <t xml:space="preserve">12.9571628570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9397468566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7830085754395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.695930480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8004236221313</t>
   </si>
   <si>
     <t xml:space="preserve">12.8875007629395</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1560497283936</t>
+    <t xml:space="preserve">12.1560487747192</t>
   </si>
   <si>
     <t xml:space="preserve">12.0341396331787</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7206602096558</t>
+    <t xml:space="preserve">11.7206592559814</t>
   </si>
   <si>
     <t xml:space="preserve">12.2431268692017</t>
@@ -1772,10 +1772,10 @@
     <t xml:space="preserve">11.7554912567139</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6684131622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9993076324463</t>
+    <t xml:space="preserve">11.6684122085571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9993095397949</t>
   </si>
   <si>
     <t xml:space="preserve">12.0689706802368</t>
@@ -1787,10 +1787,10 @@
     <t xml:space="preserve">11.790322303772</t>
   </si>
   <si>
-    <t xml:space="preserve">11.842568397522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9470615386963</t>
+    <t xml:space="preserve">11.8425693511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9470624923706</t>
   </si>
   <si>
     <t xml:space="preserve">11.8251533508301</t>
@@ -1799,19 +1799,19 @@
     <t xml:space="preserve">11.8599834442139</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7729072570801</t>
+    <t xml:space="preserve">11.7729063034058</t>
   </si>
   <si>
     <t xml:space="preserve">11.8774003982544</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6509981155396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5465049743652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3201036453247</t>
+    <t xml:space="preserve">11.6509971618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5465040206909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3201026916504</t>
   </si>
   <si>
     <t xml:space="preserve">11.2156095504761</t>
@@ -1823,37 +1823,37 @@
     <t xml:space="preserve">11.3026857376099</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3549327850342</t>
+    <t xml:space="preserve">11.3549337387085</t>
   </si>
   <si>
     <t xml:space="preserve">11.3897647857666</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1981925964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9369602203369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0414543151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8847150802612</t>
+    <t xml:space="preserve">11.1981935501099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9369611740112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0414533615112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8847141265869</t>
   </si>
   <si>
     <t xml:space="preserve">10.8672971725464</t>
   </si>
   <si>
-    <t xml:space="preserve">10.971791267395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8324670791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6234798431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6060657501221</t>
+    <t xml:space="preserve">10.9717922210693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8324661254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.623480796814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6060647964478</t>
   </si>
   <si>
     <t xml:space="preserve">10.5886497497559</t>
@@ -1862,7 +1862,7 @@
     <t xml:space="preserve">10.5189876556396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4493246078491</t>
+    <t xml:space="preserve">10.4493255615234</t>
   </si>
   <si>
     <t xml:space="preserve">10.6583118438721</t>
@@ -1871,25 +1871,25 @@
     <t xml:space="preserve">10.7802209854126</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1633625030518</t>
+    <t xml:space="preserve">11.1633615493774</t>
   </si>
   <si>
     <t xml:space="preserve">11.1111154556274</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0588693618774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9892072677612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8498821258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.024037361145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0066232681274</t>
+    <t xml:space="preserve">11.0588684082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9892063140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8498830795288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0240383148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0066223144531</t>
   </si>
   <si>
     <t xml:space="preserve">10.7976360321045</t>
@@ -1907,13 +1907,13 @@
     <t xml:space="preserve">11.7032442092896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.981894493103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9296464920044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9122304916382</t>
+    <t xml:space="preserve">11.9818925857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9296455383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9122314453125</t>
   </si>
   <si>
     <t xml:space="preserve">11.8077383041382</t>
@@ -1922,16 +1922,16 @@
     <t xml:space="preserve">12.2605419158936</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0863857269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9644765853882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5290880203247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4942588806152</t>
+    <t xml:space="preserve">12.086386680603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9644775390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.529088973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4942579269409</t>
   </si>
   <si>
     <t xml:space="preserve">11.5813360214233</t>
@@ -1943,7 +1943,7 @@
     <t xml:space="preserve">11.6858291625977</t>
   </si>
   <si>
-    <t xml:space="preserve">12.190878868103</t>
+    <t xml:space="preserve">12.1908798217773</t>
   </si>
   <si>
     <t xml:space="preserve">12.347620010376</t>
@@ -1955,10 +1955,10 @@
     <t xml:space="preserve">11.5987501144409</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7105579376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70045757293701</t>
+    <t xml:space="preserve">10.7105588912964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7004566192627</t>
   </si>
   <si>
     <t xml:space="preserve">9.49146938323975</t>
@@ -1970,10 +1970,10 @@
     <t xml:space="preserve">8.98641967773438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42912197113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18530559539795</t>
+    <t xml:space="preserve">8.42912292480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18530464172363</t>
   </si>
   <si>
     <t xml:space="preserve">8.22884368896484</t>
@@ -1982,16 +1982,16 @@
     <t xml:space="preserve">8.45524501800537</t>
   </si>
   <si>
-    <t xml:space="preserve">8.533616065979</t>
+    <t xml:space="preserve">8.53361511230469</t>
   </si>
   <si>
     <t xml:space="preserve">8.49007701873779</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31592178344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32462882995605</t>
+    <t xml:space="preserve">8.31592273712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32462978363037</t>
   </si>
   <si>
     <t xml:space="preserve">8.16788959503174</t>
@@ -2003,7 +2003,7 @@
     <t xml:space="preserve">8.28979778289795</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41170787811279</t>
+    <t xml:space="preserve">8.41170597076416</t>
   </si>
   <si>
     <t xml:space="preserve">8.4987850189209</t>
@@ -2012,19 +2012,19 @@
     <t xml:space="preserve">8.63810920715332</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69035530090332</t>
+    <t xml:space="preserve">8.69035625457764</t>
   </si>
   <si>
     <t xml:space="preserve">8.67294025421143</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79484844207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96900463104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75130939483643</t>
+    <t xml:space="preserve">8.79484939575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96900367736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75131034851074</t>
   </si>
   <si>
     <t xml:space="preserve">8.70777130126953</t>
@@ -2033,19 +2033,19 @@
     <t xml:space="preserve">8.83838748931885</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1866979598999</t>
+    <t xml:space="preserve">9.18669986724854</t>
   </si>
   <si>
     <t xml:space="preserve">9.05608177185059</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14316082000732</t>
+    <t xml:space="preserve">9.14315891265869</t>
   </si>
   <si>
     <t xml:space="preserve">9.23023796081543</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40439224243164</t>
+    <t xml:space="preserve">9.40439319610596</t>
   </si>
   <si>
     <t xml:space="preserve">9.66562652587891</t>
@@ -2054,10 +2054,10 @@
     <t xml:space="preserve">9.57854747772217</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31731510162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88192653656006</t>
+    <t xml:space="preserve">9.31731414794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88192558288574</t>
   </si>
   <si>
     <t xml:space="preserve">8.65552425384521</t>
@@ -2066,7 +2066,7 @@
     <t xml:space="preserve">8.51620006561279</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6032772064209</t>
+    <t xml:space="preserve">8.60327911376953</t>
   </si>
   <si>
     <t xml:space="preserve">8.56844711303711</t>
@@ -2075,10 +2075,10 @@
     <t xml:space="preserve">9.36085414886475</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83978176116943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0139360427856</t>
+    <t xml:space="preserve">9.83978080749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.01393699646</t>
   </si>
   <si>
     <t xml:space="preserve">10.1010150909424</t>
@@ -2090,19 +2090,19 @@
     <t xml:space="preserve">9.88332080841064</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0574769973755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97039890289307</t>
+    <t xml:space="preserve">10.0574760437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97039794921875</t>
   </si>
   <si>
     <t xml:space="preserve">9.7091646194458</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75270366668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6220874786377</t>
+    <t xml:space="preserve">9.7527027130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62208652496338</t>
   </si>
   <si>
     <t xml:space="preserve">9.53500938415527</t>
@@ -2114,16 +2114,16 @@
     <t xml:space="preserve">10.1880912780762</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2751693725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5364027023315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9282531738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0153293609619</t>
+    <t xml:space="preserve">10.2751703262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5364046096802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9282522201538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0153303146362</t>
   </si>
   <si>
     <t xml:space="preserve">10.7540979385376</t>
@@ -2132,7 +2132,7 @@
     <t xml:space="preserve">10.4928646087646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4057855606079</t>
+    <t xml:space="preserve">10.4057865142822</t>
   </si>
   <si>
     <t xml:space="preserve">10.362247467041</t>
@@ -2141,34 +2141,34 @@
     <t xml:space="preserve">10.3187084197998</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1894865036011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2765626907349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4507188796997</t>
+    <t xml:space="preserve">11.1894855499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2765636444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.450719833374</t>
   </si>
   <si>
     <t xml:space="preserve">12.0167245864868</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0602617263794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5011940002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0100755691528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8314867019653</t>
+    <t xml:space="preserve">12.060263633728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5011930465698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0100746154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.831485748291</t>
   </si>
   <si>
     <t xml:space="preserve">11.6975450515747</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4743089675903</t>
+    <t xml:space="preserve">11.4743099212646</t>
   </si>
   <si>
     <t xml:space="preserve">11.2064266204834</t>
@@ -2210,28 +2210,28 @@
     <t xml:space="preserve">12.2333097457886</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3226041793823</t>
+    <t xml:space="preserve">12.3226051330566</t>
   </si>
   <si>
     <t xml:space="preserve">11.8761339187622</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1440162658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7868385314941</t>
+    <t xml:space="preserve">12.1440172195435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7868394851685</t>
   </si>
   <si>
     <t xml:space="preserve">12.0993690490723</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4387836456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4834299087524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9299001693726</t>
+    <t xml:space="preserve">13.4387817382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4834308624268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9299011230469</t>
   </si>
   <si>
     <t xml:space="preserve">13.8406057357788</t>
@@ -2243,13 +2243,13 @@
     <t xml:space="preserve">12.9030170440674</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0816040039062</t>
+    <t xml:space="preserve">13.0816049575806</t>
   </si>
   <si>
     <t xml:space="preserve">13.036958694458</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7513113021851</t>
+    <t xml:space="preserve">13.7513122558594</t>
   </si>
   <si>
     <t xml:space="preserve">13.7959594726562</t>
@@ -2258,31 +2258,31 @@
     <t xml:space="preserve">13.3941354751587</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9745464324951</t>
+    <t xml:space="preserve">13.9745473861694</t>
   </si>
   <si>
     <t xml:space="preserve">13.2601947784424</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6620187759399</t>
+    <t xml:space="preserve">13.6620178222656</t>
   </si>
   <si>
     <t xml:space="preserve">13.6173715591431</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8852548599243</t>
+    <t xml:space="preserve">13.88525390625</t>
   </si>
   <si>
     <t xml:space="preserve">14.6442546844482</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7781953811646</t>
+    <t xml:space="preserve">14.7781944274902</t>
   </si>
   <si>
     <t xml:space="preserve">14.9121379852295</t>
   </si>
   <si>
-    <t xml:space="preserve">15.090726852417</t>
+    <t xml:space="preserve">15.0907258987427</t>
   </si>
   <si>
     <t xml:space="preserve">14.7335481643677</t>
@@ -2294,10 +2294,10 @@
     <t xml:space="preserve">14.5103130340576</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1800193786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8497285842896</t>
+    <t xml:space="preserve">15.1800203323364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8497276306152</t>
   </si>
   <si>
     <t xml:space="preserve">15.8050813674927</t>
@@ -2318,10 +2318,10 @@
     <t xml:space="preserve">16.7426681518555</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7249050140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7695541381836</t>
+    <t xml:space="preserve">17.7249069213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.769552230835</t>
   </si>
   <si>
     <t xml:space="preserve">17.8142013549805</t>
@@ -2330,13 +2330,13 @@
     <t xml:space="preserve">17.8588466644287</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0374355316162</t>
+    <t xml:space="preserve">18.0374374389648</t>
   </si>
   <si>
     <t xml:space="preserve">18.12672996521</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3946132659912</t>
+    <t xml:space="preserve">18.3946113586426</t>
   </si>
   <si>
     <t xml:space="preserve">18.5732002258301</t>
@@ -2348,13 +2348,13 @@
     <t xml:space="preserve">18.3053188323975</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5909633636475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2160224914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9481430053711</t>
+    <t xml:space="preserve">17.5909671783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2160243988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9481410980225</t>
   </si>
   <si>
     <t xml:space="preserve">19.0196723937988</t>
@@ -2363,10 +2363,10 @@
     <t xml:space="preserve">20.1804981231689</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5376758575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6269702911377</t>
+    <t xml:space="preserve">20.5376739501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6269683837891</t>
   </si>
   <si>
     <t xml:space="preserve">20.9841461181641</t>
@@ -2381,37 +2381,37 @@
     <t xml:space="preserve">20.0912036895752</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0019092559814</t>
+    <t xml:space="preserve">20.0019111633301</t>
   </si>
   <si>
     <t xml:space="preserve">19.8233203887939</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2697906494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1982612609863</t>
+    <t xml:space="preserve">20.2697925567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1982593536377</t>
   </si>
   <si>
     <t xml:space="preserve">19.9126129150391</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5554370880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6447334289551</t>
+    <t xml:space="preserve">19.5554389953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6447315216064</t>
   </si>
   <si>
     <t xml:space="preserve">18.9303779602051</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7162609100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4483776092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4306163787842</t>
+    <t xml:space="preserve">20.7162628173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4483795166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4306182861328</t>
   </si>
   <si>
     <t xml:space="preserve">21.3413219451904</t>
@@ -2435,7 +2435,7 @@
     <t xml:space="preserve">24.914701461792</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4583892822266</t>
+    <t xml:space="preserve">24.4583873748779</t>
   </si>
   <si>
     <t xml:space="preserve">24.0020771026611</t>
@@ -2444,16 +2444,16 @@
     <t xml:space="preserve">23.8195514678955</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5496520996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4622764587402</t>
+    <t xml:space="preserve">24.549654006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4622783660889</t>
   </si>
   <si>
     <t xml:space="preserve">24.8234424591064</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0933380126953</t>
+    <t xml:space="preserve">24.0933399200439</t>
   </si>
   <si>
     <t xml:space="preserve">24.732177734375</t>
@@ -2480,13 +2480,13 @@
     <t xml:space="preserve">23.7282886505127</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1846027374268</t>
+    <t xml:space="preserve">24.1846008300781</t>
   </si>
   <si>
     <t xml:space="preserve">25.0059642791748</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3593482971191</t>
+    <t xml:space="preserve">22.3593502044678</t>
   </si>
   <si>
     <t xml:space="preserve">22.8156623840332</t>
@@ -2498,10 +2498,10 @@
     <t xml:space="preserve">22.7243976593018</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4545001983643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0894508361816</t>
+    <t xml:space="preserve">23.4545021057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.089448928833</t>
   </si>
   <si>
     <t xml:space="preserve">23.1807117462158</t>
@@ -2513,7 +2513,7 @@
     <t xml:space="preserve">22.1768226623535</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5418739318848</t>
+    <t xml:space="preserve">22.5418758392334</t>
   </si>
   <si>
     <t xml:space="preserve">21.9942989349365</t>
@@ -2534,13 +2534,13 @@
     <t xml:space="preserve">21.8117733001709</t>
   </si>
   <si>
-    <t xml:space="preserve">21.446720123291</t>
+    <t xml:space="preserve">21.4467220306396</t>
   </si>
   <si>
     <t xml:space="preserve">20.8991451263428</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0738925933838</t>
+    <t xml:space="preserve">19.0738945007324</t>
   </si>
   <si>
     <t xml:space="preserve">19.8952560424805</t>
@@ -2561,13 +2561,13 @@
     <t xml:space="preserve">24.6409149169922</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3710155487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.374906539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6448040008545</t>
+    <t xml:space="preserve">25.3710174560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3749046325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6448059082031</t>
   </si>
   <si>
     <t xml:space="preserve">25.9185924530029</t>
@@ -2576,13 +2576,13 @@
     <t xml:space="preserve">25.8273296356201</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5535430908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2797565460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3632392883301</t>
+    <t xml:space="preserve">25.5535411834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2797546386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3632373809814</t>
   </si>
   <si>
     <t xml:space="preserve">22.450611114502</t>
@@ -2609,7 +2609,7 @@
     <t xml:space="preserve">20.442834854126</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9030342102051</t>
+    <t xml:space="preserve">21.9030361175537</t>
   </si>
   <si>
     <t xml:space="preserve">22.6331367492676</t>
@@ -2621,25 +2621,25 @@
     <t xml:space="preserve">20.1690464019775</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3476810455322</t>
+    <t xml:space="preserve">19.3476829528809</t>
   </si>
   <si>
     <t xml:space="preserve">19.1651554107666</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2525291442871</t>
+    <t xml:space="preserve">18.2525310516357</t>
   </si>
   <si>
     <t xml:space="preserve">18.6175804138184</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1156349182129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4311656951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5224304199219</t>
+    <t xml:space="preserve">18.1156368255615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4311676025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5224285125732</t>
   </si>
   <si>
     <t xml:space="preserve">16.2447509765625</t>
@@ -2657,7 +2657,7 @@
     <t xml:space="preserve">17.6593246459961</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2486419677734</t>
+    <t xml:space="preserve">17.2486400604248</t>
   </si>
   <si>
     <t xml:space="preserve">18.3437919616699</t>
@@ -2666,13 +2666,13 @@
     <t xml:space="preserve">18.800106048584</t>
   </si>
   <si>
-    <t xml:space="preserve">19.256420135498</t>
+    <t xml:space="preserve">19.2564182281494</t>
   </si>
   <si>
     <t xml:space="preserve">18.982629776001</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5263156890869</t>
+    <t xml:space="preserve">18.5263175964355</t>
   </si>
   <si>
     <t xml:space="preserve">18.4350566864014</t>
@@ -2702,25 +2702,25 @@
     <t xml:space="preserve">22.4049777984619</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6787662506104</t>
+    <t xml:space="preserve">22.678768157959</t>
   </si>
   <si>
     <t xml:space="preserve">23.5913963317871</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5001335144043</t>
+    <t xml:space="preserve">23.5001316070557</t>
   </si>
   <si>
     <t xml:space="preserve">23.7337303161621</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8271713256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.387809753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2009315490723</t>
+    <t xml:space="preserve">23.827169418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3878116607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2009296417236</t>
   </si>
   <si>
     <t xml:space="preserve">24.6681289672852</t>
@@ -2729,28 +2729,28 @@
     <t xml:space="preserve">24.621410369873</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0607719421387</t>
+    <t xml:space="preserve">24.06077003479</t>
   </si>
   <si>
     <t xml:space="preserve">23.9673309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5001316070557</t>
+    <t xml:space="preserve">23.500129699707</t>
   </si>
   <si>
     <t xml:space="preserve">22.9394912719727</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7058925628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6591739654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5190124511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.425573348999</t>
+    <t xml:space="preserve">22.7058906555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6591720581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5190143585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4255714416504</t>
   </si>
   <si>
     <t xml:space="preserve">23.4534130096436</t>
@@ -2768,7 +2768,7 @@
     <t xml:space="preserve">22.0985317230225</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9116554260254</t>
+    <t xml:space="preserve">21.9116535186768</t>
   </si>
   <si>
     <t xml:space="preserve">21.6780548095703</t>
@@ -2780,7 +2780,7 @@
     <t xml:space="preserve">23.0329303741455</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9862117767334</t>
+    <t xml:space="preserve">22.986213684082</t>
   </si>
   <si>
     <t xml:space="preserve">21.8182144165039</t>
@@ -2789,7 +2789,7 @@
     <t xml:space="preserve">22.1919727325439</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7714939117432</t>
+    <t xml:space="preserve">21.7714920043945</t>
   </si>
   <si>
     <t xml:space="preserve">22.2386913299561</t>
@@ -2801,13 +2801,13 @@
     <t xml:space="preserve">23.31325340271</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7993335723877</t>
+    <t xml:space="preserve">22.7993316650391</t>
   </si>
   <si>
     <t xml:space="preserve">22.3321323394775</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5846138000488</t>
+    <t xml:space="preserve">21.5846157073975</t>
   </si>
   <si>
     <t xml:space="preserve">20.930534362793</t>
@@ -2819,7 +2819,7 @@
     <t xml:space="preserve">20.2764568328857</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9494152069092</t>
+    <t xml:space="preserve">19.9494171142578</t>
   </si>
   <si>
     <t xml:space="preserve">20.4166164398193</t>
@@ -2840,25 +2840,25 @@
     <t xml:space="preserve">19.9026947021484</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8092555999756</t>
+    <t xml:space="preserve">19.8092575073242</t>
   </si>
   <si>
     <t xml:space="preserve">19.5756568908691</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3420562744141</t>
+    <t xml:space="preserve">19.3420581817627</t>
   </si>
   <si>
     <t xml:space="preserve">19.2486171722412</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9215774536133</t>
+    <t xml:space="preserve">18.9215755462646</t>
   </si>
   <si>
     <t xml:space="preserve">18.8281364440918</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5758495330811</t>
+    <t xml:space="preserve">18.5758476257324</t>
   </si>
   <si>
     <t xml:space="preserve">18.5010967254639</t>
@@ -2870,7 +2870,7 @@
     <t xml:space="preserve">19.5289363861084</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5945377349854</t>
+    <t xml:space="preserve">18.5945358276367</t>
   </si>
   <si>
     <t xml:space="preserve">18.3702812194824</t>
@@ -2879,7 +2879,7 @@
     <t xml:space="preserve">18.0525856018066</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9217700958252</t>
+    <t xml:space="preserve">17.9217720031738</t>
   </si>
   <si>
     <t xml:space="preserve">17.7535781860352</t>
@@ -2891,10 +2891,10 @@
     <t xml:space="preserve">17.7348899841309</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4919452667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2303161621094</t>
+    <t xml:space="preserve">17.4919471740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2303142547607</t>
   </si>
   <si>
     <t xml:space="preserve">17.1742496490479</t>
@@ -2909,7 +2909,7 @@
     <t xml:space="preserve">16.4454212188721</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1277236938477</t>
+    <t xml:space="preserve">16.1277256011963</t>
   </si>
   <si>
     <t xml:space="preserve">16.5014839172363</t>
@@ -2921,13 +2921,13 @@
     <t xml:space="preserve">16.0342845916748</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8847808837891</t>
+    <t xml:space="preserve">15.8847818374634</t>
   </si>
   <si>
     <t xml:space="preserve">15.3241405487061</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6044616699219</t>
+    <t xml:space="preserve">15.6044607162476</t>
   </si>
   <si>
     <t xml:space="preserve">15.7352771759033</t>
@@ -2945,7 +2945,7 @@
     <t xml:space="preserve">16.7444267272949</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7257404327393</t>
+    <t xml:space="preserve">16.7257385253906</t>
   </si>
   <si>
     <t xml:space="preserve">16.9313087463379</t>
@@ -2957,7 +2957,7 @@
     <t xml:space="preserve">17.9965229034424</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2581558227539</t>
+    <t xml:space="preserve">18.2581539154053</t>
   </si>
   <si>
     <t xml:space="preserve">17.6601371765137</t>
@@ -2966,10 +2966,10 @@
     <t xml:space="preserve">17.5666980743408</t>
   </si>
   <si>
-    <t xml:space="preserve">17.641450881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3142166137695</t>
+    <t xml:space="preserve">17.6414489746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3142185211182</t>
   </si>
   <si>
     <t xml:space="preserve">18.0712738037109</t>
@@ -3008,7 +3008,7 @@
     <t xml:space="preserve">17.7162017822266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5293216705322</t>
+    <t xml:space="preserve">17.5293235778809</t>
   </si>
   <si>
     <t xml:space="preserve">16.9873714447021</t>
@@ -3020,10 +3020,10 @@
     <t xml:space="preserve">17.5480117797852</t>
   </si>
   <si>
-    <t xml:space="preserve">16.277229309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9221572875977</t>
+    <t xml:space="preserve">16.2772274017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.922158241272</t>
   </si>
   <si>
     <t xml:space="preserve">16.0155963897705</t>
@@ -3032,19 +3032,19 @@
     <t xml:space="preserve">15.9595327377319</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9782218933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0903472900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8287172317505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6231489181519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5857744216919</t>
+    <t xml:space="preserve">15.9782209396362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0903491973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8287162780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6231479644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5857725143433</t>
   </si>
   <si>
     <t xml:space="preserve">16.0716609954834</t>
@@ -3065,10 +3065,10 @@
     <t xml:space="preserve">16.6322994232178</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6136112213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5762348175049</t>
+    <t xml:space="preserve">16.6136131286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5762367248535</t>
   </si>
   <si>
     <t xml:space="preserve">16.3519802093506</t>
@@ -3077,13 +3077,13 @@
     <t xml:space="preserve">16.2024765014648</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7913408279419</t>
+    <t xml:space="preserve">15.7913398742676</t>
   </si>
   <si>
     <t xml:space="preserve">15.7726516723633</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6978998184204</t>
+    <t xml:space="preserve">15.6979007720947</t>
   </si>
   <si>
     <t xml:space="preserve">16.5201721191406</t>
@@ -3092,34 +3092,34 @@
     <t xml:space="preserve">16.1464138031006</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1650981903076</t>
+    <t xml:space="preserve">16.1651000976562</t>
   </si>
   <si>
     <t xml:space="preserve">16.109037399292</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8474044799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7539663314819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8660917282104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6792125701904</t>
+    <t xml:space="preserve">15.8474025726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7539653778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8660936355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6792144775391</t>
   </si>
   <si>
     <t xml:space="preserve">15.8100280761719</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5110206604004</t>
+    <t xml:space="preserve">15.5110216140747</t>
   </si>
   <si>
     <t xml:space="preserve">15.3802042007446</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0064449310303</t>
+    <t xml:space="preserve">15.0064458847046</t>
   </si>
   <si>
     <t xml:space="preserve">14.8008785247803</t>
@@ -3128,7 +3128,7 @@
     <t xml:space="preserve">14.6700620651245</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4271183013916</t>
+    <t xml:space="preserve">14.4271173477173</t>
   </si>
   <si>
     <t xml:space="preserve">14.5766229629517</t>
@@ -3158,13 +3158,13 @@
     <t xml:space="preserve">15.0811967849731</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5670852661133</t>
+    <t xml:space="preserve">15.567084312439</t>
   </si>
   <si>
     <t xml:space="preserve">15.716588973999</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6605253219604</t>
+    <t xml:space="preserve">15.6605262756348</t>
   </si>
   <si>
     <t xml:space="preserve">15.1933259963989</t>
@@ -3173,13 +3173,13 @@
     <t xml:space="preserve">15.3988933563232</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4175806045532</t>
+    <t xml:space="preserve">15.4175815582275</t>
   </si>
   <si>
     <t xml:space="preserve">15.4362697601318</t>
   </si>
   <si>
-    <t xml:space="preserve">15.137261390686</t>
+    <t xml:space="preserve">15.1372623443604</t>
   </si>
   <si>
     <t xml:space="preserve">15.0438222885132</t>
@@ -3191,7 +3191,7 @@
     <t xml:space="preserve">14.9877586364746</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7261257171631</t>
+    <t xml:space="preserve">14.7261266708374</t>
   </si>
   <si>
     <t xml:space="preserve">14.950382232666</t>
@@ -3206,22 +3206,22 @@
     <t xml:space="preserve">14.3149900436401</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5018701553345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4084310531616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1654872894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.202862739563</t>
+    <t xml:space="preserve">14.5018711090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4084300994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1654863357544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2028617858887</t>
   </si>
   <si>
     <t xml:space="preserve">14.2963027954102</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1281099319458</t>
+    <t xml:space="preserve">14.1281108856201</t>
   </si>
   <si>
     <t xml:space="preserve">13.8291034698486</t>
@@ -3236,19 +3236,19 @@
     <t xml:space="preserve">13.4179677963257</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5487833023071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6422233581543</t>
+    <t xml:space="preserve">13.5487842559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6422243118286</t>
   </si>
   <si>
     <t xml:space="preserve">13.45534324646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3992805480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3245277404785</t>
+    <t xml:space="preserve">13.3992795944214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3245286941528</t>
   </si>
   <si>
     <t xml:space="preserve">13.2497758865356</t>
@@ -3257,7 +3257,7 @@
     <t xml:space="preserve">13.0815839767456</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3432149887085</t>
+    <t xml:space="preserve">13.3432159423828</t>
   </si>
   <si>
     <t xml:space="preserve">13.1937122344971</t>
@@ -3266,7 +3266,7 @@
     <t xml:space="preserve">13.3058395385742</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2589263916016</t>
+    <t xml:space="preserve">14.2589273452759</t>
   </si>
   <si>
     <t xml:space="preserve">14.2776145935059</t>
@@ -3275,7 +3275,7 @@
     <t xml:space="preserve">14.7448139190674</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5575466156006</t>
+    <t xml:space="preserve">16.5575485229492</t>
   </si>
   <si>
     <t xml:space="preserve">16.4641094207764</t>
@@ -3284,13 +3284,13 @@
     <t xml:space="preserve">16.4267311096191</t>
   </si>
   <si>
-    <t xml:space="preserve">16.314603805542</t>
+    <t xml:space="preserve">16.3146018981934</t>
   </si>
   <si>
     <t xml:space="preserve">16.2585391998291</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2398529052734</t>
+    <t xml:space="preserve">16.2398509979248</t>
   </si>
   <si>
     <t xml:space="preserve">16.1837882995605</t>
@@ -3299,13 +3299,13 @@
     <t xml:space="preserve">14.8569412231445</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7074375152588</t>
+    <t xml:space="preserve">14.7074384689331</t>
   </si>
   <si>
     <t xml:space="preserve">14.6887502670288</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3897428512573</t>
+    <t xml:space="preserve">14.389741897583</t>
   </si>
   <si>
     <t xml:space="preserve">14.782190322876</t>
@@ -3326,19 +3326,19 @@
     <t xml:space="preserve">12.9881439208984</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5956964492798</t>
+    <t xml:space="preserve">12.5956954956055</t>
   </si>
   <si>
     <t xml:space="preserve">12.7078247070312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7452001571655</t>
+    <t xml:space="preserve">12.7452011108398</t>
   </si>
   <si>
     <t xml:space="preserve">12.4275054931641</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0442085266113</t>
+    <t xml:space="preserve">13.044207572937</t>
   </si>
   <si>
     <t xml:space="preserve">13.3805913925171</t>
@@ -3365,28 +3365,28 @@
     <t xml:space="preserve">13.9972944259644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0159826278687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6513748168945</t>
+    <t xml:space="preserve">14.015983581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6513738632202</t>
   </si>
   <si>
     <t xml:space="preserve">15.0251340866089</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4736442565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.903468132019</t>
+    <t xml:space="preserve">15.4736452102661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9034700393677</t>
   </si>
   <si>
     <t xml:space="preserve">16.482795715332</t>
   </si>
   <si>
-    <t xml:space="preserve">16.912618637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8565578460693</t>
+    <t xml:space="preserve">16.9126205444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8565559387207</t>
   </si>
   <si>
     <t xml:space="preserve">16.9499950408936</t>
@@ -3395,7 +3395,7 @@
     <t xml:space="preserve">16.8752422332764</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0434341430664</t>
+    <t xml:space="preserve">17.043436050415</t>
   </si>
   <si>
     <t xml:space="preserve">15.9969091415405</t>
@@ -3407,7 +3407,7 @@
     <t xml:space="preserve">15.5483961105347</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6418361663818</t>
+    <t xml:space="preserve">15.6418380737305</t>
   </si>
   <si>
     <t xml:space="preserve">16.4080429077148</t>
@@ -3419,13 +3419,13 @@
     <t xml:space="preserve">16.6790199279785</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5855808258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8002967834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7068576812744</t>
+    <t xml:space="preserve">16.585578918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8002986907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.706859588623</t>
   </si>
   <si>
     <t xml:space="preserve">16.211820602417</t>
@@ -3434,19 +3434,19 @@
     <t xml:space="preserve">15.3708620071411</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3052597045898</t>
+    <t xml:space="preserve">16.3052616119385</t>
   </si>
   <si>
     <t xml:space="preserve">16.0249404907227</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1273384094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9404582977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6134185791016</t>
+    <t xml:space="preserve">18.1273365020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9404602050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6134204864502</t>
   </si>
   <si>
     <t xml:space="preserve">17.7070121765137</t>
@@ -69047,7 +69047,7 @@
     </row>
     <row r="2497">
       <c r="A2497" s="1" t="n">
-        <v>45954.6495486111</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B2497" t="n">
         <v>5748</v>
@@ -69068,6 +69068,32 @@
         <v>1266</v>
       </c>
       <c r="H2497" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2498">
+      <c r="A2498" s="1" t="n">
+        <v>45957.6925</v>
+      </c>
+      <c r="B2498" t="n">
+        <v>5318</v>
+      </c>
+      <c r="C2498" t="n">
+        <v>14.0500001907349</v>
+      </c>
+      <c r="D2498" t="n">
+        <v>13.8000001907349</v>
+      </c>
+      <c r="E2498" t="n">
+        <v>13.8000001907349</v>
+      </c>
+      <c r="F2498" t="n">
+        <v>13.8999996185303</v>
+      </c>
+      <c r="G2498" t="s">
+        <v>1265</v>
+      </c>
+      <c r="H2498" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SAB.MI.xlsx
+++ b/data/SAB.MI.xlsx
@@ -47,13 +47,13 @@
     <t xml:space="preserve">8.61823081970215</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4831018447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33295726776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37049293518066</t>
+    <t xml:space="preserve">8.48310279846191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33295917510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37049388885498</t>
   </si>
   <si>
     <t xml:space="preserve">8.31794357299805</t>
@@ -71,106 +71,106 @@
     <t xml:space="preserve">7.52969169616699</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66481971740723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62728404998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61226987838745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73989248275757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75490617752075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76992130279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89754438400269</t>
+    <t xml:space="preserve">7.66482162475586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62728452682495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61227178573608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73989105224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75490570068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76992082595825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89754295349121</t>
   </si>
   <si>
     <t xml:space="preserve">7.6197772026062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79994916915894</t>
+    <t xml:space="preserve">7.79995059967041</t>
   </si>
   <si>
     <t xml:space="preserve">7.72487783432007</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65731430053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5071702003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34201240539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54470682144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39080810546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5822434425354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82247114181519</t>
+    <t xml:space="preserve">7.65731287002563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50717067718506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34201145172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54470634460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39080858230591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58224153518677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82247161865234</t>
   </si>
   <si>
     <t xml:space="preserve">8.0852222442627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11524963378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95759868621826</t>
+    <t xml:space="preserve">8.11525058746338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95760107040405</t>
   </si>
   <si>
     <t xml:space="preserve">8.06270027160645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03267097473145</t>
+    <t xml:space="preserve">8.03267192840576</t>
   </si>
   <si>
     <t xml:space="preserve">7.92006397247314</t>
   </si>
   <si>
-    <t xml:space="preserve">7.777428150177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86751317977905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80745697021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98762893676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0401782989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9951343536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96510648727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9050498008728</t>
+    <t xml:space="preserve">7.77742671966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86751508712769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80745649337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98763084411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04017925262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99513578414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96510696411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90504932403564</t>
   </si>
   <si>
     <t xml:space="preserve">7.9350790977478</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89003467559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94258546829224</t>
+    <t xml:space="preserve">7.89003419876099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94258403778076</t>
   </si>
   <si>
     <t xml:space="preserve">7.82997846603394</t>
@@ -182,22 +182,22 @@
     <t xml:space="preserve">7.73238468170166</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64980506896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.717369556427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67232799530029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63479137420654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51467752456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64229726791382</t>
+    <t xml:space="preserve">7.64980554580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71737098693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67232751846313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6347918510437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51467800140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64229822158813</t>
   </si>
   <si>
     <t xml:space="preserve">7.56722736358643</t>
@@ -209,70 +209,70 @@
     <t xml:space="preserve">7.74739980697632</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46963405609131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69484901428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49215507507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47338724136353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43585014343262</t>
+    <t xml:space="preserve">7.46963310241699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69484996795654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49215459823608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47338771820068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43585109710693</t>
   </si>
   <si>
     <t xml:space="preserve">7.50341701507568</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48089456558228</t>
+    <t xml:space="preserve">7.48089504241943</t>
   </si>
   <si>
     <t xml:space="preserve">7.59725570678711</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42834520339966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38705539703369</t>
+    <t xml:space="preserve">7.42834377288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38705492019653</t>
   </si>
   <si>
     <t xml:space="preserve">7.37204027175903</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31949138641357</t>
+    <t xml:space="preserve">7.31949090957642</t>
   </si>
   <si>
     <t xml:space="preserve">7.28195476531982</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52122116088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80534029006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75009441375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7579870223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81323099136353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86058521270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69879484176636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58435964584351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68695688247681</t>
+    <t xml:space="preserve">7.52122211456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80533885955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75009346008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75798749923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81323146820068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86058330535889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69879531860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58435869216919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68695640563965</t>
   </si>
   <si>
     <t xml:space="preserve">7.57646703720093</t>
@@ -281,79 +281,79 @@
     <t xml:space="preserve">7.53700590133667</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49754476547241</t>
+    <t xml:space="preserve">7.49754571914673</t>
   </si>
   <si>
     <t xml:space="preserve">7.28445672988892</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92536401748657</t>
+    <t xml:space="preserve">6.92536354064941</t>
   </si>
   <si>
     <t xml:space="preserve">7.07926225662231</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22921228408813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45808458328247</t>
+    <t xml:space="preserve">7.22921133041382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45808410644531</t>
   </si>
   <si>
     <t xml:space="preserve">7.26078081130981</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37127113342285</t>
+    <t xml:space="preserve">7.37127208709717</t>
   </si>
   <si>
     <t xml:space="preserve">7.26472759246826</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34759521484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4699239730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36732530593872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37916421890259</t>
+    <t xml:space="preserve">7.34759473800659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46992349624634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36732578277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37916374206543</t>
   </si>
   <si>
     <t xml:space="preserve">7.1345067024231</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18975162506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1029372215271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15029144287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10688352584839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20553636550903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18185901641846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22131967544556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19369745254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24894285202026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19764375686646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18580484390259</t>
+    <t xml:space="preserve">7.18975067138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10293817520142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15029048919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10688447952271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20553588867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18186044692993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2213191986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19369697570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24894189834595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1976432800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18580436706543</t>
   </si>
   <si>
     <t xml:space="preserve">7.22526597976685</t>
@@ -362,46 +362,46 @@
     <t xml:space="preserve">7.20948266983032</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31602621078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21342849731445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16607427597046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24499654769897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13055992126465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11082983016968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17791318893433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23315811157227</t>
+    <t xml:space="preserve">7.31602668762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21342897415161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16607475280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24499559402466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13056039810181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11083030700684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17791366577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23315906524658</t>
   </si>
   <si>
     <t xml:space="preserve">7.2765645980835</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30024242401123</t>
+    <t xml:space="preserve">7.3002405166626</t>
   </si>
   <si>
     <t xml:space="preserve">7.29234933853149</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24105024337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1187219619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.095046043396</t>
+    <t xml:space="preserve">7.241051197052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11872243881226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09504508972168</t>
   </si>
   <si>
     <t xml:space="preserve">7.00428581237793</t>
@@ -413,19 +413,19 @@
     <t xml:space="preserve">6.93325614929199</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09899187088013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15423679351807</t>
+    <t xml:space="preserve">7.09899091720581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15423631668091</t>
   </si>
   <si>
     <t xml:space="preserve">7.13845300674438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15818214416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05558490753174</t>
+    <t xml:space="preserve">7.1581826210022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05558443069458</t>
   </si>
   <si>
     <t xml:space="preserve">7.07136869430542</t>
@@ -434,40 +434,40 @@
     <t xml:space="preserve">7.06742286682129</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0240159034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04769325256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0634765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0832085609436</t>
+    <t xml:space="preserve">7.02401638031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04769229888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06347703933716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08320760726929</t>
   </si>
   <si>
     <t xml:space="preserve">7.05163955688477</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04374694824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03190755844116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05953073501587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03585433959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1739673614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90563344955444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91352701187134</t>
+    <t xml:space="preserve">7.04374647140503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03190803527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05953025817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03585481643677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17396688461304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90563440322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91352558135986</t>
   </si>
   <si>
     <t xml:space="preserve">6.93720245361328</t>
@@ -476,28 +476,28 @@
     <t xml:space="preserve">6.9214186668396</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94114828109741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96877193450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1423978805542</t>
+    <t xml:space="preserve">6.94114780426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9687705039978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14239835739136</t>
   </si>
   <si>
     <t xml:space="preserve">7.45019197463989</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79349994659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9237208366394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0499963760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20783805847168</t>
+    <t xml:space="preserve">7.79350137710571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92372226715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04999542236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.207839012146</t>
   </si>
   <si>
     <t xml:space="preserve">8.16837787628174</t>
@@ -506,43 +506,43 @@
     <t xml:space="preserve">8.08945655822754</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19994735717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06578063964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12891674041748</t>
+    <t xml:space="preserve">8.19994640350342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06577968597412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12891864776611</t>
   </si>
   <si>
     <t xml:space="preserve">8.17627048492432</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32622241973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55509471893311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56298542022705</t>
+    <t xml:space="preserve">8.32622146606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55509376525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56298732757568</t>
   </si>
   <si>
     <t xml:space="preserve">8.42881965637207</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35778999328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39725112915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42092895507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44460201263428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40514183044434</t>
+    <t xml:space="preserve">8.35779094696045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39725017547607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42092704772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44460391998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40514278411865</t>
   </si>
   <si>
     <t xml:space="preserve">8.26308441162109</t>
@@ -557,43 +557,43 @@
     <t xml:space="preserve">8.22362327575684</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2867603302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25519371032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34989643096924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3104362487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36568164825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33411407470703</t>
+    <t xml:space="preserve">8.28676128387451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25519180297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34989738464355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31043720245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36568260192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33411502838135</t>
   </si>
   <si>
     <t xml:space="preserve">8.34200572967529</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46038722991943</t>
+    <t xml:space="preserve">8.46038818359375</t>
   </si>
   <si>
     <t xml:space="preserve">8.62612247467041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74450492858887</t>
+    <t xml:space="preserve">8.74450588226318</t>
   </si>
   <si>
     <t xml:space="preserve">8.88656425476074</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00494766235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23381805419922</t>
+    <t xml:space="preserve">9.00494575500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23381900787354</t>
   </si>
   <si>
     <t xml:space="preserve">9.30484867095947</t>
@@ -602,61 +602,61 @@
     <t xml:space="preserve">9.26538753509521</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1627893447876</t>
+    <t xml:space="preserve">9.16279029846191</t>
   </si>
   <si>
     <t xml:space="preserve">9.19435787200928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24960327148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29695510864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36798477172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54950523376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7468090057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2203378677368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4807786941528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4571018218994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2913675308228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2597990036011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1493091583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0861701965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0151424407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1019554138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1650924682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0546035766602</t>
+    <t xml:space="preserve">9.24960422515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29695606231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36798572540283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54950618743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67578029632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74680995941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2203369140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4807796478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4571027755737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2913665771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2597999572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1493082046509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0861711502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0151395797729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1019563674927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.165093421936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0546045303345</t>
   </si>
   <si>
     <t xml:space="preserve">10.1808767318726</t>
@@ -668,13 +668,13 @@
     <t xml:space="preserve">10.1887693405151</t>
   </si>
   <si>
-    <t xml:space="preserve">10.070387840271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1098499298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0230331420898</t>
+    <t xml:space="preserve">10.0703868865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1098489761353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0230340957642</t>
   </si>
   <si>
     <t xml:space="preserve">10.496563911438</t>
@@ -686,124 +686,124 @@
     <t xml:space="preserve">10.3150444030762</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7333288192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4492101669312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.559700012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6386203765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.591269493103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0095529556274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8832788467407</t>
+    <t xml:space="preserve">10.7333278656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4492111206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5597009658813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6386213302612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5912685394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0095520019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.883279800415</t>
   </si>
   <si>
     <t xml:space="preserve">11.3410234451294</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0592088699341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9171504974365</t>
+    <t xml:space="preserve">12.0592098236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9171514511108</t>
   </si>
   <si>
     <t xml:space="preserve">12.0513181686401</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6882801055908</t>
+    <t xml:space="preserve">11.6882791519165</t>
   </si>
   <si>
     <t xml:space="preserve">11.6803865432739</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2644052505493</t>
+    <t xml:space="preserve">12.2644062042236</t>
   </si>
   <si>
     <t xml:space="preserve">12.6274442672729</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5406322479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6747970581055</t>
+    <t xml:space="preserve">12.5406303405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6747961044312</t>
   </si>
   <si>
     <t xml:space="preserve">12.7379350662231</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4728555679321</t>
+    <t xml:space="preserve">12.4728565216064</t>
   </si>
   <si>
     <t xml:space="preserve">12.6518535614014</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8471221923828</t>
+    <t xml:space="preserve">12.8471231460571</t>
   </si>
   <si>
     <t xml:space="preserve">12.8145780563354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9203491210938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8715333938599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.936619758606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8064403533936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6437177658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8227138519287</t>
+    <t xml:space="preserve">12.9203500747681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8715314865112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9366216659546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8064413070679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6437168121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.822714805603</t>
   </si>
   <si>
     <t xml:space="preserve">11.5209159851074</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8463649749756</t>
+    <t xml:space="preserve">11.8463659286499</t>
   </si>
   <si>
     <t xml:space="preserve">11.7812747955322</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9114561080933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9277286529541</t>
+    <t xml:space="preserve">11.9114551544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9277276992798</t>
   </si>
   <si>
     <t xml:space="preserve">11.9602718353271</t>
   </si>
   <si>
-    <t xml:space="preserve">11.805685043335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1311330795288</t>
+    <t xml:space="preserve">11.8056840896606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1311340332031</t>
   </si>
   <si>
     <t xml:space="preserve">12.0009536743164</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9846811294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0416355133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0823163986206</t>
+    <t xml:space="preserve">11.9846801757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0416345596313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0823173522949</t>
   </si>
   <si>
     <t xml:space="preserve">11.9765453338623</t>
@@ -815,22 +815,22 @@
     <t xml:space="preserve">11.7161855697632</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4720983505249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5534601211548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5860061645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7975492477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8951826095581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0904521942139</t>
+    <t xml:space="preserve">11.4720993041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5534591674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5860052108765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7975482940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8951816558838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0904512405396</t>
   </si>
   <si>
     <t xml:space="preserve">12.1636791229248</t>
@@ -839,25 +839,25 @@
     <t xml:space="preserve">12.074179649353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2287693023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1392707824707</t>
+    <t xml:space="preserve">12.2287683486938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.139271736145</t>
   </si>
   <si>
     <t xml:space="preserve">12.2043590545654</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1880865097046</t>
+    <t xml:space="preserve">12.1880874633789</t>
   </si>
   <si>
     <t xml:space="preserve">12.147406578064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2531776428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3670854568481</t>
+    <t xml:space="preserve">12.2531785964966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3670845031738</t>
   </si>
   <si>
     <t xml:space="preserve">12.4077663421631</t>
@@ -866,16 +866,16 @@
     <t xml:space="preserve">12.448447227478</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9447574615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7820329666138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8959398269653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0098476409912</t>
+    <t xml:space="preserve">12.9447584152222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7820320129395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8959407806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0098466873169</t>
   </si>
   <si>
     <t xml:space="preserve">12.9528932571411</t>
@@ -884,10 +884,10 @@
     <t xml:space="preserve">12.8552589416504</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7332153320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7738971710205</t>
+    <t xml:space="preserve">12.7332162857056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7738962173462</t>
   </si>
   <si>
     <t xml:space="preserve">12.9854393005371</t>
@@ -914,19 +914,19 @@
     <t xml:space="preserve">13.8316097259521</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0187425613403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0268793106079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1814680099487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1570558547974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.230281829834</t>
+    <t xml:space="preserve">14.0187406539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.026876449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1814670562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1570568084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2302837371826</t>
   </si>
   <si>
     <t xml:space="preserve">14.7754106521606</t>
@@ -935,37 +935,37 @@
     <t xml:space="preserve">15.3205413818359</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2961320877075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4588556289673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8249883651733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.792441368103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5076723098755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8493938446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.865668296814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5158090591431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0039863586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2643432617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7769298553467</t>
+    <t xml:space="preserve">15.2961311340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4588575363159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.824987411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7924423217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5076732635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8493947982788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8656673431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5158081054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0039825439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2643451690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7769260406494</t>
   </si>
   <si>
     <t xml:space="preserve">16.955924987793</t>
@@ -974,52 +974,52 @@
     <t xml:space="preserve">17.4115524291992</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0454235076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.078727722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6475067138672</t>
+    <t xml:space="preserve">17.0454216003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0787220001221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6475048065186</t>
   </si>
   <si>
     <t xml:space="preserve">18.0217685699463</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0543155670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1275424957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2984027862549</t>
+    <t xml:space="preserve">18.0543174743652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1275444030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2984066009521</t>
   </si>
   <si>
     <t xml:space="preserve">18.4123115539551</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1682243347168</t>
+    <t xml:space="preserve">18.1682224273682</t>
   </si>
   <si>
     <t xml:space="preserve">18.1600875854492</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9160003662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.265100479126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0861053466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2976493835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0047416687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1267852783203</t>
+    <t xml:space="preserve">17.9159984588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2651023864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0861072540283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2976474761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0047397613525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1267833709717</t>
   </si>
   <si>
     <t xml:space="preserve">16.8745613098145</t>
@@ -1028,19 +1028,19 @@
     <t xml:space="preserve">17.0779666900635</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8664226531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7850646972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.988468170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5979309082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9152431488037</t>
+    <t xml:space="preserve">16.8664264678955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.785062789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9884662628174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5979290008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9152450561523</t>
   </si>
   <si>
     <t xml:space="preserve">16.8338794708252</t>
@@ -1049,37 +1049,37 @@
     <t xml:space="preserve">16.9640617370605</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8826961517334</t>
+    <t xml:space="preserve">16.882698059082</t>
   </si>
   <si>
     <t xml:space="preserve">16.9233779907227</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1349201202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0698299407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1674671173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6637744903564</t>
+    <t xml:space="preserve">17.1349220275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0698318481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1674652099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6637783050537</t>
   </si>
   <si>
     <t xml:space="preserve">18.2251777648926</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8598022460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0632076263428</t>
+    <t xml:space="preserve">18.859806060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0632095336914</t>
   </si>
   <si>
     <t xml:space="preserve">18.7052135467529</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6319885253906</t>
+    <t xml:space="preserve">18.6319923400879</t>
   </si>
   <si>
     <t xml:space="preserve">18.7377624511719</t>
@@ -1091,31 +1091,31 @@
     <t xml:space="preserve">18.59130859375</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3065414428711</t>
+    <t xml:space="preserve">18.3065395355225</t>
   </si>
   <si>
     <t xml:space="preserve">18.6157150268555</t>
   </si>
   <si>
-    <t xml:space="preserve">18.217041015625</t>
+    <t xml:space="preserve">18.2170391082764</t>
   </si>
   <si>
     <t xml:space="preserve">18.2089042663574</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4611282348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5417346954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9071044921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.475887298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3945236206055</t>
+    <t xml:space="preserve">18.4611301422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5417327880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9071083068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4758853912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3945217132568</t>
   </si>
   <si>
     <t xml:space="preserve">16.1097545623779</t>
@@ -1127,7 +1127,7 @@
     <t xml:space="preserve">16.2806167602539</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3782482147217</t>
+    <t xml:space="preserve">16.3782501220703</t>
   </si>
   <si>
     <t xml:space="preserve">16.1992530822754</t>
@@ -1139,28 +1139,28 @@
     <t xml:space="preserve">16.2724800109863</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6792907714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.313159942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.09348487854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9470310211182</t>
+    <t xml:space="preserve">16.679292678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3131618499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0934810638428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9470319747925</t>
   </si>
   <si>
     <t xml:space="preserve">16.1911163330078</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3538436889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0283908843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9144840240479</t>
+    <t xml:space="preserve">16.3538398742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.028392791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9144859313965</t>
   </si>
   <si>
     <t xml:space="preserve">15.1822242736816</t>
@@ -1169,49 +1169,49 @@
     <t xml:space="preserve">14.970682144165</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1008596420288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8730478286743</t>
+    <t xml:space="preserve">15.1008634567261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8730487823486</t>
   </si>
   <si>
     <t xml:space="preserve">14.222146987915</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8478813171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8893184661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1984968185425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3937673568726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5402193069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.938136100769</t>
+    <t xml:space="preserve">13.84787940979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8893165588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1984987258911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3937644958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5402173995972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9381351470947</t>
   </si>
   <si>
     <t xml:space="preserve">14.5964155197144</t>
   </si>
   <si>
-    <t xml:space="preserve">14.40114402771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2058734893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1082410812378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0594234466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.912971496582</t>
+    <t xml:space="preserve">14.4011449813843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2058744430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1082382202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0594244003296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9129705429077</t>
   </si>
   <si>
     <t xml:space="preserve">14.0106058120728</t>
@@ -1220,112 +1220,112 @@
     <t xml:space="preserve">14.3197822570801</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6452312469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7428684234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7265939712524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.214771270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8079566955566</t>
+    <t xml:space="preserve">14.6452331542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7428674697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7265949249268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2147703170776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8079595565796</t>
   </si>
   <si>
     <t xml:space="preserve">14.8567752838135</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9544076919556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7916860580444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2709655761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0032262802124</t>
+    <t xml:space="preserve">14.9544086456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7916841506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2709646224976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0032253265381</t>
   </si>
   <si>
     <t xml:space="preserve">14.4825067520142</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9218626022339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9055919647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0194988250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0520458221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2562084197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7354888916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8168487548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6215801239014</t>
+    <t xml:space="preserve">14.9218654632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.905590057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0194978713989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0520420074463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2562065124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7354869842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8168516159058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6215810775757</t>
   </si>
   <si>
     <t xml:space="preserve">15.9307565689087</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6866693496704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7192163467407</t>
+    <t xml:space="preserve">15.6866703033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7192182540894</t>
   </si>
   <si>
     <t xml:space="preserve">15.7029418945312</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6703987121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6053056716919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5653514862061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9956817626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0291938781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0627031326294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2470064163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2302541732788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5318412780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7161464691162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8669385910034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5821084976196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4983329772949</t>
+    <t xml:space="preserve">15.6703996658325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6053085327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5653495788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9956827163696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0291948318481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0627012252808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2470102310181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2302522659302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5318422317505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7161445617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8669395446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.582106590271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.498330116272</t>
   </si>
   <si>
     <t xml:space="preserve">15.4815759658813</t>
@@ -1334,43 +1334,43 @@
     <t xml:space="preserve">15.4145565032959</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1799869537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.07945728302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1129684448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3589935302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.291974067688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2584648132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4595241546631</t>
+    <t xml:space="preserve">15.1799879074097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0794591903687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1129674911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3589944839478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2919750213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2584638595581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4595260620117</t>
   </si>
   <si>
     <t xml:space="preserve">14.4092597961426</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5600528717041</t>
+    <t xml:space="preserve">14.5600519180298</t>
   </si>
   <si>
     <t xml:space="preserve">13.4039621353149</t>
   </si>
   <si>
-    <t xml:space="preserve">13.487738609314</t>
+    <t xml:space="preserve">13.4877376556396</t>
   </si>
   <si>
     <t xml:space="preserve">13.2364120483398</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5380001068115</t>
+    <t xml:space="preserve">13.5380010604858</t>
   </si>
   <si>
     <t xml:space="preserve">13.4374732971191</t>
@@ -1388,13 +1388,13 @@
     <t xml:space="preserve">13.4207172393799</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5212469100952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.57151222229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3201866149902</t>
+    <t xml:space="preserve">13.5212478637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5715131759644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3201875686646</t>
   </si>
   <si>
     <t xml:space="preserve">13.1526384353638</t>
@@ -1406,10 +1406,10 @@
     <t xml:space="preserve">13.2196578979492</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3034324645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8510484695435</t>
+    <t xml:space="preserve">13.3034334182739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8510494232178</t>
   </si>
   <si>
     <t xml:space="preserve">12.683500289917</t>
@@ -1418,10 +1418,10 @@
     <t xml:space="preserve">12.5662136077881</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9013137817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8342924118042</t>
+    <t xml:space="preserve">12.901312828064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8342943191528</t>
   </si>
   <si>
     <t xml:space="preserve">12.4824390411377</t>
@@ -1430,10 +1430,10 @@
     <t xml:space="preserve">12.1473407745361</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0803203582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0635652542114</t>
+    <t xml:space="preserve">12.0803213119507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0635662078857</t>
   </si>
   <si>
     <t xml:space="preserve">11.979790687561</t>
@@ -1451,13 +1451,13 @@
     <t xml:space="preserve">12.4321746826172</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1191282272339</t>
+    <t xml:space="preserve">13.1191272735596</t>
   </si>
   <si>
     <t xml:space="preserve">13.2531681060791</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2866773605347</t>
+    <t xml:space="preserve">13.2866764068604</t>
   </si>
   <si>
     <t xml:space="preserve">12.7672739028931</t>
@@ -1466,10 +1466,10 @@
     <t xml:space="preserve">13.3536977767944</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9850883483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8007831573486</t>
+    <t xml:space="preserve">12.9850873947144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8007841110229</t>
   </si>
   <si>
     <t xml:space="preserve">12.6332349777222</t>
@@ -1478,19 +1478,19 @@
     <t xml:space="preserve">12.8678035736084</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8122415542603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6279373168945</t>
+    <t xml:space="preserve">11.8122425079346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6279363632202</t>
   </si>
   <si>
     <t xml:space="preserve">11.6111822128296</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7284669876099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9630355834961</t>
+    <t xml:space="preserve">11.7284660339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9630365371704</t>
   </si>
   <si>
     <t xml:space="preserve">11.8960161209106</t>
@@ -1502,49 +1502,49 @@
     <t xml:space="preserve">11.075023651123</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0415143966675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9577379226685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7566795349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9242296218872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9744939804077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7117118835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3651561737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4603881835938</t>
+    <t xml:space="preserve">11.0415134429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9577388763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7566804885864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9242286682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.974494934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7117109298706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3651552200317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4603872299194</t>
   </si>
   <si>
     <t xml:space="preserve">11.1587982177734</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1252880096436</t>
+    <t xml:space="preserve">11.1252889633179</t>
   </si>
   <si>
     <t xml:space="preserve">11.1755542755127</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3766136169434</t>
+    <t xml:space="preserve">11.376612663269</t>
   </si>
   <si>
     <t xml:space="preserve">12.2311162948608</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3986663818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9295272827148</t>
+    <t xml:space="preserve">12.3986644744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9295253753662</t>
   </si>
   <si>
     <t xml:space="preserve">11.7954874038696</t>
@@ -1556,7 +1556,7 @@
     <t xml:space="preserve">12.197606086731</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2478704452515</t>
+    <t xml:space="preserve">12.2478694915771</t>
   </si>
   <si>
     <t xml:space="preserve">12.0133018493652</t>
@@ -1565,37 +1565,37 @@
     <t xml:space="preserve">12.1305856704712</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1808500289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3819103240967</t>
+    <t xml:space="preserve">12.180850982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3819093704224</t>
   </si>
   <si>
     <t xml:space="preserve">12.3316459655762</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4656858444214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5997247695923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7170095443726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.884557723999</t>
+    <t xml:space="preserve">12.4656848907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.599723815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7170085906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8845586776733</t>
   </si>
   <si>
     <t xml:space="preserve">12.9515781402588</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9683322906494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2029027938843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7337646484375</t>
+    <t xml:space="preserve">12.9683332443237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2029037475586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7337636947632</t>
   </si>
   <si>
     <t xml:space="preserve">12.8175392150879</t>
@@ -1607,19 +1607,19 @@
     <t xml:space="preserve">12.7002544403076</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5159492492676</t>
+    <t xml:space="preserve">12.5159482955933</t>
   </si>
   <si>
     <t xml:space="preserve">12.784029006958</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0018424987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0353536605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5494585037231</t>
+    <t xml:space="preserve">13.0018444061279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0353546142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5494594573975</t>
   </si>
   <si>
     <t xml:space="preserve">12.9348230361938</t>
@@ -1628,25 +1628,25 @@
     <t xml:space="preserve">12.9180679321289</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3872079849243</t>
+    <t xml:space="preserve">13.38720703125</t>
   </si>
   <si>
     <t xml:space="preserve">13.6217775344849</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8228359222412</t>
+    <t xml:space="preserve">13.8228368759155</t>
   </si>
   <si>
     <t xml:space="preserve">13.5044927597046</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4542264938354</t>
+    <t xml:space="preserve">13.4542255401611</t>
   </si>
   <si>
     <t xml:space="preserve">13.6385326385498</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7223052978516</t>
+    <t xml:space="preserve">13.7223062515259</t>
   </si>
   <si>
     <t xml:space="preserve">13.3704528808594</t>
@@ -1661,43 +1661,43 @@
     <t xml:space="preserve">13.1693935394287</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1023731231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.499195098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7481775283813</t>
+    <t xml:space="preserve">13.1023740768433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4991960525513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.748176574707</t>
   </si>
   <si>
     <t xml:space="preserve">12.5740203857422</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3650360107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2257099151611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2779569625854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3127889633179</t>
+    <t xml:space="preserve">12.3650341033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2257108688354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2779579162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3127880096436</t>
   </si>
   <si>
     <t xml:space="preserve">12.295373916626</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3302030563354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1212167739868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5217752456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4869451522827</t>
+    <t xml:space="preserve">12.3302040100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1212177276611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5217733383179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4869441986084</t>
   </si>
   <si>
     <t xml:space="preserve">12.452112197876</t>
@@ -1712,7 +1712,7 @@
     <t xml:space="preserve">11.8948154449463</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2082948684692</t>
+    <t xml:space="preserve">12.2082958221436</t>
   </si>
   <si>
     <t xml:space="preserve">12.8178396224976</t>
@@ -1721,22 +1721,22 @@
     <t xml:space="preserve">12.7655925750732</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6436834335327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.399866104126</t>
+    <t xml:space="preserve">12.643684387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3998651504517</t>
   </si>
   <si>
     <t xml:space="preserve">12.6262683868408</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5391893386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8700857162476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9745788574219</t>
+    <t xml:space="preserve">12.5391902923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8700847625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9745779037476</t>
   </si>
   <si>
     <t xml:space="preserve">12.95716381073</t>
@@ -1745,19 +1745,19 @@
     <t xml:space="preserve">12.9397468566895</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7830085754395</t>
+    <t xml:space="preserve">12.7830095291138</t>
   </si>
   <si>
     <t xml:space="preserve">12.6959295272827</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8004217147827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8875017166138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1560487747192</t>
+    <t xml:space="preserve">12.800422668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8875007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1560497283936</t>
   </si>
   <si>
     <t xml:space="preserve">12.0341396331787</t>
@@ -1766,13 +1766,13 @@
     <t xml:space="preserve">11.7206602096558</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2431268692017</t>
+    <t xml:space="preserve">12.2431259155273</t>
   </si>
   <si>
     <t xml:space="preserve">11.7554912567139</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6684122085571</t>
+    <t xml:space="preserve">11.6684131622314</t>
   </si>
   <si>
     <t xml:space="preserve">11.9993076324463</t>
@@ -1793,52 +1793,52 @@
     <t xml:space="preserve">11.9470624923706</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8251533508301</t>
+    <t xml:space="preserve">11.8251523971558</t>
   </si>
   <si>
     <t xml:space="preserve">11.8599834442139</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7729063034058</t>
+    <t xml:space="preserve">11.7729072570801</t>
   </si>
   <si>
     <t xml:space="preserve">11.8774003982544</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6509971618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5465040206909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3201026916504</t>
+    <t xml:space="preserve">11.6509981155396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5465049743652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3201036453247</t>
   </si>
   <si>
     <t xml:space="preserve">11.2156095504761</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4071798324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3026866912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3549337387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3897638320923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1981916427612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9369602203369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0414533615112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8847141265869</t>
+    <t xml:space="preserve">11.4071807861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3026857376099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3549327850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3897647857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1981925964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9369611740112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0414543151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8847150802612</t>
   </si>
   <si>
     <t xml:space="preserve">10.8672981262207</t>
@@ -1847,13 +1847,13 @@
     <t xml:space="preserve">10.971791267395</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8324670791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.623480796814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6060647964478</t>
+    <t xml:space="preserve">10.8324661254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6234788894653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6060657501221</t>
   </si>
   <si>
     <t xml:space="preserve">10.5886497497559</t>
@@ -1862,7 +1862,7 @@
     <t xml:space="preserve">10.5189876556396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4493255615234</t>
+    <t xml:space="preserve">10.4493246078491</t>
   </si>
   <si>
     <t xml:space="preserve">10.6583118438721</t>
@@ -1874,19 +1874,19 @@
     <t xml:space="preserve">11.1633625030518</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1111173629761</t>
+    <t xml:space="preserve">11.1111154556274</t>
   </si>
   <si>
     <t xml:space="preserve">11.0588693618774</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9892072677612</t>
+    <t xml:space="preserve">10.9892063140869</t>
   </si>
   <si>
     <t xml:space="preserve">10.8498821258545</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0240383148193</t>
+    <t xml:space="preserve">11.024037361145</t>
   </si>
   <si>
     <t xml:space="preserve">11.0066232681274</t>
@@ -1898,31 +1898,31 @@
     <t xml:space="preserve">10.8150520324707</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9543762207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0937004089355</t>
+    <t xml:space="preserve">10.9543752670288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0937013626099</t>
   </si>
   <si>
     <t xml:space="preserve">11.7032442092896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9818935394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9296464920044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9122314453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8077373504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2605409622192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.086386680603</t>
+    <t xml:space="preserve">11.981894493103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9296474456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9122304916382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8077392578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2605419158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0863857269287</t>
   </si>
   <si>
     <t xml:space="preserve">11.9644765853882</t>
@@ -1937,16 +1937,16 @@
     <t xml:space="preserve">11.5813360214233</t>
   </si>
   <si>
-    <t xml:space="preserve">11.476842880249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.685830116272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1908798217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.347620010376</t>
+    <t xml:space="preserve">11.4768419265747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6858282089233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.190878868103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3476190567017</t>
   </si>
   <si>
     <t xml:space="preserve">11.5116729736328</t>
@@ -1955,7 +1955,7 @@
     <t xml:space="preserve">11.5987510681152</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7105588912964</t>
+    <t xml:space="preserve">10.7105579376221</t>
   </si>
   <si>
     <t xml:space="preserve">9.70045852661133</t>
@@ -1964,13 +1964,13 @@
     <t xml:space="preserve">9.49147033691406</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03866672515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98641872406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.429123878479</t>
+    <t xml:space="preserve">9.03866577148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98642063140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42912292480469</t>
   </si>
   <si>
     <t xml:space="preserve">8.18530464172363</t>
@@ -1979,22 +1979,22 @@
     <t xml:space="preserve">8.22884368896484</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45524597167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53361511230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49007797241211</t>
+    <t xml:space="preserve">8.45524501800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.533616065979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49007701873779</t>
   </si>
   <si>
     <t xml:space="preserve">8.31592082977295</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32463073730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16788959503174</t>
+    <t xml:space="preserve">8.32462882995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16788864135742</t>
   </si>
   <si>
     <t xml:space="preserve">8.38558483123779</t>
@@ -2003,19 +2003,19 @@
     <t xml:space="preserve">8.28979873657227</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41170501708984</t>
+    <t xml:space="preserve">8.41170787811279</t>
   </si>
   <si>
     <t xml:space="preserve">8.4987850189209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.638108253479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69035625457764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67294025421143</t>
+    <t xml:space="preserve">8.63810920715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69035530090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67293930053711</t>
   </si>
   <si>
     <t xml:space="preserve">8.79484939575195</t>
@@ -2024,34 +2024,34 @@
     <t xml:space="preserve">8.96900463104248</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75131034851074</t>
+    <t xml:space="preserve">8.75130939483643</t>
   </si>
   <si>
     <t xml:space="preserve">8.70777130126953</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83838844299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18669891357422</t>
+    <t xml:space="preserve">8.83838748931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1866979598999</t>
   </si>
   <si>
     <t xml:space="preserve">9.05608177185059</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14315891265869</t>
+    <t xml:space="preserve">9.14316082000732</t>
   </si>
   <si>
     <t xml:space="preserve">9.23023700714111</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40439319610596</t>
+    <t xml:space="preserve">9.40439224243164</t>
   </si>
   <si>
     <t xml:space="preserve">9.66562652587891</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57854843139648</t>
+    <t xml:space="preserve">9.57854747772217</t>
   </si>
   <si>
     <t xml:space="preserve">9.31731510162354</t>
@@ -2060,7 +2060,7 @@
     <t xml:space="preserve">8.88192558288574</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65552425384521</t>
+    <t xml:space="preserve">8.65552520751953</t>
   </si>
   <si>
     <t xml:space="preserve">8.51620006561279</t>
@@ -2078,34 +2078,34 @@
     <t xml:space="preserve">9.83978176116943</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0139350891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1010150909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92685985565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88331985473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0574760437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97039794921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70916366577148</t>
+    <t xml:space="preserve">10.0139360427856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1010141372681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92685794830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88332080841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0574769973755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97039890289307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7091646194458</t>
   </si>
   <si>
     <t xml:space="preserve">9.75270366668701</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6220874786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53500843048096</t>
+    <t xml:space="preserve">9.62208843231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53500938415527</t>
   </si>
   <si>
     <t xml:space="preserve">9.79624271392822</t>
@@ -2117,10 +2117,10 @@
     <t xml:space="preserve">10.2751693725586</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5364027023315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9282531738281</t>
+    <t xml:space="preserve">10.5364036560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9282522201538</t>
   </si>
   <si>
     <t xml:space="preserve">11.0153303146362</t>
@@ -2135,19 +2135,19 @@
     <t xml:space="preserve">10.4057865142822</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3622465133667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3187084197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1894855499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2765636444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4507179260254</t>
+    <t xml:space="preserve">10.362247467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3187093734741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1894865036011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2765626907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4507188796997</t>
   </si>
   <si>
     <t xml:space="preserve">12.0167245864868</t>
@@ -2159,7 +2159,7 @@
     <t xml:space="preserve">12.5011930465698</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0100746154785</t>
+    <t xml:space="preserve">12.0100755691528</t>
   </si>
   <si>
     <t xml:space="preserve">11.8314867019653</t>
@@ -2174,16 +2174,16 @@
     <t xml:space="preserve">11.2064266204834</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4296627044678</t>
+    <t xml:space="preserve">11.4296617507935</t>
   </si>
   <si>
     <t xml:space="preserve">11.608250617981</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2510738372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5813674926758</t>
+    <t xml:space="preserve">11.2510747909546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5813665390015</t>
   </si>
   <si>
     <t xml:space="preserve">10.5367202758789</t>
@@ -2192,7 +2192,7 @@
     <t xml:space="preserve">11.0278387069702</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8938980102539</t>
+    <t xml:space="preserve">10.8938961029053</t>
   </si>
   <si>
     <t xml:space="preserve">11.1617794036865</t>
@@ -2201,19 +2201,19 @@
     <t xml:space="preserve">11.0724849700928</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9207811355591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1886625289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2333097457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3226041793823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8761339187622</t>
+    <t xml:space="preserve">11.9207801818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1886615753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2333106994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3226051330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8761329650879</t>
   </si>
   <si>
     <t xml:space="preserve">12.1440162658691</t>
@@ -2225,67 +2225,67 @@
     <t xml:space="preserve">12.0993690490723</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4387817382812</t>
+    <t xml:space="preserve">13.4387836456299</t>
   </si>
   <si>
     <t xml:space="preserve">13.4834299087524</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9299020767212</t>
+    <t xml:space="preserve">13.9299011230469</t>
   </si>
   <si>
     <t xml:space="preserve">13.8406066894531</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0191955566406</t>
+    <t xml:space="preserve">14.0191946029663</t>
   </si>
   <si>
     <t xml:space="preserve">12.9030170440674</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0816040039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0369577407837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7513122558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7959585189819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3941345214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9745483398438</t>
+    <t xml:space="preserve">13.0816049575806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.036958694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7513113021851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7959594726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3941354751587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9745473861694</t>
   </si>
   <si>
     <t xml:space="preserve">13.2601938247681</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6620178222656</t>
+    <t xml:space="preserve">13.6620187759399</t>
   </si>
   <si>
     <t xml:space="preserve">13.6173706054688</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8852548599243</t>
+    <t xml:space="preserve">13.88525390625</t>
   </si>
   <si>
     <t xml:space="preserve">14.6442546844482</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7781944274902</t>
+    <t xml:space="preserve">14.7781972885132</t>
   </si>
   <si>
     <t xml:space="preserve">14.9121379852295</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0907258987427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7335481643677</t>
+    <t xml:space="preserve">15.090726852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.733549118042</t>
   </si>
   <si>
     <t xml:space="preserve">14.4210195541382</t>
@@ -2294,13 +2294,13 @@
     <t xml:space="preserve">14.5103130340576</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1800203323364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8497276306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8050813674927</t>
+    <t xml:space="preserve">15.1800193786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8497285842896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.805079460144</t>
   </si>
   <si>
     <t xml:space="preserve">16.0729637145996</t>
@@ -2309,16 +2309,16 @@
     <t xml:space="preserve">16.3854923248291</t>
   </si>
   <si>
-    <t xml:space="preserve">16.921257019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1891403198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7426700592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7249069213867</t>
+    <t xml:space="preserve">16.9212589263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1891384124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7426681518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7249050140381</t>
   </si>
   <si>
     <t xml:space="preserve">17.769552230835</t>
@@ -2336,13 +2336,13 @@
     <t xml:space="preserve">18.12672996521</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3946113586426</t>
+    <t xml:space="preserve">18.3946132659912</t>
   </si>
   <si>
     <t xml:space="preserve">18.5732002258301</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6980247497559</t>
+    <t xml:space="preserve">16.6980228424072</t>
   </si>
   <si>
     <t xml:space="preserve">18.3053169250488</t>
@@ -2357,13 +2357,13 @@
     <t xml:space="preserve">17.9481410980225</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0196704864502</t>
+    <t xml:space="preserve">19.0196723937988</t>
   </si>
   <si>
     <t xml:space="preserve">20.1804981231689</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5376739501953</t>
+    <t xml:space="preserve">20.5376758575439</t>
   </si>
   <si>
     <t xml:space="preserve">20.6269702911377</t>
@@ -2372,7 +2372,7 @@
     <t xml:space="preserve">20.9841461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8055572509766</t>
+    <t xml:space="preserve">20.8055553436279</t>
   </si>
   <si>
     <t xml:space="preserve">21.0734405517578</t>
@@ -2384,16 +2384,16 @@
     <t xml:space="preserve">20.0019092559814</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8233222961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2697925567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1982593536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9126148223877</t>
+    <t xml:space="preserve">19.8233184814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2697906494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1982612609863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9126129150391</t>
   </si>
   <si>
     <t xml:space="preserve">19.5554370880127</t>
@@ -2405,16 +2405,16 @@
     <t xml:space="preserve">18.9303779602051</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7162647247314</t>
+    <t xml:space="preserve">20.7162609100342</t>
   </si>
   <si>
     <t xml:space="preserve">20.4483795166016</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4306163787842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3413219451904</t>
+    <t xml:space="preserve">21.4306182861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3413200378418</t>
   </si>
   <si>
     <t xml:space="preserve">22.323558807373</t>
@@ -2426,13 +2426,13 @@
     <t xml:space="preserve">22.0556774139404</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7877960205078</t>
+    <t xml:space="preserve">21.7877922058105</t>
   </si>
   <si>
     <t xml:space="preserve">22.7700309753418</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9147033691406</t>
+    <t xml:space="preserve">24.914701461792</t>
   </si>
   <si>
     <t xml:space="preserve">24.4583892822266</t>
@@ -2447,10 +2447,10 @@
     <t xml:space="preserve">24.5496520996094</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4622783660889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8234405517578</t>
+    <t xml:space="preserve">25.4622764587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8234424591064</t>
   </si>
   <si>
     <t xml:space="preserve">24.0933380126953</t>
@@ -2459,7 +2459,7 @@
     <t xml:space="preserve">24.732177734375</t>
   </si>
   <si>
-    <t xml:space="preserve">24.367130279541</t>
+    <t xml:space="preserve">24.3671283721924</t>
   </si>
   <si>
     <t xml:space="preserve">23.9108142852783</t>
@@ -2468,7 +2468,7 @@
     <t xml:space="preserve">23.2719764709473</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6370277404785</t>
+    <t xml:space="preserve">23.6370258331299</t>
   </si>
   <si>
     <t xml:space="preserve">23.5457630157471</t>
@@ -2483,7 +2483,7 @@
     <t xml:space="preserve">24.1846027374268</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0059661865234</t>
+    <t xml:space="preserve">25.0059642791748</t>
   </si>
   <si>
     <t xml:space="preserve">22.3593482971191</t>
@@ -2492,28 +2492,28 @@
     <t xml:space="preserve">22.8156623840332</t>
   </si>
   <si>
-    <t xml:space="preserve">22.268087387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7243995666504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4545021057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.089448928833</t>
+    <t xml:space="preserve">22.2680854797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7243976593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4545001983643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0894508361816</t>
   </si>
   <si>
     <t xml:space="preserve">23.1807117462158</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9069271087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1768245697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5418758392334</t>
+    <t xml:space="preserve">22.906925201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1768226623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5418739318848</t>
   </si>
   <si>
     <t xml:space="preserve">21.9942989349365</t>
@@ -2522,10 +2522,10 @@
     <t xml:space="preserve">22.0855617523193</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5379848480225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7205085754395</t>
+    <t xml:space="preserve">21.5379867553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7205104827881</t>
   </si>
   <si>
     <t xml:space="preserve">21.3554592132568</t>
@@ -2534,25 +2534,25 @@
     <t xml:space="preserve">21.8117733001709</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4467239379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8991470336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0738945007324</t>
+    <t xml:space="preserve">21.446720123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8991451263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0738925933838</t>
   </si>
   <si>
     <t xml:space="preserve">19.8952560424805</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8039970397949</t>
+    <t xml:space="preserve">19.8039951324463</t>
   </si>
   <si>
     <t xml:space="preserve">19.6214694976807</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7127323150635</t>
+    <t xml:space="preserve">19.7127342224121</t>
   </si>
   <si>
     <t xml:space="preserve">21.081672668457</t>
@@ -2567,7 +2567,7 @@
     <t xml:space="preserve">26.374906539917</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6448059082031</t>
+    <t xml:space="preserve">25.6448040008545</t>
   </si>
   <si>
     <t xml:space="preserve">25.9185924530029</t>
@@ -2576,13 +2576,13 @@
     <t xml:space="preserve">25.8273296356201</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5535411834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2797546386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3632373809814</t>
+    <t xml:space="preserve">25.5535430908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2797565460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3632392883301</t>
   </si>
   <si>
     <t xml:space="preserve">22.450611114502</t>
@@ -2591,25 +2591,25 @@
     <t xml:space="preserve">21.6292476654053</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9904079437256</t>
+    <t xml:space="preserve">20.9904098510742</t>
   </si>
   <si>
     <t xml:space="preserve">21.2641983032227</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1729354858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5340976715088</t>
+    <t xml:space="preserve">21.1729335784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5340957641602</t>
   </si>
   <si>
     <t xml:space="preserve">20.8078842163086</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4428329467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9030361175537</t>
+    <t xml:space="preserve">20.442834854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9030342102051</t>
   </si>
   <si>
     <t xml:space="preserve">22.6331367492676</t>
@@ -2624,7 +2624,7 @@
     <t xml:space="preserve">19.3476810455322</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1651573181152</t>
+    <t xml:space="preserve">19.1651554107666</t>
   </si>
   <si>
     <t xml:space="preserve">18.2525291442871</t>
@@ -2636,10 +2636,10 @@
     <t xml:space="preserve">18.1156349182129</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4311676025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5224285125732</t>
+    <t xml:space="preserve">17.4311656951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5224304199219</t>
   </si>
   <si>
     <t xml:space="preserve">16.2447509765625</t>
@@ -2654,13 +2654,13 @@
     <t xml:space="preserve">16.7010650634766</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6593227386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2486400604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3437938690186</t>
+    <t xml:space="preserve">17.6593246459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2486419677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3437919616699</t>
   </si>
   <si>
     <t xml:space="preserve">18.800106048584</t>
@@ -2672,7 +2672,7 @@
     <t xml:space="preserve">18.982629776001</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5263175964355</t>
+    <t xml:space="preserve">18.5263156890869</t>
   </si>
   <si>
     <t xml:space="preserve">18.4350566864014</t>
@@ -2687,7 +2687,7 @@
     <t xml:space="preserve">21.8574047088623</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3137168884277</t>
+    <t xml:space="preserve">22.3137187957764</t>
   </si>
   <si>
     <t xml:space="preserve">21.9486656188965</t>
@@ -2699,13 +2699,13 @@
     <t xml:space="preserve">21.4923534393311</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4049797058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.678768157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5913944244385</t>
+    <t xml:space="preserve">22.4049777984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6787662506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5913963317871</t>
   </si>
   <si>
     <t xml:space="preserve">23.5001335144043</t>
@@ -69232,7 +69232,7 @@
     </row>
     <row r="2504">
       <c r="A2504" s="1" t="n">
-        <v>45965.691099537</v>
+        <v>45965.3333333333</v>
       </c>
       <c r="B2504" t="n">
         <v>1948</v>
@@ -69253,6 +69253,32 @@
         <v>1261</v>
       </c>
       <c r="H2504" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2505">
+      <c r="A2505" s="1" t="n">
+        <v>45966.691087963</v>
+      </c>
+      <c r="B2505" t="n">
+        <v>2656</v>
+      </c>
+      <c r="C2505" t="n">
+        <v>14.1000003814697</v>
+      </c>
+      <c r="D2505" t="n">
+        <v>13.8500003814697</v>
+      </c>
+      <c r="E2505" t="n">
+        <v>14.1000003814697</v>
+      </c>
+      <c r="F2505" t="n">
+        <v>14</v>
+      </c>
+      <c r="G2505" t="s">
+        <v>1261</v>
+      </c>
+      <c r="H2505" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SAB.MI.xlsx
+++ b/data/SAB.MI.xlsx
@@ -47,82 +47,82 @@
     <t xml:space="preserve">8.61823081970215</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48310279846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33295917510986</t>
+    <t xml:space="preserve">8.4831018447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33295726776123</t>
   </si>
   <si>
     <t xml:space="preserve">8.37049388885498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31794357299805</t>
+    <t xml:space="preserve">8.31794452667236</t>
   </si>
   <si>
     <t xml:space="preserve">8.25788593292236</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16029357910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88252925872803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52969169616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66482162475586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62728452682495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61227178573608</t>
+    <t xml:space="preserve">8.16029262542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88252830505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52969217300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66481971740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62728500366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61226987838745</t>
   </si>
   <si>
     <t xml:space="preserve">7.73989105224609</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75490570068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76992082595825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89754295349121</t>
+    <t xml:space="preserve">7.75490665435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76992177963257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89754343032837</t>
   </si>
   <si>
     <t xml:space="preserve">7.6197772026062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79995059967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72487783432007</t>
+    <t xml:space="preserve">7.79994964599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72487688064575</t>
   </si>
   <si>
     <t xml:space="preserve">7.65731287002563</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50717067718506</t>
+    <t xml:space="preserve">7.5071702003479</t>
   </si>
   <si>
     <t xml:space="preserve">7.34201145172119</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54470634460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39080858230591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58224153518677</t>
+    <t xml:space="preserve">7.54470586776733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39080953598022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58224105834961</t>
   </si>
   <si>
     <t xml:space="preserve">7.82247161865234</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0852222442627</t>
+    <t xml:space="preserve">8.08522129058838</t>
   </si>
   <si>
     <t xml:space="preserve">8.11525058746338</t>
@@ -137,22 +137,22 @@
     <t xml:space="preserve">8.03267192840576</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92006397247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77742671966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86751508712769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80745649337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98763084411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04017925262451</t>
+    <t xml:space="preserve">7.92006540298462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77742910385132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86751174926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80745601654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98762989044189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0401782989502</t>
   </si>
   <si>
     <t xml:space="preserve">7.99513578414917</t>
@@ -161,214 +161,214 @@
     <t xml:space="preserve">7.96510696411133</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90504932403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9350790977478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89003419876099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94258403778076</t>
+    <t xml:space="preserve">7.90505027770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93507814407349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89003562927246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94258499145508</t>
   </si>
   <si>
     <t xml:space="preserve">7.82997846603394</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81496429443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73238468170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64980554580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71737098693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67232751846313</t>
+    <t xml:space="preserve">7.81496381759644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73238372802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64980506896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.717369556427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67232799530029</t>
   </si>
   <si>
     <t xml:space="preserve">7.6347918510437</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51467800140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64229822158813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56722736358643</t>
+    <t xml:space="preserve">7.51467704772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64229869842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56722640991211</t>
   </si>
   <si>
     <t xml:space="preserve">7.70235681533813</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74739980697632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46963310241699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69484996795654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49215459823608</t>
+    <t xml:space="preserve">7.74739933013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46963357925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69484853744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49215602874756</t>
   </si>
   <si>
     <t xml:space="preserve">7.47338771820068</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43585109710693</t>
+    <t xml:space="preserve">7.43585157394409</t>
   </si>
   <si>
     <t xml:space="preserve">7.50341701507568</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48089504241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59725570678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42834377288818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38705492019653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37204027175903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31949090957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28195476531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52122211456299</t>
+    <t xml:space="preserve">7.48089599609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59725522994995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4283447265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38705587387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37204217910767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3194899559021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28195381164551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52122116088867</t>
   </si>
   <si>
     <t xml:space="preserve">7.80533885955811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75009346008301</t>
+    <t xml:space="preserve">7.7500958442688</t>
   </si>
   <si>
     <t xml:space="preserve">7.75798749923706</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81323146820068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86058330535889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69879531860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58435869216919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68695640563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57646703720093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53700590133667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49754571914673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28445672988892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92536354064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07926225662231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22921133041382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45808410644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26078081130981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37127208709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26472759246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34759473800659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46992349624634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36732578277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37916374206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1345067024231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18975067138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10293817520142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15029048919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10688447952271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20553588867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18186044692993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2213191986084</t>
+    <t xml:space="preserve">7.81322956085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86058521270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69879388809204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58435821533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68695688247681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57646751403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53700637817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49754524230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28445720672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92536401748657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07926177978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22921228408813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45808553695679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2607798576355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37127161026001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26472568511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34759569168091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46992301940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36732482910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37916421890259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13450717926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18975114822388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1029372215271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15029144287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10688304901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20553541183472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18185949325562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22131967544556</t>
   </si>
   <si>
     <t xml:space="preserve">7.19369697570801</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24894189834595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1976432800293</t>
+    <t xml:space="preserve">7.24894332885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19764280319214</t>
   </si>
   <si>
     <t xml:space="preserve">7.18580436706543</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22526597976685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20948266983032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31602668762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21342897415161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16607475280762</t>
+    <t xml:space="preserve">7.22526550292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20948123931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31602573394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21342849731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16607427597046</t>
   </si>
   <si>
     <t xml:space="preserve">7.24499559402466</t>
@@ -377,76 +377,76 @@
     <t xml:space="preserve">7.13056039810181</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11083030700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17791366577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23315906524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2765645980835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3002405166626</t>
+    <t xml:space="preserve">7.11082887649536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17791318893433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23315811157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27656507492065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30024099349976</t>
   </si>
   <si>
     <t xml:space="preserve">7.29234933853149</t>
   </si>
   <si>
-    <t xml:space="preserve">7.241051197052</t>
+    <t xml:space="preserve">7.24105072021484</t>
   </si>
   <si>
     <t xml:space="preserve">7.11872243881226</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09504508972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00428581237793</t>
+    <t xml:space="preserve">7.09504461288452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00428628921509</t>
   </si>
   <si>
     <t xml:space="preserve">6.9450945854187</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93325614929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09899091720581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15423631668091</t>
+    <t xml:space="preserve">6.93325662612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09899139404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15423536300659</t>
   </si>
   <si>
     <t xml:space="preserve">7.13845300674438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1581826210022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05558443069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07136869430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06742286682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02401638031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04769229888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06347703933716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08320760726929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05163955688477</t>
+    <t xml:space="preserve">7.15818309783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05558490753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07136917114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06742238998413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0240159034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04769325256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0634765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08320808410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05163908004761</t>
   </si>
   <si>
     <t xml:space="preserve">7.04374647140503</t>
@@ -455,7 +455,7 @@
     <t xml:space="preserve">7.03190803527832</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05953025817871</t>
+    <t xml:space="preserve">7.05953073501587</t>
   </si>
   <si>
     <t xml:space="preserve">7.03585481643677</t>
@@ -464,58 +464,58 @@
     <t xml:space="preserve">7.17396688461304</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90563440322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91352558135986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93720245361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9214186668396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94114780426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9687705039978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14239835739136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45019197463989</t>
+    <t xml:space="preserve">6.9056339263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91352653503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93720197677612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92141819000244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94114828109741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96877098083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14239883422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45019292831421</t>
   </si>
   <si>
     <t xml:space="preserve">7.79350137710571</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92372226715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04999542236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.207839012146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16837787628174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08945655822754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19994640350342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06577968597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12891864776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17627048492432</t>
+    <t xml:space="preserve">7.92372179031372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0499963760376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20783996582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16837882995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08945560455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19994735717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06578159332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12891674041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17627143859863</t>
   </si>
   <si>
     <t xml:space="preserve">8.32622146606445</t>
@@ -524,16 +524,16 @@
     <t xml:space="preserve">8.55509376525879</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56298732757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42881965637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35779094696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39725017547607</t>
+    <t xml:space="preserve">8.56298637390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42881870269775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35778903961182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39725112915039</t>
   </si>
   <si>
     <t xml:space="preserve">8.42092704772949</t>
@@ -542,13 +542,13 @@
     <t xml:space="preserve">8.44460391998291</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40514278411865</t>
+    <t xml:space="preserve">8.40514373779297</t>
   </si>
   <si>
     <t xml:space="preserve">8.26308441162109</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18416118621826</t>
+    <t xml:space="preserve">8.18416309356689</t>
   </si>
   <si>
     <t xml:space="preserve">8.30254554748535</t>
@@ -557,13 +557,13 @@
     <t xml:space="preserve">8.22362327575684</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28676128387451</t>
+    <t xml:space="preserve">8.2867603302002</t>
   </si>
   <si>
     <t xml:space="preserve">8.25519180297852</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34989738464355</t>
+    <t xml:space="preserve">8.34989833831787</t>
   </si>
   <si>
     <t xml:space="preserve">8.31043720245361</t>
@@ -575,43 +575,43 @@
     <t xml:space="preserve">8.33411502838135</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34200572967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46038818359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62612247467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74450588226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88656425476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00494575500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23381900787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30484867095947</t>
+    <t xml:space="preserve">8.34200477600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46038913726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62612342834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7445068359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88656520843506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0049467086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23381805419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30484771728516</t>
   </si>
   <si>
     <t xml:space="preserve">9.26538753509521</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16279029846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19435787200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24960422515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29695606231689</t>
+    <t xml:space="preserve">9.16278839111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19435882568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24960327148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29695510864258</t>
   </si>
   <si>
     <t xml:space="preserve">9.36798572540283</t>
@@ -620,25 +620,25 @@
     <t xml:space="preserve">9.54950618743896</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67578029632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74680995941162</t>
+    <t xml:space="preserve">9.67577934265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7468090057373</t>
   </si>
   <si>
     <t xml:space="preserve">10.2203369140625</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4807796478271</t>
+    <t xml:space="preserve">10.4807786941528</t>
   </si>
   <si>
     <t xml:space="preserve">10.4571027755737</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2913665771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2597999572754</t>
+    <t xml:space="preserve">10.2913675308228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2597990036011</t>
   </si>
   <si>
     <t xml:space="preserve">10.1493082046509</t>
@@ -647,43 +647,43 @@
     <t xml:space="preserve">10.0861711502075</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0151395797729</t>
+    <t xml:space="preserve">10.0151414871216</t>
   </si>
   <si>
     <t xml:space="preserve">10.1019563674927</t>
   </si>
   <si>
-    <t xml:space="preserve">10.165093421936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0546045303345</t>
+    <t xml:space="preserve">10.1650915145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0546016693115</t>
   </si>
   <si>
     <t xml:space="preserve">10.1808767318726</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1177396774292</t>
+    <t xml:space="preserve">10.1177406311035</t>
   </si>
   <si>
     <t xml:space="preserve">10.1887693405151</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0703868865967</t>
+    <t xml:space="preserve">10.070387840271</t>
   </si>
   <si>
     <t xml:space="preserve">10.1098489761353</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0230340957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.496563911438</t>
+    <t xml:space="preserve">10.0230331420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4965629577637</t>
   </si>
   <si>
     <t xml:space="preserve">10.4176416397095</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3150444030762</t>
+    <t xml:space="preserve">10.3150434494019</t>
   </si>
   <si>
     <t xml:space="preserve">10.7333278656006</t>
@@ -701,22 +701,22 @@
     <t xml:space="preserve">10.5912685394287</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0095520019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.883279800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3410234451294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0592098236084</t>
+    <t xml:space="preserve">11.0095529556274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8832778930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3410224914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0592088699341</t>
   </si>
   <si>
     <t xml:space="preserve">11.9171514511108</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0513181686401</t>
+    <t xml:space="preserve">12.0513172149658</t>
   </si>
   <si>
     <t xml:space="preserve">11.6882791519165</t>
@@ -725,22 +725,22 @@
     <t xml:space="preserve">11.6803865432739</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2644062042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6274442672729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5406303405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6747961044312</t>
+    <t xml:space="preserve">12.2644052505493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6274461746216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5406312942505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6747951507568</t>
   </si>
   <si>
     <t xml:space="preserve">12.7379350662231</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4728565216064</t>
+    <t xml:space="preserve">12.4728555679321</t>
   </si>
   <si>
     <t xml:space="preserve">12.6518535614014</t>
@@ -752,16 +752,16 @@
     <t xml:space="preserve">12.8145780563354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9203500747681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8715314865112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9366216659546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8064413070679</t>
+    <t xml:space="preserve">12.9203491210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8715305328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9366207122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8064422607422</t>
   </si>
   <si>
     <t xml:space="preserve">12.6437168121338</t>
@@ -773,19 +773,19 @@
     <t xml:space="preserve">11.5209159851074</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8463659286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7812747955322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9114551544189</t>
+    <t xml:space="preserve">11.8463649749756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7812738418579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9114561080933</t>
   </si>
   <si>
     <t xml:space="preserve">11.9277276992798</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9602718353271</t>
+    <t xml:space="preserve">11.9602737426758</t>
   </si>
   <si>
     <t xml:space="preserve">11.8056840896606</t>
@@ -797,55 +797,55 @@
     <t xml:space="preserve">12.0009536743164</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9846801757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0416345596313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0823173522949</t>
+    <t xml:space="preserve">11.9846811294556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0416355133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0823163986206</t>
   </si>
   <si>
     <t xml:space="preserve">11.9765453338623</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8789110183716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7161855697632</t>
+    <t xml:space="preserve">11.8789119720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7161846160889</t>
   </si>
   <si>
     <t xml:space="preserve">11.4720993041992</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5534591674805</t>
+    <t xml:space="preserve">11.5534610748291</t>
   </si>
   <si>
     <t xml:space="preserve">11.5860052108765</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7975482940674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8951816558838</t>
+    <t xml:space="preserve">11.7975492477417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8951826095581</t>
   </si>
   <si>
     <t xml:space="preserve">12.0904512405396</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1636791229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.074179649353</t>
+    <t xml:space="preserve">12.1636772155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0741806030273</t>
   </si>
   <si>
     <t xml:space="preserve">12.2287683486938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.139271736145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2043590545654</t>
+    <t xml:space="preserve">12.1392707824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2043600082397</t>
   </si>
   <si>
     <t xml:space="preserve">12.1880874633789</t>
@@ -854,10 +854,10 @@
     <t xml:space="preserve">12.147406578064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2531785964966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3670845031738</t>
+    <t xml:space="preserve">12.2531766891479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3670854568481</t>
   </si>
   <si>
     <t xml:space="preserve">12.4077663421631</t>
@@ -866,31 +866,31 @@
     <t xml:space="preserve">12.448447227478</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9447584152222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7820320129395</t>
+    <t xml:space="preserve">12.9447574615479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7820339202881</t>
   </si>
   <si>
     <t xml:space="preserve">12.8959407806396</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0098466873169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9528932571411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8552589416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7332162857056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7738962173462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9854393005371</t>
+    <t xml:space="preserve">13.0098485946655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9528942108154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8552598953247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7332153320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7738971710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9854383468628</t>
   </si>
   <si>
     <t xml:space="preserve">13.2620706558228</t>
@@ -899,67 +899,67 @@
     <t xml:space="preserve">13.685154914856</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9292421340942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9943332672119</t>
+    <t xml:space="preserve">13.9292440414429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9943323135376</t>
   </si>
   <si>
     <t xml:space="preserve">13.7502450942993</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8153343200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8316097259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0187406539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.026876449585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1814670562744</t>
+    <t xml:space="preserve">13.8153352737427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8316078186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.018741607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0268774032593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1814680099487</t>
   </si>
   <si>
     <t xml:space="preserve">14.1570568084717</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2302837371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7754106521606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3205413818359</t>
+    <t xml:space="preserve">14.2302846908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7754096984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3205404281616</t>
   </si>
   <si>
     <t xml:space="preserve">15.2961311340332</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4588575363159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.824987411499</t>
+    <t xml:space="preserve">15.4588565826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8249845504761</t>
   </si>
   <si>
     <t xml:space="preserve">15.7924423217773</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5076732635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8493947982788</t>
+    <t xml:space="preserve">15.5076723098755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8493938446045</t>
   </si>
   <si>
     <t xml:space="preserve">15.8656673431396</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5158081054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0039825439453</t>
+    <t xml:space="preserve">15.5158090591431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0039863586426</t>
   </si>
   <si>
     <t xml:space="preserve">16.2643451690674</t>
@@ -971,31 +971,31 @@
     <t xml:space="preserve">16.955924987793</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4115524291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0454216003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0787220001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6475048065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0217685699463</t>
+    <t xml:space="preserve">17.4115543365479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0454254150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0787258148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6475028991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0217723846436</t>
   </si>
   <si>
     <t xml:space="preserve">18.0543174743652</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1275444030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2984066009521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4123115539551</t>
+    <t xml:space="preserve">18.1275424957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2984008789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4123096466064</t>
   </si>
   <si>
     <t xml:space="preserve">18.1682224273682</t>
@@ -1004,13 +1004,13 @@
     <t xml:space="preserve">18.1600875854492</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9159984588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2651023864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0861072540283</t>
+    <t xml:space="preserve">17.9160003662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.265100479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0861034393311</t>
   </si>
   <si>
     <t xml:space="preserve">17.2976474761963</t>
@@ -1019,10 +1019,10 @@
     <t xml:space="preserve">17.0047397613525</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1267833709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8745613098145</t>
+    <t xml:space="preserve">17.1267852783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8745632171631</t>
   </si>
   <si>
     <t xml:space="preserve">17.0779666900635</t>
@@ -1034,58 +1034,58 @@
     <t xml:space="preserve">16.785062789917</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9884662628174</t>
+    <t xml:space="preserve">16.988468170166</t>
   </si>
   <si>
     <t xml:space="preserve">16.5979290008545</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9152450561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8338794708252</t>
+    <t xml:space="preserve">16.9152431488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8338813781738</t>
   </si>
   <si>
     <t xml:space="preserve">16.9640617370605</t>
   </si>
   <si>
-    <t xml:space="preserve">16.882698059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9233779907227</t>
+    <t xml:space="preserve">16.8826999664307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9233798980713</t>
   </si>
   <si>
     <t xml:space="preserve">17.1349220275879</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0698318481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1674652099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6637783050537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2251777648926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.859806060791</t>
+    <t xml:space="preserve">17.0698299407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1674671173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6637763977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2251739501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8598041534424</t>
   </si>
   <si>
     <t xml:space="preserve">19.0632095336914</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7052135467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6319923400879</t>
+    <t xml:space="preserve">18.7052173614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6319904327393</t>
   </si>
   <si>
     <t xml:space="preserve">18.7377624511719</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7133502960205</t>
+    <t xml:space="preserve">18.7133541107178</t>
   </si>
   <si>
     <t xml:space="preserve">18.59130859375</t>
@@ -1094,13 +1094,13 @@
     <t xml:space="preserve">18.3065395355225</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6157150268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2170391082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2089042663574</t>
+    <t xml:space="preserve">18.6157169342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.217041015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2089023590088</t>
   </si>
   <si>
     <t xml:space="preserve">18.4611301422119</t>
@@ -1112,253 +1112,253 @@
     <t xml:space="preserve">16.9071083068848</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4758853912354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3945217132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1097545623779</t>
+    <t xml:space="preserve">16.4758834838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3945236206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1097526550293</t>
   </si>
   <si>
     <t xml:space="preserve">16.3619785308838</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2806167602539</t>
+    <t xml:space="preserve">16.2806186676025</t>
   </si>
   <si>
     <t xml:space="preserve">16.3782501220703</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1992530822754</t>
+    <t xml:space="preserve">16.199254989624</t>
   </si>
   <si>
     <t xml:space="preserve">16.2236633300781</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2724800109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.679292678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3131618499756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0934810638428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9470319747925</t>
+    <t xml:space="preserve">16.272481918335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6792907714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.313159942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0934829711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9470300674438</t>
   </si>
   <si>
     <t xml:space="preserve">16.1911163330078</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3538398742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.028392791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9144859313965</t>
+    <t xml:space="preserve">16.3538417816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0283946990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9144849777222</t>
   </si>
   <si>
     <t xml:space="preserve">15.1822242736816</t>
   </si>
   <si>
-    <t xml:space="preserve">14.970682144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1008634567261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8730487823486</t>
+    <t xml:space="preserve">14.9706792831421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1008625030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.873046875</t>
   </si>
   <si>
     <t xml:space="preserve">14.222146987915</t>
   </si>
   <si>
-    <t xml:space="preserve">13.84787940979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8893165588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1984987258911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3937644958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5402173995972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9381351470947</t>
+    <t xml:space="preserve">13.8478813171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8893184661865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1984977722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3937654495239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5402202606201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.938136100769</t>
   </si>
   <si>
     <t xml:space="preserve">14.5964155197144</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4011449813843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2058744430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1082382202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0594244003296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9129705429077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0106058120728</t>
+    <t xml:space="preserve">14.4011459350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2058753967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1082410812378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.059422492981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.912971496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0106039047241</t>
   </si>
   <si>
     <t xml:space="preserve">14.3197822570801</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6452331542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7428674697876</t>
+    <t xml:space="preserve">14.6452312469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7428684234619</t>
   </si>
   <si>
     <t xml:space="preserve">14.7265949249268</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2147703170776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8079595565796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8567752838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9544086456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7916841506958</t>
+    <t xml:space="preserve">15.214771270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8079566955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8567733764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9544057846069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7916831970215</t>
   </si>
   <si>
     <t xml:space="preserve">14.2709646224976</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0032253265381</t>
+    <t xml:space="preserve">15.0032272338867</t>
   </si>
   <si>
     <t xml:space="preserve">14.4825067520142</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9218654632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.905590057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0194978713989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0520420074463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2562065124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7354869842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8168516159058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6215810775757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9307565689087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6866703033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7192182540894</t>
+    <t xml:space="preserve">14.9218635559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9055919647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0194988250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0520429611206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2562084197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7354860305786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8168506622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6215829849243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9307584762573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6866722106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7192134857178</t>
   </si>
   <si>
     <t xml:space="preserve">15.7029418945312</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6703996658325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6053085327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5653495788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9956827163696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0291948318481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0627012252808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2470102310181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2302522659302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5318422317505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7161445617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8669395446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.582106590271</t>
+    <t xml:space="preserve">15.6703987121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6053075790405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5653514862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9956798553467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0291957855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0627031326294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2470064163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2302532196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5318412780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7161464691162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8669414520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5821056365967</t>
   </si>
   <si>
     <t xml:space="preserve">15.498330116272</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4815759658813</t>
+    <t xml:space="preserve">15.481575012207</t>
   </si>
   <si>
     <t xml:space="preserve">15.4145565032959</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1799879074097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0794591903687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1129674911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3589944839478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2919750213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2584638595581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4595260620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4092597961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5600519180298</t>
+    <t xml:space="preserve">15.1799898147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0794582366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1129684448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3589935302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2919731140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2584657669067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4595251083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4092607498169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5600538253784</t>
   </si>
   <si>
     <t xml:space="preserve">13.4039621353149</t>
@@ -1367,19 +1367,19 @@
     <t xml:space="preserve">13.4877376556396</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2364120483398</t>
+    <t xml:space="preserve">13.2364130020142</t>
   </si>
   <si>
     <t xml:space="preserve">13.5380010604858</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4374732971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1914463043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5882663726807</t>
+    <t xml:space="preserve">13.4374723434448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.191445350647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.588267326355</t>
   </si>
   <si>
     <t xml:space="preserve">13.6887969970703</t>
@@ -1388,40 +1388,40 @@
     <t xml:space="preserve">13.4207172393799</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5212478637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5715131759644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3201875686646</t>
+    <t xml:space="preserve">13.5212469100952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.57151222229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3201866149902</t>
   </si>
   <si>
     <t xml:space="preserve">13.1526384353638</t>
   </si>
   <si>
-    <t xml:space="preserve">13.186146736145</t>
+    <t xml:space="preserve">13.1861476898193</t>
   </si>
   <si>
     <t xml:space="preserve">13.2196578979492</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3034334182739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8510494232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.683500289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5662136077881</t>
+    <t xml:space="preserve">13.3034324645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8510484695435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6834993362427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5662145614624</t>
   </si>
   <si>
     <t xml:space="preserve">12.901312828064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8342943191528</t>
+    <t xml:space="preserve">12.8342933654785</t>
   </si>
   <si>
     <t xml:space="preserve">12.4824390411377</t>
@@ -1433,10 +1433,10 @@
     <t xml:space="preserve">12.0803213119507</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0635662078857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.979790687561</t>
+    <t xml:space="preserve">12.0635671615601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9797916412354</t>
   </si>
   <si>
     <t xml:space="preserve">11.5609178543091</t>
@@ -1445,7 +1445,7 @@
     <t xml:space="preserve">11.1923084259033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2258186340332</t>
+    <t xml:space="preserve">11.2258176803589</t>
   </si>
   <si>
     <t xml:space="preserve">12.4321746826172</t>
@@ -1457,22 +1457,22 @@
     <t xml:space="preserve">13.2531681060791</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2866764068604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7672739028931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3536977767944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9850873947144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8007841110229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6332349777222</t>
+    <t xml:space="preserve">13.2866773605347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7672748565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3536968231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9850883483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8007831573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6332340240479</t>
   </si>
   <si>
     <t xml:space="preserve">12.8678035736084</t>
@@ -1481,16 +1481,16 @@
     <t xml:space="preserve">11.8122425079346</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6279363632202</t>
+    <t xml:space="preserve">11.6279373168945</t>
   </si>
   <si>
     <t xml:space="preserve">11.6111822128296</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7284660339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9630365371704</t>
+    <t xml:space="preserve">11.7284669876099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9630355834961</t>
   </si>
   <si>
     <t xml:space="preserve">11.8960161209106</t>
@@ -1499,13 +1499,13 @@
     <t xml:space="preserve">11.6614475250244</t>
   </si>
   <si>
-    <t xml:space="preserve">11.075023651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0415134429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9577388763428</t>
+    <t xml:space="preserve">11.0750246047974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0415143966675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9577398300171</t>
   </si>
   <si>
     <t xml:space="preserve">10.7566804885864</t>
@@ -1523,7 +1523,7 @@
     <t xml:space="preserve">12.3651552200317</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4603872299194</t>
+    <t xml:space="preserve">11.4603881835938</t>
   </si>
   <si>
     <t xml:space="preserve">11.1587982177734</t>
@@ -1532,10 +1532,10 @@
     <t xml:space="preserve">11.1252889633179</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1755542755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.376612663269</t>
+    <t xml:space="preserve">11.1755533218384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3766117095947</t>
   </si>
   <si>
     <t xml:space="preserve">12.2311162948608</t>
@@ -1544,52 +1544,52 @@
     <t xml:space="preserve">12.3986644744873</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9295253753662</t>
+    <t xml:space="preserve">11.9295272827148</t>
   </si>
   <si>
     <t xml:space="preserve">11.7954874038696</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8792610168457</t>
+    <t xml:space="preserve">11.8792629241943</t>
   </si>
   <si>
     <t xml:space="preserve">12.197606086731</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2478694915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0133018493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1305856704712</t>
+    <t xml:space="preserve">12.2478704452515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0133008956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1305847167969</t>
   </si>
   <si>
     <t xml:space="preserve">12.180850982666</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3819093704224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3316459655762</t>
+    <t xml:space="preserve">12.3819103240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3316450119019</t>
   </si>
   <si>
     <t xml:space="preserve">12.4656848907471</t>
   </si>
   <si>
-    <t xml:space="preserve">12.599723815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7170085906982</t>
+    <t xml:space="preserve">12.5997247695923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7170095443726</t>
   </si>
   <si>
     <t xml:space="preserve">12.8845586776733</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9515781402588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9683332443237</t>
+    <t xml:space="preserve">12.9515790939331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9683322906494</t>
   </si>
   <si>
     <t xml:space="preserve">13.2029037475586</t>
@@ -1601,13 +1601,13 @@
     <t xml:space="preserve">12.8175392150879</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6499891281128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7002544403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5159482955933</t>
+    <t xml:space="preserve">12.6499910354614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7002534866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5159492492676</t>
   </si>
   <si>
     <t xml:space="preserve">12.784029006958</t>
@@ -1625,28 +1625,28 @@
     <t xml:space="preserve">12.9348230361938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9180679321289</t>
+    <t xml:space="preserve">12.9180688858032</t>
   </si>
   <si>
     <t xml:space="preserve">13.38720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6217775344849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8228368759155</t>
+    <t xml:space="preserve">13.6217765808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8228349685669</t>
   </si>
   <si>
     <t xml:space="preserve">13.5044927597046</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4542255401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6385326385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7223062515259</t>
+    <t xml:space="preserve">13.4542264938354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6385335922241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7223052978516</t>
   </si>
   <si>
     <t xml:space="preserve">13.3704528808594</t>
@@ -1658,16 +1658,16 @@
     <t xml:space="preserve">13.0185985565186</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1693935394287</t>
+    <t xml:space="preserve">13.1693916320801</t>
   </si>
   <si>
     <t xml:space="preserve">13.1023740768433</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4991960525513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.748176574707</t>
+    <t xml:space="preserve">12.499195098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7481784820557</t>
   </si>
   <si>
     <t xml:space="preserve">12.5740203857422</t>
@@ -1676,31 +1676,31 @@
     <t xml:space="preserve">12.3650341033936</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2257108688354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2779579162598</t>
+    <t xml:space="preserve">12.2257099151611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2779569625854</t>
   </si>
   <si>
     <t xml:space="preserve">12.3127880096436</t>
   </si>
   <si>
-    <t xml:space="preserve">12.295373916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3302040100098</t>
+    <t xml:space="preserve">12.2953720092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3302021026611</t>
   </si>
   <si>
     <t xml:space="preserve">12.1212177276611</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5217733383179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4869441986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.452112197876</t>
+    <t xml:space="preserve">12.5217742919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4869432449341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4521131515503</t>
   </si>
   <si>
     <t xml:space="preserve">12.138632774353</t>
@@ -1712,7 +1712,7 @@
     <t xml:space="preserve">11.8948154449463</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2082958221436</t>
+    <t xml:space="preserve">12.2082948684692</t>
   </si>
   <si>
     <t xml:space="preserve">12.8178396224976</t>
@@ -1724,34 +1724,34 @@
     <t xml:space="preserve">12.643684387207</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3998651504517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6262683868408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5391902923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8700847625732</t>
+    <t xml:space="preserve">12.399866104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6262674331665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5391912460327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8700857162476</t>
   </si>
   <si>
     <t xml:space="preserve">12.9745779037476</t>
   </si>
   <si>
-    <t xml:space="preserve">12.95716381073</t>
+    <t xml:space="preserve">12.9571628570557</t>
   </si>
   <si>
     <t xml:space="preserve">12.9397468566895</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7830095291138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6959295272827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.800422668457</t>
+    <t xml:space="preserve">12.7830085754395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.695930480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8004236221313</t>
   </si>
   <si>
     <t xml:space="preserve">12.8875007629395</t>
@@ -1763,19 +1763,19 @@
     <t xml:space="preserve">12.0341396331787</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7206602096558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2431259155273</t>
+    <t xml:space="preserve">11.7206592559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2431268692017</t>
   </si>
   <si>
     <t xml:space="preserve">11.7554912567139</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6684131622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9993076324463</t>
+    <t xml:space="preserve">11.6684122085571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9993085861206</t>
   </si>
   <si>
     <t xml:space="preserve">12.0689706802368</t>
@@ -1787,7 +1787,7 @@
     <t xml:space="preserve">11.790322303772</t>
   </si>
   <si>
-    <t xml:space="preserve">11.842568397522</t>
+    <t xml:space="preserve">11.8425693511963</t>
   </si>
   <si>
     <t xml:space="preserve">11.9470624923706</t>
@@ -1796,22 +1796,22 @@
     <t xml:space="preserve">11.8251523971558</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8599834442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7729072570801</t>
+    <t xml:space="preserve">11.8599843978882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7729063034058</t>
   </si>
   <si>
     <t xml:space="preserve">11.8774003982544</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6509981155396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5465049743652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3201036453247</t>
+    <t xml:space="preserve">11.6509971618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5465040206909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3201026916504</t>
   </si>
   <si>
     <t xml:space="preserve">11.2156095504761</t>
@@ -1820,16 +1820,16 @@
     <t xml:space="preserve">11.4071807861328</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3026857376099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3549327850342</t>
+    <t xml:space="preserve">11.3026866912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3549337387085</t>
   </si>
   <si>
     <t xml:space="preserve">11.3897647857666</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1981925964355</t>
+    <t xml:space="preserve">11.1981935501099</t>
   </si>
   <si>
     <t xml:space="preserve">10.9369611740112</t>
@@ -1838,19 +1838,19 @@
     <t xml:space="preserve">11.0414543151855</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8847150802612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8672981262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.971791267395</t>
+    <t xml:space="preserve">10.8847141265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8672971725464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9717922210693</t>
   </si>
   <si>
     <t xml:space="preserve">10.8324661254883</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6234788894653</t>
+    <t xml:space="preserve">10.623480796814</t>
   </si>
   <si>
     <t xml:space="preserve">10.6060657501221</t>
@@ -1868,25 +1868,25 @@
     <t xml:space="preserve">10.6583118438721</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7802200317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1633625030518</t>
+    <t xml:space="preserve">10.7802209854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1633615493774</t>
   </si>
   <si>
     <t xml:space="preserve">11.1111154556274</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0588693618774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9892063140869</t>
+    <t xml:space="preserve">11.0588684082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9892072677612</t>
   </si>
   <si>
     <t xml:space="preserve">10.8498821258545</t>
   </si>
   <si>
-    <t xml:space="preserve">11.024037361145</t>
+    <t xml:space="preserve">11.0240383148193</t>
   </si>
   <si>
     <t xml:space="preserve">11.0066232681274</t>
@@ -1901,31 +1901,31 @@
     <t xml:space="preserve">10.9543752670288</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0937013626099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7032442092896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.981894493103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9296474456787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9122304916382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8077392578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2605419158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0863857269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9644765853882</t>
+    <t xml:space="preserve">11.0937004089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7032432556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9818925857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9296455383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9122314453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8077383041382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2605409622192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.086386680603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9644775390625</t>
   </si>
   <si>
     <t xml:space="preserve">11.529088973999</t>
@@ -1937,16 +1937,16 @@
     <t xml:space="preserve">11.5813360214233</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4768419265747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6858282089233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.190878868103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3476190567017</t>
+    <t xml:space="preserve">11.4768438339233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6858291625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1908798217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.347620010376</t>
   </si>
   <si>
     <t xml:space="preserve">11.5116729736328</t>
@@ -1955,22 +1955,22 @@
     <t xml:space="preserve">11.5987510681152</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7105579376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70045852661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49147033691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03866577148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98642063140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42912292480469</t>
+    <t xml:space="preserve">10.7105588912964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7004566192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49146938323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03866672515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98641872406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42912197113037</t>
   </si>
   <si>
     <t xml:space="preserve">8.18530464172363</t>
@@ -1982,28 +1982,28 @@
     <t xml:space="preserve">8.45524501800537</t>
   </si>
   <si>
-    <t xml:space="preserve">8.533616065979</t>
+    <t xml:space="preserve">8.53361511230469</t>
   </si>
   <si>
     <t xml:space="preserve">8.49007701873779</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31592082977295</t>
+    <t xml:space="preserve">8.31592178344727</t>
   </si>
   <si>
     <t xml:space="preserve">8.32462882995605</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16788864135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38558483123779</t>
+    <t xml:space="preserve">8.16788959503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38558292388916</t>
   </si>
   <si>
     <t xml:space="preserve">8.28979873657227</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41170787811279</t>
+    <t xml:space="preserve">8.41170597076416</t>
   </si>
   <si>
     <t xml:space="preserve">8.4987850189209</t>
@@ -2015,13 +2015,13 @@
     <t xml:space="preserve">8.69035530090332</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67293930053711</t>
+    <t xml:space="preserve">8.67294025421143</t>
   </si>
   <si>
     <t xml:space="preserve">8.79484939575195</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96900463104248</t>
+    <t xml:space="preserve">8.96900367736816</t>
   </si>
   <si>
     <t xml:space="preserve">8.75130939483643</t>
@@ -2033,19 +2033,19 @@
     <t xml:space="preserve">8.83838748931885</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1866979598999</t>
+    <t xml:space="preserve">9.18669986724854</t>
   </si>
   <si>
     <t xml:space="preserve">9.05608177185059</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14316082000732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23023700714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40439224243164</t>
+    <t xml:space="preserve">9.14315986633301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23023796081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40439319610596</t>
   </si>
   <si>
     <t xml:space="preserve">9.66562652587891</t>
@@ -2060,31 +2060,31 @@
     <t xml:space="preserve">8.88192558288574</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65552520751953</t>
+    <t xml:space="preserve">8.65552425384521</t>
   </si>
   <si>
     <t xml:space="preserve">8.51620006561279</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6032772064209</t>
+    <t xml:space="preserve">8.60327911376953</t>
   </si>
   <si>
     <t xml:space="preserve">8.56844711303711</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36085414886475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83978176116943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0139360427856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1010141372681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92685794830322</t>
+    <t xml:space="preserve">9.36085319519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83978080749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0139379501343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1010150909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92685890197754</t>
   </si>
   <si>
     <t xml:space="preserve">9.88332080841064</t>
@@ -2093,7 +2093,7 @@
     <t xml:space="preserve">10.0574769973755</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97039890289307</t>
+    <t xml:space="preserve">9.97039794921875</t>
   </si>
   <si>
     <t xml:space="preserve">9.7091646194458</t>
@@ -2102,7 +2102,7 @@
     <t xml:space="preserve">9.75270366668701</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62208843231201</t>
+    <t xml:space="preserve">9.62208652496338</t>
   </si>
   <si>
     <t xml:space="preserve">9.53500938415527</t>
@@ -2111,7 +2111,7 @@
     <t xml:space="preserve">9.79624271392822</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1880922317505</t>
+    <t xml:space="preserve">10.1880903244019</t>
   </si>
   <si>
     <t xml:space="preserve">10.2751693725586</t>
@@ -2120,7 +2120,7 @@
     <t xml:space="preserve">10.5364036560059</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9282522201538</t>
+    <t xml:space="preserve">10.9282531738281</t>
   </si>
   <si>
     <t xml:space="preserve">11.0153303146362</t>
@@ -2138,43 +2138,43 @@
     <t xml:space="preserve">10.362247467041</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3187093734741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1894865036011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2765626907349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4507188796997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0167245864868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0602626800537</t>
+    <t xml:space="preserve">10.3187084197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1894855499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2765636444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.450719833374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0167236328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.060263633728</t>
   </si>
   <si>
     <t xml:space="preserve">12.5011930465698</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0100755691528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8314867019653</t>
+    <t xml:space="preserve">12.0100746154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.831485748291</t>
   </si>
   <si>
     <t xml:space="preserve">11.6975450515747</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4743099212646</t>
+    <t xml:space="preserve">11.4743089675903</t>
   </si>
   <si>
     <t xml:space="preserve">11.2064266204834</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4296617507935</t>
+    <t xml:space="preserve">11.4296627044678</t>
   </si>
   <si>
     <t xml:space="preserve">11.608250617981</t>
@@ -2183,7 +2183,7 @@
     <t xml:space="preserve">11.2510747909546</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5813665390015</t>
+    <t xml:space="preserve">10.5813674926758</t>
   </si>
   <si>
     <t xml:space="preserve">10.5367202758789</t>
@@ -2195,25 +2195,25 @@
     <t xml:space="preserve">10.8938961029053</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1617794036865</t>
+    <t xml:space="preserve">11.1617803573608</t>
   </si>
   <si>
     <t xml:space="preserve">11.0724849700928</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9207801818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1886615753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2333106994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3226051330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8761329650879</t>
+    <t xml:space="preserve">11.9207811355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1886625289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2333087921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3226041793823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8761339187622</t>
   </si>
   <si>
     <t xml:space="preserve">12.1440162658691</t>
@@ -2225,19 +2225,19 @@
     <t xml:space="preserve">12.0993690490723</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4387836456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4834299087524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9299011230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8406066894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0191946029663</t>
+    <t xml:space="preserve">13.4387826919556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4834308624268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9299001693726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8406057357788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0191955566406</t>
   </si>
   <si>
     <t xml:space="preserve">12.9030170440674</t>
@@ -2246,10 +2246,10 @@
     <t xml:space="preserve">13.0816049575806</t>
   </si>
   <si>
-    <t xml:space="preserve">13.036958694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7513113021851</t>
+    <t xml:space="preserve">13.0369596481323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7513122558594</t>
   </si>
   <si>
     <t xml:space="preserve">13.7959594726562</t>
@@ -2261,13 +2261,13 @@
     <t xml:space="preserve">13.9745473861694</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2601938247681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6620187759399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6173706054688</t>
+    <t xml:space="preserve">13.2601957321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6620178222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6173715591431</t>
   </si>
   <si>
     <t xml:space="preserve">13.88525390625</t>
@@ -2276,19 +2276,19 @@
     <t xml:space="preserve">14.6442546844482</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7781972885132</t>
+    <t xml:space="preserve">14.7781944274902</t>
   </si>
   <si>
     <t xml:space="preserve">14.9121379852295</t>
   </si>
   <si>
-    <t xml:space="preserve">15.090726852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.733549118042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4210195541382</t>
+    <t xml:space="preserve">15.0907258987427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7335481643677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4210186004639</t>
   </si>
   <si>
     <t xml:space="preserve">14.5103130340576</t>
@@ -2297,13 +2297,13 @@
     <t xml:space="preserve">15.1800193786621</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8497285842896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.805079460144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0729637145996</t>
+    <t xml:space="preserve">15.8497276306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8050813674927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.072961807251</t>
   </si>
   <si>
     <t xml:space="preserve">16.3854923248291</t>
@@ -2312,16 +2312,16 @@
     <t xml:space="preserve">16.9212589263916</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1891384124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7426681518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7249050140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.769552230835</t>
+    <t xml:space="preserve">17.1891422271729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7426700592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7249069213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7695541381836</t>
   </si>
   <si>
     <t xml:space="preserve">17.8142013549805</t>
@@ -2336,7 +2336,7 @@
     <t xml:space="preserve">18.12672996521</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3946132659912</t>
+    <t xml:space="preserve">18.3946113586426</t>
   </si>
   <si>
     <t xml:space="preserve">18.5732002258301</t>
@@ -2345,13 +2345,13 @@
     <t xml:space="preserve">16.6980228424072</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3053169250488</t>
+    <t xml:space="preserve">18.3053188323975</t>
   </si>
   <si>
     <t xml:space="preserve">17.5909652709961</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2160243988037</t>
+    <t xml:space="preserve">18.2160224914551</t>
   </si>
   <si>
     <t xml:space="preserve">17.9481410980225</t>
@@ -2372,7 +2372,7 @@
     <t xml:space="preserve">20.9841461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8055553436279</t>
+    <t xml:space="preserve">20.8055572509766</t>
   </si>
   <si>
     <t xml:space="preserve">21.0734405517578</t>
@@ -2381,43 +2381,43 @@
     <t xml:space="preserve">20.0912036895752</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0019092559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8233184814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2697906494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1982612609863</t>
+    <t xml:space="preserve">20.0019111633301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8233222961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2697925567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1982593536377</t>
   </si>
   <si>
     <t xml:space="preserve">19.9126129150391</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5554370880127</t>
+    <t xml:space="preserve">19.5554389953613</t>
   </si>
   <si>
     <t xml:space="preserve">19.6447334289551</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9303779602051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7162609100342</t>
+    <t xml:space="preserve">18.9303760528564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7162628173828</t>
   </si>
   <si>
     <t xml:space="preserve">20.4483795166016</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4306182861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3413200378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.323558807373</t>
+    <t xml:space="preserve">21.4306163787842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3413238525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3235607147217</t>
   </si>
   <si>
     <t xml:space="preserve">21.6092052459717</t>
@@ -2435,7 +2435,7 @@
     <t xml:space="preserve">24.914701461792</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4583892822266</t>
+    <t xml:space="preserve">24.4583873748779</t>
   </si>
   <si>
     <t xml:space="preserve">24.0020771026611</t>
@@ -2444,16 +2444,16 @@
     <t xml:space="preserve">23.8195514678955</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5496520996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4622764587402</t>
+    <t xml:space="preserve">24.549654006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4622783660889</t>
   </si>
   <si>
     <t xml:space="preserve">24.8234424591064</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0933380126953</t>
+    <t xml:space="preserve">24.0933399200439</t>
   </si>
   <si>
     <t xml:space="preserve">24.732177734375</t>
@@ -2480,13 +2480,13 @@
     <t xml:space="preserve">23.7282886505127</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1846027374268</t>
+    <t xml:space="preserve">24.1846008300781</t>
   </si>
   <si>
     <t xml:space="preserve">25.0059642791748</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3593482971191</t>
+    <t xml:space="preserve">22.3593502044678</t>
   </si>
   <si>
     <t xml:space="preserve">22.8156623840332</t>
@@ -2498,10 +2498,10 @@
     <t xml:space="preserve">22.7243976593018</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4545001983643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0894508361816</t>
+    <t xml:space="preserve">23.4545021057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.089448928833</t>
   </si>
   <si>
     <t xml:space="preserve">23.1807117462158</t>
@@ -2513,7 +2513,7 @@
     <t xml:space="preserve">22.1768226623535</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5418739318848</t>
+    <t xml:space="preserve">22.5418758392334</t>
   </si>
   <si>
     <t xml:space="preserve">21.9942989349365</t>
@@ -2534,13 +2534,13 @@
     <t xml:space="preserve">21.8117733001709</t>
   </si>
   <si>
-    <t xml:space="preserve">21.446720123291</t>
+    <t xml:space="preserve">21.4467220306396</t>
   </si>
   <si>
     <t xml:space="preserve">20.8991451263428</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0738925933838</t>
+    <t xml:space="preserve">19.0738945007324</t>
   </si>
   <si>
     <t xml:space="preserve">19.8952560424805</t>
@@ -2561,13 +2561,13 @@
     <t xml:space="preserve">24.6409149169922</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3710155487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.374906539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6448040008545</t>
+    <t xml:space="preserve">25.3710174560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3749046325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6448059082031</t>
   </si>
   <si>
     <t xml:space="preserve">25.9185924530029</t>
@@ -2576,13 +2576,13 @@
     <t xml:space="preserve">25.8273296356201</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5535430908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2797565460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3632392883301</t>
+    <t xml:space="preserve">25.5535411834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2797546386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3632373809814</t>
   </si>
   <si>
     <t xml:space="preserve">22.450611114502</t>
@@ -2609,7 +2609,7 @@
     <t xml:space="preserve">20.442834854126</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9030342102051</t>
+    <t xml:space="preserve">21.9030361175537</t>
   </si>
   <si>
     <t xml:space="preserve">22.6331367492676</t>
@@ -2621,25 +2621,25 @@
     <t xml:space="preserve">20.1690464019775</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3476810455322</t>
+    <t xml:space="preserve">19.3476829528809</t>
   </si>
   <si>
     <t xml:space="preserve">19.1651554107666</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2525291442871</t>
+    <t xml:space="preserve">18.2525310516357</t>
   </si>
   <si>
     <t xml:space="preserve">18.6175804138184</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1156349182129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4311656951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5224304199219</t>
+    <t xml:space="preserve">18.1156368255615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4311676025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5224285125732</t>
   </si>
   <si>
     <t xml:space="preserve">16.2447509765625</t>
@@ -2657,7 +2657,7 @@
     <t xml:space="preserve">17.6593246459961</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2486419677734</t>
+    <t xml:space="preserve">17.2486400604248</t>
   </si>
   <si>
     <t xml:space="preserve">18.3437919616699</t>
@@ -2666,13 +2666,13 @@
     <t xml:space="preserve">18.800106048584</t>
   </si>
   <si>
-    <t xml:space="preserve">19.256420135498</t>
+    <t xml:space="preserve">19.2564182281494</t>
   </si>
   <si>
     <t xml:space="preserve">18.982629776001</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5263156890869</t>
+    <t xml:space="preserve">18.5263175964355</t>
   </si>
   <si>
     <t xml:space="preserve">18.4350566864014</t>
@@ -2702,25 +2702,25 @@
     <t xml:space="preserve">22.4049777984619</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6787662506104</t>
+    <t xml:space="preserve">22.678768157959</t>
   </si>
   <si>
     <t xml:space="preserve">23.5913963317871</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5001335144043</t>
+    <t xml:space="preserve">23.5001316070557</t>
   </si>
   <si>
     <t xml:space="preserve">23.7337303161621</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8271713256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.387809753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2009315490723</t>
+    <t xml:space="preserve">23.827169418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3878116607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2009296417236</t>
   </si>
   <si>
     <t xml:space="preserve">24.6681289672852</t>
@@ -2729,28 +2729,28 @@
     <t xml:space="preserve">24.621410369873</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0607719421387</t>
+    <t xml:space="preserve">24.06077003479</t>
   </si>
   <si>
     <t xml:space="preserve">23.9673309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5001316070557</t>
+    <t xml:space="preserve">23.500129699707</t>
   </si>
   <si>
     <t xml:space="preserve">22.9394912719727</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7058925628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6591739654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5190124511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.425573348999</t>
+    <t xml:space="preserve">22.7058906555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6591720581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5190143585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4255714416504</t>
   </si>
   <si>
     <t xml:space="preserve">23.4534130096436</t>
@@ -2768,7 +2768,7 @@
     <t xml:space="preserve">22.0985317230225</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9116554260254</t>
+    <t xml:space="preserve">21.9116535186768</t>
   </si>
   <si>
     <t xml:space="preserve">21.6780548095703</t>
@@ -2780,7 +2780,7 @@
     <t xml:space="preserve">23.0329303741455</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9862117767334</t>
+    <t xml:space="preserve">22.986213684082</t>
   </si>
   <si>
     <t xml:space="preserve">21.8182144165039</t>
@@ -2789,7 +2789,7 @@
     <t xml:space="preserve">22.1919727325439</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7714939117432</t>
+    <t xml:space="preserve">21.7714920043945</t>
   </si>
   <si>
     <t xml:space="preserve">22.2386913299561</t>
@@ -2801,13 +2801,13 @@
     <t xml:space="preserve">23.31325340271</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7993335723877</t>
+    <t xml:space="preserve">22.7993316650391</t>
   </si>
   <si>
     <t xml:space="preserve">22.3321323394775</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5846138000488</t>
+    <t xml:space="preserve">21.5846157073975</t>
   </si>
   <si>
     <t xml:space="preserve">20.930534362793</t>
@@ -2819,7 +2819,7 @@
     <t xml:space="preserve">20.2764568328857</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9494152069092</t>
+    <t xml:space="preserve">19.9494171142578</t>
   </si>
   <si>
     <t xml:space="preserve">20.4166164398193</t>
@@ -2840,25 +2840,25 @@
     <t xml:space="preserve">19.9026947021484</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8092555999756</t>
+    <t xml:space="preserve">19.8092575073242</t>
   </si>
   <si>
     <t xml:space="preserve">19.5756568908691</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3420562744141</t>
+    <t xml:space="preserve">19.3420581817627</t>
   </si>
   <si>
     <t xml:space="preserve">19.2486171722412</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9215774536133</t>
+    <t xml:space="preserve">18.9215755462646</t>
   </si>
   <si>
     <t xml:space="preserve">18.8281364440918</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5758495330811</t>
+    <t xml:space="preserve">18.5758476257324</t>
   </si>
   <si>
     <t xml:space="preserve">18.5010967254639</t>
@@ -2870,7 +2870,7 @@
     <t xml:space="preserve">19.5289363861084</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5945377349854</t>
+    <t xml:space="preserve">18.5945358276367</t>
   </si>
   <si>
     <t xml:space="preserve">18.3702812194824</t>
@@ -2879,7 +2879,7 @@
     <t xml:space="preserve">18.0525856018066</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9217700958252</t>
+    <t xml:space="preserve">17.9217720031738</t>
   </si>
   <si>
     <t xml:space="preserve">17.7535781860352</t>
@@ -2891,10 +2891,10 @@
     <t xml:space="preserve">17.7348899841309</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4919452667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2303161621094</t>
+    <t xml:space="preserve">17.4919471740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2303142547607</t>
   </si>
   <si>
     <t xml:space="preserve">17.1742496490479</t>
@@ -2909,7 +2909,7 @@
     <t xml:space="preserve">16.4454212188721</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1277236938477</t>
+    <t xml:space="preserve">16.1277256011963</t>
   </si>
   <si>
     <t xml:space="preserve">16.5014839172363</t>
@@ -2921,13 +2921,13 @@
     <t xml:space="preserve">16.0342845916748</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8847808837891</t>
+    <t xml:space="preserve">15.8847818374634</t>
   </si>
   <si>
     <t xml:space="preserve">15.3241405487061</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6044616699219</t>
+    <t xml:space="preserve">15.6044607162476</t>
   </si>
   <si>
     <t xml:space="preserve">15.7352771759033</t>
@@ -2945,7 +2945,7 @@
     <t xml:space="preserve">16.7444267272949</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7257404327393</t>
+    <t xml:space="preserve">16.7257385253906</t>
   </si>
   <si>
     <t xml:space="preserve">16.9313087463379</t>
@@ -2957,7 +2957,7 @@
     <t xml:space="preserve">17.9965229034424</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2581558227539</t>
+    <t xml:space="preserve">18.2581539154053</t>
   </si>
   <si>
     <t xml:space="preserve">17.6601371765137</t>
@@ -2966,10 +2966,10 @@
     <t xml:space="preserve">17.5666980743408</t>
   </si>
   <si>
-    <t xml:space="preserve">17.641450881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3142166137695</t>
+    <t xml:space="preserve">17.6414489746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3142185211182</t>
   </si>
   <si>
     <t xml:space="preserve">18.0712738037109</t>
@@ -3008,7 +3008,7 @@
     <t xml:space="preserve">17.7162017822266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5293216705322</t>
+    <t xml:space="preserve">17.5293235778809</t>
   </si>
   <si>
     <t xml:space="preserve">16.9873714447021</t>
@@ -3020,10 +3020,10 @@
     <t xml:space="preserve">17.5480117797852</t>
   </si>
   <si>
-    <t xml:space="preserve">16.277229309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9221572875977</t>
+    <t xml:space="preserve">16.2772274017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.922158241272</t>
   </si>
   <si>
     <t xml:space="preserve">16.0155963897705</t>
@@ -3032,19 +3032,19 @@
     <t xml:space="preserve">15.9595327377319</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9782218933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0903472900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8287172317505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6231489181519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5857744216919</t>
+    <t xml:space="preserve">15.9782209396362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0903491973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8287162780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6231479644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5857725143433</t>
   </si>
   <si>
     <t xml:space="preserve">16.0716609954834</t>
@@ -3065,10 +3065,10 @@
     <t xml:space="preserve">16.6322994232178</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6136112213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5762348175049</t>
+    <t xml:space="preserve">16.6136131286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5762367248535</t>
   </si>
   <si>
     <t xml:space="preserve">16.3519802093506</t>
@@ -3077,13 +3077,13 @@
     <t xml:space="preserve">16.2024765014648</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7913408279419</t>
+    <t xml:space="preserve">15.7913398742676</t>
   </si>
   <si>
     <t xml:space="preserve">15.7726516723633</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6978998184204</t>
+    <t xml:space="preserve">15.6979007720947</t>
   </si>
   <si>
     <t xml:space="preserve">16.5201721191406</t>
@@ -3092,34 +3092,34 @@
     <t xml:space="preserve">16.1464138031006</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1650981903076</t>
+    <t xml:space="preserve">16.1651000976562</t>
   </si>
   <si>
     <t xml:space="preserve">16.109037399292</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8474044799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7539663314819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8660917282104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6792125701904</t>
+    <t xml:space="preserve">15.8474025726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7539653778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8660936355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6792144775391</t>
   </si>
   <si>
     <t xml:space="preserve">15.8100280761719</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5110206604004</t>
+    <t xml:space="preserve">15.5110216140747</t>
   </si>
   <si>
     <t xml:space="preserve">15.3802042007446</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0064449310303</t>
+    <t xml:space="preserve">15.0064458847046</t>
   </si>
   <si>
     <t xml:space="preserve">14.8008785247803</t>
@@ -3128,7 +3128,7 @@
     <t xml:space="preserve">14.6700620651245</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4271183013916</t>
+    <t xml:space="preserve">14.4271173477173</t>
   </si>
   <si>
     <t xml:space="preserve">14.5766229629517</t>
@@ -3158,13 +3158,13 @@
     <t xml:space="preserve">15.0811967849731</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5670852661133</t>
+    <t xml:space="preserve">15.567084312439</t>
   </si>
   <si>
     <t xml:space="preserve">15.716588973999</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6605253219604</t>
+    <t xml:space="preserve">15.6605262756348</t>
   </si>
   <si>
     <t xml:space="preserve">15.1933259963989</t>
@@ -3173,13 +3173,13 @@
     <t xml:space="preserve">15.3988933563232</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4175806045532</t>
+    <t xml:space="preserve">15.4175815582275</t>
   </si>
   <si>
     <t xml:space="preserve">15.4362697601318</t>
   </si>
   <si>
-    <t xml:space="preserve">15.137261390686</t>
+    <t xml:space="preserve">15.1372623443604</t>
   </si>
   <si>
     <t xml:space="preserve">15.0438222885132</t>
@@ -3191,7 +3191,7 @@
     <t xml:space="preserve">14.9877586364746</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7261257171631</t>
+    <t xml:space="preserve">14.7261266708374</t>
   </si>
   <si>
     <t xml:space="preserve">14.950382232666</t>
@@ -3206,22 +3206,22 @@
     <t xml:space="preserve">14.3149900436401</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5018701553345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4084310531616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1654872894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.202862739563</t>
+    <t xml:space="preserve">14.5018711090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4084300994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1654863357544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2028617858887</t>
   </si>
   <si>
     <t xml:space="preserve">14.2963027954102</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1281099319458</t>
+    <t xml:space="preserve">14.1281108856201</t>
   </si>
   <si>
     <t xml:space="preserve">13.8291034698486</t>
@@ -3236,19 +3236,19 @@
     <t xml:space="preserve">13.4179677963257</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5487833023071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6422233581543</t>
+    <t xml:space="preserve">13.5487842559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6422243118286</t>
   </si>
   <si>
     <t xml:space="preserve">13.45534324646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3992805480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3245277404785</t>
+    <t xml:space="preserve">13.3992795944214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3245286941528</t>
   </si>
   <si>
     <t xml:space="preserve">13.2497758865356</t>
@@ -3257,7 +3257,7 @@
     <t xml:space="preserve">13.0815839767456</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3432149887085</t>
+    <t xml:space="preserve">13.3432159423828</t>
   </si>
   <si>
     <t xml:space="preserve">13.1937122344971</t>
@@ -3266,7 +3266,7 @@
     <t xml:space="preserve">13.3058395385742</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2589263916016</t>
+    <t xml:space="preserve">14.2589273452759</t>
   </si>
   <si>
     <t xml:space="preserve">14.2776145935059</t>
@@ -3275,7 +3275,7 @@
     <t xml:space="preserve">14.7448139190674</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5575466156006</t>
+    <t xml:space="preserve">16.5575485229492</t>
   </si>
   <si>
     <t xml:space="preserve">16.4641094207764</t>
@@ -3284,13 +3284,13 @@
     <t xml:space="preserve">16.4267311096191</t>
   </si>
   <si>
-    <t xml:space="preserve">16.314603805542</t>
+    <t xml:space="preserve">16.3146018981934</t>
   </si>
   <si>
     <t xml:space="preserve">16.2585391998291</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2398529052734</t>
+    <t xml:space="preserve">16.2398509979248</t>
   </si>
   <si>
     <t xml:space="preserve">16.1837882995605</t>
@@ -3299,13 +3299,13 @@
     <t xml:space="preserve">14.8569412231445</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7074375152588</t>
+    <t xml:space="preserve">14.7074384689331</t>
   </si>
   <si>
     <t xml:space="preserve">14.6887502670288</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3897428512573</t>
+    <t xml:space="preserve">14.389741897583</t>
   </si>
   <si>
     <t xml:space="preserve">14.782190322876</t>
@@ -3326,19 +3326,19 @@
     <t xml:space="preserve">12.9881439208984</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5956964492798</t>
+    <t xml:space="preserve">12.5956954956055</t>
   </si>
   <si>
     <t xml:space="preserve">12.7078247070312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7452001571655</t>
+    <t xml:space="preserve">12.7452011108398</t>
   </si>
   <si>
     <t xml:space="preserve">12.4275054931641</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0442085266113</t>
+    <t xml:space="preserve">13.044207572937</t>
   </si>
   <si>
     <t xml:space="preserve">13.3805913925171</t>
@@ -3365,28 +3365,28 @@
     <t xml:space="preserve">13.9972944259644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0159826278687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6513748168945</t>
+    <t xml:space="preserve">14.015983581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6513738632202</t>
   </si>
   <si>
     <t xml:space="preserve">15.0251340866089</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4736442565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.903468132019</t>
+    <t xml:space="preserve">15.4736452102661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9034700393677</t>
   </si>
   <si>
     <t xml:space="preserve">16.482795715332</t>
   </si>
   <si>
-    <t xml:space="preserve">16.912618637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8565578460693</t>
+    <t xml:space="preserve">16.9126205444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8565559387207</t>
   </si>
   <si>
     <t xml:space="preserve">16.9499950408936</t>
@@ -3395,7 +3395,7 @@
     <t xml:space="preserve">16.8752422332764</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0434341430664</t>
+    <t xml:space="preserve">17.043436050415</t>
   </si>
   <si>
     <t xml:space="preserve">15.9969091415405</t>
@@ -3407,7 +3407,7 @@
     <t xml:space="preserve">15.5483961105347</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6418361663818</t>
+    <t xml:space="preserve">15.6418380737305</t>
   </si>
   <si>
     <t xml:space="preserve">16.4080429077148</t>
@@ -3419,13 +3419,13 @@
     <t xml:space="preserve">16.6790199279785</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5855808258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8002967834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7068576812744</t>
+    <t xml:space="preserve">16.585578918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8002986907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.706859588623</t>
   </si>
   <si>
     <t xml:space="preserve">16.211820602417</t>
@@ -3434,19 +3434,19 @@
     <t xml:space="preserve">15.3708620071411</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3052597045898</t>
+    <t xml:space="preserve">16.3052616119385</t>
   </si>
   <si>
     <t xml:space="preserve">16.0249404907227</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1273384094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9404582977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6134185791016</t>
+    <t xml:space="preserve">18.1273365020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9404602050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6134204864502</t>
   </si>
   <si>
     <t xml:space="preserve">17.7070121765137</t>
@@ -69258,25 +69258,25 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45966.691087963</v>
+        <v>45967.6910069444</v>
       </c>
       <c r="B2505" t="n">
-        <v>2656</v>
+        <v>3894</v>
       </c>
       <c r="C2505" t="n">
-        <v>14.1000003814697</v>
+        <v>13.8999996185303</v>
       </c>
       <c r="D2505" t="n">
-        <v>13.8500003814697</v>
+        <v>13.75</v>
       </c>
       <c r="E2505" t="n">
-        <v>14.1000003814697</v>
+        <v>13.8999996185303</v>
       </c>
       <c r="F2505" t="n">
-        <v>14</v>
+        <v>13.75</v>
       </c>
       <c r="G2505" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>

--- a/data/SAB.MI.xlsx
+++ b/data/SAB.MI.xlsx
@@ -38,64 +38,64 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56568050384521</t>
+    <t xml:space="preserve">8.5656795501709</t>
   </si>
   <si>
     <t xml:space="preserve">SAB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61822891235352</t>
+    <t xml:space="preserve">8.61822986602783</t>
   </si>
   <si>
     <t xml:space="preserve">8.4831018447876</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33295917510986</t>
+    <t xml:space="preserve">8.33295822143555</t>
   </si>
   <si>
     <t xml:space="preserve">8.37049388885498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31794357299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25788688659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16029262542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88252735137939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52969026565552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66482019424438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62728548049927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61226987838745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73989295959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75490665435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76992034912109</t>
+    <t xml:space="preserve">8.31794452667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25788593292236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16029357910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88252830505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52969121932983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66482067108154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62728452682495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61227083206177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73989152908325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75490617752075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76992177963257</t>
   </si>
   <si>
     <t xml:space="preserve">7.89754343032837</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6197772026062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79995012283325</t>
+    <t xml:space="preserve">7.61977672576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79994916915894</t>
   </si>
   <si>
     <t xml:space="preserve">7.72487735748291</t>
@@ -104,19 +104,19 @@
     <t xml:space="preserve">7.65731382369995</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50716876983643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34201145172119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54470682144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39080762863159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58224153518677</t>
+    <t xml:space="preserve">7.5071702003479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34201240539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54470539093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39080905914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58224248886108</t>
   </si>
   <si>
     <t xml:space="preserve">7.82247161865234</t>
@@ -128,43 +128,43 @@
     <t xml:space="preserve">8.11525058746338</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95760011672974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06270122528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03267097473145</t>
+    <t xml:space="preserve">7.95760107040405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06269931793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03267288208008</t>
   </si>
   <si>
     <t xml:space="preserve">7.92006397247314</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77742862701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86751174926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80745697021484</t>
+    <t xml:space="preserve">7.777428150177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86751461029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80745601654053</t>
   </si>
   <si>
     <t xml:space="preserve">7.98762893676758</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04017925262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99513578414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96510601043701</t>
+    <t xml:space="preserve">8.0401782989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99513483047485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96510696411133</t>
   </si>
   <si>
     <t xml:space="preserve">7.90504932403564</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93507814407349</t>
+    <t xml:space="preserve">7.9350790977478</t>
   </si>
   <si>
     <t xml:space="preserve">7.89003610610962</t>
@@ -173,88 +173,88 @@
     <t xml:space="preserve">7.94258499145508</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82997751235962</t>
+    <t xml:space="preserve">7.8299765586853</t>
   </si>
   <si>
     <t xml:space="preserve">7.81496381759644</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73238372802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64980602264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71737051010132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67232751846313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6347918510437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51467847824097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64230012893677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56722640991211</t>
+    <t xml:space="preserve">7.73238515853882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64980506896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71737098693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67232799530029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63479089736938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51467657089233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64229965209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56722784042358</t>
   </si>
   <si>
     <t xml:space="preserve">7.70235633850098</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74739837646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46963310241699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69484949111938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49215459823608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47338724136353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43585109710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50341749191284</t>
+    <t xml:space="preserve">7.74740028381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46963214874268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69484996795654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4921555519104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47338819503784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43585252761841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50341653823853</t>
   </si>
   <si>
     <t xml:space="preserve">7.48089504241943</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59725475311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4283447265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38705539703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37204074859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3194899559021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28195524215698</t>
+    <t xml:space="preserve">7.59725618362427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42834424972534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38705587387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37204027175903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31949090957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28195333480835</t>
   </si>
   <si>
     <t xml:space="preserve">7.52122116088867</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80534029006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75009489059448</t>
+    <t xml:space="preserve">7.80533933639526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75009441375732</t>
   </si>
   <si>
     <t xml:space="preserve">7.75798606872559</t>
@@ -266,37 +266,37 @@
     <t xml:space="preserve">7.86058616638184</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69879484176636</t>
+    <t xml:space="preserve">7.69879388809204</t>
   </si>
   <si>
     <t xml:space="preserve">7.58435869216919</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68695688247681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57646703720093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53700637817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49754524230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28445672988892</t>
+    <t xml:space="preserve">7.68695735931396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57646751403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53700542449951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49754571914673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28445720672607</t>
   </si>
   <si>
     <t xml:space="preserve">6.92536401748657</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07926082611084</t>
+    <t xml:space="preserve">7.079261302948</t>
   </si>
   <si>
     <t xml:space="preserve">7.22921180725098</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45808458328247</t>
+    <t xml:space="preserve">7.45808410644531</t>
   </si>
   <si>
     <t xml:space="preserve">7.26078033447266</t>
@@ -308,37 +308,37 @@
     <t xml:space="preserve">7.26472663879395</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34759426116943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4699239730835</t>
+    <t xml:space="preserve">7.34759521484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46992206573486</t>
   </si>
   <si>
     <t xml:space="preserve">7.36732530593872</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37916326522827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13450622558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18975067138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1029372215271</t>
+    <t xml:space="preserve">7.37916421890259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1345067024231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18975114822388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10293817520142</t>
   </si>
   <si>
     <t xml:space="preserve">7.15029144287109</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10688400268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20553541183472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18185949325562</t>
+    <t xml:space="preserve">7.10688352584839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20553636550903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18185901641846</t>
   </si>
   <si>
     <t xml:space="preserve">7.22131967544556</t>
@@ -347,28 +347,28 @@
     <t xml:space="preserve">7.19369745254517</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24894237518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19764280319214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18580484390259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22526550292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20948219299316</t>
+    <t xml:space="preserve">7.24894285202026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19764423370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18580436706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22526502609253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20948171615601</t>
   </si>
   <si>
     <t xml:space="preserve">7.31602621078491</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21342802047729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16607475280762</t>
+    <t xml:space="preserve">7.21342945098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16607522964478</t>
   </si>
   <si>
     <t xml:space="preserve">7.24499750137329</t>
@@ -377,52 +377,52 @@
     <t xml:space="preserve">7.13055992126465</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11082935333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17791414260864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23315811157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27656555175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30024147033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29234886169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24104976654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11872243881226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09504508972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00428676605225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9450945854187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93325614929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09899044036865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15423583984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13845252990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1581826210022</t>
+    <t xml:space="preserve">7.11083030700684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17791318893433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23315858840942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27656507492065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30024194717407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29234933853149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.241051197052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11872291564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09504556655884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00428581237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94509506225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93325567245483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09899187088013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15423631668091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13845205307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15818166732788</t>
   </si>
   <si>
     <t xml:space="preserve">7.05558490753174</t>
@@ -431,73 +431,73 @@
     <t xml:space="preserve">7.07136917114258</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06742238998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02401638031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.047691822052</t>
+    <t xml:space="preserve">7.06742334365845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0240159034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04769229888916</t>
   </si>
   <si>
     <t xml:space="preserve">7.0634765625</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08320808410645</t>
+    <t xml:space="preserve">7.0832085609436</t>
   </si>
   <si>
     <t xml:space="preserve">7.05163908004761</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04374647140503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03190851211548</t>
+    <t xml:space="preserve">7.04374694824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03190898895264</t>
   </si>
   <si>
     <t xml:space="preserve">7.05953073501587</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03585433959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17396783828735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90563344955444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91352701187134</t>
+    <t xml:space="preserve">7.03585386276245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17396688461304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9056339263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91352605819702</t>
   </si>
   <si>
     <t xml:space="preserve">6.93720197677612</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92141819000244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94114875793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9687705039978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14239978790283</t>
+    <t xml:space="preserve">6.9214186668396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94114923477173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96877098083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14239835739136</t>
   </si>
   <si>
     <t xml:space="preserve">7.45019197463989</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7935004234314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92372179031372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04999542236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20783805847168</t>
+    <t xml:space="preserve">7.79350185394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92372274398804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0499963760376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.207839012146</t>
   </si>
   <si>
     <t xml:space="preserve">8.16837787628174</t>
@@ -509,19 +509,19 @@
     <t xml:space="preserve">8.19994735717773</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06578063964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1289176940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17626953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32622051239014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55509376525879</t>
+    <t xml:space="preserve">8.06578159332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12891864776611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17627143859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32622146606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55509471893311</t>
   </si>
   <si>
     <t xml:space="preserve">8.56298542022705</t>
@@ -536,19 +536,19 @@
     <t xml:space="preserve">8.39725112915039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42092800140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44460296630859</t>
+    <t xml:space="preserve">8.42092704772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44460391998291</t>
   </si>
   <si>
     <t xml:space="preserve">8.40514278411865</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26308441162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18416309356689</t>
+    <t xml:space="preserve">8.26308536529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18416213989258</t>
   </si>
   <si>
     <t xml:space="preserve">8.30254554748535</t>
@@ -557,19 +557,19 @@
     <t xml:space="preserve">8.22362327575684</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2867603302002</t>
+    <t xml:space="preserve">8.28676128387451</t>
   </si>
   <si>
     <t xml:space="preserve">8.25519180297852</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34989833831787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31043815612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36568355560303</t>
+    <t xml:space="preserve">8.34989929199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31043720245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36568260192871</t>
   </si>
   <si>
     <t xml:space="preserve">8.33411502838135</t>
@@ -578,10 +578,10 @@
     <t xml:space="preserve">8.34200477600098</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46038913726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62612533569336</t>
+    <t xml:space="preserve">8.46038722991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62612342834473</t>
   </si>
   <si>
     <t xml:space="preserve">8.74450588226318</t>
@@ -596,16 +596,16 @@
     <t xml:space="preserve">9.23381900787354</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30484771728516</t>
+    <t xml:space="preserve">9.30484867095947</t>
   </si>
   <si>
     <t xml:space="preserve">9.26538753509521</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1627893447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19435882568359</t>
+    <t xml:space="preserve">9.16279029846191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19435787200928</t>
   </si>
   <si>
     <t xml:space="preserve">9.24960327148438</t>
@@ -617,61 +617,61 @@
     <t xml:space="preserve">9.36798572540283</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54950523376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67577934265137</t>
+    <t xml:space="preserve">9.54950428009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67577838897705</t>
   </si>
   <si>
     <t xml:space="preserve">9.7468090057373</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2203378677368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4807786941528</t>
+    <t xml:space="preserve">10.2203388214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4807796478271</t>
   </si>
   <si>
     <t xml:space="preserve">10.4571018218994</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2913684844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2597990036011</t>
+    <t xml:space="preserve">10.2913675308228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2597970962524</t>
   </si>
   <si>
     <t xml:space="preserve">10.1493072509766</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0861721038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0151414871216</t>
+    <t xml:space="preserve">10.0861711502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0151424407959</t>
   </si>
   <si>
     <t xml:space="preserve">10.1019563674927</t>
   </si>
   <si>
-    <t xml:space="preserve">10.165093421936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0546026229858</t>
+    <t xml:space="preserve">10.1650915145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0546016693115</t>
   </si>
   <si>
     <t xml:space="preserve">10.1808776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1177396774292</t>
+    <t xml:space="preserve">10.1177406311035</t>
   </si>
   <si>
     <t xml:space="preserve">10.1887693405151</t>
   </si>
   <si>
-    <t xml:space="preserve">10.070387840271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1098480224609</t>
+    <t xml:space="preserve">10.0703868865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1098489761353</t>
   </si>
   <si>
     <t xml:space="preserve">10.0230340957642</t>
@@ -680,91 +680,91 @@
     <t xml:space="preserve">10.496563911438</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4176416397095</t>
+    <t xml:space="preserve">10.4176397323608</t>
   </si>
   <si>
     <t xml:space="preserve">10.3150434494019</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7333269119263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4492111206055</t>
+    <t xml:space="preserve">10.7333278656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4492101669312</t>
   </si>
   <si>
     <t xml:space="preserve">10.5597009658813</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6386213302612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.591269493103</t>
+    <t xml:space="preserve">10.6386203765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5912685394287</t>
   </si>
   <si>
     <t xml:space="preserve">11.0095539093018</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8832788467407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3410234451294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0592088699341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9171514511108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0513181686401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6882801055908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6803865432739</t>
+    <t xml:space="preserve">10.8832778930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3410243988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0592079162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9171524047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0513191223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6882791519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6803855895996</t>
   </si>
   <si>
     <t xml:space="preserve">12.2644052505493</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6274442672729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5406303405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6747961044312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7379360198975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4728546142578</t>
+    <t xml:space="preserve">12.6274452209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5406312942505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6747970581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7379341125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4728565216064</t>
   </si>
   <si>
     <t xml:space="preserve">12.6518535614014</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8471240997314</t>
+    <t xml:space="preserve">12.8471221923828</t>
   </si>
   <si>
     <t xml:space="preserve">12.8145790100098</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9203491210938</t>
+    <t xml:space="preserve">12.9203481674194</t>
   </si>
   <si>
     <t xml:space="preserve">12.8715314865112</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9366207122803</t>
+    <t xml:space="preserve">12.936619758606</t>
   </si>
   <si>
     <t xml:space="preserve">12.8064413070679</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6437168121338</t>
+    <t xml:space="preserve">12.6437158584595</t>
   </si>
   <si>
     <t xml:space="preserve">12.8227138519287</t>
@@ -773,7 +773,7 @@
     <t xml:space="preserve">11.5209150314331</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8463659286499</t>
+    <t xml:space="preserve">11.8463649749756</t>
   </si>
   <si>
     <t xml:space="preserve">11.7812747955322</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">11.805685043335</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1311340332031</t>
+    <t xml:space="preserve">12.1311330795288</t>
   </si>
   <si>
     <t xml:space="preserve">12.0009536743164</t>
@@ -800,7 +800,7 @@
     <t xml:space="preserve">11.9846811294556</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0416355133057</t>
+    <t xml:space="preserve">12.0416345596313</t>
   </si>
   <si>
     <t xml:space="preserve">12.0823163986206</t>
@@ -812,34 +812,34 @@
     <t xml:space="preserve">11.8789100646973</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7161865234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4720993041992</t>
+    <t xml:space="preserve">11.7161855697632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4720983505249</t>
   </si>
   <si>
     <t xml:space="preserve">11.5534601211548</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5860061645508</t>
+    <t xml:space="preserve">11.5860052108765</t>
   </si>
   <si>
     <t xml:space="preserve">11.7975473403931</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8951845169067</t>
+    <t xml:space="preserve">11.8951835632324</t>
   </si>
   <si>
     <t xml:space="preserve">12.0904512405396</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1636791229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0741815567017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2287693023682</t>
+    <t xml:space="preserve">12.1636781692505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.074179649353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2287673950195</t>
   </si>
   <si>
     <t xml:space="preserve">12.1392698287964</t>
@@ -848,13 +848,13 @@
     <t xml:space="preserve">12.2043609619141</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1880865097046</t>
+    <t xml:space="preserve">12.1880855560303</t>
   </si>
   <si>
     <t xml:space="preserve">12.147406578064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2531785964966</t>
+    <t xml:space="preserve">12.2531766891479</t>
   </si>
   <si>
     <t xml:space="preserve">12.3670845031738</t>
@@ -869,40 +869,40 @@
     <t xml:space="preserve">12.9447574615479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7820320129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8959398269653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0098485946655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9528951644897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8552589416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7332143783569</t>
+    <t xml:space="preserve">12.7820329666138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8959407806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0098476409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9528942108154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8552579879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7332153320312</t>
   </si>
   <si>
     <t xml:space="preserve">12.7738962173462</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9854383468628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2620706558228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6851539611816</t>
+    <t xml:space="preserve">12.9854393005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2620697021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6851558685303</t>
   </si>
   <si>
     <t xml:space="preserve">13.9292430877686</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9943323135376</t>
+    <t xml:space="preserve">13.9943332672119</t>
   </si>
   <si>
     <t xml:space="preserve">13.7502450942993</t>
@@ -911,52 +911,52 @@
     <t xml:space="preserve">13.8153352737427</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8316097259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0187397003174</t>
+    <t xml:space="preserve">13.8316087722778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0187406539917</t>
   </si>
   <si>
     <t xml:space="preserve">14.026876449585</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1814670562744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1570568084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2302837371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.775411605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.320538520813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2961320877075</t>
+    <t xml:space="preserve">14.1814680099487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1570558547974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2302846908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7754125595093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3205404281616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2961311340332</t>
   </si>
   <si>
     <t xml:space="preserve">15.4588556289673</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8249883651733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7924394607544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5076723098755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8493947982788</t>
+    <t xml:space="preserve">15.8249864578247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.792441368103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5076732635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8493986129761</t>
   </si>
   <si>
     <t xml:space="preserve">15.865668296814</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5158090591431</t>
+    <t xml:space="preserve">15.5158109664917</t>
   </si>
   <si>
     <t xml:space="preserve">16.0039825439453</t>
@@ -965,22 +965,22 @@
     <t xml:space="preserve">16.2643451690674</t>
   </si>
   <si>
-    <t xml:space="preserve">16.776927947998</t>
+    <t xml:space="preserve">16.7769260406494</t>
   </si>
   <si>
     <t xml:space="preserve">16.9559230804443</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4115524291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0454216003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0787220001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6475028991699</t>
+    <t xml:space="preserve">17.4115562438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0454235076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0787239074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6475048065186</t>
   </si>
   <si>
     <t xml:space="preserve">18.0217723846436</t>
@@ -992,28 +992,28 @@
     <t xml:space="preserve">18.1275424957275</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2984027862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4123115539551</t>
+    <t xml:space="preserve">18.2984046936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4123096466064</t>
   </si>
   <si>
     <t xml:space="preserve">18.1682243347168</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1600894927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9160041809082</t>
+    <t xml:space="preserve">18.1600875854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9160022735596</t>
   </si>
   <si>
     <t xml:space="preserve">17.265100479126</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0861034393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2976474761963</t>
+    <t xml:space="preserve">17.0861053466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2976455688477</t>
   </si>
   <si>
     <t xml:space="preserve">17.0047416687012</t>
@@ -1022,7 +1022,7 @@
     <t xml:space="preserve">17.1267852783203</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8745632171631</t>
+    <t xml:space="preserve">16.8745613098145</t>
   </si>
   <si>
     <t xml:space="preserve">17.0779666900635</t>
@@ -1031,31 +1031,31 @@
     <t xml:space="preserve">16.8664245605469</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7850608825684</t>
+    <t xml:space="preserve">16.785062789917</t>
   </si>
   <si>
     <t xml:space="preserve">16.988468170166</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5979290008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9152412414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8338832855225</t>
+    <t xml:space="preserve">16.5979309082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9152431488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8338794708252</t>
   </si>
   <si>
     <t xml:space="preserve">16.9640617370605</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8826999664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9233779907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1349239349365</t>
+    <t xml:space="preserve">16.8826961517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9233798980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1349220275879</t>
   </si>
   <si>
     <t xml:space="preserve">17.0698299407959</t>
@@ -1064,28 +1064,28 @@
     <t xml:space="preserve">17.1674652099609</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6637783050537</t>
+    <t xml:space="preserve">17.6637763977051</t>
   </si>
   <si>
     <t xml:space="preserve">18.2251777648926</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8598022460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.06321144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7052173614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6319904327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7377605438232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7133541107178</t>
+    <t xml:space="preserve">18.8598041534424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0632095336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7052154541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.631986618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7377624511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7133522033691</t>
   </si>
   <si>
     <t xml:space="preserve">18.59130859375</t>
@@ -1097,61 +1097,61 @@
     <t xml:space="preserve">18.6157169342041</t>
   </si>
   <si>
-    <t xml:space="preserve">18.217041015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2089042663574</t>
+    <t xml:space="preserve">18.2170391082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2089061737061</t>
   </si>
   <si>
     <t xml:space="preserve">18.4611301422119</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5417327880859</t>
+    <t xml:space="preserve">17.5417346954346</t>
   </si>
   <si>
     <t xml:space="preserve">16.9071083068848</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4758853912354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3945255279541</t>
+    <t xml:space="preserve">16.475887298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3945236206055</t>
   </si>
   <si>
     <t xml:space="preserve">16.1097545623779</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3619766235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2806186676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3782520294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1992530822754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2236633300781</t>
+    <t xml:space="preserve">16.3619804382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2806167602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3782482147217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.199254989624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2236652374268</t>
   </si>
   <si>
     <t xml:space="preserve">16.2724800109863</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6792907714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3131580352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.09348487854</t>
+    <t xml:space="preserve">16.679292678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.313159942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0934829711914</t>
   </si>
   <si>
     <t xml:space="preserve">15.9470300674438</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1911144256592</t>
+    <t xml:space="preserve">16.1911163330078</t>
   </si>
   <si>
     <t xml:space="preserve">16.3538417816162</t>
@@ -1166,49 +1166,49 @@
     <t xml:space="preserve">15.1822233200073</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9706811904907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1008605957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.873046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2221479415894</t>
+    <t xml:space="preserve">14.970682144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1008615493774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8730487823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.222146987915</t>
   </si>
   <si>
     <t xml:space="preserve">13.8478803634644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8893184661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1984958648682</t>
+    <t xml:space="preserve">14.8893194198608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1984968185425</t>
   </si>
   <si>
     <t xml:space="preserve">15.3937654495239</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5402183532715</t>
+    <t xml:space="preserve">15.5402173995972</t>
   </si>
   <si>
     <t xml:space="preserve">14.9381380081177</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5964136123657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4011449813843</t>
+    <t xml:space="preserve">14.59641456604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4011430740356</t>
   </si>
   <si>
     <t xml:space="preserve">14.2058734893799</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1082401275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0594215393066</t>
+    <t xml:space="preserve">14.1082391738892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0594234466553</t>
   </si>
   <si>
     <t xml:space="preserve">13.9129705429077</t>
@@ -1217,19 +1217,19 @@
     <t xml:space="preserve">14.0106048583984</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3197822570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6452312469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7428674697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7265968322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2147693634033</t>
+    <t xml:space="preserve">14.3197832107544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6452331542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7428684234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7265939712524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.214771270752</t>
   </si>
   <si>
     <t xml:space="preserve">14.807957649231</t>
@@ -1241,148 +1241,148 @@
     <t xml:space="preserve">14.9544067382812</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7916851043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2709655761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0032272338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4825077056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9218626022339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.905590057373</t>
+    <t xml:space="preserve">14.7916831970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2709665298462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0032262802124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4825067520142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9218635559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9055910110474</t>
   </si>
   <si>
     <t xml:space="preserve">15.0194988250732</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0520439147949</t>
+    <t xml:space="preserve">15.0520448684692</t>
   </si>
   <si>
     <t xml:space="preserve">16.2562065124512</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7354879379272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8168487548828</t>
+    <t xml:space="preserve">15.7354860305786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8168506622314</t>
   </si>
   <si>
     <t xml:space="preserve">15.62158203125</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9307565689087</t>
+    <t xml:space="preserve">15.9307584762573</t>
   </si>
   <si>
     <t xml:space="preserve">15.6866722106934</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7192153930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7029418945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6703996658325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6053085327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5653524398804</t>
+    <t xml:space="preserve">15.719217300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7029438018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6703977584839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6053104400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5653505325317</t>
   </si>
   <si>
     <t xml:space="preserve">14.9956827163696</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0291919708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0627021789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2470064163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2302532196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5318403244019</t>
+    <t xml:space="preserve">15.0291929244995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0627031326294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2470073699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2302513122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5318422317505</t>
   </si>
   <si>
     <t xml:space="preserve">15.7161464691162</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8669424057007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.582106590271</t>
+    <t xml:space="preserve">15.8669404983521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5821056365967</t>
   </si>
   <si>
     <t xml:space="preserve">15.4983320236206</t>
   </si>
   <si>
-    <t xml:space="preserve">15.481575012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4145555496216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1799869537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0794582366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1129693984985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3589935302734</t>
+    <t xml:space="preserve">15.4815769195557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4145565032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.179988861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0794591903687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1129684448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3589925765991</t>
   </si>
   <si>
     <t xml:space="preserve">14.291974067688</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2584657669067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4595241546631</t>
+    <t xml:space="preserve">14.2584648132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4595260620117</t>
   </si>
   <si>
     <t xml:space="preserve">14.4092597961426</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5600528717041</t>
+    <t xml:space="preserve">14.5600538253784</t>
   </si>
   <si>
     <t xml:space="preserve">13.4039621353149</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4877376556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2364120483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5380020141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4374723434448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.191445350647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5882663726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6887969970703</t>
+    <t xml:space="preserve">13.4877367019653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2364110946655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5380010604858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4374732971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1914443969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5882654190063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6887979507446</t>
   </si>
   <si>
     <t xml:space="preserve">13.4207172393799</t>
@@ -1394,10 +1394,10 @@
     <t xml:space="preserve">13.57151222229</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3201866149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1526384353638</t>
+    <t xml:space="preserve">13.3201856613159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1526374816895</t>
   </si>
   <si>
     <t xml:space="preserve">13.1861476898193</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">13.3034324645996</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8510494232178</t>
+    <t xml:space="preserve">12.8510484695435</t>
   </si>
   <si>
     <t xml:space="preserve">12.6834993362427</t>
@@ -1427,7 +1427,7 @@
     <t xml:space="preserve">12.482439994812</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1473417282104</t>
+    <t xml:space="preserve">12.1473407745361</t>
   </si>
   <si>
     <t xml:space="preserve">12.0803213119507</t>
@@ -1445,19 +1445,19 @@
     <t xml:space="preserve">11.1923084259033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2258186340332</t>
+    <t xml:space="preserve">11.2258176803589</t>
   </si>
   <si>
     <t xml:space="preserve">12.4321737289429</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1191272735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2531671524048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.286678314209</t>
+    <t xml:space="preserve">13.1191282272339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2531681060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2866773605347</t>
   </si>
   <si>
     <t xml:space="preserve">12.7672739028931</t>
@@ -1466,13 +1466,13 @@
     <t xml:space="preserve">13.3536968231201</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9850883483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8007841110229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6332340240479</t>
+    <t xml:space="preserve">12.9850873947144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8007831573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6332330703735</t>
   </si>
   <si>
     <t xml:space="preserve">12.8678035736084</t>
@@ -1484,25 +1484,25 @@
     <t xml:space="preserve">11.6279373168945</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6111822128296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7284679412842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9630355834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.896017074585</t>
+    <t xml:space="preserve">11.6111812591553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7284669876099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9630365371704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8960161209106</t>
   </si>
   <si>
     <t xml:space="preserve">11.6614475250244</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0750246047974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0415143966675</t>
+    <t xml:space="preserve">11.0750226974487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0415134429932</t>
   </si>
   <si>
     <t xml:space="preserve">10.9577388763428</t>
@@ -1523,16 +1523,16 @@
     <t xml:space="preserve">12.3651552200317</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4603881835938</t>
+    <t xml:space="preserve">11.4603872299194</t>
   </si>
   <si>
     <t xml:space="preserve">11.1587982177734</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1252889633179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1755542755127</t>
+    <t xml:space="preserve">11.1252880096436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1755533218384</t>
   </si>
   <si>
     <t xml:space="preserve">11.376612663269</t>
@@ -1550,7 +1550,7 @@
     <t xml:space="preserve">11.7954864501953</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8792610168457</t>
+    <t xml:space="preserve">11.87926197052</t>
   </si>
   <si>
     <t xml:space="preserve">12.1976051330566</t>
@@ -1559,7 +1559,7 @@
     <t xml:space="preserve">12.2478713989258</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0133008956909</t>
+    <t xml:space="preserve">12.0132999420166</t>
   </si>
   <si>
     <t xml:space="preserve">12.1305856704712</t>
@@ -1568,7 +1568,7 @@
     <t xml:space="preserve">12.1808500289917</t>
   </si>
   <si>
-    <t xml:space="preserve">12.381911277771</t>
+    <t xml:space="preserve">12.3819093704224</t>
   </si>
   <si>
     <t xml:space="preserve">12.3316459655762</t>
@@ -1577,7 +1577,7 @@
     <t xml:space="preserve">12.4656848907471</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5997247695923</t>
+    <t xml:space="preserve">12.599723815918</t>
   </si>
   <si>
     <t xml:space="preserve">12.7170095443726</t>
@@ -1586,40 +1586,40 @@
     <t xml:space="preserve">12.8845586776733</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9515790939331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.968334197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2029037475586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7337646484375</t>
+    <t xml:space="preserve">12.9515781402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9683332443237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2029027938843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7337636947632</t>
   </si>
   <si>
     <t xml:space="preserve">12.8175392150879</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6499891281128</t>
+    <t xml:space="preserve">12.6499910354614</t>
   </si>
   <si>
     <t xml:space="preserve">12.7002534866333</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5159492492676</t>
+    <t xml:space="preserve">12.5159482955933</t>
   </si>
   <si>
     <t xml:space="preserve">12.784029006958</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0018434524536</t>
+    <t xml:space="preserve">13.0018444061279</t>
   </si>
   <si>
     <t xml:space="preserve">13.0353536605835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5494604110718</t>
+    <t xml:space="preserve">12.5494585037231</t>
   </si>
   <si>
     <t xml:space="preserve">12.9348230361938</t>
@@ -1628,22 +1628,22 @@
     <t xml:space="preserve">12.9180679321289</t>
   </si>
   <si>
-    <t xml:space="preserve">13.38720703125</t>
+    <t xml:space="preserve">13.3872060775757</t>
   </si>
   <si>
     <t xml:space="preserve">13.6217775344849</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8228368759155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5044927597046</t>
+    <t xml:space="preserve">13.8228349685669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5044918060303</t>
   </si>
   <si>
     <t xml:space="preserve">13.4542274475098</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6385316848755</t>
+    <t xml:space="preserve">13.6385307312012</t>
   </si>
   <si>
     <t xml:space="preserve">13.7223052978516</t>
@@ -1661,10 +1661,10 @@
     <t xml:space="preserve">13.1693935394287</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1023740768433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.499195098877</t>
+    <t xml:space="preserve">13.1023731231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4991941452026</t>
   </si>
   <si>
     <t xml:space="preserve">12.7481775283813</t>
@@ -1676,16 +1676,16 @@
     <t xml:space="preserve">12.3650341033936</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2257108688354</t>
+    <t xml:space="preserve">12.2257099151611</t>
   </si>
   <si>
     <t xml:space="preserve">12.2779569625854</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3127889633179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.295373916626</t>
+    <t xml:space="preserve">12.3127899169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2953729629517</t>
   </si>
   <si>
     <t xml:space="preserve">12.3302030563354</t>
@@ -1703,16 +1703,16 @@
     <t xml:space="preserve">12.4521131515503</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1386318206787</t>
+    <t xml:space="preserve">12.138632774353</t>
   </si>
   <si>
     <t xml:space="preserve">12.0515546798706</t>
   </si>
   <si>
-    <t xml:space="preserve">11.894814491272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2082958221436</t>
+    <t xml:space="preserve">11.8948163986206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2082948684692</t>
   </si>
   <si>
     <t xml:space="preserve">12.8178396224976</t>
@@ -1721,13 +1721,13 @@
     <t xml:space="preserve">12.7655916213989</t>
   </si>
   <si>
-    <t xml:space="preserve">12.643684387207</t>
+    <t xml:space="preserve">12.6436834335327</t>
   </si>
   <si>
     <t xml:space="preserve">12.399866104126</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6262693405151</t>
+    <t xml:space="preserve">12.6262683868408</t>
   </si>
   <si>
     <t xml:space="preserve">12.5391902923584</t>
@@ -1742,7 +1742,7 @@
     <t xml:space="preserve">12.95716381073</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9397478103638</t>
+    <t xml:space="preserve">12.9397487640381</t>
   </si>
   <si>
     <t xml:space="preserve">12.7830076217651</t>
@@ -1751,40 +1751,40 @@
     <t xml:space="preserve">12.6959295272827</t>
   </si>
   <si>
-    <t xml:space="preserve">12.800422668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8875017166138</t>
+    <t xml:space="preserve">12.8004236221313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8875007629395</t>
   </si>
   <si>
     <t xml:space="preserve">12.1560468673706</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0341396331787</t>
+    <t xml:space="preserve">12.0341386795044</t>
   </si>
   <si>
     <t xml:space="preserve">11.7206592559814</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2431259155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7554912567139</t>
+    <t xml:space="preserve">12.2431268692017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7554922103882</t>
   </si>
   <si>
     <t xml:space="preserve">11.6684131622314</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9993095397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0689697265625</t>
+    <t xml:space="preserve">11.9993085861206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0689706802368</t>
   </si>
   <si>
     <t xml:space="preserve">12.1038017272949</t>
   </si>
   <si>
-    <t xml:space="preserve">11.790322303772</t>
+    <t xml:space="preserve">11.7903213500977</t>
   </si>
   <si>
     <t xml:space="preserve">11.842568397522</t>
@@ -1805,10 +1805,10 @@
     <t xml:space="preserve">11.8774003982544</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6509990692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5465049743652</t>
+    <t xml:space="preserve">11.6509981155396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5465059280396</t>
   </si>
   <si>
     <t xml:space="preserve">11.3201017379761</t>
@@ -1826,7 +1826,7 @@
     <t xml:space="preserve">11.3549337387085</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3897647857666</t>
+    <t xml:space="preserve">11.3897638320923</t>
   </si>
   <si>
     <t xml:space="preserve">11.1981935501099</t>
@@ -1835,10 +1835,10 @@
     <t xml:space="preserve">10.9369611740112</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0414543151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8847131729126</t>
+    <t xml:space="preserve">11.0414533615112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8847141265869</t>
   </si>
   <si>
     <t xml:space="preserve">10.8672971725464</t>
@@ -1850,19 +1850,19 @@
     <t xml:space="preserve">10.8324670791626</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6234798431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6060657501221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5886497497559</t>
+    <t xml:space="preserve">10.623480796814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6060647964478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5886507034302</t>
   </si>
   <si>
     <t xml:space="preserve">10.5189876556396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4493246078491</t>
+    <t xml:space="preserve">10.4493255615234</t>
   </si>
   <si>
     <t xml:space="preserve">10.6583118438721</t>
@@ -1877,7 +1877,7 @@
     <t xml:space="preserve">11.1111154556274</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0588684082031</t>
+    <t xml:space="preserve">11.0588693618774</t>
   </si>
   <si>
     <t xml:space="preserve">10.9892072677612</t>
@@ -1895,16 +1895,16 @@
     <t xml:space="preserve">10.7976360321045</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8150510787964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9543762207031</t>
+    <t xml:space="preserve">10.8150520324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9543752670288</t>
   </si>
   <si>
     <t xml:space="preserve">11.0937004089355</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7032432556152</t>
+    <t xml:space="preserve">11.7032442092896</t>
   </si>
   <si>
     <t xml:space="preserve">11.9818935394287</t>
@@ -1913,7 +1913,7 @@
     <t xml:space="preserve">11.9296455383301</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9122314453125</t>
+    <t xml:space="preserve">11.9122304916382</t>
   </si>
   <si>
     <t xml:space="preserve">11.8077373504639</t>
@@ -1922,10 +1922,10 @@
     <t xml:space="preserve">12.2605419158936</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0863876342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9644775390625</t>
+    <t xml:space="preserve">12.0863857269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9644784927368</t>
   </si>
   <si>
     <t xml:space="preserve">11.5290880203247</t>
@@ -1943,7 +1943,7 @@
     <t xml:space="preserve">11.6858291625977</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1908798217773</t>
+    <t xml:space="preserve">12.1908807754517</t>
   </si>
   <si>
     <t xml:space="preserve">12.3476190567017</t>
@@ -1952,16 +1952,16 @@
     <t xml:space="preserve">11.5116729736328</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5987510681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7105588912964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70045757293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49147033691406</t>
+    <t xml:space="preserve">11.5987501144409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7105598449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7004566192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49146938323975</t>
   </si>
   <si>
     <t xml:space="preserve">9.03866767883301</t>
@@ -1973,7 +1973,7 @@
     <t xml:space="preserve">8.42912292480469</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18530464172363</t>
+    <t xml:space="preserve">8.18530559539795</t>
   </si>
   <si>
     <t xml:space="preserve">8.22884368896484</t>
@@ -1988,7 +1988,7 @@
     <t xml:space="preserve">8.49007701873779</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31592178344727</t>
+    <t xml:space="preserve">8.31592082977295</t>
   </si>
   <si>
     <t xml:space="preserve">8.32462978363037</t>
@@ -2000,7 +2000,7 @@
     <t xml:space="preserve">8.38558387756348</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28979778289795</t>
+    <t xml:space="preserve">8.28979873657227</t>
   </si>
   <si>
     <t xml:space="preserve">8.41170692443848</t>
@@ -2012,10 +2012,10 @@
     <t xml:space="preserve">8.638108253479</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69035530090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67294025421143</t>
+    <t xml:space="preserve">8.690354347229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67294120788574</t>
   </si>
   <si>
     <t xml:space="preserve">8.79484939575195</t>
@@ -2024,7 +2024,7 @@
     <t xml:space="preserve">8.96900463104248</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75131034851074</t>
+    <t xml:space="preserve">8.75130939483643</t>
   </si>
   <si>
     <t xml:space="preserve">8.70777130126953</t>
@@ -2036,7 +2036,7 @@
     <t xml:space="preserve">9.18669891357422</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05608177185059</t>
+    <t xml:space="preserve">9.05608081817627</t>
   </si>
   <si>
     <t xml:space="preserve">9.14315986633301</t>
@@ -2045,13 +2045,13 @@
     <t xml:space="preserve">9.23023796081543</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40439319610596</t>
+    <t xml:space="preserve">9.40439224243164</t>
   </si>
   <si>
     <t xml:space="preserve">9.66562652587891</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57854843139648</t>
+    <t xml:space="preserve">9.5785493850708</t>
   </si>
   <si>
     <t xml:space="preserve">9.31731510162354</t>
@@ -2063,58 +2063,58 @@
     <t xml:space="preserve">8.6555233001709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51620006561279</t>
+    <t xml:space="preserve">8.51619911193848</t>
   </si>
   <si>
     <t xml:space="preserve">8.60327911376953</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56844711303711</t>
+    <t xml:space="preserve">8.56844615936279</t>
   </si>
   <si>
     <t xml:space="preserve">9.36085414886475</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83978271484375</t>
+    <t xml:space="preserve">9.83978176116943</t>
   </si>
   <si>
     <t xml:space="preserve">10.01393699646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1010141372681</t>
+    <t xml:space="preserve">10.1010150909424</t>
   </si>
   <si>
     <t xml:space="preserve">9.92685890197754</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88332176208496</t>
+    <t xml:space="preserve">9.88332080841064</t>
   </si>
   <si>
     <t xml:space="preserve">10.0574760437012</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97039890289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7091646194458</t>
+    <t xml:space="preserve">9.97039794921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70916366577148</t>
   </si>
   <si>
     <t xml:space="preserve">9.75270366668701</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6220874786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53501033782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79624271392822</t>
+    <t xml:space="preserve">9.62208652496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53500938415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79624176025391</t>
   </si>
   <si>
     <t xml:space="preserve">10.1880912780762</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2751703262329</t>
+    <t xml:space="preserve">10.2751712799072</t>
   </si>
   <si>
     <t xml:space="preserve">10.5364027023315</t>
@@ -2126,7 +2126,7 @@
     <t xml:space="preserve">11.0153303146362</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7540979385376</t>
+    <t xml:space="preserve">10.7540969848633</t>
   </si>
   <si>
     <t xml:space="preserve">10.4928646087646</t>
@@ -2138,10 +2138,10 @@
     <t xml:space="preserve">10.3622465133667</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3187093734741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1894865036011</t>
+    <t xml:space="preserve">10.3187103271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1894855499268</t>
   </si>
   <si>
     <t xml:space="preserve">11.2765636444092</t>
@@ -2153,10 +2153,10 @@
     <t xml:space="preserve">12.0167245864868</t>
   </si>
   <si>
-    <t xml:space="preserve">12.060263633728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5011930465698</t>
+    <t xml:space="preserve">12.0602626800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5011940002441</t>
   </si>
   <si>
     <t xml:space="preserve">12.0100746154785</t>
@@ -2168,10 +2168,10 @@
     <t xml:space="preserve">11.6975450515747</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4743099212646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2064275741577</t>
+    <t xml:space="preserve">11.4743089675903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2064266204834</t>
   </si>
   <si>
     <t xml:space="preserve">11.4296627044678</t>
@@ -2183,28 +2183,28 @@
     <t xml:space="preserve">11.2510738372803</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5813674926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5367202758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0278387069702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8938961029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1617784500122</t>
+    <t xml:space="preserve">10.5813684463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5367212295532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0278377532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8938970565796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1617794036865</t>
   </si>
   <si>
     <t xml:space="preserve">11.0724849700928</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9207811355591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.188663482666</t>
+    <t xml:space="preserve">11.9207801818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1886625289917</t>
   </si>
   <si>
     <t xml:space="preserve">12.2333097457886</t>
@@ -2228,10 +2228,10 @@
     <t xml:space="preserve">12.0993700027466</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4387826919556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4834299087524</t>
+    <t xml:space="preserve">13.4387817382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4834308624268</t>
   </si>
   <si>
     <t xml:space="preserve">13.9299011230469</t>
@@ -2240,16 +2240,16 @@
     <t xml:space="preserve">13.8406066894531</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0191946029663</t>
+    <t xml:space="preserve">14.0191955566406</t>
   </si>
   <si>
     <t xml:space="preserve">12.9030170440674</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0816059112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0369596481323</t>
+    <t xml:space="preserve">13.0816049575806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.036958694458</t>
   </si>
   <si>
     <t xml:space="preserve">13.7513113021851</t>
@@ -2276,10 +2276,10 @@
     <t xml:space="preserve">13.88525390625</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6442537307739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7781963348389</t>
+    <t xml:space="preserve">14.6442546844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7781953811646</t>
   </si>
   <si>
     <t xml:space="preserve">14.9121370315552</t>
@@ -2294,19 +2294,19 @@
     <t xml:space="preserve">14.4210186004639</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5103139877319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1800212860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8497266769409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8050813674927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.072961807251</t>
+    <t xml:space="preserve">14.5103130340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1800203323364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8497257232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.805079460144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0729637145996</t>
   </si>
   <si>
     <t xml:space="preserve">16.3854942321777</t>
@@ -2315,7 +2315,7 @@
     <t xml:space="preserve">16.9212589263916</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1891384124756</t>
+    <t xml:space="preserve">17.1891403198242</t>
   </si>
   <si>
     <t xml:space="preserve">16.7426681518555</t>
@@ -2324,7 +2324,7 @@
     <t xml:space="preserve">17.7249069213867</t>
   </si>
   <si>
-    <t xml:space="preserve">17.769552230835</t>
+    <t xml:space="preserve">17.7695503234863</t>
   </si>
   <si>
     <t xml:space="preserve">17.8142013549805</t>
@@ -2342,7 +2342,7 @@
     <t xml:space="preserve">18.3946132659912</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5732002258301</t>
+    <t xml:space="preserve">18.5731983184814</t>
   </si>
   <si>
     <t xml:space="preserve">16.6980247497559</t>
@@ -2357,13 +2357,13 @@
     <t xml:space="preserve">18.2160243988037</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9481430053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0196723937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1805000305176</t>
+    <t xml:space="preserve">17.9481410980225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0196704864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1804981231689</t>
   </si>
   <si>
     <t xml:space="preserve">20.5376739501953</t>
@@ -2378,10 +2378,10 @@
     <t xml:space="preserve">20.8055553436279</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0734405517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0912036895752</t>
+    <t xml:space="preserve">21.0734424591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0912017822266</t>
   </si>
   <si>
     <t xml:space="preserve">20.0019092559814</t>
@@ -2390,46 +2390,46 @@
     <t xml:space="preserve">19.8233222961426</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2697944641113</t>
+    <t xml:space="preserve">20.2697925567627</t>
   </si>
   <si>
     <t xml:space="preserve">19.1982612609863</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9126148223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5554389953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6447315216064</t>
+    <t xml:space="preserve">19.9126129150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5554370880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6447334289551</t>
   </si>
   <si>
     <t xml:space="preserve">18.9303798675537</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7162628173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4483814239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4306144714355</t>
+    <t xml:space="preserve">20.7162647247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4483795166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4306163787842</t>
   </si>
   <si>
     <t xml:space="preserve">21.3413219451904</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3235569000244</t>
+    <t xml:space="preserve">22.323558807373</t>
   </si>
   <si>
     <t xml:space="preserve">21.6092052459717</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0556774139404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7877922058105</t>
+    <t xml:space="preserve">22.0556755065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7877941131592</t>
   </si>
   <si>
     <t xml:space="preserve">22.7700290679932</t>
@@ -69339,7 +69339,7 @@
     </row>
     <row r="2508">
       <c r="A2508" s="1" t="n">
-        <v>45971.6926967593</v>
+        <v>45971.3333333333</v>
       </c>
       <c r="B2508" t="n">
         <v>723</v>
@@ -69360,6 +69360,32 @@
         <v>1261</v>
       </c>
       <c r="H2508" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2509">
+      <c r="A2509" s="1" t="n">
+        <v>45972.6909837963</v>
+      </c>
+      <c r="B2509" t="n">
+        <v>3053</v>
+      </c>
+      <c r="C2509" t="n">
+        <v>13.9499998092651</v>
+      </c>
+      <c r="D2509" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="E2509" t="n">
+        <v>13.8999996185303</v>
+      </c>
+      <c r="F2509" t="n">
+        <v>14</v>
+      </c>
+      <c r="G2509" t="s">
+        <v>1262</v>
+      </c>
+      <c r="H2509" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SAB.MI.xlsx
+++ b/data/SAB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1269" uniqueCount="1269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1270" uniqueCount="1270">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,31 +38,31 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56568145751953</t>
+    <t xml:space="preserve">8.56568050384521</t>
   </si>
   <si>
     <t xml:space="preserve">SAB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61823081970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48310279846191</t>
+    <t xml:space="preserve">8.61823177337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4831018447876</t>
   </si>
   <si>
     <t xml:space="preserve">8.33295917510986</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3704948425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31794452667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25788593292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16029262542725</t>
+    <t xml:space="preserve">8.37049388885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31794357299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25788688659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16029357910156</t>
   </si>
   <si>
     <t xml:space="preserve">7.88252830505371</t>
@@ -71,259 +71,259 @@
     <t xml:space="preserve">7.52969074249268</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66481971740723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62728500366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61226892471313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73989295959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75490617752075</t>
+    <t xml:space="preserve">7.6648211479187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62728452682495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61226987838745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73989200592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75490665435791</t>
   </si>
   <si>
     <t xml:space="preserve">7.76992130279541</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89754295349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61977815628052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79994869232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72487878799438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65731334686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50717067718506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34201192855835</t>
+    <t xml:space="preserve">7.89754247665405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6197772026062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79994964599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72487783432007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65731287002563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50716972351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34201145172119</t>
   </si>
   <si>
     <t xml:space="preserve">7.54470634460449</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39081048965454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58224153518677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82247066497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08522319793701</t>
+    <t xml:space="preserve">7.39080905914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58224201202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82247114181519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0852222442627</t>
   </si>
   <si>
     <t xml:space="preserve">8.1152515411377</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95760011672974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06269931793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03267097473145</t>
+    <t xml:space="preserve">7.95759963989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06270122528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03267002105713</t>
   </si>
   <si>
     <t xml:space="preserve">7.92006492614746</t>
   </si>
   <si>
-    <t xml:space="preserve">7.777428150177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86751461029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80745649337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98762941360474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04017925262451</t>
+    <t xml:space="preserve">7.77742671966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86751317977905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80745697021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98762893676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0401782989502</t>
   </si>
   <si>
     <t xml:space="preserve">7.99513530731201</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96510696411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9050498008728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93507862091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8900351524353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94258451461792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82997846603394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81496381759644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73238611221313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6498064994812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71737003326416</t>
+    <t xml:space="preserve">7.96510744094849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90504884719849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93507719039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89003658294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94258546829224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82997941970825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81496238708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73238468170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64980554580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71737098693848</t>
   </si>
   <si>
     <t xml:space="preserve">7.67232847213745</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6347918510437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51467704772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64229917526245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56722688674927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70235586166382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.747398853302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46963310241699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69484758377075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49215412139893</t>
+    <t xml:space="preserve">7.63479232788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51467800140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64229822158813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56722640991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70235633850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74739933013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46963357925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69484853744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49215459823608</t>
   </si>
   <si>
     <t xml:space="preserve">7.47338628768921</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43585205078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50341653823853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48089361190796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59725570678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4283447265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38705444335938</t>
+    <t xml:space="preserve">7.43585157394409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50341606140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48089456558228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59725666046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42834424972534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38705539703369</t>
   </si>
   <si>
     <t xml:space="preserve">7.37204122543335</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31949090957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28195571899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52122116088867</t>
+    <t xml:space="preserve">7.31949138641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28195476531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52122068405151</t>
   </si>
   <si>
     <t xml:space="preserve">7.80534029006958</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75009441375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75798511505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81323099136353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86058521270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69879579544067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58435916900635</t>
+    <t xml:space="preserve">7.75009346008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75798654556274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81323146820068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8605842590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69879484176636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58435964584351</t>
   </si>
   <si>
     <t xml:space="preserve">7.68695735931396</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57646751403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53700637817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49754476547241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28445768356323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92536354064941</t>
+    <t xml:space="preserve">7.57646656036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53700590133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49754428863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28445672988892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92536401748657</t>
   </si>
   <si>
     <t xml:space="preserve">7.07926225662231</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22921228408813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45808458328247</t>
+    <t xml:space="preserve">7.22921180725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45808410644531</t>
   </si>
   <si>
     <t xml:space="preserve">7.2607798576355</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37127017974854</t>
+    <t xml:space="preserve">7.37127113342285</t>
   </si>
   <si>
     <t xml:space="preserve">7.2647271156311</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34759473800659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46992254257202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36732482910156</t>
+    <t xml:space="preserve">7.34759521484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46992349624634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36732530593872</t>
   </si>
   <si>
     <t xml:space="preserve">7.37916326522827</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1345067024231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18975067138672</t>
+    <t xml:space="preserve">7.13450717926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18975114822388</t>
   </si>
   <si>
     <t xml:space="preserve">7.10293769836426</t>
@@ -332,85 +332,85 @@
     <t xml:space="preserve">7.15029048919678</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10688400268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20553588867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18185997009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22132015228271</t>
+    <t xml:space="preserve">7.10688352584839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20553636550903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18185901641846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22131872177124</t>
   </si>
   <si>
     <t xml:space="preserve">7.19369745254517</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24894237518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1976432800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18580484390259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22526550292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20948266983032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31602668762207</t>
+    <t xml:space="preserve">7.24894285202026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19764375686646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18580532073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.225266456604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20948171615601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31602621078491</t>
   </si>
   <si>
     <t xml:space="preserve">7.21342802047729</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16607570648193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24499702453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13055944442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11083030700684</t>
+    <t xml:space="preserve">7.16607427597046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24499750137329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13056039810181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11082983016968</t>
   </si>
   <si>
     <t xml:space="preserve">7.17791366577148</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23315763473511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27656412124634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30024194717407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29234933853149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24105072021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11872243881226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09504508972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00428628921509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94509506225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93325662612915</t>
+    <t xml:space="preserve">7.23315858840942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2765645980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30024099349976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29234981536865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24104976654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11872291564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09504556655884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00428581237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9450945854187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93325567245483</t>
   </si>
   <si>
     <t xml:space="preserve">7.09899187088013</t>
@@ -419,10 +419,10 @@
     <t xml:space="preserve">7.15423679351807</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13845205307007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15818214416504</t>
+    <t xml:space="preserve">7.13845300674438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15818309783936</t>
   </si>
   <si>
     <t xml:space="preserve">7.05558443069458</t>
@@ -431,13 +431,13 @@
     <t xml:space="preserve">7.07136869430542</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06742334365845</t>
+    <t xml:space="preserve">7.06742238998413</t>
   </si>
   <si>
     <t xml:space="preserve">7.0240159034729</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04769325256348</t>
+    <t xml:space="preserve">7.04769229888916</t>
   </si>
   <si>
     <t xml:space="preserve">7.06347703933716</t>
@@ -452,10 +452,10 @@
     <t xml:space="preserve">7.04374694824219</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03190803527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05953025817871</t>
+    <t xml:space="preserve">7.03190755844116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05953121185303</t>
   </si>
   <si>
     <t xml:space="preserve">7.03585433959961</t>
@@ -464,25 +464,25 @@
     <t xml:space="preserve">7.1739673614502</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9056339263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91352701187134</t>
+    <t xml:space="preserve">6.90563344955444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91352605819702</t>
   </si>
   <si>
     <t xml:space="preserve">6.93720245361328</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92141819000244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94114875793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96877145767212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14239835739136</t>
+    <t xml:space="preserve">6.9214186668396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94114828109741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96877098083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1423978805542</t>
   </si>
   <si>
     <t xml:space="preserve">7.45019245147705</t>
@@ -491,31 +491,31 @@
     <t xml:space="preserve">7.69484949111938</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79350090026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92372274398804</t>
+    <t xml:space="preserve">7.79350185394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9237208366394</t>
   </si>
   <si>
     <t xml:space="preserve">8.0499963760376</t>
   </si>
   <si>
-    <t xml:space="preserve">8.207839012146</t>
+    <t xml:space="preserve">8.20783996582031</t>
   </si>
   <si>
     <t xml:space="preserve">8.16837787628174</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08945560455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19994640350342</t>
+    <t xml:space="preserve">8.08945655822754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19994735717773</t>
   </si>
   <si>
     <t xml:space="preserve">8.06578063964844</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12891864776611</t>
+    <t xml:space="preserve">8.12891674041748</t>
   </si>
   <si>
     <t xml:space="preserve">8.17627048492432</t>
@@ -527,25 +527,25 @@
     <t xml:space="preserve">8.55509281158447</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56298637390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42881965637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35778903961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39725208282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42092704772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44460391998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40514278411865</t>
+    <t xml:space="preserve">8.56298542022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42881870269775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35778999328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39725112915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42092800140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44460296630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40514087677002</t>
   </si>
   <si>
     <t xml:space="preserve">8.26308441162109</t>
@@ -554,7 +554,7 @@
     <t xml:space="preserve">8.18416213989258</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30254459381104</t>
+    <t xml:space="preserve">8.30254554748535</t>
   </si>
   <si>
     <t xml:space="preserve">8.22362327575684</t>
@@ -563,7 +563,7 @@
     <t xml:space="preserve">8.2867603302002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25519275665283</t>
+    <t xml:space="preserve">8.25519180297852</t>
   </si>
   <si>
     <t xml:space="preserve">8.34989738464355</t>
@@ -575,7 +575,7 @@
     <t xml:space="preserve">8.36568260192871</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33411312103271</t>
+    <t xml:space="preserve">8.33411407470703</t>
   </si>
   <si>
     <t xml:space="preserve">8.34200572967529</t>
@@ -596,7 +596,7 @@
     <t xml:space="preserve">9.0049467086792</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23381996154785</t>
+    <t xml:space="preserve">9.23381900787354</t>
   </si>
   <si>
     <t xml:space="preserve">9.30484867095947</t>
@@ -605,10 +605,10 @@
     <t xml:space="preserve">9.26538753509521</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16278839111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19435691833496</t>
+    <t xml:space="preserve">9.1627893447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19435787200928</t>
   </si>
   <si>
     <t xml:space="preserve">9.24960327148438</t>
@@ -620,10 +620,10 @@
     <t xml:space="preserve">9.36798572540283</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54950523376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67577838897705</t>
+    <t xml:space="preserve">9.54950428009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67578029632568</t>
   </si>
   <si>
     <t xml:space="preserve">9.7468090057373</t>
@@ -632,19 +632,19 @@
     <t xml:space="preserve">10.2203388214111</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4807786941528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.457103729248</t>
+    <t xml:space="preserve">10.4807796478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4571027755737</t>
   </si>
   <si>
     <t xml:space="preserve">10.2913675308228</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2597980499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1493062973022</t>
+    <t xml:space="preserve">10.2597990036011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1493082046509</t>
   </si>
   <si>
     <t xml:space="preserve">10.0861711502075</t>
@@ -656,28 +656,28 @@
     <t xml:space="preserve">10.101957321167</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1650943756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0546035766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1808776855469</t>
+    <t xml:space="preserve">10.165093421936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0546026229858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1808767318726</t>
   </si>
   <si>
     <t xml:space="preserve">10.1177396774292</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1887702941895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0703887939453</t>
+    <t xml:space="preserve">10.1887683868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0703868865967</t>
   </si>
   <si>
     <t xml:space="preserve">10.1098489761353</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0230321884155</t>
+    <t xml:space="preserve">10.0230350494385</t>
   </si>
   <si>
     <t xml:space="preserve">10.496563911438</t>
@@ -695,46 +695,46 @@
     <t xml:space="preserve">10.4492101669312</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5597009658813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6386213302612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5912704467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0095520019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8832788467407</t>
+    <t xml:space="preserve">10.559700012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6386203765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.591269493103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0095529556274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.883279800415</t>
   </si>
   <si>
     <t xml:space="preserve">11.3410224914551</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0592088699341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9171514511108</t>
+    <t xml:space="preserve">12.0592107772827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9171504974365</t>
   </si>
   <si>
     <t xml:space="preserve">12.0513181686401</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6882791519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6803865432739</t>
+    <t xml:space="preserve">11.6882801055908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6803855895996</t>
   </si>
   <si>
     <t xml:space="preserve">12.2644062042236</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6274442672729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5406312942505</t>
+    <t xml:space="preserve">12.6274452209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5406293869019</t>
   </si>
   <si>
     <t xml:space="preserve">12.6747961044312</t>
@@ -743,31 +743,31 @@
     <t xml:space="preserve">12.7379341125488</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4728555679321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6518526077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8471231460571</t>
+    <t xml:space="preserve">12.4728565216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6518535614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8471212387085</t>
   </si>
   <si>
     <t xml:space="preserve">12.8145780563354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9203481674194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8715324401855</t>
+    <t xml:space="preserve">12.9203500747681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8715314865112</t>
   </si>
   <si>
     <t xml:space="preserve">12.9366207122803</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8064422607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6437177658081</t>
+    <t xml:space="preserve">12.8064403533936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6437168121338</t>
   </si>
   <si>
     <t xml:space="preserve">12.8227138519287</t>
@@ -782,55 +782,55 @@
     <t xml:space="preserve">11.7812757492065</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9114561080933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9277267456055</t>
+    <t xml:space="preserve">11.9114551544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9277276992798</t>
   </si>
   <si>
     <t xml:space="preserve">11.9602718353271</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8056831359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1311340332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0009546279907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9846811294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.041633605957</t>
+    <t xml:space="preserve">11.805685043335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1311330795288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0009536743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9846830368042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0416345596313</t>
   </si>
   <si>
     <t xml:space="preserve">12.0823154449463</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9765462875366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8789110183716</t>
+    <t xml:space="preserve">11.9765453338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8789100646973</t>
   </si>
   <si>
     <t xml:space="preserve">11.7161846160889</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4720983505249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5534620285034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5860052108765</t>
+    <t xml:space="preserve">11.4720973968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5534601211548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5860061645508</t>
   </si>
   <si>
     <t xml:space="preserve">11.7975482940674</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8951826095581</t>
+    <t xml:space="preserve">11.8951835632324</t>
   </si>
   <si>
     <t xml:space="preserve">12.0904521942139</t>
@@ -842,16 +842,16 @@
     <t xml:space="preserve">12.074179649353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2287673950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1392707824707</t>
+    <t xml:space="preserve">12.2287693023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1392698287964</t>
   </si>
   <si>
     <t xml:space="preserve">12.2043590545654</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1880855560303</t>
+    <t xml:space="preserve">12.1880865097046</t>
   </si>
   <si>
     <t xml:space="preserve">12.147406578064</t>
@@ -860,13 +860,13 @@
     <t xml:space="preserve">12.2531785964966</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3670854568481</t>
+    <t xml:space="preserve">12.3670835494995</t>
   </si>
   <si>
     <t xml:space="preserve">12.4077644348145</t>
   </si>
   <si>
-    <t xml:space="preserve">12.448447227478</t>
+    <t xml:space="preserve">12.4484462738037</t>
   </si>
   <si>
     <t xml:space="preserve">12.9447584152222</t>
@@ -875,10 +875,10 @@
     <t xml:space="preserve">12.7820320129395</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8959398269653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0098457336426</t>
+    <t xml:space="preserve">12.8959407806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0098476409912</t>
   </si>
   <si>
     <t xml:space="preserve">12.9528932571411</t>
@@ -890,76 +890,76 @@
     <t xml:space="preserve">12.7332162857056</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7738952636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9854402542114</t>
+    <t xml:space="preserve">12.7738971710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9854393005371</t>
   </si>
   <si>
     <t xml:space="preserve">13.2620697021484</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6851568222046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9292430877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9943332672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7502460479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8153343200684</t>
+    <t xml:space="preserve">13.6851558685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9292421340942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9943323135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7502450942993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8153371810913</t>
   </si>
   <si>
     <t xml:space="preserve">13.8316087722778</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0187425613403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0268783569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1814661026001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1570568084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2302827835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7754135131836</t>
+    <t xml:space="preserve">14.018741607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0268793106079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1814670562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1570558547974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.230281829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.775411605835</t>
   </si>
   <si>
     <t xml:space="preserve">15.3205413818359</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2961301803589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.458854675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.824987411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7924451828003</t>
+    <t xml:space="preserve">15.2961330413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4588565826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8249864578247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7924432754517</t>
   </si>
   <si>
     <t xml:space="preserve">15.5076723098755</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8493957519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8656711578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5158090591431</t>
+    <t xml:space="preserve">15.8493976593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.865668296814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5158100128174</t>
   </si>
   <si>
     <t xml:space="preserve">16.0039844512939</t>
@@ -974,13 +974,13 @@
     <t xml:space="preserve">16.9559230804443</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4115543365479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0454235076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0787239074707</t>
+    <t xml:space="preserve">17.4115505218506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0454216003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0787258148193</t>
   </si>
   <si>
     <t xml:space="preserve">17.6475048065186</t>
@@ -989,10 +989,10 @@
     <t xml:space="preserve">18.0217704772949</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0543174743652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1275463104248</t>
+    <t xml:space="preserve">18.0543155670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1275444030762</t>
   </si>
   <si>
     <t xml:space="preserve">18.2984027862549</t>
@@ -1001,16 +1001,16 @@
     <t xml:space="preserve">18.4123096466064</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1682224273682</t>
+    <t xml:space="preserve">18.1682243347168</t>
   </si>
   <si>
     <t xml:space="preserve">18.1600875854492</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9160003662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.265100479126</t>
+    <t xml:space="preserve">17.9159984588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2651023864746</t>
   </si>
   <si>
     <t xml:space="preserve">17.0861034393311</t>
@@ -1019,7 +1019,7 @@
     <t xml:space="preserve">17.2976474761963</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0047416687012</t>
+    <t xml:space="preserve">17.0047397613525</t>
   </si>
   <si>
     <t xml:space="preserve">17.1267852783203</t>
@@ -1028,70 +1028,70 @@
     <t xml:space="preserve">16.8745613098145</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0779685974121</t>
+    <t xml:space="preserve">17.0779647827148</t>
   </si>
   <si>
     <t xml:space="preserve">16.8664245605469</t>
   </si>
   <si>
-    <t xml:space="preserve">16.785062789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9884662628174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5979309082031</t>
+    <t xml:space="preserve">16.7850646972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.988468170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5979290008545</t>
   </si>
   <si>
     <t xml:space="preserve">16.9152431488037</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8338813781738</t>
+    <t xml:space="preserve">16.8338794708252</t>
   </si>
   <si>
     <t xml:space="preserve">16.9640598297119</t>
   </si>
   <si>
-    <t xml:space="preserve">16.882698059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9233798980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1349201202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0698318481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1674690246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6637763977051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2251758575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8598041534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0632133483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7052154541016</t>
+    <t xml:space="preserve">16.8826961517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9233779907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1349220275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0698299407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1674671173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6637783050537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2251777648926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8598022460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0632095336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7052135467529</t>
   </si>
   <si>
     <t xml:space="preserve">18.6319885253906</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7377586364746</t>
+    <t xml:space="preserve">18.7377624511719</t>
   </si>
   <si>
     <t xml:space="preserve">18.7133502960205</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5913066864014</t>
+    <t xml:space="preserve">18.59130859375</t>
   </si>
   <si>
     <t xml:space="preserve">18.3065414428711</t>
@@ -1100,10 +1100,10 @@
     <t xml:space="preserve">18.6157169342041</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2170391082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2089023590088</t>
+    <t xml:space="preserve">18.217041015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2089042663574</t>
   </si>
   <si>
     <t xml:space="preserve">18.4611301422119</t>
@@ -1124,13 +1124,13 @@
     <t xml:space="preserve">16.1097545623779</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3619804382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2806167602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3782520294189</t>
+    <t xml:space="preserve">16.3619785308838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2806148529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3782501220703</t>
   </si>
   <si>
     <t xml:space="preserve">16.1992530822754</t>
@@ -1139,13 +1139,13 @@
     <t xml:space="preserve">16.2236633300781</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2724800109863</t>
+    <t xml:space="preserve">16.2724781036377</t>
   </si>
   <si>
     <t xml:space="preserve">16.6792907714844</t>
   </si>
   <si>
-    <t xml:space="preserve">16.313159942627</t>
+    <t xml:space="preserve">16.3131580352783</t>
   </si>
   <si>
     <t xml:space="preserve">16.09348487854</t>
@@ -1157,10 +1157,10 @@
     <t xml:space="preserve">16.1911163330078</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3538436889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.028392791748</t>
+    <t xml:space="preserve">16.3538417816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0283908843994</t>
   </si>
   <si>
     <t xml:space="preserve">15.9144840240479</t>
@@ -1169,79 +1169,79 @@
     <t xml:space="preserve">15.1822214126587</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9706811904907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1008625030518</t>
+    <t xml:space="preserve">14.9706802368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1008605957031</t>
   </si>
   <si>
     <t xml:space="preserve">14.8730478286743</t>
   </si>
   <si>
-    <t xml:space="preserve">14.222146987915</t>
+    <t xml:space="preserve">14.2221479415894</t>
   </si>
   <si>
     <t xml:space="preserve">13.8478803634644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8893194198608</t>
+    <t xml:space="preserve">14.8893175125122</t>
   </si>
   <si>
     <t xml:space="preserve">15.1984968185425</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3937654495239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5402183532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9381351470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5964164733887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4011449813843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2058744430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1082420349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0594234466553</t>
+    <t xml:space="preserve">15.3937673568726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5402193069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9381380081177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5964155197144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4011459350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2058734893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1082410812378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0594244003296</t>
   </si>
   <si>
     <t xml:space="preserve">13.9129705429077</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0106048583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3197832107544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6452312469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7428674697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7265939712524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2147693634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8079566955566</t>
+    <t xml:space="preserve">14.0106039047241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3197841644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6452322006226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7428665161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7265930175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.214771270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8079557418823</t>
   </si>
   <si>
     <t xml:space="preserve">14.8567752838135</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9544076919556</t>
+    <t xml:space="preserve">14.9544086456299</t>
   </si>
   <si>
     <t xml:space="preserve">14.7916841506958</t>
@@ -1250,40 +1250,40 @@
     <t xml:space="preserve">14.2709655761719</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0032253265381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4825067520142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9218626022339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9055919647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0194997787476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0520429611206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2562046051025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7354879379272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8168516159058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6215829849243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9307594299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6866703033447</t>
+    <t xml:space="preserve">15.0032272338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4825077056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9218645095825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9055910110474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0194988250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0520439147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2562084197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7354888916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8168506622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6215810775757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.930760383606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6866693496704</t>
   </si>
   <si>
     <t xml:space="preserve">15.7192144393921</t>
@@ -1295,13 +1295,13 @@
     <t xml:space="preserve">15.6703987121582</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6053085327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5653505325317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9956836700439</t>
+    <t xml:space="preserve">15.6053075790405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5653514862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9956827163696</t>
   </si>
   <si>
     <t xml:space="preserve">15.0291948318481</t>
@@ -1310,10 +1310,10 @@
     <t xml:space="preserve">15.0627021789551</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2470073699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2302551269531</t>
+    <t xml:space="preserve">15.2470054626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2302522659302</t>
   </si>
   <si>
     <t xml:space="preserve">15.5318422317505</t>
@@ -1322,49 +1322,49 @@
     <t xml:space="preserve">15.7161464691162</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8669424057007</t>
+    <t xml:space="preserve">15.8669404983521</t>
   </si>
   <si>
     <t xml:space="preserve">15.5821075439453</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4983320236206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.481575012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4145565032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1799879074097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0794563293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1129684448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3589944839478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.291974067688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2584657669067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4595232009888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4092597961426</t>
+    <t xml:space="preserve">15.498330116272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4815759658813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4145555496216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1799869537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0794582366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1129693984985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3589954376221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2919731140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2584648132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4595251083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4092588424683</t>
   </si>
   <si>
     <t xml:space="preserve">14.5600538253784</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4039621353149</t>
+    <t xml:space="preserve">13.4039611816406</t>
   </si>
   <si>
     <t xml:space="preserve">13.4877376556396</t>
@@ -1373,67 +1373,67 @@
     <t xml:space="preserve">13.2364120483398</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5380010604858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4374732971191</t>
+    <t xml:space="preserve">13.5380020141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4374723434448</t>
   </si>
   <si>
     <t xml:space="preserve">14.191445350647</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5882654190063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6887969970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4207172393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5212459564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5715112686157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3201875686646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1526374816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1861476898193</t>
+    <t xml:space="preserve">13.5882663726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.688796043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4207162857056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5212469100952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.57151222229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3201866149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1526384353638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.186146736145</t>
   </si>
   <si>
     <t xml:space="preserve">13.2196569442749</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3034324645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8510494232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.683500289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5662136077881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.901312828064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8342924118042</t>
+    <t xml:space="preserve">13.3034334182739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8510484695435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6834993362427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5662145614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9013137817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8342933654785</t>
   </si>
   <si>
     <t xml:space="preserve">12.482439994812</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1473407745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0803213119507</t>
+    <t xml:space="preserve">12.1473417282104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0803194046021</t>
   </si>
   <si>
     <t xml:space="preserve">12.0635652542114</t>
@@ -1442,7 +1442,7 @@
     <t xml:space="preserve">11.979790687561</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5609169006348</t>
+    <t xml:space="preserve">11.5609178543091</t>
   </si>
   <si>
     <t xml:space="preserve">11.1923084259033</t>
@@ -1454,10 +1454,10 @@
     <t xml:space="preserve">12.4321746826172</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1191272735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2531681060791</t>
+    <t xml:space="preserve">13.1191282272339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2531671524048</t>
   </si>
   <si>
     <t xml:space="preserve">13.2866773605347</t>
@@ -1469,10 +1469,10 @@
     <t xml:space="preserve">13.3536977767944</t>
   </si>
   <si>
-    <t xml:space="preserve">12.985089302063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8007841110229</t>
+    <t xml:space="preserve">12.9850883483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8007850646973</t>
   </si>
   <si>
     <t xml:space="preserve">12.6332349777222</t>
@@ -1481,13 +1481,13 @@
     <t xml:space="preserve">12.8678035736084</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8122425079346</t>
+    <t xml:space="preserve">11.8122415542603</t>
   </si>
   <si>
     <t xml:space="preserve">11.6279373168945</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6111822128296</t>
+    <t xml:space="preserve">11.6111812591553</t>
   </si>
   <si>
     <t xml:space="preserve">11.7284669876099</t>
@@ -1496,13 +1496,13 @@
     <t xml:space="preserve">11.9630355834961</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8960161209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6614456176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0750246047974</t>
+    <t xml:space="preserve">11.896017074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6614475250244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.075023651123</t>
   </si>
   <si>
     <t xml:space="preserve">11.0415143966675</t>
@@ -1520,34 +1520,34 @@
     <t xml:space="preserve">10.9744939804077</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7117128372192</t>
+    <t xml:space="preserve">11.7117109298706</t>
   </si>
   <si>
     <t xml:space="preserve">12.3651561737061</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4603891372681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1587982177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1252899169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1755533218384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3766136169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2311162948608</t>
+    <t xml:space="preserve">11.4603881835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1587991714478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1252880096436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1755542755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.376612663269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2311153411865</t>
   </si>
   <si>
     <t xml:space="preserve">12.3986654281616</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9295263290405</t>
+    <t xml:space="preserve">11.9295272827148</t>
   </si>
   <si>
     <t xml:space="preserve">11.7954864501953</t>
@@ -1556,7 +1556,7 @@
     <t xml:space="preserve">11.87926197052</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1976051330566</t>
+    <t xml:space="preserve">12.197606086731</t>
   </si>
   <si>
     <t xml:space="preserve">12.2478704452515</t>
@@ -1565,7 +1565,7 @@
     <t xml:space="preserve">12.0133018493652</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1305856704712</t>
+    <t xml:space="preserve">12.1305866241455</t>
   </si>
   <si>
     <t xml:space="preserve">12.1808500289917</t>
@@ -1574,7 +1574,7 @@
     <t xml:space="preserve">12.381911277771</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3316459655762</t>
+    <t xml:space="preserve">12.3316450119019</t>
   </si>
   <si>
     <t xml:space="preserve">12.4656858444214</t>
@@ -1586,25 +1586,25 @@
     <t xml:space="preserve">12.7170095443726</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8845586776733</t>
+    <t xml:space="preserve">12.8845596313477</t>
   </si>
   <si>
     <t xml:space="preserve">12.9515781402588</t>
   </si>
   <si>
-    <t xml:space="preserve">12.968334197998</t>
+    <t xml:space="preserve">12.9683332443237</t>
   </si>
   <si>
     <t xml:space="preserve">13.2029027938843</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7337646484375</t>
+    <t xml:space="preserve">12.7337636947632</t>
   </si>
   <si>
     <t xml:space="preserve">12.8175392150879</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6499891281128</t>
+    <t xml:space="preserve">12.6499900817871</t>
   </si>
   <si>
     <t xml:space="preserve">12.7002544403076</t>
@@ -1616,31 +1616,31 @@
     <t xml:space="preserve">12.784029006958</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0018444061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0353546142578</t>
+    <t xml:space="preserve">13.0018424987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0353536605835</t>
   </si>
   <si>
     <t xml:space="preserve">12.5494585037231</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9348220825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9180688858032</t>
+    <t xml:space="preserve">12.9348230361938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9180679321289</t>
   </si>
   <si>
     <t xml:space="preserve">13.3872079849243</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6217784881592</t>
+    <t xml:space="preserve">13.6217775344849</t>
   </si>
   <si>
     <t xml:space="preserve">13.8228349685669</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5044937133789</t>
+    <t xml:space="preserve">13.5044927597046</t>
   </si>
   <si>
     <t xml:space="preserve">13.4542255401611</t>
@@ -1649,13 +1649,13 @@
     <t xml:space="preserve">13.6385326385498</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7223052978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3704538345337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0521078109741</t>
+    <t xml:space="preserve">13.7223062515259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3704528808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0521087646484</t>
   </si>
   <si>
     <t xml:space="preserve">13.0185985565186</t>
@@ -1664,16 +1664,16 @@
     <t xml:space="preserve">13.1693925857544</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1023740768433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.499195098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7481775283813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5740203857422</t>
+    <t xml:space="preserve">13.1023731231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4991941452026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.748176574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5740213394165</t>
   </si>
   <si>
     <t xml:space="preserve">12.3650350570679</t>
@@ -1682,10 +1682,10 @@
     <t xml:space="preserve">12.2257099151611</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2779579162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3127889633179</t>
+    <t xml:space="preserve">12.2779569625854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3127880096436</t>
   </si>
   <si>
     <t xml:space="preserve">12.2953729629517</t>
@@ -1697,7 +1697,7 @@
     <t xml:space="preserve">12.1212167739868</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5217752456665</t>
+    <t xml:space="preserve">12.5217742919922</t>
   </si>
   <si>
     <t xml:space="preserve">12.4869441986084</t>
@@ -1706,13 +1706,13 @@
     <t xml:space="preserve">12.452112197876</t>
   </si>
   <si>
-    <t xml:space="preserve">12.138632774353</t>
+    <t xml:space="preserve">12.1386337280273</t>
   </si>
   <si>
     <t xml:space="preserve">12.0515556335449</t>
   </si>
   <si>
-    <t xml:space="preserve">11.894814491272</t>
+    <t xml:space="preserve">11.8948154449463</t>
   </si>
   <si>
     <t xml:space="preserve">12.2082958221436</t>
@@ -1721,13 +1721,13 @@
     <t xml:space="preserve">12.8178396224976</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7655916213989</t>
+    <t xml:space="preserve">12.7655925750732</t>
   </si>
   <si>
     <t xml:space="preserve">12.6436834335327</t>
   </si>
   <si>
-    <t xml:space="preserve">12.399866104126</t>
+    <t xml:space="preserve">12.3998670578003</t>
   </si>
   <si>
     <t xml:space="preserve">12.6262683868408</t>
@@ -1745,10 +1745,10 @@
     <t xml:space="preserve">12.95716381073</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9397478103638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7830085754395</t>
+    <t xml:space="preserve">12.9397468566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7830076217651</t>
   </si>
   <si>
     <t xml:space="preserve">12.6959295272827</t>
@@ -1760,19 +1760,19 @@
     <t xml:space="preserve">12.8875007629395</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1560487747192</t>
+    <t xml:space="preserve">12.1560497283936</t>
   </si>
   <si>
     <t xml:space="preserve">12.0341396331787</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7206602096558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2431259155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7554922103882</t>
+    <t xml:space="preserve">11.7206592559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2431268692017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7554903030396</t>
   </si>
   <si>
     <t xml:space="preserve">11.6684131622314</t>
@@ -1781,25 +1781,25 @@
     <t xml:space="preserve">11.9993076324463</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0689716339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1038007736206</t>
+    <t xml:space="preserve">12.0689697265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1038017272949</t>
   </si>
   <si>
     <t xml:space="preserve">11.790322303772</t>
   </si>
   <si>
-    <t xml:space="preserve">11.842568397522</t>
+    <t xml:space="preserve">11.8425693511963</t>
   </si>
   <si>
     <t xml:space="preserve">11.9470624923706</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8251533508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8599834442139</t>
+    <t xml:space="preserve">11.8251523971558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8599843978882</t>
   </si>
   <si>
     <t xml:space="preserve">11.7729063034058</t>
@@ -1811,7 +1811,7 @@
     <t xml:space="preserve">11.6509971618652</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5465040206909</t>
+    <t xml:space="preserve">11.5465030670166</t>
   </si>
   <si>
     <t xml:space="preserve">11.3201026916504</t>
@@ -1820,16 +1820,16 @@
     <t xml:space="preserve">11.2156095504761</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4071807861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3026866912842</t>
+    <t xml:space="preserve">11.4071798324585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3026857376099</t>
   </si>
   <si>
     <t xml:space="preserve">11.3549337387085</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3897638320923</t>
+    <t xml:space="preserve">11.3897647857666</t>
   </si>
   <si>
     <t xml:space="preserve">11.1981925964355</t>
@@ -1841,31 +1841,31 @@
     <t xml:space="preserve">11.0414533615112</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8847150802612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8672981262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9717922210693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8324670791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.623480796814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6060657501221</t>
+    <t xml:space="preserve">10.8847141265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.867299079895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.971791267395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.832465171814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6234817504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6060647964478</t>
   </si>
   <si>
     <t xml:space="preserve">10.5886487960815</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5189867019653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4493265151978</t>
+    <t xml:space="preserve">10.5189876556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4493255615234</t>
   </si>
   <si>
     <t xml:space="preserve">10.6583118438721</t>
@@ -1880,46 +1880,46 @@
     <t xml:space="preserve">11.1111164093018</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0588684082031</t>
+    <t xml:space="preserve">11.0588693618774</t>
   </si>
   <si>
     <t xml:space="preserve">10.9892072677612</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8498821258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0240383148193</t>
+    <t xml:space="preserve">10.8498830795288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.024037361145</t>
   </si>
   <si>
     <t xml:space="preserve">11.0066232681274</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7976350784302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8150510787964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9543752670288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0937013626099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7032432556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9818925857544</t>
+    <t xml:space="preserve">10.7976360321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8150520324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9543762207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0937004089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7032442092896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9818935394287</t>
   </si>
   <si>
     <t xml:space="preserve">11.9296464920044</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9122323989868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8077383041382</t>
+    <t xml:space="preserve">11.9122314453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8077373504639</t>
   </si>
   <si>
     <t xml:space="preserve">12.2605409622192</t>
@@ -1928,22 +1928,22 @@
     <t xml:space="preserve">12.086386680603</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9644765853882</t>
+    <t xml:space="preserve">11.9644775390625</t>
   </si>
   <si>
     <t xml:space="preserve">11.529088973999</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4942588806152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.581335067749</t>
+    <t xml:space="preserve">11.4942569732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5813360214233</t>
   </si>
   <si>
     <t xml:space="preserve">11.476842880249</t>
   </si>
   <si>
-    <t xml:space="preserve">11.685830116272</t>
+    <t xml:space="preserve">11.6858291625977</t>
   </si>
   <si>
     <t xml:space="preserve">12.1908798217773</t>
@@ -1961,7 +1961,7 @@
     <t xml:space="preserve">10.7105588912964</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70045852661133</t>
+    <t xml:space="preserve">9.70045757293701</t>
   </si>
   <si>
     <t xml:space="preserve">9.49146938323975</t>
@@ -1970,13 +1970,13 @@
     <t xml:space="preserve">9.03866672515869</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98641967773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42912197113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18530464172363</t>
+    <t xml:space="preserve">8.98641872406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.429123878479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18530559539795</t>
   </si>
   <si>
     <t xml:space="preserve">8.22884368896484</t>
@@ -1991,7 +1991,7 @@
     <t xml:space="preserve">8.49007701873779</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31592178344727</t>
+    <t xml:space="preserve">8.31592082977295</t>
   </si>
   <si>
     <t xml:space="preserve">8.32463073730469</t>
@@ -2000,31 +2000,31 @@
     <t xml:space="preserve">8.16788959503174</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38558483123779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28979778289795</t>
+    <t xml:space="preserve">8.38558387756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28979873657227</t>
   </si>
   <si>
     <t xml:space="preserve">8.41170597076416</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49878406524658</t>
+    <t xml:space="preserve">8.4987850189209</t>
   </si>
   <si>
     <t xml:space="preserve">8.638108253479</t>
   </si>
   <si>
-    <t xml:space="preserve">8.690354347229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67294120788574</t>
+    <t xml:space="preserve">8.69035530090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67294025421143</t>
   </si>
   <si>
     <t xml:space="preserve">8.79484939575195</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96900463104248</t>
+    <t xml:space="preserve">8.96900367736816</t>
   </si>
   <si>
     <t xml:space="preserve">8.75131034851074</t>
@@ -2033,7 +2033,7 @@
     <t xml:space="preserve">8.70777130126953</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83838844299316</t>
+    <t xml:space="preserve">8.83838748931885</t>
   </si>
   <si>
     <t xml:space="preserve">9.18669891357422</t>
@@ -2045,31 +2045,31 @@
     <t xml:space="preserve">9.14315891265869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23023796081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40439224243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66562652587891</t>
+    <t xml:space="preserve">9.23023700714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40439319610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66562747955322</t>
   </si>
   <si>
     <t xml:space="preserve">9.57854843139648</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31731510162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88192653656006</t>
+    <t xml:space="preserve">9.31731414794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88192558288574</t>
   </si>
   <si>
     <t xml:space="preserve">8.65552425384521</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51620006561279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60327816009521</t>
+    <t xml:space="preserve">8.51619911193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6032772064209</t>
   </si>
   <si>
     <t xml:space="preserve">8.56844711303711</t>
@@ -2087,25 +2087,25 @@
     <t xml:space="preserve">10.1010150909424</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92685890197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88332080841064</t>
+    <t xml:space="preserve">9.92685985565186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88332176208496</t>
   </si>
   <si>
     <t xml:space="preserve">10.0574760437012</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97039699554443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70916366577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7527027130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62208652496338</t>
+    <t xml:space="preserve">9.97039794921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7091646194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75270366668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6220874786377</t>
   </si>
   <si>
     <t xml:space="preserve">9.53500938415527</t>
@@ -2114,34 +2114,34 @@
     <t xml:space="preserve">9.79624271392822</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1880922317505</t>
+    <t xml:space="preserve">10.1880931854248</t>
   </si>
   <si>
     <t xml:space="preserve">10.2751693725586</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5364036560059</t>
+    <t xml:space="preserve">10.5364027023315</t>
   </si>
   <si>
     <t xml:space="preserve">10.9282531738281</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0153293609619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7540969848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4928636550903</t>
+    <t xml:space="preserve">11.0153303146362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7540979385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4928646087646</t>
   </si>
   <si>
     <t xml:space="preserve">10.4057865142822</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3622465133667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3187093734741</t>
+    <t xml:space="preserve">10.362247467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3187084197998</t>
   </si>
   <si>
     <t xml:space="preserve">11.1894865036011</t>
@@ -2174,10 +2174,10 @@
     <t xml:space="preserve">11.4743099212646</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2064275741577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4296617507935</t>
+    <t xml:space="preserve">11.2064266204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4296627044678</t>
   </si>
   <si>
     <t xml:space="preserve">11.608250617981</t>
@@ -2186,16 +2186,16 @@
     <t xml:space="preserve">11.2510738372803</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5813665390015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5367193222046</t>
+    <t xml:space="preserve">10.5813674926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5367202758789</t>
   </si>
   <si>
     <t xml:space="preserve">11.0278387069702</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8938970565796</t>
+    <t xml:space="preserve">10.8938980102539</t>
   </si>
   <si>
     <t xml:space="preserve">11.1617794036865</t>
@@ -2204,13 +2204,13 @@
     <t xml:space="preserve">11.0724849700928</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9207820892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.188663482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2333106994629</t>
+    <t xml:space="preserve">11.9207811355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1886625289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2333097457886</t>
   </si>
   <si>
     <t xml:space="preserve">12.3226041793823</t>
@@ -2228,28 +2228,28 @@
     <t xml:space="preserve">12.0993690490723</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4387826919556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4834289550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9299011230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8406057357788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0191946029663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9030179977417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0816059112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.036958694458</t>
+    <t xml:space="preserve">13.4387817382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4834299087524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9299020767212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8406066894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0191955566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9030170440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0816040039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0369577407837</t>
   </si>
   <si>
     <t xml:space="preserve">13.7513122558594</t>
@@ -2261,25 +2261,25 @@
     <t xml:space="preserve">13.3941345214844</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9745473861694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2601947784424</t>
+    <t xml:space="preserve">13.9745483398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2601938247681</t>
   </si>
   <si>
     <t xml:space="preserve">13.6620178222656</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6173715591431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.88525390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6442537307739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7781953811646</t>
+    <t xml:space="preserve">13.6173706054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8852548599243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6442546844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7781944274902</t>
   </si>
   <si>
     <t xml:space="preserve">14.9121379852295</t>
@@ -2300,13 +2300,13 @@
     <t xml:space="preserve">15.1800203323364</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8497285842896</t>
+    <t xml:space="preserve">15.8497276306152</t>
   </si>
   <si>
     <t xml:space="preserve">15.8050813674927</t>
   </si>
   <si>
-    <t xml:space="preserve">16.072961807251</t>
+    <t xml:space="preserve">16.0729637145996</t>
   </si>
   <si>
     <t xml:space="preserve">16.3854923248291</t>
@@ -2321,10 +2321,10 @@
     <t xml:space="preserve">16.7426700592041</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7249050140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7695541381836</t>
+    <t xml:space="preserve">17.7249069213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.769552230835</t>
   </si>
   <si>
     <t xml:space="preserve">17.8142013549805</t>
@@ -2333,13 +2333,13 @@
     <t xml:space="preserve">17.8588466644287</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0374374389648</t>
+    <t xml:space="preserve">18.0374355316162</t>
   </si>
   <si>
     <t xml:space="preserve">18.12672996521</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3946132659912</t>
+    <t xml:space="preserve">18.3946113586426</t>
   </si>
   <si>
     <t xml:space="preserve">18.5732002258301</t>
@@ -2348,7 +2348,7 @@
     <t xml:space="preserve">16.6980247497559</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3053188323975</t>
+    <t xml:space="preserve">18.3053169250488</t>
   </si>
   <si>
     <t xml:space="preserve">17.5909652709961</t>
@@ -2357,10 +2357,10 @@
     <t xml:space="preserve">18.2160243988037</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9481430053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0196723937988</t>
+    <t xml:space="preserve">17.9481410980225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0196704864502</t>
   </si>
   <si>
     <t xml:space="preserve">20.1804981231689</t>
@@ -2369,7 +2369,7 @@
     <t xml:space="preserve">20.5376739501953</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6269683837891</t>
+    <t xml:space="preserve">20.6269702911377</t>
   </si>
   <si>
     <t xml:space="preserve">20.9841461181641</t>
@@ -2378,40 +2378,40 @@
     <t xml:space="preserve">20.8055572509766</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0734386444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0912055969238</t>
+    <t xml:space="preserve">21.0734405517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0912036895752</t>
   </si>
   <si>
     <t xml:space="preserve">20.0019092559814</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8233203887939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2697944641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1982612609863</t>
+    <t xml:space="preserve">19.8233222961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2697925567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1982593536377</t>
   </si>
   <si>
     <t xml:space="preserve">19.9126148223877</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5554389953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6447315216064</t>
+    <t xml:space="preserve">19.5554370880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6447334289551</t>
   </si>
   <si>
     <t xml:space="preserve">18.9303779602051</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7162628173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4483814239502</t>
+    <t xml:space="preserve">20.7162647247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4483795166016</t>
   </si>
   <si>
     <t xml:space="preserve">21.4306163787842</t>
@@ -2429,7 +2429,7 @@
     <t xml:space="preserve">22.0556774139404</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7877941131592</t>
+    <t xml:space="preserve">21.7877960205078</t>
   </si>
   <si>
     <t xml:space="preserve">22.7700309753418</t>
@@ -3819,6 +3819,9 @@
   </si>
   <si>
     <t xml:space="preserve">13.8500003814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5</t>
   </si>
 </sst>
 </file>
@@ -69495,7 +69498,7 @@
     </row>
     <row r="2514">
       <c r="A2514" s="1" t="n">
-        <v>45979.6747106481</v>
+        <v>45979.3333333333</v>
       </c>
       <c r="B2514" t="n">
         <v>3428</v>
@@ -69516,6 +69519,32 @@
         <v>1260</v>
       </c>
       <c r="H2514" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2515">
+      <c r="A2515" s="1" t="n">
+        <v>45980.6912384259</v>
+      </c>
+      <c r="B2515" t="n">
+        <v>3477</v>
+      </c>
+      <c r="C2515" t="n">
+        <v>13.6999998092651</v>
+      </c>
+      <c r="D2515" t="n">
+        <v>13.5500001907349</v>
+      </c>
+      <c r="E2515" t="n">
+        <v>13.6999998092651</v>
+      </c>
+      <c r="F2515" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="G2515" t="s">
+        <v>1269</v>
+      </c>
+      <c r="H2515" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SAB.MI.xlsx
+++ b/data/SAB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1270" uniqueCount="1270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1271" uniqueCount="1271">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,13 +44,13 @@
     <t xml:space="preserve">SAB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61823177337646</t>
+    <t xml:space="preserve">8.61823081970215</t>
   </si>
   <si>
     <t xml:space="preserve">8.4831018447876</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33295917510986</t>
+    <t xml:space="preserve">8.33296012878418</t>
   </si>
   <si>
     <t xml:space="preserve">8.37049388885498</t>
@@ -59,7 +59,7 @@
     <t xml:space="preserve">8.31794357299805</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25788688659668</t>
+    <t xml:space="preserve">8.25788497924805</t>
   </si>
   <si>
     <t xml:space="preserve">8.16029357910156</t>
@@ -68,52 +68,52 @@
     <t xml:space="preserve">7.88252830505371</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52969074249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6648211479187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62728452682495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61226987838745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73989200592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75490665435791</t>
+    <t xml:space="preserve">7.52969169616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66482019424438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62728261947632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61227083206177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73989248275757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75490713119507</t>
   </si>
   <si>
     <t xml:space="preserve">7.76992130279541</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89754247665405</t>
+    <t xml:space="preserve">7.89754343032837</t>
   </si>
   <si>
     <t xml:space="preserve">7.6197772026062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79994964599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72487783432007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65731287002563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50716972351074</t>
+    <t xml:space="preserve">7.79995107650757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72487735748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65731239318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5071702003479</t>
   </si>
   <si>
     <t xml:space="preserve">7.34201145172119</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54470634460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39080905914307</t>
+    <t xml:space="preserve">7.54470586776733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39080810546875</t>
   </si>
   <si>
     <t xml:space="preserve">7.58224201202393</t>
@@ -128,13 +128,13 @@
     <t xml:space="preserve">8.1152515411377</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95759963989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06270122528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03267002105713</t>
+    <t xml:space="preserve">7.95760059356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06270027160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03267192840576</t>
   </si>
   <si>
     <t xml:space="preserve">7.92006492614746</t>
@@ -143,19 +143,19 @@
     <t xml:space="preserve">7.77742671966553</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86751317977905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80745697021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98762893676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0401782989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99513530731201</t>
+    <t xml:space="preserve">7.86751222610474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80745553970337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98762798309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04017925262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99513626098633</t>
   </si>
   <si>
     <t xml:space="preserve">7.96510744094849</t>
@@ -164,352 +164,352 @@
     <t xml:space="preserve">7.90504884719849</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93507719039917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89003658294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94258546829224</t>
+    <t xml:space="preserve">7.93507814407349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89003467559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94258451461792</t>
   </si>
   <si>
     <t xml:space="preserve">7.82997941970825</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81496238708496</t>
+    <t xml:space="preserve">7.81496334075928</t>
   </si>
   <si>
     <t xml:space="preserve">7.73238468170166</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64980554580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71737098693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67232847213745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63479232788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51467800140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64229822158813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56722640991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70235633850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74739933013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46963357925415</t>
+    <t xml:space="preserve">7.64980602264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71737003326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67232799530029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63479089736938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51467704772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64229965209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56722736358643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70235729217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74739837646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46963310241699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6948504447937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49215459823608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47338676452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43585157394409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50341701507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48089504241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59725666046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4283447265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38705539703369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37203979492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3194899559021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28195524215698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52122163772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80533981323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75009346008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75798749923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81323051452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86058235168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69879579544067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58435869216919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68695640563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57646751403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53700733184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49754524230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28445768356323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92536449432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07926177978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22921085357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45808506011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26078033447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37127208709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26472806930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34759521484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46992206573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36732482910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37916421890259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13450574874878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18975114822388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1029372215271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15029144287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10688447952271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20553588867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18186044692993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22131967544556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19369745254517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24894237518311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1976432800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18580484390259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.225266456604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20948171615601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31602621078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21342945098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16607475280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24499702453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13056039810181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11082983016968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17791271209717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23315906524658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2765645980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3002405166626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29234981536865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.241051197052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1187219619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.095046043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00428581237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94509410858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93325614929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09899187088013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15423679351807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13845205307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1581826210022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05558490753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07136869430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06742382049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0240159034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04769277572632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0634765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08320713043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05163860321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04374599456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03190755844116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05953121185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03585433959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1739673614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90563344955444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91352653503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93720197677612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92141914367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94114828109741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96877098083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14239835739136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45019197463989</t>
   </si>
   <si>
     <t xml:space="preserve">7.69484853744507</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49215459823608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47338628768921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43585157394409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50341606140137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48089456558228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59725666046143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42834424972534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38705539703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37204122543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31949138641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28195476531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52122068405151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80534029006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75009346008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75798654556274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81323146820068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8605842590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69879484176636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58435964584351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68695735931396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57646656036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53700590133667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49754428863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28445672988892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92536401748657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07926225662231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22921180725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45808410644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2607798576355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37127113342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2647271156311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34759521484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46992349624634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36732530593872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37916326522827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13450717926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18975114822388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10293769836426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15029048919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10688352584839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20553636550903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18185901641846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22131872177124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19369745254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24894285202026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19764375686646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18580532073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.225266456604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20948171615601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31602621078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21342802047729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16607427597046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24499750137329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13056039810181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11082983016968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17791366577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23315858840942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2765645980835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30024099349976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29234981536865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24104976654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11872291564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09504556655884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00428581237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9450945854187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93325567245483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09899187088013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15423679351807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13845300674438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15818309783936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05558443069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07136869430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06742238998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0240159034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04769229888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06347703933716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08320760726929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05163908004761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04374694824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03190755844116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05953121185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03585433959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1739673614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90563344955444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91352605819702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93720245361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9214186668396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94114828109741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96877098083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1423978805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45019245147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69484949111938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79350185394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9237208366394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0499963760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20783996582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16837787628174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08945655822754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19994735717773</t>
+    <t xml:space="preserve">7.79350090026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92372179031372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04999542236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20783805847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16837882995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08945846557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19994926452637</t>
   </si>
   <si>
     <t xml:space="preserve">8.06578063964844</t>
@@ -518,7 +518,7 @@
     <t xml:space="preserve">8.12891674041748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17627048492432</t>
+    <t xml:space="preserve">8.17626953125</t>
   </si>
   <si>
     <t xml:space="preserve">8.32622241973877</t>
@@ -527,31 +527,31 @@
     <t xml:space="preserve">8.55509281158447</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56298542022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42881870269775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35778999328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39725112915039</t>
+    <t xml:space="preserve">8.56298637390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42881965637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35779094696045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39725017547607</t>
   </si>
   <si>
     <t xml:space="preserve">8.42092800140381</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44460296630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40514087677002</t>
+    <t xml:space="preserve">8.44460391998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40514278411865</t>
   </si>
   <si>
     <t xml:space="preserve">8.26308441162109</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18416213989258</t>
+    <t xml:space="preserve">8.18416118621826</t>
   </si>
   <si>
     <t xml:space="preserve">8.30254554748535</t>
@@ -560,31 +560,31 @@
     <t xml:space="preserve">8.22362327575684</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2867603302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25519180297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34989738464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31043720245361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36568260192871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33411407470703</t>
+    <t xml:space="preserve">8.28676128387451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25519275665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34989643096924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3104362487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36568355560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33411312103271</t>
   </si>
   <si>
     <t xml:space="preserve">8.34200572967529</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46038818359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62612342834473</t>
+    <t xml:space="preserve">8.46038722991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62612247467041</t>
   </si>
   <si>
     <t xml:space="preserve">8.74450492858887</t>
@@ -596,28 +596,28 @@
     <t xml:space="preserve">9.0049467086792</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23381900787354</t>
+    <t xml:space="preserve">9.23381996154785</t>
   </si>
   <si>
     <t xml:space="preserve">9.30484867095947</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26538753509521</t>
+    <t xml:space="preserve">9.26538848876953</t>
   </si>
   <si>
     <t xml:space="preserve">9.1627893447876</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19435787200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24960327148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29695510864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36798572540283</t>
+    <t xml:space="preserve">9.19435882568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24960422515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29695606231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36798477172852</t>
   </si>
   <si>
     <t xml:space="preserve">9.54950428009033</t>
@@ -632,43 +632,43 @@
     <t xml:space="preserve">10.2203388214111</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4807796478271</t>
+    <t xml:space="preserve">10.4807786941528</t>
   </si>
   <si>
     <t xml:space="preserve">10.4571027755737</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2913675308228</t>
+    <t xml:space="preserve">10.2913665771484</t>
   </si>
   <si>
     <t xml:space="preserve">10.2597990036011</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1493082046509</t>
+    <t xml:space="preserve">10.1493072509766</t>
   </si>
   <si>
     <t xml:space="preserve">10.0861711502075</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0151424407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.101957321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.165093421936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0546026229858</t>
+    <t xml:space="preserve">10.0151405334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1019554138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1650924682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0546035766602</t>
   </si>
   <si>
     <t xml:space="preserve">10.1808767318726</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1177396774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1887683868408</t>
+    <t xml:space="preserve">10.1177406311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1887702941895</t>
   </si>
   <si>
     <t xml:space="preserve">10.0703868865967</t>
@@ -683,22 +683,22 @@
     <t xml:space="preserve">10.496563911438</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4176416397095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3150444030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7333278656006</t>
+    <t xml:space="preserve">10.4176406860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3150434494019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7333269119263</t>
   </si>
   <si>
     <t xml:space="preserve">10.4492101669312</t>
   </si>
   <si>
-    <t xml:space="preserve">10.559700012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6386203765869</t>
+    <t xml:space="preserve">10.5597009658813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6386222839355</t>
   </si>
   <si>
     <t xml:space="preserve">10.591269493103</t>
@@ -713,49 +713,49 @@
     <t xml:space="preserve">11.3410224914551</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0592107772827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9171504974365</t>
+    <t xml:space="preserve">12.0592088699341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9171514511108</t>
   </si>
   <si>
     <t xml:space="preserve">12.0513181686401</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6882801055908</t>
+    <t xml:space="preserve">11.6882791519165</t>
   </si>
   <si>
     <t xml:space="preserve">11.6803855895996</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2644062042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6274452209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5406293869019</t>
+    <t xml:space="preserve">12.2644052505493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6274461746216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5406303405762</t>
   </si>
   <si>
     <t xml:space="preserve">12.6747961044312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7379341125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4728565216064</t>
+    <t xml:space="preserve">12.7379350662231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4728555679321</t>
   </si>
   <si>
     <t xml:space="preserve">12.6518535614014</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8471212387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8145780563354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9203500747681</t>
+    <t xml:space="preserve">12.8471231460571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8145771026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9203481674194</t>
   </si>
   <si>
     <t xml:space="preserve">12.8715314865112</t>
@@ -764,7 +764,7 @@
     <t xml:space="preserve">12.9366207122803</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8064403533936</t>
+    <t xml:space="preserve">12.8064413070679</t>
   </si>
   <si>
     <t xml:space="preserve">12.6437168121338</t>
@@ -773,43 +773,43 @@
     <t xml:space="preserve">12.8227138519287</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5209159851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8463659286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7812757492065</t>
+    <t xml:space="preserve">11.5209150314331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8463649749756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7812738418579</t>
   </si>
   <si>
     <t xml:space="preserve">11.9114551544189</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9277276992798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9602718353271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.805685043335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1311330795288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0009536743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9846830368042</t>
+    <t xml:space="preserve">11.9277267456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9602727890015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8056840896606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1311340332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0009546279907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9846811294556</t>
   </si>
   <si>
     <t xml:space="preserve">12.0416345596313</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0823154449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9765453338623</t>
+    <t xml:space="preserve">12.0823163986206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.976544380188</t>
   </si>
   <si>
     <t xml:space="preserve">11.8789100646973</t>
@@ -818,25 +818,25 @@
     <t xml:space="preserve">11.7161846160889</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4720973968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5534601211548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5860061645508</t>
+    <t xml:space="preserve">11.4720983505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5534591674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5860042572021</t>
   </si>
   <si>
     <t xml:space="preserve">11.7975482940674</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8951835632324</t>
+    <t xml:space="preserve">11.8951826095581</t>
   </si>
   <si>
     <t xml:space="preserve">12.0904521942139</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1636781692505</t>
+    <t xml:space="preserve">12.1636791229248</t>
   </si>
   <si>
     <t xml:space="preserve">12.074179649353</t>
@@ -848,7 +848,7 @@
     <t xml:space="preserve">12.1392698287964</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2043590545654</t>
+    <t xml:space="preserve">12.2043581008911</t>
   </si>
   <si>
     <t xml:space="preserve">12.1880865097046</t>
@@ -857,16 +857,16 @@
     <t xml:space="preserve">12.147406578064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2531785964966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3670835494995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4077644348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4484462738037</t>
+    <t xml:space="preserve">12.2531776428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3670845031738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4077653884888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.448447227478</t>
   </si>
   <si>
     <t xml:space="preserve">12.9447584152222</t>
@@ -887,58 +887,58 @@
     <t xml:space="preserve">12.8552589416504</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7332162857056</t>
+    <t xml:space="preserve">12.7332153320312</t>
   </si>
   <si>
     <t xml:space="preserve">12.7738971710205</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9854393005371</t>
+    <t xml:space="preserve">12.9854383468628</t>
   </si>
   <si>
     <t xml:space="preserve">13.2620697021484</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6851558685303</t>
+    <t xml:space="preserve">13.685154914856</t>
   </si>
   <si>
     <t xml:space="preserve">13.9292421340942</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9943323135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7502450942993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8153371810913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8316087722778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.018741607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0268793106079</t>
+    <t xml:space="preserve">13.9943332672119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.750244140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8153352737427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8316097259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0187397003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0268774032593</t>
   </si>
   <si>
     <t xml:space="preserve">14.1814670562744</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1570558547974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.230281829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.775411605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3205413818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2961330413818</t>
+    <t xml:space="preserve">14.157057762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2302837371826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7754125595093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3205404281616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2961301803589</t>
   </si>
   <si>
     <t xml:space="preserve">15.4588565826416</t>
@@ -947,25 +947,25 @@
     <t xml:space="preserve">15.8249864578247</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7924432754517</t>
+    <t xml:space="preserve">15.7924394607544</t>
   </si>
   <si>
     <t xml:space="preserve">15.5076723098755</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8493976593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.865668296814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5158100128174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0039844512939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2643432617188</t>
+    <t xml:space="preserve">15.8493957519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8656663894653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5158081054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0039863586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2643451690674</t>
   </si>
   <si>
     <t xml:space="preserve">16.776927947998</t>
@@ -974,52 +974,52 @@
     <t xml:space="preserve">16.9559230804443</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4115505218506</t>
+    <t xml:space="preserve">17.4115543365479</t>
   </si>
   <si>
     <t xml:space="preserve">17.0454216003418</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0787258148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6475048065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0217704772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0543155670166</t>
+    <t xml:space="preserve">18.0787239074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6475067138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0217685699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0543174743652</t>
   </si>
   <si>
     <t xml:space="preserve">18.1275444030762</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2984027862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4123096466064</t>
+    <t xml:space="preserve">18.2984066009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4123115539551</t>
   </si>
   <si>
     <t xml:space="preserve">18.1682243347168</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1600875854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9159984588623</t>
+    <t xml:space="preserve">18.160083770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9160003662109</t>
   </si>
   <si>
     <t xml:space="preserve">17.2651023864746</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0861034393311</t>
+    <t xml:space="preserve">17.0861072540283</t>
   </si>
   <si>
     <t xml:space="preserve">17.2976474761963</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0047397613525</t>
+    <t xml:space="preserve">17.0047416687012</t>
   </si>
   <si>
     <t xml:space="preserve">17.1267852783203</t>
@@ -1031,10 +1031,10 @@
     <t xml:space="preserve">17.0779647827148</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8664245605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7850646972656</t>
+    <t xml:space="preserve">16.8664264678955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.785062789917</t>
   </si>
   <si>
     <t xml:space="preserve">16.988468170166</t>
@@ -1043,22 +1043,22 @@
     <t xml:space="preserve">16.5979290008545</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9152431488037</t>
+    <t xml:space="preserve">16.9152450561523</t>
   </si>
   <si>
     <t xml:space="preserve">16.8338794708252</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9640598297119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8826961517334</t>
+    <t xml:space="preserve">16.9640617370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.882698059082</t>
   </si>
   <si>
     <t xml:space="preserve">16.9233779907227</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1349220275879</t>
+    <t xml:space="preserve">17.1349201202393</t>
   </si>
   <si>
     <t xml:space="preserve">17.0698299407959</t>
@@ -1067,28 +1067,28 @@
     <t xml:space="preserve">17.1674671173096</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6637783050537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2251777648926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8598022460938</t>
+    <t xml:space="preserve">17.6637744903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2251758575439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.859806060791</t>
   </si>
   <si>
     <t xml:space="preserve">19.0632095336914</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7052135467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6319885253906</t>
+    <t xml:space="preserve">18.7052154541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6319904327393</t>
   </si>
   <si>
     <t xml:space="preserve">18.7377624511719</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7133502960205</t>
+    <t xml:space="preserve">18.7133522033691</t>
   </si>
   <si>
     <t xml:space="preserve">18.59130859375</t>
@@ -1097,22 +1097,22 @@
     <t xml:space="preserve">18.3065414428711</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6157169342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.217041015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2089042663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4611301422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5417346954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9071063995361</t>
+    <t xml:space="preserve">18.6157150268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2170429229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2089061737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4611282348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5417327880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9071083068848</t>
   </si>
   <si>
     <t xml:space="preserve">16.4758853912354</t>
@@ -1124,10 +1124,10 @@
     <t xml:space="preserve">16.1097545623779</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3619785308838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2806148529053</t>
+    <t xml:space="preserve">16.3619766235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2806167602539</t>
   </si>
   <si>
     <t xml:space="preserve">16.3782501220703</t>
@@ -1136,19 +1136,19 @@
     <t xml:space="preserve">16.1992530822754</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2236633300781</t>
+    <t xml:space="preserve">16.2236652374268</t>
   </si>
   <si>
     <t xml:space="preserve">16.2724781036377</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6792907714844</t>
+    <t xml:space="preserve">16.6792945861816</t>
   </si>
   <si>
     <t xml:space="preserve">16.3131580352783</t>
   </si>
   <si>
-    <t xml:space="preserve">16.09348487854</t>
+    <t xml:space="preserve">16.0934829711914</t>
   </si>
   <si>
     <t xml:space="preserve">15.9470291137695</t>
@@ -1175,7 +1175,7 @@
     <t xml:space="preserve">15.1008605957031</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8730478286743</t>
+    <t xml:space="preserve">14.8730497360229</t>
   </si>
   <si>
     <t xml:space="preserve">14.2221479415894</t>
@@ -1184,94 +1184,94 @@
     <t xml:space="preserve">13.8478803634644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8893175125122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1984968185425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3937673568726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5402193069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9381380081177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5964155197144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4011459350586</t>
+    <t xml:space="preserve">14.8893184661865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1984987258911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3937654495239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5402202606201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9381370544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.59641456604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4011449813843</t>
   </si>
   <si>
     <t xml:space="preserve">14.2058734893799</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1082410812378</t>
+    <t xml:space="preserve">14.1082401275635</t>
   </si>
   <si>
     <t xml:space="preserve">14.0594244003296</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9129705429077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0106039047241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3197841644287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6452322006226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7428665161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7265930175781</t>
+    <t xml:space="preserve">13.9129695892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0106048583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3197822570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6452312469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7428684234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7265939712524</t>
   </si>
   <si>
     <t xml:space="preserve">15.214771270752</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8079557418823</t>
+    <t xml:space="preserve">14.8079595565796</t>
   </si>
   <si>
     <t xml:space="preserve">14.8567752838135</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9544086456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7916841506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2709655761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0032272338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4825077056885</t>
+    <t xml:space="preserve">14.9544095993042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7916851043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2709665298462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0032262802124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4825067520142</t>
   </si>
   <si>
     <t xml:space="preserve">14.9218645095825</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9055910110474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0194988250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0520439147949</t>
+    <t xml:space="preserve">14.905590057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0195007324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0520429611206</t>
   </si>
   <si>
     <t xml:space="preserve">16.2562084197998</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7354888916016</t>
+    <t xml:space="preserve">15.7354869842529</t>
   </si>
   <si>
     <t xml:space="preserve">15.8168506622314</t>
@@ -1280,37 +1280,37 @@
     <t xml:space="preserve">15.6215810775757</t>
   </si>
   <si>
-    <t xml:space="preserve">15.930760383606</t>
+    <t xml:space="preserve">15.9307584762573</t>
   </si>
   <si>
     <t xml:space="preserve">15.6866693496704</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7192144393921</t>
+    <t xml:space="preserve">15.7192182540894</t>
   </si>
   <si>
     <t xml:space="preserve">15.7029418945312</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6703987121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6053075790405</t>
+    <t xml:space="preserve">15.6704006195068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6053094863892</t>
   </si>
   <si>
     <t xml:space="preserve">15.5653514862061</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9956827163696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0291948318481</t>
+    <t xml:space="preserve">14.9956817626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0291938781738</t>
   </si>
   <si>
     <t xml:space="preserve">15.0627021789551</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2470054626465</t>
+    <t xml:space="preserve">15.2470092773438</t>
   </si>
   <si>
     <t xml:space="preserve">15.2302522659302</t>
@@ -1322,7 +1322,7 @@
     <t xml:space="preserve">15.7161464691162</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8669404983521</t>
+    <t xml:space="preserve">15.8669385910034</t>
   </si>
   <si>
     <t xml:space="preserve">15.5821075439453</t>
@@ -1337,31 +1337,31 @@
     <t xml:space="preserve">15.4145555496216</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1799869537354</t>
+    <t xml:space="preserve">15.179988861084</t>
   </si>
   <si>
     <t xml:space="preserve">15.0794582366943</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1129693984985</t>
+    <t xml:space="preserve">15.1129674911499</t>
   </si>
   <si>
     <t xml:space="preserve">14.3589954376221</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2919731140137</t>
+    <t xml:space="preserve">14.291974067688</t>
   </si>
   <si>
     <t xml:space="preserve">14.2584648132324</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4595251083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4092588424683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5600538253784</t>
+    <t xml:space="preserve">14.4595260620117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4092597961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5600509643555</t>
   </si>
   <si>
     <t xml:space="preserve">13.4039611816406</t>
@@ -1373,16 +1373,16 @@
     <t xml:space="preserve">13.2364120483398</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5380020141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4374723434448</t>
+    <t xml:space="preserve">13.5380010604858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4374732971191</t>
   </si>
   <si>
     <t xml:space="preserve">14.191445350647</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5882663726807</t>
+    <t xml:space="preserve">13.5882654190063</t>
   </si>
   <si>
     <t xml:space="preserve">13.688796043396</t>
@@ -1391,10 +1391,10 @@
     <t xml:space="preserve">13.4207162857056</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5212469100952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.57151222229</t>
+    <t xml:space="preserve">13.5212478637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5715112686157</t>
   </si>
   <si>
     <t xml:space="preserve">13.3201866149902</t>
@@ -1403,22 +1403,22 @@
     <t xml:space="preserve">13.1526384353638</t>
   </si>
   <si>
-    <t xml:space="preserve">13.186146736145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2196569442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3034334182739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8510484695435</t>
+    <t xml:space="preserve">13.1861476898193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2196578979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3034324645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8510494232178</t>
   </si>
   <si>
     <t xml:space="preserve">12.6834993362427</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5662145614624</t>
+    <t xml:space="preserve">12.5662136077881</t>
   </si>
   <si>
     <t xml:space="preserve">12.9013137817383</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">12.1473417282104</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0803194046021</t>
+    <t xml:space="preserve">12.0803203582764</t>
   </si>
   <si>
     <t xml:space="preserve">12.0635652542114</t>
@@ -1442,13 +1442,13 @@
     <t xml:space="preserve">11.979790687561</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5609178543091</t>
+    <t xml:space="preserve">11.5609188079834</t>
   </si>
   <si>
     <t xml:space="preserve">11.1923084259033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2258186340332</t>
+    <t xml:space="preserve">11.2258176803589</t>
   </si>
   <si>
     <t xml:space="preserve">12.4321746826172</t>
@@ -1460,31 +1460,31 @@
     <t xml:space="preserve">13.2531671524048</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2866773605347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7672729492188</t>
+    <t xml:space="preserve">13.2866764068604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7672739028931</t>
   </si>
   <si>
     <t xml:space="preserve">13.3536977767944</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9850883483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8007850646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6332349777222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8678035736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8122415542603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6279373168945</t>
+    <t xml:space="preserve">12.9850873947144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8007841110229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6332340240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8678045272827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8122425079346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6279363632202</t>
   </si>
   <si>
     <t xml:space="preserve">11.6111812591553</t>
@@ -1505,16 +1505,16 @@
     <t xml:space="preserve">11.075023651123</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0415143966675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9577388763428</t>
+    <t xml:space="preserve">11.0415134429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9577379226685</t>
   </si>
   <si>
     <t xml:space="preserve">10.7566795349121</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9242296218872</t>
+    <t xml:space="preserve">10.9242286682129</t>
   </si>
   <si>
     <t xml:space="preserve">10.9744939804077</t>
@@ -1523,7 +1523,7 @@
     <t xml:space="preserve">11.7117109298706</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3651561737061</t>
+    <t xml:space="preserve">12.3651552200317</t>
   </si>
   <si>
     <t xml:space="preserve">11.4603881835938</t>
@@ -1532,7 +1532,7 @@
     <t xml:space="preserve">11.1587991714478</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1252880096436</t>
+    <t xml:space="preserve">11.1252889633179</t>
   </si>
   <si>
     <t xml:space="preserve">11.1755542755127</t>
@@ -1547,10 +1547,10 @@
     <t xml:space="preserve">12.3986654281616</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9295272827148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7954864501953</t>
+    <t xml:space="preserve">11.9295253753662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7954874038696</t>
   </si>
   <si>
     <t xml:space="preserve">11.87926197052</t>
@@ -1559,34 +1559,34 @@
     <t xml:space="preserve">12.197606086731</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2478704452515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0133018493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1305866241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1808500289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.381911277771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3316450119019</t>
+    <t xml:space="preserve">12.2478694915771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0133008956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1305856704712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.180850982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3819103240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3316440582275</t>
   </si>
   <si>
     <t xml:space="preserve">12.4656858444214</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5997247695923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7170095443726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8845596313477</t>
+    <t xml:space="preserve">12.599723815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7170085906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8845586776733</t>
   </si>
   <si>
     <t xml:space="preserve">12.9515781402588</t>
@@ -1598,34 +1598,34 @@
     <t xml:space="preserve">13.2029027938843</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7337636947632</t>
+    <t xml:space="preserve">12.7337646484375</t>
   </si>
   <si>
     <t xml:space="preserve">12.8175392150879</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6499900817871</t>
+    <t xml:space="preserve">12.6499910354614</t>
   </si>
   <si>
     <t xml:space="preserve">12.7002544403076</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5159492492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.784029006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0018424987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0353536605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5494585037231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9348230361938</t>
+    <t xml:space="preserve">12.5159502029419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7840299606323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0018444061279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0353546142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5494594573975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9348220825195</t>
   </si>
   <si>
     <t xml:space="preserve">12.9180679321289</t>
@@ -1637,13 +1637,13 @@
     <t xml:space="preserve">13.6217775344849</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8228349685669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5044927597046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4542255401611</t>
+    <t xml:space="preserve">13.8228368759155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5044937133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4542264938354</t>
   </si>
   <si>
     <t xml:space="preserve">13.6385326385498</t>
@@ -1655,25 +1655,25 @@
     <t xml:space="preserve">13.3704528808594</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0521087646484</t>
+    <t xml:space="preserve">13.0521078109741</t>
   </si>
   <si>
     <t xml:space="preserve">13.0185985565186</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1693925857544</t>
+    <t xml:space="preserve">13.1693935394287</t>
   </si>
   <si>
     <t xml:space="preserve">13.1023731231689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4991941452026</t>
+    <t xml:space="preserve">12.499195098877</t>
   </si>
   <si>
     <t xml:space="preserve">12.748176574707</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5740213394165</t>
+    <t xml:space="preserve">12.5740203857422</t>
   </si>
   <si>
     <t xml:space="preserve">12.3650350570679</t>
@@ -1682,13 +1682,13 @@
     <t xml:space="preserve">12.2257099151611</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2779569625854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3127880096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2953729629517</t>
+    <t xml:space="preserve">12.2779579162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3127889633179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.295373916626</t>
   </si>
   <si>
     <t xml:space="preserve">12.3302040100098</t>
@@ -1700,7 +1700,7 @@
     <t xml:space="preserve">12.5217742919922</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4869441986084</t>
+    <t xml:space="preserve">12.4869432449341</t>
   </si>
   <si>
     <t xml:space="preserve">12.452112197876</t>
@@ -1715,19 +1715,19 @@
     <t xml:space="preserve">11.8948154449463</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2082958221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8178396224976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7655925750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6436834335327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3998670578003</t>
+    <t xml:space="preserve">12.2082948684692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8178386688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7655916213989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.643684387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3998651504517</t>
   </si>
   <si>
     <t xml:space="preserve">12.6262683868408</t>
@@ -1736,7 +1736,7 @@
     <t xml:space="preserve">12.5391893386841</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8700866699219</t>
+    <t xml:space="preserve">12.8700857162476</t>
   </si>
   <si>
     <t xml:space="preserve">12.9745788574219</t>
@@ -1748,7 +1748,7 @@
     <t xml:space="preserve">12.9397468566895</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7830076217651</t>
+    <t xml:space="preserve">12.7830085754395</t>
   </si>
   <si>
     <t xml:space="preserve">12.6959295272827</t>
@@ -1760,13 +1760,13 @@
     <t xml:space="preserve">12.8875007629395</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1560497283936</t>
+    <t xml:space="preserve">12.1560487747192</t>
   </si>
   <si>
     <t xml:space="preserve">12.0341396331787</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7206592559814</t>
+    <t xml:space="preserve">11.7206583023071</t>
   </si>
   <si>
     <t xml:space="preserve">12.2431268692017</t>
@@ -1775,10 +1775,10 @@
     <t xml:space="preserve">11.7554903030396</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6684131622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9993076324463</t>
+    <t xml:space="preserve">11.6684122085571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9993085861206</t>
   </si>
   <si>
     <t xml:space="preserve">12.0689697265625</t>
@@ -1790,7 +1790,7 @@
     <t xml:space="preserve">11.790322303772</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8425693511963</t>
+    <t xml:space="preserve">11.842568397522</t>
   </si>
   <si>
     <t xml:space="preserve">11.9470624923706</t>
@@ -1799,22 +1799,22 @@
     <t xml:space="preserve">11.8251523971558</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8599843978882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7729063034058</t>
+    <t xml:space="preserve">11.8599834442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7729072570801</t>
   </si>
   <si>
     <t xml:space="preserve">11.8774003982544</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6509971618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5465030670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3201026916504</t>
+    <t xml:space="preserve">11.6509981155396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5465049743652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3201036453247</t>
   </si>
   <si>
     <t xml:space="preserve">11.2156095504761</t>
@@ -1826,16 +1826,16 @@
     <t xml:space="preserve">11.3026857376099</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3549337387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3897647857666</t>
+    <t xml:space="preserve">11.3549327850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3897638320923</t>
   </si>
   <si>
     <t xml:space="preserve">11.1981925964355</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9369602203369</t>
+    <t xml:space="preserve">10.9369611740112</t>
   </si>
   <si>
     <t xml:space="preserve">11.0414533615112</t>
@@ -1844,28 +1844,28 @@
     <t xml:space="preserve">10.8847141265869</t>
   </si>
   <si>
-    <t xml:space="preserve">10.867299079895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.971791267395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.832465171814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6234817504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6060647964478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5886487960815</t>
+    <t xml:space="preserve">10.8672981262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9717922210693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8324661254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6234798431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6060657501221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5886497497559</t>
   </si>
   <si>
     <t xml:space="preserve">10.5189876556396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4493255615234</t>
+    <t xml:space="preserve">10.4493246078491</t>
   </si>
   <si>
     <t xml:space="preserve">10.6583118438721</t>
@@ -1883,7 +1883,7 @@
     <t xml:space="preserve">11.0588693618774</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9892072677612</t>
+    <t xml:space="preserve">10.9892063140869</t>
   </si>
   <si>
     <t xml:space="preserve">10.8498830795288</t>
@@ -1907,25 +1907,25 @@
     <t xml:space="preserve">11.0937004089355</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7032442092896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9818935394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9296464920044</t>
+    <t xml:space="preserve">11.7032432556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.981894493103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9296474456787</t>
   </si>
   <si>
     <t xml:space="preserve">11.9122314453125</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8077373504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2605409622192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.086386680603</t>
+    <t xml:space="preserve">11.8077383041382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2605419158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0863857269287</t>
   </si>
   <si>
     <t xml:space="preserve">11.9644775390625</t>
@@ -1940,7 +1940,7 @@
     <t xml:space="preserve">11.5813360214233</t>
   </si>
   <si>
-    <t xml:space="preserve">11.476842880249</t>
+    <t xml:space="preserve">11.4768419265747</t>
   </si>
   <si>
     <t xml:space="preserve">11.6858291625977</t>
@@ -1958,7 +1958,7 @@
     <t xml:space="preserve">11.5987510681152</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7105588912964</t>
+    <t xml:space="preserve">10.7105579376221</t>
   </si>
   <si>
     <t xml:space="preserve">9.70045757293701</t>
@@ -1967,16 +1967,16 @@
     <t xml:space="preserve">9.49146938323975</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03866672515869</t>
+    <t xml:space="preserve">9.03866577148438</t>
   </si>
   <si>
     <t xml:space="preserve">8.98641872406006</t>
   </si>
   <si>
-    <t xml:space="preserve">8.429123878479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18530559539795</t>
+    <t xml:space="preserve">8.42912292480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18530464172363</t>
   </si>
   <si>
     <t xml:space="preserve">8.22884368896484</t>
@@ -1985,79 +1985,79 @@
     <t xml:space="preserve">8.45524597167969</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53361511230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49007701873779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31592082977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32463073730469</t>
+    <t xml:space="preserve">8.533616065979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49007606506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31592178344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32462978363037</t>
   </si>
   <si>
     <t xml:space="preserve">8.16788959503174</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38558387756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28979873657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41170597076416</t>
+    <t xml:space="preserve">8.38558483123779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28979969024658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41170692443848</t>
   </si>
   <si>
     <t xml:space="preserve">8.4987850189209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.638108253479</t>
+    <t xml:space="preserve">8.63810920715332</t>
   </si>
   <si>
     <t xml:space="preserve">8.69035530090332</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67294025421143</t>
+    <t xml:space="preserve">8.67293834686279</t>
   </si>
   <si>
     <t xml:space="preserve">8.79484939575195</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96900367736816</t>
+    <t xml:space="preserve">8.96900463104248</t>
   </si>
   <si>
     <t xml:space="preserve">8.75131034851074</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70777130126953</t>
+    <t xml:space="preserve">8.70777034759521</t>
   </si>
   <si>
     <t xml:space="preserve">8.83838748931885</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18669891357422</t>
+    <t xml:space="preserve">9.1866979598999</t>
   </si>
   <si>
     <t xml:space="preserve">9.05608177185059</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14315891265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23023700714111</t>
+    <t xml:space="preserve">9.14315986633301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23023796081543</t>
   </si>
   <si>
     <t xml:space="preserve">9.40439319610596</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66562747955322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57854843139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31731414794922</t>
+    <t xml:space="preserve">9.66562652587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57854747772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31731510162354</t>
   </si>
   <si>
     <t xml:space="preserve">8.88192558288574</t>
@@ -2069,13 +2069,13 @@
     <t xml:space="preserve">8.51619911193848</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6032772064209</t>
+    <t xml:space="preserve">8.60327816009521</t>
   </si>
   <si>
     <t xml:space="preserve">8.56844711303711</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36085319519043</t>
+    <t xml:space="preserve">9.36085510253906</t>
   </si>
   <si>
     <t xml:space="preserve">9.83978176116943</t>
@@ -2084,13 +2084,13 @@
     <t xml:space="preserve">10.0139360427856</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1010150909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92685985565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88332176208496</t>
+    <t xml:space="preserve">10.1010141372681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92685890197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88332080841064</t>
   </si>
   <si>
     <t xml:space="preserve">10.0574760437012</t>
@@ -2099,16 +2099,16 @@
     <t xml:space="preserve">9.97039794921875</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7091646194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75270366668701</t>
+    <t xml:space="preserve">9.70916366577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7527027130127</t>
   </si>
   <si>
     <t xml:space="preserve">9.6220874786377</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53500938415527</t>
+    <t xml:space="preserve">9.53500843048096</t>
   </si>
   <si>
     <t xml:space="preserve">9.79624271392822</t>
@@ -2117,13 +2117,13 @@
     <t xml:space="preserve">10.1880931854248</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2751693725586</t>
+    <t xml:space="preserve">10.2751703262329</t>
   </si>
   <si>
     <t xml:space="preserve">10.5364027023315</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9282531738281</t>
+    <t xml:space="preserve">10.9282522201538</t>
   </si>
   <si>
     <t xml:space="preserve">11.0153303146362</t>
@@ -2132,7 +2132,7 @@
     <t xml:space="preserve">10.7540979385376</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4928646087646</t>
+    <t xml:space="preserve">10.492865562439</t>
   </si>
   <si>
     <t xml:space="preserve">10.4057865142822</t>
@@ -2141,7 +2141,7 @@
     <t xml:space="preserve">10.362247467041</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3187084197998</t>
+    <t xml:space="preserve">10.3187093734741</t>
   </si>
   <si>
     <t xml:space="preserve">11.1894865036011</t>
@@ -2153,16 +2153,16 @@
     <t xml:space="preserve">11.4507179260254</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0167236328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0602626800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5011930465698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0100746154785</t>
+    <t xml:space="preserve">12.0167245864868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.060263633728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5011940002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0100755691528</t>
   </si>
   <si>
     <t xml:space="preserve">11.8314867019653</t>
@@ -2186,16 +2186,16 @@
     <t xml:space="preserve">11.2510738372803</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5813674926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5367202758789</t>
+    <t xml:space="preserve">10.5813684463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5367212295532</t>
   </si>
   <si>
     <t xml:space="preserve">11.0278387069702</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8938980102539</t>
+    <t xml:space="preserve">10.8938970565796</t>
   </si>
   <si>
     <t xml:space="preserve">11.1617794036865</t>
@@ -2204,16 +2204,16 @@
     <t xml:space="preserve">11.0724849700928</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9207811355591</t>
+    <t xml:space="preserve">11.9207801818848</t>
   </si>
   <si>
     <t xml:space="preserve">12.1886625289917</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2333097457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3226041793823</t>
+    <t xml:space="preserve">12.2333106994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3226051330566</t>
   </si>
   <si>
     <t xml:space="preserve">11.8761339187622</t>
@@ -2222,16 +2222,16 @@
     <t xml:space="preserve">12.1440162658691</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7868385314941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0993690490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4387817382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4834299087524</t>
+    <t xml:space="preserve">11.7868394851685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0993700027466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4387826919556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4834308624268</t>
   </si>
   <si>
     <t xml:space="preserve">13.9299020767212</t>
@@ -2246,55 +2246,55 @@
     <t xml:space="preserve">12.9030170440674</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0816040039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0369577407837</t>
+    <t xml:space="preserve">13.0816049575806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.036958694458</t>
   </si>
   <si>
     <t xml:space="preserve">13.7513122558594</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7959585189819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3941345214844</t>
+    <t xml:space="preserve">13.7959594726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3941354751587</t>
   </si>
   <si>
     <t xml:space="preserve">13.9745483398438</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2601938247681</t>
+    <t xml:space="preserve">13.2601947784424</t>
   </si>
   <si>
     <t xml:space="preserve">13.6620178222656</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6173706054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8852548599243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6442546844482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7781944274902</t>
+    <t xml:space="preserve">13.6173715591431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.88525390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6442556381226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7781963348389</t>
   </si>
   <si>
     <t xml:space="preserve">14.9121379852295</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0907258987427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7335481643677</t>
+    <t xml:space="preserve">15.090726852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.733549118042</t>
   </si>
   <si>
     <t xml:space="preserve">14.4210195541382</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5103130340576</t>
+    <t xml:space="preserve">14.5103139877319</t>
   </si>
   <si>
     <t xml:space="preserve">15.1800203323364</t>
@@ -2309,16 +2309,16 @@
     <t xml:space="preserve">16.0729637145996</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3854923248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.921257019043</t>
+    <t xml:space="preserve">16.3854942321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9212589263916</t>
   </si>
   <si>
     <t xml:space="preserve">17.1891403198242</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7426700592041</t>
+    <t xml:space="preserve">16.7426681518555</t>
   </si>
   <si>
     <t xml:space="preserve">17.7249069213867</t>
@@ -2327,19 +2327,19 @@
     <t xml:space="preserve">17.769552230835</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8142013549805</t>
+    <t xml:space="preserve">17.8142032623291</t>
   </si>
   <si>
     <t xml:space="preserve">17.8588466644287</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0374355316162</t>
+    <t xml:space="preserve">18.0374374389648</t>
   </si>
   <si>
     <t xml:space="preserve">18.12672996521</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3946113586426</t>
+    <t xml:space="preserve">18.3946132659912</t>
   </si>
   <si>
     <t xml:space="preserve">18.5732002258301</t>
@@ -2348,10 +2348,10 @@
     <t xml:space="preserve">16.6980247497559</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3053169250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5909652709961</t>
+    <t xml:space="preserve">18.3053188323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5909671783447</t>
   </si>
   <si>
     <t xml:space="preserve">18.2160243988037</t>
@@ -2360,13 +2360,13 @@
     <t xml:space="preserve">17.9481410980225</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0196704864502</t>
+    <t xml:space="preserve">19.0196723937988</t>
   </si>
   <si>
     <t xml:space="preserve">20.1804981231689</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5376739501953</t>
+    <t xml:space="preserve">20.5376758575439</t>
   </si>
   <si>
     <t xml:space="preserve">20.6269702911377</t>
@@ -2375,10 +2375,10 @@
     <t xml:space="preserve">20.9841461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8055572509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0734405517578</t>
+    <t xml:space="preserve">20.8055553436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0734424591064</t>
   </si>
   <si>
     <t xml:space="preserve">20.0912036895752</t>
@@ -2393,10 +2393,10 @@
     <t xml:space="preserve">20.2697925567627</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1982593536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9126148223877</t>
+    <t xml:space="preserve">19.1982612609863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9126129150391</t>
   </si>
   <si>
     <t xml:space="preserve">19.5554370880127</t>
@@ -2405,16 +2405,16 @@
     <t xml:space="preserve">19.6447334289551</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9303779602051</t>
+    <t xml:space="preserve">18.9303798675537</t>
   </si>
   <si>
     <t xml:space="preserve">20.7162647247314</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4483795166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4306163787842</t>
+    <t xml:space="preserve">20.4483814239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4306182861328</t>
   </si>
   <si>
     <t xml:space="preserve">21.3413219451904</t>
@@ -2429,7 +2429,7 @@
     <t xml:space="preserve">22.0556774139404</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7877960205078</t>
+    <t xml:space="preserve">21.7877941131592</t>
   </si>
   <si>
     <t xml:space="preserve">22.7700309753418</t>
@@ -2444,7 +2444,7 @@
     <t xml:space="preserve">24.0020771026611</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8195514678955</t>
+    <t xml:space="preserve">23.8195533752441</t>
   </si>
   <si>
     <t xml:space="preserve">24.5496520996094</t>
@@ -2459,19 +2459,19 @@
     <t xml:space="preserve">24.0933380126953</t>
   </si>
   <si>
-    <t xml:space="preserve">24.732177734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.367130279541</t>
+    <t xml:space="preserve">24.7321796417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3671283721924</t>
   </si>
   <si>
     <t xml:space="preserve">23.9108142852783</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2719764709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6370277404785</t>
+    <t xml:space="preserve">23.2719745635986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6370258331299</t>
   </si>
   <si>
     <t xml:space="preserve">23.5457630157471</t>
@@ -2480,22 +2480,22 @@
     <t xml:space="preserve">24.2758655548096</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7282886505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1846027374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0059661865234</t>
+    <t xml:space="preserve">23.7282867431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1846008300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0059642791748</t>
   </si>
   <si>
     <t xml:space="preserve">22.3593482971191</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8156623840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.268087387085</t>
+    <t xml:space="preserve">22.8156604766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2680854797363</t>
   </si>
   <si>
     <t xml:space="preserve">22.7243995666504</t>
@@ -2504,7 +2504,7 @@
     <t xml:space="preserve">23.4545021057129</t>
   </si>
   <si>
-    <t xml:space="preserve">23.089448928833</t>
+    <t xml:space="preserve">23.0894508361816</t>
   </si>
   <si>
     <t xml:space="preserve">23.1807117462158</t>
@@ -2513,19 +2513,19 @@
     <t xml:space="preserve">22.9069271087646</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1768245697021</t>
+    <t xml:space="preserve">22.1768226623535</t>
   </si>
   <si>
     <t xml:space="preserve">22.5418758392334</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9942989349365</t>
+    <t xml:space="preserve">21.9943008422852</t>
   </si>
   <si>
     <t xml:space="preserve">22.0855617523193</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5379848480225</t>
+    <t xml:space="preserve">21.5379867553711</t>
   </si>
   <si>
     <t xml:space="preserve">21.7205085754395</t>
@@ -2537,7 +2537,7 @@
     <t xml:space="preserve">21.8117733001709</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4467239379883</t>
+    <t xml:space="preserve">21.4467220306396</t>
   </si>
   <si>
     <t xml:space="preserve">20.8991470336914</t>
@@ -2558,7 +2558,7 @@
     <t xml:space="preserve">19.7127323150635</t>
   </si>
   <si>
-    <t xml:space="preserve">21.081672668457</t>
+    <t xml:space="preserve">21.0816745758057</t>
   </si>
   <si>
     <t xml:space="preserve">24.6409149169922</t>
@@ -2567,13 +2567,13 @@
     <t xml:space="preserve">25.3710155487061</t>
   </si>
   <si>
-    <t xml:space="preserve">26.374906539917</t>
+    <t xml:space="preserve">26.3749046325684</t>
   </si>
   <si>
     <t xml:space="preserve">25.6448059082031</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9185924530029</t>
+    <t xml:space="preserve">25.9185905456543</t>
   </si>
   <si>
     <t xml:space="preserve">25.8273296356201</t>
@@ -2585,34 +2585,34 @@
     <t xml:space="preserve">25.2797546386719</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3632373809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.450611114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6292476654053</t>
+    <t xml:space="preserve">23.3632392883301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4506130218506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6292495727539</t>
   </si>
   <si>
     <t xml:space="preserve">20.9904079437256</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2641983032227</t>
+    <t xml:space="preserve">21.264196395874</t>
   </si>
   <si>
     <t xml:space="preserve">21.1729354858398</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5340976715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8078842163086</t>
+    <t xml:space="preserve">20.5340957641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.80788230896</t>
   </si>
   <si>
     <t xml:space="preserve">20.4428329467773</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9030361175537</t>
+    <t xml:space="preserve">21.9030342102051</t>
   </si>
   <si>
     <t xml:space="preserve">22.6331367492676</t>
@@ -2624,10 +2624,10 @@
     <t xml:space="preserve">20.1690464019775</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3476810455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1651573181152</t>
+    <t xml:space="preserve">19.3476829528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1651554107666</t>
   </si>
   <si>
     <t xml:space="preserve">18.2525291442871</t>
@@ -2636,19 +2636,19 @@
     <t xml:space="preserve">18.6175804138184</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1156349182129</t>
+    <t xml:space="preserve">18.1156368255615</t>
   </si>
   <si>
     <t xml:space="preserve">17.4311676025391</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5224285125732</t>
+    <t xml:space="preserve">17.5224304199219</t>
   </si>
   <si>
     <t xml:space="preserve">16.2447509765625</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5185394287109</t>
+    <t xml:space="preserve">16.5185413360596</t>
   </si>
   <si>
     <t xml:space="preserve">16.6098022460938</t>
@@ -2657,7 +2657,7 @@
     <t xml:space="preserve">16.7010650634766</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6593227386475</t>
+    <t xml:space="preserve">17.6593246459961</t>
   </si>
   <si>
     <t xml:space="preserve">17.2486400604248</t>
@@ -2687,16 +2687,16 @@
     <t xml:space="preserve">21.7661418914795</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8574047088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3137168884277</t>
+    <t xml:space="preserve">21.8574066162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3137187957764</t>
   </si>
   <si>
     <t xml:space="preserve">21.9486656188965</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0399303436279</t>
+    <t xml:space="preserve">22.0399284362793</t>
   </si>
   <si>
     <t xml:space="preserve">21.4923534393311</t>
@@ -2711,19 +2711,19 @@
     <t xml:space="preserve">23.5913944244385</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5001335144043</t>
+    <t xml:space="preserve">23.5001316070557</t>
   </si>
   <si>
     <t xml:space="preserve">23.7337303161621</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8271713256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.387809753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2009315490723</t>
+    <t xml:space="preserve">23.827169418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3878116607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2009296417236</t>
   </si>
   <si>
     <t xml:space="preserve">24.6681289672852</t>
@@ -2732,28 +2732,28 @@
     <t xml:space="preserve">24.621410369873</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0607719421387</t>
+    <t xml:space="preserve">24.06077003479</t>
   </si>
   <si>
     <t xml:space="preserve">23.9673309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5001316070557</t>
+    <t xml:space="preserve">23.500129699707</t>
   </si>
   <si>
     <t xml:space="preserve">22.9394912719727</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7058925628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6591739654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5190124511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.425573348999</t>
+    <t xml:space="preserve">22.7058906555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6591720581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5190143585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4255714416504</t>
   </si>
   <si>
     <t xml:space="preserve">23.4534130096436</t>
@@ -2771,7 +2771,7 @@
     <t xml:space="preserve">22.0985317230225</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9116554260254</t>
+    <t xml:space="preserve">21.9116535186768</t>
   </si>
   <si>
     <t xml:space="preserve">21.6780548095703</t>
@@ -2783,7 +2783,7 @@
     <t xml:space="preserve">23.0329303741455</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9862117767334</t>
+    <t xml:space="preserve">22.986213684082</t>
   </si>
   <si>
     <t xml:space="preserve">21.8182144165039</t>
@@ -2792,7 +2792,7 @@
     <t xml:space="preserve">22.1919727325439</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7714939117432</t>
+    <t xml:space="preserve">21.7714920043945</t>
   </si>
   <si>
     <t xml:space="preserve">22.2386913299561</t>
@@ -2804,13 +2804,13 @@
     <t xml:space="preserve">23.31325340271</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7993335723877</t>
+    <t xml:space="preserve">22.7993316650391</t>
   </si>
   <si>
     <t xml:space="preserve">22.3321323394775</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5846138000488</t>
+    <t xml:space="preserve">21.5846157073975</t>
   </si>
   <si>
     <t xml:space="preserve">20.930534362793</t>
@@ -2822,7 +2822,7 @@
     <t xml:space="preserve">20.2764568328857</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9494152069092</t>
+    <t xml:space="preserve">19.9494171142578</t>
   </si>
   <si>
     <t xml:space="preserve">20.4166164398193</t>
@@ -2843,25 +2843,25 @@
     <t xml:space="preserve">19.9026947021484</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8092555999756</t>
+    <t xml:space="preserve">19.8092575073242</t>
   </si>
   <si>
     <t xml:space="preserve">19.5756568908691</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3420562744141</t>
+    <t xml:space="preserve">19.3420581817627</t>
   </si>
   <si>
     <t xml:space="preserve">19.2486171722412</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9215774536133</t>
+    <t xml:space="preserve">18.9215755462646</t>
   </si>
   <si>
     <t xml:space="preserve">18.8281364440918</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5758495330811</t>
+    <t xml:space="preserve">18.5758476257324</t>
   </si>
   <si>
     <t xml:space="preserve">18.5010967254639</t>
@@ -2873,7 +2873,7 @@
     <t xml:space="preserve">19.5289363861084</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5945377349854</t>
+    <t xml:space="preserve">18.5945358276367</t>
   </si>
   <si>
     <t xml:space="preserve">18.3702812194824</t>
@@ -2882,7 +2882,7 @@
     <t xml:space="preserve">18.0525856018066</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9217700958252</t>
+    <t xml:space="preserve">17.9217720031738</t>
   </si>
   <si>
     <t xml:space="preserve">17.7535781860352</t>
@@ -2894,10 +2894,10 @@
     <t xml:space="preserve">17.7348899841309</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4919452667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2303161621094</t>
+    <t xml:space="preserve">17.4919471740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2303142547607</t>
   </si>
   <si>
     <t xml:space="preserve">17.1742496490479</t>
@@ -2912,7 +2912,7 @@
     <t xml:space="preserve">16.4454212188721</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1277236938477</t>
+    <t xml:space="preserve">16.1277256011963</t>
   </si>
   <si>
     <t xml:space="preserve">16.5014839172363</t>
@@ -2924,13 +2924,13 @@
     <t xml:space="preserve">16.0342845916748</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8847808837891</t>
+    <t xml:space="preserve">15.8847818374634</t>
   </si>
   <si>
     <t xml:space="preserve">15.3241405487061</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6044616699219</t>
+    <t xml:space="preserve">15.6044607162476</t>
   </si>
   <si>
     <t xml:space="preserve">15.7352771759033</t>
@@ -2948,7 +2948,7 @@
     <t xml:space="preserve">16.7444267272949</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7257404327393</t>
+    <t xml:space="preserve">16.7257385253906</t>
   </si>
   <si>
     <t xml:space="preserve">16.9313087463379</t>
@@ -2960,7 +2960,7 @@
     <t xml:space="preserve">17.9965229034424</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2581558227539</t>
+    <t xml:space="preserve">18.2581539154053</t>
   </si>
   <si>
     <t xml:space="preserve">17.6601371765137</t>
@@ -2969,10 +2969,10 @@
     <t xml:space="preserve">17.5666980743408</t>
   </si>
   <si>
-    <t xml:space="preserve">17.641450881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3142166137695</t>
+    <t xml:space="preserve">17.6414489746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3142185211182</t>
   </si>
   <si>
     <t xml:space="preserve">18.0712738037109</t>
@@ -3011,7 +3011,7 @@
     <t xml:space="preserve">17.7162017822266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5293216705322</t>
+    <t xml:space="preserve">17.5293235778809</t>
   </si>
   <si>
     <t xml:space="preserve">16.9873714447021</t>
@@ -3023,10 +3023,10 @@
     <t xml:space="preserve">17.5480117797852</t>
   </si>
   <si>
-    <t xml:space="preserve">16.277229309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9221572875977</t>
+    <t xml:space="preserve">16.2772274017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.922158241272</t>
   </si>
   <si>
     <t xml:space="preserve">16.0155963897705</t>
@@ -3035,19 +3035,19 @@
     <t xml:space="preserve">15.9595327377319</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9782218933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0903472900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8287172317505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6231489181519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5857744216919</t>
+    <t xml:space="preserve">15.9782209396362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0903491973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8287162780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6231479644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5857725143433</t>
   </si>
   <si>
     <t xml:space="preserve">16.0716609954834</t>
@@ -3068,10 +3068,10 @@
     <t xml:space="preserve">16.6322994232178</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6136112213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5762348175049</t>
+    <t xml:space="preserve">16.6136131286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5762367248535</t>
   </si>
   <si>
     <t xml:space="preserve">16.3519802093506</t>
@@ -3080,13 +3080,13 @@
     <t xml:space="preserve">16.2024765014648</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7913408279419</t>
+    <t xml:space="preserve">15.7913398742676</t>
   </si>
   <si>
     <t xml:space="preserve">15.7726516723633</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6978998184204</t>
+    <t xml:space="preserve">15.6979007720947</t>
   </si>
   <si>
     <t xml:space="preserve">16.5201721191406</t>
@@ -3095,34 +3095,34 @@
     <t xml:space="preserve">16.1464138031006</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1650981903076</t>
+    <t xml:space="preserve">16.1651000976562</t>
   </si>
   <si>
     <t xml:space="preserve">16.109037399292</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8474044799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7539663314819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8660917282104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6792125701904</t>
+    <t xml:space="preserve">15.8474025726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7539653778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8660936355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6792144775391</t>
   </si>
   <si>
     <t xml:space="preserve">15.8100280761719</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5110206604004</t>
+    <t xml:space="preserve">15.5110216140747</t>
   </si>
   <si>
     <t xml:space="preserve">15.3802042007446</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0064449310303</t>
+    <t xml:space="preserve">15.0064458847046</t>
   </si>
   <si>
     <t xml:space="preserve">14.8008785247803</t>
@@ -3131,7 +3131,7 @@
     <t xml:space="preserve">14.6700620651245</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4271183013916</t>
+    <t xml:space="preserve">14.4271173477173</t>
   </si>
   <si>
     <t xml:space="preserve">14.5766229629517</t>
@@ -3161,13 +3161,13 @@
     <t xml:space="preserve">15.0811967849731</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5670852661133</t>
+    <t xml:space="preserve">15.567084312439</t>
   </si>
   <si>
     <t xml:space="preserve">15.716588973999</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6605253219604</t>
+    <t xml:space="preserve">15.6605262756348</t>
   </si>
   <si>
     <t xml:space="preserve">15.1933259963989</t>
@@ -3176,13 +3176,13 @@
     <t xml:space="preserve">15.3988933563232</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4175806045532</t>
+    <t xml:space="preserve">15.4175815582275</t>
   </si>
   <si>
     <t xml:space="preserve">15.4362697601318</t>
   </si>
   <si>
-    <t xml:space="preserve">15.137261390686</t>
+    <t xml:space="preserve">15.1372623443604</t>
   </si>
   <si>
     <t xml:space="preserve">15.0438222885132</t>
@@ -3194,7 +3194,7 @@
     <t xml:space="preserve">14.9877586364746</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7261257171631</t>
+    <t xml:space="preserve">14.7261266708374</t>
   </si>
   <si>
     <t xml:space="preserve">14.950382232666</t>
@@ -3209,22 +3209,22 @@
     <t xml:space="preserve">14.3149900436401</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5018701553345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4084310531616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1654872894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.202862739563</t>
+    <t xml:space="preserve">14.5018711090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4084300994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1654863357544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2028617858887</t>
   </si>
   <si>
     <t xml:space="preserve">14.2963027954102</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1281099319458</t>
+    <t xml:space="preserve">14.1281108856201</t>
   </si>
   <si>
     <t xml:space="preserve">13.8291034698486</t>
@@ -3239,19 +3239,19 @@
     <t xml:space="preserve">13.4179677963257</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5487833023071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6422233581543</t>
+    <t xml:space="preserve">13.5487842559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6422243118286</t>
   </si>
   <si>
     <t xml:space="preserve">13.45534324646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3992805480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3245277404785</t>
+    <t xml:space="preserve">13.3992795944214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3245286941528</t>
   </si>
   <si>
     <t xml:space="preserve">13.2497758865356</t>
@@ -3260,7 +3260,7 @@
     <t xml:space="preserve">13.0815839767456</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3432149887085</t>
+    <t xml:space="preserve">13.3432159423828</t>
   </si>
   <si>
     <t xml:space="preserve">13.1937122344971</t>
@@ -3269,7 +3269,7 @@
     <t xml:space="preserve">13.3058395385742</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2589263916016</t>
+    <t xml:space="preserve">14.2589273452759</t>
   </si>
   <si>
     <t xml:space="preserve">14.2776145935059</t>
@@ -3278,7 +3278,7 @@
     <t xml:space="preserve">14.7448139190674</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5575466156006</t>
+    <t xml:space="preserve">16.5575485229492</t>
   </si>
   <si>
     <t xml:space="preserve">16.4641094207764</t>
@@ -3287,13 +3287,13 @@
     <t xml:space="preserve">16.4267311096191</t>
   </si>
   <si>
-    <t xml:space="preserve">16.314603805542</t>
+    <t xml:space="preserve">16.3146018981934</t>
   </si>
   <si>
     <t xml:space="preserve">16.2585391998291</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2398529052734</t>
+    <t xml:space="preserve">16.2398509979248</t>
   </si>
   <si>
     <t xml:space="preserve">16.1837882995605</t>
@@ -3302,13 +3302,13 @@
     <t xml:space="preserve">14.8569412231445</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7074375152588</t>
+    <t xml:space="preserve">14.7074384689331</t>
   </si>
   <si>
     <t xml:space="preserve">14.6887502670288</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3897428512573</t>
+    <t xml:space="preserve">14.389741897583</t>
   </si>
   <si>
     <t xml:space="preserve">14.782190322876</t>
@@ -3329,19 +3329,19 @@
     <t xml:space="preserve">12.9881439208984</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5956964492798</t>
+    <t xml:space="preserve">12.5956954956055</t>
   </si>
   <si>
     <t xml:space="preserve">12.7078247070312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7452001571655</t>
+    <t xml:space="preserve">12.7452011108398</t>
   </si>
   <si>
     <t xml:space="preserve">12.4275054931641</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0442085266113</t>
+    <t xml:space="preserve">13.044207572937</t>
   </si>
   <si>
     <t xml:space="preserve">13.3805913925171</t>
@@ -3368,28 +3368,28 @@
     <t xml:space="preserve">13.9972944259644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0159826278687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6513748168945</t>
+    <t xml:space="preserve">14.015983581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6513738632202</t>
   </si>
   <si>
     <t xml:space="preserve">15.0251340866089</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4736442565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.903468132019</t>
+    <t xml:space="preserve">15.4736452102661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9034700393677</t>
   </si>
   <si>
     <t xml:space="preserve">16.482795715332</t>
   </si>
   <si>
-    <t xml:space="preserve">16.912618637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8565578460693</t>
+    <t xml:space="preserve">16.9126205444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8565559387207</t>
   </si>
   <si>
     <t xml:space="preserve">16.9499950408936</t>
@@ -3398,7 +3398,7 @@
     <t xml:space="preserve">16.8752422332764</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0434341430664</t>
+    <t xml:space="preserve">17.043436050415</t>
   </si>
   <si>
     <t xml:space="preserve">15.9969091415405</t>
@@ -3410,7 +3410,7 @@
     <t xml:space="preserve">15.5483961105347</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6418361663818</t>
+    <t xml:space="preserve">15.6418380737305</t>
   </si>
   <si>
     <t xml:space="preserve">16.4080429077148</t>
@@ -3422,13 +3422,13 @@
     <t xml:space="preserve">16.6790199279785</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5855808258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8002967834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7068576812744</t>
+    <t xml:space="preserve">16.585578918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8002986907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.706859588623</t>
   </si>
   <si>
     <t xml:space="preserve">16.211820602417</t>
@@ -3437,19 +3437,19 @@
     <t xml:space="preserve">15.3708620071411</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3052597045898</t>
+    <t xml:space="preserve">16.3052616119385</t>
   </si>
   <si>
     <t xml:space="preserve">16.0249404907227</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1273384094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9404582977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6134185791016</t>
+    <t xml:space="preserve">18.1273365020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9404602050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6134204864502</t>
   </si>
   <si>
     <t xml:space="preserve">17.7070121765137</t>
@@ -3822,6 +3822,9 @@
   </si>
   <si>
     <t xml:space="preserve">13.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4499998092651</t>
   </si>
 </sst>
 </file>
@@ -69524,7 +69527,7 @@
     </row>
     <row r="2515">
       <c r="A2515" s="1" t="n">
-        <v>45980.6912384259</v>
+        <v>45980.3333333333</v>
       </c>
       <c r="B2515" t="n">
         <v>3477</v>
@@ -69533,7 +69536,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="D2515" t="n">
-        <v>13.5500001907349</v>
+        <v>13.5</v>
       </c>
       <c r="E2515" t="n">
         <v>13.6999998092651</v>
@@ -69545,6 +69548,32 @@
         <v>1269</v>
       </c>
       <c r="H2515" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2516">
+      <c r="A2516" s="1" t="n">
+        <v>45981.691099537</v>
+      </c>
+      <c r="B2516" t="n">
+        <v>3508</v>
+      </c>
+      <c r="C2516" t="n">
+        <v>13.6499996185303</v>
+      </c>
+      <c r="D2516" t="n">
+        <v>13.4499998092651</v>
+      </c>
+      <c r="E2516" t="n">
+        <v>13.6000003814697</v>
+      </c>
+      <c r="F2516" t="n">
+        <v>13.4499998092651</v>
+      </c>
+      <c r="G2516" t="s">
+        <v>1270</v>
+      </c>
+      <c r="H2516" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SAB.MI.xlsx
+++ b/data/SAB.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5656795501709</t>
+    <t xml:space="preserve">8.56568050384521</t>
   </si>
   <si>
     <t xml:space="preserve">SAB.MI</t>
@@ -47,85 +47,85 @@
     <t xml:space="preserve">8.61823081970215</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48310279846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33296012878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37049198150635</t>
+    <t xml:space="preserve">8.4831018447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33295822143555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37049293518066</t>
   </si>
   <si>
     <t xml:space="preserve">8.31794357299805</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25788688659668</t>
+    <t xml:space="preserve">8.25788497924805</t>
   </si>
   <si>
     <t xml:space="preserve">8.16029262542725</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88252878189087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52969074249268</t>
+    <t xml:space="preserve">7.88252830505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52969169616699</t>
   </si>
   <si>
     <t xml:space="preserve">7.66482019424438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62728595733643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61227083206177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73989152908325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75490522384644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76992130279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89754390716553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61977624893188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79994964599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72487640380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65731334686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50716972351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34201240539551</t>
+    <t xml:space="preserve">7.62728309631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61226987838745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73989200592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75490665435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76992034912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89754152297974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61977672576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79995107650757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72487735748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65731430053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50716924667358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34201145172119</t>
   </si>
   <si>
     <t xml:space="preserve">7.54470634460449</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39081001281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58224201202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82247066497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0852222442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11524963378906</t>
+    <t xml:space="preserve">7.39080905914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58224153518677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82247114181519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08522129058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11525058746338</t>
   </si>
   <si>
     <t xml:space="preserve">7.95760059356689</t>
@@ -134,121 +134,121 @@
     <t xml:space="preserve">8.06270027160645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03267288208008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9200644493103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.777428150177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86751461029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80745649337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98762798309326</t>
+    <t xml:space="preserve">8.03267097473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92006397247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77742719650269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86751365661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80745601654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98762941360474</t>
   </si>
   <si>
     <t xml:space="preserve">8.0401782989502</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99513483047485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96510696411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90504884719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93507766723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89003562927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94258499145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82997941970825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81496524810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7323842048645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64980697631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71737003326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67232799530029</t>
+    <t xml:space="preserve">7.99513530731201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96510744094849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90505123138428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93507814407349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89003419876099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94258594512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82997894287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81496286392212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73238372802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64980602264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71737146377563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67232656478882</t>
   </si>
   <si>
     <t xml:space="preserve">7.63479232788086</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51467752456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64229917526245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56722784042358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70235538482666</t>
+    <t xml:space="preserve">7.51467657089233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64229965209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56722831726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70235633850098</t>
   </si>
   <si>
     <t xml:space="preserve">7.74739837646484</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46963310241699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69484901428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49215507507324</t>
+    <t xml:space="preserve">7.46963405609131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69484949111938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4921555519104</t>
   </si>
   <si>
     <t xml:space="preserve">7.47338819503784</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43585157394409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50341558456421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48089504241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59725475311279</t>
+    <t xml:space="preserve">7.43585109710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50341606140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48089551925659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59725618362427</t>
   </si>
   <si>
     <t xml:space="preserve">7.42834520339966</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38705635070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37203979492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31949043273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28195428848267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52122116088867</t>
+    <t xml:space="preserve">7.38705492019653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37204122543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31949090957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28195476531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52122163772583</t>
   </si>
   <si>
     <t xml:space="preserve">7.80533981323242</t>
@@ -257,67 +257,67 @@
     <t xml:space="preserve">7.75009346008301</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75798559188843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81323194503784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86058521270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69879531860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58435869216919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68695545196533</t>
+    <t xml:space="preserve">7.75798654556274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81323099136353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86058378219604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69879627227783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58435821533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68695640563965</t>
   </si>
   <si>
     <t xml:space="preserve">7.57646799087524</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53700590133667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49754571914673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28445672988892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92536306381226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07926177978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22921180725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45808458328247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2607798576355</t>
+    <t xml:space="preserve">7.53700637817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49754428863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28445720672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92536354064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07926082611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22921228408813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45808506011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26078033447266</t>
   </si>
   <si>
     <t xml:space="preserve">7.37127113342285</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26472663879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34759378433228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46992349624634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36732482910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37916326522827</t>
+    <t xml:space="preserve">7.26472759246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34759521484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46992206573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36732387542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37916278839111</t>
   </si>
   <si>
     <t xml:space="preserve">7.13450574874878</t>
@@ -326,106 +326,106 @@
     <t xml:space="preserve">7.18975114822388</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1029372215271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15029144287109</t>
+    <t xml:space="preserve">7.10293865203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15029096603394</t>
   </si>
   <si>
     <t xml:space="preserve">7.10688400268555</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20553493499756</t>
+    <t xml:space="preserve">7.20553541183472</t>
   </si>
   <si>
     <t xml:space="preserve">7.18185949325562</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22131967544556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19369792938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24894142150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1976432800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18580484390259</t>
+    <t xml:space="preserve">7.22132015228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19369745254517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24894189834595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19764280319214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18580532073975</t>
   </si>
   <si>
     <t xml:space="preserve">7.22526550292969</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20948266983032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31602621078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21342802047729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16607570648193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24499559402466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13055992126465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11082935333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17791271209717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23315763473511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27656555175781</t>
+    <t xml:space="preserve">7.20948171615601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3160252571106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21342897415161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16607522964478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24499607086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13056039810181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11083030700684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17791366577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23315858840942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27656507492065</t>
   </si>
   <si>
     <t xml:space="preserve">7.30024147033691</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29234886169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24104976654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1187219619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.095046043396</t>
+    <t xml:space="preserve">7.29235029220581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24105167388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11872243881226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09504556655884</t>
   </si>
   <si>
     <t xml:space="preserve">7.00428581237793</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94509410858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93325614929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09899139404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15423631668091</t>
+    <t xml:space="preserve">6.94509506225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93325710296631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09899091720581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15423583984375</t>
   </si>
   <si>
     <t xml:space="preserve">7.13845300674438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15818214416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05558443069458</t>
+    <t xml:space="preserve">7.1581826210022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05558490753174</t>
   </si>
   <si>
     <t xml:space="preserve">7.07136917114258</t>
@@ -434,7 +434,7 @@
     <t xml:space="preserve">7.06742334365845</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02401638031006</t>
+    <t xml:space="preserve">7.02401542663574</t>
   </si>
   <si>
     <t xml:space="preserve">7.04769325256348</t>
@@ -446,67 +446,67 @@
     <t xml:space="preserve">7.08320760726929</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05164003372192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04374599456787</t>
+    <t xml:space="preserve">7.05163908004761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04374647140503</t>
   </si>
   <si>
     <t xml:space="preserve">7.03190803527832</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05953025817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03585481643677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17396688461304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90563488006592</t>
+    <t xml:space="preserve">7.05953073501587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03585338592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17396783828735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9056339263916</t>
   </si>
   <si>
     <t xml:space="preserve">6.91352605819702</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93720245361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92141914367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94114828109741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9687705039978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14239883422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45019197463989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79350137710571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92372131347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0499963760376</t>
+    <t xml:space="preserve">6.93720197677612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92141819000244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94114875793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96877002716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14239835739136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45019245147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79350090026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9237208366394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04999542236328</t>
   </si>
   <si>
     <t xml:space="preserve">8.207839012146</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16837882995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08945655822754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19994735717773</t>
+    <t xml:space="preserve">8.16837787628174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08945751190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19994926452637</t>
   </si>
   <si>
     <t xml:space="preserve">8.06578063964844</t>
@@ -521,37 +521,37 @@
     <t xml:space="preserve">8.32622146606445</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55509376525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56298637390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42881965637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35779094696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39725017547607</t>
+    <t xml:space="preserve">8.55509281158447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56298732757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42882061004639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35778903961182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39725208282471</t>
   </si>
   <si>
     <t xml:space="preserve">8.42092704772949</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44460487365723</t>
+    <t xml:space="preserve">8.44460296630859</t>
   </si>
   <si>
     <t xml:space="preserve">8.40514183044434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26308441162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18416309356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30254650115967</t>
+    <t xml:space="preserve">8.26308536529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18416118621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30254459381104</t>
   </si>
   <si>
     <t xml:space="preserve">8.22362327575684</t>
@@ -569,13 +569,13 @@
     <t xml:space="preserve">8.3104362487793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36568260192871</t>
+    <t xml:space="preserve">8.36568164825439</t>
   </si>
   <si>
     <t xml:space="preserve">8.33411407470703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34200477600098</t>
+    <t xml:space="preserve">8.34200572967529</t>
   </si>
   <si>
     <t xml:space="preserve">8.46038818359375</t>
@@ -587,55 +587,55 @@
     <t xml:space="preserve">8.74450492858887</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88656330108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00494575500488</t>
+    <t xml:space="preserve">8.88656425476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00494766235352</t>
   </si>
   <si>
     <t xml:space="preserve">9.23381900787354</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30484771728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2653865814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16279029846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19435882568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24960422515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29695510864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36798667907715</t>
+    <t xml:space="preserve">9.30484867095947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26538753509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1627893447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19435787200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24960327148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29695701599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36798477172852</t>
   </si>
   <si>
     <t xml:space="preserve">9.54950428009033</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67577838897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74680805206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2203388214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4807786941528</t>
+    <t xml:space="preserve">9.67577934265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7468090057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2203378677368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4807796478271</t>
   </si>
   <si>
     <t xml:space="preserve">10.4571027755737</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2913675308228</t>
+    <t xml:space="preserve">10.2913684844971</t>
   </si>
   <si>
     <t xml:space="preserve">10.2597990036011</t>
@@ -644,16 +644,16 @@
     <t xml:space="preserve">10.1493082046509</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0861721038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0151414871216</t>
+    <t xml:space="preserve">10.0861701965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0151395797729</t>
   </si>
   <si>
     <t xml:space="preserve">10.1019563674927</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1650924682617</t>
+    <t xml:space="preserve">10.165093421936</t>
   </si>
   <si>
     <t xml:space="preserve">10.0546035766602</t>
@@ -662,10 +662,10 @@
     <t xml:space="preserve">10.1808767318726</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1177396774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1887683868408</t>
+    <t xml:space="preserve">10.1177406311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1887693405151</t>
   </si>
   <si>
     <t xml:space="preserve">10.070387840271</t>
@@ -674,16 +674,16 @@
     <t xml:space="preserve">10.1098489761353</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0230331420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4965620040894</t>
+    <t xml:space="preserve">10.0230340957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.496563911438</t>
   </si>
   <si>
     <t xml:space="preserve">10.4176416397095</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3150444030762</t>
+    <t xml:space="preserve">10.3150434494019</t>
   </si>
   <si>
     <t xml:space="preserve">10.7333288192749</t>
@@ -695,76 +695,76 @@
     <t xml:space="preserve">10.5597019195557</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6386203765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.591269493103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0095539093018</t>
+    <t xml:space="preserve">10.6386213302612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5912704467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0095520019531</t>
   </si>
   <si>
     <t xml:space="preserve">10.8832778930664</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3410243988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0592088699341</t>
+    <t xml:space="preserve">11.3410224914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0592107772827</t>
   </si>
   <si>
     <t xml:space="preserve">11.9171514511108</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0513172149658</t>
+    <t xml:space="preserve">12.0513181686401</t>
   </si>
   <si>
     <t xml:space="preserve">11.6882791519165</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6803874969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2644052505493</t>
+    <t xml:space="preserve">11.6803865432739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2644062042236</t>
   </si>
   <si>
     <t xml:space="preserve">12.6274452209473</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5406322479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6747961044312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7379341125488</t>
+    <t xml:space="preserve">12.5406303405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6747951507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7379350662231</t>
   </si>
   <si>
     <t xml:space="preserve">12.4728555679321</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6518545150757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8471221923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8145780563354</t>
+    <t xml:space="preserve">12.6518516540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8471231460571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8145771026611</t>
   </si>
   <si>
     <t xml:space="preserve">12.9203481674194</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8715314865112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9366207122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8064413070679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6437158584595</t>
+    <t xml:space="preserve">12.8715305328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9366216659546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8064403533936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6437168121338</t>
   </si>
   <si>
     <t xml:space="preserve">12.8227138519287</t>
@@ -779,67 +779,67 @@
     <t xml:space="preserve">11.7812747955322</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9114561080933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9277276992798</t>
+    <t xml:space="preserve">11.9114551544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9277267456055</t>
   </si>
   <si>
     <t xml:space="preserve">11.9602727890015</t>
   </si>
   <si>
-    <t xml:space="preserve">11.805685043335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1311330795288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0009527206421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9846820831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0416355133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0823173522949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.976544380188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8789110183716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7161855697632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4720993041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5534591674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5860061645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7975473403931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8951835632324</t>
+    <t xml:space="preserve">11.8056840896606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1311340332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0009546279907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9846811294556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0416345596313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0823163986206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9765453338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8789100646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7161846160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4721002578735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5534601211548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5860052108765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7975482940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8951826095581</t>
   </si>
   <si>
     <t xml:space="preserve">12.0904512405396</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1636781692505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.074179649353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2287693023682</t>
+    <t xml:space="preserve">12.1636791229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0741806030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2287683486938</t>
   </si>
   <si>
     <t xml:space="preserve">12.1392698287964</t>
@@ -848,13 +848,13 @@
     <t xml:space="preserve">12.2043600082397</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1880884170532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.147406578064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2531776428223</t>
+    <t xml:space="preserve">12.1880874633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1474056243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2531785964966</t>
   </si>
   <si>
     <t xml:space="preserve">12.3670854568481</t>
@@ -866,28 +866,28 @@
     <t xml:space="preserve">12.448447227478</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9447593688965</t>
+    <t xml:space="preserve">12.9447584152222</t>
   </si>
   <si>
     <t xml:space="preserve">12.7820329666138</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8959398269653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0098476409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9528942108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8552598953247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7332143783569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7738952636719</t>
+    <t xml:space="preserve">12.895941734314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0098466873169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9528932571411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8552589416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7332153320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7738971710205</t>
   </si>
   <si>
     <t xml:space="preserve">12.9854393005371</t>
@@ -896,10 +896,10 @@
     <t xml:space="preserve">13.2620706558228</t>
   </si>
   <si>
-    <t xml:space="preserve">13.685154914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9292430877686</t>
+    <t xml:space="preserve">13.6851539611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9292421340942</t>
   </si>
   <si>
     <t xml:space="preserve">13.9943332672119</t>
@@ -908,49 +908,49 @@
     <t xml:space="preserve">13.7502450942993</t>
   </si>
   <si>
-    <t xml:space="preserve">13.815336227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8316097259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0187406539917</t>
+    <t xml:space="preserve">13.8153352737427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8316078186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0187397003174</t>
   </si>
   <si>
     <t xml:space="preserve">14.026876449585</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1814670562744</t>
+    <t xml:space="preserve">14.1814680099487</t>
   </si>
   <si>
     <t xml:space="preserve">14.1570568084717</t>
   </si>
   <si>
-    <t xml:space="preserve">14.230281829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7754125595093</t>
+    <t xml:space="preserve">14.2302837371826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7754106521606</t>
   </si>
   <si>
     <t xml:space="preserve">15.3205404281616</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2961311340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4588575363159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8249855041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7924423217773</t>
+    <t xml:space="preserve">15.2961301803589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4588537216187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8249864578247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.792441368103</t>
   </si>
   <si>
     <t xml:space="preserve">15.5076723098755</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8493928909302</t>
+    <t xml:space="preserve">15.8493957519531</t>
   </si>
   <si>
     <t xml:space="preserve">15.8656673431396</t>
@@ -959,7 +959,7 @@
     <t xml:space="preserve">15.5158081054688</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0039825439453</t>
+    <t xml:space="preserve">16.0039844512939</t>
   </si>
   <si>
     <t xml:space="preserve">16.2643432617188</t>
@@ -968,10 +968,10 @@
     <t xml:space="preserve">16.7769260406494</t>
   </si>
   <si>
-    <t xml:space="preserve">16.955924987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4115543365479</t>
+    <t xml:space="preserve">16.9559230804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4115524291992</t>
   </si>
   <si>
     <t xml:space="preserve">17.0454235076904</t>
@@ -980,70 +980,70 @@
     <t xml:space="preserve">18.0787239074707</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6475048065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0217723846436</t>
+    <t xml:space="preserve">17.6475067138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0217704772949</t>
   </si>
   <si>
     <t xml:space="preserve">18.0543174743652</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1275424957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2984027862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4123096466064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1682224273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1600894927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9160022735596</t>
+    <t xml:space="preserve">18.1275444030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2984008789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4123115539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1682262420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1600875854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9160003662109</t>
   </si>
   <si>
     <t xml:space="preserve">17.2651023864746</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0861053466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2976455688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0047416687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1267852783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8745613098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0779666900635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8664283752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7850608825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.988468170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5979290008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.915246963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8338813781738</t>
+    <t xml:space="preserve">17.0861034393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2976474761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0047397613525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1267833709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8745594024658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0779685974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8664245605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.785062789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9884662628174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5979270935059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9152450561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8338775634766</t>
   </si>
   <si>
     <t xml:space="preserve">16.9640617370605</t>
@@ -1055,19 +1055,19 @@
     <t xml:space="preserve">16.9233779907227</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1349220275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0698299407959</t>
+    <t xml:space="preserve">17.1349239349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0698318481445</t>
   </si>
   <si>
     <t xml:space="preserve">17.1674671173096</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6637744903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2251758575439</t>
+    <t xml:space="preserve">17.6637783050537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2251796722412</t>
   </si>
   <si>
     <t xml:space="preserve">18.8598041534424</t>
@@ -1079,7 +1079,7 @@
     <t xml:space="preserve">18.7052154541016</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6319923400879</t>
+    <t xml:space="preserve">18.6319904327393</t>
   </si>
   <si>
     <t xml:space="preserve">18.7377624511719</t>
@@ -1091,13 +1091,13 @@
     <t xml:space="preserve">18.59130859375</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3065395355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6157150268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2170391082764</t>
+    <t xml:space="preserve">18.3065376281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6157169342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.217041015625</t>
   </si>
   <si>
     <t xml:space="preserve">18.2089042663574</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">16.9071083068848</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4758853912354</t>
+    <t xml:space="preserve">16.4758834838867</t>
   </si>
   <si>
     <t xml:space="preserve">16.3945217132568</t>
@@ -1124,7 +1124,7 @@
     <t xml:space="preserve">16.3619785308838</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2806167602539</t>
+    <t xml:space="preserve">16.2806148529053</t>
   </si>
   <si>
     <t xml:space="preserve">16.3782501220703</t>
@@ -1133,7 +1133,7 @@
     <t xml:space="preserve">16.1992568969727</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2236633300781</t>
+    <t xml:space="preserve">16.2236614227295</t>
   </si>
   <si>
     <t xml:space="preserve">16.2724800109863</t>
@@ -1142,16 +1142,16 @@
     <t xml:space="preserve">16.679292678833</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3131618499756</t>
+    <t xml:space="preserve">16.313159942627</t>
   </si>
   <si>
     <t xml:space="preserve">16.0934829711914</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9470300674438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1911144256592</t>
+    <t xml:space="preserve">15.9470319747925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1911163330078</t>
   </si>
   <si>
     <t xml:space="preserve">16.3538436889648</t>
@@ -1160,16 +1160,16 @@
     <t xml:space="preserve">16.0283946990967</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9144859313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1822233200073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9706802368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1008615493774</t>
+    <t xml:space="preserve">15.9144849777222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1822242736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9706811904907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1008605957031</t>
   </si>
   <si>
     <t xml:space="preserve">14.873046875</t>
@@ -1178,28 +1178,28 @@
     <t xml:space="preserve">14.222146987915</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8478813171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8893175125122</t>
+    <t xml:space="preserve">13.8478803634644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8893194198608</t>
   </si>
   <si>
     <t xml:space="preserve">15.1984968185425</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3937683105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5402173995972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9381351470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.59641456604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4011459350586</t>
+    <t xml:space="preserve">15.3937664031982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5402164459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.938136100769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5964136123657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4011449813843</t>
   </si>
   <si>
     <t xml:space="preserve">14.2058734893799</t>
@@ -1208,91 +1208,91 @@
     <t xml:space="preserve">14.1082401275635</t>
   </si>
   <si>
-    <t xml:space="preserve">14.059422492981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9129705429077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0106039047241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3197813034058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6452302932739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7428684234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7265958786011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2147693634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.807957649231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8567724227905</t>
+    <t xml:space="preserve">14.0594244003296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9129686355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0106048583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3197832107544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6452322006226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7428674697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7265939712524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2147703170776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8079566955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8567752838135</t>
   </si>
   <si>
     <t xml:space="preserve">14.9544086456299</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7916841506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2709665298462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0032272338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4825086593628</t>
+    <t xml:space="preserve">14.7916860580444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2709646224976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0032262802124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4825048446655</t>
   </si>
   <si>
     <t xml:space="preserve">14.9218645095825</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9055919647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0194978713989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0520439147949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2562084197998</t>
+    <t xml:space="preserve">14.9055910110474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0194997787476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0520448684692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2562065124512</t>
   </si>
   <si>
     <t xml:space="preserve">15.7354869842529</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8168516159058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6215829849243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9307565689087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6866703033447</t>
+    <t xml:space="preserve">15.8168506622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6215810775757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9307584762573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6866693496704</t>
   </si>
   <si>
     <t xml:space="preserve">15.7192163467407</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7029418945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6703996658325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6053085327148</t>
+    <t xml:space="preserve">15.7029409408569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6703977584839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6053094863892</t>
   </si>
   <si>
     <t xml:space="preserve">15.5653514862061</t>
@@ -1301,16 +1301,16 @@
     <t xml:space="preserve">14.9956827163696</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0291938781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0627021789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2470083236694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2302532196045</t>
+    <t xml:space="preserve">15.0291919708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0627031326294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2470073699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2302541732788</t>
   </si>
   <si>
     <t xml:space="preserve">15.5318422317505</t>
@@ -1319,31 +1319,31 @@
     <t xml:space="preserve">15.7161464691162</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8669414520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5821084976196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.498330116272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4815740585327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4145545959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.179988861084</t>
+    <t xml:space="preserve">15.8669424057007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.582106590271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4983320236206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4815769195557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4145565032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1799879074097</t>
   </si>
   <si>
     <t xml:space="preserve">15.0794582366943</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1129693984985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3589954376221</t>
+    <t xml:space="preserve">15.1129674911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3589944839478</t>
   </si>
   <si>
     <t xml:space="preserve">14.291974067688</t>
@@ -1352,13 +1352,13 @@
     <t xml:space="preserve">14.2584648132324</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4595241546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4092607498169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5600547790527</t>
+    <t xml:space="preserve">14.4595232009888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4092597961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5600519180298</t>
   </si>
   <si>
     <t xml:space="preserve">13.4039621353149</t>
@@ -1367,10 +1367,10 @@
     <t xml:space="preserve">13.4877376556396</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2364120483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5380010604858</t>
+    <t xml:space="preserve">13.2364130020142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5380020141602</t>
   </si>
   <si>
     <t xml:space="preserve">13.4374732971191</t>
@@ -1382,31 +1382,31 @@
     <t xml:space="preserve">13.5882663726807</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6887969970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4207181930542</t>
+    <t xml:space="preserve">13.6887950897217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4207172393799</t>
   </si>
   <si>
     <t xml:space="preserve">13.5212459564209</t>
   </si>
   <si>
-    <t xml:space="preserve">13.57151222229</t>
+    <t xml:space="preserve">13.5715112686157</t>
   </si>
   <si>
     <t xml:space="preserve">13.3201875686646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1526374816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1861476898193</t>
+    <t xml:space="preserve">13.1526384353638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.186146736145</t>
   </si>
   <si>
     <t xml:space="preserve">13.2196578979492</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3034324645996</t>
+    <t xml:space="preserve">13.3034315109253</t>
   </si>
   <si>
     <t xml:space="preserve">12.8510494232178</t>
@@ -1415,7 +1415,7 @@
     <t xml:space="preserve">12.683500289917</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5662136077881</t>
+    <t xml:space="preserve">12.5662145614624</t>
   </si>
   <si>
     <t xml:space="preserve">12.901312828064</t>
@@ -1439,7 +1439,7 @@
     <t xml:space="preserve">11.979790687561</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5609178543091</t>
+    <t xml:space="preserve">11.5609169006348</t>
   </si>
   <si>
     <t xml:space="preserve">11.1923084259033</t>
@@ -1448,52 +1448,52 @@
     <t xml:space="preserve">11.2258176803589</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4321746826172</t>
+    <t xml:space="preserve">12.4321756362915</t>
   </si>
   <si>
     <t xml:space="preserve">13.1191272735596</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2531681060791</t>
+    <t xml:space="preserve">13.2531661987305</t>
   </si>
   <si>
     <t xml:space="preserve">13.2866773605347</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7672729492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3536977767944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9850883483887</t>
+    <t xml:space="preserve">12.7672739028931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3536968231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.985089302063</t>
   </si>
   <si>
     <t xml:space="preserve">12.8007841110229</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6332349777222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8678035736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8122415542603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6279373168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6111822128296</t>
+    <t xml:space="preserve">12.6332340240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8678045272827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8122434616089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6279382705688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6111812591553</t>
   </si>
   <si>
     <t xml:space="preserve">11.7284669876099</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9630365371704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.896017074585</t>
+    <t xml:space="preserve">11.9630355834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8960161209106</t>
   </si>
   <si>
     <t xml:space="preserve">11.6614465713501</t>
@@ -1502,94 +1502,94 @@
     <t xml:space="preserve">11.075023651123</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0415143966675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9577388763428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7566804885864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9242296218872</t>
+    <t xml:space="preserve">11.0415134429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9577398300171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7566795349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9242286682129</t>
   </si>
   <si>
     <t xml:space="preserve">10.9744939804077</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7117118835449</t>
+    <t xml:space="preserve">11.7117128372192</t>
   </si>
   <si>
     <t xml:space="preserve">12.3651552200317</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4603881835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1587982177734</t>
+    <t xml:space="preserve">11.4603891372681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1587972640991</t>
   </si>
   <si>
     <t xml:space="preserve">11.1252889633179</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1755533218384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3766136169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2311162948608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3986654281616</t>
+    <t xml:space="preserve">11.1755542755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3766117095947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2311153411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3986644744873</t>
   </si>
   <si>
     <t xml:space="preserve">11.9295263290405</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7954864501953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.87926197052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1976051330566</t>
+    <t xml:space="preserve">11.7954874038696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8792629241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.197606086731</t>
   </si>
   <si>
     <t xml:space="preserve">12.2478704452515</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0133028030396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1305856704712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.180850982666</t>
+    <t xml:space="preserve">12.0132999420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1305847167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1808500289917</t>
   </si>
   <si>
     <t xml:space="preserve">12.3819103240967</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3316459655762</t>
+    <t xml:space="preserve">12.3316450119019</t>
   </si>
   <si>
     <t xml:space="preserve">12.4656848907471</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5997247695923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7170095443726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8845586776733</t>
+    <t xml:space="preserve">12.599723815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7170085906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8845596313477</t>
   </si>
   <si>
     <t xml:space="preserve">12.9515781402588</t>
   </si>
   <si>
-    <t xml:space="preserve">12.968334197998</t>
+    <t xml:space="preserve">12.9683332443237</t>
   </si>
   <si>
     <t xml:space="preserve">13.2029027938843</t>
@@ -1598,28 +1598,28 @@
     <t xml:space="preserve">12.7337646484375</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8175401687622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6499891281128</t>
+    <t xml:space="preserve">12.8175392150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6499900817871</t>
   </si>
   <si>
     <t xml:space="preserve">12.7002544403076</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5159482955933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7840299606323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0018434524536</t>
+    <t xml:space="preserve">12.5159492492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.784029006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0018444061279</t>
   </si>
   <si>
     <t xml:space="preserve">13.0353546142578</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5494585037231</t>
+    <t xml:space="preserve">12.5494594573975</t>
   </si>
   <si>
     <t xml:space="preserve">12.9348230361938</t>
@@ -1637,7 +1637,7 @@
     <t xml:space="preserve">13.8228359222412</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5044918060303</t>
+    <t xml:space="preserve">13.5044937133789</t>
   </si>
   <si>
     <t xml:space="preserve">13.4542255401611</t>
@@ -1649,55 +1649,55 @@
     <t xml:space="preserve">13.7223062515259</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3704538345337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0521078109741</t>
+    <t xml:space="preserve">13.3704528808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0521087646484</t>
   </si>
   <si>
     <t xml:space="preserve">13.0185985565186</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1693935394287</t>
+    <t xml:space="preserve">13.1693925857544</t>
   </si>
   <si>
     <t xml:space="preserve">13.1023740768433</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4991941452026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7481775283813</t>
+    <t xml:space="preserve">12.499195098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.748176574707</t>
   </si>
   <si>
     <t xml:space="preserve">12.5740203857422</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3650360107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2257099151611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2779569625854</t>
+    <t xml:space="preserve">12.3650341033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2257108688354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2779579162598</t>
   </si>
   <si>
     <t xml:space="preserve">12.3127889633179</t>
   </si>
   <si>
-    <t xml:space="preserve">12.295373916626</t>
+    <t xml:space="preserve">12.2953720092773</t>
   </si>
   <si>
     <t xml:space="preserve">12.3302030563354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1212167739868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5217752456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4869451522827</t>
+    <t xml:space="preserve">12.1212177276611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5217742919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4869432449341</t>
   </si>
   <si>
     <t xml:space="preserve">12.452112197876</t>
@@ -1712,16 +1712,16 @@
     <t xml:space="preserve">11.8948154449463</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2082948684692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8178396224976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7655925750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6436834335327</t>
+    <t xml:space="preserve">12.2082958221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8178386688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7655916213989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.643684387207</t>
   </si>
   <si>
     <t xml:space="preserve">12.399866104126</t>
@@ -1730,34 +1730,34 @@
     <t xml:space="preserve">12.6262683868408</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5391893386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8700857162476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9745788574219</t>
+    <t xml:space="preserve">12.5391902923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8700866699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9745779037476</t>
   </si>
   <si>
     <t xml:space="preserve">12.95716381073</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9397468566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7830085754395</t>
+    <t xml:space="preserve">12.9397478103638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7830095291138</t>
   </si>
   <si>
     <t xml:space="preserve">12.6959295272827</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8004217147827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8875017166138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1560487747192</t>
+    <t xml:space="preserve">12.8004236221313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8875007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1560478210449</t>
   </si>
   <si>
     <t xml:space="preserve">12.0341396331787</t>
@@ -1766,22 +1766,22 @@
     <t xml:space="preserve">11.7206602096558</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2431268692017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7554912567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6684122085571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9993076324463</t>
+    <t xml:space="preserve">12.2431259155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7554922103882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6684131622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9993085861206</t>
   </si>
   <si>
     <t xml:space="preserve">12.0689706802368</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1038017272949</t>
+    <t xml:space="preserve">12.1038007736206</t>
   </si>
   <si>
     <t xml:space="preserve">11.790322303772</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">11.8251533508301</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8599834442139</t>
+    <t xml:space="preserve">11.8599843978882</t>
   </si>
   <si>
     <t xml:space="preserve">11.7729063034058</t>
@@ -1805,7 +1805,7 @@
     <t xml:space="preserve">11.8774003982544</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6509971618652</t>
+    <t xml:space="preserve">11.6509981155396</t>
   </si>
   <si>
     <t xml:space="preserve">11.5465040206909</t>
@@ -1817,70 +1817,70 @@
     <t xml:space="preserve">11.2156095504761</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4071798324585</t>
+    <t xml:space="preserve">11.4071807861328</t>
   </si>
   <si>
     <t xml:space="preserve">11.3026866912842</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3549337387085</t>
+    <t xml:space="preserve">11.3549327850342</t>
   </si>
   <si>
     <t xml:space="preserve">11.3897638320923</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1981916427612</t>
+    <t xml:space="preserve">11.1981935501099</t>
   </si>
   <si>
     <t xml:space="preserve">10.9369602203369</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0414533615112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8847141265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8672981262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.971791267395</t>
+    <t xml:space="preserve">11.0414543151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8847150802612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8672971725464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9717931747437</t>
   </si>
   <si>
     <t xml:space="preserve">10.8324670791626</t>
   </si>
   <si>
-    <t xml:space="preserve">10.623480796814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6060647964478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5886497497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5189876556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4493255615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6583118438721</t>
+    <t xml:space="preserve">10.6234798431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6060657501221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5886487960815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5189867019653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4493265151978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6583108901978</t>
   </si>
   <si>
     <t xml:space="preserve">10.7802200317383</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1633625030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1111173629761</t>
+    <t xml:space="preserve">11.1633634567261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1111154556274</t>
   </si>
   <si>
     <t xml:space="preserve">11.0588693618774</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9892072677612</t>
+    <t xml:space="preserve">10.9892063140869</t>
   </si>
   <si>
     <t xml:space="preserve">10.8498821258545</t>
@@ -1892,34 +1892,34 @@
     <t xml:space="preserve">11.0066232681274</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7976360321045</t>
+    <t xml:space="preserve">10.7976350784302</t>
   </si>
   <si>
     <t xml:space="preserve">10.8150520324707</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9543762207031</t>
+    <t xml:space="preserve">10.9543752670288</t>
   </si>
   <si>
     <t xml:space="preserve">11.0937004089355</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7032442092896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9818935394287</t>
+    <t xml:space="preserve">11.7032432556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9818925857544</t>
   </si>
   <si>
     <t xml:space="preserve">11.9296464920044</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9122314453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8077373504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2605409622192</t>
+    <t xml:space="preserve">11.9122304916382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8077392578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2605419158936</t>
   </si>
   <si>
     <t xml:space="preserve">12.086386680603</t>
@@ -1934,19 +1934,19 @@
     <t xml:space="preserve">11.4942579269409</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5813360214233</t>
+    <t xml:space="preserve">11.581335067749</t>
   </si>
   <si>
     <t xml:space="preserve">11.476842880249</t>
   </si>
   <si>
-    <t xml:space="preserve">11.685830116272</t>
+    <t xml:space="preserve">11.6858291625977</t>
   </si>
   <si>
     <t xml:space="preserve">12.1908798217773</t>
   </si>
   <si>
-    <t xml:space="preserve">12.347620010376</t>
+    <t xml:space="preserve">12.3476209640503</t>
   </si>
   <si>
     <t xml:space="preserve">11.5116729736328</t>
@@ -1955,22 +1955,22 @@
     <t xml:space="preserve">11.5987510681152</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7105588912964</t>
+    <t xml:space="preserve">10.7105579376221</t>
   </si>
   <si>
     <t xml:space="preserve">9.70045852661133</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49147033691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03866672515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98641872406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.429123878479</t>
+    <t xml:space="preserve">9.49146938323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03866577148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98641967773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42912101745605</t>
   </si>
   <si>
     <t xml:space="preserve">8.18530464172363</t>
@@ -1979,16 +1979,16 @@
     <t xml:space="preserve">8.22884368896484</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45524597167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53361511230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49007797241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31592082977295</t>
+    <t xml:space="preserve">8.45524501800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.533616065979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49007701873779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31592178344727</t>
   </si>
   <si>
     <t xml:space="preserve">8.32463073730469</t>
@@ -2000,40 +2000,40 @@
     <t xml:space="preserve">8.38558483123779</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28979873657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41170501708984</t>
+    <t xml:space="preserve">8.28979778289795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41170787811279</t>
   </si>
   <si>
     <t xml:space="preserve">8.4987850189209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.638108253479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69035625457764</t>
+    <t xml:space="preserve">8.63810920715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69035530090332</t>
   </si>
   <si>
     <t xml:space="preserve">8.67294025421143</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79484939575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96900463104248</t>
+    <t xml:space="preserve">8.79485034942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96900367736816</t>
   </si>
   <si>
     <t xml:space="preserve">8.75131034851074</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70777130126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83838844299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18669891357422</t>
+    <t xml:space="preserve">8.70777034759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83838748931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1866979598999</t>
   </si>
   <si>
     <t xml:space="preserve">9.05608177185059</t>
@@ -2042,10 +2042,10 @@
     <t xml:space="preserve">9.14315891265869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23023700714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40439319610596</t>
+    <t xml:space="preserve">9.23023796081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40439224243164</t>
   </si>
   <si>
     <t xml:space="preserve">9.66562652587891</t>
@@ -2057,16 +2057,16 @@
     <t xml:space="preserve">9.31731510162354</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88192558288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65552425384521</t>
+    <t xml:space="preserve">8.88192653656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65552520751953</t>
   </si>
   <si>
     <t xml:space="preserve">8.51620006561279</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6032772064209</t>
+    <t xml:space="preserve">8.60327816009521</t>
   </si>
   <si>
     <t xml:space="preserve">8.56844711303711</t>
@@ -2078,16 +2078,16 @@
     <t xml:space="preserve">9.83978176116943</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0139350891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1010150909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92685985565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88331985473633</t>
+    <t xml:space="preserve">10.01393699646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1010141372681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92685890197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88332176208496</t>
   </si>
   <si>
     <t xml:space="preserve">10.0574760437012</t>
@@ -2105,49 +2105,49 @@
     <t xml:space="preserve">9.6220874786377</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53500843048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79624271392822</t>
+    <t xml:space="preserve">9.53500938415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79624176025391</t>
   </si>
   <si>
     <t xml:space="preserve">10.1880922317505</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2751693725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5364027023315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9282531738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0153303146362</t>
+    <t xml:space="preserve">10.2751703262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5364036560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9282522201538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0153284072876</t>
   </si>
   <si>
     <t xml:space="preserve">10.7540979385376</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4928646087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4057865142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3622465133667</t>
+    <t xml:space="preserve">10.4928636550903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4057855606079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.362247467041</t>
   </si>
   <si>
     <t xml:space="preserve">10.3187084197998</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1894855499268</t>
+    <t xml:space="preserve">11.1894865036011</t>
   </si>
   <si>
     <t xml:space="preserve">11.2765636444092</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4507179260254</t>
+    <t xml:space="preserve">11.4507188796997</t>
   </si>
   <si>
     <t xml:space="preserve">12.0167245864868</t>
@@ -2162,7 +2162,7 @@
     <t xml:space="preserve">12.0100746154785</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8314867019653</t>
+    <t xml:space="preserve">11.831485748291</t>
   </si>
   <si>
     <t xml:space="preserve">11.6975450515747</t>
@@ -2171,13 +2171,13 @@
     <t xml:space="preserve">11.4743099212646</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2064266204834</t>
+    <t xml:space="preserve">11.2064275741577</t>
   </si>
   <si>
     <t xml:space="preserve">11.4296627044678</t>
   </si>
   <si>
-    <t xml:space="preserve">11.608250617981</t>
+    <t xml:space="preserve">11.6082496643066</t>
   </si>
   <si>
     <t xml:space="preserve">11.2510738372803</t>
@@ -2192,10 +2192,10 @@
     <t xml:space="preserve">11.0278387069702</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8938980102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1617794036865</t>
+    <t xml:space="preserve">10.8938961029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1617784500122</t>
   </si>
   <si>
     <t xml:space="preserve">11.0724849700928</t>
@@ -2204,13 +2204,13 @@
     <t xml:space="preserve">11.9207811355591</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1886625289917</t>
+    <t xml:space="preserve">12.188663482666</t>
   </si>
   <si>
     <t xml:space="preserve">12.2333097457886</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3226041793823</t>
+    <t xml:space="preserve">12.3226051330566</t>
   </si>
   <si>
     <t xml:space="preserve">11.8761339187622</t>
@@ -2222,100 +2222,100 @@
     <t xml:space="preserve">11.7868385314941</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0993690490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4387817382812</t>
+    <t xml:space="preserve">12.0993700027466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4387826919556</t>
   </si>
   <si>
     <t xml:space="preserve">13.4834299087524</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9299020767212</t>
+    <t xml:space="preserve">13.9299011230469</t>
   </si>
   <si>
     <t xml:space="preserve">13.8406066894531</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0191955566406</t>
+    <t xml:space="preserve">14.0191946029663</t>
   </si>
   <si>
     <t xml:space="preserve">12.9030170440674</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0816040039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0369577407837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7513122558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7959585189819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3941345214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9745483398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2601938247681</t>
+    <t xml:space="preserve">13.0816059112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0369596481323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7513113021851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7959594726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3941354751587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9745473861694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2601947784424</t>
   </si>
   <si>
     <t xml:space="preserve">13.6620178222656</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6173706054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8852548599243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6442546844482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7781944274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9121379852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0907258987427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7335481643677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4210195541382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5103130340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1800203323364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8497276306152</t>
+    <t xml:space="preserve">13.6173715591431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.88525390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6442537307739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7781963348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9121370315552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0907249450684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.733549118042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4210186004639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5103139877319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1800212860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8497266769409</t>
   </si>
   <si>
     <t xml:space="preserve">15.8050813674927</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0729637145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3854923248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.921257019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1891403198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7426700592041</t>
+    <t xml:space="preserve">16.072961807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3854942321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9212589263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1891384124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7426681518555</t>
   </si>
   <si>
     <t xml:space="preserve">17.7249069213867</t>
@@ -2330,13 +2330,13 @@
     <t xml:space="preserve">17.8588466644287</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0374355316162</t>
+    <t xml:space="preserve">18.0374374389648</t>
   </si>
   <si>
     <t xml:space="preserve">18.12672996521</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3946113586426</t>
+    <t xml:space="preserve">18.3946132659912</t>
   </si>
   <si>
     <t xml:space="preserve">18.5732002258301</t>
@@ -2345,22 +2345,22 @@
     <t xml:space="preserve">16.6980247497559</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3053169250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5909652709961</t>
+    <t xml:space="preserve">18.3053188323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5909671783447</t>
   </si>
   <si>
     <t xml:space="preserve">18.2160243988037</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9481410980225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0196704864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1804981231689</t>
+    <t xml:space="preserve">17.9481430053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0196723937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1805000305176</t>
   </si>
   <si>
     <t xml:space="preserve">20.5376739501953</t>
@@ -2369,10 +2369,10 @@
     <t xml:space="preserve">20.6269702911377</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9841461181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8055572509766</t>
+    <t xml:space="preserve">20.9841442108154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8055553436279</t>
   </si>
   <si>
     <t xml:space="preserve">21.0734405517578</t>
@@ -2387,37 +2387,37 @@
     <t xml:space="preserve">19.8233222961426</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2697925567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1982593536377</t>
+    <t xml:space="preserve">20.2697944641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1982612609863</t>
   </si>
   <si>
     <t xml:space="preserve">19.9126148223877</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5554370880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6447334289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9303779602051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7162647247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4483795166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4306163787842</t>
+    <t xml:space="preserve">19.5554389953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6447315216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9303798675537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7162628173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4483814239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4306144714355</t>
   </si>
   <si>
     <t xml:space="preserve">21.3413219451904</t>
   </si>
   <si>
-    <t xml:space="preserve">22.323558807373</t>
+    <t xml:space="preserve">22.3235569000244</t>
   </si>
   <si>
     <t xml:space="preserve">21.6092052459717</t>
@@ -2426,10 +2426,10 @@
     <t xml:space="preserve">22.0556774139404</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7877960205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7700309753418</t>
+    <t xml:space="preserve">21.7877922058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7700290679932</t>
   </si>
   <si>
     <t xml:space="preserve">24.9147033691406</t>
@@ -2441,7 +2441,7 @@
     <t xml:space="preserve">24.0020771026611</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8195514678955</t>
+    <t xml:space="preserve">23.8195533752441</t>
   </si>
   <si>
     <t xml:space="preserve">24.5496520996094</t>
@@ -2456,19 +2456,19 @@
     <t xml:space="preserve">24.0933380126953</t>
   </si>
   <si>
-    <t xml:space="preserve">24.732177734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.367130279541</t>
+    <t xml:space="preserve">24.7321796417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3671283721924</t>
   </si>
   <si>
     <t xml:space="preserve">23.9108142852783</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2719764709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6370277404785</t>
+    <t xml:space="preserve">23.2719745635986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6370258331299</t>
   </si>
   <si>
     <t xml:space="preserve">23.5457630157471</t>
@@ -2477,22 +2477,22 @@
     <t xml:space="preserve">24.2758655548096</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7282886505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1846027374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0059661865234</t>
+    <t xml:space="preserve">23.7282867431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1846008300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0059642791748</t>
   </si>
   <si>
     <t xml:space="preserve">22.3593482971191</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8156623840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.268087387085</t>
+    <t xml:space="preserve">22.8156604766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2680854797363</t>
   </si>
   <si>
     <t xml:space="preserve">22.7243995666504</t>
@@ -2501,7 +2501,7 @@
     <t xml:space="preserve">23.4545021057129</t>
   </si>
   <si>
-    <t xml:space="preserve">23.089448928833</t>
+    <t xml:space="preserve">23.0894508361816</t>
   </si>
   <si>
     <t xml:space="preserve">23.1807117462158</t>
@@ -2510,19 +2510,19 @@
     <t xml:space="preserve">22.9069271087646</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1768245697021</t>
+    <t xml:space="preserve">22.1768226623535</t>
   </si>
   <si>
     <t xml:space="preserve">22.5418758392334</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9942989349365</t>
+    <t xml:space="preserve">21.9943008422852</t>
   </si>
   <si>
     <t xml:space="preserve">22.0855617523193</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5379848480225</t>
+    <t xml:space="preserve">21.5379867553711</t>
   </si>
   <si>
     <t xml:space="preserve">21.7205085754395</t>
@@ -2534,7 +2534,7 @@
     <t xml:space="preserve">21.8117733001709</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4467239379883</t>
+    <t xml:space="preserve">21.4467220306396</t>
   </si>
   <si>
     <t xml:space="preserve">20.8991470336914</t>
@@ -2555,7 +2555,7 @@
     <t xml:space="preserve">19.7127323150635</t>
   </si>
   <si>
-    <t xml:space="preserve">21.081672668457</t>
+    <t xml:space="preserve">21.0816745758057</t>
   </si>
   <si>
     <t xml:space="preserve">24.6409149169922</t>
@@ -2564,13 +2564,13 @@
     <t xml:space="preserve">25.3710155487061</t>
   </si>
   <si>
-    <t xml:space="preserve">26.374906539917</t>
+    <t xml:space="preserve">26.3749046325684</t>
   </si>
   <si>
     <t xml:space="preserve">25.6448059082031</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9185924530029</t>
+    <t xml:space="preserve">25.9185905456543</t>
   </si>
   <si>
     <t xml:space="preserve">25.8273296356201</t>
@@ -2582,34 +2582,34 @@
     <t xml:space="preserve">25.2797546386719</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3632373809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.450611114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6292476654053</t>
+    <t xml:space="preserve">23.3632392883301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4506130218506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6292495727539</t>
   </si>
   <si>
     <t xml:space="preserve">20.9904079437256</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2641983032227</t>
+    <t xml:space="preserve">21.264196395874</t>
   </si>
   <si>
     <t xml:space="preserve">21.1729354858398</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5340976715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8078842163086</t>
+    <t xml:space="preserve">20.5340957641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.80788230896</t>
   </si>
   <si>
     <t xml:space="preserve">20.4428329467773</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9030361175537</t>
+    <t xml:space="preserve">21.9030342102051</t>
   </si>
   <si>
     <t xml:space="preserve">22.6331367492676</t>
@@ -2621,10 +2621,10 @@
     <t xml:space="preserve">20.1690464019775</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3476810455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1651573181152</t>
+    <t xml:space="preserve">19.3476829528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1651554107666</t>
   </si>
   <si>
     <t xml:space="preserve">18.2525291442871</t>
@@ -2633,19 +2633,19 @@
     <t xml:space="preserve">18.6175804138184</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1156349182129</t>
+    <t xml:space="preserve">18.1156368255615</t>
   </si>
   <si>
     <t xml:space="preserve">17.4311676025391</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5224285125732</t>
+    <t xml:space="preserve">17.5224304199219</t>
   </si>
   <si>
     <t xml:space="preserve">16.2447509765625</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5185394287109</t>
+    <t xml:space="preserve">16.5185413360596</t>
   </si>
   <si>
     <t xml:space="preserve">16.6098022460938</t>
@@ -2654,7 +2654,7 @@
     <t xml:space="preserve">16.7010650634766</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6593227386475</t>
+    <t xml:space="preserve">17.6593246459961</t>
   </si>
   <si>
     <t xml:space="preserve">17.2486400604248</t>
@@ -2684,16 +2684,16 @@
     <t xml:space="preserve">21.7661418914795</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8574047088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3137168884277</t>
+    <t xml:space="preserve">21.8574066162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3137187957764</t>
   </si>
   <si>
     <t xml:space="preserve">21.9486656188965</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0399303436279</t>
+    <t xml:space="preserve">22.0399284362793</t>
   </si>
   <si>
     <t xml:space="preserve">21.4923534393311</t>
@@ -2708,19 +2708,19 @@
     <t xml:space="preserve">23.5913944244385</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5001335144043</t>
+    <t xml:space="preserve">23.5001316070557</t>
   </si>
   <si>
     <t xml:space="preserve">23.7337303161621</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8271713256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.387809753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2009315490723</t>
+    <t xml:space="preserve">23.827169418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3878116607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2009296417236</t>
   </si>
   <si>
     <t xml:space="preserve">24.6681289672852</t>
@@ -2729,28 +2729,28 @@
     <t xml:space="preserve">24.621410369873</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0607719421387</t>
+    <t xml:space="preserve">24.06077003479</t>
   </si>
   <si>
     <t xml:space="preserve">23.9673309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5001316070557</t>
+    <t xml:space="preserve">23.500129699707</t>
   </si>
   <si>
     <t xml:space="preserve">22.9394912719727</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7058925628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6591739654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5190124511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.425573348999</t>
+    <t xml:space="preserve">22.7058906555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6591720581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5190143585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4255714416504</t>
   </si>
   <si>
     <t xml:space="preserve">23.4534130096436</t>
@@ -2768,7 +2768,7 @@
     <t xml:space="preserve">22.0985317230225</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9116554260254</t>
+    <t xml:space="preserve">21.9116535186768</t>
   </si>
   <si>
     <t xml:space="preserve">21.6780548095703</t>
@@ -2780,7 +2780,7 @@
     <t xml:space="preserve">23.0329303741455</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9862117767334</t>
+    <t xml:space="preserve">22.986213684082</t>
   </si>
   <si>
     <t xml:space="preserve">21.8182144165039</t>
@@ -2789,7 +2789,7 @@
     <t xml:space="preserve">22.1919727325439</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7714939117432</t>
+    <t xml:space="preserve">21.7714920043945</t>
   </si>
   <si>
     <t xml:space="preserve">22.2386913299561</t>
@@ -2801,13 +2801,13 @@
     <t xml:space="preserve">23.31325340271</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7993335723877</t>
+    <t xml:space="preserve">22.7993316650391</t>
   </si>
   <si>
     <t xml:space="preserve">22.3321323394775</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5846138000488</t>
+    <t xml:space="preserve">21.5846157073975</t>
   </si>
   <si>
     <t xml:space="preserve">20.930534362793</t>
@@ -2819,7 +2819,7 @@
     <t xml:space="preserve">20.2764568328857</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9494152069092</t>
+    <t xml:space="preserve">19.9494171142578</t>
   </si>
   <si>
     <t xml:space="preserve">20.4166164398193</t>
@@ -2840,25 +2840,25 @@
     <t xml:space="preserve">19.9026947021484</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8092555999756</t>
+    <t xml:space="preserve">19.8092575073242</t>
   </si>
   <si>
     <t xml:space="preserve">19.5756568908691</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3420562744141</t>
+    <t xml:space="preserve">19.3420581817627</t>
   </si>
   <si>
     <t xml:space="preserve">19.2486171722412</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9215774536133</t>
+    <t xml:space="preserve">18.9215755462646</t>
   </si>
   <si>
     <t xml:space="preserve">18.8281364440918</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5758495330811</t>
+    <t xml:space="preserve">18.5758476257324</t>
   </si>
   <si>
     <t xml:space="preserve">18.5010967254639</t>
@@ -2870,7 +2870,7 @@
     <t xml:space="preserve">19.5289363861084</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5945377349854</t>
+    <t xml:space="preserve">18.5945358276367</t>
   </si>
   <si>
     <t xml:space="preserve">18.3702812194824</t>
@@ -2879,7 +2879,7 @@
     <t xml:space="preserve">18.0525856018066</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9217700958252</t>
+    <t xml:space="preserve">17.9217720031738</t>
   </si>
   <si>
     <t xml:space="preserve">17.7535781860352</t>
@@ -2891,10 +2891,10 @@
     <t xml:space="preserve">17.7348899841309</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4919452667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2303161621094</t>
+    <t xml:space="preserve">17.4919471740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2303142547607</t>
   </si>
   <si>
     <t xml:space="preserve">17.1742496490479</t>
@@ -2909,7 +2909,7 @@
     <t xml:space="preserve">16.4454212188721</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1277236938477</t>
+    <t xml:space="preserve">16.1277256011963</t>
   </si>
   <si>
     <t xml:space="preserve">16.5014839172363</t>
@@ -2921,13 +2921,13 @@
     <t xml:space="preserve">16.0342845916748</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8847808837891</t>
+    <t xml:space="preserve">15.8847818374634</t>
   </si>
   <si>
     <t xml:space="preserve">15.3241405487061</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6044616699219</t>
+    <t xml:space="preserve">15.6044607162476</t>
   </si>
   <si>
     <t xml:space="preserve">15.7352771759033</t>
@@ -2945,7 +2945,7 @@
     <t xml:space="preserve">16.7444267272949</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7257404327393</t>
+    <t xml:space="preserve">16.7257385253906</t>
   </si>
   <si>
     <t xml:space="preserve">16.9313087463379</t>
@@ -2957,7 +2957,7 @@
     <t xml:space="preserve">17.9965229034424</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2581558227539</t>
+    <t xml:space="preserve">18.2581539154053</t>
   </si>
   <si>
     <t xml:space="preserve">17.6601371765137</t>
@@ -2966,10 +2966,10 @@
     <t xml:space="preserve">17.5666980743408</t>
   </si>
   <si>
-    <t xml:space="preserve">17.641450881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3142166137695</t>
+    <t xml:space="preserve">17.6414489746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3142185211182</t>
   </si>
   <si>
     <t xml:space="preserve">18.0712738037109</t>
@@ -3008,7 +3008,7 @@
     <t xml:space="preserve">17.7162017822266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5293216705322</t>
+    <t xml:space="preserve">17.5293235778809</t>
   </si>
   <si>
     <t xml:space="preserve">16.9873714447021</t>
@@ -3020,10 +3020,10 @@
     <t xml:space="preserve">17.5480117797852</t>
   </si>
   <si>
-    <t xml:space="preserve">16.277229309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9221572875977</t>
+    <t xml:space="preserve">16.2772274017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.922158241272</t>
   </si>
   <si>
     <t xml:space="preserve">16.0155963897705</t>
@@ -3032,19 +3032,19 @@
     <t xml:space="preserve">15.9595327377319</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9782218933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0903472900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8287172317505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6231489181519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5857744216919</t>
+    <t xml:space="preserve">15.9782209396362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0903491973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8287162780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6231479644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5857725143433</t>
   </si>
   <si>
     <t xml:space="preserve">16.0716609954834</t>
@@ -3065,10 +3065,10 @@
     <t xml:space="preserve">16.6322994232178</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6136112213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5762348175049</t>
+    <t xml:space="preserve">16.6136131286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5762367248535</t>
   </si>
   <si>
     <t xml:space="preserve">16.3519802093506</t>
@@ -3077,13 +3077,13 @@
     <t xml:space="preserve">16.2024765014648</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7913408279419</t>
+    <t xml:space="preserve">15.7913398742676</t>
   </si>
   <si>
     <t xml:space="preserve">15.7726516723633</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6978998184204</t>
+    <t xml:space="preserve">15.6979007720947</t>
   </si>
   <si>
     <t xml:space="preserve">16.5201721191406</t>
@@ -3092,34 +3092,34 @@
     <t xml:space="preserve">16.1464138031006</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1650981903076</t>
+    <t xml:space="preserve">16.1651000976562</t>
   </si>
   <si>
     <t xml:space="preserve">16.109037399292</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8474044799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7539663314819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8660917282104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6792125701904</t>
+    <t xml:space="preserve">15.8474025726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7539653778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8660936355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6792144775391</t>
   </si>
   <si>
     <t xml:space="preserve">15.8100280761719</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5110206604004</t>
+    <t xml:space="preserve">15.5110216140747</t>
   </si>
   <si>
     <t xml:space="preserve">15.3802042007446</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0064449310303</t>
+    <t xml:space="preserve">15.0064458847046</t>
   </si>
   <si>
     <t xml:space="preserve">14.8008785247803</t>
@@ -3128,7 +3128,7 @@
     <t xml:space="preserve">14.6700620651245</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4271183013916</t>
+    <t xml:space="preserve">14.4271173477173</t>
   </si>
   <si>
     <t xml:space="preserve">14.5766229629517</t>
@@ -3158,13 +3158,13 @@
     <t xml:space="preserve">15.0811967849731</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5670852661133</t>
+    <t xml:space="preserve">15.567084312439</t>
   </si>
   <si>
     <t xml:space="preserve">15.716588973999</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6605253219604</t>
+    <t xml:space="preserve">15.6605262756348</t>
   </si>
   <si>
     <t xml:space="preserve">15.1933259963989</t>
@@ -3173,13 +3173,13 @@
     <t xml:space="preserve">15.3988933563232</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4175806045532</t>
+    <t xml:space="preserve">15.4175815582275</t>
   </si>
   <si>
     <t xml:space="preserve">15.4362697601318</t>
   </si>
   <si>
-    <t xml:space="preserve">15.137261390686</t>
+    <t xml:space="preserve">15.1372623443604</t>
   </si>
   <si>
     <t xml:space="preserve">15.0438222885132</t>
@@ -3191,7 +3191,7 @@
     <t xml:space="preserve">14.9877586364746</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7261257171631</t>
+    <t xml:space="preserve">14.7261266708374</t>
   </si>
   <si>
     <t xml:space="preserve">14.950382232666</t>
@@ -3206,22 +3206,22 @@
     <t xml:space="preserve">14.3149900436401</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5018701553345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4084310531616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1654872894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.202862739563</t>
+    <t xml:space="preserve">14.5018711090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4084300994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1654863357544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2028617858887</t>
   </si>
   <si>
     <t xml:space="preserve">14.2963027954102</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1281099319458</t>
+    <t xml:space="preserve">14.1281108856201</t>
   </si>
   <si>
     <t xml:space="preserve">13.8291034698486</t>
@@ -3236,19 +3236,19 @@
     <t xml:space="preserve">13.4179677963257</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5487833023071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6422233581543</t>
+    <t xml:space="preserve">13.5487842559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6422243118286</t>
   </si>
   <si>
     <t xml:space="preserve">13.45534324646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3992805480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3245277404785</t>
+    <t xml:space="preserve">13.3992795944214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3245286941528</t>
   </si>
   <si>
     <t xml:space="preserve">13.2497758865356</t>
@@ -3257,7 +3257,7 @@
     <t xml:space="preserve">13.0815839767456</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3432149887085</t>
+    <t xml:space="preserve">13.3432159423828</t>
   </si>
   <si>
     <t xml:space="preserve">13.1937122344971</t>
@@ -3266,7 +3266,7 @@
     <t xml:space="preserve">13.3058395385742</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2589263916016</t>
+    <t xml:space="preserve">14.2589273452759</t>
   </si>
   <si>
     <t xml:space="preserve">14.2776145935059</t>
@@ -3275,7 +3275,7 @@
     <t xml:space="preserve">14.7448139190674</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5575466156006</t>
+    <t xml:space="preserve">16.5575485229492</t>
   </si>
   <si>
     <t xml:space="preserve">16.4641094207764</t>
@@ -3284,13 +3284,13 @@
     <t xml:space="preserve">16.4267311096191</t>
   </si>
   <si>
-    <t xml:space="preserve">16.314603805542</t>
+    <t xml:space="preserve">16.3146018981934</t>
   </si>
   <si>
     <t xml:space="preserve">16.2585391998291</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2398529052734</t>
+    <t xml:space="preserve">16.2398509979248</t>
   </si>
   <si>
     <t xml:space="preserve">16.1837882995605</t>
@@ -3299,13 +3299,13 @@
     <t xml:space="preserve">14.8569412231445</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7074375152588</t>
+    <t xml:space="preserve">14.7074384689331</t>
   </si>
   <si>
     <t xml:space="preserve">14.6887502670288</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3897428512573</t>
+    <t xml:space="preserve">14.389741897583</t>
   </si>
   <si>
     <t xml:space="preserve">14.782190322876</t>
@@ -3326,19 +3326,19 @@
     <t xml:space="preserve">12.9881439208984</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5956964492798</t>
+    <t xml:space="preserve">12.5956954956055</t>
   </si>
   <si>
     <t xml:space="preserve">12.7078247070312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7452001571655</t>
+    <t xml:space="preserve">12.7452011108398</t>
   </si>
   <si>
     <t xml:space="preserve">12.4275054931641</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0442085266113</t>
+    <t xml:space="preserve">13.044207572937</t>
   </si>
   <si>
     <t xml:space="preserve">13.3805913925171</t>
@@ -3365,28 +3365,28 @@
     <t xml:space="preserve">13.9972944259644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0159826278687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6513748168945</t>
+    <t xml:space="preserve">14.015983581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6513738632202</t>
   </si>
   <si>
     <t xml:space="preserve">15.0251340866089</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4736442565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.903468132019</t>
+    <t xml:space="preserve">15.4736452102661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9034700393677</t>
   </si>
   <si>
     <t xml:space="preserve">16.482795715332</t>
   </si>
   <si>
-    <t xml:space="preserve">16.912618637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8565578460693</t>
+    <t xml:space="preserve">16.9126205444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8565559387207</t>
   </si>
   <si>
     <t xml:space="preserve">16.9499950408936</t>
@@ -3395,7 +3395,7 @@
     <t xml:space="preserve">16.8752422332764</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0434341430664</t>
+    <t xml:space="preserve">17.043436050415</t>
   </si>
   <si>
     <t xml:space="preserve">15.9969091415405</t>
@@ -3407,7 +3407,7 @@
     <t xml:space="preserve">15.5483961105347</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6418361663818</t>
+    <t xml:space="preserve">15.6418380737305</t>
   </si>
   <si>
     <t xml:space="preserve">16.4080429077148</t>
@@ -3419,13 +3419,13 @@
     <t xml:space="preserve">16.6790199279785</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5855808258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8002967834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7068576812744</t>
+    <t xml:space="preserve">16.585578918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8002986907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.706859588623</t>
   </si>
   <si>
     <t xml:space="preserve">16.211820602417</t>
@@ -3434,19 +3434,19 @@
     <t xml:space="preserve">15.3708620071411</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3052597045898</t>
+    <t xml:space="preserve">16.3052616119385</t>
   </si>
   <si>
     <t xml:space="preserve">16.0249404907227</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1273384094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9404582977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6134185791016</t>
+    <t xml:space="preserve">18.1273365020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9404602050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6134204864502</t>
   </si>
   <si>
     <t xml:space="preserve">17.7070121765137</t>
@@ -69602,7 +69602,7 @@
     </row>
     <row r="2518">
       <c r="A2518" s="1" t="n">
-        <v>45985.6912615741</v>
+        <v>45985.3333333333</v>
       </c>
       <c r="B2518" t="n">
         <v>4161</v>
@@ -69623,6 +69623,32 @@
         <v>1268</v>
       </c>
       <c r="H2518" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2519">
+      <c r="A2519" s="1" t="n">
+        <v>45986.6911342593</v>
+      </c>
+      <c r="B2519" t="n">
+        <v>2495</v>
+      </c>
+      <c r="C2519" t="n">
+        <v>13.6000003814697</v>
+      </c>
+      <c r="D2519" t="n">
+        <v>13.4499998092651</v>
+      </c>
+      <c r="E2519" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F2519" t="n">
+        <v>13.6000003814697</v>
+      </c>
+      <c r="G2519" t="s">
+        <v>1258</v>
+      </c>
+      <c r="H2519" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SAB.MI.xlsx
+++ b/data/SAB.MI.xlsx
@@ -44,16 +44,16 @@
     <t xml:space="preserve">SAB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61823081970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4831018447876</t>
+    <t xml:space="preserve">8.61823177337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48310279846191</t>
   </si>
   <si>
     <t xml:space="preserve">8.33295917510986</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37049293518066</t>
+    <t xml:space="preserve">8.37049388885498</t>
   </si>
   <si>
     <t xml:space="preserve">8.31794357299805</t>
@@ -62,34 +62,34 @@
     <t xml:space="preserve">8.25788688659668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16029357910156</t>
+    <t xml:space="preserve">8.16029167175293</t>
   </si>
   <si>
     <t xml:space="preserve">7.88252782821655</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52969026565552</t>
+    <t xml:space="preserve">7.52969121932983</t>
   </si>
   <si>
     <t xml:space="preserve">7.66482019424438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62728404998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61226987838745</t>
+    <t xml:space="preserve">7.62728309631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61227083206177</t>
   </si>
   <si>
     <t xml:space="preserve">7.73989152908325</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75490713119507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76992034912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89754343032837</t>
+    <t xml:space="preserve">7.75490760803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76992130279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89754247665405</t>
   </si>
   <si>
     <t xml:space="preserve">7.6197772026062</t>
@@ -98,19 +98,19 @@
     <t xml:space="preserve">7.79994964599609</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72487735748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65731334686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50716972351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34201240539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54470539093018</t>
+    <t xml:space="preserve">7.72487831115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65731191635132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5071702003479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34201097488403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54470634460449</t>
   </si>
   <si>
     <t xml:space="preserve">7.39080858230591</t>
@@ -122,52 +122,52 @@
     <t xml:space="preserve">7.82247161865234</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08522129058838</t>
+    <t xml:space="preserve">8.08522319793701</t>
   </si>
   <si>
     <t xml:space="preserve">8.11525058746338</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95760059356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06270027160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03267192840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92006349563599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.777428150177</t>
+    <t xml:space="preserve">7.95759963989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06269931793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03267097473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9200644493103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77742719650269</t>
   </si>
   <si>
     <t xml:space="preserve">7.86751270294189</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80745649337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98762798309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04017925262451</t>
+    <t xml:space="preserve">7.807457447052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98762893676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0401782989502</t>
   </si>
   <si>
     <t xml:space="preserve">7.99513483047485</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96510601043701</t>
+    <t xml:space="preserve">7.96510791778564</t>
   </si>
   <si>
     <t xml:space="preserve">7.9050498008728</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93507862091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89003467559814</t>
+    <t xml:space="preserve">7.93507766723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89003658294678</t>
   </si>
   <si>
     <t xml:space="preserve">7.94258499145508</t>
@@ -179,7 +179,7 @@
     <t xml:space="preserve">7.81496334075928</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7323842048645</t>
+    <t xml:space="preserve">7.73238515853882</t>
   </si>
   <si>
     <t xml:space="preserve">7.64980602264404</t>
@@ -188,28 +188,28 @@
     <t xml:space="preserve">7.71737051010132</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67232704162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6347918510437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51467657089233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64230012893677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56722784042358</t>
+    <t xml:space="preserve">7.67232799530029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63479232788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51467752456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64229917526245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56722736358643</t>
   </si>
   <si>
     <t xml:space="preserve">7.70235729217529</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74739837646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46963310241699</t>
+    <t xml:space="preserve">7.74739933013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46963453292847</t>
   </si>
   <si>
     <t xml:space="preserve">7.69484901428223</t>
@@ -218,58 +218,58 @@
     <t xml:space="preserve">7.4921555519104</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47338676452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43585062026978</t>
+    <t xml:space="preserve">7.47338914871216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43585157394409</t>
   </si>
   <si>
     <t xml:space="preserve">7.50341558456421</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48089504241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59725570678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42834615707397</t>
+    <t xml:space="preserve">7.48089551925659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59725713729858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4283447265625</t>
   </si>
   <si>
     <t xml:space="preserve">7.38705587387085</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37203979492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31949090957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28195524215698</t>
+    <t xml:space="preserve">7.37204074859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31949138641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28195476531982</t>
   </si>
   <si>
     <t xml:space="preserve">7.52122116088867</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80533981323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75009346008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75798559188843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81323051452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86058330535889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69879579544067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58435821533203</t>
+    <t xml:space="preserve">7.80534029006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75009441375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75798606872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81323194503784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86058521270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69879484176636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58435869216919</t>
   </si>
   <si>
     <t xml:space="preserve">7.68695640563965</t>
@@ -278,28 +278,28 @@
     <t xml:space="preserve">7.57646608352661</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53700685501099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49754571914673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28445672988892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92536354064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.079261302948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22921133041382</t>
+    <t xml:space="preserve">7.53700542449951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49754476547241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28445768356323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9253625869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07926082611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22921228408813</t>
   </si>
   <si>
     <t xml:space="preserve">7.45808458328247</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26078033447266</t>
+    <t xml:space="preserve">7.26078081130981</t>
   </si>
   <si>
     <t xml:space="preserve">7.37127113342285</t>
@@ -308,79 +308,79 @@
     <t xml:space="preserve">7.26472663879395</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34759569168091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46992254257202</t>
+    <t xml:space="preserve">7.34759521484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46992301940918</t>
   </si>
   <si>
     <t xml:space="preserve">7.36732482910156</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37916278839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13450574874878</t>
+    <t xml:space="preserve">7.37916326522827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13450622558594</t>
   </si>
   <si>
     <t xml:space="preserve">7.18975067138672</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1029372215271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15029191970825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10688352584839</t>
+    <t xml:space="preserve">7.10293769836426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15029048919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10688304901123</t>
   </si>
   <si>
     <t xml:space="preserve">7.20553588867188</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18185901641846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22131967544556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19369745254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24894332885742</t>
+    <t xml:space="preserve">7.18185949325562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22132015228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19369697570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24894237518311</t>
   </si>
   <si>
     <t xml:space="preserve">7.19764375686646</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1858057975769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.225266456604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20948171615601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31602621078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21342849731445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16607427597046</t>
+    <t xml:space="preserve">7.18580484390259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22526597976685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20948266983032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31602573394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21342897415161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16607570648193</t>
   </si>
   <si>
     <t xml:space="preserve">7.24499607086182</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13055944442749</t>
+    <t xml:space="preserve">7.13056135177612</t>
   </si>
   <si>
     <t xml:space="preserve">7.11082983016968</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17791318893433</t>
+    <t xml:space="preserve">7.17791366577148</t>
   </si>
   <si>
     <t xml:space="preserve">7.23315811157227</t>
@@ -389,10 +389,10 @@
     <t xml:space="preserve">7.27656507492065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30024099349976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29234981536865</t>
+    <t xml:space="preserve">7.30024147033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29234933853149</t>
   </si>
   <si>
     <t xml:space="preserve">7.241051197052</t>
@@ -401,73 +401,73 @@
     <t xml:space="preserve">7.11872243881226</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09504508972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00428533554077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9450945854187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93325567245483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09899187088013</t>
+    <t xml:space="preserve">7.09504556655884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00428581237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94509506225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93325614929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09899091720581</t>
   </si>
   <si>
     <t xml:space="preserve">7.15423631668091</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13845252990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15818309783936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05558347702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07137012481689</t>
+    <t xml:space="preserve">7.13845348358154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1581826210022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05558443069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07136917114258</t>
   </si>
   <si>
     <t xml:space="preserve">7.06742286682129</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02401542663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04769229888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06347703933716</t>
+    <t xml:space="preserve">7.02401494979858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04769277572632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0634765625</t>
   </si>
   <si>
     <t xml:space="preserve">7.08320713043213</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05163908004761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04374742507935</t>
+    <t xml:space="preserve">7.05163955688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04374647140503</t>
   </si>
   <si>
     <t xml:space="preserve">7.03190755844116</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05952978134155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03585529327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1739673614502</t>
+    <t xml:space="preserve">7.05953025817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03585386276245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17396783828735</t>
   </si>
   <si>
     <t xml:space="preserve">6.9056339263916</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91352558135986</t>
+    <t xml:space="preserve">6.91352605819702</t>
   </si>
   <si>
     <t xml:space="preserve">6.93720245361328</t>
@@ -476,34 +476,34 @@
     <t xml:space="preserve">6.9214186668396</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94114828109741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9687705039978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14239883422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45019245147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69484949111938</t>
+    <t xml:space="preserve">6.94114875793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96877002716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14239835739136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45019149780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69484996795654</t>
   </si>
   <si>
     <t xml:space="preserve">7.79350137710571</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92372131347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0499963760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.207839012146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16837787628174</t>
+    <t xml:space="preserve">7.92372179031372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04999446868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20783996582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16837882995605</t>
   </si>
   <si>
     <t xml:space="preserve">8.08945655822754</t>
@@ -512,37 +512,37 @@
     <t xml:space="preserve">8.19994735717773</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06577968597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12891674041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17627048492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32622051239014</t>
+    <t xml:space="preserve">8.06578063964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1289176940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17626953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32622146606445</t>
   </si>
   <si>
     <t xml:space="preserve">8.55509376525879</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56298637390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42882061004639</t>
+    <t xml:space="preserve">8.56298542022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42881965637207</t>
   </si>
   <si>
     <t xml:space="preserve">8.35778999328613</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39725017547607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42092800140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44460391998291</t>
+    <t xml:space="preserve">8.39725112915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42092609405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44460296630859</t>
   </si>
   <si>
     <t xml:space="preserve">8.40514183044434</t>
@@ -551,10 +551,10 @@
     <t xml:space="preserve">8.26308441162109</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18416309356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30254554748535</t>
+    <t xml:space="preserve">8.18416213989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30254459381104</t>
   </si>
   <si>
     <t xml:space="preserve">8.22362422943115</t>
@@ -572,40 +572,40 @@
     <t xml:space="preserve">8.31043720245361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36568260192871</t>
+    <t xml:space="preserve">8.36568164825439</t>
   </si>
   <si>
     <t xml:space="preserve">8.33411407470703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34200572967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46038818359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62612152099609</t>
+    <t xml:space="preserve">8.34200477600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46038722991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62612342834473</t>
   </si>
   <si>
     <t xml:space="preserve">8.74450492858887</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88656425476074</t>
+    <t xml:space="preserve">8.88656520843506</t>
   </si>
   <si>
     <t xml:space="preserve">9.0049467086792</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23381900787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30484867095947</t>
+    <t xml:space="preserve">9.23381996154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30484771728516</t>
   </si>
   <si>
     <t xml:space="preserve">9.2653865814209</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1627893447876</t>
+    <t xml:space="preserve">9.16278839111328</t>
   </si>
   <si>
     <t xml:space="preserve">9.19435882568359</t>
@@ -617,22 +617,22 @@
     <t xml:space="preserve">9.29695510864258</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36798667907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54950523376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67578029632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74680805206299</t>
+    <t xml:space="preserve">9.36798572540283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54950428009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67577934265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7468090057373</t>
   </si>
   <si>
     <t xml:space="preserve">10.2203388214111</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4807806015015</t>
+    <t xml:space="preserve">10.4807796478271</t>
   </si>
   <si>
     <t xml:space="preserve">10.4571027755737</t>
@@ -644,7 +644,7 @@
     <t xml:space="preserve">10.2597990036011</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1493082046509</t>
+    <t xml:space="preserve">10.1493072509766</t>
   </si>
   <si>
     <t xml:space="preserve">10.0861721038818</t>
@@ -653,16 +653,16 @@
     <t xml:space="preserve">10.0151405334473</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1019563674927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1650943756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0546026229858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1808757781982</t>
+    <t xml:space="preserve">10.1019554138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1650924682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0546035766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1808776855469</t>
   </si>
   <si>
     <t xml:space="preserve">10.1177396774292</t>
@@ -671,25 +671,25 @@
     <t xml:space="preserve">10.1887683868408</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0703868865967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1098480224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0230350494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4965629577637</t>
+    <t xml:space="preserve">10.070387840271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1098489761353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0230331420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.496563911438</t>
   </si>
   <si>
     <t xml:space="preserve">10.4176416397095</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3150444030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7333278656006</t>
+    <t xml:space="preserve">10.3150434494019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7333288192749</t>
   </si>
   <si>
     <t xml:space="preserve">10.4492101669312</t>
@@ -698,13 +698,13 @@
     <t xml:space="preserve">10.5597009658813</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6386222839355</t>
+    <t xml:space="preserve">10.6386232376099</t>
   </si>
   <si>
     <t xml:space="preserve">10.591269493103</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0095520019531</t>
+    <t xml:space="preserve">11.0095529556274</t>
   </si>
   <si>
     <t xml:space="preserve">10.8832788467407</t>
@@ -719,25 +719,25 @@
     <t xml:space="preserve">11.9171514511108</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0513191223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6882791519165</t>
+    <t xml:space="preserve">12.0513181686401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6882781982422</t>
   </si>
   <si>
     <t xml:space="preserve">11.6803865432739</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2644052505493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6274452209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5406303405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6747970581055</t>
+    <t xml:space="preserve">12.264404296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6274442672729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5406322479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6747961044312</t>
   </si>
   <si>
     <t xml:space="preserve">12.7379350662231</t>
@@ -746,43 +746,43 @@
     <t xml:space="preserve">12.4728555679321</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6518535614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8471231460571</t>
+    <t xml:space="preserve">12.6518526077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8471221923828</t>
   </si>
   <si>
     <t xml:space="preserve">12.8145780563354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9203481674194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8715314865112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9366216659546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8064422607422</t>
+    <t xml:space="preserve">12.9203491210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8715324401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9366207122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8064403533936</t>
   </si>
   <si>
     <t xml:space="preserve">12.6437158584595</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8227138519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5209150314331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8463649749756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7812747955322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9114542007446</t>
+    <t xml:space="preserve">12.822714805603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5209140777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8463659286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7812757492065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9114570617676</t>
   </si>
   <si>
     <t xml:space="preserve">11.9277276992798</t>
@@ -794,40 +794,40 @@
     <t xml:space="preserve">11.8056840896606</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1311330795288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0009536743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9846811294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0416345596313</t>
+    <t xml:space="preserve">12.1311340332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0009546279907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9846820831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0416355133057</t>
   </si>
   <si>
     <t xml:space="preserve">12.0823173522949</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9765434265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8789110183716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7161865234375</t>
+    <t xml:space="preserve">11.9765453338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8789100646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7161846160889</t>
   </si>
   <si>
     <t xml:space="preserve">11.4720983505249</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5534591674805</t>
+    <t xml:space="preserve">11.5534601211548</t>
   </si>
   <si>
     <t xml:space="preserve">11.5860052108765</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7975473403931</t>
+    <t xml:space="preserve">11.7975482940674</t>
   </si>
   <si>
     <t xml:space="preserve">11.8951835632324</t>
@@ -842,19 +842,19 @@
     <t xml:space="preserve">12.0741806030273</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2287693023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1392707824707</t>
+    <t xml:space="preserve">12.2287683486938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1392698287964</t>
   </si>
   <si>
     <t xml:space="preserve">12.2043600082397</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1880874633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1474056243896</t>
+    <t xml:space="preserve">12.1880865097046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.147406578064</t>
   </si>
   <si>
     <t xml:space="preserve">12.2531785964966</t>
@@ -863,25 +863,25 @@
     <t xml:space="preserve">12.3670854568481</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4077653884888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.448447227478</t>
+    <t xml:space="preserve">12.4077644348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4484462738037</t>
   </si>
   <si>
     <t xml:space="preserve">12.9447584152222</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7820329666138</t>
+    <t xml:space="preserve">12.7820339202881</t>
   </si>
   <si>
     <t xml:space="preserve">12.8959407806396</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0098476409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9528932571411</t>
+    <t xml:space="preserve">13.0098466873169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9528942108154</t>
   </si>
   <si>
     <t xml:space="preserve">12.8552598953247</t>
@@ -890,7 +890,7 @@
     <t xml:space="preserve">12.7332153320312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7738962173462</t>
+    <t xml:space="preserve">12.7738971710205</t>
   </si>
   <si>
     <t xml:space="preserve">12.9854393005371</t>
@@ -902,76 +902,76 @@
     <t xml:space="preserve">13.685154914856</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9292421340942</t>
+    <t xml:space="preserve">13.9292430877686</t>
   </si>
   <si>
     <t xml:space="preserve">13.9943332672119</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7502450942993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8153343200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8316078186035</t>
+    <t xml:space="preserve">13.750244140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8153352737427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8316087722778</t>
   </si>
   <si>
     <t xml:space="preserve">14.0187406539917</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0268774032593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1814670562744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.157057762146</t>
+    <t xml:space="preserve">14.026876449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1814680099487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1570568084717</t>
   </si>
   <si>
     <t xml:space="preserve">14.2302837371826</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7754096984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3205394744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2961320877075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4588575363159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8249855041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7924404144287</t>
+    <t xml:space="preserve">14.7754135131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3205404281616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2961292266846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.458854675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8249864578247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7924394607544</t>
   </si>
   <si>
     <t xml:space="preserve">15.5076723098755</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8493947982788</t>
+    <t xml:space="preserve">15.8493938446045</t>
   </si>
   <si>
     <t xml:space="preserve">15.8656692504883</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5158100128174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0039844512939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2643413543701</t>
+    <t xml:space="preserve">15.5158081054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0039825439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2643432617188</t>
   </si>
   <si>
     <t xml:space="preserve">16.7769260406494</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9559268951416</t>
+    <t xml:space="preserve">16.955924987793</t>
   </si>
   <si>
     <t xml:space="preserve">17.4115524291992</t>
@@ -983,10 +983,10 @@
     <t xml:space="preserve">18.0787239074707</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6475067138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0217704772949</t>
+    <t xml:space="preserve">17.6475048065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0217723846436</t>
   </si>
   <si>
     <t xml:space="preserve">18.0543193817139</t>
@@ -998,7 +998,7 @@
     <t xml:space="preserve">18.2984027862549</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4123096466064</t>
+    <t xml:space="preserve">18.4123115539551</t>
   </si>
   <si>
     <t xml:space="preserve">18.1682243347168</t>
@@ -1010,7 +1010,7 @@
     <t xml:space="preserve">17.9160003662109</t>
   </si>
   <si>
-    <t xml:space="preserve">17.265100479126</t>
+    <t xml:space="preserve">17.2651023864746</t>
   </si>
   <si>
     <t xml:space="preserve">17.0861034393311</t>
@@ -1019,10 +1019,10 @@
     <t xml:space="preserve">17.2976455688477</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0047435760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1267852783203</t>
+    <t xml:space="preserve">17.0047397613525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.126781463623</t>
   </si>
   <si>
     <t xml:space="preserve">16.8745613098145</t>
@@ -1031,55 +1031,55 @@
     <t xml:space="preserve">17.0779685974121</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8664264678955</t>
+    <t xml:space="preserve">16.8664245605469</t>
   </si>
   <si>
     <t xml:space="preserve">16.785062789917</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9884662628174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5979309082031</t>
+    <t xml:space="preserve">16.988468170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5979270935059</t>
   </si>
   <si>
     <t xml:space="preserve">16.9152450561523</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8338775634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9640598297119</t>
+    <t xml:space="preserve">16.8338794708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9640617370605</t>
   </si>
   <si>
     <t xml:space="preserve">16.8826961517334</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9233779907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1349239349365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0698318481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1674652099609</t>
+    <t xml:space="preserve">16.9233798980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1349220275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0698299407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1674671173096</t>
   </si>
   <si>
     <t xml:space="preserve">17.6637763977051</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2251758575439</t>
+    <t xml:space="preserve">18.2251796722412</t>
   </si>
   <si>
     <t xml:space="preserve">18.8598041534424</t>
   </si>
   <si>
-    <t xml:space="preserve">19.06321144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7052135467529</t>
+    <t xml:space="preserve">19.0632095336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7052154541016</t>
   </si>
   <si>
     <t xml:space="preserve">18.6319885253906</t>
@@ -1088,28 +1088,28 @@
     <t xml:space="preserve">18.7377624511719</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7133522033691</t>
+    <t xml:space="preserve">18.7133502960205</t>
   </si>
   <si>
     <t xml:space="preserve">18.59130859375</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3065376281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6157150268555</t>
+    <t xml:space="preserve">18.3065395355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6157169342041</t>
   </si>
   <si>
     <t xml:space="preserve">18.217041015625</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2089042663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4611301422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5417346954346</t>
+    <t xml:space="preserve">18.2089061737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4611320495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5417327880859</t>
   </si>
   <si>
     <t xml:space="preserve">16.9071083068848</t>
@@ -1118,10 +1118,10 @@
     <t xml:space="preserve">16.4758853912354</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3945217132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1097526550293</t>
+    <t xml:space="preserve">16.3945236206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1097564697266</t>
   </si>
   <si>
     <t xml:space="preserve">16.3619785308838</t>
@@ -1133,46 +1133,46 @@
     <t xml:space="preserve">16.3782501220703</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1992530822754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2236614227295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2724781036377</t>
+    <t xml:space="preserve">16.1992568969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2236633300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2724800109863</t>
   </si>
   <si>
     <t xml:space="preserve">16.6792907714844</t>
   </si>
   <si>
-    <t xml:space="preserve">16.313159942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0934829711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9470319747925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1911163330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3538417816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0283946990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9144840240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.182225227356</t>
+    <t xml:space="preserve">16.3131618499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.09348487854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9470300674438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1911182403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3538436889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.028392791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9144830703735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1822214126587</t>
   </si>
   <si>
     <t xml:space="preserve">14.9706811904907</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1008625030518</t>
+    <t xml:space="preserve">15.1008615493774</t>
   </si>
   <si>
     <t xml:space="preserve">14.8730487823486</t>
@@ -1184,7 +1184,7 @@
     <t xml:space="preserve">13.8478803634644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8893184661865</t>
+    <t xml:space="preserve">14.8893194198608</t>
   </si>
   <si>
     <t xml:space="preserve">15.1984968185425</t>
@@ -1193,13 +1193,13 @@
     <t xml:space="preserve">15.3937664031982</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5402193069458</t>
+    <t xml:space="preserve">15.5402164459229</t>
   </si>
   <si>
     <t xml:space="preserve">14.938136100769</t>
   </si>
   <si>
-    <t xml:space="preserve">14.59641456604</t>
+    <t xml:space="preserve">14.5964136123657</t>
   </si>
   <si>
     <t xml:space="preserve">14.4011449813843</t>
@@ -1208,13 +1208,13 @@
     <t xml:space="preserve">14.2058734893799</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1082410812378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.059422492981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9129705429077</t>
+    <t xml:space="preserve">14.1082401275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0594244003296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9129695892334</t>
   </si>
   <si>
     <t xml:space="preserve">14.0106048583984</t>
@@ -1223,49 +1223,49 @@
     <t xml:space="preserve">14.3197832107544</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6452312469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7428693771362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7265958786011</t>
+    <t xml:space="preserve">14.6452322006226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7428665161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7265939712524</t>
   </si>
   <si>
     <t xml:space="preserve">15.2147693634033</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8079566955566</t>
+    <t xml:space="preserve">14.807957649231</t>
   </si>
   <si>
     <t xml:space="preserve">14.8567743301392</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9544067382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7916851043701</t>
+    <t xml:space="preserve">14.9544086456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7916860580444</t>
   </si>
   <si>
     <t xml:space="preserve">14.2709655761719</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0032253265381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4825057983398</t>
+    <t xml:space="preserve">15.0032262802124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4825048446655</t>
   </si>
   <si>
     <t xml:space="preserve">14.9218635559082</t>
   </si>
   <si>
-    <t xml:space="preserve">14.905590057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0194978713989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0520429611206</t>
+    <t xml:space="preserve">14.9055919647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0194997787476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0520439147949</t>
   </si>
   <si>
     <t xml:space="preserve">16.2562065124512</t>
@@ -1274,7 +1274,7 @@
     <t xml:space="preserve">15.7354869842529</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8168516159058</t>
+    <t xml:space="preserve">15.8168487548828</t>
   </si>
   <si>
     <t xml:space="preserve">15.6215791702271</t>
@@ -1283,85 +1283,85 @@
     <t xml:space="preserve">15.9307565689087</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6866703033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7192182540894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7029399871826</t>
+    <t xml:space="preserve">15.6866693496704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7192163467407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7029390335083</t>
   </si>
   <si>
     <t xml:space="preserve">15.6703996658325</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6053104400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5653495788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9956836700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0291929244995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0627012252808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2470073699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2302532196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5318422317505</t>
+    <t xml:space="preserve">15.6053094863892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5653514862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9956817626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0291919708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0627031326294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2470083236694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2302541732788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5318412780762</t>
   </si>
   <si>
     <t xml:space="preserve">15.7161464691162</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8669414520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.582106590271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.498330116272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.48157787323</t>
+    <t xml:space="preserve">15.8669404983521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5821084976196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4983310699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4815759658813</t>
   </si>
   <si>
     <t xml:space="preserve">15.4145565032959</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1799898147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.07945728302</t>
+    <t xml:space="preserve">15.1799869537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0794582366943</t>
   </si>
   <si>
     <t xml:space="preserve">15.1129684448242</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3589935302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2919750213623</t>
+    <t xml:space="preserve">14.3589954376221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.291974067688</t>
   </si>
   <si>
     <t xml:space="preserve">14.2584648132324</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4595251083374</t>
+    <t xml:space="preserve">14.4595232009888</t>
   </si>
   <si>
     <t xml:space="preserve">14.4092597961426</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5600528717041</t>
+    <t xml:space="preserve">14.5600519180298</t>
   </si>
   <si>
     <t xml:space="preserve">13.4039621353149</t>
@@ -1370,10 +1370,10 @@
     <t xml:space="preserve">13.4877376556396</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2364130020142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5380010604858</t>
+    <t xml:space="preserve">13.2364139556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5380020141602</t>
   </si>
   <si>
     <t xml:space="preserve">13.4374732971191</t>
@@ -1388,7 +1388,7 @@
     <t xml:space="preserve">13.688796043396</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4207162857056</t>
+    <t xml:space="preserve">13.4207172393799</t>
   </si>
   <si>
     <t xml:space="preserve">13.5212469100952</t>
@@ -1397,25 +1397,25 @@
     <t xml:space="preserve">13.57151222229</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3201885223389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1526374816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1861476898193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2196569442749</t>
+    <t xml:space="preserve">13.3201866149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1526384353638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.186146736145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2196588516235</t>
   </si>
   <si>
     <t xml:space="preserve">13.3034324645996</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8510484695435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6835012435913</t>
+    <t xml:space="preserve">12.8510494232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6834993362427</t>
   </si>
   <si>
     <t xml:space="preserve">12.5662145614624</t>
@@ -1424,10 +1424,10 @@
     <t xml:space="preserve">12.9013137817383</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8342943191528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4824390411377</t>
+    <t xml:space="preserve">12.8342924118042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.482439994812</t>
   </si>
   <si>
     <t xml:space="preserve">12.1473407745361</t>
@@ -1436,7 +1436,7 @@
     <t xml:space="preserve">12.0803203582764</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0635662078857</t>
+    <t xml:space="preserve">12.0635652542114</t>
   </si>
   <si>
     <t xml:space="preserve">11.979790687561</t>
@@ -1445,10 +1445,10 @@
     <t xml:space="preserve">11.5609178543091</t>
   </si>
   <si>
-    <t xml:space="preserve">11.192307472229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2258186340332</t>
+    <t xml:space="preserve">11.1923084259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2258176803589</t>
   </si>
   <si>
     <t xml:space="preserve">12.4321756362915</t>
@@ -1460,16 +1460,16 @@
     <t xml:space="preserve">13.2531681060791</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2866764068604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7672729492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3536968231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9850873947144</t>
+    <t xml:space="preserve">13.2866773605347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7672739028931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3536977767944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9850883483887</t>
   </si>
   <si>
     <t xml:space="preserve">12.8007841110229</t>
@@ -1478,22 +1478,22 @@
     <t xml:space="preserve">12.6332340240479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8678035736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8122425079346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6279373168945</t>
+    <t xml:space="preserve">12.8678026199341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8122415542603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6279382705688</t>
   </si>
   <si>
     <t xml:space="preserve">11.6111822128296</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7284669876099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9630365371704</t>
+    <t xml:space="preserve">11.7284660339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9630355834961</t>
   </si>
   <si>
     <t xml:space="preserve">11.8960161209106</t>
@@ -1505,10 +1505,10 @@
     <t xml:space="preserve">11.075023651123</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0415143966675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9577388763428</t>
+    <t xml:space="preserve">11.0415134429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9577379226685</t>
   </si>
   <si>
     <t xml:space="preserve">10.7566795349121</t>
@@ -1526,25 +1526,25 @@
     <t xml:space="preserve">12.3651552200317</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4603872299194</t>
+    <t xml:space="preserve">11.4603881835938</t>
   </si>
   <si>
     <t xml:space="preserve">11.1587982177734</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1252899169922</t>
+    <t xml:space="preserve">11.1252889633179</t>
   </si>
   <si>
     <t xml:space="preserve">11.1755542755127</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3766136169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2311162948608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3986644744873</t>
+    <t xml:space="preserve">11.376612663269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2311153411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3986654281616</t>
   </si>
   <si>
     <t xml:space="preserve">11.9295263290405</t>
@@ -1553,25 +1553,25 @@
     <t xml:space="preserve">11.7954874038696</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8792629241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1976051330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2478704452515</t>
+    <t xml:space="preserve">11.87926197052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.197606086731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2478713989258</t>
   </si>
   <si>
     <t xml:space="preserve">12.0133008956909</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1305847167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1808519363403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.381911277771</t>
+    <t xml:space="preserve">12.1305856704712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.180850982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3819103240967</t>
   </si>
   <si>
     <t xml:space="preserve">12.3316450119019</t>
@@ -1580,43 +1580,43 @@
     <t xml:space="preserve">12.4656848907471</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5997247695923</t>
+    <t xml:space="preserve">12.599723815918</t>
   </si>
   <si>
     <t xml:space="preserve">12.7170085906982</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8845586776733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9515790939331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9683332443237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2029027938843</t>
+    <t xml:space="preserve">12.8845596313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9515771865845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9683322906494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2029037475586</t>
   </si>
   <si>
     <t xml:space="preserve">12.7337646484375</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8175392150879</t>
+    <t xml:space="preserve">12.8175382614136</t>
   </si>
   <si>
     <t xml:space="preserve">12.6499900817871</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7002544403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5159482955933</t>
+    <t xml:space="preserve">12.7002534866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5159492492676</t>
   </si>
   <si>
     <t xml:space="preserve">12.784029006958</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0018444061279</t>
+    <t xml:space="preserve">13.0018434524536</t>
   </si>
   <si>
     <t xml:space="preserve">13.0353536605835</t>
@@ -1631,31 +1631,31 @@
     <t xml:space="preserve">12.9180688858032</t>
   </si>
   <si>
-    <t xml:space="preserve">13.38720703125</t>
+    <t xml:space="preserve">13.3872079849243</t>
   </si>
   <si>
     <t xml:space="preserve">13.6217775344849</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8228368759155</t>
+    <t xml:space="preserve">13.8228349685669</t>
   </si>
   <si>
     <t xml:space="preserve">13.5044927597046</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4542264938354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6385326385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7223052978516</t>
+    <t xml:space="preserve">13.4542255401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6385316848755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7223062515259</t>
   </si>
   <si>
     <t xml:space="preserve">13.3704528808594</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0521087646484</t>
+    <t xml:space="preserve">13.0521078109741</t>
   </si>
   <si>
     <t xml:space="preserve">13.0185976028442</t>
@@ -1664,13 +1664,13 @@
     <t xml:space="preserve">13.1693935394287</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1023740768433</t>
+    <t xml:space="preserve">13.1023731231689</t>
   </si>
   <si>
     <t xml:space="preserve">12.499195098877</t>
   </si>
   <si>
-    <t xml:space="preserve">12.748176574707</t>
+    <t xml:space="preserve">12.7481775283813</t>
   </si>
   <si>
     <t xml:space="preserve">12.5740203857422</t>
@@ -1682,28 +1682,28 @@
     <t xml:space="preserve">12.2257108688354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2779579162598</t>
+    <t xml:space="preserve">12.2779569625854</t>
   </si>
   <si>
     <t xml:space="preserve">12.3127889633179</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2953720092773</t>
+    <t xml:space="preserve">12.295373916626</t>
   </si>
   <si>
     <t xml:space="preserve">12.3302030563354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1212177276611</t>
+    <t xml:space="preserve">12.1212167739868</t>
   </si>
   <si>
     <t xml:space="preserve">12.5217742919922</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4869432449341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.452112197876</t>
+    <t xml:space="preserve">12.4869441986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4521131515503</t>
   </si>
   <si>
     <t xml:space="preserve">12.138632774353</t>
@@ -1715,76 +1715,76 @@
     <t xml:space="preserve">11.8948154449463</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2082958221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8178386688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7655916213989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.643684387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.399866104126</t>
+    <t xml:space="preserve">12.2082948684692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8178396224976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7655925750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6436834335327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3998651504517</t>
   </si>
   <si>
     <t xml:space="preserve">12.6262683868408</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5391902923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8700866699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9745779037476</t>
+    <t xml:space="preserve">12.5391893386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8700847625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9745788574219</t>
   </si>
   <si>
     <t xml:space="preserve">12.95716381073</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9397478103638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7830095291138</t>
+    <t xml:space="preserve">12.9397468566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7830085754395</t>
   </si>
   <si>
     <t xml:space="preserve">12.6959295272827</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8004236221313</t>
+    <t xml:space="preserve">12.800422668457</t>
   </si>
   <si>
     <t xml:space="preserve">12.8875007629395</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1560478210449</t>
+    <t xml:space="preserve">12.1560487747192</t>
   </si>
   <si>
     <t xml:space="preserve">12.0341396331787</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7206602096558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2431259155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7554922103882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6684131622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9993085861206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0689706802368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1038007736206</t>
+    <t xml:space="preserve">11.7206592559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2431268692017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7554912567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6684122085571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9993076324463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0689697265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1038017272949</t>
   </si>
   <si>
     <t xml:space="preserve">11.790322303772</t>
@@ -1796,19 +1796,19 @@
     <t xml:space="preserve">11.9470624923706</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8251533508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8599843978882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7729063034058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8774003982544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6509981155396</t>
+    <t xml:space="preserve">11.8251523971558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8599834442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7729072570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8773994445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6509971618652</t>
   </si>
   <si>
     <t xml:space="preserve">11.5465040206909</t>
@@ -1820,10 +1820,10 @@
     <t xml:space="preserve">11.2156095504761</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4071807861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3026866912842</t>
+    <t xml:space="preserve">11.4071798324585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3026857376099</t>
   </si>
   <si>
     <t xml:space="preserve">11.3549327850342</t>
@@ -1832,40 +1832,40 @@
     <t xml:space="preserve">11.3897638320923</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1981935501099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9369602203369</t>
+    <t xml:space="preserve">11.1981925964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9369611740112</t>
   </si>
   <si>
     <t xml:space="preserve">11.0414543151855</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8847150802612</t>
+    <t xml:space="preserve">10.8847141265869</t>
   </si>
   <si>
     <t xml:space="preserve">10.8672971725464</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9717931747437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8324670791626</t>
+    <t xml:space="preserve">10.9717922210693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8324661254883</t>
   </si>
   <si>
     <t xml:space="preserve">10.6234798431396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6060657501221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5886487960815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5189867019653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4493265151978</t>
+    <t xml:space="preserve">10.6060647964478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5886497497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5189876556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4493255615234</t>
   </si>
   <si>
     <t xml:space="preserve">10.6583108901978</t>
@@ -1874,10 +1874,10 @@
     <t xml:space="preserve">10.7802200317383</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1633634567261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1111154556274</t>
+    <t xml:space="preserve">11.1633625030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1111164093018</t>
   </si>
   <si>
     <t xml:space="preserve">11.0588693618774</t>
@@ -1886,7 +1886,7 @@
     <t xml:space="preserve">10.9892063140869</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8498821258545</t>
+    <t xml:space="preserve">10.8498830795288</t>
   </si>
   <si>
     <t xml:space="preserve">11.0240383148193</t>
@@ -1895,31 +1895,31 @@
     <t xml:space="preserve">11.0066232681274</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7976350784302</t>
+    <t xml:space="preserve">10.7976360321045</t>
   </si>
   <si>
     <t xml:space="preserve">10.8150520324707</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9543752670288</t>
+    <t xml:space="preserve">10.9543762207031</t>
   </si>
   <si>
     <t xml:space="preserve">11.0937004089355</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7032432556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9818925857544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9296464920044</t>
+    <t xml:space="preserve">11.7032442092896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.981894493103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9296474456787</t>
   </si>
   <si>
     <t xml:space="preserve">11.9122304916382</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8077392578125</t>
+    <t xml:space="preserve">11.8077383041382</t>
   </si>
   <si>
     <t xml:space="preserve">12.2605419158936</t>
@@ -1928,7 +1928,7 @@
     <t xml:space="preserve">12.086386680603</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9644765853882</t>
+    <t xml:space="preserve">11.9644775390625</t>
   </si>
   <si>
     <t xml:space="preserve">11.529088973999</t>
@@ -1937,34 +1937,34 @@
     <t xml:space="preserve">11.4942579269409</t>
   </si>
   <si>
-    <t xml:space="preserve">11.581335067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.476842880249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6858291625977</t>
+    <t xml:space="preserve">11.5813360214233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4768419265747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.685830116272</t>
   </si>
   <si>
     <t xml:space="preserve">12.1908798217773</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3476209640503</t>
+    <t xml:space="preserve">12.347620010376</t>
   </si>
   <si>
     <t xml:space="preserve">11.5116729736328</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5987510681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7105579376221</t>
+    <t xml:space="preserve">11.5987501144409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7105588912964</t>
   </si>
   <si>
     <t xml:space="preserve">9.70045852661133</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49146938323975</t>
+    <t xml:space="preserve">9.49147033691406</t>
   </si>
   <si>
     <t xml:space="preserve">9.03866577148438</t>
@@ -1973,7 +1973,7 @@
     <t xml:space="preserve">8.98641967773438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42912101745605</t>
+    <t xml:space="preserve">8.429123878479</t>
   </si>
   <si>
     <t xml:space="preserve">8.18530464172363</t>
@@ -1994,7 +1994,7 @@
     <t xml:space="preserve">8.31592178344727</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32463073730469</t>
+    <t xml:space="preserve">8.32462978363037</t>
   </si>
   <si>
     <t xml:space="preserve">8.16788959503174</t>
@@ -2003,10 +2003,10 @@
     <t xml:space="preserve">8.38558483123779</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28979778289795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41170787811279</t>
+    <t xml:space="preserve">8.28979969024658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41170692443848</t>
   </si>
   <si>
     <t xml:space="preserve">8.4987850189209</t>
@@ -2015,25 +2015,25 @@
     <t xml:space="preserve">8.63810920715332</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69035530090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67294025421143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79485034942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96900367736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75131034851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70777034759521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83838748931885</t>
+    <t xml:space="preserve">8.69035625457764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67293930053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79484939575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96900463104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75130939483643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70777130126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83838844299316</t>
   </si>
   <si>
     <t xml:space="preserve">9.1866979598999</t>
@@ -2054,34 +2054,34 @@
     <t xml:space="preserve">9.66562652587891</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57854843139648</t>
+    <t xml:space="preserve">9.57854747772217</t>
   </si>
   <si>
     <t xml:space="preserve">9.31731510162354</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88192653656006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65552520751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51620006561279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60327816009521</t>
+    <t xml:space="preserve">8.88192462921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65552425384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51619911193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6032772064209</t>
   </si>
   <si>
     <t xml:space="preserve">8.56844711303711</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36085414886475</t>
+    <t xml:space="preserve">9.36085510253906</t>
   </si>
   <si>
     <t xml:space="preserve">9.83978176116943</t>
   </si>
   <si>
-    <t xml:space="preserve">10.01393699646</t>
+    <t xml:space="preserve">10.0139360427856</t>
   </si>
   <si>
     <t xml:space="preserve">10.1010141372681</t>
@@ -2090,7 +2090,7 @@
     <t xml:space="preserve">9.92685890197754</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88332176208496</t>
+    <t xml:space="preserve">9.88332080841064</t>
   </si>
   <si>
     <t xml:space="preserve">10.0574760437012</t>
@@ -2105,34 +2105,34 @@
     <t xml:space="preserve">9.75270366668701</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6220874786377</t>
+    <t xml:space="preserve">9.62208843231201</t>
   </si>
   <si>
     <t xml:space="preserve">9.53500938415527</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79624176025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1880922317505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2751703262329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5364036560059</t>
+    <t xml:space="preserve">9.79624271392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1880931854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2751693725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5364027023315</t>
   </si>
   <si>
     <t xml:space="preserve">10.9282522201538</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0153284072876</t>
+    <t xml:space="preserve">11.0153303146362</t>
   </si>
   <si>
     <t xml:space="preserve">10.7540979385376</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4928636550903</t>
+    <t xml:space="preserve">10.492865562439</t>
   </si>
   <si>
     <t xml:space="preserve">10.4057855606079</t>
@@ -2141,31 +2141,31 @@
     <t xml:space="preserve">10.362247467041</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3187084197998</t>
+    <t xml:space="preserve">10.3187093734741</t>
   </si>
   <si>
     <t xml:space="preserve">11.1894865036011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2765636444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4507188796997</t>
+    <t xml:space="preserve">11.2765626907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4507179260254</t>
   </si>
   <si>
     <t xml:space="preserve">12.0167245864868</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0602626800537</t>
+    <t xml:space="preserve">12.060263633728</t>
   </si>
   <si>
     <t xml:space="preserve">12.5011930465698</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0100746154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.831485748291</t>
+    <t xml:space="preserve">12.0100755691528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8314867019653</t>
   </si>
   <si>
     <t xml:space="preserve">11.6975450515747</t>
@@ -2174,7 +2174,7 @@
     <t xml:space="preserve">11.4743099212646</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2064275741577</t>
+    <t xml:space="preserve">11.2064256668091</t>
   </si>
   <si>
     <t xml:space="preserve">11.4296627044678</t>
@@ -2195,7 +2195,7 @@
     <t xml:space="preserve">11.0278387069702</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8938961029053</t>
+    <t xml:space="preserve">10.8938970565796</t>
   </si>
   <si>
     <t xml:space="preserve">11.1617784500122</t>
@@ -2204,10 +2204,10 @@
     <t xml:space="preserve">11.0724849700928</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9207811355591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.188663482666</t>
+    <t xml:space="preserve">11.9207801818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1886625289917</t>
   </si>
   <si>
     <t xml:space="preserve">12.2333097457886</t>
@@ -2225,16 +2225,16 @@
     <t xml:space="preserve">11.7868385314941</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0993700027466</t>
+    <t xml:space="preserve">12.0993690490723</t>
   </si>
   <si>
     <t xml:space="preserve">13.4387826919556</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4834299087524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9299011230469</t>
+    <t xml:space="preserve">13.4834308624268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9299020767212</t>
   </si>
   <si>
     <t xml:space="preserve">13.8406066894531</t>
@@ -2246,76 +2246,76 @@
     <t xml:space="preserve">12.9030170440674</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0816059112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0369596481323</t>
+    <t xml:space="preserve">13.0816049575806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.036958694458</t>
   </si>
   <si>
     <t xml:space="preserve">13.7513113021851</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7959594726562</t>
+    <t xml:space="preserve">13.7959585189819</t>
   </si>
   <si>
     <t xml:space="preserve">13.3941354751587</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9745473861694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2601947784424</t>
+    <t xml:space="preserve">13.9745483398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2601938247681</t>
   </si>
   <si>
     <t xml:space="preserve">13.6620178222656</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6173715591431</t>
+    <t xml:space="preserve">13.6173706054688</t>
   </si>
   <si>
     <t xml:space="preserve">13.88525390625</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6442537307739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7781963348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9121370315552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0907249450684</t>
+    <t xml:space="preserve">14.6442546844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7781953811646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9121379852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0907258987427</t>
   </si>
   <si>
     <t xml:space="preserve">14.733549118042</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4210186004639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5103139877319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1800212860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8497266769409</t>
+    <t xml:space="preserve">14.4210195541382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5103130340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1800203323364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8497276306152</t>
   </si>
   <si>
     <t xml:space="preserve">15.8050813674927</t>
   </si>
   <si>
-    <t xml:space="preserve">16.072961807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3854942321777</t>
+    <t xml:space="preserve">16.0729637145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3854923248291</t>
   </si>
   <si>
     <t xml:space="preserve">16.9212589263916</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1891384124756</t>
+    <t xml:space="preserve">17.1891403198242</t>
   </si>
   <si>
     <t xml:space="preserve">16.7426681518555</t>
@@ -2327,19 +2327,19 @@
     <t xml:space="preserve">17.769552230835</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8142013549805</t>
+    <t xml:space="preserve">17.8142032623291</t>
   </si>
   <si>
     <t xml:space="preserve">17.8588466644287</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0374374389648</t>
+    <t xml:space="preserve">18.0374355316162</t>
   </si>
   <si>
     <t xml:space="preserve">18.12672996521</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3946132659912</t>
+    <t xml:space="preserve">18.3946113586426</t>
   </si>
   <si>
     <t xml:space="preserve">18.5732002258301</t>
@@ -2351,19 +2351,19 @@
     <t xml:space="preserve">18.3053188323975</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5909671783447</t>
+    <t xml:space="preserve">17.5909652709961</t>
   </si>
   <si>
     <t xml:space="preserve">18.2160243988037</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9481430053711</t>
+    <t xml:space="preserve">17.9481410980225</t>
   </si>
   <si>
     <t xml:space="preserve">19.0196723937988</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1805000305176</t>
+    <t xml:space="preserve">20.1804962158203</t>
   </si>
   <si>
     <t xml:space="preserve">20.5376739501953</t>
@@ -2372,7 +2372,7 @@
     <t xml:space="preserve">20.6269702911377</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9841442108154</t>
+    <t xml:space="preserve">20.9841461181641</t>
   </si>
   <si>
     <t xml:space="preserve">20.8055553436279</t>
@@ -2390,31 +2390,31 @@
     <t xml:space="preserve">19.8233222961426</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2697944641113</t>
+    <t xml:space="preserve">20.2697906494141</t>
   </si>
   <si>
     <t xml:space="preserve">19.1982612609863</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9126148223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5554389953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6447315216064</t>
+    <t xml:space="preserve">19.9126129150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5554370880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6447334289551</t>
   </si>
   <si>
     <t xml:space="preserve">18.9303798675537</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7162628173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4483814239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4306144714355</t>
+    <t xml:space="preserve">20.7162647247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4483795166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4306163787842</t>
   </si>
   <si>
     <t xml:space="preserve">21.3413219451904</t>
@@ -2429,10 +2429,10 @@
     <t xml:space="preserve">22.0556774139404</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7877922058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7700290679932</t>
+    <t xml:space="preserve">21.7877941131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7700309753418</t>
   </si>
   <si>
     <t xml:space="preserve">24.9147033691406</t>
@@ -2444,7 +2444,7 @@
     <t xml:space="preserve">24.0020771026611</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8195533752441</t>
+    <t xml:space="preserve">23.8195514678955</t>
   </si>
   <si>
     <t xml:space="preserve">24.5496520996094</t>
@@ -2459,19 +2459,19 @@
     <t xml:space="preserve">24.0933380126953</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7321796417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3671283721924</t>
+    <t xml:space="preserve">24.732177734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.367130279541</t>
   </si>
   <si>
     <t xml:space="preserve">23.9108142852783</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2719745635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6370258331299</t>
+    <t xml:space="preserve">23.2719764709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6370277404785</t>
   </si>
   <si>
     <t xml:space="preserve">23.5457630157471</t>
@@ -2480,22 +2480,22 @@
     <t xml:space="preserve">24.2758655548096</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7282867431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1846008300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0059642791748</t>
+    <t xml:space="preserve">23.7282886505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1846027374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0059661865234</t>
   </si>
   <si>
     <t xml:space="preserve">22.3593482971191</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8156604766846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2680854797363</t>
+    <t xml:space="preserve">22.8156623840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.268087387085</t>
   </si>
   <si>
     <t xml:space="preserve">22.7243995666504</t>
@@ -2504,7 +2504,7 @@
     <t xml:space="preserve">23.4545021057129</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0894508361816</t>
+    <t xml:space="preserve">23.089448928833</t>
   </si>
   <si>
     <t xml:space="preserve">23.1807117462158</t>
@@ -2513,19 +2513,19 @@
     <t xml:space="preserve">22.9069271087646</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1768226623535</t>
+    <t xml:space="preserve">22.1768245697021</t>
   </si>
   <si>
     <t xml:space="preserve">22.5418758392334</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9943008422852</t>
+    <t xml:space="preserve">21.9942989349365</t>
   </si>
   <si>
     <t xml:space="preserve">22.0855617523193</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5379867553711</t>
+    <t xml:space="preserve">21.5379848480225</t>
   </si>
   <si>
     <t xml:space="preserve">21.7205085754395</t>
@@ -2537,7 +2537,7 @@
     <t xml:space="preserve">21.8117733001709</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4467220306396</t>
+    <t xml:space="preserve">21.4467239379883</t>
   </si>
   <si>
     <t xml:space="preserve">20.8991470336914</t>
@@ -2558,7 +2558,7 @@
     <t xml:space="preserve">19.7127323150635</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0816745758057</t>
+    <t xml:space="preserve">21.081672668457</t>
   </si>
   <si>
     <t xml:space="preserve">24.6409149169922</t>
@@ -2567,13 +2567,13 @@
     <t xml:space="preserve">25.3710155487061</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3749046325684</t>
+    <t xml:space="preserve">26.374906539917</t>
   </si>
   <si>
     <t xml:space="preserve">25.6448059082031</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9185905456543</t>
+    <t xml:space="preserve">25.9185924530029</t>
   </si>
   <si>
     <t xml:space="preserve">25.8273296356201</t>
@@ -2585,34 +2585,34 @@
     <t xml:space="preserve">25.2797546386719</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3632392883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4506130218506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6292495727539</t>
+    <t xml:space="preserve">23.3632373809814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.450611114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6292476654053</t>
   </si>
   <si>
     <t xml:space="preserve">20.9904079437256</t>
   </si>
   <si>
-    <t xml:space="preserve">21.264196395874</t>
+    <t xml:space="preserve">21.2641983032227</t>
   </si>
   <si>
     <t xml:space="preserve">21.1729354858398</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5340957641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.80788230896</t>
+    <t xml:space="preserve">20.5340976715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8078842163086</t>
   </si>
   <si>
     <t xml:space="preserve">20.4428329467773</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9030342102051</t>
+    <t xml:space="preserve">21.9030361175537</t>
   </si>
   <si>
     <t xml:space="preserve">22.6331367492676</t>
@@ -2624,10 +2624,10 @@
     <t xml:space="preserve">20.1690464019775</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3476829528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1651554107666</t>
+    <t xml:space="preserve">19.3476810455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1651573181152</t>
   </si>
   <si>
     <t xml:space="preserve">18.2525291442871</t>
@@ -2636,19 +2636,19 @@
     <t xml:space="preserve">18.6175804138184</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1156368255615</t>
+    <t xml:space="preserve">18.1156349182129</t>
   </si>
   <si>
     <t xml:space="preserve">17.4311676025391</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5224304199219</t>
+    <t xml:space="preserve">17.5224285125732</t>
   </si>
   <si>
     <t xml:space="preserve">16.2447509765625</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5185413360596</t>
+    <t xml:space="preserve">16.5185394287109</t>
   </si>
   <si>
     <t xml:space="preserve">16.6098022460938</t>
@@ -2657,7 +2657,7 @@
     <t xml:space="preserve">16.7010650634766</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6593246459961</t>
+    <t xml:space="preserve">17.6593227386475</t>
   </si>
   <si>
     <t xml:space="preserve">17.2486400604248</t>
@@ -2687,16 +2687,16 @@
     <t xml:space="preserve">21.7661418914795</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8574066162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3137187957764</t>
+    <t xml:space="preserve">21.8574047088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3137168884277</t>
   </si>
   <si>
     <t xml:space="preserve">21.9486656188965</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0399284362793</t>
+    <t xml:space="preserve">22.0399303436279</t>
   </si>
   <si>
     <t xml:space="preserve">21.4923534393311</t>
@@ -2711,49 +2711,49 @@
     <t xml:space="preserve">23.5913944244385</t>
   </si>
   <si>
+    <t xml:space="preserve">23.5001335144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7337303161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8271713256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.387809753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2009315490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6681289672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.621410369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0607719421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9673309326172</t>
+  </si>
+  <si>
     <t xml:space="preserve">23.5001316070557</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7337303161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.827169418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3878116607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2009296417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6681289672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.621410369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.06077003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9673309326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.500129699707</t>
-  </si>
-  <si>
     <t xml:space="preserve">22.9394912719727</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7058906555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6591720581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5190143585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4255714416504</t>
+    <t xml:space="preserve">22.7058925628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6591739654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5190124511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.425573348999</t>
   </si>
   <si>
     <t xml:space="preserve">23.4534130096436</t>
@@ -2771,7 +2771,7 @@
     <t xml:space="preserve">22.0985317230225</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9116535186768</t>
+    <t xml:space="preserve">21.9116554260254</t>
   </si>
   <si>
     <t xml:space="preserve">21.6780548095703</t>
@@ -2783,7 +2783,7 @@
     <t xml:space="preserve">23.0329303741455</t>
   </si>
   <si>
-    <t xml:space="preserve">22.986213684082</t>
+    <t xml:space="preserve">22.9862117767334</t>
   </si>
   <si>
     <t xml:space="preserve">21.8182144165039</t>
@@ -2792,7 +2792,7 @@
     <t xml:space="preserve">22.1919727325439</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7714920043945</t>
+    <t xml:space="preserve">21.7714939117432</t>
   </si>
   <si>
     <t xml:space="preserve">22.2386913299561</t>
@@ -2804,13 +2804,13 @@
     <t xml:space="preserve">23.31325340271</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7993316650391</t>
+    <t xml:space="preserve">22.7993335723877</t>
   </si>
   <si>
     <t xml:space="preserve">22.3321323394775</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5846157073975</t>
+    <t xml:space="preserve">21.5846138000488</t>
   </si>
   <si>
     <t xml:space="preserve">20.930534362793</t>
@@ -2822,7 +2822,7 @@
     <t xml:space="preserve">20.2764568328857</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9494171142578</t>
+    <t xml:space="preserve">19.9494152069092</t>
   </si>
   <si>
     <t xml:space="preserve">20.4166164398193</t>
@@ -2843,25 +2843,25 @@
     <t xml:space="preserve">19.9026947021484</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8092575073242</t>
+    <t xml:space="preserve">19.8092555999756</t>
   </si>
   <si>
     <t xml:space="preserve">19.5756568908691</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3420581817627</t>
+    <t xml:space="preserve">19.3420562744141</t>
   </si>
   <si>
     <t xml:space="preserve">19.2486171722412</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9215755462646</t>
+    <t xml:space="preserve">18.9215774536133</t>
   </si>
   <si>
     <t xml:space="preserve">18.8281364440918</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5758476257324</t>
+    <t xml:space="preserve">18.5758495330811</t>
   </si>
   <si>
     <t xml:space="preserve">18.5010967254639</t>
@@ -2873,7 +2873,7 @@
     <t xml:space="preserve">19.5289363861084</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5945358276367</t>
+    <t xml:space="preserve">18.5945377349854</t>
   </si>
   <si>
     <t xml:space="preserve">18.3702812194824</t>
@@ -2882,7 +2882,7 @@
     <t xml:space="preserve">18.0525856018066</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9217720031738</t>
+    <t xml:space="preserve">17.9217700958252</t>
   </si>
   <si>
     <t xml:space="preserve">17.7535781860352</t>
@@ -2894,10 +2894,10 @@
     <t xml:space="preserve">17.7348899841309</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4919471740723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2303142547607</t>
+    <t xml:space="preserve">17.4919452667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2303161621094</t>
   </si>
   <si>
     <t xml:space="preserve">17.1742496490479</t>
@@ -2912,7 +2912,7 @@
     <t xml:space="preserve">16.4454212188721</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1277256011963</t>
+    <t xml:space="preserve">16.1277236938477</t>
   </si>
   <si>
     <t xml:space="preserve">16.5014839172363</t>
@@ -2924,13 +2924,13 @@
     <t xml:space="preserve">16.0342845916748</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8847818374634</t>
+    <t xml:space="preserve">15.8847808837891</t>
   </si>
   <si>
     <t xml:space="preserve">15.3241405487061</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6044607162476</t>
+    <t xml:space="preserve">15.6044616699219</t>
   </si>
   <si>
     <t xml:space="preserve">15.7352771759033</t>
@@ -2948,7 +2948,7 @@
     <t xml:space="preserve">16.7444267272949</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7257385253906</t>
+    <t xml:space="preserve">16.7257404327393</t>
   </si>
   <si>
     <t xml:space="preserve">16.9313087463379</t>
@@ -2960,7 +2960,7 @@
     <t xml:space="preserve">17.9965229034424</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2581539154053</t>
+    <t xml:space="preserve">18.2581558227539</t>
   </si>
   <si>
     <t xml:space="preserve">17.6601371765137</t>
@@ -2969,10 +2969,10 @@
     <t xml:space="preserve">17.5666980743408</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6414489746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3142185211182</t>
+    <t xml:space="preserve">17.641450881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3142166137695</t>
   </si>
   <si>
     <t xml:space="preserve">18.0712738037109</t>
@@ -3011,7 +3011,7 @@
     <t xml:space="preserve">17.7162017822266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5293235778809</t>
+    <t xml:space="preserve">17.5293216705322</t>
   </si>
   <si>
     <t xml:space="preserve">16.9873714447021</t>
@@ -3023,10 +3023,10 @@
     <t xml:space="preserve">17.5480117797852</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2772274017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.922158241272</t>
+    <t xml:space="preserve">16.277229309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9221572875977</t>
   </si>
   <si>
     <t xml:space="preserve">16.0155963897705</t>
@@ -3035,19 +3035,19 @@
     <t xml:space="preserve">15.9595327377319</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9782209396362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0903491973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8287162780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6231479644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5857725143433</t>
+    <t xml:space="preserve">15.9782218933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0903472900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8287172317505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6231489181519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5857744216919</t>
   </si>
   <si>
     <t xml:space="preserve">16.0716609954834</t>
@@ -3068,10 +3068,10 @@
     <t xml:space="preserve">16.6322994232178</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6136131286621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5762367248535</t>
+    <t xml:space="preserve">16.6136112213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5762348175049</t>
   </si>
   <si>
     <t xml:space="preserve">16.3519802093506</t>
@@ -3080,13 +3080,13 @@
     <t xml:space="preserve">16.2024765014648</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7913398742676</t>
+    <t xml:space="preserve">15.7913408279419</t>
   </si>
   <si>
     <t xml:space="preserve">15.7726516723633</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6979007720947</t>
+    <t xml:space="preserve">15.6978998184204</t>
   </si>
   <si>
     <t xml:space="preserve">16.5201721191406</t>
@@ -3095,34 +3095,34 @@
     <t xml:space="preserve">16.1464138031006</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1651000976562</t>
+    <t xml:space="preserve">16.1650981903076</t>
   </si>
   <si>
     <t xml:space="preserve">16.109037399292</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8474025726318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7539653778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8660936355591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6792144775391</t>
+    <t xml:space="preserve">15.8474044799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7539663314819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8660917282104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6792125701904</t>
   </si>
   <si>
     <t xml:space="preserve">15.8100280761719</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5110216140747</t>
+    <t xml:space="preserve">15.5110206604004</t>
   </si>
   <si>
     <t xml:space="preserve">15.3802042007446</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0064458847046</t>
+    <t xml:space="preserve">15.0064449310303</t>
   </si>
   <si>
     <t xml:space="preserve">14.8008785247803</t>
@@ -3131,7 +3131,7 @@
     <t xml:space="preserve">14.6700620651245</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4271173477173</t>
+    <t xml:space="preserve">14.4271183013916</t>
   </si>
   <si>
     <t xml:space="preserve">14.5766229629517</t>
@@ -3161,13 +3161,13 @@
     <t xml:space="preserve">15.0811967849731</t>
   </si>
   <si>
-    <t xml:space="preserve">15.567084312439</t>
+    <t xml:space="preserve">15.5670852661133</t>
   </si>
   <si>
     <t xml:space="preserve">15.716588973999</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6605262756348</t>
+    <t xml:space="preserve">15.6605253219604</t>
   </si>
   <si>
     <t xml:space="preserve">15.1933259963989</t>
@@ -3176,13 +3176,13 @@
     <t xml:space="preserve">15.3988933563232</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4175815582275</t>
+    <t xml:space="preserve">15.4175806045532</t>
   </si>
   <si>
     <t xml:space="preserve">15.4362697601318</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1372623443604</t>
+    <t xml:space="preserve">15.137261390686</t>
   </si>
   <si>
     <t xml:space="preserve">15.0438222885132</t>
@@ -3194,7 +3194,7 @@
     <t xml:space="preserve">14.9877586364746</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7261266708374</t>
+    <t xml:space="preserve">14.7261257171631</t>
   </si>
   <si>
     <t xml:space="preserve">14.950382232666</t>
@@ -3209,22 +3209,22 @@
     <t xml:space="preserve">14.3149900436401</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5018711090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4084300994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1654863357544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2028617858887</t>
+    <t xml:space="preserve">14.5018701553345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4084310531616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1654872894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.202862739563</t>
   </si>
   <si>
     <t xml:space="preserve">14.2963027954102</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1281108856201</t>
+    <t xml:space="preserve">14.1281099319458</t>
   </si>
   <si>
     <t xml:space="preserve">13.8291034698486</t>
@@ -3239,19 +3239,19 @@
     <t xml:space="preserve">13.4179677963257</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5487842559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6422243118286</t>
+    <t xml:space="preserve">13.5487833023071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6422233581543</t>
   </si>
   <si>
     <t xml:space="preserve">13.45534324646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3992795944214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3245286941528</t>
+    <t xml:space="preserve">13.3992805480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3245277404785</t>
   </si>
   <si>
     <t xml:space="preserve">13.2497758865356</t>
@@ -3260,7 +3260,7 @@
     <t xml:space="preserve">13.0815839767456</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3432159423828</t>
+    <t xml:space="preserve">13.3432149887085</t>
   </si>
   <si>
     <t xml:space="preserve">13.1937122344971</t>
@@ -3269,7 +3269,7 @@
     <t xml:space="preserve">13.3058395385742</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2589273452759</t>
+    <t xml:space="preserve">14.2589263916016</t>
   </si>
   <si>
     <t xml:space="preserve">14.2776145935059</t>
@@ -3278,7 +3278,7 @@
     <t xml:space="preserve">14.7448139190674</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5575485229492</t>
+    <t xml:space="preserve">16.5575466156006</t>
   </si>
   <si>
     <t xml:space="preserve">16.4641094207764</t>
@@ -3287,13 +3287,13 @@
     <t xml:space="preserve">16.4267311096191</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3146018981934</t>
+    <t xml:space="preserve">16.314603805542</t>
   </si>
   <si>
     <t xml:space="preserve">16.2585391998291</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2398509979248</t>
+    <t xml:space="preserve">16.2398529052734</t>
   </si>
   <si>
     <t xml:space="preserve">16.1837882995605</t>
@@ -3302,13 +3302,13 @@
     <t xml:space="preserve">14.8569412231445</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7074384689331</t>
+    <t xml:space="preserve">14.7074375152588</t>
   </si>
   <si>
     <t xml:space="preserve">14.6887502670288</t>
   </si>
   <si>
-    <t xml:space="preserve">14.389741897583</t>
+    <t xml:space="preserve">14.3897428512573</t>
   </si>
   <si>
     <t xml:space="preserve">14.782190322876</t>
@@ -3329,19 +3329,19 @@
     <t xml:space="preserve">12.9881439208984</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5956954956055</t>
+    <t xml:space="preserve">12.5956964492798</t>
   </si>
   <si>
     <t xml:space="preserve">12.7078247070312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7452011108398</t>
+    <t xml:space="preserve">12.7452001571655</t>
   </si>
   <si>
     <t xml:space="preserve">12.4275054931641</t>
   </si>
   <si>
-    <t xml:space="preserve">13.044207572937</t>
+    <t xml:space="preserve">13.0442085266113</t>
   </si>
   <si>
     <t xml:space="preserve">13.3805913925171</t>
@@ -3368,28 +3368,28 @@
     <t xml:space="preserve">13.9972944259644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.015983581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6513738632202</t>
+    <t xml:space="preserve">14.0159826278687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6513748168945</t>
   </si>
   <si>
     <t xml:space="preserve">15.0251340866089</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4736452102661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9034700393677</t>
+    <t xml:space="preserve">15.4736442565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.903468132019</t>
   </si>
   <si>
     <t xml:space="preserve">16.482795715332</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9126205444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8565559387207</t>
+    <t xml:space="preserve">16.912618637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8565578460693</t>
   </si>
   <si>
     <t xml:space="preserve">16.9499950408936</t>
@@ -3398,7 +3398,7 @@
     <t xml:space="preserve">16.8752422332764</t>
   </si>
   <si>
-    <t xml:space="preserve">17.043436050415</t>
+    <t xml:space="preserve">17.0434341430664</t>
   </si>
   <si>
     <t xml:space="preserve">15.9969091415405</t>
@@ -3410,7 +3410,7 @@
     <t xml:space="preserve">15.5483961105347</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6418380737305</t>
+    <t xml:space="preserve">15.6418361663818</t>
   </si>
   <si>
     <t xml:space="preserve">16.4080429077148</t>
@@ -3422,13 +3422,13 @@
     <t xml:space="preserve">16.6790199279785</t>
   </si>
   <si>
-    <t xml:space="preserve">16.585578918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8002986907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.706859588623</t>
+    <t xml:space="preserve">16.5855808258057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8002967834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7068576812744</t>
   </si>
   <si>
     <t xml:space="preserve">16.211820602417</t>
@@ -3437,19 +3437,19 @@
     <t xml:space="preserve">15.3708620071411</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3052616119385</t>
+    <t xml:space="preserve">16.3052597045898</t>
   </si>
   <si>
     <t xml:space="preserve">16.0249404907227</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1273365020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9404602050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6134204864502</t>
+    <t xml:space="preserve">18.1273384094238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9404582977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6134185791016</t>
   </si>
   <si>
     <t xml:space="preserve">17.7070121765137</t>
@@ -69657,7 +69657,7 @@
     </row>
     <row r="2520">
       <c r="A2520" s="1" t="n">
-        <v>45987.6912268518</v>
+        <v>45987.3333333333</v>
       </c>
       <c r="B2520" t="n">
         <v>2351</v>
@@ -69678,6 +69678,32 @@
         <v>1270</v>
       </c>
       <c r="H2520" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2521">
+      <c r="A2521" s="1" t="n">
+        <v>45988.6909837963</v>
+      </c>
+      <c r="B2521" t="n">
+        <v>2808</v>
+      </c>
+      <c r="C2521" t="n">
+        <v>13.6999998092651</v>
+      </c>
+      <c r="D2521" t="n">
+        <v>13.4499998092651</v>
+      </c>
+      <c r="E2521" t="n">
+        <v>13.5500001907349</v>
+      </c>
+      <c r="F2521" t="n">
+        <v>13.5500001907349</v>
+      </c>
+      <c r="G2521" t="s">
+        <v>1257</v>
+      </c>
+      <c r="H2521" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SAB.MI.xlsx
+++ b/data/SAB.MI.xlsx
@@ -38,22 +38,22 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56568145751953</t>
+    <t xml:space="preserve">8.56568050384521</t>
   </si>
   <si>
     <t xml:space="preserve">SAB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61823081970215</t>
+    <t xml:space="preserve">8.61823177337646</t>
   </si>
   <si>
     <t xml:space="preserve">8.4831018447876</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33295822143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37049293518066</t>
+    <t xml:space="preserve">8.33296012878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37049388885498</t>
   </si>
   <si>
     <t xml:space="preserve">8.31794357299805</t>
@@ -65,34 +65,34 @@
     <t xml:space="preserve">8.16029453277588</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88252973556519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52969264984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66482019424438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62728500366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61227083206177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73989152908325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75490617752075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76992130279541</t>
+    <t xml:space="preserve">7.88252830505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52969074249268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66481924057007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62728404998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61226987838745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73989248275757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75490713119507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76992082595825</t>
   </si>
   <si>
     <t xml:space="preserve">7.89754343032837</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6197772026062</t>
+    <t xml:space="preserve">7.61977815628052</t>
   </si>
   <si>
     <t xml:space="preserve">7.79994964599609</t>
@@ -101,25 +101,25 @@
     <t xml:space="preserve">7.72487831115723</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65731239318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50716972351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34201240539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54470634460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39080905914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58224105834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82247066497803</t>
+    <t xml:space="preserve">7.65731334686279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5071702003479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34201145172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54470586776733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39080858230591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58224201202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82247018814087</t>
   </si>
   <si>
     <t xml:space="preserve">8.0852222442627</t>
@@ -128,22 +128,22 @@
     <t xml:space="preserve">8.11525058746338</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95759963989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06269931793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03267192840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92006349563599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77742719650269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86751365661621</t>
+    <t xml:space="preserve">7.95760059356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06270122528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03267097473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92006301879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77742671966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86751413345337</t>
   </si>
   <si>
     <t xml:space="preserve">7.80745649337769</t>
@@ -152,370 +152,370 @@
     <t xml:space="preserve">7.98762893676758</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04017925262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99513578414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96510601043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90504884719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93507766723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89003658294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94258499145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82997846603394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81496429443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73238515853882</t>
+    <t xml:space="preserve">8.0401782989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99513530731201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96510648727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90505075454712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93507814407349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89003562927246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94258642196655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82997941970825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81496238708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73238468170166</t>
   </si>
   <si>
     <t xml:space="preserve">7.64980602264404</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71737051010132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67232799530029</t>
+    <t xml:space="preserve">7.71737003326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67232894897461</t>
   </si>
   <si>
     <t xml:space="preserve">7.6347918510437</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51467800140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64229917526245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56722688674927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70235633850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74739933013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46963357925415</t>
+    <t xml:space="preserve">7.51467704772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64229774475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56722736358643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70235538482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.747398853302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46963405609131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69484949111938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4921555519104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47338771820068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43585252761841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50341701507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48089408874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59725570678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42834424972534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38705539703369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37204122543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31949043273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28195476531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52122163772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80533981323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75009489059448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75798511505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81323003768921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8605842590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69879579544067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58435916900635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68695545196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57646656036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53700637817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49754571914673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28445672988892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92536449432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.079261302948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22921228408813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45808458328247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26078033447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37127017974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26472663879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34759521484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46992254257202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3673243522644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37916421890259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13450574874878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18975067138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10293769836426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15029096603394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10688352584839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20553541183472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18185901641846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22131967544556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19369697570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24894237518311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19764375686646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18580532073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22526597976685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20948171615601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31602621078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21342802047729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16607475280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24499654769897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13056039810181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11082983016968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17791318893433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23315811157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2765645980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30024147033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29234933853149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24105024337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11872243881226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09504556655884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00428676605225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94509553909302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93325567245483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09899091720581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15423679351807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13845205307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1581826210022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05558443069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07136869430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06742286682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02401638031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04769325256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0634765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08320713043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05163860321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04374647140503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03190803527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05953073501587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03585433959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1739673614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9056339263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91352558135986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93720293045044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92141819000244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94114828109741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96877098083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14239883422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45019245147705</t>
   </si>
   <si>
     <t xml:space="preserve">7.69484901428223</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49215507507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47338724136353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43585157394409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50341558456421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48089456558228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59725427627563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4283447265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38705587387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37204122543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31948900222778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28195333480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52122211456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80533933639526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75009489059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75798654556274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81323194503784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86058521270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69879579544067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58435869216919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68695688247681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57646656036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53700733184814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49754476547241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28445672988892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92536354064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07926225662231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22921276092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45808506011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26078081130981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37127113342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26472616195679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34759521484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46992349624634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36732530593872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37916278839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13450622558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18975114822388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10293769836426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15029144287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10688352584839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20553493499756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18185997009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22132015228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19369745254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24894380569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19764375686646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18580484390259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22526550292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20948219299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3160252571106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21342754364014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16607475280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24499750137329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13055992126465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11082935333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17791414260864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23315811157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27656555175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30024099349976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29234886169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24105024337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11872100830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09504652023315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00428676605225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94509553909302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93325567245483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09899187088013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15423679351807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13845205307007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15818166732788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0555853843689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07136917114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06742238998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02401494979858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04769372940063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06347703933716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08320808410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05163860321045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04374599456787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03190851211548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05953025817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03585481643677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17396640777588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90563440322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91352701187134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93720293045044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92141819000244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94114780426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96877145767212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1423978805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45019149780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69484758377075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79349994659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92372226715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04999542236328</t>
+    <t xml:space="preserve">7.79350090026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9237208366394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0499963760376</t>
   </si>
   <si>
     <t xml:space="preserve">8.207839012146</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16837882995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08945655822754</t>
+    <t xml:space="preserve">8.16837787628174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08945751190186</t>
   </si>
   <si>
     <t xml:space="preserve">8.19994735717773</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06578063964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1289176940918</t>
+    <t xml:space="preserve">8.06578159332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12891674041748</t>
   </si>
   <si>
     <t xml:space="preserve">8.17626953125</t>
@@ -524,31 +524,31 @@
     <t xml:space="preserve">8.32622051239014</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55509281158447</t>
+    <t xml:space="preserve">8.55509376525879</t>
   </si>
   <si>
     <t xml:space="preserve">8.56298637390137</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42881870269775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35778903961182</t>
+    <t xml:space="preserve">8.42881965637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35779094696045</t>
   </si>
   <si>
     <t xml:space="preserve">8.39725112915039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42092704772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44460391998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40514278411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26308536529541</t>
+    <t xml:space="preserve">8.42092800140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44460296630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40514183044434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26308345794678</t>
   </si>
   <si>
     <t xml:space="preserve">8.18416118621826</t>
@@ -557,34 +557,34 @@
     <t xml:space="preserve">8.30254554748535</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22362327575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28676223754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25519371032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34989738464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3104362487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36568164825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33411312103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34200477600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46038818359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62612438201904</t>
+    <t xml:space="preserve">8.22362232208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2867603302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25519180297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34989833831787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31043815612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36568355560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3341121673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34200572967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46038722991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62612342834473</t>
   </si>
   <si>
     <t xml:space="preserve">8.74450492858887</t>
@@ -593,10 +593,10 @@
     <t xml:space="preserve">8.88656425476074</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00494766235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23381805419922</t>
+    <t xml:space="preserve">9.0049467086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23381900787354</t>
   </si>
   <si>
     <t xml:space="preserve">9.30484771728516</t>
@@ -611,22 +611,22 @@
     <t xml:space="preserve">9.19435787200928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24960422515869</t>
+    <t xml:space="preserve">9.24960231781006</t>
   </si>
   <si>
     <t xml:space="preserve">9.29695606231689</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36798667907715</t>
+    <t xml:space="preserve">9.36798477172852</t>
   </si>
   <si>
     <t xml:space="preserve">9.54950523376465</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67578029632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74680995941162</t>
+    <t xml:space="preserve">9.67577934265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7468090057373</t>
   </si>
   <si>
     <t xml:space="preserve">10.2203378677368</t>
@@ -638,22 +638,22 @@
     <t xml:space="preserve">10.4571027755737</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2913665771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2597990036011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1493082046509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0861711502075</t>
+    <t xml:space="preserve">10.2913675308228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2597999572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1493091583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0861721038818</t>
   </si>
   <si>
     <t xml:space="preserve">10.0151414871216</t>
   </si>
   <si>
-    <t xml:space="preserve">10.101954460144</t>
+    <t xml:space="preserve">10.1019554138184</t>
   </si>
   <si>
     <t xml:space="preserve">10.1650924682617</t>
@@ -662,16 +662,16 @@
     <t xml:space="preserve">10.0546026229858</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1808776855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1177396774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1887693405151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0703887939453</t>
+    <t xml:space="preserve">10.1808757781982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1177406311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1887702941895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0703859329224</t>
   </si>
   <si>
     <t xml:space="preserve">10.1098480224609</t>
@@ -680,31 +680,31 @@
     <t xml:space="preserve">10.0230340957642</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4965629577637</t>
+    <t xml:space="preserve">10.496563911438</t>
   </si>
   <si>
     <t xml:space="preserve">10.4176416397095</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3150434494019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7333288192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4492111206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5597009658813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6386213302612</t>
+    <t xml:space="preserve">10.3150444030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7333278656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4492101669312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.559700012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6386203765869</t>
   </si>
   <si>
     <t xml:space="preserve">10.5912685394287</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0095539093018</t>
+    <t xml:space="preserve">11.0095520019531</t>
   </si>
   <si>
     <t xml:space="preserve">10.883279800415</t>
@@ -713,7 +713,7 @@
     <t xml:space="preserve">11.3410234451294</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0592098236084</t>
+    <t xml:space="preserve">12.0592079162598</t>
   </si>
   <si>
     <t xml:space="preserve">11.9171514511108</t>
@@ -725,25 +725,25 @@
     <t xml:space="preserve">11.6882791519165</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6803874969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2644062042236</t>
+    <t xml:space="preserve">11.6803865432739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2644052505493</t>
   </si>
   <si>
     <t xml:space="preserve">12.6274442672729</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5406312942505</t>
+    <t xml:space="preserve">12.5406303405762</t>
   </si>
   <si>
     <t xml:space="preserve">12.6747980117798</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7379350662231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4728565216064</t>
+    <t xml:space="preserve">12.7379341125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4728555679321</t>
   </si>
   <si>
     <t xml:space="preserve">12.6518526077271</t>
@@ -752,46 +752,46 @@
     <t xml:space="preserve">12.8471231460571</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8145771026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9203481674194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8715305328369</t>
+    <t xml:space="preserve">12.8145780563354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9203491210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8715314865112</t>
   </si>
   <si>
     <t xml:space="preserve">12.9366207122803</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8064413070679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6437168121338</t>
+    <t xml:space="preserve">12.8064422607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6437177658081</t>
   </si>
   <si>
     <t xml:space="preserve">12.822714805603</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5209140777588</t>
+    <t xml:space="preserve">11.5209159851074</t>
   </si>
   <si>
     <t xml:space="preserve">11.8463659286499</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7812738418579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9114551544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9277276992798</t>
+    <t xml:space="preserve">11.7812757492065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9114570617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9277286529541</t>
   </si>
   <si>
     <t xml:space="preserve">11.9602727890015</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8056840896606</t>
+    <t xml:space="preserve">11.805685043335</t>
   </si>
   <si>
     <t xml:space="preserve">12.1311330795288</t>
@@ -815,34 +815,34 @@
     <t xml:space="preserve">11.8789110183716</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7161855697632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4720993041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5534601211548</t>
+    <t xml:space="preserve">11.7161836624146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4720983505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5534591674805</t>
   </si>
   <si>
     <t xml:space="preserve">11.5860061645508</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7975473403931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8951826095581</t>
+    <t xml:space="preserve">11.7975492477417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8951835632324</t>
   </si>
   <si>
     <t xml:space="preserve">12.0904521942139</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1636791229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.074179649353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2287673950195</t>
+    <t xml:space="preserve">12.1636781692505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0741806030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2287683486938</t>
   </si>
   <si>
     <t xml:space="preserve">12.1392698287964</t>
@@ -851,22 +851,22 @@
     <t xml:space="preserve">12.2043600082397</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1880884170532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1474075317383</t>
+    <t xml:space="preserve">12.1880865097046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.147406578064</t>
   </si>
   <si>
     <t xml:space="preserve">12.2531785964966</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3670835494995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4077663421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.448447227478</t>
+    <t xml:space="preserve">12.3670845031738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4077653884888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4484462738037</t>
   </si>
   <si>
     <t xml:space="preserve">12.9447574615479</t>
@@ -881,22 +881,22 @@
     <t xml:space="preserve">13.0098476409912</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9528932571411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8552589416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7332143783569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7738971710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9854393005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2620706558228</t>
+    <t xml:space="preserve">12.9528942108154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.855260848999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7332162857056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7738962173462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9854383468628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2620716094971</t>
   </si>
   <si>
     <t xml:space="preserve">13.685154914856</t>
@@ -905,112 +905,112 @@
     <t xml:space="preserve">13.9292430877686</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9943323135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7502470016479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.815336227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8316078186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.018741607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0268774032593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1814651489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.157057762146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2302846908569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7754106521606</t>
+    <t xml:space="preserve">13.9943332672119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7502450942993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8153352737427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8316097259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0187406539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.026876449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1814680099487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1570587158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2302827835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.775411605835</t>
   </si>
   <si>
     <t xml:space="preserve">15.3205394744873</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2961301803589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4588537216187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8249893188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7924423217773</t>
+    <t xml:space="preserve">15.2961330413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4588575363159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8249864578247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7924394607544</t>
   </si>
   <si>
     <t xml:space="preserve">15.5076732635498</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8493957519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8656663894653</t>
+    <t xml:space="preserve">15.8493938446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.865668296814</t>
   </si>
   <si>
     <t xml:space="preserve">15.5158100128174</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0039825439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2643432617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7769260406494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.955924987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4115543365479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0454196929932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0787220001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6475028991699</t>
+    <t xml:space="preserve">16.0039844512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.264347076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.776927947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9559230804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4115562438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0454216003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0787258148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6475048065186</t>
   </si>
   <si>
     <t xml:space="preserve">18.0217723846436</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0543174743652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1275444030762</t>
+    <t xml:space="preserve">18.0543193817139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1275424957275</t>
   </si>
   <si>
     <t xml:space="preserve">18.2984027862549</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4123134613037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1682224273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1600875854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9160003662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.265100479126</t>
+    <t xml:space="preserve">18.4123115539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1682262420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1600894927979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9159984588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2651023864746</t>
   </si>
   <si>
     <t xml:space="preserve">17.0861053466797</t>
@@ -1025,7 +1025,7 @@
     <t xml:space="preserve">17.1267852783203</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8745594024658</t>
+    <t xml:space="preserve">16.8745613098145</t>
   </si>
   <si>
     <t xml:space="preserve">17.0779666900635</t>
@@ -1034,13 +1034,13 @@
     <t xml:space="preserve">16.8664245605469</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7850646972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9884700775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5979290008545</t>
+    <t xml:space="preserve">16.7850608825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9884662628174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5979309082031</t>
   </si>
   <si>
     <t xml:space="preserve">16.9152431488037</t>
@@ -1055,34 +1055,34 @@
     <t xml:space="preserve">16.882698059082</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9233779907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1349239349365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0698299407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1674652099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6637763977051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2251777648926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8598041534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.06321144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7052154541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6319885253906</t>
+    <t xml:space="preserve">16.9233798980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1349220275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0698280334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1674690246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6637744903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2251758575439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8598022460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0632095336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7052173614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6319904327393</t>
   </si>
   <si>
     <t xml:space="preserve">18.7377605438232</t>
@@ -1091,25 +1091,25 @@
     <t xml:space="preserve">18.7133522033691</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5913105010986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3065414428711</t>
+    <t xml:space="preserve">18.59130859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3065376281738</t>
   </si>
   <si>
     <t xml:space="preserve">18.6157169342041</t>
   </si>
   <si>
-    <t xml:space="preserve">18.217041015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2089042663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4611282348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5417327880859</t>
+    <t xml:space="preserve">18.2170391082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2089061737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4611301422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5417346954346</t>
   </si>
   <si>
     <t xml:space="preserve">16.9071063995361</t>
@@ -1118,13 +1118,13 @@
     <t xml:space="preserve">16.4758853912354</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3945236206055</t>
+    <t xml:space="preserve">16.3945217132568</t>
   </si>
   <si>
     <t xml:space="preserve">16.1097545623779</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3619785308838</t>
+    <t xml:space="preserve">16.3619804382324</t>
   </si>
   <si>
     <t xml:space="preserve">16.2806148529053</t>
@@ -1139,112 +1139,112 @@
     <t xml:space="preserve">16.2236633300781</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2724781036377</t>
+    <t xml:space="preserve">16.272481918335</t>
   </si>
   <si>
     <t xml:space="preserve">16.679292678833</t>
   </si>
   <si>
-    <t xml:space="preserve">16.313159942627</t>
+    <t xml:space="preserve">16.3131580352783</t>
   </si>
   <si>
     <t xml:space="preserve">16.0934829711914</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9470329284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1911182403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3538417816162</t>
+    <t xml:space="preserve">15.9470310211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1911163330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3538436889648</t>
   </si>
   <si>
     <t xml:space="preserve">16.028392791748</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9144868850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1822242736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.970682144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1008625030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.873046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2221460342407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8478813171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8893194198608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1984958648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3937654495239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5402202606201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9381380081177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5964155197144</t>
+    <t xml:space="preserve">15.9144840240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1822233200073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9706802368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1008596420288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8730478286743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.222146987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.847882270813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8893175125122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1984949111938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3937673568726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5402193069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9381370544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5964136123657</t>
   </si>
   <si>
     <t xml:space="preserve">14.4011449813843</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2058744430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1082401275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0594234466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9129695892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0106048583984</t>
+    <t xml:space="preserve">14.2058734893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1082410812378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.059422492981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9129705429077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0106039047241</t>
   </si>
   <si>
     <t xml:space="preserve">14.3197841644287</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6452331542969</t>
+    <t xml:space="preserve">14.6452302932739</t>
   </si>
   <si>
     <t xml:space="preserve">14.7428674697876</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7265949249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.214768409729</t>
+    <t xml:space="preserve">14.7265958786011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2147674560547</t>
   </si>
   <si>
     <t xml:space="preserve">14.8079566955566</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8567724227905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9544086456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7916831970215</t>
+    <t xml:space="preserve">14.8567743301392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9544067382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7916851043701</t>
   </si>
   <si>
     <t xml:space="preserve">14.2709646224976</t>
@@ -1256,34 +1256,34 @@
     <t xml:space="preserve">14.4825048446655</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9218654632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.905592918396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0194978713989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0520429611206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2562065124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7354879379272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8168506622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6215810775757</t>
+    <t xml:space="preserve">14.9218635559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9055910110474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0194997787476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0520448684692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2562084197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7354869842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8168487548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6215829849243</t>
   </si>
   <si>
     <t xml:space="preserve">15.9307584762573</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6866703033447</t>
+    <t xml:space="preserve">15.6866731643677</t>
   </si>
   <si>
     <t xml:space="preserve">15.7192163467407</t>
@@ -1292,67 +1292,67 @@
     <t xml:space="preserve">15.7029418945312</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6703987121582</t>
+    <t xml:space="preserve">15.6703968048096</t>
   </si>
   <si>
     <t xml:space="preserve">15.6053094863892</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5653524398804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9956836700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0291938781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0627031326294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2470083236694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2302513122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5318412780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7161436080933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8669414520264</t>
+    <t xml:space="preserve">15.5653495788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9956827163696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0291919708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0627021789551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2470064163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2302522659302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5318422317505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7161464691162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8669404983521</t>
   </si>
   <si>
     <t xml:space="preserve">15.5821084976196</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4983320236206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4815759658813</t>
+    <t xml:space="preserve">15.498330116272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4815769195557</t>
   </si>
   <si>
     <t xml:space="preserve">15.4145555496216</t>
   </si>
   <si>
-    <t xml:space="preserve">15.179988861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0794591903687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1129665374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3589954376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.291974067688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2584657669067</t>
+    <t xml:space="preserve">15.1799898147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0794582366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1129684448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3589944839478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2919750213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2584648132324</t>
   </si>
   <si>
     <t xml:space="preserve">14.4595251083374</t>
@@ -1361,76 +1361,76 @@
     <t xml:space="preserve">14.4092597961426</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5600538253784</t>
+    <t xml:space="preserve">14.5600528717041</t>
   </si>
   <si>
     <t xml:space="preserve">13.4039621353149</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4877367019653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2364120483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5380020141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4374723434448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.191445350647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5882654190063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6887969970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4207181930542</t>
+    <t xml:space="preserve">13.4877376556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2364139556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5380010604858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4374732971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1914463043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5882663726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.688796043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4207162857056</t>
   </si>
   <si>
     <t xml:space="preserve">13.5212469100952</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5715131759644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3201866149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1526374816895</t>
+    <t xml:space="preserve">13.5715112686157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3201875686646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1526384353638</t>
   </si>
   <si>
     <t xml:space="preserve">13.1861476898193</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2196569442749</t>
+    <t xml:space="preserve">13.2196578979492</t>
   </si>
   <si>
     <t xml:space="preserve">13.3034315109253</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8510494232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6834983825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5662155151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.901312828064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8342933654785</t>
+    <t xml:space="preserve">12.8510484695435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6834993362427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5662136077881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9013147354126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8342943191528</t>
   </si>
   <si>
     <t xml:space="preserve">12.4824390411377</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1473398208618</t>
+    <t xml:space="preserve">12.1473407745361</t>
   </si>
   <si>
     <t xml:space="preserve">12.0803213119507</t>
@@ -1445,10 +1445,10 @@
     <t xml:space="preserve">11.5609178543091</t>
   </si>
   <si>
-    <t xml:space="preserve">11.192307472229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2258186340332</t>
+    <t xml:space="preserve">11.1923084259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2258176803589</t>
   </si>
   <si>
     <t xml:space="preserve">12.4321746826172</t>
@@ -1460,34 +1460,34 @@
     <t xml:space="preserve">13.2531671524048</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2866773605347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7672729492188</t>
+    <t xml:space="preserve">13.286675453186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7672739028931</t>
   </si>
   <si>
     <t xml:space="preserve">13.3536968231201</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9850883483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8007831573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6332349777222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8678026199341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8122425079346</t>
+    <t xml:space="preserve">12.9850873947144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8007841110229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6332340240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8678035736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8122415542603</t>
   </si>
   <si>
     <t xml:space="preserve">11.6279373168945</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6111822128296</t>
+    <t xml:space="preserve">11.6111812591553</t>
   </si>
   <si>
     <t xml:space="preserve">11.7284669876099</t>
@@ -1499,25 +1499,25 @@
     <t xml:space="preserve">11.8960161209106</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6614465713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0750246047974</t>
+    <t xml:space="preserve">11.6614475250244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.075023651123</t>
   </si>
   <si>
     <t xml:space="preserve">11.0415134429932</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9577398300171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7566804885864</t>
+    <t xml:space="preserve">10.9577388763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7566795349121</t>
   </si>
   <si>
     <t xml:space="preserve">10.9242286682129</t>
   </si>
   <si>
-    <t xml:space="preserve">10.974494934082</t>
+    <t xml:space="preserve">10.9744939804077</t>
   </si>
   <si>
     <t xml:space="preserve">11.7117118835449</t>
@@ -1526,91 +1526,91 @@
     <t xml:space="preserve">12.3651552200317</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4603881835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1587972640991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1252880096436</t>
+    <t xml:space="preserve">11.4603862762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1587991714478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1252889633179</t>
   </si>
   <si>
     <t xml:space="preserve">11.1755542755127</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3766145706177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2311153411865</t>
+    <t xml:space="preserve">11.3766136169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2311162948608</t>
   </si>
   <si>
     <t xml:space="preserve">12.3986654281616</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9295272827148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7954864501953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8792610168457</t>
+    <t xml:space="preserve">11.9295263290405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7954874038696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8792629241943</t>
   </si>
   <si>
     <t xml:space="preserve">12.197606086731</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2478713989258</t>
+    <t xml:space="preserve">12.2478704452515</t>
   </si>
   <si>
     <t xml:space="preserve">12.0133018493652</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1305856704712</t>
+    <t xml:space="preserve">12.1305847167969</t>
   </si>
   <si>
     <t xml:space="preserve">12.1808500289917</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3819093704224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3316459655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4656839370728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.599723815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7170095443726</t>
+    <t xml:space="preserve">12.3819103240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3316450119019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4656848907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5997247695923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7170085906982</t>
   </si>
   <si>
     <t xml:space="preserve">12.8845586776733</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9515790939331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.968334197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2029027938843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7337636947632</t>
+    <t xml:space="preserve">12.9515781402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9683332443237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.20290184021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7337646484375</t>
   </si>
   <si>
     <t xml:space="preserve">12.8175392150879</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6499910354614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7002534866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5159492492676</t>
+    <t xml:space="preserve">12.6499900817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7002544403076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5159502029419</t>
   </si>
   <si>
     <t xml:space="preserve">12.784029006958</t>
@@ -1622,31 +1622,31 @@
     <t xml:space="preserve">13.0353536605835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5494604110718</t>
+    <t xml:space="preserve">12.5494585037231</t>
   </si>
   <si>
     <t xml:space="preserve">12.9348230361938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9180679321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3872060775757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6217765808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8228359222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5044927597046</t>
+    <t xml:space="preserve">12.9180688858032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.38720703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6217775344849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8228349685669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5044937133789</t>
   </si>
   <si>
     <t xml:space="preserve">13.4542264938354</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6385316848755</t>
+    <t xml:space="preserve">13.6385326385498</t>
   </si>
   <si>
     <t xml:space="preserve">13.7223062515259</t>
@@ -1661,10 +1661,10 @@
     <t xml:space="preserve">13.0185985565186</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1693935394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1023740768433</t>
+    <t xml:space="preserve">13.1693925857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1023731231689</t>
   </si>
   <si>
     <t xml:space="preserve">12.499195098877</t>
@@ -1673,19 +1673,19 @@
     <t xml:space="preserve">12.748176574707</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5740222930908</t>
+    <t xml:space="preserve">12.5740203857422</t>
   </si>
   <si>
     <t xml:space="preserve">12.3650341033936</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2257099151611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2779579162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3127880096436</t>
+    <t xml:space="preserve">12.2257108688354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2779569625854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3127889633179</t>
   </si>
   <si>
     <t xml:space="preserve">12.2953729629517</t>
@@ -1694,13 +1694,13 @@
     <t xml:space="preserve">12.3302030563354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1212167739868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5217752456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4869441986084</t>
+    <t xml:space="preserve">12.1212177276611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5217742919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4869432449341</t>
   </si>
   <si>
     <t xml:space="preserve">12.4521131515503</t>
@@ -1709,43 +1709,43 @@
     <t xml:space="preserve">12.138632774353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0515546798706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.894814491272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2082948684692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8178396224976</t>
+    <t xml:space="preserve">12.0515556335449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8948163986206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2082958221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8178386688232</t>
   </si>
   <si>
     <t xml:space="preserve">12.7655925750732</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6436824798584</t>
+    <t xml:space="preserve">12.643684387207</t>
   </si>
   <si>
     <t xml:space="preserve">12.399866104126</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6262674331665</t>
+    <t xml:space="preserve">12.6262683868408</t>
   </si>
   <si>
     <t xml:space="preserve">12.5391902923584</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8700847625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9745779037476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9571628570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9397478103638</t>
+    <t xml:space="preserve">12.8700866699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9745788574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.95716381073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9397468566895</t>
   </si>
   <si>
     <t xml:space="preserve">12.7830085754395</t>
@@ -1757,19 +1757,19 @@
     <t xml:space="preserve">12.800422668457</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8875017166138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1560487747192</t>
+    <t xml:space="preserve">12.8875007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1560478210449</t>
   </si>
   <si>
     <t xml:space="preserve">12.0341396331787</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7206611633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2431259155273</t>
+    <t xml:space="preserve">11.7206592559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2431268692017</t>
   </si>
   <si>
     <t xml:space="preserve">11.7554912567139</t>
@@ -1784,25 +1784,25 @@
     <t xml:space="preserve">12.0689697265625</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1038007736206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7903213500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8425693511963</t>
+    <t xml:space="preserve">12.1038017272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.790322303772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.842568397522</t>
   </si>
   <si>
     <t xml:space="preserve">11.9470624923706</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8251543045044</t>
+    <t xml:space="preserve">11.8251523971558</t>
   </si>
   <si>
     <t xml:space="preserve">11.8599843978882</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7729072570801</t>
+    <t xml:space="preserve">11.7729063034058</t>
   </si>
   <si>
     <t xml:space="preserve">11.8774003982544</t>
@@ -1811,7 +1811,7 @@
     <t xml:space="preserve">11.6509981155396</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5465049743652</t>
+    <t xml:space="preserve">11.5465040206909</t>
   </si>
   <si>
     <t xml:space="preserve">11.3201026916504</t>
@@ -1820,37 +1820,37 @@
     <t xml:space="preserve">11.2156095504761</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4071807861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3026857376099</t>
+    <t xml:space="preserve">11.4071798324585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3026866912842</t>
   </si>
   <si>
     <t xml:space="preserve">11.3549327850342</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3897657394409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1981935501099</t>
+    <t xml:space="preserve">11.3897638320923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1981925964355</t>
   </si>
   <si>
     <t xml:space="preserve">10.9369602203369</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0414533615112</t>
+    <t xml:space="preserve">11.0414543151855</t>
   </si>
   <si>
     <t xml:space="preserve">10.8847141265869</t>
   </si>
   <si>
-    <t xml:space="preserve">10.867299079895</t>
+    <t xml:space="preserve">10.8672971725464</t>
   </si>
   <si>
     <t xml:space="preserve">10.9717922210693</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8324661254883</t>
+    <t xml:space="preserve">10.8324670791626</t>
   </si>
   <si>
     <t xml:space="preserve">10.6234798431396</t>
@@ -1862,118 +1862,118 @@
     <t xml:space="preserve">10.5886497497559</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5189867019653</t>
+    <t xml:space="preserve">10.5189876556396</t>
   </si>
   <si>
     <t xml:space="preserve">10.4493255615234</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6583127975464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7802209854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1633615493774</t>
+    <t xml:space="preserve">10.6583108901978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7802200317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1633634567261</t>
   </si>
   <si>
     <t xml:space="preserve">11.1111164093018</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0588684082031</t>
+    <t xml:space="preserve">11.0588703155518</t>
   </si>
   <si>
     <t xml:space="preserve">10.9892063140869</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8498821258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.024037361145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0066223144531</t>
+    <t xml:space="preserve">10.8498830795288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0240383148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0066232681274</t>
   </si>
   <si>
     <t xml:space="preserve">10.7976360321045</t>
   </si>
   <si>
-    <t xml:space="preserve">10.815052986145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9543752670288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0937004089355</t>
+    <t xml:space="preserve">10.8150520324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9543762207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0936994552612</t>
   </si>
   <si>
     <t xml:space="preserve">11.7032442092896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.981894493103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9296474456787</t>
+    <t xml:space="preserve">11.9818935394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9296464920044</t>
   </si>
   <si>
     <t xml:space="preserve">11.9122304916382</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8077373504639</t>
+    <t xml:space="preserve">11.8077392578125</t>
   </si>
   <si>
     <t xml:space="preserve">12.2605419158936</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0863857269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9644775390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5290880203247</t>
+    <t xml:space="preserve">12.086386680603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9644765853882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.529088973999</t>
   </si>
   <si>
     <t xml:space="preserve">11.4942579269409</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5813341140747</t>
+    <t xml:space="preserve">11.5813360214233</t>
   </si>
   <si>
     <t xml:space="preserve">11.476842880249</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6858282089233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.190878868103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3476190567017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5116739273071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5987501144409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7105588912964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70045852661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49147033691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03866672515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98641967773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42912292480469</t>
+    <t xml:space="preserve">11.6858291625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1908798217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3476209640503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5116729736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5987510681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7105579376221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70045757293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49146938323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03866481781006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98641872406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42912197113037</t>
   </si>
   <si>
     <t xml:space="preserve">8.18530464172363</t>
@@ -1985,55 +1985,55 @@
     <t xml:space="preserve">8.45524501800537</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53361701965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49007606506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31592178344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32462882995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16788768768311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38558387756348</t>
+    <t xml:space="preserve">8.533616065979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49007797241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31592082977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32463073730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16788959503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38558483123779</t>
   </si>
   <si>
     <t xml:space="preserve">8.28979778289795</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41170787811279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49878406524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63811016082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69035530090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67294025421143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79484844207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96900463104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75130939483643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70777034759521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83838844299316</t>
+    <t xml:space="preserve">8.41170692443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4987850189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63810920715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69035625457764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67293930053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79485034942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96900367736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75131034851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70777130126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83838748931885</t>
   </si>
   <si>
     <t xml:space="preserve">9.1866979598999</t>
@@ -2042,19 +2042,19 @@
     <t xml:space="preserve">9.05608177185059</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14316082000732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23023700714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40439224243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66562557220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57854843139648</t>
+    <t xml:space="preserve">9.14315891265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23023796081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40439319610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66562747955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57854747772217</t>
   </si>
   <si>
     <t xml:space="preserve">9.31731510162354</t>
@@ -2063,13 +2063,13 @@
     <t xml:space="preserve">8.88192653656006</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65552425384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51620006561279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6032772064209</t>
+    <t xml:space="preserve">8.65552520751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51619911193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60327816009521</t>
   </si>
   <si>
     <t xml:space="preserve">8.56844711303711</t>
@@ -2078,10 +2078,10 @@
     <t xml:space="preserve">9.36085414886475</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83978080749512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.01393699646</t>
+    <t xml:space="preserve">9.83978176116943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0139360427856</t>
   </si>
   <si>
     <t xml:space="preserve">10.1010141372681</t>
@@ -2090,10 +2090,10 @@
     <t xml:space="preserve">9.92685890197754</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88331985473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0574769973755</t>
+    <t xml:space="preserve">9.88332176208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0574760437012</t>
   </si>
   <si>
     <t xml:space="preserve">9.97039794921875</t>
@@ -2102,31 +2102,31 @@
     <t xml:space="preserve">9.70916366577148</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75270462036133</t>
+    <t xml:space="preserve">9.75270366668701</t>
   </si>
   <si>
     <t xml:space="preserve">9.6220874786377</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53500843048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79624271392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1880912780762</t>
+    <t xml:space="preserve">9.53500938415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79624080657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1880931854248</t>
   </si>
   <si>
     <t xml:space="preserve">10.2751703262329</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5364036560059</t>
+    <t xml:space="preserve">10.5364027023315</t>
   </si>
   <si>
     <t xml:space="preserve">10.9282522201538</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0153303146362</t>
+    <t xml:space="preserve">11.0153293609619</t>
   </si>
   <si>
     <t xml:space="preserve">10.7540979385376</t>
@@ -2138,16 +2138,16 @@
     <t xml:space="preserve">10.4057855606079</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3622484207153</t>
+    <t xml:space="preserve">10.362247467041</t>
   </si>
   <si>
     <t xml:space="preserve">10.3187084197998</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1894874572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2765626907349</t>
+    <t xml:space="preserve">11.1894855499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2765645980835</t>
   </si>
   <si>
     <t xml:space="preserve">11.4507188796997</t>
@@ -2162,10 +2162,10 @@
     <t xml:space="preserve">12.5011930465698</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0100755691528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8314867019653</t>
+    <t xml:space="preserve">12.0100746154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.831485748291</t>
   </si>
   <si>
     <t xml:space="preserve">11.6975450515747</t>
@@ -2177,28 +2177,28 @@
     <t xml:space="preserve">11.2064266204834</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4296617507935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.608250617981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2510747909546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5813665390015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5367202758789</t>
+    <t xml:space="preserve">11.4296627044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6082496643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2510738372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5813674926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5367212295532</t>
   </si>
   <si>
     <t xml:space="preserve">11.0278387069702</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8938961029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1617794036865</t>
+    <t xml:space="preserve">10.8938970565796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1617784500122</t>
   </si>
   <si>
     <t xml:space="preserve">11.0724849700928</t>
@@ -2207,16 +2207,16 @@
     <t xml:space="preserve">11.9207801818848</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1886615753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2333106994629</t>
+    <t xml:space="preserve">12.1886625289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2333097457886</t>
   </si>
   <si>
     <t xml:space="preserve">12.3226051330566</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8761329650879</t>
+    <t xml:space="preserve">11.8761339187622</t>
   </si>
   <si>
     <t xml:space="preserve">12.1440162658691</t>
@@ -2225,16 +2225,16 @@
     <t xml:space="preserve">11.7868385314941</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0993690490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4387836456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4834299087524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9299011230469</t>
+    <t xml:space="preserve">12.0993700027466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4387826919556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4834308624268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9299020767212</t>
   </si>
   <si>
     <t xml:space="preserve">13.8406066894531</t>
@@ -2243,7 +2243,7 @@
     <t xml:space="preserve">14.0191946029663</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9030170440674</t>
+    <t xml:space="preserve">12.9030160903931</t>
   </si>
   <si>
     <t xml:space="preserve">13.0816049575806</t>
@@ -2264,43 +2264,43 @@
     <t xml:space="preserve">13.9745473861694</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2601938247681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6620187759399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6173706054688</t>
+    <t xml:space="preserve">13.2601947784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6620178222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6173715591431</t>
   </si>
   <si>
     <t xml:space="preserve">13.88525390625</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6442546844482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7781972885132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9121379852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.090726852417</t>
+    <t xml:space="preserve">14.6442537307739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7781963348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9121370315552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0907249450684</t>
   </si>
   <si>
     <t xml:space="preserve">14.733549118042</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4210195541382</t>
+    <t xml:space="preserve">14.4210186004639</t>
   </si>
   <si>
     <t xml:space="preserve">14.5103130340576</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1800193786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8497285842896</t>
+    <t xml:space="preserve">15.1800212860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8497257232666</t>
   </si>
   <si>
     <t xml:space="preserve">15.805079460144</t>
@@ -2309,19 +2309,19 @@
     <t xml:space="preserve">16.0729637145996</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3854923248291</t>
+    <t xml:space="preserve">16.3854942321777</t>
   </si>
   <si>
     <t xml:space="preserve">16.9212589263916</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1891384124756</t>
+    <t xml:space="preserve">17.1891403198242</t>
   </si>
   <si>
     <t xml:space="preserve">16.7426681518555</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7249050140381</t>
+    <t xml:space="preserve">17.7249069213867</t>
   </si>
   <si>
     <t xml:space="preserve">17.769552230835</t>
@@ -2333,7 +2333,7 @@
     <t xml:space="preserve">17.8588466644287</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0374355316162</t>
+    <t xml:space="preserve">18.0374374389648</t>
   </si>
   <si>
     <t xml:space="preserve">18.12672996521</t>
@@ -2345,13 +2345,13 @@
     <t xml:space="preserve">18.5732002258301</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6980228424072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3053169250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5909652709961</t>
+    <t xml:space="preserve">16.6980247497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3053188323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5909671783447</t>
   </si>
   <si>
     <t xml:space="preserve">18.2160243988037</t>
@@ -2366,34 +2366,34 @@
     <t xml:space="preserve">20.1804981231689</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5376758575439</t>
+    <t xml:space="preserve">20.5376739501953</t>
   </si>
   <si>
     <t xml:space="preserve">20.6269702911377</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9841461181641</t>
+    <t xml:space="preserve">20.9841442108154</t>
   </si>
   <si>
     <t xml:space="preserve">20.8055553436279</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0734405517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0912036895752</t>
+    <t xml:space="preserve">21.0734424591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0912017822266</t>
   </si>
   <si>
     <t xml:space="preserve">20.0019092559814</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8233184814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2697906494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1982612609863</t>
+    <t xml:space="preserve">19.8233222961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2697925567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1982593536377</t>
   </si>
   <si>
     <t xml:space="preserve">19.9126129150391</t>
@@ -2402,25 +2402,25 @@
     <t xml:space="preserve">19.5554370880127</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6447334289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9303779602051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7162609100342</t>
+    <t xml:space="preserve">19.6447315216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9303798675537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7162628173828</t>
   </si>
   <si>
     <t xml:space="preserve">20.4483795166016</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4306182861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3413200378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.323558807373</t>
+    <t xml:space="preserve">21.4306144714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3413219451904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3235569000244</t>
   </si>
   <si>
     <t xml:space="preserve">21.6092052459717</t>
@@ -2429,13 +2429,13 @@
     <t xml:space="preserve">22.0556774139404</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7877922058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7700309753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.914701461792</t>
+    <t xml:space="preserve">21.7877941131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7700290679932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9147033691406</t>
   </si>
   <si>
     <t xml:space="preserve">24.4583892822266</t>
@@ -2444,22 +2444,22 @@
     <t xml:space="preserve">24.0020771026611</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8195514678955</t>
+    <t xml:space="preserve">23.8195533752441</t>
   </si>
   <si>
     <t xml:space="preserve">24.5496520996094</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4622764587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8234424591064</t>
+    <t xml:space="preserve">25.4622783660889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8234405517578</t>
   </si>
   <si>
     <t xml:space="preserve">24.0933380126953</t>
   </si>
   <si>
-    <t xml:space="preserve">24.732177734375</t>
+    <t xml:space="preserve">24.7321796417236</t>
   </si>
   <si>
     <t xml:space="preserve">24.3671283721924</t>
@@ -2468,7 +2468,7 @@
     <t xml:space="preserve">23.9108142852783</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2719764709473</t>
+    <t xml:space="preserve">23.2719745635986</t>
   </si>
   <si>
     <t xml:space="preserve">23.6370258331299</t>
@@ -2480,10 +2480,10 @@
     <t xml:space="preserve">24.2758655548096</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7282886505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1846027374268</t>
+    <t xml:space="preserve">23.7282867431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1846008300781</t>
   </si>
   <si>
     <t xml:space="preserve">25.0059642791748</t>
@@ -2492,16 +2492,16 @@
     <t xml:space="preserve">22.3593482971191</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8156623840332</t>
+    <t xml:space="preserve">22.8156604766846</t>
   </si>
   <si>
     <t xml:space="preserve">22.2680854797363</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7243976593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4545001983643</t>
+    <t xml:space="preserve">22.7243995666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4545021057129</t>
   </si>
   <si>
     <t xml:space="preserve">23.0894508361816</t>
@@ -2510,16 +2510,16 @@
     <t xml:space="preserve">23.1807117462158</t>
   </si>
   <si>
-    <t xml:space="preserve">22.906925201416</t>
+    <t xml:space="preserve">22.9069271087646</t>
   </si>
   <si>
     <t xml:space="preserve">22.1768226623535</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5418739318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9942989349365</t>
+    <t xml:space="preserve">22.5418758392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9943008422852</t>
   </si>
   <si>
     <t xml:space="preserve">22.0855617523193</t>
@@ -2528,7 +2528,7 @@
     <t xml:space="preserve">21.5379867553711</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7205104827881</t>
+    <t xml:space="preserve">21.7205085754395</t>
   </si>
   <si>
     <t xml:space="preserve">21.3554592132568</t>
@@ -2537,28 +2537,28 @@
     <t xml:space="preserve">21.8117733001709</t>
   </si>
   <si>
-    <t xml:space="preserve">21.446720123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8991451263428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0738925933838</t>
+    <t xml:space="preserve">21.4467220306396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8991470336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0738945007324</t>
   </si>
   <si>
     <t xml:space="preserve">19.8952560424805</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8039951324463</t>
+    <t xml:space="preserve">19.8039970397949</t>
   </si>
   <si>
     <t xml:space="preserve">19.6214694976807</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7127342224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.081672668457</t>
+    <t xml:space="preserve">19.7127323150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0816745758057</t>
   </si>
   <si>
     <t xml:space="preserve">24.6409149169922</t>
@@ -2567,49 +2567,49 @@
     <t xml:space="preserve">25.3710155487061</t>
   </si>
   <si>
-    <t xml:space="preserve">26.374906539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6448040008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9185924530029</t>
+    <t xml:space="preserve">26.3749046325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6448059082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9185905456543</t>
   </si>
   <si>
     <t xml:space="preserve">25.8273296356201</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5535430908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2797565460205</t>
+    <t xml:space="preserve">25.5535411834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2797546386719</t>
   </si>
   <si>
     <t xml:space="preserve">23.3632392883301</t>
   </si>
   <si>
-    <t xml:space="preserve">22.450611114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6292476654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9904098510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2641983032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1729335784912</t>
+    <t xml:space="preserve">22.4506130218506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6292495727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9904079437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.264196395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1729354858398</t>
   </si>
   <si>
     <t xml:space="preserve">20.5340957641602</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8078842163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.442834854126</t>
+    <t xml:space="preserve">20.80788230896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4428329467773</t>
   </si>
   <si>
     <t xml:space="preserve">21.9030342102051</t>
@@ -2624,7 +2624,7 @@
     <t xml:space="preserve">20.1690464019775</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3476810455322</t>
+    <t xml:space="preserve">19.3476829528809</t>
   </si>
   <si>
     <t xml:space="preserve">19.1651554107666</t>
@@ -2636,10 +2636,10 @@
     <t xml:space="preserve">18.6175804138184</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1156349182129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4311656951904</t>
+    <t xml:space="preserve">18.1156368255615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4311676025391</t>
   </si>
   <si>
     <t xml:space="preserve">17.5224304199219</t>
@@ -2648,7 +2648,7 @@
     <t xml:space="preserve">16.2447509765625</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5185394287109</t>
+    <t xml:space="preserve">16.5185413360596</t>
   </si>
   <si>
     <t xml:space="preserve">16.6098022460938</t>
@@ -2660,10 +2660,10 @@
     <t xml:space="preserve">17.6593246459961</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2486419677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3437919616699</t>
+    <t xml:space="preserve">17.2486400604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3437938690186</t>
   </si>
   <si>
     <t xml:space="preserve">18.800106048584</t>
@@ -2675,7 +2675,7 @@
     <t xml:space="preserve">18.982629776001</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5263156890869</t>
+    <t xml:space="preserve">18.5263175964355</t>
   </si>
   <si>
     <t xml:space="preserve">18.4350566864014</t>
@@ -2687,7 +2687,7 @@
     <t xml:space="preserve">21.7661418914795</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8574047088623</t>
+    <t xml:space="preserve">21.8574066162109</t>
   </si>
   <si>
     <t xml:space="preserve">22.3137187957764</t>
@@ -2696,34 +2696,34 @@
     <t xml:space="preserve">21.9486656188965</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0399303436279</t>
+    <t xml:space="preserve">22.0399284362793</t>
   </si>
   <si>
     <t xml:space="preserve">21.4923534393311</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4049777984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6787662506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5913963317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5001335144043</t>
+    <t xml:space="preserve">22.4049797058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.678768157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5913944244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5001316070557</t>
   </si>
   <si>
     <t xml:space="preserve">23.7337303161621</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8271713256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.387809753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2009315490723</t>
+    <t xml:space="preserve">23.827169418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3878116607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2009296417236</t>
   </si>
   <si>
     <t xml:space="preserve">24.6681289672852</t>
@@ -2732,28 +2732,28 @@
     <t xml:space="preserve">24.621410369873</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0607719421387</t>
+    <t xml:space="preserve">24.06077003479</t>
   </si>
   <si>
     <t xml:space="preserve">23.9673309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5001316070557</t>
+    <t xml:space="preserve">23.500129699707</t>
   </si>
   <si>
     <t xml:space="preserve">22.9394912719727</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7058925628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6591739654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5190124511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.425573348999</t>
+    <t xml:space="preserve">22.7058906555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6591720581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5190143585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4255714416504</t>
   </si>
   <si>
     <t xml:space="preserve">23.4534130096436</t>
@@ -2771,7 +2771,7 @@
     <t xml:space="preserve">22.0985317230225</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9116554260254</t>
+    <t xml:space="preserve">21.9116535186768</t>
   </si>
   <si>
     <t xml:space="preserve">21.6780548095703</t>
@@ -2783,7 +2783,7 @@
     <t xml:space="preserve">23.0329303741455</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9862117767334</t>
+    <t xml:space="preserve">22.986213684082</t>
   </si>
   <si>
     <t xml:space="preserve">21.8182144165039</t>
@@ -2792,7 +2792,7 @@
     <t xml:space="preserve">22.1919727325439</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7714939117432</t>
+    <t xml:space="preserve">21.7714920043945</t>
   </si>
   <si>
     <t xml:space="preserve">22.2386913299561</t>
@@ -2804,13 +2804,13 @@
     <t xml:space="preserve">23.31325340271</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7993335723877</t>
+    <t xml:space="preserve">22.7993316650391</t>
   </si>
   <si>
     <t xml:space="preserve">22.3321323394775</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5846138000488</t>
+    <t xml:space="preserve">21.5846157073975</t>
   </si>
   <si>
     <t xml:space="preserve">20.930534362793</t>
@@ -2822,7 +2822,7 @@
     <t xml:space="preserve">20.2764568328857</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9494152069092</t>
+    <t xml:space="preserve">19.9494171142578</t>
   </si>
   <si>
     <t xml:space="preserve">20.4166164398193</t>
@@ -2843,25 +2843,25 @@
     <t xml:space="preserve">19.9026947021484</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8092555999756</t>
+    <t xml:space="preserve">19.8092575073242</t>
   </si>
   <si>
     <t xml:space="preserve">19.5756568908691</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3420562744141</t>
+    <t xml:space="preserve">19.3420581817627</t>
   </si>
   <si>
     <t xml:space="preserve">19.2486171722412</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9215774536133</t>
+    <t xml:space="preserve">18.9215755462646</t>
   </si>
   <si>
     <t xml:space="preserve">18.8281364440918</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5758495330811</t>
+    <t xml:space="preserve">18.5758476257324</t>
   </si>
   <si>
     <t xml:space="preserve">18.5010967254639</t>
@@ -2873,7 +2873,7 @@
     <t xml:space="preserve">19.5289363861084</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5945377349854</t>
+    <t xml:space="preserve">18.5945358276367</t>
   </si>
   <si>
     <t xml:space="preserve">18.3702812194824</t>
@@ -2882,7 +2882,7 @@
     <t xml:space="preserve">18.0525856018066</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9217700958252</t>
+    <t xml:space="preserve">17.9217720031738</t>
   </si>
   <si>
     <t xml:space="preserve">17.7535781860352</t>
@@ -2894,10 +2894,10 @@
     <t xml:space="preserve">17.7348899841309</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4919452667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2303161621094</t>
+    <t xml:space="preserve">17.4919471740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2303142547607</t>
   </si>
   <si>
     <t xml:space="preserve">17.1742496490479</t>
@@ -2912,7 +2912,7 @@
     <t xml:space="preserve">16.4454212188721</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1277236938477</t>
+    <t xml:space="preserve">16.1277256011963</t>
   </si>
   <si>
     <t xml:space="preserve">16.5014839172363</t>
@@ -2924,13 +2924,13 @@
     <t xml:space="preserve">16.0342845916748</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8847808837891</t>
+    <t xml:space="preserve">15.8847818374634</t>
   </si>
   <si>
     <t xml:space="preserve">15.3241405487061</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6044616699219</t>
+    <t xml:space="preserve">15.6044607162476</t>
   </si>
   <si>
     <t xml:space="preserve">15.7352771759033</t>
@@ -2948,7 +2948,7 @@
     <t xml:space="preserve">16.7444267272949</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7257404327393</t>
+    <t xml:space="preserve">16.7257385253906</t>
   </si>
   <si>
     <t xml:space="preserve">16.9313087463379</t>
@@ -2960,7 +2960,7 @@
     <t xml:space="preserve">17.9965229034424</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2581558227539</t>
+    <t xml:space="preserve">18.2581539154053</t>
   </si>
   <si>
     <t xml:space="preserve">17.6601371765137</t>
@@ -2969,10 +2969,10 @@
     <t xml:space="preserve">17.5666980743408</t>
   </si>
   <si>
-    <t xml:space="preserve">17.641450881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3142166137695</t>
+    <t xml:space="preserve">17.6414489746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3142185211182</t>
   </si>
   <si>
     <t xml:space="preserve">18.0712738037109</t>
@@ -3011,7 +3011,7 @@
     <t xml:space="preserve">17.7162017822266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5293216705322</t>
+    <t xml:space="preserve">17.5293235778809</t>
   </si>
   <si>
     <t xml:space="preserve">16.9873714447021</t>
@@ -3023,10 +3023,10 @@
     <t xml:space="preserve">17.5480117797852</t>
   </si>
   <si>
-    <t xml:space="preserve">16.277229309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9221572875977</t>
+    <t xml:space="preserve">16.2772274017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.922158241272</t>
   </si>
   <si>
     <t xml:space="preserve">16.0155963897705</t>
@@ -3035,19 +3035,19 @@
     <t xml:space="preserve">15.9595327377319</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9782218933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0903472900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8287172317505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6231489181519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5857744216919</t>
+    <t xml:space="preserve">15.9782209396362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0903491973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8287162780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6231479644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5857725143433</t>
   </si>
   <si>
     <t xml:space="preserve">16.0716609954834</t>
@@ -3068,10 +3068,10 @@
     <t xml:space="preserve">16.6322994232178</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6136112213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5762348175049</t>
+    <t xml:space="preserve">16.6136131286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5762367248535</t>
   </si>
   <si>
     <t xml:space="preserve">16.3519802093506</t>
@@ -3080,13 +3080,13 @@
     <t xml:space="preserve">16.2024765014648</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7913408279419</t>
+    <t xml:space="preserve">15.7913398742676</t>
   </si>
   <si>
     <t xml:space="preserve">15.7726516723633</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6978998184204</t>
+    <t xml:space="preserve">15.6979007720947</t>
   </si>
   <si>
     <t xml:space="preserve">16.5201721191406</t>
@@ -3095,34 +3095,34 @@
     <t xml:space="preserve">16.1464138031006</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1650981903076</t>
+    <t xml:space="preserve">16.1651000976562</t>
   </si>
   <si>
     <t xml:space="preserve">16.109037399292</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8474044799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7539663314819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8660917282104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6792125701904</t>
+    <t xml:space="preserve">15.8474025726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7539653778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8660936355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6792144775391</t>
   </si>
   <si>
     <t xml:space="preserve">15.8100280761719</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5110206604004</t>
+    <t xml:space="preserve">15.5110216140747</t>
   </si>
   <si>
     <t xml:space="preserve">15.3802042007446</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0064449310303</t>
+    <t xml:space="preserve">15.0064458847046</t>
   </si>
   <si>
     <t xml:space="preserve">14.8008785247803</t>
@@ -3131,7 +3131,7 @@
     <t xml:space="preserve">14.6700620651245</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4271183013916</t>
+    <t xml:space="preserve">14.4271173477173</t>
   </si>
   <si>
     <t xml:space="preserve">14.5766229629517</t>
@@ -3161,13 +3161,13 @@
     <t xml:space="preserve">15.0811967849731</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5670852661133</t>
+    <t xml:space="preserve">15.567084312439</t>
   </si>
   <si>
     <t xml:space="preserve">15.716588973999</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6605253219604</t>
+    <t xml:space="preserve">15.6605262756348</t>
   </si>
   <si>
     <t xml:space="preserve">15.1933259963989</t>
@@ -3176,13 +3176,13 @@
     <t xml:space="preserve">15.3988933563232</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4175806045532</t>
+    <t xml:space="preserve">15.4175815582275</t>
   </si>
   <si>
     <t xml:space="preserve">15.4362697601318</t>
   </si>
   <si>
-    <t xml:space="preserve">15.137261390686</t>
+    <t xml:space="preserve">15.1372623443604</t>
   </si>
   <si>
     <t xml:space="preserve">15.0438222885132</t>
@@ -3194,7 +3194,7 @@
     <t xml:space="preserve">14.9877586364746</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7261257171631</t>
+    <t xml:space="preserve">14.7261266708374</t>
   </si>
   <si>
     <t xml:space="preserve">14.950382232666</t>
@@ -3209,22 +3209,22 @@
     <t xml:space="preserve">14.3149900436401</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5018701553345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4084310531616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1654872894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.202862739563</t>
+    <t xml:space="preserve">14.5018711090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4084300994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1654863357544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2028617858887</t>
   </si>
   <si>
     <t xml:space="preserve">14.2963027954102</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1281099319458</t>
+    <t xml:space="preserve">14.1281108856201</t>
   </si>
   <si>
     <t xml:space="preserve">13.8291034698486</t>
@@ -3239,19 +3239,19 @@
     <t xml:space="preserve">13.4179677963257</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5487833023071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6422233581543</t>
+    <t xml:space="preserve">13.5487842559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6422243118286</t>
   </si>
   <si>
     <t xml:space="preserve">13.45534324646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3992805480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3245277404785</t>
+    <t xml:space="preserve">13.3992795944214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3245286941528</t>
   </si>
   <si>
     <t xml:space="preserve">13.2497758865356</t>
@@ -3260,7 +3260,7 @@
     <t xml:space="preserve">13.0815839767456</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3432149887085</t>
+    <t xml:space="preserve">13.3432159423828</t>
   </si>
   <si>
     <t xml:space="preserve">13.1937122344971</t>
@@ -3269,7 +3269,7 @@
     <t xml:space="preserve">13.3058395385742</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2589263916016</t>
+    <t xml:space="preserve">14.2589273452759</t>
   </si>
   <si>
     <t xml:space="preserve">14.2776145935059</t>
@@ -3278,7 +3278,7 @@
     <t xml:space="preserve">14.7448139190674</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5575466156006</t>
+    <t xml:space="preserve">16.5575485229492</t>
   </si>
   <si>
     <t xml:space="preserve">16.4641094207764</t>
@@ -3287,13 +3287,13 @@
     <t xml:space="preserve">16.4267311096191</t>
   </si>
   <si>
-    <t xml:space="preserve">16.314603805542</t>
+    <t xml:space="preserve">16.3146018981934</t>
   </si>
   <si>
     <t xml:space="preserve">16.2585391998291</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2398529052734</t>
+    <t xml:space="preserve">16.2398509979248</t>
   </si>
   <si>
     <t xml:space="preserve">16.1837882995605</t>
@@ -3302,13 +3302,13 @@
     <t xml:space="preserve">14.8569412231445</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7074375152588</t>
+    <t xml:space="preserve">14.7074384689331</t>
   </si>
   <si>
     <t xml:space="preserve">14.6887502670288</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3897428512573</t>
+    <t xml:space="preserve">14.389741897583</t>
   </si>
   <si>
     <t xml:space="preserve">14.782190322876</t>
@@ -3329,19 +3329,19 @@
     <t xml:space="preserve">12.9881439208984</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5956964492798</t>
+    <t xml:space="preserve">12.5956954956055</t>
   </si>
   <si>
     <t xml:space="preserve">12.7078247070312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7452001571655</t>
+    <t xml:space="preserve">12.7452011108398</t>
   </si>
   <si>
     <t xml:space="preserve">12.4275054931641</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0442085266113</t>
+    <t xml:space="preserve">13.044207572937</t>
   </si>
   <si>
     <t xml:space="preserve">13.3805913925171</t>
@@ -3368,28 +3368,28 @@
     <t xml:space="preserve">13.9972944259644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0159826278687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6513748168945</t>
+    <t xml:space="preserve">14.015983581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6513738632202</t>
   </si>
   <si>
     <t xml:space="preserve">15.0251340866089</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4736442565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.903468132019</t>
+    <t xml:space="preserve">15.4736452102661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9034700393677</t>
   </si>
   <si>
     <t xml:space="preserve">16.482795715332</t>
   </si>
   <si>
-    <t xml:space="preserve">16.912618637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8565578460693</t>
+    <t xml:space="preserve">16.9126205444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8565559387207</t>
   </si>
   <si>
     <t xml:space="preserve">16.9499950408936</t>
@@ -3398,7 +3398,7 @@
     <t xml:space="preserve">16.8752422332764</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0434341430664</t>
+    <t xml:space="preserve">17.043436050415</t>
   </si>
   <si>
     <t xml:space="preserve">15.9969091415405</t>
@@ -3410,7 +3410,7 @@
     <t xml:space="preserve">15.5483961105347</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6418361663818</t>
+    <t xml:space="preserve">15.6418380737305</t>
   </si>
   <si>
     <t xml:space="preserve">16.4080429077148</t>
@@ -3422,13 +3422,13 @@
     <t xml:space="preserve">16.6790199279785</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5855808258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8002967834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7068576812744</t>
+    <t xml:space="preserve">16.585578918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8002986907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.706859588623</t>
   </si>
   <si>
     <t xml:space="preserve">16.211820602417</t>
@@ -3437,19 +3437,19 @@
     <t xml:space="preserve">15.3708620071411</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3052597045898</t>
+    <t xml:space="preserve">16.3052616119385</t>
   </si>
   <si>
     <t xml:space="preserve">16.0249404907227</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1273384094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9404582977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6134185791016</t>
+    <t xml:space="preserve">18.1273365020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9404602050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6134204864502</t>
   </si>
   <si>
     <t xml:space="preserve">17.7070121765137</t>
@@ -70125,7 +70125,7 @@
     </row>
     <row r="2538">
       <c r="A2538" s="1" t="n">
-        <v>46013.6912384259</v>
+        <v>46013.3333333333</v>
       </c>
       <c r="B2538" t="n">
         <v>4156</v>
@@ -70146,6 +70146,32 @@
         <v>1261</v>
       </c>
       <c r="H2538" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2539">
+      <c r="A2539" s="1" t="n">
+        <v>46014.6910300926</v>
+      </c>
+      <c r="B2539" t="n">
+        <v>3652</v>
+      </c>
+      <c r="C2539" t="n">
+        <v>13.8999996185303</v>
+      </c>
+      <c r="D2539" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="E2539" t="n">
+        <v>13.8999996185303</v>
+      </c>
+      <c r="F2539" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="G2539" t="s">
+        <v>1260</v>
+      </c>
+      <c r="H2539" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SAB.MI.xlsx
+++ b/data/SAB.MI.xlsx
@@ -44,37 +44,37 @@
     <t xml:space="preserve">SAB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61823177337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4831018447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33296012878418</t>
+    <t xml:space="preserve">8.61823081970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48310279846191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33295822143555</t>
   </si>
   <si>
     <t xml:space="preserve">8.37049388885498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31794357299805</t>
+    <t xml:space="preserve">8.31794452667236</t>
   </si>
   <si>
     <t xml:space="preserve">8.25788593292236</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16029453277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88252830505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52969074249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66481924057007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62728404998779</t>
+    <t xml:space="preserve">8.16029357910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88252735137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52969121932983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6648211479187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62728452682495</t>
   </si>
   <si>
     <t xml:space="preserve">7.61226987838745</t>
@@ -83,43 +83,43 @@
     <t xml:space="preserve">7.73989248275757</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75490713119507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76992082595825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89754343032837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61977815628052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79994964599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72487831115723</t>
+    <t xml:space="preserve">7.75490665435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76992034912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89754438400269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61977767944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79994916915894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72487735748291</t>
   </si>
   <si>
     <t xml:space="preserve">7.65731334686279</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5071702003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34201145172119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54470586776733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39080858230591</t>
+    <t xml:space="preserve">7.50716924667358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34201192855835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54470539093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39080810546875</t>
   </si>
   <si>
     <t xml:space="preserve">7.58224201202393</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82247018814087</t>
+    <t xml:space="preserve">7.82247114181519</t>
   </si>
   <si>
     <t xml:space="preserve">8.0852222442627</t>
@@ -131,40 +131,40 @@
     <t xml:space="preserve">7.95760059356689</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06270122528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03267097473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92006301879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77742671966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86751413345337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80745649337769</t>
+    <t xml:space="preserve">8.06270027160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03267192840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92006397247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77742719650269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86751222610474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80745601654053</t>
   </si>
   <si>
     <t xml:space="preserve">7.98762893676758</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0401782989502</t>
+    <t xml:space="preserve">8.04017925262451</t>
   </si>
   <si>
     <t xml:space="preserve">7.99513530731201</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96510648727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90505075454712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93507814407349</t>
+    <t xml:space="preserve">7.96510744094849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90504884719849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93507719039917</t>
   </si>
   <si>
     <t xml:space="preserve">7.89003562927246</t>
@@ -173,22 +173,22 @@
     <t xml:space="preserve">7.94258642196655</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82997941970825</t>
+    <t xml:space="preserve">7.82997751235962</t>
   </si>
   <si>
     <t xml:space="preserve">7.81496238708496</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73238468170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64980602264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71737003326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67232894897461</t>
+    <t xml:space="preserve">7.73238515853882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64980554580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.717369556427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67232847213745</t>
   </si>
   <si>
     <t xml:space="preserve">7.6347918510437</t>
@@ -197,300 +197,300 @@
     <t xml:space="preserve">7.51467704772949</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64229774475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56722736358643</t>
+    <t xml:space="preserve">7.64229869842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56722831726074</t>
   </si>
   <si>
     <t xml:space="preserve">7.70235538482666</t>
   </si>
   <si>
-    <t xml:space="preserve">7.747398853302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46963405609131</t>
+    <t xml:space="preserve">7.74739980697632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46963453292847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69484901428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49215507507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47338724136353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43585348129272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50341606140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48089504241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59725522994995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42834424972534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38705587387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37203979492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31949090957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28195428848267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52122163772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80533981323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75009393692017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75798511505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81323099136353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8605842590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69879579544067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58435916900635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68695640563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57646751403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53700637817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49754476547241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28445720672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92536354064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.079261302948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22921133041382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45808362960815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26078033447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37127017974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26472663879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34759521484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46992254257202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3673243522644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37916326522827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13450622558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18975114822388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10293817520142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15029048919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10688400268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20553636550903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1818585395813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22131967544556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19369792938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24894285202026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19764375686646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18580436706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22526597976685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20948171615601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31602621078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21342802047729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16607475280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24499654769897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13055896759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11083030700684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17791366577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23315906524658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27656555175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30024147033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29234981536865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24105024337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11872243881226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09504652023315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00428581237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94509506225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93325614929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09899091720581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15423679351807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13845252990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15818166732788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05558443069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07136869430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06742286682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02401638031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04769325256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06347703933716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08320760726929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05163860321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04374742507935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03190755844116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05953073501587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03585386276245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1739673614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9056339263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91352701187134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93720245361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9214186668396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94114875793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9687705039978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14239883422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45019245147705</t>
   </si>
   <si>
     <t xml:space="preserve">7.69484949111938</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4921555519104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47338771820068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43585252761841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50341701507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48089408874512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59725570678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42834424972534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38705539703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37204122543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31949043273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28195476531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52122163772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80533981323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75009489059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75798511505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81323003768921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8605842590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69879579544067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58435916900635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68695545196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57646656036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53700637817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49754571914673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28445672988892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92536449432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.079261302948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22921228408813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45808458328247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26078033447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37127017974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26472663879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34759521484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46992254257202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3673243522644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37916421890259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13450574874878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18975067138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10293769836426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15029096603394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10688352584839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20553541183472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18185901641846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22131967544556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19369697570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24894237518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19764375686646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18580532073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22526597976685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20948171615601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31602621078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21342802047729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16607475280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24499654769897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13056039810181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11082983016968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17791318893433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23315811157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2765645980835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30024147033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29234933853149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24105024337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11872243881226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09504556655884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00428676605225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94509553909302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93325567245483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09899091720581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15423679351807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13845205307007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1581826210022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05558443069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07136869430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06742286682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02401638031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04769325256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0634765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08320713043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05163860321045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04374647140503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03190803527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05953073501587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03585433959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1739673614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9056339263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91352558135986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93720293045044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92141819000244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94114828109741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96877098083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14239883422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45019245147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69484901428223</t>
-  </si>
-  <si>
     <t xml:space="preserve">7.79350090026855</t>
   </si>
   <si>
@@ -500,7 +500,7 @@
     <t xml:space="preserve">8.0499963760376</t>
   </si>
   <si>
-    <t xml:space="preserve">8.207839012146</t>
+    <t xml:space="preserve">8.20783805847168</t>
   </si>
   <si>
     <t xml:space="preserve">8.16837787628174</t>
@@ -512,13 +512,13 @@
     <t xml:space="preserve">8.19994735717773</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06578159332275</t>
+    <t xml:space="preserve">8.06578063964844</t>
   </si>
   <si>
     <t xml:space="preserve">8.12891674041748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17626953125</t>
+    <t xml:space="preserve">8.17627048492432</t>
   </si>
   <si>
     <t xml:space="preserve">8.32622051239014</t>
@@ -530,13 +530,13 @@
     <t xml:space="preserve">8.56298637390137</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42881965637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35779094696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39725112915039</t>
+    <t xml:space="preserve">8.42881870269775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35778999328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39725017547607</t>
   </si>
   <si>
     <t xml:space="preserve">8.42092800140381</t>
@@ -545,46 +545,46 @@
     <t xml:space="preserve">8.44460296630859</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40514183044434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26308345794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18416118621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30254554748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22362232208252</t>
+    <t xml:space="preserve">8.40514278411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26308441162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18416213989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30254650115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22362327575684</t>
   </si>
   <si>
     <t xml:space="preserve">8.2867603302002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25519180297852</t>
+    <t xml:space="preserve">8.25519371032715</t>
   </si>
   <si>
     <t xml:space="preserve">8.34989833831787</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31043815612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36568355560303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3341121673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34200572967529</t>
+    <t xml:space="preserve">8.31043720245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36568450927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33411312103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34200477600098</t>
   </si>
   <si>
     <t xml:space="preserve">8.46038722991943</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62612342834473</t>
+    <t xml:space="preserve">8.62612247467041</t>
   </si>
   <si>
     <t xml:space="preserve">8.74450492858887</t>
@@ -596,10 +596,10 @@
     <t xml:space="preserve">9.0049467086792</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23381900787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30484771728516</t>
+    <t xml:space="preserve">9.23381996154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30484867095947</t>
   </si>
   <si>
     <t xml:space="preserve">9.26538848876953</t>
@@ -608,25 +608,25 @@
     <t xml:space="preserve">9.1627893447876</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19435787200928</t>
+    <t xml:space="preserve">9.19435691833496</t>
   </si>
   <si>
     <t xml:space="preserve">9.24960231781006</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29695606231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36798477172852</t>
+    <t xml:space="preserve">9.29695510864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36798572540283</t>
   </si>
   <si>
     <t xml:space="preserve">9.54950523376465</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67577934265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7468090057373</t>
+    <t xml:space="preserve">9.67578029632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74680995941162</t>
   </si>
   <si>
     <t xml:space="preserve">10.2203378677368</t>
@@ -635,16 +635,16 @@
     <t xml:space="preserve">10.4807786941528</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4571027755737</t>
+    <t xml:space="preserve">10.4571018218994</t>
   </si>
   <si>
     <t xml:space="preserve">10.2913675308228</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2597999572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1493091583252</t>
+    <t xml:space="preserve">10.2597980499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1493082046509</t>
   </si>
   <si>
     <t xml:space="preserve">10.0861721038818</t>
@@ -674,10 +674,10 @@
     <t xml:space="preserve">10.0703859329224</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1098480224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0230340957642</t>
+    <t xml:space="preserve">10.1098470687866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0230350494385</t>
   </si>
   <si>
     <t xml:space="preserve">10.496563911438</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">10.4176416397095</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3150444030762</t>
+    <t xml:space="preserve">10.3150434494019</t>
   </si>
   <si>
     <t xml:space="preserve">10.7333278656006</t>
@@ -695,7 +695,7 @@
     <t xml:space="preserve">10.4492101669312</t>
   </si>
   <si>
-    <t xml:space="preserve">10.559700012207</t>
+    <t xml:space="preserve">10.5597009658813</t>
   </si>
   <si>
     <t xml:space="preserve">10.6386203765869</t>
@@ -704,13 +704,13 @@
     <t xml:space="preserve">10.5912685394287</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0095520019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.883279800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3410234451294</t>
+    <t xml:space="preserve">11.0095539093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8832788467407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3410224914551</t>
   </si>
   <si>
     <t xml:space="preserve">12.0592079162598</t>
@@ -719,7 +719,7 @@
     <t xml:space="preserve">11.9171514511108</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0513181686401</t>
+    <t xml:space="preserve">12.0513191223145</t>
   </si>
   <si>
     <t xml:space="preserve">11.6882791519165</t>
@@ -728,13 +728,13 @@
     <t xml:space="preserve">11.6803865432739</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2644052505493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6274442672729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5406303405762</t>
+    <t xml:space="preserve">12.2644062042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6274452209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5406312942505</t>
   </si>
   <si>
     <t xml:space="preserve">12.6747980117798</t>
@@ -743,19 +743,19 @@
     <t xml:space="preserve">12.7379341125488</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4728555679321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6518526077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8471231460571</t>
+    <t xml:space="preserve">12.4728565216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6518516540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8471221923828</t>
   </si>
   <si>
     <t xml:space="preserve">12.8145780563354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9203491210938</t>
+    <t xml:space="preserve">12.9203481674194</t>
   </si>
   <si>
     <t xml:space="preserve">12.8715314865112</t>
@@ -764,16 +764,16 @@
     <t xml:space="preserve">12.9366207122803</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8064422607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6437177658081</t>
+    <t xml:space="preserve">12.8064413070679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6437168121338</t>
   </si>
   <si>
     <t xml:space="preserve">12.822714805603</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5209159851074</t>
+    <t xml:space="preserve">11.5209150314331</t>
   </si>
   <si>
     <t xml:space="preserve">11.8463659286499</t>
@@ -782,13 +782,13 @@
     <t xml:space="preserve">11.7812757492065</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9114570617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9277286529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9602727890015</t>
+    <t xml:space="preserve">11.9114561080933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9277276992798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9602718353271</t>
   </si>
   <si>
     <t xml:space="preserve">11.805685043335</t>
@@ -797,10 +797,10 @@
     <t xml:space="preserve">12.1311330795288</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0009536743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9846811294556</t>
+    <t xml:space="preserve">12.0009546279907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9846820831299</t>
   </si>
   <si>
     <t xml:space="preserve">12.0416355133057</t>
@@ -815,10 +815,10 @@
     <t xml:space="preserve">11.8789110183716</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7161836624146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4720983505249</t>
+    <t xml:space="preserve">11.7161846160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4720973968506</t>
   </si>
   <si>
     <t xml:space="preserve">11.5534591674805</t>
@@ -833,7 +833,7 @@
     <t xml:space="preserve">11.8951835632324</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0904521942139</t>
+    <t xml:space="preserve">12.0904531478882</t>
   </si>
   <si>
     <t xml:space="preserve">12.1636781692505</t>
@@ -854,7 +854,7 @@
     <t xml:space="preserve">12.1880865097046</t>
   </si>
   <si>
-    <t xml:space="preserve">12.147406578064</t>
+    <t xml:space="preserve">12.1474056243896</t>
   </si>
   <si>
     <t xml:space="preserve">12.2531785964966</t>
@@ -863,7 +863,7 @@
     <t xml:space="preserve">12.3670845031738</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4077653884888</t>
+    <t xml:space="preserve">12.4077663421631</t>
   </si>
   <si>
     <t xml:space="preserve">12.4484462738037</t>
@@ -872,7 +872,7 @@
     <t xml:space="preserve">12.9447574615479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7820329666138</t>
+    <t xml:space="preserve">12.7820339202881</t>
   </si>
   <si>
     <t xml:space="preserve">12.8959407806396</t>
@@ -884,61 +884,61 @@
     <t xml:space="preserve">12.9528942108154</t>
   </si>
   <si>
-    <t xml:space="preserve">12.855260848999</t>
+    <t xml:space="preserve">12.8552598953247</t>
   </si>
   <si>
     <t xml:space="preserve">12.7332162857056</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7738962173462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9854383468628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2620716094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.685154914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9292430877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9943332672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7502450942993</t>
+    <t xml:space="preserve">12.7738971710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9854393005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2620706558228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6851558685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9292421340942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9943313598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.750244140625</t>
   </si>
   <si>
     <t xml:space="preserve">13.8153352737427</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8316097259521</t>
+    <t xml:space="preserve">13.8316087722778</t>
   </si>
   <si>
     <t xml:space="preserve">14.0187406539917</t>
   </si>
   <si>
-    <t xml:space="preserve">14.026876449585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1814680099487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1570587158203</t>
+    <t xml:space="preserve">14.0268774032593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1814670562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.157057762146</t>
   </si>
   <si>
     <t xml:space="preserve">14.2302827835083</t>
   </si>
   <si>
-    <t xml:space="preserve">14.775411605835</t>
+    <t xml:space="preserve">14.7754106521606</t>
   </si>
   <si>
     <t xml:space="preserve">15.3205394744873</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2961330413818</t>
+    <t xml:space="preserve">15.2961320877075</t>
   </si>
   <si>
     <t xml:space="preserve">15.4588575363159</t>
@@ -947,16 +947,16 @@
     <t xml:space="preserve">15.8249864578247</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7924394607544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5076732635498</t>
+    <t xml:space="preserve">15.792441368103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5076751708984</t>
   </si>
   <si>
     <t xml:space="preserve">15.8493938446045</t>
   </si>
   <si>
-    <t xml:space="preserve">15.865668296814</t>
+    <t xml:space="preserve">15.8656702041626</t>
   </si>
   <si>
     <t xml:space="preserve">15.5158100128174</t>
@@ -965,58 +965,58 @@
     <t xml:space="preserve">16.0039844512939</t>
   </si>
   <si>
-    <t xml:space="preserve">16.264347076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.776927947998</t>
+    <t xml:space="preserve">16.2643432617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7769260406494</t>
   </si>
   <si>
     <t xml:space="preserve">16.9559230804443</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4115562438965</t>
+    <t xml:space="preserve">17.4115543365479</t>
   </si>
   <si>
     <t xml:space="preserve">17.0454216003418</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0787258148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6475048065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0217723846436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0543193817139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1275424957275</t>
+    <t xml:space="preserve">18.0787239074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6475067138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0217704772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0543174743652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1275405883789</t>
   </si>
   <si>
     <t xml:space="preserve">18.2984027862549</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4123115539551</t>
+    <t xml:space="preserve">18.4123134613037</t>
   </si>
   <si>
     <t xml:space="preserve">18.1682262420654</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1600894927979</t>
+    <t xml:space="preserve">18.1600875854492</t>
   </si>
   <si>
     <t xml:space="preserve">17.9159984588623</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2651023864746</t>
+    <t xml:space="preserve">17.2651042938232</t>
   </si>
   <si>
     <t xml:space="preserve">17.0861053466797</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2976474761963</t>
+    <t xml:space="preserve">17.2976493835449</t>
   </si>
   <si>
     <t xml:space="preserve">17.0047397613525</t>
@@ -1031,22 +1031,22 @@
     <t xml:space="preserve">17.0779666900635</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8664245605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7850608825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9884662628174</t>
+    <t xml:space="preserve">16.8664226531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.785062789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.988468170166</t>
   </si>
   <si>
     <t xml:space="preserve">16.5979309082031</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9152431488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8338813781738</t>
+    <t xml:space="preserve">16.9152450561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8338794708252</t>
   </si>
   <si>
     <t xml:space="preserve">16.9640598297119</t>
@@ -1055,67 +1055,67 @@
     <t xml:space="preserve">16.882698059082</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9233798980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1349220275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0698280334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1674690246582</t>
+    <t xml:space="preserve">16.9233779907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1349201202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0698299407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1674671173096</t>
   </si>
   <si>
     <t xml:space="preserve">17.6637744903564</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2251758575439</t>
+    <t xml:space="preserve">18.2251777648926</t>
   </si>
   <si>
     <t xml:space="preserve">18.8598022460938</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0632095336914</t>
+    <t xml:space="preserve">19.0632076263428</t>
   </si>
   <si>
     <t xml:space="preserve">18.7052173614502</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6319904327393</t>
+    <t xml:space="preserve">18.6319885253906</t>
   </si>
   <si>
     <t xml:space="preserve">18.7377605438232</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7133522033691</t>
+    <t xml:space="preserve">18.7133502960205</t>
   </si>
   <si>
     <t xml:space="preserve">18.59130859375</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3065376281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6157169342041</t>
+    <t xml:space="preserve">18.3065395355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6157188415527</t>
   </si>
   <si>
     <t xml:space="preserve">18.2170391082764</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2089061737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4611301422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5417346954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9071063995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4758853912354</t>
+    <t xml:space="preserve">18.2089080810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4611282348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5417308807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9071044921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.475887298584</t>
   </si>
   <si>
     <t xml:space="preserve">16.3945217132568</t>
@@ -1130,7 +1130,7 @@
     <t xml:space="preserve">16.2806148529053</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3782501220703</t>
+    <t xml:space="preserve">16.3782520294189</t>
   </si>
   <si>
     <t xml:space="preserve">16.199254989624</t>
@@ -1145,7 +1145,7 @@
     <t xml:space="preserve">16.679292678833</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3131580352783</t>
+    <t xml:space="preserve">16.313159942627</t>
   </si>
   <si>
     <t xml:space="preserve">16.0934829711914</t>
@@ -1154,31 +1154,31 @@
     <t xml:space="preserve">15.9470310211182</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1911163330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3538436889648</t>
+    <t xml:space="preserve">16.1911144256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3538455963135</t>
   </si>
   <si>
     <t xml:space="preserve">16.028392791748</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9144840240479</t>
+    <t xml:space="preserve">15.9144859313965</t>
   </si>
   <si>
     <t xml:space="preserve">15.1822233200073</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9706802368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1008596420288</t>
+    <t xml:space="preserve">14.970682144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1008615493774</t>
   </si>
   <si>
     <t xml:space="preserve">14.8730478286743</t>
   </si>
   <si>
-    <t xml:space="preserve">14.222146987915</t>
+    <t xml:space="preserve">14.2221479415894</t>
   </si>
   <si>
     <t xml:space="preserve">13.847882270813</t>
@@ -1190,40 +1190,40 @@
     <t xml:space="preserve">15.1984949111938</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3937673568726</t>
+    <t xml:space="preserve">15.3937654495239</t>
   </si>
   <si>
     <t xml:space="preserve">15.5402193069458</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9381370544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5964136123657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4011449813843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2058734893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1082410812378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.059422492981</t>
+    <t xml:space="preserve">14.9381351470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5964155197144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4011430740356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2058725357056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1082401275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0594215393066</t>
   </si>
   <si>
     <t xml:space="preserve">13.9129705429077</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0106039047241</t>
+    <t xml:space="preserve">14.0106058120728</t>
   </si>
   <si>
     <t xml:space="preserve">14.3197841644287</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6452302932739</t>
+    <t xml:space="preserve">14.6452322006226</t>
   </si>
   <si>
     <t xml:space="preserve">14.7428674697876</t>
@@ -1232,7 +1232,7 @@
     <t xml:space="preserve">14.7265958786011</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2147674560547</t>
+    <t xml:space="preserve">15.2147693634033</t>
   </si>
   <si>
     <t xml:space="preserve">14.8079566955566</t>
@@ -1244,10 +1244,10 @@
     <t xml:space="preserve">14.9544067382812</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7916851043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2709646224976</t>
+    <t xml:space="preserve">14.7916831970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2709655761719</t>
   </si>
   <si>
     <t xml:space="preserve">15.0032272338867</t>
@@ -1265,22 +1265,22 @@
     <t xml:space="preserve">15.0194997787476</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0520448684692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2562084197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7354869842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8168487548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6215829849243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9307584762573</t>
+    <t xml:space="preserve">15.0520458221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2562065124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7354888916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8168506622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6215810775757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9307565689087</t>
   </si>
   <si>
     <t xml:space="preserve">15.6866731643677</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">15.7029418945312</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6703968048096</t>
+    <t xml:space="preserve">15.6703987121582</t>
   </si>
   <si>
     <t xml:space="preserve">15.6053094863892</t>
@@ -1307,10 +1307,10 @@
     <t xml:space="preserve">15.0291919708252</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0627021789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2470064163208</t>
+    <t xml:space="preserve">15.0627031326294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2470054626465</t>
   </si>
   <si>
     <t xml:space="preserve">15.2302522659302</t>
@@ -1328,7 +1328,7 @@
     <t xml:space="preserve">15.5821084976196</t>
   </si>
   <si>
-    <t xml:space="preserve">15.498330116272</t>
+    <t xml:space="preserve">15.4983320236206</t>
   </si>
   <si>
     <t xml:space="preserve">15.4815769195557</t>
@@ -1337,7 +1337,7 @@
     <t xml:space="preserve">15.4145555496216</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1799898147583</t>
+    <t xml:space="preserve">15.1799879074097</t>
   </si>
   <si>
     <t xml:space="preserve">15.0794582366943</t>
@@ -1352,13 +1352,13 @@
     <t xml:space="preserve">14.2919750213623</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2584648132324</t>
+    <t xml:space="preserve">14.2584667205811</t>
   </si>
   <si>
     <t xml:space="preserve">14.4595251083374</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4092597961426</t>
+    <t xml:space="preserve">14.4092578887939</t>
   </si>
   <si>
     <t xml:space="preserve">14.5600528717041</t>
@@ -1370,7 +1370,7 @@
     <t xml:space="preserve">13.4877376556396</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2364139556885</t>
+    <t xml:space="preserve">13.2364130020142</t>
   </si>
   <si>
     <t xml:space="preserve">13.5380010604858</t>
@@ -1379,7 +1379,7 @@
     <t xml:space="preserve">13.4374732971191</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1914463043213</t>
+    <t xml:space="preserve">14.1914443969727</t>
   </si>
   <si>
     <t xml:space="preserve">13.5882663726807</t>
@@ -1388,13 +1388,13 @@
     <t xml:space="preserve">13.688796043396</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4207162857056</t>
+    <t xml:space="preserve">13.4207172393799</t>
   </si>
   <si>
     <t xml:space="preserve">13.5212469100952</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5715112686157</t>
+    <t xml:space="preserve">13.57151222229</t>
   </si>
   <si>
     <t xml:space="preserve">13.3201875686646</t>
@@ -1412,13 +1412,13 @@
     <t xml:space="preserve">13.3034315109253</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8510484695435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6834993362427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5662136077881</t>
+    <t xml:space="preserve">12.8510494232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6834983825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5662145614624</t>
   </si>
   <si>
     <t xml:space="preserve">12.9013147354126</t>
@@ -1439,7 +1439,7 @@
     <t xml:space="preserve">12.0635652542114</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9797916412354</t>
+    <t xml:space="preserve">11.9797925949097</t>
   </si>
   <si>
     <t xml:space="preserve">11.5609178543091</t>
@@ -1454,7 +1454,7 @@
     <t xml:space="preserve">12.4321746826172</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1191291809082</t>
+    <t xml:space="preserve">13.1191282272339</t>
   </si>
   <si>
     <t xml:space="preserve">13.2531671524048</t>
@@ -1466,25 +1466,25 @@
     <t xml:space="preserve">12.7672739028931</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3536968231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9850873947144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8007841110229</t>
+    <t xml:space="preserve">13.3536977767944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9850883483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8007831573486</t>
   </si>
   <si>
     <t xml:space="preserve">12.6332340240479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8678035736084</t>
+    <t xml:space="preserve">12.8678045272827</t>
   </si>
   <si>
     <t xml:space="preserve">11.8122415542603</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6279373168945</t>
+    <t xml:space="preserve">11.6279382705688</t>
   </si>
   <si>
     <t xml:space="preserve">11.6111812591553</t>
@@ -1505,7 +1505,7 @@
     <t xml:space="preserve">11.075023651123</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0415134429932</t>
+    <t xml:space="preserve">11.0415143966675</t>
   </si>
   <si>
     <t xml:space="preserve">10.9577388763428</t>
@@ -1517,16 +1517,16 @@
     <t xml:space="preserve">10.9242286682129</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9744939804077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7117118835449</t>
+    <t xml:space="preserve">10.9744930267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7117109298706</t>
   </si>
   <si>
     <t xml:space="preserve">12.3651552200317</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4603862762451</t>
+    <t xml:space="preserve">11.4603872299194</t>
   </si>
   <si>
     <t xml:space="preserve">11.1587991714478</t>
@@ -1538,7 +1538,7 @@
     <t xml:space="preserve">11.1755542755127</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3766136169434</t>
+    <t xml:space="preserve">11.376612663269</t>
   </si>
   <si>
     <t xml:space="preserve">12.2311162948608</t>
@@ -1547,13 +1547,13 @@
     <t xml:space="preserve">12.3986654281616</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9295263290405</t>
+    <t xml:space="preserve">11.9295272827148</t>
   </si>
   <si>
     <t xml:space="preserve">11.7954874038696</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8792629241943</t>
+    <t xml:space="preserve">11.87926197052</t>
   </si>
   <si>
     <t xml:space="preserve">12.197606086731</t>
@@ -1565,7 +1565,7 @@
     <t xml:space="preserve">12.0133018493652</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1305847167969</t>
+    <t xml:space="preserve">12.1305856704712</t>
   </si>
   <si>
     <t xml:space="preserve">12.1808500289917</t>
@@ -1574,7 +1574,7 @@
     <t xml:space="preserve">12.3819103240967</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3316450119019</t>
+    <t xml:space="preserve">12.3316459655762</t>
   </si>
   <si>
     <t xml:space="preserve">12.4656848907471</t>
@@ -1589,7 +1589,7 @@
     <t xml:space="preserve">12.8845586776733</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9515781402588</t>
+    <t xml:space="preserve">12.9515790939331</t>
   </si>
   <si>
     <t xml:space="preserve">12.9683332443237</t>
@@ -1598,10 +1598,10 @@
     <t xml:space="preserve">13.20290184021</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7337646484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8175392150879</t>
+    <t xml:space="preserve">12.7337636947632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8175382614136</t>
   </si>
   <si>
     <t xml:space="preserve">12.6499900817871</t>
@@ -1619,10 +1619,10 @@
     <t xml:space="preserve">13.0018434524536</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0353536605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5494585037231</t>
+    <t xml:space="preserve">13.0353527069092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5494594573975</t>
   </si>
   <si>
     <t xml:space="preserve">12.9348230361938</t>
@@ -1643,7 +1643,7 @@
     <t xml:space="preserve">13.5044937133789</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4542264938354</t>
+    <t xml:space="preserve">13.4542274475098</t>
   </si>
   <si>
     <t xml:space="preserve">13.6385326385498</t>
@@ -1652,7 +1652,7 @@
     <t xml:space="preserve">13.7223062515259</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3704528808594</t>
+    <t xml:space="preserve">13.3704538345337</t>
   </si>
   <si>
     <t xml:space="preserve">13.0521087646484</t>
@@ -1697,19 +1697,19 @@
     <t xml:space="preserve">12.1212177276611</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5217742919922</t>
+    <t xml:space="preserve">12.5217752456665</t>
   </si>
   <si>
     <t xml:space="preserve">12.4869432449341</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4521131515503</t>
+    <t xml:space="preserve">12.4521141052246</t>
   </si>
   <si>
     <t xml:space="preserve">12.138632774353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0515556335449</t>
+    <t xml:space="preserve">12.0515546798706</t>
   </si>
   <si>
     <t xml:space="preserve">11.8948163986206</t>
@@ -1718,7 +1718,7 @@
     <t xml:space="preserve">12.2082958221436</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8178386688232</t>
+    <t xml:space="preserve">12.8178396224976</t>
   </si>
   <si>
     <t xml:space="preserve">12.7655925750732</t>
@@ -1727,7 +1727,7 @@
     <t xml:space="preserve">12.643684387207</t>
   </si>
   <si>
-    <t xml:space="preserve">12.399866104126</t>
+    <t xml:space="preserve">12.3998670578003</t>
   </si>
   <si>
     <t xml:space="preserve">12.6262683868408</t>
@@ -1745,16 +1745,16 @@
     <t xml:space="preserve">12.95716381073</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9397468566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7830085754395</t>
+    <t xml:space="preserve">12.9397478103638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7830076217651</t>
   </si>
   <si>
     <t xml:space="preserve">12.6959295272827</t>
   </si>
   <si>
-    <t xml:space="preserve">12.800422668457</t>
+    <t xml:space="preserve">12.8004217147827</t>
   </si>
   <si>
     <t xml:space="preserve">12.8875007629395</t>
@@ -1811,19 +1811,19 @@
     <t xml:space="preserve">11.6509981155396</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5465040206909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3201026916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2156095504761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4071798324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3026866912842</t>
+    <t xml:space="preserve">11.5465049743652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3201017379761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2156085968018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4071788787842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3026857376099</t>
   </si>
   <si>
     <t xml:space="preserve">11.3549327850342</t>
@@ -1835,13 +1835,13 @@
     <t xml:space="preserve">11.1981925964355</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9369602203369</t>
+    <t xml:space="preserve">10.9369611740112</t>
   </si>
   <si>
     <t xml:space="preserve">11.0414543151855</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8847141265869</t>
+    <t xml:space="preserve">10.8847131729126</t>
   </si>
   <si>
     <t xml:space="preserve">10.8672971725464</t>
@@ -1853,7 +1853,7 @@
     <t xml:space="preserve">10.8324670791626</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6234798431396</t>
+    <t xml:space="preserve">10.623480796814</t>
   </si>
   <si>
     <t xml:space="preserve">10.6060657501221</t>
@@ -1901,7 +1901,7 @@
     <t xml:space="preserve">10.8150520324707</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9543762207031</t>
+    <t xml:space="preserve">10.9543771743774</t>
   </si>
   <si>
     <t xml:space="preserve">11.0936994552612</t>
@@ -1910,25 +1910,25 @@
     <t xml:space="preserve">11.7032442092896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9818935394287</t>
+    <t xml:space="preserve">11.981894493103</t>
   </si>
   <si>
     <t xml:space="preserve">11.9296464920044</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9122304916382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8077392578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2605419158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.086386680603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9644765853882</t>
+    <t xml:space="preserve">11.9122314453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8077383041382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2605409622192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0863876342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9644775390625</t>
   </si>
   <si>
     <t xml:space="preserve">11.529088973999</t>
@@ -1940,7 +1940,7 @@
     <t xml:space="preserve">11.5813360214233</t>
   </si>
   <si>
-    <t xml:space="preserve">11.476842880249</t>
+    <t xml:space="preserve">11.4768438339233</t>
   </si>
   <si>
     <t xml:space="preserve">11.6858291625977</t>
@@ -1949,7 +1949,7 @@
     <t xml:space="preserve">12.1908798217773</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3476209640503</t>
+    <t xml:space="preserve">12.347620010376</t>
   </si>
   <si>
     <t xml:space="preserve">11.5116729736328</t>
@@ -1958,19 +1958,19 @@
     <t xml:space="preserve">11.5987510681152</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7105579376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70045757293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49146938323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03866481781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98641872406006</t>
+    <t xml:space="preserve">10.7105588912964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7004566192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49147033691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03866577148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98641967773438</t>
   </si>
   <si>
     <t xml:space="preserve">8.42912197113037</t>
@@ -1979,7 +1979,7 @@
     <t xml:space="preserve">8.18530464172363</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22884368896484</t>
+    <t xml:space="preserve">8.22884273529053</t>
   </si>
   <si>
     <t xml:space="preserve">8.45524501800537</t>
@@ -1994,7 +1994,7 @@
     <t xml:space="preserve">8.31592082977295</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32463073730469</t>
+    <t xml:space="preserve">8.32462978363037</t>
   </si>
   <si>
     <t xml:space="preserve">8.16788959503174</t>
@@ -2006,7 +2006,7 @@
     <t xml:space="preserve">8.28979778289795</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41170692443848</t>
+    <t xml:space="preserve">8.41170597076416</t>
   </si>
   <si>
     <t xml:space="preserve">8.4987850189209</t>
@@ -2018,7 +2018,7 @@
     <t xml:space="preserve">8.69035625457764</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67293930053711</t>
+    <t xml:space="preserve">8.67294025421143</t>
   </si>
   <si>
     <t xml:space="preserve">8.79485034942627</t>
@@ -2048,13 +2048,13 @@
     <t xml:space="preserve">9.23023796081543</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40439319610596</t>
+    <t xml:space="preserve">9.40439224243164</t>
   </si>
   <si>
     <t xml:space="preserve">9.66562747955322</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57854747772217</t>
+    <t xml:space="preserve">9.57854843139648</t>
   </si>
   <si>
     <t xml:space="preserve">9.31731510162354</t>
@@ -2063,13 +2063,13 @@
     <t xml:space="preserve">8.88192653656006</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65552520751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51619911193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60327816009521</t>
+    <t xml:space="preserve">8.65552425384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51620006561279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60327911376953</t>
   </si>
   <si>
     <t xml:space="preserve">8.56844711303711</t>
@@ -2084,10 +2084,10 @@
     <t xml:space="preserve">10.0139360427856</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1010141372681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92685890197754</t>
+    <t xml:space="preserve">10.1010150909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92685794830322</t>
   </si>
   <si>
     <t xml:space="preserve">9.88332176208496</t>
@@ -2105,13 +2105,13 @@
     <t xml:space="preserve">9.75270366668701</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6220874786377</t>
+    <t xml:space="preserve">9.62208652496338</t>
   </si>
   <si>
     <t xml:space="preserve">9.53500938415527</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79624080657959</t>
+    <t xml:space="preserve">9.79624176025391</t>
   </si>
   <si>
     <t xml:space="preserve">10.1880931854248</t>
@@ -2123,10 +2123,10 @@
     <t xml:space="preserve">10.5364027023315</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9282522201538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0153293609619</t>
+    <t xml:space="preserve">10.9282531738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0153303146362</t>
   </si>
   <si>
     <t xml:space="preserve">10.7540979385376</t>
@@ -2135,10 +2135,10 @@
     <t xml:space="preserve">10.4928646087646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4057855606079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.362247467041</t>
+    <t xml:space="preserve">10.4057865142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3622465133667</t>
   </si>
   <si>
     <t xml:space="preserve">10.3187084197998</t>
@@ -70151,7 +70151,7 @@
     </row>
     <row r="2539">
       <c r="A2539" s="1" t="n">
-        <v>46014.6910300926</v>
+        <v>46014.3333333333</v>
       </c>
       <c r="B2539" t="n">
         <v>3652</v>

--- a/data/SAB.MI.xlsx
+++ b/data/SAB.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56568241119385</t>
+    <t xml:space="preserve">8.56568050384521</t>
   </si>
   <si>
     <t xml:space="preserve">SAB.MI</t>
@@ -47,16 +47,16 @@
     <t xml:space="preserve">8.61822986602783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48310279846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33295822143555</t>
+    <t xml:space="preserve">8.48310089111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33295917510986</t>
   </si>
   <si>
     <t xml:space="preserve">8.3704948425293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31794357299805</t>
+    <t xml:space="preserve">8.31794261932373</t>
   </si>
   <si>
     <t xml:space="preserve">8.25788593292236</t>
@@ -65,22 +65,22 @@
     <t xml:space="preserve">8.16029357910156</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88252878189087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52969074249268</t>
+    <t xml:space="preserve">7.88252735137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52969121932983</t>
   </si>
   <si>
     <t xml:space="preserve">7.66482067108154</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62728404998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61227035522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73989295959473</t>
+    <t xml:space="preserve">7.62728357315063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61227083206177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73989152908325</t>
   </si>
   <si>
     <t xml:space="preserve">7.75490617752075</t>
@@ -89,199 +89,199 @@
     <t xml:space="preserve">7.76992082595825</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89754152297974</t>
+    <t xml:space="preserve">7.89754247665405</t>
   </si>
   <si>
     <t xml:space="preserve">7.61977672576904</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79995012283325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72487688064575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65731143951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50716829299927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34201097488403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54470634460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39080858230591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58224201202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82247161865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08522129058838</t>
+    <t xml:space="preserve">7.79994869232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72487735748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65731382369995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5071702003479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34201240539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54470539093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39080905914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58224153518677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82247066497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08522319793701</t>
   </si>
   <si>
     <t xml:space="preserve">8.1152515411377</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95759963989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06269836425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03267288208008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92006397247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77742767333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86751317977905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80745506286621</t>
+    <t xml:space="preserve">7.95760107040405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06270027160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03267192840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92006301879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.777428150177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86751365661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80745601654053</t>
   </si>
   <si>
     <t xml:space="preserve">7.98762893676758</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0401782989502</t>
+    <t xml:space="preserve">8.04017925262451</t>
   </si>
   <si>
     <t xml:space="preserve">7.99513483047485</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96510744094849</t>
+    <t xml:space="preserve">7.96510696411133</t>
   </si>
   <si>
     <t xml:space="preserve">7.90504932403564</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93507862091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89003562927246</t>
+    <t xml:space="preserve">7.93507814407349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89003610610962</t>
   </si>
   <si>
     <t xml:space="preserve">7.94258499145508</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82997846603394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81496286392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73238563537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64980554580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.717369556427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67232704162598</t>
+    <t xml:space="preserve">7.82997751235962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81496381759644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73238515853882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64980602264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71737098693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67232799530029</t>
   </si>
   <si>
     <t xml:space="preserve">7.6347918510437</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51467704772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64229917526245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56722593307495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70235633850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74739742279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46963405609131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69484901428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4921555519104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47338819503784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43585062026978</t>
+    <t xml:space="preserve">7.51467752456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64229869842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56722688674927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70235538482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74739837646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46963262557983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69484996795654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49215507507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47338771820068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43585109710693</t>
   </si>
   <si>
     <t xml:space="preserve">7.50341606140137</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48089456558228</t>
+    <t xml:space="preserve">7.48089504241943</t>
   </si>
   <si>
     <t xml:space="preserve">7.59725618362427</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42834615707397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38705444335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37203979492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31949043273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28195333480835</t>
+    <t xml:space="preserve">7.42834424972534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38705539703369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37204027175903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31949138641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28195428848267</t>
   </si>
   <si>
     <t xml:space="preserve">7.52122163772583</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80533838272095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75009441375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75798559188843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81323194503784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8605842590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69879579544067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58435916900635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68695831298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57646799087524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53700590133667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49754571914673</t>
+    <t xml:space="preserve">7.80533933639526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75009346008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75798606872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81323003768921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86058521270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69879484176636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58435869216919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68695545196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57646608352661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53700733184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49754476547241</t>
   </si>
   <si>
     <t xml:space="preserve">7.28445720672607</t>
@@ -290,64 +290,64 @@
     <t xml:space="preserve">6.92536401748657</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07926082611084</t>
+    <t xml:space="preserve">7.07926177978516</t>
   </si>
   <si>
     <t xml:space="preserve">7.22921180725098</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45808362960815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26078033447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37127065658569</t>
+    <t xml:space="preserve">7.45808506011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2607798576355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37127113342285</t>
   </si>
   <si>
     <t xml:space="preserve">7.26472663879395</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34759473800659</t>
+    <t xml:space="preserve">7.34759569168091</t>
   </si>
   <si>
     <t xml:space="preserve">7.46992301940918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36732578277588</t>
+    <t xml:space="preserve">7.36732482910156</t>
   </si>
   <si>
     <t xml:space="preserve">7.37916231155396</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13450527191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18975162506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1029372215271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15029239654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10688400268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20553588867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18185901641846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22132015228271</t>
+    <t xml:space="preserve">7.13450574874878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18975114822388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10293769836426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15029096603394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10688495635986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20553493499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18185949325562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22131967544556</t>
   </si>
   <si>
     <t xml:space="preserve">7.19369745254517</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24894285202026</t>
+    <t xml:space="preserve">7.24894237518311</t>
   </si>
   <si>
     <t xml:space="preserve">7.1976432800293</t>
@@ -356,10 +356,10 @@
     <t xml:space="preserve">7.18580484390259</t>
   </si>
   <si>
-    <t xml:space="preserve">7.225266456604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20948171615601</t>
+    <t xml:space="preserve">7.22526693344116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20948123931885</t>
   </si>
   <si>
     <t xml:space="preserve">7.31602621078491</t>
@@ -368,100 +368,100 @@
     <t xml:space="preserve">7.21342754364014</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16607427597046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24499654769897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13055992126465</t>
+    <t xml:space="preserve">7.16607522964478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24499797821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13055944442749</t>
   </si>
   <si>
     <t xml:space="preserve">7.11083030700684</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17791318893433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23315811157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27656555175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30024194717407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29234743118286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24105072021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1187219619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.095046043396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00428581237793</t>
+    <t xml:space="preserve">7.17791366577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23315906524658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27656602859497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30024147033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29234838485718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24105024337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11872243881226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09504508972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00428628921509</t>
   </si>
   <si>
     <t xml:space="preserve">6.94509506225586</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93325662612915</t>
+    <t xml:space="preserve">6.93325614929199</t>
   </si>
   <si>
     <t xml:space="preserve">7.09899139404297</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15423679351807</t>
+    <t xml:space="preserve">7.15423631668091</t>
   </si>
   <si>
     <t xml:space="preserve">7.13845252990723</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1581826210022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05558395385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07137012481689</t>
+    <t xml:space="preserve">7.15818166732788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05558490753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07136917114258</t>
   </si>
   <si>
     <t xml:space="preserve">7.06742286682129</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02401542663574</t>
+    <t xml:space="preserve">7.0240159034729</t>
   </si>
   <si>
     <t xml:space="preserve">7.04769229888916</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06347799301147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08320665359497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05163812637329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04374694824219</t>
+    <t xml:space="preserve">7.06347703933716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08320713043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05164003372192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04374599456787</t>
   </si>
   <si>
     <t xml:space="preserve">7.03190851211548</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05953025817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03585433959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17396688461304</t>
+    <t xml:space="preserve">7.05953073501587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03585338592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17396831512451</t>
   </si>
   <si>
     <t xml:space="preserve">6.9056339263916</t>
@@ -473,31 +473,31 @@
     <t xml:space="preserve">6.93720293045044</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92141914367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94114875793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9687705039978</t>
+    <t xml:space="preserve">6.92141819000244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94114923477173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96877098083496</t>
   </si>
   <si>
     <t xml:space="preserve">7.14239883422852</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45019340515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7935004234314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9237208366394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04999542236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20783996582031</t>
+    <t xml:space="preserve">7.45019245147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79350090026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92372179031372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0499963760376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.207839012146</t>
   </si>
   <si>
     <t xml:space="preserve">8.16837882995605</t>
@@ -506,31 +506,31 @@
     <t xml:space="preserve">8.08945751190186</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19994735717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06578063964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1289176940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17626953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32622146606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55509471893311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56298637390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42881774902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35779094696045</t>
+    <t xml:space="preserve">8.19994640350342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06578159332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12891864776611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17627048492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32622051239014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55509376525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56298542022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42882061004639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35779190063477</t>
   </si>
   <si>
     <t xml:space="preserve">8.39725112915039</t>
@@ -542,85 +542,85 @@
     <t xml:space="preserve">8.44460391998291</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40514373779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26308536529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18416213989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30254554748535</t>
+    <t xml:space="preserve">8.40514183044434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26308345794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18416309356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30254459381104</t>
   </si>
   <si>
     <t xml:space="preserve">8.22362327575684</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28676128387451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25519275665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34989738464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3104362487793</t>
+    <t xml:space="preserve">8.2867603302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25519180297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34989833831787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31043720245361</t>
   </si>
   <si>
     <t xml:space="preserve">8.36568260192871</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3341121673584</t>
+    <t xml:space="preserve">8.33411407470703</t>
   </si>
   <si>
     <t xml:space="preserve">8.34200477600098</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46038722991943</t>
+    <t xml:space="preserve">8.46038818359375</t>
   </si>
   <si>
     <t xml:space="preserve">8.62612342834473</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74450588226318</t>
+    <t xml:space="preserve">8.74450492858887</t>
   </si>
   <si>
     <t xml:space="preserve">8.88656520843506</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00494575500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23381900787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30484867095947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2653865814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1627893447876</t>
+    <t xml:space="preserve">9.0049467086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23381805419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30484962463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26538753509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16279029846191</t>
   </si>
   <si>
     <t xml:space="preserve">9.19435787200928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24960422515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29695510864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36798572540283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54950523376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67577838897705</t>
+    <t xml:space="preserve">9.24960327148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29695606231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36798667907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54950618743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67577934265137</t>
   </si>
   <si>
     <t xml:space="preserve">9.7468090057373</t>
@@ -629,31 +629,31 @@
     <t xml:space="preserve">10.2203378677368</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4807796478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4571027755737</t>
+    <t xml:space="preserve">10.4807786941528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4571018218994</t>
   </si>
   <si>
     <t xml:space="preserve">10.2913675308228</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2598009109497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1493082046509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0861711502075</t>
+    <t xml:space="preserve">10.2597990036011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1493072509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0861721038818</t>
   </si>
   <si>
     <t xml:space="preserve">10.0151414871216</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1019563674927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1650924682617</t>
+    <t xml:space="preserve">10.1019554138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.165093421936</t>
   </si>
   <si>
     <t xml:space="preserve">10.0546035766602</t>
@@ -668,31 +668,31 @@
     <t xml:space="preserve">10.1887683868408</t>
   </si>
   <si>
-    <t xml:space="preserve">10.070387840271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1098470687866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0230331420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4965648651123</t>
+    <t xml:space="preserve">10.0703868865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1098489761353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0230340957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.496563911438</t>
   </si>
   <si>
     <t xml:space="preserve">10.4176416397095</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3150444030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7333288192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4492101669312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5597019195557</t>
+    <t xml:space="preserve">10.3150434494019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7333278656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4492111206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5597009658813</t>
   </si>
   <si>
     <t xml:space="preserve">10.6386222839355</t>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">10.591269493103</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0095529556274</t>
+    <t xml:space="preserve">11.0095539093018</t>
   </si>
   <si>
     <t xml:space="preserve">10.883279800415</t>
@@ -710,28 +710,28 @@
     <t xml:space="preserve">11.3410234451294</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0592098236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9171504974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0513172149658</t>
+    <t xml:space="preserve">12.0592107772827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9171524047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0513181686401</t>
   </si>
   <si>
     <t xml:space="preserve">11.6882791519165</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6803855895996</t>
+    <t xml:space="preserve">11.6803865432739</t>
   </si>
   <si>
     <t xml:space="preserve">12.2644052505493</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6274452209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5406303405762</t>
+    <t xml:space="preserve">12.6274442672729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5406312942505</t>
   </si>
   <si>
     <t xml:space="preserve">12.6747970581055</t>
@@ -740,7 +740,7 @@
     <t xml:space="preserve">12.7379341125488</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4728555679321</t>
+    <t xml:space="preserve">12.4728546142578</t>
   </si>
   <si>
     <t xml:space="preserve">12.6518535614014</t>
@@ -752,58 +752,58 @@
     <t xml:space="preserve">12.8145780563354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9203500747681</t>
+    <t xml:space="preserve">12.9203491210938</t>
   </si>
   <si>
     <t xml:space="preserve">12.8715305328369</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9366207122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8064413070679</t>
+    <t xml:space="preserve">12.936619758606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8064422607422</t>
   </si>
   <si>
     <t xml:space="preserve">12.6437168121338</t>
   </si>
   <si>
-    <t xml:space="preserve">12.822714805603</t>
+    <t xml:space="preserve">12.8227138519287</t>
   </si>
   <si>
     <t xml:space="preserve">11.5209159851074</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8463659286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7812757492065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9114561080933</t>
+    <t xml:space="preserve">11.8463649749756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7812747955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9114570617676</t>
   </si>
   <si>
     <t xml:space="preserve">11.9277276992798</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9602727890015</t>
+    <t xml:space="preserve">11.9602718353271</t>
   </si>
   <si>
     <t xml:space="preserve">11.8056840896606</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1311340332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0009536743164</t>
+    <t xml:space="preserve">12.1311330795288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0009527206421</t>
   </si>
   <si>
     <t xml:space="preserve">11.9846801757812</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0416345596313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0823173522949</t>
+    <t xml:space="preserve">12.0416355133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0823163986206</t>
   </si>
   <si>
     <t xml:space="preserve">11.9765453338623</t>
@@ -812,16 +812,16 @@
     <t xml:space="preserve">11.8789100646973</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7161846160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4720993041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5534601211548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5860061645508</t>
+    <t xml:space="preserve">11.7161865234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4720983505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5534610748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5860052108765</t>
   </si>
   <si>
     <t xml:space="preserve">11.7975482940674</t>
@@ -830,46 +830,46 @@
     <t xml:space="preserve">11.8951826095581</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0904512405396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1636781692505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0741786956787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2287683486938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1392698287964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2043600082397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1880865097046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1474075317383</t>
+    <t xml:space="preserve">12.0904521942139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1636791229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0741806030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2287673950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1392707824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2043609619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1880855560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.147406578064</t>
   </si>
   <si>
     <t xml:space="preserve">12.2531776428223</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3670854568481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4077663421631</t>
+    <t xml:space="preserve">12.3670845031738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4077672958374</t>
   </si>
   <si>
     <t xml:space="preserve">12.448447227478</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9447574615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7820320129395</t>
+    <t xml:space="preserve">12.9447584152222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7820329666138</t>
   </si>
   <si>
     <t xml:space="preserve">12.8959407806396</t>
@@ -884,28 +884,28 @@
     <t xml:space="preserve">12.8552589416504</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7332153320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7738962173462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9854393005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2620697021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.685154914856</t>
+    <t xml:space="preserve">12.7332143783569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7738971710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9854383468628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2620706558228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6851558685303</t>
   </si>
   <si>
     <t xml:space="preserve">13.9292430877686</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9943323135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.750244140625</t>
+    <t xml:space="preserve">13.9943342208862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7502470016479</t>
   </si>
   <si>
     <t xml:space="preserve">13.8153343200684</t>
@@ -917,64 +917,64 @@
     <t xml:space="preserve">14.0187406539917</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0268783569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1814651489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1570568084717</t>
+    <t xml:space="preserve">14.0268774032593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1814661026001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.157057762146</t>
   </si>
   <si>
     <t xml:space="preserve">14.2302837371826</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7754106521606</t>
+    <t xml:space="preserve">14.7754125595093</t>
   </si>
   <si>
     <t xml:space="preserve">15.3205404281616</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2961301803589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4588565826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8249864578247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7924423217773</t>
+    <t xml:space="preserve">15.2961311340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4588556289673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8249883651733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.792441368103</t>
   </si>
   <si>
     <t xml:space="preserve">15.5076732635498</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8493976593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8656673431396</t>
+    <t xml:space="preserve">15.8493947982788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.865668296814</t>
   </si>
   <si>
     <t xml:space="preserve">15.5158109664917</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0039844512939</t>
+    <t xml:space="preserve">16.0039825439453</t>
   </si>
   <si>
     <t xml:space="preserve">16.2643432617188</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7769298553467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9559230804443</t>
+    <t xml:space="preserve">16.7769260406494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.955924987793</t>
   </si>
   <si>
     <t xml:space="preserve">17.4115543365479</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0454235076904</t>
+    <t xml:space="preserve">17.0454216003418</t>
   </si>
   <si>
     <t xml:space="preserve">18.0787239074707</t>
@@ -983,49 +983,49 @@
     <t xml:space="preserve">17.6475067138672</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0217723846436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0543155670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1275444030762</t>
+    <t xml:space="preserve">18.0217704772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0543174743652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1275424957275</t>
   </si>
   <si>
     <t xml:space="preserve">18.2984027862549</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4123096466064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1682224273682</t>
+    <t xml:space="preserve">18.4123115539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1682243347168</t>
   </si>
   <si>
     <t xml:space="preserve">18.1600875854492</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9160003662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.265100479126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0861053466797</t>
+    <t xml:space="preserve">17.9160022735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2650985717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0861034393311</t>
   </si>
   <si>
     <t xml:space="preserve">17.2976474761963</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0047397613525</t>
+    <t xml:space="preserve">17.0047435760498</t>
   </si>
   <si>
     <t xml:space="preserve">17.1267852783203</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8745613098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0779666900635</t>
+    <t xml:space="preserve">16.8745632171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0779685974121</t>
   </si>
   <si>
     <t xml:space="preserve">16.8664264678955</t>
@@ -1037,10 +1037,10 @@
     <t xml:space="preserve">16.988468170166</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5979290008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9152431488037</t>
+    <t xml:space="preserve">16.5979309082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9152412414551</t>
   </si>
   <si>
     <t xml:space="preserve">16.8338813781738</t>
@@ -1049,28 +1049,28 @@
     <t xml:space="preserve">16.9640617370605</t>
   </si>
   <si>
-    <t xml:space="preserve">16.882698059082</t>
+    <t xml:space="preserve">16.8826999664307</t>
   </si>
   <si>
     <t xml:space="preserve">16.9233798980713</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1349201202393</t>
+    <t xml:space="preserve">17.1349239349365</t>
   </si>
   <si>
     <t xml:space="preserve">17.0698318481445</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1674671173096</t>
+    <t xml:space="preserve">17.1674652099609</t>
   </si>
   <si>
     <t xml:space="preserve">17.6637763977051</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2251758575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8598022460938</t>
+    <t xml:space="preserve">18.2251777648926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8598041534424</t>
   </si>
   <si>
     <t xml:space="preserve">19.06321144104</t>
@@ -1079,7 +1079,7 @@
     <t xml:space="preserve">18.7052154541016</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6319904327393</t>
+    <t xml:space="preserve">18.631986618042</t>
   </si>
   <si>
     <t xml:space="preserve">18.7377605438232</t>
@@ -1088,25 +1088,25 @@
     <t xml:space="preserve">18.7133522033691</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5913105010986</t>
+    <t xml:space="preserve">18.59130859375</t>
   </si>
   <si>
     <t xml:space="preserve">18.3065395355225</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6157131195068</t>
+    <t xml:space="preserve">18.6157169342041</t>
   </si>
   <si>
     <t xml:space="preserve">18.217041015625</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2089042663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4611301422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5417346954346</t>
+    <t xml:space="preserve">18.2089080810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4611320495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5417308807373</t>
   </si>
   <si>
     <t xml:space="preserve">16.9071083068848</t>
@@ -1115,25 +1115,25 @@
     <t xml:space="preserve">16.475887298584</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3945217132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1097564697266</t>
+    <t xml:space="preserve">16.3945255279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1097545623779</t>
   </si>
   <si>
     <t xml:space="preserve">16.3619804382324</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2806167602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3782501220703</t>
+    <t xml:space="preserve">16.2806186676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3782520294189</t>
   </si>
   <si>
     <t xml:space="preserve">16.1992530822754</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2236633300781</t>
+    <t xml:space="preserve">16.2236652374268</t>
   </si>
   <si>
     <t xml:space="preserve">16.2724800109863</t>
@@ -1142,10 +1142,10 @@
     <t xml:space="preserve">16.679292678833</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3131618499756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0934810638428</t>
+    <t xml:space="preserve">16.313159942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0934829711914</t>
   </si>
   <si>
     <t xml:space="preserve">15.9470300674438</t>
@@ -1154,25 +1154,25 @@
     <t xml:space="preserve">16.1911163330078</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3538417816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.028392791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9144849777222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1822242736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9706802368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1008596420288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8730459213257</t>
+    <t xml:space="preserve">16.3538398742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0283966064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9144878387451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.182225227356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9706811904907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1008605957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.873046875</t>
   </si>
   <si>
     <t xml:space="preserve">14.222146987915</t>
@@ -1181,40 +1181,40 @@
     <t xml:space="preserve">13.8478813171387</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8893194198608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1984958648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3937664031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5402183532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9381370544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5964136123657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4011468887329</t>
+    <t xml:space="preserve">14.8893203735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1984968185425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3937654495239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5402193069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.938138961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5964155197144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4011449813843</t>
   </si>
   <si>
     <t xml:space="preserve">14.2058753967285</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1082391738892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.059422492981</t>
+    <t xml:space="preserve">14.1082410812378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0594215393066</t>
   </si>
   <si>
     <t xml:space="preserve">13.9129705429077</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0106048583984</t>
+    <t xml:space="preserve">14.0106029510498</t>
   </si>
   <si>
     <t xml:space="preserve">14.3197832107544</t>
@@ -1223,7 +1223,7 @@
     <t xml:space="preserve">14.6452312469482</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7428703308105</t>
+    <t xml:space="preserve">14.7428674697876</t>
   </si>
   <si>
     <t xml:space="preserve">14.7265949249268</t>
@@ -1235,16 +1235,16 @@
     <t xml:space="preserve">14.8079566955566</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8567743301392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9544086456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7916841506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2709665298462</t>
+    <t xml:space="preserve">14.8567733764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9544076919556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7916851043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2709655761719</t>
   </si>
   <si>
     <t xml:space="preserve">15.0032272338867</t>
@@ -1253,13 +1253,13 @@
     <t xml:space="preserve">14.4825057983398</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9218626022339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9055910110474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0194988250732</t>
+    <t xml:space="preserve">14.9218645095825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9055919647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0194978713989</t>
   </si>
   <si>
     <t xml:space="preserve">15.0520448684692</t>
@@ -1268,19 +1268,19 @@
     <t xml:space="preserve">16.2562084197998</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7354879379272</t>
+    <t xml:space="preserve">15.7354860305786</t>
   </si>
   <si>
     <t xml:space="preserve">15.8168487548828</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6215829849243</t>
+    <t xml:space="preserve">15.6215801239014</t>
   </si>
   <si>
     <t xml:space="preserve">15.9307584762573</t>
   </si>
   <si>
-    <t xml:space="preserve">15.686674118042</t>
+    <t xml:space="preserve">15.6866722106934</t>
   </si>
   <si>
     <t xml:space="preserve">15.7192153930664</t>
@@ -1289,13 +1289,13 @@
     <t xml:space="preserve">15.7029399871826</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6703987121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6053094863892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5653514862061</t>
+    <t xml:space="preserve">15.6703977584839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6053085327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5653524398804</t>
   </si>
   <si>
     <t xml:space="preserve">14.9956836700439</t>
@@ -1304,61 +1304,61 @@
     <t xml:space="preserve">15.0291938781738</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0627040863037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2470083236694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2302532196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5318403244019</t>
+    <t xml:space="preserve">15.0627021789551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2470064163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2302541732788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5318422317505</t>
   </si>
   <si>
     <t xml:space="preserve">15.7161464691162</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8669414520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5821075439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4983310699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4815759658813</t>
+    <t xml:space="preserve">15.8669404983521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.582106590271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4983320236206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4815769195557</t>
   </si>
   <si>
     <t xml:space="preserve">15.4145555496216</t>
   </si>
   <si>
-    <t xml:space="preserve">15.179988861084</t>
+    <t xml:space="preserve">15.1799879074097</t>
   </si>
   <si>
     <t xml:space="preserve">15.0794582366943</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1129665374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3589944839478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.291974067688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2584648132324</t>
+    <t xml:space="preserve">15.1129693984985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3589925765991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2919731140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2584657669067</t>
   </si>
   <si>
     <t xml:space="preserve">14.4595241546631</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4092588424683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5600528717041</t>
+    <t xml:space="preserve">14.4092607498169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5600538253784</t>
   </si>
   <si>
     <t xml:space="preserve">13.4039621353149</t>
@@ -1367,10 +1367,10 @@
     <t xml:space="preserve">13.4877376556396</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2364130020142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5380010604858</t>
+    <t xml:space="preserve">13.2364120483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5380020141602</t>
   </si>
   <si>
     <t xml:space="preserve">13.4374732971191</t>
@@ -1382,7 +1382,7 @@
     <t xml:space="preserve">13.5882663726807</t>
   </si>
   <si>
-    <t xml:space="preserve">13.688796043396</t>
+    <t xml:space="preserve">13.6887969970703</t>
   </si>
   <si>
     <t xml:space="preserve">13.4207181930542</t>
@@ -1394,76 +1394,76 @@
     <t xml:space="preserve">13.57151222229</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3201875686646</t>
+    <t xml:space="preserve">13.3201856613159</t>
   </si>
   <si>
     <t xml:space="preserve">13.1526384353638</t>
   </si>
   <si>
-    <t xml:space="preserve">13.186146736145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2196578979492</t>
+    <t xml:space="preserve">13.1861486434937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2196569442749</t>
   </si>
   <si>
     <t xml:space="preserve">13.3034324645996</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8510494232178</t>
+    <t xml:space="preserve">12.8510484695435</t>
   </si>
   <si>
     <t xml:space="preserve">12.6834993362427</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5662145614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.901312828064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8342943191528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4824390411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1473407745361</t>
+    <t xml:space="preserve">12.5662155151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9013137817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8342933654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.482439994812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1473417282104</t>
   </si>
   <si>
     <t xml:space="preserve">12.0803213119507</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0635652542114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.979790687561</t>
+    <t xml:space="preserve">12.0635671615601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9797916412354</t>
   </si>
   <si>
     <t xml:space="preserve">11.5609178543091</t>
   </si>
   <si>
-    <t xml:space="preserve">11.192307472229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2258176803589</t>
+    <t xml:space="preserve">11.1923084259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2258167266846</t>
   </si>
   <si>
     <t xml:space="preserve">12.4321746826172</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1191272735596</t>
+    <t xml:space="preserve">13.1191282272339</t>
   </si>
   <si>
     <t xml:space="preserve">13.2531671524048</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2866764068604</t>
+    <t xml:space="preserve">13.2866773605347</t>
   </si>
   <si>
     <t xml:space="preserve">12.7672739028931</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3536977767944</t>
+    <t xml:space="preserve">13.3536958694458</t>
   </si>
   <si>
     <t xml:space="preserve">12.9850873947144</t>
@@ -1472,37 +1472,37 @@
     <t xml:space="preserve">12.8007841110229</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6332349777222</t>
+    <t xml:space="preserve">12.6332340240479</t>
   </si>
   <si>
     <t xml:space="preserve">12.8678026199341</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8122434616089</t>
+    <t xml:space="preserve">11.8122415542603</t>
   </si>
   <si>
     <t xml:space="preserve">11.6279373168945</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6111822128296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7284669876099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9630365371704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8960151672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6614475250244</t>
+    <t xml:space="preserve">11.6111812591553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7284660339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9630355834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.896017074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6614465713501</t>
   </si>
   <si>
     <t xml:space="preserve">11.075023651123</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0415134429932</t>
+    <t xml:space="preserve">11.0415143966675</t>
   </si>
   <si>
     <t xml:space="preserve">10.9577388763428</t>
@@ -1511,10 +1511,10 @@
     <t xml:space="preserve">10.7566795349121</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9242286682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.974494934082</t>
+    <t xml:space="preserve">10.9242296218872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9744939804077</t>
   </si>
   <si>
     <t xml:space="preserve">11.7117118835449</t>
@@ -1529,34 +1529,34 @@
     <t xml:space="preserve">11.1587982177734</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1252889633179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1755542755127</t>
+    <t xml:space="preserve">11.1252880096436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1755533218384</t>
   </si>
   <si>
     <t xml:space="preserve">11.376612663269</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2311162948608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3986654281616</t>
+    <t xml:space="preserve">12.2311153411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3986663818359</t>
   </si>
   <si>
     <t xml:space="preserve">11.9295263290405</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7954874038696</t>
+    <t xml:space="preserve">11.7954864501953</t>
   </si>
   <si>
     <t xml:space="preserve">11.87926197052</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1976070404053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2478713989258</t>
+    <t xml:space="preserve">12.1976051330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2478704452515</t>
   </si>
   <si>
     <t xml:space="preserve">12.0133008956909</t>
@@ -1568,13 +1568,13 @@
     <t xml:space="preserve">12.1808500289917</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3819103240967</t>
+    <t xml:space="preserve">12.381911277771</t>
   </si>
   <si>
     <t xml:space="preserve">12.3316459655762</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4656839370728</t>
+    <t xml:space="preserve">12.4656848907471</t>
   </si>
   <si>
     <t xml:space="preserve">12.5997247695923</t>
@@ -1583,34 +1583,34 @@
     <t xml:space="preserve">12.7170095443726</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8845596313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9515790939331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9683322906494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2029037475586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7337646484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8175382614136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6499900817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7002534866333</t>
+    <t xml:space="preserve">12.8845586776733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9515800476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.968334197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2029027938843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7337636947632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8175392150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6499910354614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7002544403076</t>
   </si>
   <si>
     <t xml:space="preserve">12.5159502029419</t>
   </si>
   <si>
-    <t xml:space="preserve">12.784029006958</t>
+    <t xml:space="preserve">12.7840280532837</t>
   </si>
   <si>
     <t xml:space="preserve">13.0018434524536</t>
@@ -1622,52 +1622,52 @@
     <t xml:space="preserve">12.5494585037231</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9348239898682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9180698394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3872060775757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6217765808105</t>
+    <t xml:space="preserve">12.9348230361938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9180688858032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.38720703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6217775344849</t>
   </si>
   <si>
     <t xml:space="preserve">13.8228349685669</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5044918060303</t>
+    <t xml:space="preserve">13.5044937133789</t>
   </si>
   <si>
     <t xml:space="preserve">13.4542274475098</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6385316848755</t>
+    <t xml:space="preserve">13.6385326385498</t>
   </si>
   <si>
     <t xml:space="preserve">13.7223052978516</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3704528808594</t>
+    <t xml:space="preserve">13.3704519271851</t>
   </si>
   <si>
     <t xml:space="preserve">13.0521087646484</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0185976028442</t>
+    <t xml:space="preserve">13.0185985565186</t>
   </si>
   <si>
     <t xml:space="preserve">13.1693925857544</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1023721694946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4991941452026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7481775283813</t>
+    <t xml:space="preserve">13.1023731231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.499195098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7481784820557</t>
   </si>
   <si>
     <t xml:space="preserve">12.5740203857422</t>
@@ -1676,565 +1676,565 @@
     <t xml:space="preserve">12.3650350570679</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2257099151611</t>
+    <t xml:space="preserve">12.2257108688354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2779569625854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3127880096436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.295373916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3302030563354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1212167739868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5217742919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4869432449341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4521131515503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.138632774353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0515546798706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8948154449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2082958221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8178396224976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7655916213989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.643684387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.399866104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6262693405151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5391912460327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8700857162476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9745788574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9571628570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9397478103638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7830076217651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6959295272827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8004236221313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8875017166138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1560478210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0341396331787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7206592559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2431259155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7554912567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6684122085571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9993085861206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0689697265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1038026809692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7903213500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8425693511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9470615386963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8251523971558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8599843978882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7729072570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8773994445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6509981155396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5465049743652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3201026916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2156095504761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4071798324585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3026866912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3549327850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3897647857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1981935501099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9369602203369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0414543151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8847141265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8672981262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9717922210693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8324670791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6234798431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6060657501221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5886497497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5189876556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4493255615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6583118438721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7802209854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1633615493774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1111164093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0588684082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9892072677612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8498830795288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0240383148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0066232681274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7976360321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8150510787964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9543752670288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0937013626099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7032432556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9818925857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9296455383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9122304916382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8077373504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2605419158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0863876342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9644775390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.529088973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4942579269409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5813360214233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.476842880249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6858291625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1908798217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3476190567017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5116729736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5987501144409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7105579376221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7004566192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49147033691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03866767883301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98641872406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42912292480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18530559539795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22884368896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45524597167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53361511230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49007701873779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31592178344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32462882995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16788959503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38558387756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28979873657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41170692443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49878597259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63810920715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69035530090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67294025421143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79484939575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96900463104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75130939483643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70777130126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83838748931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1866979598999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05608177185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14315986633301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23023796081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40439414978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66562652587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57854843139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31731510162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88192653656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6555233001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51620101928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60327816009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56844615936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36085414886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83978176116943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0139379501343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1010131835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92685985565186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88332176208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0574750900269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97039794921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7091646194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75270462036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6220874786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53501033782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79624271392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1880912780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2751703262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5364027023315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9282531738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0153293609619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7540979385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4928646087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4057865142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.362247467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3187084197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1894865036011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2765636444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4507188796997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0167245864868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.060263633728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5011930465698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0100755691528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.831485748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6975450515747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4743099212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2064266204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4296617507935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.608250617981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2510747909546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5813665390015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5367202758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0278387069702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8938961029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1617794036865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0724849700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9207811355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1886625289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2333097457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3226051330566</t>
   </si>
   <si>
     <t xml:space="preserve">12.2779579162598</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3127880096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2953729629517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3302030563354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1212177276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5217742919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4869432449341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4521131515503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1386337280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0515556335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8948154449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2082958221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8178396224976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7655925750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.643684387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.399866104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6262683868408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5391912460327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8700866699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9745779037476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.95716381073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9397468566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7830085754395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.695930480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8004245758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8875017166138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1560487747192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.034140586853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7206592559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2431259155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7554903030396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6684122085571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9993085861206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0689706802368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1038017272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.790322303772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.842568397522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9470634460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8251523971558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8599843978882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7729063034058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8774003982544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6509971618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5465049743652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3201017379761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2156095504761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4071807861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3026866912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3549337387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3897647857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1981935501099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9369611740112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0414543151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8847141265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8672981262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9717922210693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8324661254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.623480796814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6060657501221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5886497497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5189876556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4493246078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6583108901978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7802209854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1633615493774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1111154556274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0588684082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9892063140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8498821258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0240383148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0066223144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7976369857788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8150520324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9543752670288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0937004089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7032442092896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9818925857544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9296455383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9122304916382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8077383041382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2605409622192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.086386680603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9644775390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.529088973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4942579269409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.581335067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4768438339233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6858291625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1908798217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3476190567017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5116729736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5987510681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7105579376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7004566192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49147033691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03866577148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98641872406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42912292480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18530464172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22884273529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45524597167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53361511230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49007606506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31592178344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32462882995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16788959503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38558387756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28979873657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41170692443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49878597259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.638108253479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69035625457764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67294120788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79484844207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96900367736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75130939483643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70777130126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83838748931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18669891357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05608081817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14315891265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23023700714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40439319610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66562652587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57854843139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31731510162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88192558288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65552425384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51620006561279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60327816009521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56844711303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36085319519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83978176116943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0139379501343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1010150909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92685890197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88332080841064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0574769973755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97039794921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7091646194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75270462036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62208652496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53500938415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79624271392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1880912780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2751703262329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5364036560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9282522201538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0153293609619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7540979385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4928646087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4057865142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.362247467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3187093734741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1894855499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2765626907349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4507188796997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0167236328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.060263633728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5011930465698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0100746154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.831485748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6975450515747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4743089675903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2064266204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4296627044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.608250617981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2510747909546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5813674926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5367202758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0278387069702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8938961029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1617803573608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0724849700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9207811355591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1886625289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2333087921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3226041793823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2779569625854</t>
-  </si>
-  <si>
     <t xml:space="preserve">11.8761339187622</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1440162658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7868385314941</t>
+    <t xml:space="preserve">12.1440172195435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7868394851685</t>
   </si>
   <si>
     <t xml:space="preserve">12.0993690490723</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4387826919556</t>
+    <t xml:space="preserve">13.4387817382812</t>
   </si>
   <si>
     <t xml:space="preserve">13.4834308624268</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9299001693726</t>
+    <t xml:space="preserve">13.9299011230469</t>
   </si>
   <si>
     <t xml:space="preserve">13.8406057357788</t>
@@ -2246,10 +2246,10 @@
     <t xml:space="preserve">12.9030170440674</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0816049575806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0369596481323</t>
+    <t xml:space="preserve">13.0816059112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.036958694458</t>
   </si>
   <si>
     <t xml:space="preserve">13.7513122558594</t>
@@ -2261,10 +2261,10 @@
     <t xml:space="preserve">13.3941354751587</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9745473861694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2601957321167</t>
+    <t xml:space="preserve">13.9745464324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2601938247681</t>
   </si>
   <si>
     <t xml:space="preserve">13.6620178222656</t>
@@ -2285,7 +2285,7 @@
     <t xml:space="preserve">14.9121379852295</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0907258987427</t>
+    <t xml:space="preserve">15.090726852417</t>
   </si>
   <si>
     <t xml:space="preserve">14.7335481643677</t>
@@ -2297,10 +2297,10 @@
     <t xml:space="preserve">14.5103130340576</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1800193786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8497276306152</t>
+    <t xml:space="preserve">15.1800203323364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8497285842896</t>
   </si>
   <si>
     <t xml:space="preserve">15.8050813674927</t>
@@ -2315,46 +2315,46 @@
     <t xml:space="preserve">16.9212589263916</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1891422271729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7426700592041</t>
+    <t xml:space="preserve">17.1891403198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7426681518555</t>
   </si>
   <si>
     <t xml:space="preserve">17.7249069213867</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7695541381836</t>
+    <t xml:space="preserve">17.769552230835</t>
   </si>
   <si>
     <t xml:space="preserve">17.8142013549805</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8588466644287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0374355316162</t>
+    <t xml:space="preserve">17.8588485717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0374374389648</t>
   </si>
   <si>
     <t xml:space="preserve">18.12672996521</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3946113586426</t>
+    <t xml:space="preserve">18.3946132659912</t>
   </si>
   <si>
     <t xml:space="preserve">18.5732002258301</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6980228424072</t>
+    <t xml:space="preserve">16.6980209350586</t>
   </si>
   <si>
     <t xml:space="preserve">18.3053188323975</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5909652709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2160224914551</t>
+    <t xml:space="preserve">17.5909671783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2160243988037</t>
   </si>
   <si>
     <t xml:space="preserve">17.9481410980225</t>
@@ -2369,10 +2369,10 @@
     <t xml:space="preserve">20.5376758575439</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6269702911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9841461181641</t>
+    <t xml:space="preserve">20.6269683837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9841442108154</t>
   </si>
   <si>
     <t xml:space="preserve">20.8055572509766</t>
@@ -2390,25 +2390,25 @@
     <t xml:space="preserve">19.8233222961426</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2697925567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1982593536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9126129150391</t>
+    <t xml:space="preserve">20.2697944641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1982612609863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9126148223877</t>
   </si>
   <si>
     <t xml:space="preserve">19.5554389953613</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6447334289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9303760528564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7162628173828</t>
+    <t xml:space="preserve">19.6447315216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9303798675537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7162609100342</t>
   </si>
   <si>
     <t xml:space="preserve">20.4483795166016</t>
@@ -2417,10 +2417,10 @@
     <t xml:space="preserve">21.4306163787842</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3413238525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3235607147217</t>
+    <t xml:space="preserve">21.3413219451904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.323558807373</t>
   </si>
   <si>
     <t xml:space="preserve">21.6092052459717</t>
@@ -70175,6 +70175,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2540">
+      <c r="A2540" s="1" t="n">
+        <v>46020.6913194444</v>
+      </c>
+      <c r="B2540" t="n">
+        <v>2281</v>
+      </c>
+      <c r="C2540" t="n">
+        <v>13.9499998092651</v>
+      </c>
+      <c r="D2540" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="E2540" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="F2540" t="n">
+        <v>13.8999996185303</v>
+      </c>
+      <c r="G2540" t="s">
+        <v>1266</v>
+      </c>
+      <c r="H2540" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SAB.MI.xlsx
+++ b/data/SAB.MI.xlsx
@@ -47,13 +47,13 @@
     <t xml:space="preserve">8.61823177337646</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48310089111328</t>
+    <t xml:space="preserve">8.4831018447876</t>
   </si>
   <si>
     <t xml:space="preserve">8.33295917510986</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37049388885498</t>
+    <t xml:space="preserve">8.37049293518066</t>
   </si>
   <si>
     <t xml:space="preserve">8.31794452667236</t>
@@ -65,25 +65,25 @@
     <t xml:space="preserve">8.16029357910156</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88252830505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52969121932983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6648211479187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62728452682495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61226892471313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73989200592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75490570068359</t>
+    <t xml:space="preserve">7.88252782821655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52969169616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66482019424438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62728404998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61227083206177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73989343643188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75490713119507</t>
   </si>
   <si>
     <t xml:space="preserve">7.76992130279541</t>
@@ -92,100 +92,100 @@
     <t xml:space="preserve">7.89754343032837</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61977577209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79995012283325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72487735748291</t>
+    <t xml:space="preserve">7.61977815628052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79994964599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72487640380859</t>
   </si>
   <si>
     <t xml:space="preserve">7.65731334686279</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5071702003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34201192855835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54470586776733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39080810546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58224201202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82247114181519</t>
+    <t xml:space="preserve">7.50716972351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34201145172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54470539093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39080905914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58224105834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82247066497803</t>
   </si>
   <si>
     <t xml:space="preserve">8.0852222442627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11525058746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95759868621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06270027160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03267002105713</t>
+    <t xml:space="preserve">8.11524963378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95760059356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06269931793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03267288208008</t>
   </si>
   <si>
     <t xml:space="preserve">7.92006492614746</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77742910385132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86751317977905</t>
+    <t xml:space="preserve">7.777428150177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86751365661621</t>
   </si>
   <si>
     <t xml:space="preserve">7.80745649337769</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98762989044189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04017734527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99513530731201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96510744094849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90504884719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93507814407349</t>
+    <t xml:space="preserve">7.98762893676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0401782989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99513483047485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96510696411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9050498008728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93507766723633</t>
   </si>
   <si>
     <t xml:space="preserve">7.89003467559814</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94258642196655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82997846603394</t>
+    <t xml:space="preserve">7.94258499145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82997751235962</t>
   </si>
   <si>
     <t xml:space="preserve">7.81496334075928</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73238325119019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64980554580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71737051010132</t>
+    <t xml:space="preserve">7.73238515853882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64980602264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71736907958984</t>
   </si>
   <si>
     <t xml:space="preserve">7.67232894897461</t>
@@ -194,28 +194,28 @@
     <t xml:space="preserve">7.6347918510437</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51467800140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64229965209961</t>
+    <t xml:space="preserve">7.51467609405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64229917526245</t>
   </si>
   <si>
     <t xml:space="preserve">7.56722688674927</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70235633850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.747398853302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46963357925415</t>
+    <t xml:space="preserve">7.70235729217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74739933013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46963262557983</t>
   </si>
   <si>
     <t xml:space="preserve">7.69484901428223</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49215602874756</t>
+    <t xml:space="preserve">7.4921555519104</t>
   </si>
   <si>
     <t xml:space="preserve">7.47338819503784</t>
@@ -224,118 +224,118 @@
     <t xml:space="preserve">7.43585157394409</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50341701507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48089456558228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59725618362427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42834424972534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38705492019653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37204122543335</t>
+    <t xml:space="preserve">7.50341606140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48089504241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59725475311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4283447265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38705444335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37204027175903</t>
   </si>
   <si>
     <t xml:space="preserve">7.31949138641357</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28195524215698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52122068405151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80533981323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75009489059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75798606872559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81323003768921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86058521270752</t>
+    <t xml:space="preserve">7.28195428848267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52122163772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80534029006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75009393692017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75798654556274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81323099136353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8605842590332</t>
   </si>
   <si>
     <t xml:space="preserve">7.69879484176636</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58435821533203</t>
+    <t xml:space="preserve">7.58435964584351</t>
   </si>
   <si>
     <t xml:space="preserve">7.68695640563965</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57646703720093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53700685501099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49754476547241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28445720672607</t>
+    <t xml:space="preserve">7.57646751403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53700542449951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49754524230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28445672988892</t>
   </si>
   <si>
     <t xml:space="preserve">6.92536354064941</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07926082611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22921180725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45808458328247</t>
+    <t xml:space="preserve">7.079261302948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22921228408813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45808506011963</t>
   </si>
   <si>
     <t xml:space="preserve">7.26078033447266</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37127017974854</t>
+    <t xml:space="preserve">7.37127161026001</t>
   </si>
   <si>
     <t xml:space="preserve">7.26472663879395</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34759473800659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46992254257202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3673243522644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37916374206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13450574874878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18975067138672</t>
+    <t xml:space="preserve">7.34759426116943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46992301940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36732530593872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37916278839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1345067024231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18975162506104</t>
   </si>
   <si>
     <t xml:space="preserve">7.10293769836426</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15029144287109</t>
+    <t xml:space="preserve">7.15029191970825</t>
   </si>
   <si>
     <t xml:space="preserve">7.10688447952271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20553541183472</t>
+    <t xml:space="preserve">7.20553493499756</t>
   </si>
   <si>
     <t xml:space="preserve">7.18185997009277</t>
@@ -344,94 +344,94 @@
     <t xml:space="preserve">7.22131967544556</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19369649887085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24894237518311</t>
+    <t xml:space="preserve">7.19369745254517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24894142150879</t>
   </si>
   <si>
     <t xml:space="preserve">7.19764375686646</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18580532073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22526597976685</t>
+    <t xml:space="preserve">7.18580484390259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22526502609253</t>
   </si>
   <si>
     <t xml:space="preserve">7.20948171615601</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31602573394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21342897415161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16607427597046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24499607086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13055944442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11083030700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17791366577148</t>
+    <t xml:space="preserve">7.3160252571106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21342849731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16607475280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24499702453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13056039810181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11082935333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17791318893433</t>
   </si>
   <si>
     <t xml:space="preserve">7.23315763473511</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27656412124634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30024147033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29234981536865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24104976654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11872243881226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09504556655884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00428628921509</t>
+    <t xml:space="preserve">7.27656602859497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30024099349976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29234886169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24105024337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11872148513794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09504508972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00428581237793</t>
   </si>
   <si>
     <t xml:space="preserve">6.9450945854187</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93325662612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09899139404297</t>
+    <t xml:space="preserve">6.93325567245483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09899091720581</t>
   </si>
   <si>
     <t xml:space="preserve">7.15423679351807</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13845157623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1581826210022</t>
+    <t xml:space="preserve">7.13845252990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15818214416504</t>
   </si>
   <si>
     <t xml:space="preserve">7.05558443069458</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07136917114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06742286682129</t>
+    <t xml:space="preserve">7.07136869430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06742238998413</t>
   </si>
   <si>
     <t xml:space="preserve">7.02401542663574</t>
@@ -440,61 +440,61 @@
     <t xml:space="preserve">7.04769277572632</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0634765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08320665359497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05163908004761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04374647140503</t>
+    <t xml:space="preserve">7.06347703933716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08320713043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05163860321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04374742507935</t>
   </si>
   <si>
     <t xml:space="preserve">7.03190803527832</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05953073501587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03585481643677</t>
+    <t xml:space="preserve">7.05953121185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03585433959961</t>
   </si>
   <si>
     <t xml:space="preserve">7.1739673614502</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90563344955444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91352558135986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9372034072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92141819000244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94114875793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9687705039978</t>
+    <t xml:space="preserve">6.9056339263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91352701187134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93720197677612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9214186668396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9411473274231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96877098083496</t>
   </si>
   <si>
     <t xml:space="preserve">7.14239931106567</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45019197463989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69484949111938</t>
+    <t xml:space="preserve">7.45019292831421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69484996795654</t>
   </si>
   <si>
     <t xml:space="preserve">7.79350090026855</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9237208366394</t>
+    <t xml:space="preserve">7.92372226715088</t>
   </si>
   <si>
     <t xml:space="preserve">8.0499963760376</t>
@@ -503,7 +503,7 @@
     <t xml:space="preserve">8.207839012146</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16837787628174</t>
+    <t xml:space="preserve">8.16837882995605</t>
   </si>
   <si>
     <t xml:space="preserve">8.08945655822754</t>
@@ -515,13 +515,13 @@
     <t xml:space="preserve">8.06578159332275</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12891674041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17627143859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32622051239014</t>
+    <t xml:space="preserve">8.1289176940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17627048492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32622241973877</t>
   </si>
   <si>
     <t xml:space="preserve">8.55509376525879</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">8.56298637390137</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42881965637207</t>
+    <t xml:space="preserve">8.42881870269775</t>
   </si>
   <si>
     <t xml:space="preserve">8.35778999328613</t>
@@ -539,10 +539,10 @@
     <t xml:space="preserve">8.39725112915039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42092800140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44460296630859</t>
+    <t xml:space="preserve">8.42092609405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44460487365723</t>
   </si>
   <si>
     <t xml:space="preserve">8.40514183044434</t>
@@ -551,7 +551,7 @@
     <t xml:space="preserve">8.26308536529541</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18416213989258</t>
+    <t xml:space="preserve">8.18416309356689</t>
   </si>
   <si>
     <t xml:space="preserve">8.30254554748535</t>
@@ -563,133 +563,133 @@
     <t xml:space="preserve">8.2867603302002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25519180297852</t>
+    <t xml:space="preserve">8.25519275665283</t>
   </si>
   <si>
     <t xml:space="preserve">8.34989738464355</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3104362487793</t>
+    <t xml:space="preserve">8.31043720245361</t>
   </si>
   <si>
     <t xml:space="preserve">8.36568260192871</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33411312103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34200572967529</t>
+    <t xml:space="preserve">8.33411407470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34200477600098</t>
   </si>
   <si>
     <t xml:space="preserve">8.46038818359375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62612342834473</t>
+    <t xml:space="preserve">8.62612438201904</t>
   </si>
   <si>
     <t xml:space="preserve">8.74450588226318</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88656330108643</t>
+    <t xml:space="preserve">8.88656425476074</t>
   </si>
   <si>
     <t xml:space="preserve">9.0049467086792</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23381900787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30484867095947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26538848876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16278839111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19435787200928</t>
+    <t xml:space="preserve">9.23381805419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30484771728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26538753509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16278743743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19435882568359</t>
   </si>
   <si>
     <t xml:space="preserve">9.24960327148438</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29695606231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36798572540283</t>
+    <t xml:space="preserve">9.29695510864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36798477172852</t>
   </si>
   <si>
     <t xml:space="preserve">9.54950523376465</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67578029632568</t>
+    <t xml:space="preserve">9.67577934265137</t>
   </si>
   <si>
     <t xml:space="preserve">9.74680995941162</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2203378677368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4807796478271</t>
+    <t xml:space="preserve">10.2203388214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4807786941528</t>
   </si>
   <si>
     <t xml:space="preserve">10.4571027755737</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2913665771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2597990036011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1493101119995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0861701965332</t>
+    <t xml:space="preserve">10.2913675308228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2597999572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1493082046509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0861711502075</t>
   </si>
   <si>
     <t xml:space="preserve">10.0151424407959</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1019554138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.165093421936</t>
+    <t xml:space="preserve">10.1019563674927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1650924682617</t>
   </si>
   <si>
     <t xml:space="preserve">10.0546026229858</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1808757781982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1177406311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1887702941895</t>
+    <t xml:space="preserve">10.1808767318726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1177396774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1887683868408</t>
   </si>
   <si>
     <t xml:space="preserve">10.0703868865967</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1098489761353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0230350494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.496563911438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4176406860352</t>
+    <t xml:space="preserve">10.1098470687866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0230331420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4965629577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4176416397095</t>
   </si>
   <si>
     <t xml:space="preserve">10.3150434494019</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7333269119263</t>
+    <t xml:space="preserve">10.7333288192749</t>
   </si>
   <si>
     <t xml:space="preserve">10.4492101669312</t>
@@ -698,61 +698,61 @@
     <t xml:space="preserve">10.5597019195557</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6386203765869</t>
+    <t xml:space="preserve">10.6386213302612</t>
   </si>
   <si>
     <t xml:space="preserve">10.591269493103</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0095529556274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.883279800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3410243988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0592088699341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9171524047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0513181686401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6882791519165</t>
+    <t xml:space="preserve">11.0095539093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8832778930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3410224914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0592098236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9171514511108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0513191223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6882801055908</t>
   </si>
   <si>
     <t xml:space="preserve">11.6803874969482</t>
   </si>
   <si>
-    <t xml:space="preserve">12.264404296875</t>
+    <t xml:space="preserve">12.2644052505493</t>
   </si>
   <si>
     <t xml:space="preserve">12.6274442672729</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5406312942505</t>
+    <t xml:space="preserve">12.5406303405762</t>
   </si>
   <si>
     <t xml:space="preserve">12.6747970581055</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7379341125488</t>
+    <t xml:space="preserve">12.7379350662231</t>
   </si>
   <si>
     <t xml:space="preserve">12.4728555679321</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6518526077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8471212387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8145761489868</t>
+    <t xml:space="preserve">12.6518535614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8471231460571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8145780563354</t>
   </si>
   <si>
     <t xml:space="preserve">12.9203491210938</t>
@@ -761,16 +761,16 @@
     <t xml:space="preserve">12.8715305328369</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9366207122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8064413070679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6437177658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.822714805603</t>
+    <t xml:space="preserve">12.9366216659546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8064422607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6437168121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8227138519287</t>
   </si>
   <si>
     <t xml:space="preserve">11.5209159851074</t>
@@ -779,31 +779,31 @@
     <t xml:space="preserve">11.8463649749756</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7812757492065</t>
+    <t xml:space="preserve">11.7812738418579</t>
   </si>
   <si>
     <t xml:space="preserve">11.9114561080933</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9277286529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9602727890015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8056840896606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1311340332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0009546279907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9846801757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0416345596313</t>
+    <t xml:space="preserve">11.9277267456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9602737426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.805685043335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1311330795288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0009536743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9846811294556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0416355133057</t>
   </si>
   <si>
     <t xml:space="preserve">12.0823163986206</t>
@@ -812,22 +812,22 @@
     <t xml:space="preserve">11.9765453338623</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8789110183716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7161846160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4720983505249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5534601211548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5860052108765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7975473403931</t>
+    <t xml:space="preserve">11.8789119720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7161855697632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4720993041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5534610748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5860061645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7975492477417</t>
   </si>
   <si>
     <t xml:space="preserve">11.8951835632324</t>
@@ -836,25 +836,25 @@
     <t xml:space="preserve">12.0904521942139</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1636791229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.074179649353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2287673950195</t>
+    <t xml:space="preserve">12.1636781692505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0741806030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2287683486938</t>
   </si>
   <si>
     <t xml:space="preserve">12.1392698287964</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2043590545654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1880855560303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1474075317383</t>
+    <t xml:space="preserve">12.2043600082397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1880874633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1474056243896</t>
   </si>
   <si>
     <t xml:space="preserve">12.2531766891479</t>
@@ -863,16 +863,16 @@
     <t xml:space="preserve">12.3670845031738</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4077653884888</t>
+    <t xml:space="preserve">12.4077663421631</t>
   </si>
   <si>
     <t xml:space="preserve">12.4484462738037</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9447574615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7820320129395</t>
+    <t xml:space="preserve">12.9447584152222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7820339202881</t>
   </si>
   <si>
     <t xml:space="preserve">12.8959398269653</t>
@@ -884,13 +884,13 @@
     <t xml:space="preserve">12.9528942108154</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8552598953247</t>
+    <t xml:space="preserve">12.855260848999</t>
   </si>
   <si>
     <t xml:space="preserve">12.7332153320312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7738962173462</t>
+    <t xml:space="preserve">12.7738971710205</t>
   </si>
   <si>
     <t xml:space="preserve">12.9854383468628</t>
@@ -899,34 +899,34 @@
     <t xml:space="preserve">13.2620706558228</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6851558685303</t>
+    <t xml:space="preserve">13.685154914856</t>
   </si>
   <si>
     <t xml:space="preserve">13.9292430877686</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9943332672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.750244140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8153352737427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8316097259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0187406539917</t>
+    <t xml:space="preserve">13.9943323135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7502450942993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.815336227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8316078186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0187425613403</t>
   </si>
   <si>
     <t xml:space="preserve">14.0268783569336</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1814661026001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1570568084717</t>
+    <t xml:space="preserve">14.1814680099487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.157057762146</t>
   </si>
   <si>
     <t xml:space="preserve">14.2302837371826</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">14.7754106521606</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3205413818359</t>
+    <t xml:space="preserve">15.3205404281616</t>
   </si>
   <si>
     <t xml:space="preserve">15.2961320877075</t>
@@ -944,46 +944,46 @@
     <t xml:space="preserve">15.4588556289673</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8249864578247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.792441368103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5076723098755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8493957519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.865668296814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5158100128174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0039863586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2643432617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.776927947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9559211730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4115524291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0454216003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0787239074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6475067138672</t>
+    <t xml:space="preserve">15.8249855041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7924423217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5076732635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8493938446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8656663894653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5158081054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0039844512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2643451690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7769260406494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.955924987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4115543365479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0454235076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0787258148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6475028991699</t>
   </si>
   <si>
     <t xml:space="preserve">18.0217723846436</t>
@@ -1001,64 +1001,64 @@
     <t xml:space="preserve">18.4123115539551</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1682224273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1600856781006</t>
+    <t xml:space="preserve">18.1682243347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1600875854492</t>
   </si>
   <si>
     <t xml:space="preserve">17.9160003662109</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2651023864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0861053466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2976474761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0047397613525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1267833709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8745613098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0779647827148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8664245605469</t>
+    <t xml:space="preserve">17.265100479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0861034393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2976455688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0047416687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1267871856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8745632171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0779685974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8664264678955</t>
   </si>
   <si>
     <t xml:space="preserve">16.785062789917</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9884662628174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5979309082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9152450561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8338794708252</t>
+    <t xml:space="preserve">16.9884700775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5979290008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9152431488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8338813781738</t>
   </si>
   <si>
     <t xml:space="preserve">16.9640617370605</t>
   </si>
   <si>
-    <t xml:space="preserve">16.882698059082</t>
+    <t xml:space="preserve">16.8826999664307</t>
   </si>
   <si>
     <t xml:space="preserve">16.9233779907227</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1349201202393</t>
+    <t xml:space="preserve">17.1349220275879</t>
   </si>
   <si>
     <t xml:space="preserve">17.0698299407959</t>
@@ -1070,79 +1070,79 @@
     <t xml:space="preserve">17.6637763977051</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2251758575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8598022460938</t>
+    <t xml:space="preserve">18.2251739501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8598041534424</t>
   </si>
   <si>
     <t xml:space="preserve">19.0632095336914</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7052154541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6319885253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7377605438232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7133502960205</t>
+    <t xml:space="preserve">18.7052173614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6319904327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7377624511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7133541107178</t>
   </si>
   <si>
     <t xml:space="preserve">18.59130859375</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3065376281738</t>
+    <t xml:space="preserve">18.3065395355225</t>
   </si>
   <si>
     <t xml:space="preserve">18.6157169342041</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2170391082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2089042663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4611301422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5417308807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9071083068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4758892059326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3945217132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1097564697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3619804382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2806167602539</t>
+    <t xml:space="preserve">18.217041015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2089023590088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4611282348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5417327880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9071063995361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4758834838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3945236206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1097526550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3619785308838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2806186676025</t>
   </si>
   <si>
     <t xml:space="preserve">16.3782501220703</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1992530822754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2236614227295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2724781036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.679292678833</t>
+    <t xml:space="preserve">16.199254989624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2236633300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2724800109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6792907714844</t>
   </si>
   <si>
     <t xml:space="preserve">16.313159942627</t>
@@ -1154,25 +1154,25 @@
     <t xml:space="preserve">15.9470310211182</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1911144256592</t>
+    <t xml:space="preserve">16.1911182403564</t>
   </si>
   <si>
     <t xml:space="preserve">16.3538436889648</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0283908843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9144859313965</t>
+    <t xml:space="preserve">16.028392791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9144849777222</t>
   </si>
   <si>
     <t xml:space="preserve">15.1822242736816</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9706811904907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1008586883545</t>
+    <t xml:space="preserve">14.9706802368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1008615493774</t>
   </si>
   <si>
     <t xml:space="preserve">14.8730478286743</t>
@@ -1181,22 +1181,22 @@
     <t xml:space="preserve">14.222146987915</t>
   </si>
   <si>
-    <t xml:space="preserve">13.847882270813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8893194198608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1984958648682</t>
+    <t xml:space="preserve">13.8478803634644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8893175125122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1984977722168</t>
   </si>
   <si>
     <t xml:space="preserve">15.3937654495239</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5402183532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9381370544434</t>
+    <t xml:space="preserve">15.5402202606201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9381351470947</t>
   </si>
   <si>
     <t xml:space="preserve">14.5964155197144</t>
@@ -1208,19 +1208,19 @@
     <t xml:space="preserve">14.2058753967285</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1082391738892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0594234466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9129705429077</t>
+    <t xml:space="preserve">14.1082410812378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0594215393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.912971496582</t>
   </si>
   <si>
     <t xml:space="preserve">14.0106048583984</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3197841644287</t>
+    <t xml:space="preserve">14.3197822570801</t>
   </si>
   <si>
     <t xml:space="preserve">14.6452312469482</t>
@@ -1232,61 +1232,61 @@
     <t xml:space="preserve">14.7265949249268</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2147693634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.807957649231</t>
+    <t xml:space="preserve">15.214771270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8079566955566</t>
   </si>
   <si>
     <t xml:space="preserve">14.8567743301392</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9544095993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7916841506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2709674835205</t>
+    <t xml:space="preserve">14.9544057846069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7916831970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2709646224976</t>
   </si>
   <si>
     <t xml:space="preserve">15.0032262802124</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4825057983398</t>
+    <t xml:space="preserve">14.4825067520142</t>
   </si>
   <si>
     <t xml:space="preserve">14.9218635559082</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9055910110474</t>
+    <t xml:space="preserve">14.9055919647217</t>
   </si>
   <si>
     <t xml:space="preserve">15.0194978713989</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0520448684692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2562046051025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7354888916016</t>
+    <t xml:space="preserve">15.0520439147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2562065124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7354879379272</t>
   </si>
   <si>
     <t xml:space="preserve">15.8168506622314</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6215829849243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9307565689087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6866731643677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7192163467407</t>
+    <t xml:space="preserve">15.6215810775757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9307584762573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6866722106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7192144393921</t>
   </si>
   <si>
     <t xml:space="preserve">15.7029418945312</t>
@@ -1295,76 +1295,76 @@
     <t xml:space="preserve">15.6703987121582</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6053094863892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5653514862061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9956817626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0291919708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0627021789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2470073699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2302522659302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5318422317505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7161483764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8669385910034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.582106590271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4983339309692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4815769195557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4145555496216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1799898147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.07945728302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1129674911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3589954376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2919750213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2584648132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4595241546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4092597961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5600528717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4039611816406</t>
+    <t xml:space="preserve">15.6053075790405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5653505325317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.995680809021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0291948318481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0627031326294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2470064163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2302532196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5318412780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7161474227905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8669395446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5821046829224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.498330116272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4815759658813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4145574569702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.179988861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0794582366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1129684448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3589935302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.291974067688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2584657669067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4595251083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4092617034912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5600547790527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4039630889893</t>
   </si>
   <si>
     <t xml:space="preserve">13.487738609314</t>
@@ -1376,7 +1376,7 @@
     <t xml:space="preserve">13.5380010604858</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4374732971191</t>
+    <t xml:space="preserve">13.4374723434448</t>
   </si>
   <si>
     <t xml:space="preserve">14.191445350647</t>
@@ -1400,7 +1400,7 @@
     <t xml:space="preserve">13.3201866149902</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1526393890381</t>
+    <t xml:space="preserve">13.1526374816895</t>
   </si>
   <si>
     <t xml:space="preserve">13.1861476898193</t>
@@ -1412,61 +1412,61 @@
     <t xml:space="preserve">13.3034324645996</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8510484695435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6834983825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5662136077881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9013137817383</t>
+    <t xml:space="preserve">12.8510494232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6834993362427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5662155151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.901312828064</t>
   </si>
   <si>
     <t xml:space="preserve">12.8342933654785</t>
   </si>
   <si>
-    <t xml:space="preserve">12.482439994812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1473407745361</t>
+    <t xml:space="preserve">12.4824390411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1473398208618</t>
   </si>
   <si>
     <t xml:space="preserve">12.0803213119507</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0635652542114</t>
+    <t xml:space="preserve">12.0635671615601</t>
   </si>
   <si>
     <t xml:space="preserve">11.9797916412354</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5609178543091</t>
+    <t xml:space="preserve">11.5609169006348</t>
   </si>
   <si>
     <t xml:space="preserve">11.1923084259033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2258167266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4321737289429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1191282272339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2531661987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2866764068604</t>
+    <t xml:space="preserve">11.2258176803589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4321746826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1191272735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2531681060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.286678314209</t>
   </si>
   <si>
     <t xml:space="preserve">12.7672748565674</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3536958694458</t>
+    <t xml:space="preserve">13.3536968231201</t>
   </si>
   <si>
     <t xml:space="preserve">12.9850883483887</t>
@@ -1475,10 +1475,10 @@
     <t xml:space="preserve">12.8007831573486</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6332349777222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8678045272827</t>
+    <t xml:space="preserve">12.6332340240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8678035736084</t>
   </si>
   <si>
     <t xml:space="preserve">11.8122425079346</t>
@@ -1487,16 +1487,16 @@
     <t xml:space="preserve">11.6279373168945</t>
   </si>
   <si>
-    <t xml:space="preserve">11.611180305481</t>
+    <t xml:space="preserve">11.6111822128296</t>
   </si>
   <si>
     <t xml:space="preserve">11.7284669876099</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9630365371704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8960151672363</t>
+    <t xml:space="preserve">11.9630355834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.896017074585</t>
   </si>
   <si>
     <t xml:space="preserve">11.6614475250244</t>
@@ -1505,25 +1505,25 @@
     <t xml:space="preserve">11.075023651123</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0415134429932</t>
+    <t xml:space="preserve">11.0415143966675</t>
   </si>
   <si>
     <t xml:space="preserve">10.9577388763428</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7566785812378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9242296218872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9744939804077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7117118835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3651561737061</t>
+    <t xml:space="preserve">10.7566804885864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9242286682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.974494934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7117109298706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3651552200317</t>
   </si>
   <si>
     <t xml:space="preserve">11.4603881835938</t>
@@ -1535,19 +1535,19 @@
     <t xml:space="preserve">11.1252889633179</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1755542755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3766136169434</t>
+    <t xml:space="preserve">11.1755533218384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.376612663269</t>
   </si>
   <si>
     <t xml:space="preserve">12.2311162948608</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3986644744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9295263290405</t>
+    <t xml:space="preserve">12.398663520813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9295272827148</t>
   </si>
   <si>
     <t xml:space="preserve">11.7954874038696</t>
@@ -1556,19 +1556,19 @@
     <t xml:space="preserve">11.87926197052</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1976070404053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2478713989258</t>
+    <t xml:space="preserve">12.197606086731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2478704452515</t>
   </si>
   <si>
     <t xml:space="preserve">12.0133008956909</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1305856704712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1808490753174</t>
+    <t xml:space="preserve">12.1305847167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.180850982666</t>
   </si>
   <si>
     <t xml:space="preserve">12.3819103240967</t>
@@ -1577,100 +1577,100 @@
     <t xml:space="preserve">12.3316459655762</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4656839370728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5997257232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7170085906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8845596313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9515781402588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9683322906494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2029037475586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7337646484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8175382614136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6499900817871</t>
+    <t xml:space="preserve">12.4656848907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5997247695923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7170095443726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8845586776733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9515790939331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9683332443237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2029027938843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7337636947632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8175401687622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6499910354614</t>
   </si>
   <si>
     <t xml:space="preserve">12.7002544403076</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5159492492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.784029006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0018424987793</t>
+    <t xml:space="preserve">12.5159482955933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7840280532837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0018434524536</t>
   </si>
   <si>
     <t xml:space="preserve">13.0353536605835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5494585037231</t>
+    <t xml:space="preserve">12.5494594573975</t>
   </si>
   <si>
     <t xml:space="preserve">12.9348230361938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9180679321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3872060775757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6217775344849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8228359222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5044937133789</t>
+    <t xml:space="preserve">12.9180688858032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.38720703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6217765808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8228349685669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5044927597046</t>
   </si>
   <si>
     <t xml:space="preserve">13.4542264938354</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6385316848755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7223062515259</t>
+    <t xml:space="preserve">13.6385326385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7223052978516</t>
   </si>
   <si>
     <t xml:space="preserve">13.3704528808594</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0521087646484</t>
+    <t xml:space="preserve">13.0521078109741</t>
   </si>
   <si>
     <t xml:space="preserve">13.0185985565186</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1693935394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1023731231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4991941452026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.748176574707</t>
+    <t xml:space="preserve">13.1693925857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1023740768433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.499195098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7481775283813</t>
   </si>
   <si>
     <t xml:space="preserve">12.5740203857422</t>
@@ -1679,13 +1679,13 @@
     <t xml:space="preserve">12.3650341033936</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2257108688354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2779569625854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3127889633179</t>
+    <t xml:space="preserve">12.2257099151611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2779579162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3127880096436</t>
   </si>
   <si>
     <t xml:space="preserve">12.2953729629517</t>
@@ -1697,22 +1697,22 @@
     <t xml:space="preserve">12.1212177276611</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5217752456665</t>
+    <t xml:space="preserve">12.5217733383179</t>
   </si>
   <si>
     <t xml:space="preserve">12.4869432449341</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4521141052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.138632774353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0515546798706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8948163986206</t>
+    <t xml:space="preserve">12.4521131515503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1386318206787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0515556335449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8948154449463</t>
   </si>
   <si>
     <t xml:space="preserve">12.2082958221436</t>
@@ -1727,19 +1727,19 @@
     <t xml:space="preserve">12.643684387207</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3998670578003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6262683868408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5391902923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8700866699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9745788574219</t>
+    <t xml:space="preserve">12.399866104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6262674331665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5391912460327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8700857162476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9745779037476</t>
   </si>
   <si>
     <t xml:space="preserve">12.95716381073</t>
@@ -1748,25 +1748,25 @@
     <t xml:space="preserve">12.9397478103638</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7830076217651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6959295272827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8004217147827</t>
+    <t xml:space="preserve">12.7830085754395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.695930480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.800422668457</t>
   </si>
   <si>
     <t xml:space="preserve">12.8875007629395</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1560478210449</t>
+    <t xml:space="preserve">12.1560497283936</t>
   </si>
   <si>
     <t xml:space="preserve">12.0341396331787</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7206592559814</t>
+    <t xml:space="preserve">11.7206602096558</t>
   </si>
   <si>
     <t xml:space="preserve">12.2431268692017</t>
@@ -1781,7 +1781,7 @@
     <t xml:space="preserve">11.9993085861206</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0689697265625</t>
+    <t xml:space="preserve">12.0689706802368</t>
   </si>
   <si>
     <t xml:space="preserve">12.1038017272949</t>
@@ -1790,16 +1790,16 @@
     <t xml:space="preserve">11.790322303772</t>
   </si>
   <si>
-    <t xml:space="preserve">11.842568397522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9470624923706</t>
+    <t xml:space="preserve">11.8425693511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9470615386963</t>
   </si>
   <si>
     <t xml:space="preserve">11.8251523971558</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8599843978882</t>
+    <t xml:space="preserve">11.8599834442139</t>
   </si>
   <si>
     <t xml:space="preserve">11.7729063034058</t>
@@ -1808,19 +1808,19 @@
     <t xml:space="preserve">11.8774003982544</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6509981155396</t>
+    <t xml:space="preserve">11.6509971618652</t>
   </si>
   <si>
     <t xml:space="preserve">11.5465049743652</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3201017379761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2156085968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4071788787842</t>
+    <t xml:space="preserve">11.3201026916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2156095504761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4071807861328</t>
   </si>
   <si>
     <t xml:space="preserve">11.3026857376099</t>
@@ -1829,10 +1829,10 @@
     <t xml:space="preserve">11.3549327850342</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3897638320923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1981925964355</t>
+    <t xml:space="preserve">11.3897647857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1981935501099</t>
   </si>
   <si>
     <t xml:space="preserve">10.9369611740112</t>
@@ -1841,10 +1841,10 @@
     <t xml:space="preserve">11.0414543151855</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8847131729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8672971725464</t>
+    <t xml:space="preserve">10.8847150802612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8672981262207</t>
   </si>
   <si>
     <t xml:space="preserve">10.9717922210693</t>
@@ -1853,7 +1853,7 @@
     <t xml:space="preserve">10.8324670791626</t>
   </si>
   <si>
-    <t xml:space="preserve">10.623480796814</t>
+    <t xml:space="preserve">10.6234798431396</t>
   </si>
   <si>
     <t xml:space="preserve">10.6060657501221</t>
@@ -1865,31 +1865,31 @@
     <t xml:space="preserve">10.5189876556396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4493255615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6583108901978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7802200317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1633634567261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1111164093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0588703155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9892063140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8498830795288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0240383148193</t>
+    <t xml:space="preserve">10.4493246078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6583118438721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7802209854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1633615493774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1111154556274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0588684082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9892072677612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8498821258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.024037361145</t>
   </si>
   <si>
     <t xml:space="preserve">11.0066232681274</t>
@@ -1901,31 +1901,31 @@
     <t xml:space="preserve">10.8150520324707</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9543771743774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0936994552612</t>
+    <t xml:space="preserve">10.9543752670288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0937013626099</t>
   </si>
   <si>
     <t xml:space="preserve">11.7032442092896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.981894493103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9296464920044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9122314453125</t>
+    <t xml:space="preserve">11.9818935394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9296455383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9122304916382</t>
   </si>
   <si>
     <t xml:space="preserve">11.8077383041382</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2605409622192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0863876342773</t>
+    <t xml:space="preserve">12.2605419158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0863857269287</t>
   </si>
   <si>
     <t xml:space="preserve">11.9644775390625</t>
@@ -1940,7 +1940,7 @@
     <t xml:space="preserve">11.5813360214233</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4768438339233</t>
+    <t xml:space="preserve">11.476842880249</t>
   </si>
   <si>
     <t xml:space="preserve">11.6858291625977</t>
@@ -1958,16 +1958,16 @@
     <t xml:space="preserve">11.5987510681152</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7105588912964</t>
+    <t xml:space="preserve">10.7105579376221</t>
   </si>
   <si>
     <t xml:space="preserve">9.7004566192627</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49147033691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03866577148438</t>
+    <t xml:space="preserve">9.49146938323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03866672515869</t>
   </si>
   <si>
     <t xml:space="preserve">8.98641967773438</t>
@@ -1976,37 +1976,37 @@
     <t xml:space="preserve">8.42912197113037</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18530464172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22884273529053</t>
+    <t xml:space="preserve">8.18530559539795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22884368896484</t>
   </si>
   <si>
     <t xml:space="preserve">8.45524501800537</t>
   </si>
   <si>
-    <t xml:space="preserve">8.533616065979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49007797241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31592082977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32462978363037</t>
+    <t xml:space="preserve">8.53361511230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49007701873779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31592178344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32462882995605</t>
   </si>
   <si>
     <t xml:space="preserve">8.16788959503174</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38558483123779</t>
+    <t xml:space="preserve">8.38558387756348</t>
   </si>
   <si>
     <t xml:space="preserve">8.28979778289795</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41170597076416</t>
+    <t xml:space="preserve">8.41170692443848</t>
   </si>
   <si>
     <t xml:space="preserve">8.4987850189209</t>
@@ -2015,19 +2015,19 @@
     <t xml:space="preserve">8.63810920715332</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69035625457764</t>
+    <t xml:space="preserve">8.69035530090332</t>
   </si>
   <si>
     <t xml:space="preserve">8.67294025421143</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79485034942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96900367736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75131034851074</t>
+    <t xml:space="preserve">8.79484939575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96900463104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75130939483643</t>
   </si>
   <si>
     <t xml:space="preserve">8.70777130126953</t>
@@ -2036,13 +2036,13 @@
     <t xml:space="preserve">8.83838748931885</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1866979598999</t>
+    <t xml:space="preserve">9.18669891357422</t>
   </si>
   <si>
     <t xml:space="preserve">9.05608177185059</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14315891265869</t>
+    <t xml:space="preserve">9.14315986633301</t>
   </si>
   <si>
     <t xml:space="preserve">9.23023796081543</t>
@@ -2051,7 +2051,7 @@
     <t xml:space="preserve">9.40439224243164</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66562747955322</t>
+    <t xml:space="preserve">9.66562652587891</t>
   </si>
   <si>
     <t xml:space="preserve">9.57854843139648</t>
@@ -2060,7 +2060,7 @@
     <t xml:space="preserve">9.31731510162354</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88192653656006</t>
+    <t xml:space="preserve">8.88192558288574</t>
   </si>
   <si>
     <t xml:space="preserve">8.65552425384521</t>
@@ -2069,58 +2069,58 @@
     <t xml:space="preserve">8.51620006561279</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60327911376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56844711303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36085414886475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83978176116943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0139360427856</t>
+    <t xml:space="preserve">8.60327816009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56844615936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36085319519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83978080749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.01393699646</t>
   </si>
   <si>
     <t xml:space="preserve">10.1010150909424</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92685794830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88332176208496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0574760437012</t>
+    <t xml:space="preserve">9.92685890197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88332080841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0574769973755</t>
   </si>
   <si>
     <t xml:space="preserve">9.97039794921875</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70916366577148</t>
+    <t xml:space="preserve">9.7091646194458</t>
   </si>
   <si>
     <t xml:space="preserve">9.75270366668701</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62208652496338</t>
+    <t xml:space="preserve">9.6220874786377</t>
   </si>
   <si>
     <t xml:space="preserve">9.53500938415527</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79624176025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1880931854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2751703262329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5364027023315</t>
+    <t xml:space="preserve">9.79624271392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1880903244019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2751693725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5364036560059</t>
   </si>
   <si>
     <t xml:space="preserve">10.9282531738281</t>
@@ -2138,7 +2138,7 @@
     <t xml:space="preserve">10.4057865142822</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3622465133667</t>
+    <t xml:space="preserve">10.362247467041</t>
   </si>
   <si>
     <t xml:space="preserve">10.3187084197998</t>
@@ -2147,31 +2147,31 @@
     <t xml:space="preserve">11.1894855499268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2765645980835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4507188796997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0167245864868</t>
+    <t xml:space="preserve">11.2765626907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.450719833374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0167236328125</t>
   </si>
   <si>
     <t xml:space="preserve">12.0602626800537</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5011930465698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0100746154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.831485748291</t>
+    <t xml:space="preserve">12.5011940002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0100755691528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8314867019653</t>
   </si>
   <si>
     <t xml:space="preserve">11.6975450515747</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4743099212646</t>
+    <t xml:space="preserve">11.4743089675903</t>
   </si>
   <si>
     <t xml:space="preserve">11.2064266204834</t>
@@ -2180,31 +2180,31 @@
     <t xml:space="preserve">11.4296627044678</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6082496643066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2510738372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5813674926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5367212295532</t>
+    <t xml:space="preserve">11.608250617981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2510747909546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5813665390015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5367202758789</t>
   </si>
   <si>
     <t xml:space="preserve">11.0278387069702</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8938970565796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1617784500122</t>
+    <t xml:space="preserve">10.8938961029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1617803573608</t>
   </si>
   <si>
     <t xml:space="preserve">11.0724849700928</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9207801818848</t>
+    <t xml:space="preserve">11.9207811355591</t>
   </si>
   <si>
     <t xml:space="preserve">12.1886625289917</t>
@@ -2213,7 +2213,7 @@
     <t xml:space="preserve">12.2333097457886</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3226051330566</t>
+    <t xml:space="preserve">12.3226041793823</t>
   </si>
   <si>
     <t xml:space="preserve">11.8761339187622</t>
@@ -2225,28 +2225,28 @@
     <t xml:space="preserve">11.7868385314941</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0993700027466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4387826919556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4834308624268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9299020767212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8406066894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0191946029663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9030160903931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0816049575806</t>
+    <t xml:space="preserve">12.0993690490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4387836456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4834299087524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9299001693726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8406057357788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0191955566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9030170440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0816040039062</t>
   </si>
   <si>
     <t xml:space="preserve">13.036958694458</t>
@@ -2261,34 +2261,34 @@
     <t xml:space="preserve">13.3941354751587</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9745473861694</t>
+    <t xml:space="preserve">13.9745464324951</t>
   </si>
   <si>
     <t xml:space="preserve">13.2601947784424</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6620178222656</t>
+    <t xml:space="preserve">13.6620187759399</t>
   </si>
   <si>
     <t xml:space="preserve">13.6173715591431</t>
   </si>
   <si>
-    <t xml:space="preserve">13.88525390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6442537307739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7781963348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9121370315552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0907249450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.733549118042</t>
+    <t xml:space="preserve">13.8852548599243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6442546844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7781953811646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9121379852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.090726852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7335481643677</t>
   </si>
   <si>
     <t xml:space="preserve">14.4210186004639</t>
@@ -2297,19 +2297,19 @@
     <t xml:space="preserve">14.5103130340576</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1800212860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8497257232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.805079460144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0729637145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3854942321777</t>
+    <t xml:space="preserve">15.1800193786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8497285842896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8050813674927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.072961807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3854923248291</t>
   </si>
   <si>
     <t xml:space="preserve">16.9212589263916</t>
@@ -2321,10 +2321,10 @@
     <t xml:space="preserve">16.7426681518555</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7249069213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.769552230835</t>
+    <t xml:space="preserve">17.7249050140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7695541381836</t>
   </si>
   <si>
     <t xml:space="preserve">17.8142013549805</t>
@@ -2333,7 +2333,7 @@
     <t xml:space="preserve">17.8588466644287</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0374374389648</t>
+    <t xml:space="preserve">18.0374355316162</t>
   </si>
   <si>
     <t xml:space="preserve">18.12672996521</t>
@@ -2345,19 +2345,19 @@
     <t xml:space="preserve">18.5732002258301</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6980247497559</t>
+    <t xml:space="preserve">16.6980228424072</t>
   </si>
   <si>
     <t xml:space="preserve">18.3053188323975</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5909671783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2160243988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9481410980225</t>
+    <t xml:space="preserve">17.5909633636475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2160224914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9481430053711</t>
   </si>
   <si>
     <t xml:space="preserve">19.0196723937988</t>
@@ -2366,34 +2366,34 @@
     <t xml:space="preserve">20.1804981231689</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5376739501953</t>
+    <t xml:space="preserve">20.5376758575439</t>
   </si>
   <si>
     <t xml:space="preserve">20.6269702911377</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9841442108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8055553436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0734424591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0912017822266</t>
+    <t xml:space="preserve">20.9841461181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8055572509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0734405517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0912036895752</t>
   </si>
   <si>
     <t xml:space="preserve">20.0019092559814</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8233222961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2697925567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1982593536377</t>
+    <t xml:space="preserve">19.8233203887939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2697906494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1982612609863</t>
   </si>
   <si>
     <t xml:space="preserve">19.9126129150391</t>
@@ -2402,25 +2402,25 @@
     <t xml:space="preserve">19.5554370880127</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6447315216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9303798675537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7162628173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4483795166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4306144714355</t>
+    <t xml:space="preserve">19.6447334289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9303779602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7162609100342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4483776092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4306163787842</t>
   </si>
   <si>
     <t xml:space="preserve">21.3413219451904</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3235569000244</t>
+    <t xml:space="preserve">22.3235607147217</t>
   </si>
   <si>
     <t xml:space="preserve">21.6092052459717</t>
@@ -2429,13 +2429,13 @@
     <t xml:space="preserve">22.0556774139404</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7877941131592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7700290679932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9147033691406</t>
+    <t xml:space="preserve">21.7877922058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7700309753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.914701461792</t>
   </si>
   <si>
     <t xml:space="preserve">24.4583892822266</t>
@@ -2444,22 +2444,22 @@
     <t xml:space="preserve">24.0020771026611</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8195533752441</t>
+    <t xml:space="preserve">23.8195514678955</t>
   </si>
   <si>
     <t xml:space="preserve">24.5496520996094</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4622783660889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8234405517578</t>
+    <t xml:space="preserve">25.4622764587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8234424591064</t>
   </si>
   <si>
     <t xml:space="preserve">24.0933380126953</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7321796417236</t>
+    <t xml:space="preserve">24.732177734375</t>
   </si>
   <si>
     <t xml:space="preserve">24.3671283721924</t>
@@ -2468,7 +2468,7 @@
     <t xml:space="preserve">23.9108142852783</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2719745635986</t>
+    <t xml:space="preserve">23.2719764709473</t>
   </si>
   <si>
     <t xml:space="preserve">23.6370258331299</t>
@@ -2480,10 +2480,10 @@
     <t xml:space="preserve">24.2758655548096</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7282867431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1846008300781</t>
+    <t xml:space="preserve">23.7282886505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1846027374268</t>
   </si>
   <si>
     <t xml:space="preserve">25.0059642791748</t>
@@ -2492,16 +2492,16 @@
     <t xml:space="preserve">22.3593482971191</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8156604766846</t>
+    <t xml:space="preserve">22.8156623840332</t>
   </si>
   <si>
     <t xml:space="preserve">22.2680854797363</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7243995666504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4545021057129</t>
+    <t xml:space="preserve">22.7243976593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4545001983643</t>
   </si>
   <si>
     <t xml:space="preserve">23.0894508361816</t>
@@ -2510,16 +2510,16 @@
     <t xml:space="preserve">23.1807117462158</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9069271087646</t>
+    <t xml:space="preserve">22.906925201416</t>
   </si>
   <si>
     <t xml:space="preserve">22.1768226623535</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5418758392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9943008422852</t>
+    <t xml:space="preserve">22.5418739318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9942989349365</t>
   </si>
   <si>
     <t xml:space="preserve">22.0855617523193</t>
@@ -2528,7 +2528,7 @@
     <t xml:space="preserve">21.5379867553711</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7205085754395</t>
+    <t xml:space="preserve">21.7205104827881</t>
   </si>
   <si>
     <t xml:space="preserve">21.3554592132568</t>
@@ -2537,28 +2537,28 @@
     <t xml:space="preserve">21.8117733001709</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4467220306396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8991470336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0738945007324</t>
+    <t xml:space="preserve">21.446720123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8991451263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0738925933838</t>
   </si>
   <si>
     <t xml:space="preserve">19.8952560424805</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8039970397949</t>
+    <t xml:space="preserve">19.8039951324463</t>
   </si>
   <si>
     <t xml:space="preserve">19.6214694976807</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7127323150635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0816745758057</t>
+    <t xml:space="preserve">19.7127342224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.081672668457</t>
   </si>
   <si>
     <t xml:space="preserve">24.6409149169922</t>
@@ -2567,49 +2567,49 @@
     <t xml:space="preserve">25.3710155487061</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3749046325684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6448059082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9185905456543</t>
+    <t xml:space="preserve">26.374906539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6448040008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9185924530029</t>
   </si>
   <si>
     <t xml:space="preserve">25.8273296356201</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5535411834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2797546386719</t>
+    <t xml:space="preserve">25.5535430908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2797565460205</t>
   </si>
   <si>
     <t xml:space="preserve">23.3632392883301</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4506130218506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6292495727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9904079437256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.264196395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1729354858398</t>
+    <t xml:space="preserve">22.450611114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6292476654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9904098510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2641983032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1729335784912</t>
   </si>
   <si>
     <t xml:space="preserve">20.5340957641602</t>
   </si>
   <si>
-    <t xml:space="preserve">20.80788230896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4428329467773</t>
+    <t xml:space="preserve">20.8078842163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.442834854126</t>
   </si>
   <si>
     <t xml:space="preserve">21.9030342102051</t>
@@ -2624,7 +2624,7 @@
     <t xml:space="preserve">20.1690464019775</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3476829528809</t>
+    <t xml:space="preserve">19.3476810455322</t>
   </si>
   <si>
     <t xml:space="preserve">19.1651554107666</t>
@@ -2636,10 +2636,10 @@
     <t xml:space="preserve">18.6175804138184</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1156368255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4311676025391</t>
+    <t xml:space="preserve">18.1156349182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4311656951904</t>
   </si>
   <si>
     <t xml:space="preserve">17.5224304199219</t>
@@ -2648,7 +2648,7 @@
     <t xml:space="preserve">16.2447509765625</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5185413360596</t>
+    <t xml:space="preserve">16.5185394287109</t>
   </si>
   <si>
     <t xml:space="preserve">16.6098022460938</t>
@@ -2660,10 +2660,10 @@
     <t xml:space="preserve">17.6593246459961</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2486400604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3437938690186</t>
+    <t xml:space="preserve">17.2486419677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3437919616699</t>
   </si>
   <si>
     <t xml:space="preserve">18.800106048584</t>
@@ -2675,7 +2675,7 @@
     <t xml:space="preserve">18.982629776001</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5263175964355</t>
+    <t xml:space="preserve">18.5263156890869</t>
   </si>
   <si>
     <t xml:space="preserve">18.4350566864014</t>
@@ -2687,7 +2687,7 @@
     <t xml:space="preserve">21.7661418914795</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8574066162109</t>
+    <t xml:space="preserve">21.8574047088623</t>
   </si>
   <si>
     <t xml:space="preserve">22.3137187957764</t>
@@ -2696,64 +2696,64 @@
     <t xml:space="preserve">21.9486656188965</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0399284362793</t>
+    <t xml:space="preserve">22.0399303436279</t>
   </si>
   <si>
     <t xml:space="preserve">21.4923534393311</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4049797058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.678768157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5913944244385</t>
+    <t xml:space="preserve">22.4049777984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6787662506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5913963317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5001335144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7337303161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8271713256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.387809753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2009315490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6681289672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.621410369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0607719421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9673309326172</t>
   </si>
   <si>
     <t xml:space="preserve">23.5001316070557</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7337303161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.827169418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3878116607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2009296417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6681289672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.621410369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.06077003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9673309326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.500129699707</t>
-  </si>
-  <si>
     <t xml:space="preserve">22.9394912719727</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7058906555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6591720581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5190143585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4255714416504</t>
+    <t xml:space="preserve">22.7058925628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6591739654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5190124511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.425573348999</t>
   </si>
   <si>
     <t xml:space="preserve">23.4534130096436</t>
@@ -2771,7 +2771,7 @@
     <t xml:space="preserve">22.0985317230225</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9116535186768</t>
+    <t xml:space="preserve">21.9116554260254</t>
   </si>
   <si>
     <t xml:space="preserve">21.6780548095703</t>
@@ -2783,7 +2783,7 @@
     <t xml:space="preserve">23.0329303741455</t>
   </si>
   <si>
-    <t xml:space="preserve">22.986213684082</t>
+    <t xml:space="preserve">22.9862117767334</t>
   </si>
   <si>
     <t xml:space="preserve">21.8182144165039</t>
@@ -2792,7 +2792,7 @@
     <t xml:space="preserve">22.1919727325439</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7714920043945</t>
+    <t xml:space="preserve">21.7714939117432</t>
   </si>
   <si>
     <t xml:space="preserve">22.2386913299561</t>
@@ -2804,13 +2804,13 @@
     <t xml:space="preserve">23.31325340271</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7993316650391</t>
+    <t xml:space="preserve">22.7993335723877</t>
   </si>
   <si>
     <t xml:space="preserve">22.3321323394775</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5846157073975</t>
+    <t xml:space="preserve">21.5846138000488</t>
   </si>
   <si>
     <t xml:space="preserve">20.930534362793</t>
@@ -2822,7 +2822,7 @@
     <t xml:space="preserve">20.2764568328857</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9494171142578</t>
+    <t xml:space="preserve">19.9494152069092</t>
   </si>
   <si>
     <t xml:space="preserve">20.4166164398193</t>
@@ -2843,25 +2843,25 @@
     <t xml:space="preserve">19.9026947021484</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8092575073242</t>
+    <t xml:space="preserve">19.8092555999756</t>
   </si>
   <si>
     <t xml:space="preserve">19.5756568908691</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3420581817627</t>
+    <t xml:space="preserve">19.3420562744141</t>
   </si>
   <si>
     <t xml:space="preserve">19.2486171722412</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9215755462646</t>
+    <t xml:space="preserve">18.9215774536133</t>
   </si>
   <si>
     <t xml:space="preserve">18.8281364440918</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5758476257324</t>
+    <t xml:space="preserve">18.5758495330811</t>
   </si>
   <si>
     <t xml:space="preserve">18.5010967254639</t>
@@ -2873,7 +2873,7 @@
     <t xml:space="preserve">19.5289363861084</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5945358276367</t>
+    <t xml:space="preserve">18.5945377349854</t>
   </si>
   <si>
     <t xml:space="preserve">18.3702812194824</t>
@@ -2882,7 +2882,7 @@
     <t xml:space="preserve">18.0525856018066</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9217720031738</t>
+    <t xml:space="preserve">17.9217700958252</t>
   </si>
   <si>
     <t xml:space="preserve">17.7535781860352</t>
@@ -2894,10 +2894,10 @@
     <t xml:space="preserve">17.7348899841309</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4919471740723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2303142547607</t>
+    <t xml:space="preserve">17.4919452667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2303161621094</t>
   </si>
   <si>
     <t xml:space="preserve">17.1742496490479</t>
@@ -2912,7 +2912,7 @@
     <t xml:space="preserve">16.4454212188721</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1277256011963</t>
+    <t xml:space="preserve">16.1277236938477</t>
   </si>
   <si>
     <t xml:space="preserve">16.5014839172363</t>
@@ -2924,13 +2924,13 @@
     <t xml:space="preserve">16.0342845916748</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8847818374634</t>
+    <t xml:space="preserve">15.8847808837891</t>
   </si>
   <si>
     <t xml:space="preserve">15.3241405487061</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6044607162476</t>
+    <t xml:space="preserve">15.6044616699219</t>
   </si>
   <si>
     <t xml:space="preserve">15.7352771759033</t>
@@ -2948,7 +2948,7 @@
     <t xml:space="preserve">16.7444267272949</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7257385253906</t>
+    <t xml:space="preserve">16.7257404327393</t>
   </si>
   <si>
     <t xml:space="preserve">16.9313087463379</t>
@@ -2960,7 +2960,7 @@
     <t xml:space="preserve">17.9965229034424</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2581539154053</t>
+    <t xml:space="preserve">18.2581558227539</t>
   </si>
   <si>
     <t xml:space="preserve">17.6601371765137</t>
@@ -2969,10 +2969,10 @@
     <t xml:space="preserve">17.5666980743408</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6414489746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3142185211182</t>
+    <t xml:space="preserve">17.641450881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3142166137695</t>
   </si>
   <si>
     <t xml:space="preserve">18.0712738037109</t>
@@ -3011,7 +3011,7 @@
     <t xml:space="preserve">17.7162017822266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5293235778809</t>
+    <t xml:space="preserve">17.5293216705322</t>
   </si>
   <si>
     <t xml:space="preserve">16.9873714447021</t>
@@ -3023,10 +3023,10 @@
     <t xml:space="preserve">17.5480117797852</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2772274017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.922158241272</t>
+    <t xml:space="preserve">16.277229309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9221572875977</t>
   </si>
   <si>
     <t xml:space="preserve">16.0155963897705</t>
@@ -3035,19 +3035,19 @@
     <t xml:space="preserve">15.9595327377319</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9782209396362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0903491973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8287162780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6231479644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5857725143433</t>
+    <t xml:space="preserve">15.9782218933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0903472900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8287172317505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6231489181519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5857744216919</t>
   </si>
   <si>
     <t xml:space="preserve">16.0716609954834</t>
@@ -3068,10 +3068,10 @@
     <t xml:space="preserve">16.6322994232178</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6136131286621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5762367248535</t>
+    <t xml:space="preserve">16.6136112213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5762348175049</t>
   </si>
   <si>
     <t xml:space="preserve">16.3519802093506</t>
@@ -3080,13 +3080,13 @@
     <t xml:space="preserve">16.2024765014648</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7913398742676</t>
+    <t xml:space="preserve">15.7913408279419</t>
   </si>
   <si>
     <t xml:space="preserve">15.7726516723633</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6979007720947</t>
+    <t xml:space="preserve">15.6978998184204</t>
   </si>
   <si>
     <t xml:space="preserve">16.5201721191406</t>
@@ -3095,34 +3095,34 @@
     <t xml:space="preserve">16.1464138031006</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1651000976562</t>
+    <t xml:space="preserve">16.1650981903076</t>
   </si>
   <si>
     <t xml:space="preserve">16.109037399292</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8474025726318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7539653778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8660936355591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6792144775391</t>
+    <t xml:space="preserve">15.8474044799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7539663314819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8660917282104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6792125701904</t>
   </si>
   <si>
     <t xml:space="preserve">15.8100280761719</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5110216140747</t>
+    <t xml:space="preserve">15.5110206604004</t>
   </si>
   <si>
     <t xml:space="preserve">15.3802042007446</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0064458847046</t>
+    <t xml:space="preserve">15.0064449310303</t>
   </si>
   <si>
     <t xml:space="preserve">14.8008785247803</t>
@@ -3131,7 +3131,7 @@
     <t xml:space="preserve">14.6700620651245</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4271173477173</t>
+    <t xml:space="preserve">14.4271183013916</t>
   </si>
   <si>
     <t xml:space="preserve">14.5766229629517</t>
@@ -3161,13 +3161,13 @@
     <t xml:space="preserve">15.0811967849731</t>
   </si>
   <si>
-    <t xml:space="preserve">15.567084312439</t>
+    <t xml:space="preserve">15.5670852661133</t>
   </si>
   <si>
     <t xml:space="preserve">15.716588973999</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6605262756348</t>
+    <t xml:space="preserve">15.6605253219604</t>
   </si>
   <si>
     <t xml:space="preserve">15.1933259963989</t>
@@ -3176,13 +3176,13 @@
     <t xml:space="preserve">15.3988933563232</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4175815582275</t>
+    <t xml:space="preserve">15.4175806045532</t>
   </si>
   <si>
     <t xml:space="preserve">15.4362697601318</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1372623443604</t>
+    <t xml:space="preserve">15.137261390686</t>
   </si>
   <si>
     <t xml:space="preserve">15.0438222885132</t>
@@ -3194,7 +3194,7 @@
     <t xml:space="preserve">14.9877586364746</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7261266708374</t>
+    <t xml:space="preserve">14.7261257171631</t>
   </si>
   <si>
     <t xml:space="preserve">14.950382232666</t>
@@ -3209,22 +3209,22 @@
     <t xml:space="preserve">14.3149900436401</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5018711090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4084300994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1654863357544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2028617858887</t>
+    <t xml:space="preserve">14.5018701553345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4084310531616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1654872894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.202862739563</t>
   </si>
   <si>
     <t xml:space="preserve">14.2963027954102</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1281108856201</t>
+    <t xml:space="preserve">14.1281099319458</t>
   </si>
   <si>
     <t xml:space="preserve">13.8291034698486</t>
@@ -3239,19 +3239,19 @@
     <t xml:space="preserve">13.4179677963257</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5487842559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6422243118286</t>
+    <t xml:space="preserve">13.5487833023071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6422233581543</t>
   </si>
   <si>
     <t xml:space="preserve">13.45534324646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3992795944214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3245286941528</t>
+    <t xml:space="preserve">13.3992805480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3245277404785</t>
   </si>
   <si>
     <t xml:space="preserve">13.2497758865356</t>
@@ -3260,7 +3260,7 @@
     <t xml:space="preserve">13.0815839767456</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3432159423828</t>
+    <t xml:space="preserve">13.3432149887085</t>
   </si>
   <si>
     <t xml:space="preserve">13.1937122344971</t>
@@ -3269,7 +3269,7 @@
     <t xml:space="preserve">13.3058395385742</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2589273452759</t>
+    <t xml:space="preserve">14.2589263916016</t>
   </si>
   <si>
     <t xml:space="preserve">14.2776145935059</t>
@@ -3278,7 +3278,7 @@
     <t xml:space="preserve">14.7448139190674</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5575485229492</t>
+    <t xml:space="preserve">16.5575466156006</t>
   </si>
   <si>
     <t xml:space="preserve">16.4641094207764</t>
@@ -3287,13 +3287,13 @@
     <t xml:space="preserve">16.4267311096191</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3146018981934</t>
+    <t xml:space="preserve">16.314603805542</t>
   </si>
   <si>
     <t xml:space="preserve">16.2585391998291</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2398509979248</t>
+    <t xml:space="preserve">16.2398529052734</t>
   </si>
   <si>
     <t xml:space="preserve">16.1837882995605</t>
@@ -3302,13 +3302,13 @@
     <t xml:space="preserve">14.8569412231445</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7074384689331</t>
+    <t xml:space="preserve">14.7074375152588</t>
   </si>
   <si>
     <t xml:space="preserve">14.6887502670288</t>
   </si>
   <si>
-    <t xml:space="preserve">14.389741897583</t>
+    <t xml:space="preserve">14.3897428512573</t>
   </si>
   <si>
     <t xml:space="preserve">14.782190322876</t>
@@ -3329,19 +3329,19 @@
     <t xml:space="preserve">12.9881439208984</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5956954956055</t>
+    <t xml:space="preserve">12.5956964492798</t>
   </si>
   <si>
     <t xml:space="preserve">12.7078247070312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7452011108398</t>
+    <t xml:space="preserve">12.7452001571655</t>
   </si>
   <si>
     <t xml:space="preserve">12.4275054931641</t>
   </si>
   <si>
-    <t xml:space="preserve">13.044207572937</t>
+    <t xml:space="preserve">13.0442085266113</t>
   </si>
   <si>
     <t xml:space="preserve">13.3805913925171</t>
@@ -3368,28 +3368,28 @@
     <t xml:space="preserve">13.9972944259644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.015983581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6513738632202</t>
+    <t xml:space="preserve">14.0159826278687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6513748168945</t>
   </si>
   <si>
     <t xml:space="preserve">15.0251340866089</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4736452102661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9034700393677</t>
+    <t xml:space="preserve">15.4736442565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.903468132019</t>
   </si>
   <si>
     <t xml:space="preserve">16.482795715332</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9126205444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8565559387207</t>
+    <t xml:space="preserve">16.912618637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8565578460693</t>
   </si>
   <si>
     <t xml:space="preserve">16.9499950408936</t>
@@ -3398,7 +3398,7 @@
     <t xml:space="preserve">16.8752422332764</t>
   </si>
   <si>
-    <t xml:space="preserve">17.043436050415</t>
+    <t xml:space="preserve">17.0434341430664</t>
   </si>
   <si>
     <t xml:space="preserve">15.9969091415405</t>
@@ -3410,7 +3410,7 @@
     <t xml:space="preserve">15.5483961105347</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6418380737305</t>
+    <t xml:space="preserve">15.6418361663818</t>
   </si>
   <si>
     <t xml:space="preserve">16.4080429077148</t>
@@ -3422,13 +3422,13 @@
     <t xml:space="preserve">16.6790199279785</t>
   </si>
   <si>
-    <t xml:space="preserve">16.585578918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8002986907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.706859588623</t>
+    <t xml:space="preserve">16.5855808258057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8002967834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7068576812744</t>
   </si>
   <si>
     <t xml:space="preserve">16.211820602417</t>
@@ -3437,19 +3437,19 @@
     <t xml:space="preserve">15.3708620071411</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3052616119385</t>
+    <t xml:space="preserve">16.3052597045898</t>
   </si>
   <si>
     <t xml:space="preserve">16.0249404907227</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1273365020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9404602050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6134204864502</t>
+    <t xml:space="preserve">18.1273384094238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9404582977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6134185791016</t>
   </si>
   <si>
     <t xml:space="preserve">17.7070121765137</t>
@@ -70229,7 +70229,7 @@
     </row>
     <row r="2542">
       <c r="A2542" s="1" t="n">
-        <v>46024.5896875</v>
+        <v>46024.3333333333</v>
       </c>
       <c r="B2542" t="n">
         <v>765</v>
@@ -70250,6 +70250,32 @@
         <v>1262</v>
       </c>
       <c r="H2542" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2543">
+      <c r="A2543" s="1" t="n">
+        <v>46027.6435069444</v>
+      </c>
+      <c r="B2543" t="n">
+        <v>1567</v>
+      </c>
+      <c r="C2543" t="n">
+        <v>14.1000003814697</v>
+      </c>
+      <c r="D2543" t="n">
+        <v>13.8999996185303</v>
+      </c>
+      <c r="E2543" t="n">
+        <v>14</v>
+      </c>
+      <c r="F2543" t="n">
+        <v>14</v>
+      </c>
+      <c r="G2543" t="s">
+        <v>1262</v>
+      </c>
+      <c r="H2543" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SAB.MI.xlsx
+++ b/data/SAB.MI.xlsx
@@ -38,97 +38,97 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5656795501709</t>
+    <t xml:space="preserve">8.56568050384521</t>
   </si>
   <si>
     <t xml:space="preserve">SAB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61823177337646</t>
+    <t xml:space="preserve">8.61823081970215</t>
   </si>
   <si>
     <t xml:space="preserve">8.48310279846191</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33295917510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37049579620361</t>
+    <t xml:space="preserve">8.33296012878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3704948425293</t>
   </si>
   <si>
     <t xml:space="preserve">8.31794357299805</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25788688659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16029262542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88252735137939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52969169616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66481971740723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62728500366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61226987838745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73989200592041</t>
+    <t xml:space="preserve">8.25788497924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16029357910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88252830505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52969074249268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66482067108154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62728452682495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61227083206177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73989152908325</t>
   </si>
   <si>
     <t xml:space="preserve">7.75490713119507</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76992225646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89754390716553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6197772026062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79995012283325</t>
+    <t xml:space="preserve">7.76992082595825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89754247665405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61977672576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79994916915894</t>
   </si>
   <si>
     <t xml:space="preserve">7.72487735748291</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65731287002563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50717067718506</t>
+    <t xml:space="preserve">7.65731382369995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5071702003479</t>
   </si>
   <si>
     <t xml:space="preserve">7.34201192855835</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54470634460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39080858230591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58224201202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82247018814087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08522319793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1152515411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95760011672974</t>
+    <t xml:space="preserve">7.54470491409302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39080810546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5822434425354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82247066497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08522129058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11525058746338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95760107040405</t>
   </si>
   <si>
     <t xml:space="preserve">8.06270027160645</t>
@@ -137,121 +137,121 @@
     <t xml:space="preserve">8.03267192840576</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92006492614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77742767333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86751461029053</t>
+    <t xml:space="preserve">7.92006301879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77742862701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86751365661621</t>
   </si>
   <si>
     <t xml:space="preserve">7.80745601654053</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98762845993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04017925262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99513530731201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96510601043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90505170822144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93507862091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8900351524353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94258642196655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82997846603394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81496429443359</t>
+    <t xml:space="preserve">7.98762893676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0401782989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99513483047485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96510696411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90504932403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9350790977478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89003610610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94258594512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82997751235962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81496286392212</t>
   </si>
   <si>
     <t xml:space="preserve">7.73238515853882</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64980602264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71736907958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67232799530029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63479232788086</t>
+    <t xml:space="preserve">7.64980411529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71737003326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67232704162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63479280471802</t>
   </si>
   <si>
     <t xml:space="preserve">7.51467704772949</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64230060577393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56722688674927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70235681533813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74739837646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46963310241699</t>
+    <t xml:space="preserve">7.64229869842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56722736358643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70235538482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74739933013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46963405609131</t>
   </si>
   <si>
     <t xml:space="preserve">7.69484901428223</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49215602874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47338819503784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43585062026978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50341701507568</t>
+    <t xml:space="preserve">7.49215507507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47338724136353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43585157394409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50341606140137</t>
   </si>
   <si>
     <t xml:space="preserve">7.48089504241943</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59725522994995</t>
+    <t xml:space="preserve">7.59725618362427</t>
   </si>
   <si>
     <t xml:space="preserve">7.4283447265625</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38705492019653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37203979492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31949043273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28195428848267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52122211456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80533981323242</t>
+    <t xml:space="preserve">7.38705444335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37204027175903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31949186325073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28195476531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52122116088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80533933639526</t>
   </si>
   <si>
     <t xml:space="preserve">7.75009346008301</t>
@@ -260,52 +260,52 @@
     <t xml:space="preserve">7.75798606872559</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81323051452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86058616638184</t>
+    <t xml:space="preserve">7.81323099136353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86058521270752</t>
   </si>
   <si>
     <t xml:space="preserve">7.69879484176636</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58435869216919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68695640563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57646703720093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53700590133667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49754571914673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28445672988892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92536306381226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.079261302948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22921180725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45808458328247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2607798576355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37127113342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26472616195679</t>
+    <t xml:space="preserve">7.58435773849487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68695735931396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57646656036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53700637817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49754524230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28445720672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92536354064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07926082611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22921228408813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45808506011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26077890396118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37127017974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26472663879395</t>
   </si>
   <si>
     <t xml:space="preserve">7.34759473800659</t>
@@ -317,100 +317,100 @@
     <t xml:space="preserve">7.36732482910156</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37916231155396</t>
+    <t xml:space="preserve">7.37916421890259</t>
   </si>
   <si>
     <t xml:space="preserve">7.13450717926025</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18975162506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10293674468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15029096603394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10688447952271</t>
+    <t xml:space="preserve">7.18975114822388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10293769836426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15029001235962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10688352584839</t>
   </si>
   <si>
     <t xml:space="preserve">7.20553588867188</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18185949325562</t>
+    <t xml:space="preserve">7.18185806274414</t>
   </si>
   <si>
     <t xml:space="preserve">7.22131967544556</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19369649887085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24894237518311</t>
+    <t xml:space="preserve">7.19369697570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24894380569458</t>
   </si>
   <si>
     <t xml:space="preserve">7.19764375686646</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18580436706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.225266456604</t>
+    <t xml:space="preserve">7.18580484390259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22526502609253</t>
   </si>
   <si>
     <t xml:space="preserve">7.20948219299316</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31602668762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21342802047729</t>
+    <t xml:space="preserve">7.31602621078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21342849731445</t>
   </si>
   <si>
     <t xml:space="preserve">7.16607475280762</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24499607086182</t>
+    <t xml:space="preserve">7.24499654769897</t>
   </si>
   <si>
     <t xml:space="preserve">7.13056039810181</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11082983016968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17791366577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23315763473511</t>
+    <t xml:space="preserve">7.11083030700684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17791414260864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23315906524658</t>
   </si>
   <si>
     <t xml:space="preserve">7.27656507492065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30024147033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29235029220581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24105024337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11872148513794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09504508972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00428581237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94509506225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93325614929199</t>
+    <t xml:space="preserve">7.3002405166626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29234933853149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24105167388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11872243881226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.095046043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00428676605225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94509410858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93325519561768</t>
   </si>
   <si>
     <t xml:space="preserve">7.09899187088013</t>
@@ -419,13 +419,13 @@
     <t xml:space="preserve">7.15423631668091</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13845157623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15818357467651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05558395385742</t>
+    <t xml:space="preserve">7.13845300674438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15818119049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05558347702026</t>
   </si>
   <si>
     <t xml:space="preserve">7.07136821746826</t>
@@ -434,22 +434,22 @@
     <t xml:space="preserve">7.06742334365845</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02401494979858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04769277572632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0634765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08320713043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05163955688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04374742507935</t>
+    <t xml:space="preserve">7.02401638031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04769229888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06347608566284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08320760726929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05163908004761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04374694824219</t>
   </si>
   <si>
     <t xml:space="preserve">7.03190851211548</t>
@@ -458,46 +458,46 @@
     <t xml:space="preserve">7.05953073501587</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03585433959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17396783828735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90563344955444</t>
+    <t xml:space="preserve">7.03585338592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17396688461304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90563440322876</t>
   </si>
   <si>
     <t xml:space="preserve">6.91352653503418</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93720245361328</t>
+    <t xml:space="preserve">6.93720197677612</t>
   </si>
   <si>
     <t xml:space="preserve">6.92141819000244</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94114828109741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9687705039978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14239931106567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45019245147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79350137710571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9237208366394</t>
+    <t xml:space="preserve">6.94114875793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96877098083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1423978805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45019197463989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79350090026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92372179031372</t>
   </si>
   <si>
     <t xml:space="preserve">8.04999732971191</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20783805847168</t>
+    <t xml:space="preserve">8.207839012146</t>
   </si>
   <si>
     <t xml:space="preserve">8.16837882995605</t>
@@ -512,55 +512,55 @@
     <t xml:space="preserve">8.06578159332275</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12891674041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17627048492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32622241973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55509471893311</t>
+    <t xml:space="preserve">8.1289176940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17627143859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32622146606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55509567260742</t>
   </si>
   <si>
     <t xml:space="preserve">8.56298542022705</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42881965637207</t>
+    <t xml:space="preserve">8.42882061004639</t>
   </si>
   <si>
     <t xml:space="preserve">8.35778999328613</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39725112915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42092704772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44460391998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40514278411865</t>
+    <t xml:space="preserve">8.39725208282471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42092609405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44460487365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40514183044434</t>
   </si>
   <si>
     <t xml:space="preserve">8.26308345794678</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18416309356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30254554748535</t>
+    <t xml:space="preserve">8.18416213989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30254459381104</t>
   </si>
   <si>
     <t xml:space="preserve">8.22362327575684</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2867603302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25519180297852</t>
+    <t xml:space="preserve">8.28676223754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25519275665283</t>
   </si>
   <si>
     <t xml:space="preserve">8.34989833831787</t>
@@ -569,31 +569,31 @@
     <t xml:space="preserve">8.31043720245361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36568164825439</t>
+    <t xml:space="preserve">8.36568260192871</t>
   </si>
   <si>
     <t xml:space="preserve">8.33411407470703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34200572967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46038818359375</t>
+    <t xml:space="preserve">8.34200477600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46038722991943</t>
   </si>
   <si>
     <t xml:space="preserve">8.62612342834473</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74450492858887</t>
+    <t xml:space="preserve">8.74450588226318</t>
   </si>
   <si>
     <t xml:space="preserve">8.88656425476074</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00494480133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23381805419922</t>
+    <t xml:space="preserve">9.0049467086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23381900787354</t>
   </si>
   <si>
     <t xml:space="preserve">9.30484867095947</t>
@@ -602,52 +602,52 @@
     <t xml:space="preserve">9.26538753509521</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16278839111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19435787200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24960231781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29695510864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36798667907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54950523376465</t>
+    <t xml:space="preserve">9.1627893447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19435691833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24960327148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29695701599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36798572540283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54950618743896</t>
   </si>
   <si>
     <t xml:space="preserve">9.67577934265137</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74680995941162</t>
+    <t xml:space="preserve">9.7468090057373</t>
   </si>
   <si>
     <t xml:space="preserve">10.2203378677368</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4807777404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4571027755737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2913675308228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2597999572754</t>
+    <t xml:space="preserve">10.4807796478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4571018218994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2913684844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2597990036011</t>
   </si>
   <si>
     <t xml:space="preserve">10.1493082046509</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0861711502075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0151424407959</t>
+    <t xml:space="preserve">10.0861721038818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0151414871216</t>
   </si>
   <si>
     <t xml:space="preserve">10.1019554138184</t>
@@ -656,16 +656,16 @@
     <t xml:space="preserve">10.165093421936</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0546026229858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1808776855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1177396774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1887674331665</t>
+    <t xml:space="preserve">10.0546035766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1808786392212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1177406311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1887693405151</t>
   </si>
   <si>
     <t xml:space="preserve">10.070387840271</t>
@@ -683,22 +683,22 @@
     <t xml:space="preserve">10.4176416397095</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3150434494019</t>
+    <t xml:space="preserve">10.3150424957275</t>
   </si>
   <si>
     <t xml:space="preserve">10.7333288192749</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4492092132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5596990585327</t>
+    <t xml:space="preserve">10.4492111206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5597019195557</t>
   </si>
   <si>
     <t xml:space="preserve">10.6386213302612</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5912704467773</t>
+    <t xml:space="preserve">10.591269493103</t>
   </si>
   <si>
     <t xml:space="preserve">11.0095539093018</t>
@@ -707,13 +707,13 @@
     <t xml:space="preserve">10.8832788467407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3410243988037</t>
+    <t xml:space="preserve">11.3410234451294</t>
   </si>
   <si>
     <t xml:space="preserve">12.0592088699341</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9171524047852</t>
+    <t xml:space="preserve">11.9171514511108</t>
   </si>
   <si>
     <t xml:space="preserve">12.0513181686401</t>
@@ -722,16 +722,16 @@
     <t xml:space="preserve">11.6882791519165</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6803874969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2644052505493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6274442672729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5406312942505</t>
+    <t xml:space="preserve">11.6803865432739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.264404296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6274433135986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5406303405762</t>
   </si>
   <si>
     <t xml:space="preserve">12.6747970581055</t>
@@ -746,52 +746,52 @@
     <t xml:space="preserve">12.6518535614014</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8471231460571</t>
+    <t xml:space="preserve">12.8471221923828</t>
   </si>
   <si>
     <t xml:space="preserve">12.8145780563354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9203481674194</t>
+    <t xml:space="preserve">12.9203491210938</t>
   </si>
   <si>
     <t xml:space="preserve">12.8715305328369</t>
   </si>
   <si>
-    <t xml:space="preserve">12.936619758606</t>
+    <t xml:space="preserve">12.9366216659546</t>
   </si>
   <si>
     <t xml:space="preserve">12.8064413070679</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6437168121338</t>
+    <t xml:space="preserve">12.6437158584595</t>
   </si>
   <si>
     <t xml:space="preserve">12.822714805603</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5209150314331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8463659286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7812757492065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9114551544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9277267456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9602727890015</t>
+    <t xml:space="preserve">11.5209159851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8463640213013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7812747955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9114561080933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9277276992798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9602718353271</t>
   </si>
   <si>
     <t xml:space="preserve">11.8056840896606</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1311349868774</t>
+    <t xml:space="preserve">12.1311330795288</t>
   </si>
   <si>
     <t xml:space="preserve">12.0009536743164</t>
@@ -800,28 +800,28 @@
     <t xml:space="preserve">11.9846811294556</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0416355133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0823154449463</t>
+    <t xml:space="preserve">12.0416345596313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0823173522949</t>
   </si>
   <si>
     <t xml:space="preserve">11.9765453338623</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8789100646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7161846160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4720993041992</t>
+    <t xml:space="preserve">11.8789110183716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7161855697632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4720983505249</t>
   </si>
   <si>
     <t xml:space="preserve">11.5534601211548</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5860061645508</t>
+    <t xml:space="preserve">11.5860052108765</t>
   </si>
   <si>
     <t xml:space="preserve">11.7975473403931</t>
@@ -830,7 +830,7 @@
     <t xml:space="preserve">11.8951835632324</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0904512405396</t>
+    <t xml:space="preserve">12.0904531478882</t>
   </si>
   <si>
     <t xml:space="preserve">12.1636781692505</t>
@@ -839,13 +839,13 @@
     <t xml:space="preserve">12.0741806030273</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2287683486938</t>
+    <t xml:space="preserve">12.2287664413452</t>
   </si>
   <si>
     <t xml:space="preserve">12.1392707824707</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2043600082397</t>
+    <t xml:space="preserve">12.2043609619141</t>
   </si>
   <si>
     <t xml:space="preserve">12.1880865097046</t>
@@ -854,13 +854,13 @@
     <t xml:space="preserve">12.147406578064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2531785964966</t>
+    <t xml:space="preserve">12.2531776428223</t>
   </si>
   <si>
     <t xml:space="preserve">12.3670845031738</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4077653884888</t>
+    <t xml:space="preserve">12.4077672958374</t>
   </si>
   <si>
     <t xml:space="preserve">12.448447227478</t>
@@ -869,31 +869,31 @@
     <t xml:space="preserve">12.9447574615479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7820320129395</t>
+    <t xml:space="preserve">12.7820339202881</t>
   </si>
   <si>
     <t xml:space="preserve">12.8959398269653</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0098466873169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9528942108154</t>
+    <t xml:space="preserve">13.0098476409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9528932571411</t>
   </si>
   <si>
     <t xml:space="preserve">12.8552589416504</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7332143783569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7738962173462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9854383468628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2620716094971</t>
+    <t xml:space="preserve">12.7332153320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7738971710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9854402542114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2620697021484</t>
   </si>
   <si>
     <t xml:space="preserve">13.6851558685303</t>
@@ -902,61 +902,61 @@
     <t xml:space="preserve">13.9292430877686</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9943332672119</t>
+    <t xml:space="preserve">13.9943342208862</t>
   </si>
   <si>
     <t xml:space="preserve">13.7502450942993</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8153352737427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8316097259521</t>
+    <t xml:space="preserve">13.815336227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8316087722778</t>
   </si>
   <si>
     <t xml:space="preserve">14.018741607666</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0268783569336</t>
+    <t xml:space="preserve">14.0268774032593</t>
   </si>
   <si>
     <t xml:space="preserve">14.1814670562744</t>
   </si>
   <si>
-    <t xml:space="preserve">14.157057762146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2302837371826</t>
+    <t xml:space="preserve">14.157054901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2302846908569</t>
   </si>
   <si>
     <t xml:space="preserve">14.7754106521606</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3205404281616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2961301803589</t>
+    <t xml:space="preserve">15.3205423355103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2961292266846</t>
   </si>
   <si>
     <t xml:space="preserve">15.4588556289673</t>
   </si>
   <si>
-    <t xml:space="preserve">15.824987411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7924432754517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5076723098755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8493957519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8656673431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5158109664917</t>
+    <t xml:space="preserve">15.8249883651733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.792441368103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5076713562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8493947982788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.865668296814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5158090591431</t>
   </si>
   <si>
     <t xml:space="preserve">16.0039825439453</t>
@@ -965,19 +965,19 @@
     <t xml:space="preserve">16.2643432617188</t>
   </si>
   <si>
-    <t xml:space="preserve">16.776927947998</t>
+    <t xml:space="preserve">16.7769260406494</t>
   </si>
   <si>
     <t xml:space="preserve">16.9559230804443</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4115524291992</t>
+    <t xml:space="preserve">17.4115543365479</t>
   </si>
   <si>
     <t xml:space="preserve">17.0454216003418</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0787220001221</t>
+    <t xml:space="preserve">18.0787258148193</t>
   </si>
   <si>
     <t xml:space="preserve">17.6475048065186</t>
@@ -986,19 +986,19 @@
     <t xml:space="preserve">18.0217723846436</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0543174743652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1275424957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2984027862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4123077392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1682243347168</t>
+    <t xml:space="preserve">18.0543193817139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1275405883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2984046936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4123096466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1682262420654</t>
   </si>
   <si>
     <t xml:space="preserve">18.1600875854492</t>
@@ -1010,25 +1010,25 @@
     <t xml:space="preserve">17.2650985717773</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0861015319824</t>
+    <t xml:space="preserve">17.0861053466797</t>
   </si>
   <si>
     <t xml:space="preserve">17.2976474761963</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0047397613525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1267871856689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8745632171631</t>
+    <t xml:space="preserve">17.0047435760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1267833709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8745613098145</t>
   </si>
   <si>
     <t xml:space="preserve">17.0779666900635</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8664245605469</t>
+    <t xml:space="preserve">16.8664264678955</t>
   </si>
   <si>
     <t xml:space="preserve">16.785062789917</t>
@@ -1037,34 +1037,34 @@
     <t xml:space="preserve">16.9884662628174</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5979290008545</t>
+    <t xml:space="preserve">16.5979309082031</t>
   </si>
   <si>
     <t xml:space="preserve">16.9152431488037</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8338832855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9640598297119</t>
+    <t xml:space="preserve">16.8338794708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9640617370605</t>
   </si>
   <si>
     <t xml:space="preserve">16.8826999664307</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9233779907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1349239349365</t>
+    <t xml:space="preserve">16.9233798980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1349220275879</t>
   </si>
   <si>
     <t xml:space="preserve">17.0698299407959</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1674671173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6637763977051</t>
+    <t xml:space="preserve">17.1674652099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6637744903564</t>
   </si>
   <si>
     <t xml:space="preserve">18.2251777648926</t>
@@ -1085,52 +1085,52 @@
     <t xml:space="preserve">18.7377605438232</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7133502960205</t>
+    <t xml:space="preserve">18.7133522033691</t>
   </si>
   <si>
     <t xml:space="preserve">18.59130859375</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3065376281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6157150268555</t>
+    <t xml:space="preserve">18.3065414428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6157207489014</t>
   </si>
   <si>
     <t xml:space="preserve">18.217041015625</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2089042663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4611301422119</t>
+    <t xml:space="preserve">18.2089080810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4611282348633</t>
   </si>
   <si>
     <t xml:space="preserve">17.5417327880859</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9071063995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4758853912354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3945236206055</t>
+    <t xml:space="preserve">16.9071083068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.475887298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3945217132568</t>
   </si>
   <si>
     <t xml:space="preserve">16.1097545623779</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3619785308838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2806167602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3782501220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.199254989624</t>
+    <t xml:space="preserve">16.3619804382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2806148529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3782520294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1992530822754</t>
   </si>
   <si>
     <t xml:space="preserve">16.2236633300781</t>
@@ -1139,7 +1139,7 @@
     <t xml:space="preserve">16.2724781036377</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6792907714844</t>
+    <t xml:space="preserve">16.679292678833</t>
   </si>
   <si>
     <t xml:space="preserve">16.313159942627</t>
@@ -1148,34 +1148,34 @@
     <t xml:space="preserve">16.09348487854</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9470300674438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1911163330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3538417816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.028392791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9144859313965</t>
+    <t xml:space="preserve">15.9470281600952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1911144256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3538398742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0283946990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9144840240479</t>
   </si>
   <si>
     <t xml:space="preserve">15.1822233200073</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9706792831421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1008605957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8730478286743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.222146987915</t>
+    <t xml:space="preserve">14.9706802368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1008596420288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8730487823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2221488952637</t>
   </si>
   <si>
     <t xml:space="preserve">13.8478813171387</t>
@@ -1184,82 +1184,82 @@
     <t xml:space="preserve">14.8893194198608</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1984968185425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3937654495239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5402193069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9381380081177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5964155197144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4011449813843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2058734893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1082410812378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.059422492981</t>
+    <t xml:space="preserve">15.1984949111938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3937635421753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5402173995972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9381370544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.59641456604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.40114402771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2058725357056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1082401275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0594234466553</t>
   </si>
   <si>
     <t xml:space="preserve">13.9129705429077</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0106058120728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3197822570801</t>
+    <t xml:space="preserve">14.0106048583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3197813034058</t>
   </si>
   <si>
     <t xml:space="preserve">14.6452312469482</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7428684234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7265949249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2147693634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.807957649231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8567752838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9544067382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7916831970215</t>
+    <t xml:space="preserve">14.7428674697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7265939712524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.214771270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8079566955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8567743301392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9544076919556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7916841506958</t>
   </si>
   <si>
     <t xml:space="preserve">14.2709655761719</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0032291412354</t>
+    <t xml:space="preserve">15.0032253265381</t>
   </si>
   <si>
     <t xml:space="preserve">14.4825077056885</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9218626022339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.905590057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0194988250732</t>
+    <t xml:space="preserve">14.9218635559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9055910110474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0194997787476</t>
   </si>
   <si>
     <t xml:space="preserve">15.0520439147949</t>
@@ -1268,85 +1268,85 @@
     <t xml:space="preserve">16.2562065124512</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7354879379272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8168497085571</t>
+    <t xml:space="preserve">15.7354860305786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8168506622314</t>
   </si>
   <si>
     <t xml:space="preserve">15.62158203125</t>
   </si>
   <si>
-    <t xml:space="preserve">15.930757522583</t>
+    <t xml:space="preserve">15.9307565689087</t>
   </si>
   <si>
     <t xml:space="preserve">15.6866722106934</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7192144393921</t>
+    <t xml:space="preserve">15.7192153930664</t>
   </si>
   <si>
     <t xml:space="preserve">15.7029418945312</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6703987121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6053085327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5653514862061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9956836700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0291919708252</t>
+    <t xml:space="preserve">15.6704015731812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6053104400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5653505325317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9956827163696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0291929244995</t>
   </si>
   <si>
     <t xml:space="preserve">15.0627021789551</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2470083236694</t>
+    <t xml:space="preserve">15.2470064163208</t>
   </si>
   <si>
     <t xml:space="preserve">15.2302522659302</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5318403244019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7161445617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8669404983521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5821075439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4983320236206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.481575012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4145565032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1799898147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0794563293457</t>
+    <t xml:space="preserve">15.5318412780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7161483764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8669424057007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.582106590271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4983310699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4815759658813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4145545959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1799879074097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.07945728302</t>
   </si>
   <si>
     <t xml:space="preserve">15.1129674911499</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3589954376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2919750213623</t>
+    <t xml:space="preserve">14.3589925765991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.291974067688</t>
   </si>
   <si>
     <t xml:space="preserve">14.2584657669067</t>
@@ -1355,7 +1355,7 @@
     <t xml:space="preserve">14.4595241546631</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4092597961426</t>
+    <t xml:space="preserve">14.4092607498169</t>
   </si>
   <si>
     <t xml:space="preserve">14.5600519180298</t>
@@ -1364,52 +1364,52 @@
     <t xml:space="preserve">13.4039621353149</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4877376556396</t>
+    <t xml:space="preserve">13.4877367019653</t>
   </si>
   <si>
     <t xml:space="preserve">13.2364120483398</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5380010604858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4374732971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1914463043213</t>
+    <t xml:space="preserve">13.5380029678345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4374723434448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.191445350647</t>
   </si>
   <si>
     <t xml:space="preserve">13.5882663726807</t>
   </si>
   <si>
-    <t xml:space="preserve">13.688796043396</t>
+    <t xml:space="preserve">13.6887969970703</t>
   </si>
   <si>
     <t xml:space="preserve">13.4207181930542</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5212459564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.57151222229</t>
+    <t xml:space="preserve">13.5212469100952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5715131759644</t>
   </si>
   <si>
     <t xml:space="preserve">13.3201875686646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1526393890381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.186146736145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2196578979492</t>
+    <t xml:space="preserve">13.1526384353638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1861476898193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2196569442749</t>
   </si>
   <si>
     <t xml:space="preserve">13.3034324645996</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8510494232178</t>
+    <t xml:space="preserve">12.8510484695435</t>
   </si>
   <si>
     <t xml:space="preserve">12.6834993362427</t>
@@ -1418,13 +1418,13 @@
     <t xml:space="preserve">12.5662155151367</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9013137817383</t>
+    <t xml:space="preserve">12.901312828064</t>
   </si>
   <si>
     <t xml:space="preserve">12.8342933654785</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4824390411377</t>
+    <t xml:space="preserve">12.482439994812</t>
   </si>
   <si>
     <t xml:space="preserve">12.1473407745361</t>
@@ -1442,19 +1442,19 @@
     <t xml:space="preserve">11.5609178543091</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1923084259033</t>
+    <t xml:space="preserve">11.192307472229</t>
   </si>
   <si>
     <t xml:space="preserve">11.2258176803589</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4321737289429</t>
+    <t xml:space="preserve">12.4321746826172</t>
   </si>
   <si>
     <t xml:space="preserve">13.1191272735596</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2531661987305</t>
+    <t xml:space="preserve">13.2531671524048</t>
   </si>
   <si>
     <t xml:space="preserve">13.2866773605347</t>
@@ -1463,28 +1463,28 @@
     <t xml:space="preserve">12.7672739028931</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3536958694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.985089302063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8007841110229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6332349777222</t>
+    <t xml:space="preserve">13.3536977767944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9850873947144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8007831573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6332340240479</t>
   </si>
   <si>
     <t xml:space="preserve">12.8678045272827</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8122425079346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6279373168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6111822128296</t>
+    <t xml:space="preserve">11.8122415542603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6279382705688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6111812591553</t>
   </si>
   <si>
     <t xml:space="preserve">11.7284669876099</t>
@@ -1499,37 +1499,37 @@
     <t xml:space="preserve">11.6614465713501</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0750246047974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0415134429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9577398300171</t>
+    <t xml:space="preserve">11.0750226974487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0415143966675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9577388763428</t>
   </si>
   <si>
     <t xml:space="preserve">10.7566795349121</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9242286682129</t>
+    <t xml:space="preserve">10.9242296218872</t>
   </si>
   <si>
     <t xml:space="preserve">10.9744939804077</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7117118835449</t>
+    <t xml:space="preserve">11.7117109298706</t>
   </si>
   <si>
     <t xml:space="preserve">12.3651552200317</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4603881835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1587972640991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1252899169922</t>
+    <t xml:space="preserve">11.4603872299194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1587991714478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1252880096436</t>
   </si>
   <si>
     <t xml:space="preserve">11.1755542755127</t>
@@ -1538,7 +1538,7 @@
     <t xml:space="preserve">11.3766136169434</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2311162948608</t>
+    <t xml:space="preserve">12.2311172485352</t>
   </si>
   <si>
     <t xml:space="preserve">12.3986654281616</t>
@@ -1550,13 +1550,13 @@
     <t xml:space="preserve">11.7954864501953</t>
   </si>
   <si>
-    <t xml:space="preserve">11.87926197052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.197606086731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2478704452515</t>
+    <t xml:space="preserve">11.8792610168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1976041793823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2478713989258</t>
   </si>
   <si>
     <t xml:space="preserve">12.0133008956909</t>
@@ -1565,10 +1565,10 @@
     <t xml:space="preserve">12.1305856704712</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1808490753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.381911277771</t>
+    <t xml:space="preserve">12.180850982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3819103240967</t>
   </si>
   <si>
     <t xml:space="preserve">12.3316459655762</t>
@@ -1577,34 +1577,34 @@
     <t xml:space="preserve">12.4656848907471</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5997257232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7170085906982</t>
+    <t xml:space="preserve">12.599723815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7170095443726</t>
   </si>
   <si>
     <t xml:space="preserve">12.8845596313477</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9515781402588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9683322906494</t>
+    <t xml:space="preserve">12.9515790939331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.968334197998</t>
   </si>
   <si>
     <t xml:space="preserve">13.2029037475586</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7337646484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8175382614136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6499891281128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7002534866333</t>
+    <t xml:space="preserve">12.7337636947632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8175392150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6499900817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7002544403076</t>
   </si>
   <si>
     <t xml:space="preserve">12.5159492492676</t>
@@ -1622,19 +1622,19 @@
     <t xml:space="preserve">12.5494594573975</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9348220825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9180698394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.38720703125</t>
+    <t xml:space="preserve">12.9348230361938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9180679321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3872060775757</t>
   </si>
   <si>
     <t xml:space="preserve">13.6217775344849</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8228368759155</t>
+    <t xml:space="preserve">13.8228359222412</t>
   </si>
   <si>
     <t xml:space="preserve">13.5044927597046</t>
@@ -1643,19 +1643,19 @@
     <t xml:space="preserve">13.4542264938354</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6385316848755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7223052978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3704528808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0521078109741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0185985565186</t>
+    <t xml:space="preserve">13.6385326385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7223043441772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3704538345337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0521087646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0185976028442</t>
   </si>
   <si>
     <t xml:space="preserve">13.1693935394287</t>
@@ -1676,49 +1676,49 @@
     <t xml:space="preserve">12.3650341033936</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2257118225098</t>
+    <t xml:space="preserve">12.2257108688354</t>
   </si>
   <si>
     <t xml:space="preserve">12.2779569625854</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3127889633179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2953729629517</t>
+    <t xml:space="preserve">12.3127899169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.295373916626</t>
   </si>
   <si>
     <t xml:space="preserve">12.3302030563354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1212177276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5217752456665</t>
+    <t xml:space="preserve">12.1212167739868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5217761993408</t>
   </si>
   <si>
     <t xml:space="preserve">12.4869432449341</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4521131515503</t>
+    <t xml:space="preserve">12.452112197876</t>
   </si>
   <si>
     <t xml:space="preserve">12.1386318206787</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0515556335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.894814491272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2082958221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8178396224976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7655916213989</t>
+    <t xml:space="preserve">12.0515546798706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8948154449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2082948684692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8178386688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7655925750732</t>
   </si>
   <si>
     <t xml:space="preserve">12.643684387207</t>
@@ -1727,22 +1727,22 @@
     <t xml:space="preserve">12.399866104126</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6262693405151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5391893386841</t>
+    <t xml:space="preserve">12.6262683868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5391902923584</t>
   </si>
   <si>
     <t xml:space="preserve">12.8700857162476</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9745779037476</t>
+    <t xml:space="preserve">12.9745788574219</t>
   </si>
   <si>
     <t xml:space="preserve">12.95716381073</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9397478103638</t>
+    <t xml:space="preserve">12.9397487640381</t>
   </si>
   <si>
     <t xml:space="preserve">12.7830085754395</t>
@@ -1760,7 +1760,7 @@
     <t xml:space="preserve">12.1560478210449</t>
   </si>
   <si>
-    <t xml:space="preserve">12.034140586853</t>
+    <t xml:space="preserve">12.0341396331787</t>
   </si>
   <si>
     <t xml:space="preserve">11.7206592559814</t>
@@ -1772,22 +1772,22 @@
     <t xml:space="preserve">11.7554912567139</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6684122085571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9993095397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0689697265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1038007736206</t>
+    <t xml:space="preserve">11.6684131622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9993085861206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0689706802368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1038017272949</t>
   </si>
   <si>
     <t xml:space="preserve">11.790322303772</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8425693511963</t>
+    <t xml:space="preserve">11.842568397522</t>
   </si>
   <si>
     <t xml:space="preserve">11.9470615386963</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">11.8251533508301</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8599834442139</t>
+    <t xml:space="preserve">11.8599843978882</t>
   </si>
   <si>
     <t xml:space="preserve">11.7729072570801</t>
@@ -1808,16 +1808,16 @@
     <t xml:space="preserve">11.6509981155396</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5465040206909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3201017379761</t>
+    <t xml:space="preserve">11.5465059280396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3201026916504</t>
   </si>
   <si>
     <t xml:space="preserve">11.2156095504761</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4071807861328</t>
+    <t xml:space="preserve">11.4071798324585</t>
   </si>
   <si>
     <t xml:space="preserve">11.3026857376099</t>
@@ -1835,25 +1835,25 @@
     <t xml:space="preserve">10.9369611740112</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0414543151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8847131729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8672971725464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9717922210693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8324670791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.623480796814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6060657501221</t>
+    <t xml:space="preserve">11.0414533615112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8847141265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8672981262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.971791267395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8324661254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6234798431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6060647964478</t>
   </si>
   <si>
     <t xml:space="preserve">10.5886497497559</t>
@@ -1862,19 +1862,19 @@
     <t xml:space="preserve">10.5189876556396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4493246078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6583108901978</t>
+    <t xml:space="preserve">10.4493265151978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6583127975464</t>
   </si>
   <si>
     <t xml:space="preserve">10.7802209854126</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1633625030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1111145019531</t>
+    <t xml:space="preserve">11.1633615493774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1111164093018</t>
   </si>
   <si>
     <t xml:space="preserve">11.0588684082031</t>
@@ -1892,28 +1892,28 @@
     <t xml:space="preserve">11.0066232681274</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7976360321045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8150520324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9543762207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0936994552612</t>
+    <t xml:space="preserve">10.7976369857788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8150510787964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9543752670288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0937004089355</t>
   </si>
   <si>
     <t xml:space="preserve">11.7032432556152</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9818935394287</t>
+    <t xml:space="preserve">11.9818925857544</t>
   </si>
   <si>
     <t xml:space="preserve">11.9296455383301</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9122314453125</t>
+    <t xml:space="preserve">11.9122304916382</t>
   </si>
   <si>
     <t xml:space="preserve">11.8077383041382</t>
@@ -1922,10 +1922,10 @@
     <t xml:space="preserve">12.2605409622192</t>
   </si>
   <si>
-    <t xml:space="preserve">12.086386680603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9644775390625</t>
+    <t xml:space="preserve">12.0863876342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9644784927368</t>
   </si>
   <si>
     <t xml:space="preserve">11.5290880203247</t>
@@ -1946,31 +1946,31 @@
     <t xml:space="preserve">12.1908798217773</t>
   </si>
   <si>
-    <t xml:space="preserve">12.347620010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5116729736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5987520217896</t>
+    <t xml:space="preserve">12.3476190567017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5116720199585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5987510681152</t>
   </si>
   <si>
     <t xml:space="preserve">10.7105588912964</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70045757293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49146938323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03866672515869</t>
+    <t xml:space="preserve">9.7004566192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49147129058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03866767883301</t>
   </si>
   <si>
     <t xml:space="preserve">8.98641967773438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42912197113037</t>
+    <t xml:space="preserve">8.42912292480469</t>
   </si>
   <si>
     <t xml:space="preserve">8.18530464172363</t>
@@ -1982,34 +1982,34 @@
     <t xml:space="preserve">8.45524597167969</t>
   </si>
   <si>
-    <t xml:space="preserve">8.533616065979</t>
+    <t xml:space="preserve">8.53361511230469</t>
   </si>
   <si>
     <t xml:space="preserve">8.49007701873779</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31592178344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32462978363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16789054870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38558387756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28979778289795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41170597076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49878406524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.638108253479</t>
+    <t xml:space="preserve">8.31592082977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32462882995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16788959503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38558483123779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28979873657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41170692443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4987850189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63810920715332</t>
   </si>
   <si>
     <t xml:space="preserve">8.69035530090332</t>
@@ -2018,37 +2018,37 @@
     <t xml:space="preserve">8.67294025421143</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79485034942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96900463104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75131034851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70777034759521</t>
+    <t xml:space="preserve">8.79484939575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96900367736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75130939483643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70777130126953</t>
   </si>
   <si>
     <t xml:space="preserve">8.83838748931885</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18669891357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05608081817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14315891265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23023796081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40439319610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66562652587891</t>
+    <t xml:space="preserve">9.1866979598999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05608177185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14316082000732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23023700714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40439224243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66562557220459</t>
   </si>
   <si>
     <t xml:space="preserve">9.57854843139648</t>
@@ -2060,16 +2060,16 @@
     <t xml:space="preserve">8.88192653656006</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6555233001709</t>
+    <t xml:space="preserve">8.65552425384521</t>
   </si>
   <si>
     <t xml:space="preserve">8.51620006561279</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60327911376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56844806671143</t>
+    <t xml:space="preserve">8.60327816009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56844711303711</t>
   </si>
   <si>
     <t xml:space="preserve">9.36085319519043</t>
@@ -2087,25 +2087,25 @@
     <t xml:space="preserve">9.92685794830322</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88332176208496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0574769973755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97039794921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7091646194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75270366668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6220874786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53500938415527</t>
+    <t xml:space="preserve">9.88332080841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0574750900269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97039890289307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70916366577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75270462036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62208652496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53501033782959</t>
   </si>
   <si>
     <t xml:space="preserve">9.79624271392822</t>
@@ -2117,19 +2117,19 @@
     <t xml:space="preserve">10.2751703262329</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5364036560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9282541275024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0153303146362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7540979385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.492865562439</t>
+    <t xml:space="preserve">10.5364027023315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9282531738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0153293609619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7540969848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4928646087646</t>
   </si>
   <si>
     <t xml:space="preserve">10.4057865142822</t>
@@ -2138,7 +2138,7 @@
     <t xml:space="preserve">10.3622465133667</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3187103271484</t>
+    <t xml:space="preserve">10.3187084197998</t>
   </si>
   <si>
     <t xml:space="preserve">11.1894865036011</t>
@@ -2147,19 +2147,19 @@
     <t xml:space="preserve">11.2765636444092</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4507188796997</t>
+    <t xml:space="preserve">11.4507179260254</t>
   </si>
   <si>
     <t xml:space="preserve">12.0167245864868</t>
   </si>
   <si>
-    <t xml:space="preserve">12.060263633728</t>
+    <t xml:space="preserve">12.0602626800537</t>
   </si>
   <si>
     <t xml:space="preserve">12.5011930465698</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0100746154785</t>
+    <t xml:space="preserve">12.0100736618042</t>
   </si>
   <si>
     <t xml:space="preserve">11.831485748291</t>
@@ -2174,31 +2174,31 @@
     <t xml:space="preserve">11.2064275741577</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4296627044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6082496643066</t>
+    <t xml:space="preserve">11.4296636581421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.608250617981</t>
   </si>
   <si>
     <t xml:space="preserve">11.2510738372803</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5813674926758</t>
+    <t xml:space="preserve">10.5813665390015</t>
   </si>
   <si>
     <t xml:space="preserve">10.5367202758789</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0278387069702</t>
+    <t xml:space="preserve">11.0278377532959</t>
   </si>
   <si>
     <t xml:space="preserve">10.8938961029053</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1617784500122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0724849700928</t>
+    <t xml:space="preserve">11.1617794036865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0724859237671</t>
   </si>
   <si>
     <t xml:space="preserve">11.9207811355591</t>
@@ -2225,10 +2225,10 @@
     <t xml:space="preserve">11.7868385314941</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0993700027466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4387826919556</t>
+    <t xml:space="preserve">12.0993690490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4387817382812</t>
   </si>
   <si>
     <t xml:space="preserve">13.4834299087524</t>
@@ -2237,22 +2237,22 @@
     <t xml:space="preserve">13.9299011230469</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8406066894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0191946029663</t>
+    <t xml:space="preserve">13.8406057357788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0191955566406</t>
   </si>
   <si>
     <t xml:space="preserve">12.9030170440674</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0816059112549</t>
+    <t xml:space="preserve">13.0816049575806</t>
   </si>
   <si>
     <t xml:space="preserve">13.0369596481323</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7513113021851</t>
+    <t xml:space="preserve">13.7513122558594</t>
   </si>
   <si>
     <t xml:space="preserve">13.7959594726562</t>
@@ -2261,10 +2261,10 @@
     <t xml:space="preserve">13.3941354751587</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9745473861694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2601947784424</t>
+    <t xml:space="preserve">13.9745483398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2601957321167</t>
   </si>
   <si>
     <t xml:space="preserve">13.6620178222656</t>
@@ -2276,13 +2276,13 @@
     <t xml:space="preserve">13.88525390625</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6442537307739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7781963348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9121370315552</t>
+    <t xml:space="preserve">14.6442546844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7781953811646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9121379852295</t>
   </si>
   <si>
     <t xml:space="preserve">15.0907249450684</t>
@@ -2294,16 +2294,16 @@
     <t xml:space="preserve">14.4210186004639</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5103139877319</t>
+    <t xml:space="preserve">14.5103130340576</t>
   </si>
   <si>
     <t xml:space="preserve">15.1800212860107</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8497266769409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8050813674927</t>
+    <t xml:space="preserve">15.8497276306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.805079460144</t>
   </si>
   <si>
     <t xml:space="preserve">16.072961807251</t>
@@ -2315,7 +2315,7 @@
     <t xml:space="preserve">16.9212589263916</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1891384124756</t>
+    <t xml:space="preserve">17.1891403198242</t>
   </si>
   <si>
     <t xml:space="preserve">16.7426681518555</t>
@@ -2324,7 +2324,7 @@
     <t xml:space="preserve">17.7249069213867</t>
   </si>
   <si>
-    <t xml:space="preserve">17.769552230835</t>
+    <t xml:space="preserve">17.7695503234863</t>
   </si>
   <si>
     <t xml:space="preserve">17.8142013549805</t>
@@ -2339,7 +2339,7 @@
     <t xml:space="preserve">18.12672996521</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3946132659912</t>
+    <t xml:space="preserve">18.3946113586426</t>
   </si>
   <si>
     <t xml:space="preserve">18.5732002258301</t>
@@ -2357,22 +2357,22 @@
     <t xml:space="preserve">18.2160243988037</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9481430053711</t>
+    <t xml:space="preserve">17.9481410980225</t>
   </si>
   <si>
     <t xml:space="preserve">19.0196723937988</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1805000305176</t>
+    <t xml:space="preserve">20.1804981231689</t>
   </si>
   <si>
     <t xml:space="preserve">20.5376739501953</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6269702911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9841442108154</t>
+    <t xml:space="preserve">20.6269683837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9841461181641</t>
   </si>
   <si>
     <t xml:space="preserve">20.8055553436279</t>
@@ -2384,19 +2384,19 @@
     <t xml:space="preserve">20.0912036895752</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0019092559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8233222961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2697944641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1982612609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9126148223877</t>
+    <t xml:space="preserve">20.0019111633301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8233203887939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2697925567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1982593536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9126129150391</t>
   </si>
   <si>
     <t xml:space="preserve">19.5554389953613</t>
@@ -2405,28 +2405,28 @@
     <t xml:space="preserve">19.6447315216064</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9303798675537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7162628173828</t>
+    <t xml:space="preserve">18.9303779602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7162647247314</t>
   </si>
   <si>
     <t xml:space="preserve">20.4483814239502</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4306144714355</t>
+    <t xml:space="preserve">21.4306182861328</t>
   </si>
   <si>
     <t xml:space="preserve">21.3413219451904</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3235569000244</t>
+    <t xml:space="preserve">22.323558807373</t>
   </si>
   <si>
     <t xml:space="preserve">21.6092052459717</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0556774139404</t>
+    <t xml:space="preserve">22.0556755065918</t>
   </si>
   <si>
     <t xml:space="preserve">21.7877922058105</t>
@@ -2444,7 +2444,7 @@
     <t xml:space="preserve">24.0020771026611</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8195533752441</t>
+    <t xml:space="preserve">23.8195514678955</t>
   </si>
   <si>
     <t xml:space="preserve">24.5496520996094</t>
@@ -2459,7 +2459,7 @@
     <t xml:space="preserve">24.0933380126953</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7321796417236</t>
+    <t xml:space="preserve">24.732177734375</t>
   </si>
   <si>
     <t xml:space="preserve">24.3671283721924</t>
@@ -2480,7 +2480,7 @@
     <t xml:space="preserve">24.2758655548096</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7282867431641</t>
+    <t xml:space="preserve">23.7282886505127</t>
   </si>
   <si>
     <t xml:space="preserve">24.1846008300781</t>
@@ -2504,10 +2504,10 @@
     <t xml:space="preserve">23.4545021057129</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0894508361816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1807117462158</t>
+    <t xml:space="preserve">23.089448928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1807136535645</t>
   </si>
   <si>
     <t xml:space="preserve">22.9069271087646</t>
@@ -2516,10 +2516,10 @@
     <t xml:space="preserve">22.1768226623535</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5418758392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9943008422852</t>
+    <t xml:space="preserve">22.5418739318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9942989349365</t>
   </si>
   <si>
     <t xml:space="preserve">22.0855617523193</t>
@@ -2546,10 +2546,10 @@
     <t xml:space="preserve">19.0738945007324</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8952560424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8039970397949</t>
+    <t xml:space="preserve">19.8952579498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8039951324463</t>
   </si>
   <si>
     <t xml:space="preserve">19.6214694976807</t>
@@ -2558,13 +2558,13 @@
     <t xml:space="preserve">19.7127323150635</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0816745758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6409149169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3710155487061</t>
+    <t xml:space="preserve">21.081672668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6409168243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3710174560547</t>
   </si>
   <si>
     <t xml:space="preserve">26.3749046325684</t>
@@ -2573,16 +2573,16 @@
     <t xml:space="preserve">25.6448059082031</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9185905456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8273296356201</t>
+    <t xml:space="preserve">25.9185924530029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8273277282715</t>
   </si>
   <si>
     <t xml:space="preserve">25.5535411834717</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2797546386719</t>
+    <t xml:space="preserve">25.2797527313232</t>
   </si>
   <si>
     <t xml:space="preserve">23.3632392883301</t>
@@ -2591,10 +2591,10 @@
     <t xml:space="preserve">22.4506130218506</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6292495727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9904079437256</t>
+    <t xml:space="preserve">21.6292476654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9904098510742</t>
   </si>
   <si>
     <t xml:space="preserve">21.264196395874</t>
@@ -2609,16 +2609,16 @@
     <t xml:space="preserve">20.80788230896</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4428329467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9030342102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6331367492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3515701293945</t>
+    <t xml:space="preserve">20.442834854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9030361175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6331386566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3515682220459</t>
   </si>
   <si>
     <t xml:space="preserve">20.1690464019775</t>
@@ -2627,10 +2627,10 @@
     <t xml:space="preserve">19.3476829528809</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1651554107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2525291442871</t>
+    <t xml:space="preserve">19.1651573181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2525310516357</t>
   </si>
   <si>
     <t xml:space="preserve">18.6175804138184</t>
@@ -2648,7 +2648,7 @@
     <t xml:space="preserve">16.2447509765625</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5185413360596</t>
+    <t xml:space="preserve">16.5185394287109</t>
   </si>
   <si>
     <t xml:space="preserve">16.6098022460938</t>
@@ -2657,19 +2657,19 @@
     <t xml:space="preserve">16.7010650634766</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6593246459961</t>
+    <t xml:space="preserve">17.6593227386475</t>
   </si>
   <si>
     <t xml:space="preserve">17.2486400604248</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3437938690186</t>
+    <t xml:space="preserve">18.3437919616699</t>
   </si>
   <si>
     <t xml:space="preserve">18.800106048584</t>
   </si>
   <si>
-    <t xml:space="preserve">19.256420135498</t>
+    <t xml:space="preserve">19.2564182281494</t>
   </si>
   <si>
     <t xml:space="preserve">18.982629776001</t>
@@ -2687,13 +2687,13 @@
     <t xml:space="preserve">21.7661418914795</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8574066162109</t>
+    <t xml:space="preserve">21.8574047088623</t>
   </si>
   <si>
     <t xml:space="preserve">22.3137187957764</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9486656188965</t>
+    <t xml:space="preserve">21.9486675262451</t>
   </si>
   <si>
     <t xml:space="preserve">22.0399284362793</t>
@@ -70544,7 +70544,7 @@
     </row>
     <row r="2554">
       <c r="A2554" s="1" t="n">
-        <v>46042.6911342593</v>
+        <v>46042.3333333333</v>
       </c>
       <c r="B2554" t="n">
         <v>40818</v>
@@ -70553,7 +70553,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="D2554" t="n">
-        <v>13.5</v>
+        <v>13.3999996185303</v>
       </c>
       <c r="E2554" t="n">
         <v>13.6999998092651</v>
@@ -70565,6 +70565,32 @@
         <v>1271</v>
       </c>
       <c r="H2554" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2555">
+      <c r="A2555" s="1" t="n">
+        <v>46043.6910300926</v>
+      </c>
+      <c r="B2555" t="n">
+        <v>14289</v>
+      </c>
+      <c r="C2555" t="n">
+        <v>13.6000003814697</v>
+      </c>
+      <c r="D2555" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="E2555" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F2555" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="G2555" t="s">
+        <v>1269</v>
+      </c>
+      <c r="H2555" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SAB.MI.xlsx
+++ b/data/SAB.MI.xlsx
@@ -38,115 +38,115 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56568145751953</t>
+    <t xml:space="preserve">8.56568050384521</t>
   </si>
   <si>
     <t xml:space="preserve">SAB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61823081970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4831018447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33296012878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37049579620361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31794357299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.257887840271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16029357910156</t>
+    <t xml:space="preserve">8.61822986602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48310089111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33295726776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3704948425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31794452667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25788593292236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16029262542725</t>
   </si>
   <si>
     <t xml:space="preserve">7.88252830505371</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52969121932983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66482067108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62728452682495</t>
+    <t xml:space="preserve">7.52969169616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66481971740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62728357315063</t>
   </si>
   <si>
     <t xml:space="preserve">7.61227035522461</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73989343643188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75490713119507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76992034912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89754390716553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61977672576904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79994964599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72487640380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65731191635132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50716924667358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34201240539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54470586776733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39080810546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58224248886108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82246971130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08522319793701</t>
+    <t xml:space="preserve">7.73989152908325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75490522384644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76992225646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89754343032837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61977624893188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79995012283325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72487783432007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65731287002563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50717067718506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34201192855835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54470491409302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39080858230591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58224201202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82247018814087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0852222442627</t>
   </si>
   <si>
     <t xml:space="preserve">8.1152515411377</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95760011672974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06270027160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03267192840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92006397247314</t>
+    <t xml:space="preserve">7.95759963989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06269931793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03267097473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92006492614746</t>
   </si>
   <si>
     <t xml:space="preserve">7.77742719650269</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86751365661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80745649337769</t>
+    <t xml:space="preserve">7.86751270294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80745601654053</t>
   </si>
   <si>
     <t xml:space="preserve">7.98762941360474</t>
@@ -158,139 +158,139 @@
     <t xml:space="preserve">7.99513626098633</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96510601043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90504884719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93507766723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89003705978394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94258642196655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82997846603394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81496334075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73238515853882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64980602264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71737146377563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67232847213745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63479232788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51467657089233</t>
+    <t xml:space="preserve">7.96510696411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90505027770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93507814407349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8900351524353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94258689880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82997798919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81496286392212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7323842048645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64980554580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71737003326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67232704162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6347918510437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51467752456665</t>
   </si>
   <si>
     <t xml:space="preserve">7.64229917526245</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56722593307495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70235633850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74739933013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46963500976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69484853744507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49215602874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47338724136353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43585109710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50341749191284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48089408874512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59725666046143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4283447265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38705492019653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37204122543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31949043273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28195428848267</t>
+    <t xml:space="preserve">7.56722688674927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70235681533813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.747398853302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46963453292847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69484901428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49215507507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47338771820068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43585205078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50341606140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48089647293091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59725618362427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42834520339966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38705539703369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37204027175903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31949090957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28195476531982</t>
   </si>
   <si>
     <t xml:space="preserve">7.52122163772583</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80533933639526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75009393692017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75798606872559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81323146820068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8605842590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69879627227783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58435821533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68695545196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57646751403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53700590133667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49754476547241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28445768356323</t>
+    <t xml:space="preserve">7.80533981323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75009298324585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75798654556274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81323003768921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86058473587036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69879484176636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58435869216919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68695640563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57646703720093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53700733184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49754524230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28445672988892</t>
   </si>
   <si>
     <t xml:space="preserve">6.92536401748657</t>
   </si>
   <si>
-    <t xml:space="preserve">7.079261302948</t>
+    <t xml:space="preserve">7.07926082611084</t>
   </si>
   <si>
     <t xml:space="preserve">7.22921228408813</t>
@@ -302,217 +302,217 @@
     <t xml:space="preserve">7.26078081130981</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37127161026001</t>
+    <t xml:space="preserve">7.37127113342285</t>
   </si>
   <si>
     <t xml:space="preserve">7.2647271156311</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34759473800659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46992301940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36732482910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37916326522827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1345067024231</t>
+    <t xml:space="preserve">7.34759521484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46992349624634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36732387542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37916278839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13450622558594</t>
   </si>
   <si>
     <t xml:space="preserve">7.18975067138672</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10293674468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15029191970825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10688447952271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20553636550903</t>
+    <t xml:space="preserve">7.10293817520142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15029048919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10688304901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20553541183472</t>
   </si>
   <si>
     <t xml:space="preserve">7.18185901641846</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22132062911987</t>
+    <t xml:space="preserve">7.22131967544556</t>
   </si>
   <si>
     <t xml:space="preserve">7.19369745254517</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24894332885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19764518737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18580484390259</t>
+    <t xml:space="preserve">7.24894285202026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19764280319214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18580436706543</t>
   </si>
   <si>
     <t xml:space="preserve">7.22526550292969</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20948123931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31602668762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21342897415161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16607475280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24499750137329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13055992126465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11082887649536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17791414260864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23315763473511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2765645980835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30024147033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29234981536865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.241051197052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11872243881226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09504461288452</t>
+    <t xml:space="preserve">7.20948266983032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3160252571106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21342945098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16607522964478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24499654769897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13056039810181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11082983016968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17791318893433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23315811157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27656555175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30024194717407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29234838485718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24105024337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11872291564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09504652023315</t>
   </si>
   <si>
     <t xml:space="preserve">7.00428628921509</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9450945854187</t>
+    <t xml:space="preserve">6.94509506225586</t>
   </si>
   <si>
     <t xml:space="preserve">6.93325662612915</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09899234771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15423727035522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13845157623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15818214416504</t>
+    <t xml:space="preserve">7.09899044036865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15423631668091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1384539604187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1581826210022</t>
   </si>
   <si>
     <t xml:space="preserve">7.05558443069458</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07136917114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06742286682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02401638031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04769325256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06347608566284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08320760726929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05163860321045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04374647140503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03190851211548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05952930450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03585338592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1739673614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90563344955444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91352653503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93720293045044</t>
+    <t xml:space="preserve">7.07136869430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06742238998413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02401542663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04769229888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06347703933716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08320808410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05163955688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04374742507935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03190755844116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05953073501587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03585481643677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17396831512451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9056339263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91352605819702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93720149993896</t>
   </si>
   <si>
     <t xml:space="preserve">6.92141819000244</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94114875793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96877145767212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14239931106567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45019197463989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79350137710571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92372274398804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04999542236328</t>
+    <t xml:space="preserve">6.94114828109741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96877098083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14239740371704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45019245147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79349994659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92372179031372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04999732971191</t>
   </si>
   <si>
     <t xml:space="preserve">8.20783805847168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16837882995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08945846557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19994735717773</t>
+    <t xml:space="preserve">8.16837787628174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08945655822754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19994831085205</t>
   </si>
   <si>
     <t xml:space="preserve">8.06578063964844</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1289176940918</t>
+    <t xml:space="preserve">8.12891864776611</t>
   </si>
   <si>
     <t xml:space="preserve">8.17627048492432</t>
@@ -521,34 +521,34 @@
     <t xml:space="preserve">8.32622146606445</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55509376525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56298637390137</t>
+    <t xml:space="preserve">8.55509471893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56298542022705</t>
   </si>
   <si>
     <t xml:space="preserve">8.42881870269775</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35778999328613</t>
+    <t xml:space="preserve">8.35778903961182</t>
   </si>
   <si>
     <t xml:space="preserve">8.39725112915039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42092609405518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44460391998291</t>
+    <t xml:space="preserve">8.42092800140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44460201263428</t>
   </si>
   <si>
     <t xml:space="preserve">8.40514183044434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26308441162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18416404724121</t>
+    <t xml:space="preserve">8.26308536529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18416213989258</t>
   </si>
   <si>
     <t xml:space="preserve">8.30254554748535</t>
@@ -557,7 +557,7 @@
     <t xml:space="preserve">8.22362327575684</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2867603302002</t>
+    <t xml:space="preserve">8.28676128387451</t>
   </si>
   <si>
     <t xml:space="preserve">8.25519180297852</t>
@@ -569,7 +569,7 @@
     <t xml:space="preserve">8.3104362487793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36568164825439</t>
+    <t xml:space="preserve">8.36568260192871</t>
   </si>
   <si>
     <t xml:space="preserve">8.33411407470703</t>
@@ -581,64 +581,64 @@
     <t xml:space="preserve">8.46038818359375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62612438201904</t>
+    <t xml:space="preserve">8.62612342834473</t>
   </si>
   <si>
     <t xml:space="preserve">8.74450492858887</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88656616210938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0049467086792</t>
+    <t xml:space="preserve">8.88656520843506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00494575500488</t>
   </si>
   <si>
     <t xml:space="preserve">9.23381900787354</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30484771728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26538848876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1627893447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19435787200928</t>
+    <t xml:space="preserve">9.30484676361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2653865814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16279029846191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19435691833496</t>
   </si>
   <si>
     <t xml:space="preserve">9.24960422515869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29695510864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36798667907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54950523376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67578029632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74680805206299</t>
+    <t xml:space="preserve">9.29695606231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36798572540283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54950618743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67577934265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74680995941162</t>
   </si>
   <si>
     <t xml:space="preserve">10.2203388214111</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4807786941528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4571027755737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2913675308228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2597970962524</t>
+    <t xml:space="preserve">10.4807796478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.457103729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2913684844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2597999572754</t>
   </si>
   <si>
     <t xml:space="preserve">10.1493082046509</t>
@@ -647,13 +647,13 @@
     <t xml:space="preserve">10.0861721038818</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0151424407959</t>
+    <t xml:space="preserve">10.0151414871216</t>
   </si>
   <si>
     <t xml:space="preserve">10.1019554138184</t>
   </si>
   <si>
-    <t xml:space="preserve">10.165093421936</t>
+    <t xml:space="preserve">10.1650924682617</t>
   </si>
   <si>
     <t xml:space="preserve">10.0546035766602</t>
@@ -662,7 +662,7 @@
     <t xml:space="preserve">10.1808776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1177406311035</t>
+    <t xml:space="preserve">10.1177396774292</t>
   </si>
   <si>
     <t xml:space="preserve">10.1887693405151</t>
@@ -671,106 +671,106 @@
     <t xml:space="preserve">10.070387840271</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1098489761353</t>
+    <t xml:space="preserve">10.1098499298096</t>
   </si>
   <si>
     <t xml:space="preserve">10.0230340957642</t>
   </si>
   <si>
-    <t xml:space="preserve">10.496563911438</t>
+    <t xml:space="preserve">10.4965629577637</t>
   </si>
   <si>
     <t xml:space="preserve">10.4176406860352</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3150424957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7333288192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4492101669312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5597009658813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6386222839355</t>
+    <t xml:space="preserve">10.3150434494019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7333278656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4492092132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.559700012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6386213302612</t>
   </si>
   <si>
     <t xml:space="preserve">10.5912704467773</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0095529556274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8832788467407</t>
+    <t xml:space="preserve">11.0095520019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.883279800415</t>
   </si>
   <si>
     <t xml:space="preserve">11.3410234451294</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0592098236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9171533584595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0513181686401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6882791519165</t>
+    <t xml:space="preserve">12.059211730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9171504974365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0513172149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6882801055908</t>
   </si>
   <si>
     <t xml:space="preserve">11.6803865432739</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2644052505493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6274452209473</t>
+    <t xml:space="preserve">12.2644062042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6274442672729</t>
   </si>
   <si>
     <t xml:space="preserve">12.5406312942505</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6747980117798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7379341125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4728555679321</t>
+    <t xml:space="preserve">12.6747970581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7379350662231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4728546142578</t>
   </si>
   <si>
     <t xml:space="preserve">12.6518526077271</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8471231460571</t>
+    <t xml:space="preserve">12.8471221923828</t>
   </si>
   <si>
     <t xml:space="preserve">12.8145780563354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9203500747681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8715305328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9366207122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8064422607422</t>
+    <t xml:space="preserve">12.9203491210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8715324401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.936619758606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8064413070679</t>
   </si>
   <si>
     <t xml:space="preserve">12.6437168121338</t>
   </si>
   <si>
-    <t xml:space="preserve">12.822714805603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5209159851074</t>
+    <t xml:space="preserve">12.8227138519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5209140777588</t>
   </si>
   <si>
     <t xml:space="preserve">11.8463659286499</t>
@@ -782,16 +782,16 @@
     <t xml:space="preserve">11.9114561080933</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9277267456055</t>
+    <t xml:space="preserve">11.9277276992798</t>
   </si>
   <si>
     <t xml:space="preserve">11.9602727890015</t>
   </si>
   <si>
-    <t xml:space="preserve">11.805685043335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1311340332031</t>
+    <t xml:space="preserve">11.8056840896606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1311321258545</t>
   </si>
   <si>
     <t xml:space="preserve">12.0009546279907</t>
@@ -809,22 +809,22 @@
     <t xml:space="preserve">11.9765462875366</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8789119720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7161865234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4720983505249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5534620285034</t>
+    <t xml:space="preserve">11.8789100646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7161855697632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4720993041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5534610748291</t>
   </si>
   <si>
     <t xml:space="preserve">11.5860052108765</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7975482940674</t>
+    <t xml:space="preserve">11.7975492477417</t>
   </si>
   <si>
     <t xml:space="preserve">11.8951826095581</t>
@@ -833,22 +833,22 @@
     <t xml:space="preserve">12.0904521942139</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1636781692505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0741806030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2287693023682</t>
+    <t xml:space="preserve">12.1636800765991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.074179649353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2287683486938</t>
   </si>
   <si>
     <t xml:space="preserve">12.1392698287964</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2043609619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1880865097046</t>
+    <t xml:space="preserve">12.2043600082397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1880874633789</t>
   </si>
   <si>
     <t xml:space="preserve">12.147406578064</t>
@@ -857,34 +857,34 @@
     <t xml:space="preserve">12.2531785964966</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3670854568481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4077644348145</t>
+    <t xml:space="preserve">12.3670864105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4077663421631</t>
   </si>
   <si>
     <t xml:space="preserve">12.448447227478</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9447584152222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7820339202881</t>
+    <t xml:space="preserve">12.9447574615479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7820329666138</t>
   </si>
   <si>
     <t xml:space="preserve">12.8959398269653</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0098476409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9528951644897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8552598953247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7332143783569</t>
+    <t xml:space="preserve">13.0098466873169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9528932571411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8552579879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7332153320312</t>
   </si>
   <si>
     <t xml:space="preserve">12.7738962173462</t>
@@ -893,25 +893,25 @@
     <t xml:space="preserve">12.9854393005371</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2620706558228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.685154914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9292440414429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9943342208862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7502470016479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.815333366394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8316078186035</t>
+    <t xml:space="preserve">13.2620697021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6851568222046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9292421340942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9943332672119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.750244140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8153343200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8316087722778</t>
   </si>
   <si>
     <t xml:space="preserve">14.018741607666</t>
@@ -920,28 +920,28 @@
     <t xml:space="preserve">14.0268783569336</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1814651489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1570587158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2302837371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.775411605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3205404281616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2961301803589</t>
+    <t xml:space="preserve">14.1814680099487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1570568084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.230281829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7754125595093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3205413818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2961292266846</t>
   </si>
   <si>
     <t xml:space="preserve">15.4588556289673</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8249864578247</t>
+    <t xml:space="preserve">15.8249883651733</t>
   </si>
   <si>
     <t xml:space="preserve">15.7924432754517</t>
@@ -959,58 +959,58 @@
     <t xml:space="preserve">15.5158090591431</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0039825439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2643413543701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.776927947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9559230804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4115524291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0454216003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0787258148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6475048065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0217704772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0543193817139</t>
+    <t xml:space="preserve">16.0039863586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2643432617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7769298553467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.955924987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4115505218506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0454254150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0787239074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6475067138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0217685699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0543174743652</t>
   </si>
   <si>
     <t xml:space="preserve">18.1275444030762</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2984027862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4123096466064</t>
+    <t xml:space="preserve">18.2984046936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4123134613037</t>
   </si>
   <si>
     <t xml:space="preserve">18.1682243347168</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1600894927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9160003662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.265100479126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0861015319824</t>
+    <t xml:space="preserve">18.1600875854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9159984588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2651023864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0861034393311</t>
   </si>
   <si>
     <t xml:space="preserve">17.2976455688477</t>
@@ -1028,7 +1028,7 @@
     <t xml:space="preserve">17.0779685974121</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8664264678955</t>
+    <t xml:space="preserve">16.8664245605469</t>
   </si>
   <si>
     <t xml:space="preserve">16.785062789917</t>
@@ -1037,28 +1037,28 @@
     <t xml:space="preserve">16.988468170166</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5979270935059</t>
+    <t xml:space="preserve">16.5979309082031</t>
   </si>
   <si>
     <t xml:space="preserve">16.9152431488037</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8338813781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9640598297119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8826999664307</t>
+    <t xml:space="preserve">16.8338794708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9640617370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8826961517334</t>
   </si>
   <si>
     <t xml:space="preserve">16.9233779907227</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1349201202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0698318481445</t>
+    <t xml:space="preserve">17.1349220275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0698299407959</t>
   </si>
   <si>
     <t xml:space="preserve">17.1674671173096</t>
@@ -1073,13 +1073,13 @@
     <t xml:space="preserve">18.8598041534424</t>
   </si>
   <si>
-    <t xml:space="preserve">19.06321144104</t>
+    <t xml:space="preserve">19.0632095336914</t>
   </si>
   <si>
     <t xml:space="preserve">18.7052154541016</t>
   </si>
   <si>
-    <t xml:space="preserve">18.631986618042</t>
+    <t xml:space="preserve">18.6319885253906</t>
   </si>
   <si>
     <t xml:space="preserve">18.7377605438232</t>
@@ -1088,7 +1088,7 @@
     <t xml:space="preserve">18.7133522033691</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5913105010986</t>
+    <t xml:space="preserve">18.59130859375</t>
   </si>
   <si>
     <t xml:space="preserve">18.3065395355225</t>
@@ -1097,16 +1097,16 @@
     <t xml:space="preserve">18.6157169342041</t>
   </si>
   <si>
-    <t xml:space="preserve">18.217041015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2089042663574</t>
+    <t xml:space="preserve">18.2170391082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2089061737061</t>
   </si>
   <si>
     <t xml:space="preserve">18.4611301422119</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5417308807373</t>
+    <t xml:space="preserve">17.5417327880859</t>
   </si>
   <si>
     <t xml:space="preserve">16.9071083068848</t>
@@ -1115,43 +1115,43 @@
     <t xml:space="preserve">16.4758853912354</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3945236206055</t>
+    <t xml:space="preserve">16.3945217132568</t>
   </si>
   <si>
     <t xml:space="preserve">16.1097526550293</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3619785308838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2806167602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3782520294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1992511749268</t>
+    <t xml:space="preserve">16.3619804382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2806186676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3782482147217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.199254989624</t>
   </si>
   <si>
     <t xml:space="preserve">16.2236633300781</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2724781036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.679292678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.313159942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0934810638428</t>
+    <t xml:space="preserve">16.2724800109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6792907714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3131618499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.09348487854</t>
   </si>
   <si>
     <t xml:space="preserve">15.9470300674438</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1911182403564</t>
+    <t xml:space="preserve">16.1911163330078</t>
   </si>
   <si>
     <t xml:space="preserve">16.3538417816162</t>
@@ -1160,25 +1160,25 @@
     <t xml:space="preserve">16.028392791748</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9144840240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.182225227356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9706811904907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1008625030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8730478286743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.222146987915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8478813171387</t>
+    <t xml:space="preserve">15.9144859313965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1822242736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.970682144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1008615493774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8730497360229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2221479415894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8478803634644</t>
   </si>
   <si>
     <t xml:space="preserve">14.8893184661865</t>
@@ -1187,160 +1187,160 @@
     <t xml:space="preserve">15.1984968185425</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3937683105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5402173995972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9381380081177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.59641456604</t>
+    <t xml:space="preserve">15.3937664031982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5402202606201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.938136100769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5964136123657</t>
   </si>
   <si>
     <t xml:space="preserve">14.4011459350586</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2058753967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1082401275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0594215393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9129695892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0106039047241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3197822570801</t>
+    <t xml:space="preserve">14.2058734893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1082410812378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0594234466553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.912971496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0106048583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3197832107544</t>
   </si>
   <si>
     <t xml:space="preserve">14.6452322006226</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7428684234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7265939712524</t>
+    <t xml:space="preserve">14.7428665161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7265930175781</t>
   </si>
   <si>
     <t xml:space="preserve">15.2147693634033</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8079566955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8567762374878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9544067382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7916841506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2709655761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0032253265381</t>
+    <t xml:space="preserve">14.8079557418823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8567743301392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9544095993042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7916870117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2709646224976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0032272338867</t>
   </si>
   <si>
     <t xml:space="preserve">14.4825067520142</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9218635559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9055910110474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0194997787476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0520429611206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2562046051025</t>
+    <t xml:space="preserve">14.9218626022339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9055919647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0194988250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0520448684692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2562065124512</t>
   </si>
   <si>
     <t xml:space="preserve">15.7354879379272</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8168516159058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6215801239014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9307594299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6866722106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7192144393921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7029418945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6704006195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6053066253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5653514862061</t>
+    <t xml:space="preserve">15.8168506622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6215810775757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9307565689087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.686671257019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7192163467407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7029428482056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6703977584839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6053075790405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5653505325317</t>
   </si>
   <si>
     <t xml:space="preserve">14.9956827163696</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0291938781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0627021789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2470073699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2302522659302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5318412780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7161464691162</t>
+    <t xml:space="preserve">15.0291919708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0627040863037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2470064163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2302551269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5318403244019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7161445617676</t>
   </si>
   <si>
     <t xml:space="preserve">15.8669404983521</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5821075439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4983291625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4815769195557</t>
+    <t xml:space="preserve">15.5821084976196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4983320236206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.481575012207</t>
   </si>
   <si>
     <t xml:space="preserve">15.4145574569702</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1799898147583</t>
+    <t xml:space="preserve">15.1799869537354</t>
   </si>
   <si>
     <t xml:space="preserve">15.0794582366943</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1129674911499</t>
+    <t xml:space="preserve">15.1129693984985</t>
   </si>
   <si>
     <t xml:space="preserve">14.3589935302734</t>
@@ -1349,16 +1349,16 @@
     <t xml:space="preserve">14.291974067688</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2584657669067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4595241546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4092607498169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5600547790527</t>
+    <t xml:space="preserve">14.2584648132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4595232009888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4092597961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5600528717041</t>
   </si>
   <si>
     <t xml:space="preserve">13.4039621353149</t>
@@ -1367,7 +1367,7 @@
     <t xml:space="preserve">13.4877376556396</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2364120483398</t>
+    <t xml:space="preserve">13.2364110946655</t>
   </si>
   <si>
     <t xml:space="preserve">13.5380020141602</t>
@@ -1376,28 +1376,28 @@
     <t xml:space="preserve">13.4374732971191</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1914463043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5882663726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.688796043396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4207162857056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5212459564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5715112686157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3201875686646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1526384353638</t>
+    <t xml:space="preserve">14.191445350647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5882654190063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6887969970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4207172393799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5212469100952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.57151222229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3201856613159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1526374816895</t>
   </si>
   <si>
     <t xml:space="preserve">13.1861476898193</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">13.3034324645996</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8510484695435</t>
+    <t xml:space="preserve">12.8510494232178</t>
   </si>
   <si>
     <t xml:space="preserve">12.683500289917</t>
@@ -1418,16 +1418,16 @@
     <t xml:space="preserve">12.5662145614624</t>
   </si>
   <si>
-    <t xml:space="preserve">12.901312828064</t>
+    <t xml:space="preserve">12.9013137817383</t>
   </si>
   <si>
     <t xml:space="preserve">12.8342933654785</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4824390411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1473407745361</t>
+    <t xml:space="preserve">12.482439994812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1473417282104</t>
   </si>
   <si>
     <t xml:space="preserve">12.0803213119507</t>
@@ -1436,19 +1436,19 @@
     <t xml:space="preserve">12.0635662078857</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9797916412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5609178543091</t>
+    <t xml:space="preserve">11.979790687561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5609169006348</t>
   </si>
   <si>
     <t xml:space="preserve">11.1923084259033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2258186340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4321756362915</t>
+    <t xml:space="preserve">11.2258176803589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4321746826172</t>
   </si>
   <si>
     <t xml:space="preserve">13.1191272735596</t>
@@ -1457,22 +1457,22 @@
     <t xml:space="preserve">13.2531681060791</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2866773605347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7672748565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3536968231201</t>
+    <t xml:space="preserve">13.286678314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7672729492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3536977767944</t>
   </si>
   <si>
     <t xml:space="preserve">12.9850883483887</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8007841110229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6332349777222</t>
+    <t xml:space="preserve">12.8007850646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6332340240479</t>
   </si>
   <si>
     <t xml:space="preserve">12.8678035736084</t>
@@ -1481,28 +1481,28 @@
     <t xml:space="preserve">11.8122425079346</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6279373168945</t>
+    <t xml:space="preserve">11.6279363632202</t>
   </si>
   <si>
     <t xml:space="preserve">11.6111822128296</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7284679412842</t>
+    <t xml:space="preserve">11.7284669876099</t>
   </si>
   <si>
     <t xml:space="preserve">11.9630355834961</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8960161209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6614465713501</t>
+    <t xml:space="preserve">11.896017074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6614475250244</t>
   </si>
   <si>
     <t xml:space="preserve">11.0750246047974</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0415153503418</t>
+    <t xml:space="preserve">11.0415143966675</t>
   </si>
   <si>
     <t xml:space="preserve">10.9577388763428</t>
@@ -1514,13 +1514,13 @@
     <t xml:space="preserve">10.9242296218872</t>
   </si>
   <si>
-    <t xml:space="preserve">10.974494934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7117109298706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3651552200317</t>
+    <t xml:space="preserve">10.9744930267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7117128372192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3651561737061</t>
   </si>
   <si>
     <t xml:space="preserve">11.4603881835938</t>
@@ -1532,25 +1532,25 @@
     <t xml:space="preserve">11.1252889633179</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1755533218384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.376612663269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2311162948608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3986644744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9295272827148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7954874038696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.87926197052</t>
+    <t xml:space="preserve">11.1755542755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3766136169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2311153411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3986654281616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9295263290405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7954864501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8792610168457</t>
   </si>
   <si>
     <t xml:space="preserve">12.197606086731</t>
@@ -1559,10 +1559,10 @@
     <t xml:space="preserve">12.2478704452515</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0132999420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1305847167969</t>
+    <t xml:space="preserve">12.0133018493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1305856704712</t>
   </si>
   <si>
     <t xml:space="preserve">12.1808500289917</t>
@@ -1574,13 +1574,13 @@
     <t xml:space="preserve">12.3316459655762</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4656848907471</t>
+    <t xml:space="preserve">12.4656858444214</t>
   </si>
   <si>
     <t xml:space="preserve">12.5997247695923</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7170095443726</t>
+    <t xml:space="preserve">12.7170104980469</t>
   </si>
   <si>
     <t xml:space="preserve">12.884557723999</t>
@@ -1592,34 +1592,34 @@
     <t xml:space="preserve">12.9683332443237</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2029037475586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7337627410889</t>
+    <t xml:space="preserve">13.2029027938843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7337656021118</t>
   </si>
   <si>
     <t xml:space="preserve">12.8175392150879</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6499900817871</t>
+    <t xml:space="preserve">12.6499891281128</t>
   </si>
   <si>
     <t xml:space="preserve">12.7002534866333</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5159492492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.784029006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0018434524536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0353536605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5494585037231</t>
+    <t xml:space="preserve">12.5159482955933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7840280532837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0018424987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0353546142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5494594573975</t>
   </si>
   <si>
     <t xml:space="preserve">12.9348230361938</t>
@@ -1631,7 +1631,7 @@
     <t xml:space="preserve">13.38720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6217765808105</t>
+    <t xml:space="preserve">13.6217784881592</t>
   </si>
   <si>
     <t xml:space="preserve">13.8228359222412</t>
@@ -1640,34 +1640,34 @@
     <t xml:space="preserve">13.5044927597046</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4542274475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6385335922241</t>
+    <t xml:space="preserve">13.4542264938354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6385326385498</t>
   </si>
   <si>
     <t xml:space="preserve">13.7223052978516</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3704519271851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0521068572998</t>
+    <t xml:space="preserve">13.3704528808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0521078109741</t>
   </si>
   <si>
     <t xml:space="preserve">13.0185985565186</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1693925857544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1023740768433</t>
+    <t xml:space="preserve">13.1693935394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1023731231689</t>
   </si>
   <si>
     <t xml:space="preserve">12.499195098877</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7481784820557</t>
+    <t xml:space="preserve">12.7481775283813</t>
   </si>
   <si>
     <t xml:space="preserve">12.5740203857422</t>
@@ -1676,7 +1676,7 @@
     <t xml:space="preserve">12.3650350570679</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2257108688354</t>
+    <t xml:space="preserve">12.2257099151611</t>
   </si>
   <si>
     <t xml:space="preserve">12.2779579162598</t>
@@ -1685,7 +1685,7 @@
     <t xml:space="preserve">12.3127889633179</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2953720092773</t>
+    <t xml:space="preserve">12.295373916626</t>
   </si>
   <si>
     <t xml:space="preserve">12.3302030563354</t>
@@ -1694,22 +1694,22 @@
     <t xml:space="preserve">12.1212177276611</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5217742919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4869432449341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.452112197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1386318206787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0515556335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8948154449463</t>
+    <t xml:space="preserve">12.5217752456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4869441986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4521131515503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.138632774353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0515546798706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.894814491272</t>
   </si>
   <si>
     <t xml:space="preserve">12.2082958221436</t>
@@ -1724,7 +1724,7 @@
     <t xml:space="preserve">12.643684387207</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3998670578003</t>
+    <t xml:space="preserve">12.399866104126</t>
   </si>
   <si>
     <t xml:space="preserve">12.6262683868408</t>
@@ -1736,103 +1736,103 @@
     <t xml:space="preserve">12.8700857162476</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9745779037476</t>
+    <t xml:space="preserve">12.9745788574219</t>
   </si>
   <si>
     <t xml:space="preserve">12.95716381073</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9397478103638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7830085754395</t>
+    <t xml:space="preserve">12.9397468566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7830076217651</t>
   </si>
   <si>
     <t xml:space="preserve">12.6959295272827</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8004236221313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8874998092651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1560487747192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.034140586853</t>
+    <t xml:space="preserve">12.800422668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8875017166138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1560478210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0341396331787</t>
   </si>
   <si>
     <t xml:space="preserve">11.7206602096558</t>
   </si>
   <si>
-    <t xml:space="preserve">12.243127822876</t>
+    <t xml:space="preserve">12.243124961853</t>
   </si>
   <si>
     <t xml:space="preserve">11.7554912567139</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6684122085571</t>
+    <t xml:space="preserve">11.6684131622314</t>
   </si>
   <si>
     <t xml:space="preserve">11.9993085861206</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0689706802368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1038007736206</t>
+    <t xml:space="preserve">12.0689697265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1038017272949</t>
   </si>
   <si>
     <t xml:space="preserve">11.790322303772</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8425703048706</t>
+    <t xml:space="preserve">11.842568397522</t>
   </si>
   <si>
     <t xml:space="preserve">11.9470615386963</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8251523971558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8599834442139</t>
+    <t xml:space="preserve">11.8251533508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8599843978882</t>
   </si>
   <si>
     <t xml:space="preserve">11.7729063034058</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8774003982544</t>
+    <t xml:space="preserve">11.8773994445801</t>
   </si>
   <si>
     <t xml:space="preserve">11.6509981155396</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5465040206909</t>
+    <t xml:space="preserve">11.5465049743652</t>
   </si>
   <si>
     <t xml:space="preserve">11.3201026916504</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2156095504761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4071807861328</t>
+    <t xml:space="preserve">11.2156105041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4071798324585</t>
   </si>
   <si>
     <t xml:space="preserve">11.3026866912842</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3549327850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3897638320923</t>
+    <t xml:space="preserve">11.3549337387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3897647857666</t>
   </si>
   <si>
     <t xml:space="preserve">11.1981935501099</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9369611740112</t>
+    <t xml:space="preserve">10.9369602203369</t>
   </si>
   <si>
     <t xml:space="preserve">11.0414543151855</t>
@@ -1844,7 +1844,7 @@
     <t xml:space="preserve">10.8672981262207</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9717931747437</t>
+    <t xml:space="preserve">10.971791267395</t>
   </si>
   <si>
     <t xml:space="preserve">10.8324670791626</t>
@@ -1856,7 +1856,7 @@
     <t xml:space="preserve">10.6060657501221</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5886497497559</t>
+    <t xml:space="preserve">10.5886487960815</t>
   </si>
   <si>
     <t xml:space="preserve">10.5189876556396</t>
@@ -1865,16 +1865,16 @@
     <t xml:space="preserve">10.4493255615234</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6583118438721</t>
+    <t xml:space="preserve">10.6583127975464</t>
   </si>
   <si>
     <t xml:space="preserve">10.7802209854126</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1633625030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1111154556274</t>
+    <t xml:space="preserve">11.1633615493774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1111164093018</t>
   </si>
   <si>
     <t xml:space="preserve">11.0588684082031</t>
@@ -1883,70 +1883,70 @@
     <t xml:space="preserve">10.9892072677612</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8498830795288</t>
+    <t xml:space="preserve">10.8498821258545</t>
   </si>
   <si>
     <t xml:space="preserve">11.0240383148193</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0066232681274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7976350784302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8150520324707</t>
+    <t xml:space="preserve">11.0066242218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7976360321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8150510787964</t>
   </si>
   <si>
     <t xml:space="preserve">10.9543752670288</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0937004089355</t>
+    <t xml:space="preserve">11.0937013626099</t>
   </si>
   <si>
     <t xml:space="preserve">11.7032432556152</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9818916320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9296455383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9122314453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8077383041382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2605409622192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.086386680603</t>
+    <t xml:space="preserve">11.9818925857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9296464920044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9122323989868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8077373504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2605419158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0863876342773</t>
   </si>
   <si>
     <t xml:space="preserve">11.9644775390625</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5290899276733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4942579269409</t>
+    <t xml:space="preserve">11.529088973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4942569732666</t>
   </si>
   <si>
     <t xml:space="preserve">11.5813360214233</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4768438339233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.685830116272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1908807754517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.347620010376</t>
+    <t xml:space="preserve">11.476842880249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6858291625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1908798217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3476190567017</t>
   </si>
   <si>
     <t xml:space="preserve">11.5116729736328</t>
@@ -1958,19 +1958,19 @@
     <t xml:space="preserve">10.7105579376221</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70045757293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49146938323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03866672515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98641967773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42912197113037</t>
+    <t xml:space="preserve">9.70045852661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49147033691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03866767883301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98641872406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.429123878479</t>
   </si>
   <si>
     <t xml:space="preserve">8.18530464172363</t>
@@ -1985,10 +1985,10 @@
     <t xml:space="preserve">8.53361511230469</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49007606506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31592273712158</t>
+    <t xml:space="preserve">8.49007797241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31592178344727</t>
   </si>
   <si>
     <t xml:space="preserve">8.32462978363037</t>
@@ -2000,16 +2000,16 @@
     <t xml:space="preserve">8.38558387756348</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28979873657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41170597076416</t>
+    <t xml:space="preserve">8.28979778289795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41170692443848</t>
   </si>
   <si>
     <t xml:space="preserve">8.4987850189209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63810920715332</t>
+    <t xml:space="preserve">8.638108253479</t>
   </si>
   <si>
     <t xml:space="preserve">8.69035530090332</t>
@@ -2021,10 +2021,10 @@
     <t xml:space="preserve">8.79484939575195</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96900367736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75130939483643</t>
+    <t xml:space="preserve">8.96900463104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75131034851074</t>
   </si>
   <si>
     <t xml:space="preserve">8.70777130126953</t>
@@ -2039,25 +2039,25 @@
     <t xml:space="preserve">9.05608177185059</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14315891265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23023796081543</t>
+    <t xml:space="preserve">9.14316082000732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23023700714111</t>
   </si>
   <si>
     <t xml:space="preserve">9.40439319610596</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66562652587891</t>
+    <t xml:space="preserve">9.66562557220459</t>
   </si>
   <si>
     <t xml:space="preserve">9.57854843139648</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31731414794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88192558288574</t>
+    <t xml:space="preserve">9.31731510162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88192653656006</t>
   </si>
   <si>
     <t xml:space="preserve">8.65552425384521</t>
@@ -2066,34 +2066,34 @@
     <t xml:space="preserve">8.51620006561279</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60327816009521</t>
+    <t xml:space="preserve">8.60327911376953</t>
   </si>
   <si>
     <t xml:space="preserve">8.56844615936279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36085319519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83978080749512</t>
+    <t xml:space="preserve">9.36085414886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83978176116943</t>
   </si>
   <si>
     <t xml:space="preserve">10.01393699646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1010150909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92685890197754</t>
+    <t xml:space="preserve">10.1010141372681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92685985565186</t>
   </si>
   <si>
     <t xml:space="preserve">9.88332176208496</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0574760437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97039794921875</t>
+    <t xml:space="preserve">10.0574750900269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97039890289307</t>
   </si>
   <si>
     <t xml:space="preserve">9.7091646194458</t>
@@ -2102,28 +2102,28 @@
     <t xml:space="preserve">9.75270366668701</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62208652496338</t>
+    <t xml:space="preserve">9.6220874786377</t>
   </si>
   <si>
     <t xml:space="preserve">9.53501033782959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79624271392822</t>
+    <t xml:space="preserve">9.79624366760254</t>
   </si>
   <si>
     <t xml:space="preserve">10.1880912780762</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2751703262329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5364036560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9282522201538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0153303146362</t>
+    <t xml:space="preserve">10.2751693725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5364027023315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9282531738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0153293609619</t>
   </si>
   <si>
     <t xml:space="preserve">10.7540979385376</t>
@@ -2135,16 +2135,16 @@
     <t xml:space="preserve">10.4057865142822</t>
   </si>
   <si>
-    <t xml:space="preserve">10.362247467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3187093734741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1894855499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2765626907349</t>
+    <t xml:space="preserve">10.3622465133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3187084197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1894865036011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2765645980835</t>
   </si>
   <si>
     <t xml:space="preserve">11.4507188796997</t>
@@ -2156,7 +2156,7 @@
     <t xml:space="preserve">12.060263633728</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5011940002441</t>
+    <t xml:space="preserve">12.5011930465698</t>
   </si>
   <si>
     <t xml:space="preserve">12.0100746154785</t>
@@ -2168,13 +2168,13 @@
     <t xml:space="preserve">11.6975450515747</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4743089675903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2064266204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4296627044678</t>
+    <t xml:space="preserve">11.4743099212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2064275741577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4296617507935</t>
   </si>
   <si>
     <t xml:space="preserve">11.608250617981</t>
@@ -2186,13 +2186,13 @@
     <t xml:space="preserve">10.5813665390015</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5367202758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0278377532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8938961029053</t>
+    <t xml:space="preserve">10.5367193222046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0278387069702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8938970565796</t>
   </si>
   <si>
     <t xml:space="preserve">11.1617794036865</t>
@@ -2201,13 +2201,13 @@
     <t xml:space="preserve">11.0724849700928</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9207811355591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1886625289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2333097457886</t>
+    <t xml:space="preserve">11.9207820892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.188663482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2333106994629</t>
   </si>
   <si>
     <t xml:space="preserve">12.3226041793823</t>
@@ -2216,7 +2216,7 @@
     <t xml:space="preserve">11.8761339187622</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1440172195435</t>
+    <t xml:space="preserve">12.1440162658691</t>
   </si>
   <si>
     <t xml:space="preserve">11.7868385314941</t>
@@ -2225,10 +2225,10 @@
     <t xml:space="preserve">12.0993690490723</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4387817382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4834299087524</t>
+    <t xml:space="preserve">13.4387826919556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4834289550781</t>
   </si>
   <si>
     <t xml:space="preserve">13.9299011230469</t>
@@ -2243,67 +2243,67 @@
     <t xml:space="preserve">12.9030179977417</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0816049575806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0369596481323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7513113021851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7959594726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3941354751587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9745464324951</t>
+    <t xml:space="preserve">13.0816059112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.036958694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7513122558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7959585189819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3941345214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9745473861694</t>
   </si>
   <si>
     <t xml:space="preserve">13.2601947784424</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6620187759399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6173706054688</t>
+    <t xml:space="preserve">13.6620178222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6173715591431</t>
   </si>
   <si>
     <t xml:space="preserve">13.88525390625</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6442546844482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7781944274902</t>
+    <t xml:space="preserve">14.6442537307739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7781953811646</t>
   </si>
   <si>
     <t xml:space="preserve">14.9121379852295</t>
   </si>
   <si>
-    <t xml:space="preserve">15.090726852417</t>
+    <t xml:space="preserve">15.0907258987427</t>
   </si>
   <si>
     <t xml:space="preserve">14.7335481643677</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4210186004639</t>
+    <t xml:space="preserve">14.4210195541382</t>
   </si>
   <si>
     <t xml:space="preserve">14.5103130340576</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1800193786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8497266769409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8050832748413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0729637145996</t>
+    <t xml:space="preserve">15.1800203323364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8497285842896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8050813674927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.072961807251</t>
   </si>
   <si>
     <t xml:space="preserve">16.3854923248291</t>
@@ -2312,10 +2312,10 @@
     <t xml:space="preserve">16.921257019043</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1891384124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7426681518555</t>
+    <t xml:space="preserve">17.1891403198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7426700592041</t>
   </si>
   <si>
     <t xml:space="preserve">17.7249050140381</t>
@@ -2333,7 +2333,7 @@
     <t xml:space="preserve">18.0374374389648</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1267280578613</t>
+    <t xml:space="preserve">18.12672996521</t>
   </si>
   <si>
     <t xml:space="preserve">18.3946132659912</t>
@@ -2342,7 +2342,7 @@
     <t xml:space="preserve">18.5732002258301</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6980228424072</t>
+    <t xml:space="preserve">16.6980247497559</t>
   </si>
   <si>
     <t xml:space="preserve">18.3053188323975</t>
@@ -2354,7 +2354,7 @@
     <t xml:space="preserve">18.2160243988037</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9481410980225</t>
+    <t xml:space="preserve">17.9481430053711</t>
   </si>
   <si>
     <t xml:space="preserve">19.0196723937988</t>
@@ -2363,28 +2363,28 @@
     <t xml:space="preserve">20.1804981231689</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5376758575439</t>
+    <t xml:space="preserve">20.5376739501953</t>
   </si>
   <si>
     <t xml:space="preserve">20.6269683837891</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9841423034668</t>
+    <t xml:space="preserve">20.9841461181641</t>
   </si>
   <si>
     <t xml:space="preserve">20.8055572509766</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0734405517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0912036895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0019111633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8233222961426</t>
+    <t xml:space="preserve">21.0734386444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0912055969238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0019092559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8233203887939</t>
   </si>
   <si>
     <t xml:space="preserve">20.2697944641113</t>
@@ -2405,13 +2405,13 @@
     <t xml:space="preserve">18.9303779602051</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7162609100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4483795166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4306144714355</t>
+    <t xml:space="preserve">20.7162628173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4483814239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4306163787842</t>
   </si>
   <si>
     <t xml:space="preserve">21.3413219451904</t>
@@ -2423,16 +2423,16 @@
     <t xml:space="preserve">21.6092052459717</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0556755065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7877922058105</t>
+    <t xml:space="preserve">22.0556774139404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7877941131592</t>
   </si>
   <si>
     <t xml:space="preserve">22.7700309753418</t>
   </si>
   <si>
-    <t xml:space="preserve">24.914701461792</t>
+    <t xml:space="preserve">24.9147033691406</t>
   </si>
   <si>
     <t xml:space="preserve">24.4583892822266</t>
@@ -2447,10 +2447,10 @@
     <t xml:space="preserve">24.5496520996094</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4622764587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8234424591064</t>
+    <t xml:space="preserve">25.4622783660889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8234405517578</t>
   </si>
   <si>
     <t xml:space="preserve">24.0933380126953</t>
@@ -2459,7 +2459,7 @@
     <t xml:space="preserve">24.732177734375</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3671283721924</t>
+    <t xml:space="preserve">24.367130279541</t>
   </si>
   <si>
     <t xml:space="preserve">23.9108142852783</t>
@@ -2468,7 +2468,7 @@
     <t xml:space="preserve">23.2719764709473</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6370258331299</t>
+    <t xml:space="preserve">23.6370277404785</t>
   </si>
   <si>
     <t xml:space="preserve">23.5457630157471</t>
@@ -2483,7 +2483,7 @@
     <t xml:space="preserve">24.1846027374268</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0059642791748</t>
+    <t xml:space="preserve">25.0059661865234</t>
   </si>
   <si>
     <t xml:space="preserve">22.3593482971191</t>
@@ -2492,28 +2492,28 @@
     <t xml:space="preserve">22.8156623840332</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2680854797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7243976593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4545001983643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0894508361816</t>
+    <t xml:space="preserve">22.268087387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7243995666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4545021057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.089448928833</t>
   </si>
   <si>
     <t xml:space="preserve">23.1807117462158</t>
   </si>
   <si>
-    <t xml:space="preserve">22.906925201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1768226623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5418739318848</t>
+    <t xml:space="preserve">22.9069271087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1768245697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5418758392334</t>
   </si>
   <si>
     <t xml:space="preserve">21.9942989349365</t>
@@ -2522,10 +2522,10 @@
     <t xml:space="preserve">22.0855617523193</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5379867553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7205104827881</t>
+    <t xml:space="preserve">21.5379848480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7205085754395</t>
   </si>
   <si>
     <t xml:space="preserve">21.3554592132568</t>
@@ -2534,25 +2534,25 @@
     <t xml:space="preserve">21.8117733001709</t>
   </si>
   <si>
-    <t xml:space="preserve">21.446720123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8991451263428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0738925933838</t>
+    <t xml:space="preserve">21.4467239379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8991470336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0738945007324</t>
   </si>
   <si>
     <t xml:space="preserve">19.8952560424805</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8039951324463</t>
+    <t xml:space="preserve">19.8039970397949</t>
   </si>
   <si>
     <t xml:space="preserve">19.6214694976807</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7127342224121</t>
+    <t xml:space="preserve">19.7127323150635</t>
   </si>
   <si>
     <t xml:space="preserve">21.081672668457</t>
@@ -2567,7 +2567,7 @@
     <t xml:space="preserve">26.374906539917</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6448040008545</t>
+    <t xml:space="preserve">25.6448059082031</t>
   </si>
   <si>
     <t xml:space="preserve">25.9185924530029</t>
@@ -2576,13 +2576,13 @@
     <t xml:space="preserve">25.8273296356201</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5535430908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2797565460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3632392883301</t>
+    <t xml:space="preserve">25.5535411834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2797546386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3632373809814</t>
   </si>
   <si>
     <t xml:space="preserve">22.450611114502</t>
@@ -2591,25 +2591,25 @@
     <t xml:space="preserve">21.6292476654053</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9904098510742</t>
+    <t xml:space="preserve">20.9904079437256</t>
   </si>
   <si>
     <t xml:space="preserve">21.2641983032227</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1729335784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5340957641602</t>
+    <t xml:space="preserve">21.1729354858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5340976715088</t>
   </si>
   <si>
     <t xml:space="preserve">20.8078842163086</t>
   </si>
   <si>
-    <t xml:space="preserve">20.442834854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9030342102051</t>
+    <t xml:space="preserve">20.4428329467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9030361175537</t>
   </si>
   <si>
     <t xml:space="preserve">22.6331367492676</t>
@@ -2624,7 +2624,7 @@
     <t xml:space="preserve">19.3476810455322</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1651554107666</t>
+    <t xml:space="preserve">19.1651573181152</t>
   </si>
   <si>
     <t xml:space="preserve">18.2525291442871</t>
@@ -2636,10 +2636,10 @@
     <t xml:space="preserve">18.1156349182129</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4311656951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5224304199219</t>
+    <t xml:space="preserve">17.4311676025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5224285125732</t>
   </si>
   <si>
     <t xml:space="preserve">16.2447509765625</t>
@@ -2654,13 +2654,13 @@
     <t xml:space="preserve">16.7010650634766</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6593246459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2486419677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3437919616699</t>
+    <t xml:space="preserve">17.6593227386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2486400604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3437938690186</t>
   </si>
   <si>
     <t xml:space="preserve">18.800106048584</t>
@@ -2672,7 +2672,7 @@
     <t xml:space="preserve">18.982629776001</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5263156890869</t>
+    <t xml:space="preserve">18.5263175964355</t>
   </si>
   <si>
     <t xml:space="preserve">18.4350566864014</t>
@@ -2687,7 +2687,7 @@
     <t xml:space="preserve">21.8574047088623</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3137187957764</t>
+    <t xml:space="preserve">22.3137168884277</t>
   </si>
   <si>
     <t xml:space="preserve">21.9486656188965</t>
@@ -2699,13 +2699,13 @@
     <t xml:space="preserve">21.4923534393311</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4049777984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6787662506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5913963317871</t>
+    <t xml:space="preserve">22.4049797058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.678768157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5913944244385</t>
   </si>
   <si>
     <t xml:space="preserve">23.5001335144043</t>
@@ -71113,7 +71113,7 @@
     </row>
     <row r="2576">
       <c r="A2576" s="1" t="n">
-        <v>46072.6911805556</v>
+        <v>46072.3333333333</v>
       </c>
       <c r="B2576" t="n">
         <v>4394</v>
@@ -71134,6 +71134,32 @@
         <v>1266</v>
       </c>
       <c r="H2576" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2577">
+      <c r="A2577" s="1" t="n">
+        <v>46073.69125</v>
+      </c>
+      <c r="B2577" t="n">
+        <v>2888</v>
+      </c>
+      <c r="C2577" t="n">
+        <v>13.9499998092651</v>
+      </c>
+      <c r="D2577" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="E2577" t="n">
+        <v>13.8999996185303</v>
+      </c>
+      <c r="F2577" t="n">
+        <v>13.8999996185303</v>
+      </c>
+      <c r="G2577" t="s">
+        <v>1265</v>
+      </c>
+      <c r="H2577" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SAB.MI.xlsx
+++ b/data/SAB.MI.xlsx
@@ -44,88 +44,88 @@
     <t xml:space="preserve">SAB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61823177337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48310089111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3329610824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37049293518066</t>
+    <t xml:space="preserve">8.61822986602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4831018447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33295917510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37049388885498</t>
   </si>
   <si>
     <t xml:space="preserve">8.31794357299805</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25788593292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16029357910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88252782821655</t>
+    <t xml:space="preserve">8.25788688659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16029262542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88252735137939</t>
   </si>
   <si>
     <t xml:space="preserve">7.52969074249268</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66481828689575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62728404998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61227083206177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73989343643188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75490617752075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76991939544678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89754247665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6197772026062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79994964599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72487735748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65731239318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50716972351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34201240539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54470634460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39080810546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58224201202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82246971130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0852222442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11524963378906</t>
+    <t xml:space="preserve">7.66481971740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62728548049927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61227035522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73989295959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75490570068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76992034912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89754343032837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61977815628052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79994916915894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72487688064575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65731287002563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50716924667358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34201145172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54470586776733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39080858230591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58224105834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82247114181519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08522319793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11525058746338</t>
   </si>
   <si>
     <t xml:space="preserve">7.95760059356689</t>
@@ -137,256 +137,256 @@
     <t xml:space="preserve">8.03267097473145</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92006492614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77742719650269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86751365661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80745649337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98762893676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04017925262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99513483047485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96510791778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90504884719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93507862091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89003562927246</t>
+    <t xml:space="preserve">7.9200644493103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77742767333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86751461029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80745553970337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98762941360474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0401782989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99513673782349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96510696411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9050498008728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93507957458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8900351524353</t>
   </si>
   <si>
     <t xml:space="preserve">7.94258499145508</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82997846603394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81496429443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73238611221313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64980506896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71737003326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67232894897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6347918510437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51467609405518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64229822158813</t>
+    <t xml:space="preserve">7.82997751235962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8149619102478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73238468170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64980602264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71737146377563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67232847213745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63479137420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51467800140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64230012893677</t>
   </si>
   <si>
     <t xml:space="preserve">7.56722688674927</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70235729217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74739933013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46963357925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69484901428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49215507507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47338724136353</t>
+    <t xml:space="preserve">7.70235681533813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74739837646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46963453292847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69484853744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49215459823608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47338771820068</t>
   </si>
   <si>
     <t xml:space="preserve">7.43585157394409</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50341701507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48089361190796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59725618362427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4283447265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38705444335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37204027175903</t>
+    <t xml:space="preserve">7.50341653823853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48089599609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59725666046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42834424972534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38705492019653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37204170227051</t>
   </si>
   <si>
     <t xml:space="preserve">7.31949138641357</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28195428848267</t>
+    <t xml:space="preserve">7.28195476531982</t>
   </si>
   <si>
     <t xml:space="preserve">7.52122163772583</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8053412437439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75009393692017</t>
+    <t xml:space="preserve">7.80533933639526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75009489059448</t>
   </si>
   <si>
     <t xml:space="preserve">7.75798559188843</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81323099136353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86058521270752</t>
+    <t xml:space="preserve">7.81323194503784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8605842590332</t>
   </si>
   <si>
     <t xml:space="preserve">7.69879579544067</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58435964584351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68695592880249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57646656036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53700542449951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49754524230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28445625305176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92536354064941</t>
+    <t xml:space="preserve">7.58435821533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68695735931396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57646799087524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53700685501099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49754428863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28445720672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92536449432373</t>
   </si>
   <si>
     <t xml:space="preserve">7.079261302948</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22921323776245</t>
+    <t xml:space="preserve">7.22921180725098</t>
   </si>
   <si>
     <t xml:space="preserve">7.45808506011963</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2607798576355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37127065658569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2647271156311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34759473800659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46992301940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36732482910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37916278839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13450527191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18975019454956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10293817520142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15029096603394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10688257217407</t>
+    <t xml:space="preserve">7.26078033447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37127208709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26472568511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34759521484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46992206573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36732578277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3791618347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13450622558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18975162506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10293865203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15029144287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10688400268555</t>
   </si>
   <si>
     <t xml:space="preserve">7.20553493499756</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18185949325562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22132062911987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19369697570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24894237518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1976432800293</t>
+    <t xml:space="preserve">7.18185901641846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22132015228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19369792938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24894428253174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19764423370361</t>
   </si>
   <si>
     <t xml:space="preserve">7.18580532073975</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22526597976685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20948171615601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31602621078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21342802047729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16607475280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24499607086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13056135177612</t>
+    <t xml:space="preserve">7.22526550292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20948219299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31602668762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21342754364014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16607522964478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24499702453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13055992126465</t>
   </si>
   <si>
     <t xml:space="preserve">7.11082887649536</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17791271209717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23315763473511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2765645980835</t>
+    <t xml:space="preserve">7.17791414260864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23315715789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27656507492065</t>
   </si>
   <si>
     <t xml:space="preserve">7.30024147033691</t>
@@ -398,100 +398,100 @@
     <t xml:space="preserve">7.24105072021484</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1187219619751</t>
+    <t xml:space="preserve">7.11872243881226</t>
   </si>
   <si>
     <t xml:space="preserve">7.09504508972168</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00428628921509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94509506225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93325567245483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09899091720581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15423679351807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13845300674438</t>
+    <t xml:space="preserve">7.00428581237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9450945854187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93325614929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09899139404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15423727035522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13845109939575</t>
   </si>
   <si>
     <t xml:space="preserve">7.15818309783936</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05558395385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07136869430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06742238998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02401542663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04769325256348</t>
+    <t xml:space="preserve">7.05558443069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07137012481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06742286682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0240159034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.047691822052</t>
   </si>
   <si>
     <t xml:space="preserve">7.06347703933716</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08320713043213</t>
+    <t xml:space="preserve">7.08320760726929</t>
   </si>
   <si>
     <t xml:space="preserve">7.05163860321045</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04374694824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03190851211548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05953073501587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03585529327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1739673614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9056339263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91352605819702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9372034072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9214186668396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94114780426025</t>
+    <t xml:space="preserve">7.04374742507935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03190898895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05952978134155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03585433959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17396640777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90563440322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91352653503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93720293045044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92141819000244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94114828109741</t>
   </si>
   <si>
     <t xml:space="preserve">6.96877098083496</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14239835739136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45019292831421</t>
+    <t xml:space="preserve">7.14239740371704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45019197463989</t>
   </si>
   <si>
     <t xml:space="preserve">7.69484996795654</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79350185394287</t>
+    <t xml:space="preserve">7.79349994659424</t>
   </si>
   <si>
     <t xml:space="preserve">7.92372179031372</t>
@@ -500,10 +500,10 @@
     <t xml:space="preserve">8.04999542236328</t>
   </si>
   <si>
-    <t xml:space="preserve">8.207839012146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16837692260742</t>
+    <t xml:space="preserve">8.20783805847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16837787628174</t>
   </si>
   <si>
     <t xml:space="preserve">8.08945655822754</t>
@@ -515,37 +515,37 @@
     <t xml:space="preserve">8.06578159332275</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12891864776611</t>
+    <t xml:space="preserve">8.1289176940918</t>
   </si>
   <si>
     <t xml:space="preserve">8.17626953125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32622241973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55509376525879</t>
+    <t xml:space="preserve">8.32622146606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55509281158447</t>
   </si>
   <si>
     <t xml:space="preserve">8.56298637390137</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42881965637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35778999328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39725112915039</t>
+    <t xml:space="preserve">8.42882061004639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35779094696045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39725208282471</t>
   </si>
   <si>
     <t xml:space="preserve">8.42092704772949</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44460296630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40514183044434</t>
+    <t xml:space="preserve">8.44460391998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40514373779297</t>
   </si>
   <si>
     <t xml:space="preserve">8.26308441162109</t>
@@ -554,16 +554,16 @@
     <t xml:space="preserve">8.18416213989258</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30254459381104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22362232208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2867603302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25519180297852</t>
+    <t xml:space="preserve">8.30254554748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22362327575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28675937652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25519275665283</t>
   </si>
   <si>
     <t xml:space="preserve">8.34989738464355</t>
@@ -575,22 +575,22 @@
     <t xml:space="preserve">8.36568260192871</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33411312103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34200572967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46038818359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62612438201904</t>
+    <t xml:space="preserve">8.33411407470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34200668334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46038722991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62612342834473</t>
   </si>
   <si>
     <t xml:space="preserve">8.74450492858887</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88656425476074</t>
+    <t xml:space="preserve">8.88656520843506</t>
   </si>
   <si>
     <t xml:space="preserve">9.00494766235352</t>
@@ -599,16 +599,16 @@
     <t xml:space="preserve">9.23381805419922</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30484676361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26538848876953</t>
+    <t xml:space="preserve">9.30484867095947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26538753509521</t>
   </si>
   <si>
     <t xml:space="preserve">9.16278839111328</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19435787200928</t>
+    <t xml:space="preserve">9.19435691833496</t>
   </si>
   <si>
     <t xml:space="preserve">9.24960422515869</t>
@@ -620,55 +620,55 @@
     <t xml:space="preserve">9.36798477172852</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54950428009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67577743530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74680995941162</t>
+    <t xml:space="preserve">9.54950523376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67577934265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7468090057373</t>
   </si>
   <si>
     <t xml:space="preserve">10.2203378677368</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4807796478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4571027755737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2913675308228</t>
+    <t xml:space="preserve">10.4807777404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4571018218994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2913684844971</t>
   </si>
   <si>
     <t xml:space="preserve">10.2597990036011</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1493082046509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0861711502075</t>
+    <t xml:space="preserve">10.1493091583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0861721038818</t>
   </si>
   <si>
     <t xml:space="preserve">10.0151424407959</t>
   </si>
   <si>
-    <t xml:space="preserve">10.101957321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1650924682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0546026229858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1808767318726</t>
+    <t xml:space="preserve">10.1019554138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1650915145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0546035766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1808776855469</t>
   </si>
   <si>
     <t xml:space="preserve">10.1177396774292</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1887702941895</t>
+    <t xml:space="preserve">10.1887683868408</t>
   </si>
   <si>
     <t xml:space="preserve">10.0703868865967</t>
@@ -677,13 +677,13 @@
     <t xml:space="preserve">10.1098480224609</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0230350494385</t>
+    <t xml:space="preserve">10.0230340957642</t>
   </si>
   <si>
     <t xml:space="preserve">10.496563911438</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4176416397095</t>
+    <t xml:space="preserve">10.4176406860352</t>
   </si>
   <si>
     <t xml:space="preserve">10.3150444030762</t>
@@ -692,55 +692,55 @@
     <t xml:space="preserve">10.7333278656006</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4492092132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5597009658813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6386213302612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.591269493103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0095529556274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.883279800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3410224914551</t>
+    <t xml:space="preserve">10.4492101669312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5597019195557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6386232376099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5912704467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0095520019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8832807540894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3410234451294</t>
   </si>
   <si>
     <t xml:space="preserve">12.0592098236084</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9171514511108</t>
+    <t xml:space="preserve">11.9171524047852</t>
   </si>
   <si>
     <t xml:space="preserve">12.0513181686401</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6882801055908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6803874969482</t>
+    <t xml:space="preserve">11.6882791519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6803865432739</t>
   </si>
   <si>
     <t xml:space="preserve">12.2644052505493</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6274442672729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5406303405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6747989654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7379350662231</t>
+    <t xml:space="preserve">12.6274452209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5406312942505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6747970581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7379341125488</t>
   </si>
   <si>
     <t xml:space="preserve">12.4728565216064</t>
@@ -755,22 +755,22 @@
     <t xml:space="preserve">12.8145771026611</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9203491210938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8715314865112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9366207122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8064413070679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6437177658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.822714805603</t>
+    <t xml:space="preserve">12.9203481674194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8715305328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.936619758606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8064422607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6437168121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8227138519287</t>
   </si>
   <si>
     <t xml:space="preserve">11.5209150314331</t>
@@ -782,13 +782,13 @@
     <t xml:space="preserve">11.7812747955322</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9114561080933</t>
+    <t xml:space="preserve">11.9114551544189</t>
   </si>
   <si>
     <t xml:space="preserve">11.9277267456055</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9602727890015</t>
+    <t xml:space="preserve">11.9602737426758</t>
   </si>
   <si>
     <t xml:space="preserve">11.805685043335</t>
@@ -797,7 +797,7 @@
     <t xml:space="preserve">12.1311330795288</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0009546279907</t>
+    <t xml:space="preserve">12.0009536743164</t>
   </si>
   <si>
     <t xml:space="preserve">11.9846811294556</t>
@@ -806,46 +806,46 @@
     <t xml:space="preserve">12.0416355133057</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0823173522949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.976544380188</t>
+    <t xml:space="preserve">12.0823163986206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9765453338623</t>
   </si>
   <si>
     <t xml:space="preserve">11.8789100646973</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7161846160889</t>
+    <t xml:space="preserve">11.7161855697632</t>
   </si>
   <si>
     <t xml:space="preserve">11.4720983505249</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5534601211548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5860071182251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7975492477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8951835632324</t>
+    <t xml:space="preserve">11.5534610748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5860061645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7975473403931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8951826095581</t>
   </si>
   <si>
     <t xml:space="preserve">12.0904521942139</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1636781692505</t>
+    <t xml:space="preserve">12.1636791229248</t>
   </si>
   <si>
     <t xml:space="preserve">12.074179649353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2287693023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1392688751221</t>
+    <t xml:space="preserve">12.2287673950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1392698287964</t>
   </si>
   <si>
     <t xml:space="preserve">12.2043600082397</t>
@@ -857,43 +857,43 @@
     <t xml:space="preserve">12.1474056243896</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2531776428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3670845031738</t>
+    <t xml:space="preserve">12.2531785964966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3670835494995</t>
   </si>
   <si>
     <t xml:space="preserve">12.4077663421631</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4484462738037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9447574615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7820329666138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8959398269653</t>
+    <t xml:space="preserve">12.448447227478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9447584152222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7820339202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8959407806396</t>
   </si>
   <si>
     <t xml:space="preserve">13.0098476409912</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9528942108154</t>
+    <t xml:space="preserve">12.9528951644897</t>
   </si>
   <si>
     <t xml:space="preserve">12.8552598953247</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7332153320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7738962173462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9854393005371</t>
+    <t xml:space="preserve">12.7332143783569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7738971710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9854383468628</t>
   </si>
   <si>
     <t xml:space="preserve">13.2620706558228</t>
@@ -902,16 +902,16 @@
     <t xml:space="preserve">13.685154914856</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9292440414429</t>
+    <t xml:space="preserve">13.9292421340942</t>
   </si>
   <si>
     <t xml:space="preserve">13.9943323135376</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7502450942993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.815336227417</t>
+    <t xml:space="preserve">13.7502470016479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8153343200684</t>
   </si>
   <si>
     <t xml:space="preserve">13.8316068649292</t>
@@ -920,22 +920,22 @@
     <t xml:space="preserve">14.018741607666</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0268783569336</t>
+    <t xml:space="preserve">14.026876449585</t>
   </si>
   <si>
     <t xml:space="preserve">14.1814661026001</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1570568084717</t>
+    <t xml:space="preserve">14.157057762146</t>
   </si>
   <si>
     <t xml:space="preserve">14.2302837371826</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7754125595093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.320538520813</t>
+    <t xml:space="preserve">14.7754106521606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3205375671387</t>
   </si>
   <si>
     <t xml:space="preserve">15.2961320877075</t>
@@ -944,10 +944,10 @@
     <t xml:space="preserve">15.4588537216187</t>
   </si>
   <si>
-    <t xml:space="preserve">15.824987411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.792444229126</t>
+    <t xml:space="preserve">15.8249893188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7924423217773</t>
   </si>
   <si>
     <t xml:space="preserve">15.5076732635498</t>
@@ -965,28 +965,28 @@
     <t xml:space="preserve">16.0039844512939</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2643451690674</t>
+    <t xml:space="preserve">16.2643432617188</t>
   </si>
   <si>
     <t xml:space="preserve">16.7769260406494</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9559230804443</t>
+    <t xml:space="preserve">16.9559268951416</t>
   </si>
   <si>
     <t xml:space="preserve">17.4115543365479</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0454216003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0787258148193</t>
+    <t xml:space="preserve">17.0454235076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0787220001221</t>
   </si>
   <si>
     <t xml:space="preserve">17.6475028991699</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0217723846436</t>
+    <t xml:space="preserve">18.0217742919922</t>
   </si>
   <si>
     <t xml:space="preserve">18.0543174743652</t>
@@ -995,52 +995,52 @@
     <t xml:space="preserve">18.1275444030762</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2984027862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4123134613037</t>
+    <t xml:space="preserve">18.2984046936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4123115539551</t>
   </si>
   <si>
     <t xml:space="preserve">18.1682243347168</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1600856781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9159984588623</t>
+    <t xml:space="preserve">18.1600875854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9160003662109</t>
   </si>
   <si>
     <t xml:space="preserve">17.265100479126</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0861034393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2976455688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0047416687012</t>
+    <t xml:space="preserve">17.0861053466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2976474761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0047397613525</t>
   </si>
   <si>
     <t xml:space="preserve">17.1267852783203</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8745613098145</t>
+    <t xml:space="preserve">16.8745594024658</t>
   </si>
   <si>
     <t xml:space="preserve">17.0779685974121</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8664264678955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7850608825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9884700775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5979290008545</t>
+    <t xml:space="preserve">16.8664226531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7850646972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.988468170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5979270935059</t>
   </si>
   <si>
     <t xml:space="preserve">16.9152450561523</t>
@@ -1049,7 +1049,7 @@
     <t xml:space="preserve">16.8338813781738</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9640617370605</t>
+    <t xml:space="preserve">16.9640598297119</t>
   </si>
   <si>
     <t xml:space="preserve">16.882698059082</t>
@@ -1058,7 +1058,7 @@
     <t xml:space="preserve">16.9233779907227</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1349220275879</t>
+    <t xml:space="preserve">17.1349201202393</t>
   </si>
   <si>
     <t xml:space="preserve">17.0698299407959</t>
@@ -1076,7 +1076,7 @@
     <t xml:space="preserve">18.8598041534424</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0632095336914</t>
+    <t xml:space="preserve">19.0632133483887</t>
   </si>
   <si>
     <t xml:space="preserve">18.7052154541016</t>
@@ -1085,7 +1085,7 @@
     <t xml:space="preserve">18.6319885253906</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7377643585205</t>
+    <t xml:space="preserve">18.7377624511719</t>
   </si>
   <si>
     <t xml:space="preserve">18.7133522033691</t>
@@ -1094,19 +1094,19 @@
     <t xml:space="preserve">18.5913105010986</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3065395355225</t>
+    <t xml:space="preserve">18.3065414428711</t>
   </si>
   <si>
     <t xml:space="preserve">18.6157169342041</t>
   </si>
   <si>
-    <t xml:space="preserve">18.217041015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2089023590088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4611301422119</t>
+    <t xml:space="preserve">18.2170391082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2089042663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4611320495605</t>
   </si>
   <si>
     <t xml:space="preserve">17.5417327880859</t>
@@ -1115,7 +1115,7 @@
     <t xml:space="preserve">16.9071063995361</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4758853912354</t>
+    <t xml:space="preserve">16.475887298584</t>
   </si>
   <si>
     <t xml:space="preserve">16.3945217132568</t>
@@ -1124,7 +1124,7 @@
     <t xml:space="preserve">16.1097545623779</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3619804382324</t>
+    <t xml:space="preserve">16.3619785308838</t>
   </si>
   <si>
     <t xml:space="preserve">16.2806186676025</t>
@@ -1157,67 +1157,67 @@
     <t xml:space="preserve">16.1911182403564</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3538455963135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.028392791748</t>
+    <t xml:space="preserve">16.3538436889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0283908843994</t>
   </si>
   <si>
     <t xml:space="preserve">15.9144849777222</t>
   </si>
   <si>
-    <t xml:space="preserve">15.182222366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9706802368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1008615493774</t>
+    <t xml:space="preserve">15.1822233200073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.970682144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1008625030518</t>
   </si>
   <si>
     <t xml:space="preserve">14.873046875</t>
   </si>
   <si>
-    <t xml:space="preserve">14.222146987915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8478803634644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8893175125122</t>
+    <t xml:space="preserve">14.2221460342407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8478813171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8893184661865</t>
   </si>
   <si>
     <t xml:space="preserve">15.1984958648682</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3937673568726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5402183532715</t>
+    <t xml:space="preserve">15.3937654495239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5402202606201</t>
   </si>
   <si>
     <t xml:space="preserve">14.9381370544434</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5964136123657</t>
+    <t xml:space="preserve">14.5964155197144</t>
   </si>
   <si>
     <t xml:space="preserve">14.4011468887329</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2058744430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1082401275635</t>
+    <t xml:space="preserve">14.2058753967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1082420349121</t>
   </si>
   <si>
     <t xml:space="preserve">14.0594215393066</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9129705429077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0106039047241</t>
+    <t xml:space="preserve">13.9129695892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0106029510498</t>
   </si>
   <si>
     <t xml:space="preserve">14.3197822570801</t>
@@ -1226,49 +1226,49 @@
     <t xml:space="preserve">14.6452312469482</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7428665161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7265968322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2147674560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8079566955566</t>
+    <t xml:space="preserve">14.7428684234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7265939712524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2147693634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.807957649231</t>
   </si>
   <si>
     <t xml:space="preserve">14.8567733764648</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9544076919556</t>
+    <t xml:space="preserve">14.9544086456299</t>
   </si>
   <si>
     <t xml:space="preserve">14.7916841506958</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2709655761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.003228187561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4825067520142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9218626022339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.905592918396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0194978713989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0520467758179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2562065124512</t>
+    <t xml:space="preserve">14.2709646224976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0032262802124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4825048446655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9218635559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9055919647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0194969177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0520429611206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2562046051025</t>
   </si>
   <si>
     <t xml:space="preserve">15.7354898452759</t>
@@ -1277,10 +1277,10 @@
     <t xml:space="preserve">15.8168506622314</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6215829849243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9307584762573</t>
+    <t xml:space="preserve">15.6215810775757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.930757522583</t>
   </si>
   <si>
     <t xml:space="preserve">15.6866703033447</t>
@@ -1289,7 +1289,7 @@
     <t xml:space="preserve">15.7192163467407</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7029438018799</t>
+    <t xml:space="preserve">15.7029418945312</t>
   </si>
   <si>
     <t xml:space="preserve">15.6703987121582</t>
@@ -1298,16 +1298,16 @@
     <t xml:space="preserve">15.6053094863892</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5653505325317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.995680809021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0291910171509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0627031326294</t>
+    <t xml:space="preserve">15.5653524398804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9956836700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0291938781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0627021789551</t>
   </si>
   <si>
     <t xml:space="preserve">15.2470083236694</t>
@@ -1319,19 +1319,19 @@
     <t xml:space="preserve">15.5318412780762</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7161474227905</t>
+    <t xml:space="preserve">15.7161455154419</t>
   </si>
   <si>
     <t xml:space="preserve">15.8669395446777</t>
   </si>
   <si>
-    <t xml:space="preserve">15.582106590271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4983320236206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.48157787323</t>
+    <t xml:space="preserve">15.5821084976196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.498330116272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4815759658813</t>
   </si>
   <si>
     <t xml:space="preserve">15.4145574569702</t>
@@ -1340,16 +1340,16 @@
     <t xml:space="preserve">15.179988861084</t>
   </si>
   <si>
-    <t xml:space="preserve">15.079460144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1129684448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3589944839478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2919750213623</t>
+    <t xml:space="preserve">15.07945728302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1129674911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3589954376221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.291974067688</t>
   </si>
   <si>
     <t xml:space="preserve">14.2584657669067</t>
@@ -1358,16 +1358,16 @@
     <t xml:space="preserve">14.4595251083374</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4092607498169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5600547790527</t>
+    <t xml:space="preserve">14.4092597961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5600538253784</t>
   </si>
   <si>
     <t xml:space="preserve">13.4039621353149</t>
   </si>
   <si>
-    <t xml:space="preserve">13.487738609314</t>
+    <t xml:space="preserve">13.4877376556396</t>
   </si>
   <si>
     <t xml:space="preserve">13.2364130020142</t>
@@ -1376,25 +1376,25 @@
     <t xml:space="preserve">13.5380020141602</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4374723434448</t>
+    <t xml:space="preserve">13.4374732971191</t>
   </si>
   <si>
     <t xml:space="preserve">14.191445350647</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5882654190063</t>
+    <t xml:space="preserve">13.5882663726807</t>
   </si>
   <si>
     <t xml:space="preserve">13.6887969970703</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4207181930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5212469100952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5715131759644</t>
+    <t xml:space="preserve">13.4207172393799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5212459564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.57151222229</t>
   </si>
   <si>
     <t xml:space="preserve">13.3201866149902</t>
@@ -1403,43 +1403,43 @@
     <t xml:space="preserve">13.1526384353638</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1861476898193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2196588516235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3034324645996</t>
+    <t xml:space="preserve">13.1861486434937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2196569442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3034315109253</t>
   </si>
   <si>
     <t xml:space="preserve">12.8510494232178</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6834993362427</t>
+    <t xml:space="preserve">12.6834983825684</t>
   </si>
   <si>
     <t xml:space="preserve">12.5662155151367</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9013137817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8342943191528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4824380874634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1473407745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0803203582764</t>
+    <t xml:space="preserve">12.901312828064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8342933654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4824390411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1473398208618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0803213119507</t>
   </si>
   <si>
     <t xml:space="preserve">12.0635662078857</t>
   </si>
   <si>
-    <t xml:space="preserve">11.979790687561</t>
+    <t xml:space="preserve">11.9797916412354</t>
   </si>
   <si>
     <t xml:space="preserve">11.5609169006348</t>
@@ -1448,7 +1448,7 @@
     <t xml:space="preserve">11.1923084259033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2258186340332</t>
+    <t xml:space="preserve">11.2258176803589</t>
   </si>
   <si>
     <t xml:space="preserve">12.4321746826172</t>
@@ -1457,7 +1457,7 @@
     <t xml:space="preserve">13.1191282272339</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2531681060791</t>
+    <t xml:space="preserve">13.2531671524048</t>
   </si>
   <si>
     <t xml:space="preserve">13.2866773605347</t>
@@ -1469,13 +1469,13 @@
     <t xml:space="preserve">13.3536968231201</t>
   </si>
   <si>
-    <t xml:space="preserve">12.985089302063</t>
+    <t xml:space="preserve">12.9850873947144</t>
   </si>
   <si>
     <t xml:space="preserve">12.8007831573486</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6332330703735</t>
+    <t xml:space="preserve">12.6332349777222</t>
   </si>
   <si>
     <t xml:space="preserve">12.8678035736084</t>
@@ -1493,25 +1493,25 @@
     <t xml:space="preserve">11.7284669876099</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9630355834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8960161209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6614475250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0750246047974</t>
+    <t xml:space="preserve">11.9630346298218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.896017074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6614465713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.075023651123</t>
   </si>
   <si>
     <t xml:space="preserve">11.0415143966675</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9577388763428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7566795349121</t>
+    <t xml:space="preserve">10.9577398300171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7566804885864</t>
   </si>
   <si>
     <t xml:space="preserve">10.9242286682129</t>
@@ -1529,46 +1529,46 @@
     <t xml:space="preserve">11.4603881835938</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1587982177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1252889633179</t>
+    <t xml:space="preserve">11.1587972640991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1252870559692</t>
   </si>
   <si>
     <t xml:space="preserve">11.1755542755127</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3766145706177</t>
+    <t xml:space="preserve">11.3766136169434</t>
   </si>
   <si>
     <t xml:space="preserve">12.2311153411865</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3986644744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9295263290405</t>
+    <t xml:space="preserve">12.3986654281616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9295272827148</t>
   </si>
   <si>
     <t xml:space="preserve">11.7954864501953</t>
   </si>
   <si>
-    <t xml:space="preserve">11.87926197052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.197606086731</t>
+    <t xml:space="preserve">11.8792610168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1976051330566</t>
   </si>
   <si>
     <t xml:space="preserve">12.2478704452515</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0133008956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1305847167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.180850982666</t>
+    <t xml:space="preserve">12.0133018493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1305856704712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1808500289917</t>
   </si>
   <si>
     <t xml:space="preserve">12.3819093704224</t>
@@ -1583,16 +1583,16 @@
     <t xml:space="preserve">12.5997247695923</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7170085906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8845596313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9515800476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.968334197998</t>
+    <t xml:space="preserve">12.7170095443726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8845586776733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9515790939331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9683332443237</t>
   </si>
   <si>
     <t xml:space="preserve">13.2029027938843</t>
@@ -1604,19 +1604,19 @@
     <t xml:space="preserve">12.8175392150879</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6499900817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7002544403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5159482955933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7840280532837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0018444061279</t>
+    <t xml:space="preserve">12.6499910354614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7002534866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5159492492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.784029006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0018434524536</t>
   </si>
   <si>
     <t xml:space="preserve">13.0353536605835</t>
@@ -1628,16 +1628,16 @@
     <t xml:space="preserve">12.9348230361938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9180679321289</t>
+    <t xml:space="preserve">12.9180688858032</t>
   </si>
   <si>
     <t xml:space="preserve">13.38720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6217775344849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8228359222412</t>
+    <t xml:space="preserve">13.6217756271362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8228349685669</t>
   </si>
   <si>
     <t xml:space="preserve">13.5044927597046</t>
@@ -1652,7 +1652,7 @@
     <t xml:space="preserve">13.7223062515259</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3704538345337</t>
+    <t xml:space="preserve">13.3704519271851</t>
   </si>
   <si>
     <t xml:space="preserve">13.0521087646484</t>
@@ -1664,7 +1664,7 @@
     <t xml:space="preserve">13.1693935394287</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1023750305176</t>
+    <t xml:space="preserve">13.1023740768433</t>
   </si>
   <si>
     <t xml:space="preserve">12.499195098877</t>
@@ -1676,10 +1676,10 @@
     <t xml:space="preserve">12.5740213394165</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3650341033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2257108688354</t>
+    <t xml:space="preserve">12.3650350570679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2257099151611</t>
   </si>
   <si>
     <t xml:space="preserve">12.2779579162598</t>
@@ -1688,31 +1688,31 @@
     <t xml:space="preserve">12.3127880096436</t>
   </si>
   <si>
-    <t xml:space="preserve">12.295373916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3302040100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1212177276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5217742919922</t>
+    <t xml:space="preserve">12.2953729629517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3302030563354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1212167739868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5217752456665</t>
   </si>
   <si>
     <t xml:space="preserve">12.4869441986084</t>
   </si>
   <si>
-    <t xml:space="preserve">12.452112197876</t>
+    <t xml:space="preserve">12.4521131515503</t>
   </si>
   <si>
     <t xml:space="preserve">12.138632774353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0515546798706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.894814491272</t>
+    <t xml:space="preserve">12.0515556335449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8948154449463</t>
   </si>
   <si>
     <t xml:space="preserve">12.2082958221436</t>
@@ -1724,16 +1724,16 @@
     <t xml:space="preserve">12.7655925750732</t>
   </si>
   <si>
-    <t xml:space="preserve">12.643684387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3998651504517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6262683868408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5391902923584</t>
+    <t xml:space="preserve">12.6436834335327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.399866104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6262674331665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5391912460327</t>
   </si>
   <si>
     <t xml:space="preserve">12.8700847625732</t>
@@ -1748,13 +1748,13 @@
     <t xml:space="preserve">12.9397478103638</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7830095291138</t>
+    <t xml:space="preserve">12.7830085754395</t>
   </si>
   <si>
     <t xml:space="preserve">12.695930480957</t>
   </si>
   <si>
-    <t xml:space="preserve">12.800422668457</t>
+    <t xml:space="preserve">12.8004236221313</t>
   </si>
   <si>
     <t xml:space="preserve">12.8875017166138</t>
@@ -1766,34 +1766,34 @@
     <t xml:space="preserve">12.0341396331787</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7206611633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2431268692017</t>
+    <t xml:space="preserve">11.7206602096558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2431259155273</t>
   </si>
   <si>
     <t xml:space="preserve">11.7554912567139</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6684141159058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9993076324463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0689706802368</t>
+    <t xml:space="preserve">11.6684122085571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9993085861206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0689697265625</t>
   </si>
   <si>
     <t xml:space="preserve">12.1038007736206</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7903213500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.842568397522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9470615386963</t>
+    <t xml:space="preserve">11.790322303772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8425693511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9470634460449</t>
   </si>
   <si>
     <t xml:space="preserve">11.8251533508301</t>
@@ -1802,10 +1802,10 @@
     <t xml:space="preserve">11.8599834442139</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7729072570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8774013519287</t>
+    <t xml:space="preserve">11.7729063034058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8774003982544</t>
   </si>
   <si>
     <t xml:space="preserve">11.6509981155396</t>
@@ -1814,34 +1814,34 @@
     <t xml:space="preserve">11.5465049743652</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3201036453247</t>
+    <t xml:space="preserve">11.3201026916504</t>
   </si>
   <si>
     <t xml:space="preserve">11.2156095504761</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4071798324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3026857376099</t>
+    <t xml:space="preserve">11.4071807861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3026866912842</t>
   </si>
   <si>
     <t xml:space="preserve">11.3549327850342</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3897647857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1981925964355</t>
+    <t xml:space="preserve">11.3897657394409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1981935501099</t>
   </si>
   <si>
     <t xml:space="preserve">10.9369602203369</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0414533615112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8847141265869</t>
+    <t xml:space="preserve">11.0414543151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8847150802612</t>
   </si>
   <si>
     <t xml:space="preserve">10.867299079895</t>
@@ -1850,13 +1850,13 @@
     <t xml:space="preserve">10.9717922210693</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8324661254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6234788894653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6060667037964</t>
+    <t xml:space="preserve">10.8324670791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6234798431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6060647964478</t>
   </si>
   <si>
     <t xml:space="preserve">10.5886497497559</t>
@@ -1865,43 +1865,43 @@
     <t xml:space="preserve">10.5189867019653</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4493255615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6583127975464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7802200317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1633625030518</t>
+    <t xml:space="preserve">10.4493246078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6583118438721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7802209854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1633615493774</t>
   </si>
   <si>
     <t xml:space="preserve">11.1111154556274</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0588693618774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9892063140869</t>
+    <t xml:space="preserve">11.0588684082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9892072677612</t>
   </si>
   <si>
     <t xml:space="preserve">10.8498821258545</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0240383148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0066232681274</t>
+    <t xml:space="preserve">11.024037361145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0066223144531</t>
   </si>
   <si>
     <t xml:space="preserve">10.7976360321045</t>
   </si>
   <si>
-    <t xml:space="preserve">10.815052986145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9543762207031</t>
+    <t xml:space="preserve">10.8150520324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9543743133545</t>
   </si>
   <si>
     <t xml:space="preserve">11.0937004089355</t>
@@ -1910,34 +1910,34 @@
     <t xml:space="preserve">11.7032442092896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.981894493103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9296474456787</t>
+    <t xml:space="preserve">11.9818935394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9296464920044</t>
   </si>
   <si>
     <t xml:space="preserve">11.9122304916382</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8077383041382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2605409622192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.086386680603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9644765853882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.529088973999</t>
+    <t xml:space="preserve">11.8077373504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2605419158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0863857269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9644775390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5290880203247</t>
   </si>
   <si>
     <t xml:space="preserve">11.4942579269409</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5813360214233</t>
+    <t xml:space="preserve">11.581335067749</t>
   </si>
   <si>
     <t xml:space="preserve">11.476842880249</t>
@@ -1949,34 +1949,34 @@
     <t xml:space="preserve">12.1908798217773</t>
   </si>
   <si>
-    <t xml:space="preserve">12.347620010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5116739273071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5987510681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7105588912964</t>
+    <t xml:space="preserve">12.3476190567017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5116729736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5987501144409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7105579376221</t>
   </si>
   <si>
     <t xml:space="preserve">9.70045757293701</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49147129058838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03866577148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98642063140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42912197113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18530464172363</t>
+    <t xml:space="preserve">9.49147033691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03866672515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98641872406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42912292480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18530559539795</t>
   </si>
   <si>
     <t xml:space="preserve">8.22884368896484</t>
@@ -1988,10 +1988,10 @@
     <t xml:space="preserve">8.533616065979</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49007701873779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31592082977295</t>
+    <t xml:space="preserve">8.49007606506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31592178344727</t>
   </si>
   <si>
     <t xml:space="preserve">8.32462882995605</t>
@@ -2006,7 +2006,7 @@
     <t xml:space="preserve">8.28979778289795</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41170787811279</t>
+    <t xml:space="preserve">8.41170692443848</t>
   </si>
   <si>
     <t xml:space="preserve">8.4987850189209</t>
@@ -2021,22 +2021,22 @@
     <t xml:space="preserve">8.67294025421143</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79484939575195</t>
+    <t xml:space="preserve">8.79484844207764</t>
   </si>
   <si>
     <t xml:space="preserve">8.96900463104248</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75130939483643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70777130126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83838748931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1866979598999</t>
+    <t xml:space="preserve">8.75131034851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70777034759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83838844299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18669891357422</t>
   </si>
   <si>
     <t xml:space="preserve">9.05608177185059</t>
@@ -2048,10 +2048,10 @@
     <t xml:space="preserve">9.23023700714111</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40439224243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66562557220459</t>
+    <t xml:space="preserve">9.40439319610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66562652587891</t>
   </si>
   <si>
     <t xml:space="preserve">9.57854843139648</t>
@@ -2060,7 +2060,7 @@
     <t xml:space="preserve">9.31731510162354</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88192653656006</t>
+    <t xml:space="preserve">8.88192558288574</t>
   </si>
   <si>
     <t xml:space="preserve">8.65552425384521</t>
@@ -2069,25 +2069,25 @@
     <t xml:space="preserve">8.51620006561279</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6032772064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56844711303711</t>
+    <t xml:space="preserve">8.60327816009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56844615936279</t>
   </si>
   <si>
     <t xml:space="preserve">9.36085414886475</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83978176116943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0139360427856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1010150909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92685794830322</t>
+    <t xml:space="preserve">9.83978080749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.01393699646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1010141372681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92685890197754</t>
   </si>
   <si>
     <t xml:space="preserve">9.88331985473633</t>
@@ -2096,19 +2096,19 @@
     <t xml:space="preserve">10.0574769973755</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97039890289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7091646194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75270366668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62208843231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53500938415527</t>
+    <t xml:space="preserve">9.97039699554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70916366577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75270462036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62208652496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53500843048096</t>
   </si>
   <si>
     <t xml:space="preserve">9.79624271392822</t>
@@ -2117,7 +2117,7 @@
     <t xml:space="preserve">10.1880912780762</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2751693725586</t>
+    <t xml:space="preserve">10.2751703262329</t>
   </si>
   <si>
     <t xml:space="preserve">10.5364036560059</t>
@@ -2132,34 +2132,34 @@
     <t xml:space="preserve">10.7540979385376</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4928636550903</t>
+    <t xml:space="preserve">10.4928646087646</t>
   </si>
   <si>
     <t xml:space="preserve">10.4057865142822</t>
   </si>
   <si>
-    <t xml:space="preserve">10.362247467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3187093734741</t>
+    <t xml:space="preserve">10.3622484207153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3187084197998</t>
   </si>
   <si>
     <t xml:space="preserve">11.1894865036011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2765626907349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.450719833374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0167245864868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0602626800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5011930465698</t>
+    <t xml:space="preserve">11.2765617370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4507188796997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0167236328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.060263633728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5011940002441</t>
   </si>
   <si>
     <t xml:space="preserve">12.0100755691528</t>
@@ -2171,13 +2171,13 @@
     <t xml:space="preserve">11.6975450515747</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4743099212646</t>
+    <t xml:space="preserve">11.4743089675903</t>
   </si>
   <si>
     <t xml:space="preserve">11.2064266204834</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4296617507935</t>
+    <t xml:space="preserve">11.4296627044678</t>
   </si>
   <si>
     <t xml:space="preserve">11.608250617981</t>
@@ -2198,25 +2198,25 @@
     <t xml:space="preserve">10.8938961029053</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1617794036865</t>
+    <t xml:space="preserve">11.1617803573608</t>
   </si>
   <si>
     <t xml:space="preserve">11.0724849700928</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9207801818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1886615753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2333106994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3226051330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8761329650879</t>
+    <t xml:space="preserve">11.9207811355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1886625289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2333097457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3226041793823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8761339187622</t>
   </si>
   <si>
     <t xml:space="preserve">12.1440162658691</t>
@@ -2234,19 +2234,19 @@
     <t xml:space="preserve">13.4834299087524</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9299011230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8406066894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0191946029663</t>
+    <t xml:space="preserve">13.9299001693726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8406057357788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0191955566406</t>
   </si>
   <si>
     <t xml:space="preserve">12.9030170440674</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0816049575806</t>
+    <t xml:space="preserve">13.0816040039062</t>
   </si>
   <si>
     <t xml:space="preserve">13.036958694458</t>
@@ -2261,25 +2261,25 @@
     <t xml:space="preserve">13.3941354751587</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9745473861694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2601938247681</t>
+    <t xml:space="preserve">13.9745464324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2601947784424</t>
   </si>
   <si>
     <t xml:space="preserve">13.6620187759399</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6173706054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.88525390625</t>
+    <t xml:space="preserve">13.6173715591431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8852548599243</t>
   </si>
   <si>
     <t xml:space="preserve">14.6442546844482</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7781972885132</t>
+    <t xml:space="preserve">14.7781953811646</t>
   </si>
   <si>
     <t xml:space="preserve">14.9121379852295</t>
@@ -2288,10 +2288,10 @@
     <t xml:space="preserve">15.090726852417</t>
   </si>
   <si>
-    <t xml:space="preserve">14.733549118042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4210195541382</t>
+    <t xml:space="preserve">14.7335481643677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4210186004639</t>
   </si>
   <si>
     <t xml:space="preserve">14.5103130340576</t>
@@ -2303,10 +2303,10 @@
     <t xml:space="preserve">15.8497285842896</t>
   </si>
   <si>
-    <t xml:space="preserve">15.805079460144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0729637145996</t>
+    <t xml:space="preserve">15.8050813674927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.072961807251</t>
   </si>
   <si>
     <t xml:space="preserve">16.3854923248291</t>
@@ -2315,7 +2315,7 @@
     <t xml:space="preserve">16.9212589263916</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1891384124756</t>
+    <t xml:space="preserve">17.1891403198242</t>
   </si>
   <si>
     <t xml:space="preserve">16.7426681518555</t>
@@ -2324,7 +2324,7 @@
     <t xml:space="preserve">17.7249050140381</t>
   </si>
   <si>
-    <t xml:space="preserve">17.769552230835</t>
+    <t xml:space="preserve">17.7695541381836</t>
   </si>
   <si>
     <t xml:space="preserve">17.8142013549805</t>
@@ -2348,16 +2348,16 @@
     <t xml:space="preserve">16.6980228424072</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3053169250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5909652709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2160243988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9481410980225</t>
+    <t xml:space="preserve">18.3053188323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5909633636475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2160224914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9481430053711</t>
   </si>
   <si>
     <t xml:space="preserve">19.0196723937988</t>
@@ -2375,7 +2375,7 @@
     <t xml:space="preserve">20.9841461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8055553436279</t>
+    <t xml:space="preserve">20.8055572509766</t>
   </si>
   <si>
     <t xml:space="preserve">21.0734405517578</t>
@@ -2387,7 +2387,7 @@
     <t xml:space="preserve">20.0019092559814</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8233184814453</t>
+    <t xml:space="preserve">19.8233203887939</t>
   </si>
   <si>
     <t xml:space="preserve">20.2697906494141</t>
@@ -2411,16 +2411,16 @@
     <t xml:space="preserve">20.7162609100342</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4483795166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4306182861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3413200378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.323558807373</t>
+    <t xml:space="preserve">20.4483776092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4306163787842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3413219451904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3235607147217</t>
   </si>
   <si>
     <t xml:space="preserve">21.6092052459717</t>
@@ -71220,7 +71220,7 @@
     </row>
     <row r="2580">
       <c r="A2580" s="1" t="n">
-        <v>46078.691099537</v>
+        <v>46078.3333333333</v>
       </c>
       <c r="B2580" t="n">
         <v>7100</v>
@@ -71241,6 +71241,32 @@
         <v>1252</v>
       </c>
       <c r="H2580" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2581">
+      <c r="A2581" s="1" t="n">
+        <v>46079.6912037037</v>
+      </c>
+      <c r="B2581" t="n">
+        <v>4380</v>
+      </c>
+      <c r="C2581" t="n">
+        <v>14.3000001907349</v>
+      </c>
+      <c r="D2581" t="n">
+        <v>14.0500001907349</v>
+      </c>
+      <c r="E2581" t="n">
+        <v>14.0500001907349</v>
+      </c>
+      <c r="F2581" t="n">
+        <v>14</v>
+      </c>
+      <c r="G2581" t="s">
+        <v>1262</v>
+      </c>
+      <c r="H2581" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SAB.MI.xlsx
+++ b/data/SAB.MI.xlsx
@@ -38,25 +38,25 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56568145751953</t>
+    <t xml:space="preserve">8.56568050384521</t>
   </si>
   <si>
     <t xml:space="preserve">SAB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61822986602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4831018447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33296012878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37049388885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31794548034668</t>
+    <t xml:space="preserve">8.61823081970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48310089111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33295917510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3704948425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31794357299805</t>
   </si>
   <si>
     <t xml:space="preserve">8.25788593292236</t>
@@ -65,202 +65,202 @@
     <t xml:space="preserve">8.16029357910156</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88252878189087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52969026565552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66481971740723</t>
+    <t xml:space="preserve">7.88252830505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52969121932983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66482067108154</t>
   </si>
   <si>
     <t xml:space="preserve">7.62728452682495</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61227035522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73989343643188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75490665435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76992177963257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89754247665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61977767944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79994916915894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72487783432007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65731334686279</t>
+    <t xml:space="preserve">7.61226987838745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73989248275757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75490713119507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76991987228394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89754152297974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61977577209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79995012283325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72487831115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65731477737427</t>
   </si>
   <si>
     <t xml:space="preserve">7.5071702003479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34201145172119</t>
+    <t xml:space="preserve">7.34201240539551</t>
   </si>
   <si>
     <t xml:space="preserve">7.54470586776733</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39080905914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58224296569824</t>
+    <t xml:space="preserve">7.39080810546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58224058151245</t>
   </si>
   <si>
     <t xml:space="preserve">7.82247066497803</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08522129058838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11525058746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95760154724121</t>
+    <t xml:space="preserve">8.08522319793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1152515411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95760107040405</t>
   </si>
   <si>
     <t xml:space="preserve">8.06270027160645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03267097473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92006492614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77742767333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86751317977905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80745697021484</t>
+    <t xml:space="preserve">8.03267192840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92006397247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.777428150177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86751365661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80745601654053</t>
   </si>
   <si>
     <t xml:space="preserve">7.98762893676758</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04017925262451</t>
+    <t xml:space="preserve">8.0401782989502</t>
   </si>
   <si>
     <t xml:space="preserve">7.99513578414917</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96510648727417</t>
+    <t xml:space="preserve">7.96510791778564</t>
   </si>
   <si>
     <t xml:space="preserve">7.90505027770996</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93507766723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89003562927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94258642196655</t>
+    <t xml:space="preserve">7.93507719039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89003610610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94258594512939</t>
   </si>
   <si>
     <t xml:space="preserve">7.82997751235962</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81496286392212</t>
+    <t xml:space="preserve">7.81496381759644</t>
   </si>
   <si>
     <t xml:space="preserve">7.73238515853882</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64980554580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71737003326416</t>
+    <t xml:space="preserve">7.64980506896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71737194061279</t>
   </si>
   <si>
     <t xml:space="preserve">7.67232704162598</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63479089736938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51467800140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64229917526245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56722736358643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70235633850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.747398853302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46963357925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69484901428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4921555519104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47338819503784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43585014343262</t>
+    <t xml:space="preserve">7.6347918510437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51467657089233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64229869842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56722688674927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70235538482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74739933013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46963453292847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69484996795654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49215507507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47338771820068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43585157394409</t>
   </si>
   <si>
     <t xml:space="preserve">7.50341606140137</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48089456558228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59725570678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42834377288818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38705492019653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37204122543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31949090957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28195476531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52122068405151</t>
+    <t xml:space="preserve">7.4808931350708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59725713729858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42834520339966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38705539703369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37204027175903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31949138641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28195428848267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52122163772583</t>
   </si>
   <si>
     <t xml:space="preserve">7.80533933639526</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75009441375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75798606872559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81323003768921</t>
+    <t xml:space="preserve">7.75009346008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75798654556274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81323099136353</t>
   </si>
   <si>
     <t xml:space="preserve">7.8605842590332</t>
@@ -269,61 +269,61 @@
     <t xml:space="preserve">7.69879484176636</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58435869216919</t>
+    <t xml:space="preserve">7.58435773849487</t>
   </si>
   <si>
     <t xml:space="preserve">7.68695735931396</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57646703720093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53700590133667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49754571914673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28445720672607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92536354064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.079261302948</t>
+    <t xml:space="preserve">7.57646608352661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53700685501099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49754524230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28445672988892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92536401748657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07926082611084</t>
   </si>
   <si>
     <t xml:space="preserve">7.22921228408813</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45808458328247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2607798576355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37127065658569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26472759246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34759426116943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46992349624634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3673243522644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37916374206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13450574874878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18975162506104</t>
+    <t xml:space="preserve">7.45808506011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26078033447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37127113342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26472616195679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34759521484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46992301940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36732530593872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37916231155396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13450527191162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18975067138672</t>
   </si>
   <si>
     <t xml:space="preserve">7.10293769836426</t>
@@ -335,112 +335,112 @@
     <t xml:space="preserve">7.10688304901123</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20553684234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1818585395813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22132015228271</t>
+    <t xml:space="preserve">7.20553541183472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18185949325562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22131967544556</t>
   </si>
   <si>
     <t xml:space="preserve">7.19369745254517</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24894332885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19764423370361</t>
+    <t xml:space="preserve">7.24894285202026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19764280319214</t>
   </si>
   <si>
     <t xml:space="preserve">7.18580532073975</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22526502609253</t>
+    <t xml:space="preserve">7.22526550292969</t>
   </si>
   <si>
     <t xml:space="preserve">7.20948219299316</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31602621078491</t>
+    <t xml:space="preserve">7.3160252571106</t>
   </si>
   <si>
     <t xml:space="preserve">7.21342897415161</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16607427597046</t>
+    <t xml:space="preserve">7.16607522964478</t>
   </si>
   <si>
     <t xml:space="preserve">7.24499654769897</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13055944442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11082983016968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17791223526001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23315858840942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2765645980835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30024099349976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29234933853149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.241051197052</t>
+    <t xml:space="preserve">7.13056039810181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11083030700684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17791318893433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23315811157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27656650543213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30024194717407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29234838485718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24105167388916</t>
   </si>
   <si>
     <t xml:space="preserve">7.1187219619751</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09504508972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00428485870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94509506225586</t>
+    <t xml:space="preserve">7.09504652023315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00428628921509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9450945854187</t>
   </si>
   <si>
     <t xml:space="preserve">6.93325614929199</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09899091720581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15423583984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13845348358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15818214416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05558490753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07136869430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06742429733276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02401638031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04769277572632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0634765625</t>
+    <t xml:space="preserve">7.09899044036865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15423631668091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13845252990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1581826210022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05558347702026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07136917114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06742286682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02401542663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04769229888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06347703933716</t>
   </si>
   <si>
     <t xml:space="preserve">7.08320760726929</t>
@@ -452,61 +452,61 @@
     <t xml:space="preserve">7.04374742507935</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03190898895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05953121185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03585338592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17396688461304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90563344955444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91352605819702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93720197677612</t>
+    <t xml:space="preserve">7.03190851211548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05953073501587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03585433959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17396783828735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9056339263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91352653503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93720149993896</t>
   </si>
   <si>
     <t xml:space="preserve">6.92141819000244</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94114971160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9687705039978</t>
+    <t xml:space="preserve">6.94114923477173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96877002716064</t>
   </si>
   <si>
     <t xml:space="preserve">7.14239883422852</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45019197463989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79349946975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92372274398804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04999446868896</t>
+    <t xml:space="preserve">7.45019245147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79350090026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92372179031372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04999732971191</t>
   </si>
   <si>
     <t xml:space="preserve">8.207839012146</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16837882995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08945655822754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19994735717773</t>
+    <t xml:space="preserve">8.16837787628174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08945751190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19994831085205</t>
   </si>
   <si>
     <t xml:space="preserve">8.06578063964844</t>
@@ -521,7 +521,7 @@
     <t xml:space="preserve">8.32622146606445</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55509376525879</t>
+    <t xml:space="preserve">8.55509471893311</t>
   </si>
   <si>
     <t xml:space="preserve">8.56298637390137</t>
@@ -530,34 +530,34 @@
     <t xml:space="preserve">8.42881870269775</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35779190063477</t>
+    <t xml:space="preserve">8.35778903961182</t>
   </si>
   <si>
     <t xml:space="preserve">8.39725112915039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42092609405518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44460296630859</t>
+    <t xml:space="preserve">8.42092704772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44460391998291</t>
   </si>
   <si>
     <t xml:space="preserve">8.40514278411865</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26308345794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18416213989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30254554748535</t>
+    <t xml:space="preserve">8.26308441162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18416309356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30254364013672</t>
   </si>
   <si>
     <t xml:space="preserve">8.22362327575684</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2867603302002</t>
+    <t xml:space="preserve">8.28676128387451</t>
   </si>
   <si>
     <t xml:space="preserve">8.25519180297852</t>
@@ -569,25 +569,25 @@
     <t xml:space="preserve">8.31043815612793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36568355560303</t>
+    <t xml:space="preserve">8.36568164825439</t>
   </si>
   <si>
     <t xml:space="preserve">8.33411407470703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34200668334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46038722991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62612247467041</t>
+    <t xml:space="preserve">8.34200382232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46038818359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62612438201904</t>
   </si>
   <si>
     <t xml:space="preserve">8.74450588226318</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88656330108643</t>
+    <t xml:space="preserve">8.88656520843506</t>
   </si>
   <si>
     <t xml:space="preserve">9.0049467086792</t>
@@ -596,19 +596,19 @@
     <t xml:space="preserve">9.23381900787354</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30484771728516</t>
+    <t xml:space="preserve">9.30484867095947</t>
   </si>
   <si>
     <t xml:space="preserve">9.2653865814209</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16278839111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19435882568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24960422515869</t>
+    <t xml:space="preserve">9.16279125213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19435691833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24960327148438</t>
   </si>
   <si>
     <t xml:space="preserve">9.29695606231689</t>
@@ -617,10 +617,10 @@
     <t xml:space="preserve">9.36798667907715</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54950523376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67577838897705</t>
+    <t xml:space="preserve">9.54950618743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67577934265137</t>
   </si>
   <si>
     <t xml:space="preserve">9.7468090057373</t>
@@ -638,28 +638,28 @@
     <t xml:space="preserve">10.2913675308228</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2597980499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1493072509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0861730575562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0151405334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1019563674927</t>
+    <t xml:space="preserve">10.2597999572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1493082046509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0861721038818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0151424407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.101954460144</t>
   </si>
   <si>
     <t xml:space="preserve">10.1650924682617</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0546026229858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1808776855469</t>
+    <t xml:space="preserve">10.0546035766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1808786392212</t>
   </si>
   <si>
     <t xml:space="preserve">10.1177406311035</t>
@@ -668,16 +668,16 @@
     <t xml:space="preserve">10.1887693405151</t>
   </si>
   <si>
-    <t xml:space="preserve">10.070387840271</t>
+    <t xml:space="preserve">10.0703868865967</t>
   </si>
   <si>
     <t xml:space="preserve">10.1098489761353</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0230331420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.496563911438</t>
+    <t xml:space="preserve">10.0230350494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4965629577637</t>
   </si>
   <si>
     <t xml:space="preserve">10.4176406860352</t>
@@ -686,13 +686,13 @@
     <t xml:space="preserve">10.3150444030762</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7333288192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4492101669312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5597009658813</t>
+    <t xml:space="preserve">10.7333278656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4492111206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.559700012207</t>
   </si>
   <si>
     <t xml:space="preserve">10.6386213302612</t>
@@ -701,25 +701,25 @@
     <t xml:space="preserve">10.591269493103</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0095529556274</t>
+    <t xml:space="preserve">11.0095539093018</t>
   </si>
   <si>
     <t xml:space="preserve">10.8832788467407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3410243988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0592098236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9171514511108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0513181686401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6882781982422</t>
+    <t xml:space="preserve">11.3410234451294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0592107772827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9171504974365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0513191223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6882801055908</t>
   </si>
   <si>
     <t xml:space="preserve">11.6803865432739</t>
@@ -740,7 +740,7 @@
     <t xml:space="preserve">12.7379350662231</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4728555679321</t>
+    <t xml:space="preserve">12.4728546142578</t>
   </si>
   <si>
     <t xml:space="preserve">12.6518535614014</t>
@@ -755,10 +755,10 @@
     <t xml:space="preserve">12.9203491210938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8715314865112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9366216659546</t>
+    <t xml:space="preserve">12.8715305328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.936619758606</t>
   </si>
   <si>
     <t xml:space="preserve">12.8064413070679</t>
@@ -770,52 +770,52 @@
     <t xml:space="preserve">12.8227138519287</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5209159851074</t>
+    <t xml:space="preserve">11.5209150314331</t>
   </si>
   <si>
     <t xml:space="preserve">11.8463659286499</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7812757492065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9114551544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9277267456055</t>
+    <t xml:space="preserve">11.7812747955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9114570617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9277276992798</t>
   </si>
   <si>
     <t xml:space="preserve">11.9602727890015</t>
   </si>
   <si>
-    <t xml:space="preserve">11.805685043335</t>
+    <t xml:space="preserve">11.8056840896606</t>
   </si>
   <si>
     <t xml:space="preserve">12.1311321258545</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0009546279907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9846820831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0416355133057</t>
+    <t xml:space="preserve">12.0009536743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9846811294556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0416345596313</t>
   </si>
   <si>
     <t xml:space="preserve">12.0823163986206</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9765462875366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8789110183716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7161846160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4720983505249</t>
+    <t xml:space="preserve">11.9765453338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8789100646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7161855697632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4720993041992</t>
   </si>
   <si>
     <t xml:space="preserve">11.5534601211548</t>
@@ -824,40 +824,40 @@
     <t xml:space="preserve">11.5860052108765</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7975492477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8951826095581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0904521942139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1636781692505</t>
+    <t xml:space="preserve">11.7975473403931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8951835632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0904531478882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1636800765991</t>
   </si>
   <si>
     <t xml:space="preserve">12.0741806030273</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2287683486938</t>
+    <t xml:space="preserve">12.2287673950195</t>
   </si>
   <si>
     <t xml:space="preserve">12.1392698287964</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2043600082397</t>
+    <t xml:space="preserve">12.2043609619141</t>
   </si>
   <si>
     <t xml:space="preserve">12.1880865097046</t>
   </si>
   <si>
-    <t xml:space="preserve">12.147406578064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2531766891479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3670845031738</t>
+    <t xml:space="preserve">12.1474056243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2531785964966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3670864105225</t>
   </si>
   <si>
     <t xml:space="preserve">12.4077663421631</t>
@@ -866,13 +866,13 @@
     <t xml:space="preserve">12.448447227478</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9447584152222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7820320129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.895941734314</t>
+    <t xml:space="preserve">12.9447574615479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7820329666138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8959407806396</t>
   </si>
   <si>
     <t xml:space="preserve">13.0098476409912</t>
@@ -884,7 +884,7 @@
     <t xml:space="preserve">12.8552589416504</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7332143783569</t>
+    <t xml:space="preserve">12.7332153320312</t>
   </si>
   <si>
     <t xml:space="preserve">12.7738962173462</t>
@@ -896,7 +896,7 @@
     <t xml:space="preserve">13.2620697021484</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6851558685303</t>
+    <t xml:space="preserve">13.685154914856</t>
   </si>
   <si>
     <t xml:space="preserve">13.9292421340942</t>
@@ -905,64 +905,64 @@
     <t xml:space="preserve">13.9943332672119</t>
   </si>
   <si>
-    <t xml:space="preserve">13.750244140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.815336227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8316097259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0187406539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0268783569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1814680099487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1570568084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2302837371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7754106521606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3205394744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2961311340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4588565826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8249864578247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7924432754517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5076713562012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8493957519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8656673431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5158100128174</t>
+    <t xml:space="preserve">13.7502450942993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.815333366394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8316087722778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.018741607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0268774032593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1814661026001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1570558547974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2302827835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7754125595093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3205423355103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2961292266846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4588556289673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8249883651733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.792441368103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5076732635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8493967056274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.865668296814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5158090591431</t>
   </si>
   <si>
     <t xml:space="preserve">16.0039844512939</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2643451690674</t>
+    <t xml:space="preserve">16.2643432617188</t>
   </si>
   <si>
     <t xml:space="preserve">16.776927947998</t>
@@ -971,7 +971,7 @@
     <t xml:space="preserve">16.9559230804443</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4115524291992</t>
+    <t xml:space="preserve">17.4115543365479</t>
   </si>
   <si>
     <t xml:space="preserve">17.0454235076904</t>
@@ -980,7 +980,7 @@
     <t xml:space="preserve">18.0787258148193</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6475048065186</t>
+    <t xml:space="preserve">17.6475067138672</t>
   </si>
   <si>
     <t xml:space="preserve">18.0217704772949</t>
@@ -995,22 +995,22 @@
     <t xml:space="preserve">18.2984046936035</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4123077392578</t>
+    <t xml:space="preserve">18.4123115539551</t>
   </si>
   <si>
     <t xml:space="preserve">18.1682243347168</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1600875854492</t>
+    <t xml:space="preserve">18.1600856781006</t>
   </si>
   <si>
     <t xml:space="preserve">17.9160003662109</t>
   </si>
   <si>
-    <t xml:space="preserve">17.265100479126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0861034393311</t>
+    <t xml:space="preserve">17.2651023864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0861053466797</t>
   </si>
   <si>
     <t xml:space="preserve">17.2976474761963</t>
@@ -1019,28 +1019,28 @@
     <t xml:space="preserve">17.0047416687012</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1267852783203</t>
+    <t xml:space="preserve">17.1267833709717</t>
   </si>
   <si>
     <t xml:space="preserve">16.8745613098145</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0779647827148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8664226531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7850608825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9884643554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5979270935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9152450561523</t>
+    <t xml:space="preserve">17.0779685974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8664264678955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.785062789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9884700775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5979309082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9152412414551</t>
   </si>
   <si>
     <t xml:space="preserve">16.8338794708252</t>
@@ -1049,46 +1049,46 @@
     <t xml:space="preserve">16.9640617370605</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8826942443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9233779907227</t>
+    <t xml:space="preserve">16.882698059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9233798980713</t>
   </si>
   <si>
     <t xml:space="preserve">17.1349239349365</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0698280334473</t>
+    <t xml:space="preserve">17.0698299407959</t>
   </si>
   <si>
     <t xml:space="preserve">17.1674671173096</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6637744903564</t>
+    <t xml:space="preserve">17.6637763977051</t>
   </si>
   <si>
     <t xml:space="preserve">18.2251777648926</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8598041534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0632095336914</t>
+    <t xml:space="preserve">18.859806060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.06321144104</t>
   </si>
   <si>
     <t xml:space="preserve">18.7052154541016</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6319904327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7377643585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7133502960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5913105010986</t>
+    <t xml:space="preserve">18.6319885253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7377586364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7133522033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.59130859375</t>
   </si>
   <si>
     <t xml:space="preserve">18.3065395355225</t>
@@ -1100,46 +1100,46 @@
     <t xml:space="preserve">18.2170391082764</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2089061737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4611282348633</t>
+    <t xml:space="preserve">18.2089080810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4611301422119</t>
   </si>
   <si>
     <t xml:space="preserve">17.5417327880859</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9071083068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4758834838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3945217132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1097526550293</t>
+    <t xml:space="preserve">16.9071102142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.475887298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3945236206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1097545623779</t>
   </si>
   <si>
     <t xml:space="preserve">16.3619804382324</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2806167602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3782501220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.199254989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2236633300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2724800109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6792907714844</t>
+    <t xml:space="preserve">16.2806186676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3782482147217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1992530822754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2236671447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2724781036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.679292678833</t>
   </si>
   <si>
     <t xml:space="preserve">16.3131618499756</t>
@@ -1157,16 +1157,16 @@
     <t xml:space="preserve">16.3538417816162</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0283946990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9144830703735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1822233200073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9706792831421</t>
+    <t xml:space="preserve">16.028392791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9144859313965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.182225227356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9706811904907</t>
   </si>
   <si>
     <t xml:space="preserve">15.1008596420288</t>
@@ -1175,52 +1175,52 @@
     <t xml:space="preserve">14.8730487823486</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2221460342407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.847882270813</t>
+    <t xml:space="preserve">14.2221479415894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8478813171387</t>
   </si>
   <si>
     <t xml:space="preserve">14.8893194198608</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1984958648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3937664031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5402183532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9381370544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.59641456604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.40114402771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2058725357056</t>
+    <t xml:space="preserve">15.1984968185425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3937654495239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5402193069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.938136100769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5964136123657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4011449813843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2058753967285</t>
   </si>
   <si>
     <t xml:space="preserve">14.1082401275635</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0594244003296</t>
+    <t xml:space="preserve">14.0594234466553</t>
   </si>
   <si>
     <t xml:space="preserve">13.9129705429077</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0106058120728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3197832107544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6452322006226</t>
+    <t xml:space="preserve">14.0106039047241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3197822570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6452312469482</t>
   </si>
   <si>
     <t xml:space="preserve">14.7428684234619</t>
@@ -1229,40 +1229,40 @@
     <t xml:space="preserve">14.7265949249268</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2147703170776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8079557418823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8567762374878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9544067382812</t>
+    <t xml:space="preserve">15.2147674560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8079586029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8567733764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9544095993042</t>
   </si>
   <si>
     <t xml:space="preserve">14.7916841506958</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2709646224976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0032253265381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4825077056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9218645095825</t>
+    <t xml:space="preserve">14.2709655761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0032291412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4825057983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9218626022339</t>
   </si>
   <si>
     <t xml:space="preserve">14.9055919647217</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0194988250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0520429611206</t>
+    <t xml:space="preserve">15.0194978713989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0520448684692</t>
   </si>
   <si>
     <t xml:space="preserve">16.2562065124512</t>
@@ -1274,64 +1274,64 @@
     <t xml:space="preserve">15.8168506622314</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6215810775757</t>
+    <t xml:space="preserve">15.6215801239014</t>
   </si>
   <si>
     <t xml:space="preserve">15.9307584762573</t>
   </si>
   <si>
-    <t xml:space="preserve">15.686671257019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7192125320435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7029409408569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6703977584839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6053094863892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5653495788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9956817626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0291929244995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0627021789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2470064163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2302522659302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5318422317505</t>
+    <t xml:space="preserve">15.686674118042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.719217300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7029418945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6703996658325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6053104400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5653505325317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9956827163696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0291919708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0627040863037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2470083236694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2302532196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5318403244019</t>
   </si>
   <si>
     <t xml:space="preserve">15.7161464691162</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8669414520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.582106590271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.498330116272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4815759658813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4145545959473</t>
+    <t xml:space="preserve">15.8669404983521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5821084976196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4983320236206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.481575012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4145555496216</t>
   </si>
   <si>
     <t xml:space="preserve">15.179988861084</t>
@@ -1343,16 +1343,16 @@
     <t xml:space="preserve">15.1129674911499</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3589944839478</t>
+    <t xml:space="preserve">14.3589954376221</t>
   </si>
   <si>
     <t xml:space="preserve">14.2919750213623</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2584667205811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4595260620117</t>
+    <t xml:space="preserve">14.2584657669067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4595232009888</t>
   </si>
   <si>
     <t xml:space="preserve">14.4092597961426</t>
@@ -1364,25 +1364,25 @@
     <t xml:space="preserve">13.4039621353149</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4877367019653</t>
+    <t xml:space="preserve">13.4877376556396</t>
   </si>
   <si>
     <t xml:space="preserve">13.2364120483398</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5380010604858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4374723434448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1914443969727</t>
+    <t xml:space="preserve">13.5380020141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4374732971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.191445350647</t>
   </si>
   <si>
     <t xml:space="preserve">13.5882654190063</t>
   </si>
   <si>
-    <t xml:space="preserve">13.688796043396</t>
+    <t xml:space="preserve">13.6887969970703</t>
   </si>
   <si>
     <t xml:space="preserve">13.4207181930542</t>
@@ -1391,10 +1391,10 @@
     <t xml:space="preserve">13.5212469100952</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5715131759644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3201875686646</t>
+    <t xml:space="preserve">13.57151222229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3201856613159</t>
   </si>
   <si>
     <t xml:space="preserve">13.1526374816895</t>
@@ -1412,28 +1412,28 @@
     <t xml:space="preserve">12.8510494232178</t>
   </si>
   <si>
-    <t xml:space="preserve">12.683500289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5662145614624</t>
+    <t xml:space="preserve">12.6834993362427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5662155151367</t>
   </si>
   <si>
     <t xml:space="preserve">12.901312828064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8342943191528</t>
+    <t xml:space="preserve">12.8342933654785</t>
   </si>
   <si>
     <t xml:space="preserve">12.482439994812</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1473417282104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0803203582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0635652542114</t>
+    <t xml:space="preserve">12.1473407745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0803213119507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0635662078857</t>
   </si>
   <si>
     <t xml:space="preserve">11.9797916412354</t>
@@ -1445,52 +1445,52 @@
     <t xml:space="preserve">11.1923084259033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2258186340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4321756362915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1191282272339</t>
+    <t xml:space="preserve">11.2258176803589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4321746826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1191272735596</t>
   </si>
   <si>
     <t xml:space="preserve">13.2531671524048</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2866773605347</t>
+    <t xml:space="preserve">13.286678314209</t>
   </si>
   <si>
     <t xml:space="preserve">12.7672729492188</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3536977767944</t>
+    <t xml:space="preserve">13.3536968231201</t>
   </si>
   <si>
     <t xml:space="preserve">12.9850883483887</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8007841110229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6332349777222</t>
+    <t xml:space="preserve">12.8007850646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6332340240479</t>
   </si>
   <si>
     <t xml:space="preserve">12.8678035736084</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8122415542603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6279382705688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6111812591553</t>
+    <t xml:space="preserve">11.8122425079346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6279373168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6111822128296</t>
   </si>
   <si>
     <t xml:space="preserve">11.7284669876099</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9630365371704</t>
+    <t xml:space="preserve">11.9630355834961</t>
   </si>
   <si>
     <t xml:space="preserve">11.8960161209106</t>
@@ -1502,61 +1502,61 @@
     <t xml:space="preserve">11.075023651123</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0415143966675</t>
+    <t xml:space="preserve">11.0415134429932</t>
   </si>
   <si>
     <t xml:space="preserve">10.9577388763428</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7566804885864</t>
+    <t xml:space="preserve">10.7566795349121</t>
   </si>
   <si>
     <t xml:space="preserve">10.9242296218872</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9744939804077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7117109298706</t>
+    <t xml:space="preserve">10.9744930267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7117128372192</t>
   </si>
   <si>
     <t xml:space="preserve">12.3651552200317</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4603872299194</t>
+    <t xml:space="preserve">11.4603881835938</t>
   </si>
   <si>
     <t xml:space="preserve">11.1587982177734</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1252889633179</t>
+    <t xml:space="preserve">11.1252880096436</t>
   </si>
   <si>
     <t xml:space="preserve">11.1755542755127</t>
   </si>
   <si>
-    <t xml:space="preserve">11.376612663269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2311162948608</t>
+    <t xml:space="preserve">11.3766136169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2311153411865</t>
   </si>
   <si>
     <t xml:space="preserve">12.3986654281616</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9295263290405</t>
+    <t xml:space="preserve">11.9295253753662</t>
   </si>
   <si>
     <t xml:space="preserve">11.7954864501953</t>
   </si>
   <si>
-    <t xml:space="preserve">11.87926197052</t>
+    <t xml:space="preserve">11.8792610168457</t>
   </si>
   <si>
     <t xml:space="preserve">12.197606086731</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2478704452515</t>
+    <t xml:space="preserve">12.2478713989258</t>
   </si>
   <si>
     <t xml:space="preserve">12.0133008956909</t>
@@ -1565,28 +1565,28 @@
     <t xml:space="preserve">12.1305856704712</t>
   </si>
   <si>
-    <t xml:space="preserve">12.180850982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3819103240967</t>
+    <t xml:space="preserve">12.1808500289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.381911277771</t>
   </si>
   <si>
     <t xml:space="preserve">12.3316459655762</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4656839370728</t>
+    <t xml:space="preserve">12.4656848907471</t>
   </si>
   <si>
     <t xml:space="preserve">12.5997247695923</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7170085906982</t>
+    <t xml:space="preserve">12.7170095443726</t>
   </si>
   <si>
     <t xml:space="preserve">12.8845586776733</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9515781402588</t>
+    <t xml:space="preserve">12.9515790939331</t>
   </si>
   <si>
     <t xml:space="preserve">12.9683332443237</t>
@@ -1595,22 +1595,22 @@
     <t xml:space="preserve">13.2029027938843</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7337636947632</t>
+    <t xml:space="preserve">12.7337656021118</t>
   </si>
   <si>
     <t xml:space="preserve">12.8175392150879</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6499900817871</t>
+    <t xml:space="preserve">12.6499891281128</t>
   </si>
   <si>
     <t xml:space="preserve">12.7002534866333</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5159482955933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7840299606323</t>
+    <t xml:space="preserve">12.5159492492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7840280532837</t>
   </si>
   <si>
     <t xml:space="preserve">13.0018434524536</t>
@@ -1619,7 +1619,7 @@
     <t xml:space="preserve">13.0353536605835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5494585037231</t>
+    <t xml:space="preserve">12.5494594573975</t>
   </si>
   <si>
     <t xml:space="preserve">12.9348230361938</t>
@@ -1631,7 +1631,7 @@
     <t xml:space="preserve">13.3872060775757</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6217775344849</t>
+    <t xml:space="preserve">13.6217784881592</t>
   </si>
   <si>
     <t xml:space="preserve">13.8228368759155</t>
@@ -1640,19 +1640,19 @@
     <t xml:space="preserve">13.5044927597046</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4542264938354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6385316848755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7223062515259</t>
+    <t xml:space="preserve">13.4542274475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6385326385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7223052978516</t>
   </si>
   <si>
     <t xml:space="preserve">13.3704528808594</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0521087646484</t>
+    <t xml:space="preserve">13.0521078109741</t>
   </si>
   <si>
     <t xml:space="preserve">13.0185985565186</t>
@@ -1667,28 +1667,28 @@
     <t xml:space="preserve">12.4991941452026</t>
   </si>
   <si>
-    <t xml:space="preserve">12.748176574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5740213394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3650341033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2257108688354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2779569625854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3127880096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2953729629517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3302040100098</t>
+    <t xml:space="preserve">12.7481775283813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5740203857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3650350570679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2257099151611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2779579162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3127889633179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.295373916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3302030563354</t>
   </si>
   <si>
     <t xml:space="preserve">12.1212177276611</t>
@@ -1697,7 +1697,7 @@
     <t xml:space="preserve">12.5217752456665</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4869432449341</t>
+    <t xml:space="preserve">12.4869441986084</t>
   </si>
   <si>
     <t xml:space="preserve">12.4521131515503</t>
@@ -1709,7 +1709,7 @@
     <t xml:space="preserve">12.0515546798706</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8948154449463</t>
+    <t xml:space="preserve">11.894814491272</t>
   </si>
   <si>
     <t xml:space="preserve">12.2082958221436</t>
@@ -1727,10 +1727,10 @@
     <t xml:space="preserve">12.399866104126</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6262693405151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5391893386841</t>
+    <t xml:space="preserve">12.6262683868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5391902923584</t>
   </si>
   <si>
     <t xml:space="preserve">12.8700857162476</t>
@@ -1739,10 +1739,10 @@
     <t xml:space="preserve">12.9745788574219</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9571628570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9397478103638</t>
+    <t xml:space="preserve">12.95716381073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9397468566895</t>
   </si>
   <si>
     <t xml:space="preserve">12.7830076217651</t>
@@ -1763,13 +1763,13 @@
     <t xml:space="preserve">12.0341396331787</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7206592559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2431268692017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7554903030396</t>
+    <t xml:space="preserve">11.7206602096558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.243124961853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7554912567139</t>
   </si>
   <si>
     <t xml:space="preserve">11.6684131622314</t>
@@ -1787,40 +1787,40 @@
     <t xml:space="preserve">11.790322303772</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8425693511963</t>
+    <t xml:space="preserve">11.842568397522</t>
   </si>
   <si>
     <t xml:space="preserve">11.9470615386963</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8251523971558</t>
+    <t xml:space="preserve">11.8251533508301</t>
   </si>
   <si>
     <t xml:space="preserve">11.8599843978882</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7729072570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8774003982544</t>
+    <t xml:space="preserve">11.7729063034058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8773994445801</t>
   </si>
   <si>
     <t xml:space="preserve">11.6509981155396</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5465040206909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3201017379761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2156095504761</t>
+    <t xml:space="preserve">11.5465049743652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3201026916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2156105041504</t>
   </si>
   <si>
     <t xml:space="preserve">11.4071798324585</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3026847839355</t>
+    <t xml:space="preserve">11.3026866912842</t>
   </si>
   <si>
     <t xml:space="preserve">11.3549337387085</t>
@@ -1829,25 +1829,25 @@
     <t xml:space="preserve">11.3897647857666</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1981925964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9369611740112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0414533615112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8847131729126</t>
+    <t xml:space="preserve">11.1981935501099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9369602203369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0414543151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8847141265869</t>
   </si>
   <si>
     <t xml:space="preserve">10.8672981262207</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9717922210693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8324661254883</t>
+    <t xml:space="preserve">10.971791267395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8324670791626</t>
   </si>
   <si>
     <t xml:space="preserve">10.623480796814</t>
@@ -1856,79 +1856,79 @@
     <t xml:space="preserve">10.6060657501221</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5886497497559</t>
+    <t xml:space="preserve">10.5886487960815</t>
   </si>
   <si>
     <t xml:space="preserve">10.5189876556396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4493246078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6583118438721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7802200317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1633634567261</t>
+    <t xml:space="preserve">10.4493255615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6583127975464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7802209854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1633615493774</t>
   </si>
   <si>
     <t xml:space="preserve">11.1111164093018</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0588693618774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9892063140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8498830795288</t>
+    <t xml:space="preserve">11.0588684082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9892072677612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8498821258545</t>
   </si>
   <si>
     <t xml:space="preserve">11.0240383148193</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0066223144531</t>
+    <t xml:space="preserve">11.0066242218018</t>
   </si>
   <si>
     <t xml:space="preserve">10.7976360321045</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8150520324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9543762207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0936994552612</t>
+    <t xml:space="preserve">10.8150510787964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9543752670288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0937013626099</t>
   </si>
   <si>
     <t xml:space="preserve">11.7032432556152</t>
   </si>
   <si>
-    <t xml:space="preserve">11.981894493103</t>
+    <t xml:space="preserve">11.9818925857544</t>
   </si>
   <si>
     <t xml:space="preserve">11.9296464920044</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9122304916382</t>
+    <t xml:space="preserve">11.9122323989868</t>
   </si>
   <si>
     <t xml:space="preserve">11.8077373504639</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2605409622192</t>
+    <t xml:space="preserve">12.2605419158936</t>
   </si>
   <si>
     <t xml:space="preserve">12.0863876342773</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9644765853882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5290880203247</t>
+    <t xml:space="preserve">11.9644775390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.529088973999</t>
   </si>
   <si>
     <t xml:space="preserve">11.4942569732666</t>
@@ -1946,7 +1946,7 @@
     <t xml:space="preserve">12.1908798217773</t>
   </si>
   <si>
-    <t xml:space="preserve">12.347620010376</t>
+    <t xml:space="preserve">12.3476190567017</t>
   </si>
   <si>
     <t xml:space="preserve">11.5116729736328</t>
@@ -1955,22 +1955,22 @@
     <t xml:space="preserve">11.5987510681152</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7105598449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70045757293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49146938323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03866577148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98641967773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42912292480469</t>
+    <t xml:space="preserve">10.7105579376221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70045852661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49147033691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03866767883301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98641872406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.429123878479</t>
   </si>
   <si>
     <t xml:space="preserve">8.18530464172363</t>
@@ -1979,13 +1979,13 @@
     <t xml:space="preserve">8.22884368896484</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45524501800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.533616065979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49007701873779</t>
+    <t xml:space="preserve">8.45524597167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53361511230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49007797241211</t>
   </si>
   <si>
     <t xml:space="preserve">8.31592178344727</t>
@@ -2000,10 +2000,10 @@
     <t xml:space="preserve">8.38558387756348</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28979873657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41170597076416</t>
+    <t xml:space="preserve">8.28979778289795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41170692443848</t>
   </si>
   <si>
     <t xml:space="preserve">8.4987850189209</t>
@@ -2012,13 +2012,13 @@
     <t xml:space="preserve">8.638108253479</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69035625457764</t>
+    <t xml:space="preserve">8.69035530090332</t>
   </si>
   <si>
     <t xml:space="preserve">8.67294025421143</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79485034942627</t>
+    <t xml:space="preserve">8.79484939575195</t>
   </si>
   <si>
     <t xml:space="preserve">8.96900463104248</t>
@@ -2039,82 +2039,82 @@
     <t xml:space="preserve">9.05608177185059</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14315891265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23023796081543</t>
+    <t xml:space="preserve">9.14316082000732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23023700714111</t>
   </si>
   <si>
     <t xml:space="preserve">9.40439319610596</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66562747955322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57854747772217</t>
+    <t xml:space="preserve">9.66562557220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57854843139648</t>
   </si>
   <si>
     <t xml:space="preserve">9.31731510162354</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88192558288574</t>
+    <t xml:space="preserve">8.88192653656006</t>
   </si>
   <si>
     <t xml:space="preserve">8.65552425384521</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51619911193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60327816009521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56844711303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36085319519043</t>
+    <t xml:space="preserve">8.51620006561279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60327911376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56844615936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36085414886475</t>
   </si>
   <si>
     <t xml:space="preserve">9.83978176116943</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0139360427856</t>
+    <t xml:space="preserve">10.01393699646</t>
   </si>
   <si>
     <t xml:space="preserve">10.1010141372681</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92685890197754</t>
+    <t xml:space="preserve">9.92685985565186</t>
   </si>
   <si>
     <t xml:space="preserve">9.88332176208496</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0574760437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97039794921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70916366577148</t>
+    <t xml:space="preserve">10.0574750900269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97039890289307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7091646194458</t>
   </si>
   <si>
     <t xml:space="preserve">9.75270366668701</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62208652496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53500938415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79624176025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1880922317505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2751703262329</t>
+    <t xml:space="preserve">9.6220874786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53501033782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79624366760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1880912780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2751693725586</t>
   </si>
   <si>
     <t xml:space="preserve">10.5364027023315</t>
@@ -2123,19 +2123,19 @@
     <t xml:space="preserve">10.9282531738281</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0153303146362</t>
+    <t xml:space="preserve">11.0153293609619</t>
   </si>
   <si>
     <t xml:space="preserve">10.7540979385376</t>
   </si>
   <si>
-    <t xml:space="preserve">10.492865562439</t>
+    <t xml:space="preserve">10.4928646087646</t>
   </si>
   <si>
     <t xml:space="preserve">10.4057865142822</t>
   </si>
   <si>
-    <t xml:space="preserve">10.362247467041</t>
+    <t xml:space="preserve">10.3622465133667</t>
   </si>
   <si>
     <t xml:space="preserve">10.3187084197998</t>
@@ -2144,16 +2144,16 @@
     <t xml:space="preserve">11.1894865036011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2765626907349</t>
+    <t xml:space="preserve">11.2765645980835</t>
   </si>
   <si>
     <t xml:space="preserve">11.4507188796997</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0167245864868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0602626800537</t>
+    <t xml:space="preserve">12.0167236328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.060263633728</t>
   </si>
   <si>
     <t xml:space="preserve">12.5011930465698</t>
@@ -2162,7 +2162,7 @@
     <t xml:space="preserve">12.0100746154785</t>
   </si>
   <si>
-    <t xml:space="preserve">11.831485748291</t>
+    <t xml:space="preserve">11.8314867019653</t>
   </si>
   <si>
     <t xml:space="preserve">11.6975450515747</t>
@@ -2171,22 +2171,22 @@
     <t xml:space="preserve">11.4743099212646</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2064266204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4296627044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6082496643066</t>
+    <t xml:space="preserve">11.2064275741577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4296617507935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.608250617981</t>
   </si>
   <si>
     <t xml:space="preserve">11.2510738372803</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5813674926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5367212295532</t>
+    <t xml:space="preserve">10.5813665390015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5367193222046</t>
   </si>
   <si>
     <t xml:space="preserve">11.0278387069702</t>
@@ -2195,22 +2195,22 @@
     <t xml:space="preserve">10.8938970565796</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1617784500122</t>
+    <t xml:space="preserve">11.1617794036865</t>
   </si>
   <si>
     <t xml:space="preserve">11.0724849700928</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9207801818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1886625289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2333097457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3226051330566</t>
+    <t xml:space="preserve">11.9207820892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.188663482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2333106994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3226041793823</t>
   </si>
   <si>
     <t xml:space="preserve">11.8761339187622</t>
@@ -2222,40 +2222,40 @@
     <t xml:space="preserve">11.7868385314941</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0993700027466</t>
+    <t xml:space="preserve">12.0993690490723</t>
   </si>
   <si>
     <t xml:space="preserve">13.4387826919556</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4834308624268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9299020767212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8406066894531</t>
+    <t xml:space="preserve">13.4834289550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9299011230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8406057357788</t>
   </si>
   <si>
     <t xml:space="preserve">14.0191946029663</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9030160903931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0816049575806</t>
+    <t xml:space="preserve">12.9030179977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0816059112549</t>
   </si>
   <si>
     <t xml:space="preserve">13.036958694458</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7513113021851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7959594726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3941354751587</t>
+    <t xml:space="preserve">13.7513122558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7959585189819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3941345214844</t>
   </si>
   <si>
     <t xml:space="preserve">13.9745473861694</t>
@@ -2276,52 +2276,52 @@
     <t xml:space="preserve">14.6442537307739</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7781963348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9121370315552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0907249450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.733549118042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4210186004639</t>
+    <t xml:space="preserve">14.7781953811646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9121379852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0907258987427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7335481643677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4210195541382</t>
   </si>
   <si>
     <t xml:space="preserve">14.5103130340576</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1800212860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8497257232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.805079460144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0729637145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3854942321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9212589263916</t>
+    <t xml:space="preserve">15.1800203323364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8497285842896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8050813674927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.072961807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3854923248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.921257019043</t>
   </si>
   <si>
     <t xml:space="preserve">17.1891403198242</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7426681518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7249069213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.769552230835</t>
+    <t xml:space="preserve">16.7426700592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7249050140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7695541381836</t>
   </si>
   <si>
     <t xml:space="preserve">17.8142013549805</t>
@@ -2348,13 +2348,13 @@
     <t xml:space="preserve">18.3053188323975</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5909671783447</t>
+    <t xml:space="preserve">17.5909652709961</t>
   </si>
   <si>
     <t xml:space="preserve">18.2160243988037</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9481410980225</t>
+    <t xml:space="preserve">17.9481430053711</t>
   </si>
   <si>
     <t xml:space="preserve">19.0196723937988</t>
@@ -2366,58 +2366,58 @@
     <t xml:space="preserve">20.5376739501953</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6269702911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9841442108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8055553436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0734424591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0912017822266</t>
+    <t xml:space="preserve">20.6269683837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9841461181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8055572509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0734386444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0912055969238</t>
   </si>
   <si>
     <t xml:space="preserve">20.0019092559814</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8233222961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2697925567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1982593536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9126129150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5554370880127</t>
+    <t xml:space="preserve">19.8233203887939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2697944641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1982612609863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9126148223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5554389953613</t>
   </si>
   <si>
     <t xml:space="preserve">19.6447315216064</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9303798675537</t>
+    <t xml:space="preserve">18.9303779602051</t>
   </si>
   <si>
     <t xml:space="preserve">20.7162628173828</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4483795166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4306144714355</t>
+    <t xml:space="preserve">20.4483814239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4306163787842</t>
   </si>
   <si>
     <t xml:space="preserve">21.3413219451904</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3235569000244</t>
+    <t xml:space="preserve">22.323558807373</t>
   </si>
   <si>
     <t xml:space="preserve">21.6092052459717</t>
@@ -2429,7 +2429,7 @@
     <t xml:space="preserve">21.7877941131592</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7700290679932</t>
+    <t xml:space="preserve">22.7700309753418</t>
   </si>
   <si>
     <t xml:space="preserve">24.9147033691406</t>
@@ -2441,7 +2441,7 @@
     <t xml:space="preserve">24.0020771026611</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8195533752441</t>
+    <t xml:space="preserve">23.8195514678955</t>
   </si>
   <si>
     <t xml:space="preserve">24.5496520996094</t>
@@ -2456,19 +2456,19 @@
     <t xml:space="preserve">24.0933380126953</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7321796417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3671283721924</t>
+    <t xml:space="preserve">24.732177734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.367130279541</t>
   </si>
   <si>
     <t xml:space="preserve">23.9108142852783</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2719745635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6370258331299</t>
+    <t xml:space="preserve">23.2719764709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6370277404785</t>
   </si>
   <si>
     <t xml:space="preserve">23.5457630157471</t>
@@ -2477,22 +2477,22 @@
     <t xml:space="preserve">24.2758655548096</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7282867431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1846008300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0059642791748</t>
+    <t xml:space="preserve">23.7282886505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1846027374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0059661865234</t>
   </si>
   <si>
     <t xml:space="preserve">22.3593482971191</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8156604766846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2680854797363</t>
+    <t xml:space="preserve">22.8156623840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.268087387085</t>
   </si>
   <si>
     <t xml:space="preserve">22.7243995666504</t>
@@ -2501,7 +2501,7 @@
     <t xml:space="preserve">23.4545021057129</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0894508361816</t>
+    <t xml:space="preserve">23.089448928833</t>
   </si>
   <si>
     <t xml:space="preserve">23.1807117462158</t>
@@ -2510,19 +2510,19 @@
     <t xml:space="preserve">22.9069271087646</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1768226623535</t>
+    <t xml:space="preserve">22.1768245697021</t>
   </si>
   <si>
     <t xml:space="preserve">22.5418758392334</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9943008422852</t>
+    <t xml:space="preserve">21.9942989349365</t>
   </si>
   <si>
     <t xml:space="preserve">22.0855617523193</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5379867553711</t>
+    <t xml:space="preserve">21.5379848480225</t>
   </si>
   <si>
     <t xml:space="preserve">21.7205085754395</t>
@@ -2534,7 +2534,7 @@
     <t xml:space="preserve">21.8117733001709</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4467220306396</t>
+    <t xml:space="preserve">21.4467239379883</t>
   </si>
   <si>
     <t xml:space="preserve">20.8991470336914</t>
@@ -2555,7 +2555,7 @@
     <t xml:space="preserve">19.7127323150635</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0816745758057</t>
+    <t xml:space="preserve">21.081672668457</t>
   </si>
   <si>
     <t xml:space="preserve">24.6409149169922</t>
@@ -2564,13 +2564,13 @@
     <t xml:space="preserve">25.3710155487061</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3749046325684</t>
+    <t xml:space="preserve">26.374906539917</t>
   </si>
   <si>
     <t xml:space="preserve">25.6448059082031</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9185905456543</t>
+    <t xml:space="preserve">25.9185924530029</t>
   </si>
   <si>
     <t xml:space="preserve">25.8273296356201</t>
@@ -2582,34 +2582,34 @@
     <t xml:space="preserve">25.2797546386719</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3632392883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4506130218506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6292495727539</t>
+    <t xml:space="preserve">23.3632373809814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.450611114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6292476654053</t>
   </si>
   <si>
     <t xml:space="preserve">20.9904079437256</t>
   </si>
   <si>
-    <t xml:space="preserve">21.264196395874</t>
+    <t xml:space="preserve">21.2641983032227</t>
   </si>
   <si>
     <t xml:space="preserve">21.1729354858398</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5340957641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.80788230896</t>
+    <t xml:space="preserve">20.5340976715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8078842163086</t>
   </si>
   <si>
     <t xml:space="preserve">20.4428329467773</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9030342102051</t>
+    <t xml:space="preserve">21.9030361175537</t>
   </si>
   <si>
     <t xml:space="preserve">22.6331367492676</t>
@@ -2621,10 +2621,10 @@
     <t xml:space="preserve">20.1690464019775</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3476829528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1651554107666</t>
+    <t xml:space="preserve">19.3476810455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1651573181152</t>
   </si>
   <si>
     <t xml:space="preserve">18.2525291442871</t>
@@ -2633,19 +2633,19 @@
     <t xml:space="preserve">18.6175804138184</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1156368255615</t>
+    <t xml:space="preserve">18.1156349182129</t>
   </si>
   <si>
     <t xml:space="preserve">17.4311676025391</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5224304199219</t>
+    <t xml:space="preserve">17.5224285125732</t>
   </si>
   <si>
     <t xml:space="preserve">16.2447509765625</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5185413360596</t>
+    <t xml:space="preserve">16.5185394287109</t>
   </si>
   <si>
     <t xml:space="preserve">16.6098022460938</t>
@@ -2654,7 +2654,7 @@
     <t xml:space="preserve">16.7010650634766</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6593246459961</t>
+    <t xml:space="preserve">17.6593227386475</t>
   </si>
   <si>
     <t xml:space="preserve">17.2486400604248</t>
@@ -2684,16 +2684,16 @@
     <t xml:space="preserve">21.7661418914795</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8574066162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3137187957764</t>
+    <t xml:space="preserve">21.8574047088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3137168884277</t>
   </si>
   <si>
     <t xml:space="preserve">21.9486656188965</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0399284362793</t>
+    <t xml:space="preserve">22.0399303436279</t>
   </si>
   <si>
     <t xml:space="preserve">21.4923534393311</t>
@@ -2708,49 +2708,49 @@
     <t xml:space="preserve">23.5913944244385</t>
   </si>
   <si>
+    <t xml:space="preserve">23.5001335144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7337303161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8271713256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.387809753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2009315490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6681289672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.621410369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0607719421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9673309326172</t>
+  </si>
+  <si>
     <t xml:space="preserve">23.5001316070557</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7337303161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.827169418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3878116607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2009296417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6681289672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.621410369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.06077003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9673309326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.500129699707</t>
-  </si>
-  <si>
     <t xml:space="preserve">22.9394912719727</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7058906555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6591720581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5190143585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4255714416504</t>
+    <t xml:space="preserve">22.7058925628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6591739654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5190124511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.425573348999</t>
   </si>
   <si>
     <t xml:space="preserve">23.4534130096436</t>
@@ -2768,7 +2768,7 @@
     <t xml:space="preserve">22.0985317230225</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9116535186768</t>
+    <t xml:space="preserve">21.9116554260254</t>
   </si>
   <si>
     <t xml:space="preserve">21.6780548095703</t>
@@ -2780,7 +2780,7 @@
     <t xml:space="preserve">23.0329303741455</t>
   </si>
   <si>
-    <t xml:space="preserve">22.986213684082</t>
+    <t xml:space="preserve">22.9862117767334</t>
   </si>
   <si>
     <t xml:space="preserve">21.8182144165039</t>
@@ -2789,7 +2789,7 @@
     <t xml:space="preserve">22.1919727325439</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7714920043945</t>
+    <t xml:space="preserve">21.7714939117432</t>
   </si>
   <si>
     <t xml:space="preserve">22.2386913299561</t>
@@ -2801,13 +2801,13 @@
     <t xml:space="preserve">23.31325340271</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7993316650391</t>
+    <t xml:space="preserve">22.7993335723877</t>
   </si>
   <si>
     <t xml:space="preserve">22.3321323394775</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5846157073975</t>
+    <t xml:space="preserve">21.5846138000488</t>
   </si>
   <si>
     <t xml:space="preserve">20.930534362793</t>
@@ -2819,7 +2819,7 @@
     <t xml:space="preserve">20.2764568328857</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9494171142578</t>
+    <t xml:space="preserve">19.9494152069092</t>
   </si>
   <si>
     <t xml:space="preserve">20.4166164398193</t>
@@ -2840,25 +2840,25 @@
     <t xml:space="preserve">19.9026947021484</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8092575073242</t>
+    <t xml:space="preserve">19.8092555999756</t>
   </si>
   <si>
     <t xml:space="preserve">19.5756568908691</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3420581817627</t>
+    <t xml:space="preserve">19.3420562744141</t>
   </si>
   <si>
     <t xml:space="preserve">19.2486171722412</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9215755462646</t>
+    <t xml:space="preserve">18.9215774536133</t>
   </si>
   <si>
     <t xml:space="preserve">18.8281364440918</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5758476257324</t>
+    <t xml:space="preserve">18.5758495330811</t>
   </si>
   <si>
     <t xml:space="preserve">18.5010967254639</t>
@@ -2870,7 +2870,7 @@
     <t xml:space="preserve">19.5289363861084</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5945358276367</t>
+    <t xml:space="preserve">18.5945377349854</t>
   </si>
   <si>
     <t xml:space="preserve">18.3702812194824</t>
@@ -2879,7 +2879,7 @@
     <t xml:space="preserve">18.0525856018066</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9217720031738</t>
+    <t xml:space="preserve">17.9217700958252</t>
   </si>
   <si>
     <t xml:space="preserve">17.7535781860352</t>
@@ -2891,10 +2891,10 @@
     <t xml:space="preserve">17.7348899841309</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4919471740723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2303142547607</t>
+    <t xml:space="preserve">17.4919452667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2303161621094</t>
   </si>
   <si>
     <t xml:space="preserve">17.1742496490479</t>
@@ -2909,7 +2909,7 @@
     <t xml:space="preserve">16.4454212188721</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1277256011963</t>
+    <t xml:space="preserve">16.1277236938477</t>
   </si>
   <si>
     <t xml:space="preserve">16.5014839172363</t>
@@ -2921,13 +2921,13 @@
     <t xml:space="preserve">16.0342845916748</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8847818374634</t>
+    <t xml:space="preserve">15.8847808837891</t>
   </si>
   <si>
     <t xml:space="preserve">15.3241405487061</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6044607162476</t>
+    <t xml:space="preserve">15.6044616699219</t>
   </si>
   <si>
     <t xml:space="preserve">15.7352771759033</t>
@@ -2945,7 +2945,7 @@
     <t xml:space="preserve">16.7444267272949</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7257385253906</t>
+    <t xml:space="preserve">16.7257404327393</t>
   </si>
   <si>
     <t xml:space="preserve">16.9313087463379</t>
@@ -2957,7 +2957,7 @@
     <t xml:space="preserve">17.9965229034424</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2581539154053</t>
+    <t xml:space="preserve">18.2581558227539</t>
   </si>
   <si>
     <t xml:space="preserve">17.6601371765137</t>
@@ -2966,10 +2966,10 @@
     <t xml:space="preserve">17.5666980743408</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6414489746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3142185211182</t>
+    <t xml:space="preserve">17.641450881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3142166137695</t>
   </si>
   <si>
     <t xml:space="preserve">18.0712738037109</t>
@@ -3008,7 +3008,7 @@
     <t xml:space="preserve">17.7162017822266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5293235778809</t>
+    <t xml:space="preserve">17.5293216705322</t>
   </si>
   <si>
     <t xml:space="preserve">16.9873714447021</t>
@@ -3020,10 +3020,10 @@
     <t xml:space="preserve">17.5480117797852</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2772274017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.922158241272</t>
+    <t xml:space="preserve">16.277229309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9221572875977</t>
   </si>
   <si>
     <t xml:space="preserve">16.0155963897705</t>
@@ -3032,19 +3032,19 @@
     <t xml:space="preserve">15.9595327377319</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9782209396362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0903491973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8287162780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6231479644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5857725143433</t>
+    <t xml:space="preserve">15.9782218933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0903472900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8287172317505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6231489181519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5857744216919</t>
   </si>
   <si>
     <t xml:space="preserve">16.0716609954834</t>
@@ -3065,10 +3065,10 @@
     <t xml:space="preserve">16.6322994232178</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6136131286621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5762367248535</t>
+    <t xml:space="preserve">16.6136112213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5762348175049</t>
   </si>
   <si>
     <t xml:space="preserve">16.3519802093506</t>
@@ -3077,13 +3077,13 @@
     <t xml:space="preserve">16.2024765014648</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7913398742676</t>
+    <t xml:space="preserve">15.7913408279419</t>
   </si>
   <si>
     <t xml:space="preserve">15.7726516723633</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6979007720947</t>
+    <t xml:space="preserve">15.6978998184204</t>
   </si>
   <si>
     <t xml:space="preserve">16.5201721191406</t>
@@ -3092,34 +3092,34 @@
     <t xml:space="preserve">16.1464138031006</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1651000976562</t>
+    <t xml:space="preserve">16.1650981903076</t>
   </si>
   <si>
     <t xml:space="preserve">16.109037399292</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8474025726318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7539653778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8660936355591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6792144775391</t>
+    <t xml:space="preserve">15.8474044799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7539663314819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8660917282104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6792125701904</t>
   </si>
   <si>
     <t xml:space="preserve">15.8100280761719</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5110216140747</t>
+    <t xml:space="preserve">15.5110206604004</t>
   </si>
   <si>
     <t xml:space="preserve">15.3802042007446</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0064458847046</t>
+    <t xml:space="preserve">15.0064449310303</t>
   </si>
   <si>
     <t xml:space="preserve">14.8008785247803</t>
@@ -3128,7 +3128,7 @@
     <t xml:space="preserve">14.6700620651245</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4271173477173</t>
+    <t xml:space="preserve">14.4271183013916</t>
   </si>
   <si>
     <t xml:space="preserve">14.5766229629517</t>
@@ -3158,13 +3158,13 @@
     <t xml:space="preserve">15.0811967849731</t>
   </si>
   <si>
-    <t xml:space="preserve">15.567084312439</t>
+    <t xml:space="preserve">15.5670852661133</t>
   </si>
   <si>
     <t xml:space="preserve">15.716588973999</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6605262756348</t>
+    <t xml:space="preserve">15.6605253219604</t>
   </si>
   <si>
     <t xml:space="preserve">15.1933259963989</t>
@@ -3173,13 +3173,13 @@
     <t xml:space="preserve">15.3988933563232</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4175815582275</t>
+    <t xml:space="preserve">15.4175806045532</t>
   </si>
   <si>
     <t xml:space="preserve">15.4362697601318</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1372623443604</t>
+    <t xml:space="preserve">15.137261390686</t>
   </si>
   <si>
     <t xml:space="preserve">15.0438222885132</t>
@@ -3191,7 +3191,7 @@
     <t xml:space="preserve">14.9877586364746</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7261266708374</t>
+    <t xml:space="preserve">14.7261257171631</t>
   </si>
   <si>
     <t xml:space="preserve">14.950382232666</t>
@@ -3206,22 +3206,22 @@
     <t xml:space="preserve">14.3149900436401</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5018711090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4084300994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1654863357544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2028617858887</t>
+    <t xml:space="preserve">14.5018701553345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4084310531616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1654872894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.202862739563</t>
   </si>
   <si>
     <t xml:space="preserve">14.2963027954102</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1281108856201</t>
+    <t xml:space="preserve">14.1281099319458</t>
   </si>
   <si>
     <t xml:space="preserve">13.8291034698486</t>
@@ -3236,19 +3236,19 @@
     <t xml:space="preserve">13.4179677963257</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5487842559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6422243118286</t>
+    <t xml:space="preserve">13.5487833023071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6422233581543</t>
   </si>
   <si>
     <t xml:space="preserve">13.45534324646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3992795944214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3245286941528</t>
+    <t xml:space="preserve">13.3992805480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3245277404785</t>
   </si>
   <si>
     <t xml:space="preserve">13.2497758865356</t>
@@ -3257,7 +3257,7 @@
     <t xml:space="preserve">13.0815839767456</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3432159423828</t>
+    <t xml:space="preserve">13.3432149887085</t>
   </si>
   <si>
     <t xml:space="preserve">13.1937122344971</t>
@@ -3266,7 +3266,7 @@
     <t xml:space="preserve">13.3058395385742</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2589273452759</t>
+    <t xml:space="preserve">14.2589263916016</t>
   </si>
   <si>
     <t xml:space="preserve">14.2776145935059</t>
@@ -3275,7 +3275,7 @@
     <t xml:space="preserve">14.7448139190674</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5575485229492</t>
+    <t xml:space="preserve">16.5575466156006</t>
   </si>
   <si>
     <t xml:space="preserve">16.4641094207764</t>
@@ -3284,13 +3284,13 @@
     <t xml:space="preserve">16.4267311096191</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3146018981934</t>
+    <t xml:space="preserve">16.314603805542</t>
   </si>
   <si>
     <t xml:space="preserve">16.2585391998291</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2398509979248</t>
+    <t xml:space="preserve">16.2398529052734</t>
   </si>
   <si>
     <t xml:space="preserve">16.1837882995605</t>
@@ -3299,13 +3299,13 @@
     <t xml:space="preserve">14.8569412231445</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7074384689331</t>
+    <t xml:space="preserve">14.7074375152588</t>
   </si>
   <si>
     <t xml:space="preserve">14.6887502670288</t>
   </si>
   <si>
-    <t xml:space="preserve">14.389741897583</t>
+    <t xml:space="preserve">14.3897428512573</t>
   </si>
   <si>
     <t xml:space="preserve">14.782190322876</t>
@@ -3326,19 +3326,19 @@
     <t xml:space="preserve">12.9881439208984</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5956954956055</t>
+    <t xml:space="preserve">12.5956964492798</t>
   </si>
   <si>
     <t xml:space="preserve">12.7078247070312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7452011108398</t>
+    <t xml:space="preserve">12.7452001571655</t>
   </si>
   <si>
     <t xml:space="preserve">12.4275054931641</t>
   </si>
   <si>
-    <t xml:space="preserve">13.044207572937</t>
+    <t xml:space="preserve">13.0442085266113</t>
   </si>
   <si>
     <t xml:space="preserve">13.3805913925171</t>
@@ -3365,28 +3365,28 @@
     <t xml:space="preserve">13.9972944259644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.015983581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6513738632202</t>
+    <t xml:space="preserve">14.0159826278687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6513748168945</t>
   </si>
   <si>
     <t xml:space="preserve">15.0251340866089</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4736452102661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9034700393677</t>
+    <t xml:space="preserve">15.4736442565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.903468132019</t>
   </si>
   <si>
     <t xml:space="preserve">16.482795715332</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9126205444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8565559387207</t>
+    <t xml:space="preserve">16.912618637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8565578460693</t>
   </si>
   <si>
     <t xml:space="preserve">16.9499950408936</t>
@@ -3395,7 +3395,7 @@
     <t xml:space="preserve">16.8752422332764</t>
   </si>
   <si>
-    <t xml:space="preserve">17.043436050415</t>
+    <t xml:space="preserve">17.0434341430664</t>
   </si>
   <si>
     <t xml:space="preserve">15.9969091415405</t>
@@ -3407,7 +3407,7 @@
     <t xml:space="preserve">15.5483961105347</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6418380737305</t>
+    <t xml:space="preserve">15.6418361663818</t>
   </si>
   <si>
     <t xml:space="preserve">16.4080429077148</t>
@@ -3419,13 +3419,13 @@
     <t xml:space="preserve">16.6790199279785</t>
   </si>
   <si>
-    <t xml:space="preserve">16.585578918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8002986907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.706859588623</t>
+    <t xml:space="preserve">16.5855808258057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8002967834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7068576812744</t>
   </si>
   <si>
     <t xml:space="preserve">16.211820602417</t>
@@ -3434,19 +3434,19 @@
     <t xml:space="preserve">15.3708620071411</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3052616119385</t>
+    <t xml:space="preserve">16.3052597045898</t>
   </si>
   <si>
     <t xml:space="preserve">16.0249404907227</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1273365020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9404602050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6134204864502</t>
+    <t xml:space="preserve">18.1273384094238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9404582977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6134185791016</t>
   </si>
   <si>
     <t xml:space="preserve">17.7070121765137</t>
@@ -71477,7 +71477,7 @@
     </row>
     <row r="2590">
       <c r="A2590" s="1" t="n">
-        <v>46092.6909722222</v>
+        <v>46092.3333333333</v>
       </c>
       <c r="B2590" t="n">
         <v>6746</v>
@@ -71498,6 +71498,32 @@
         <v>1256</v>
       </c>
       <c r="H2590" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2591">
+      <c r="A2591" s="1" t="n">
+        <v>46093.6919328704</v>
+      </c>
+      <c r="B2591" t="n">
+        <v>5545</v>
+      </c>
+      <c r="C2591" t="n">
+        <v>13.8000001907349</v>
+      </c>
+      <c r="D2591" t="n">
+        <v>13.4499998092651</v>
+      </c>
+      <c r="E2591" t="n">
+        <v>13.6000003814697</v>
+      </c>
+      <c r="F2591" t="n">
+        <v>14</v>
+      </c>
+      <c r="G2591" t="s">
+        <v>1261</v>
+      </c>
+      <c r="H2591" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SAB.MI.xlsx
+++ b/data/SAB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1279" uniqueCount="1279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1278" uniqueCount="1278">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,82 +38,82 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56568145751953</t>
+    <t xml:space="preserve">8.56568050384521</t>
   </si>
   <si>
     <t xml:space="preserve">SAB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61822986602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48310279846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33295917510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3704948425293</t>
+    <t xml:space="preserve">8.61823177337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48310089111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33295631408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37049388885498</t>
   </si>
   <si>
     <t xml:space="preserve">8.31794452667236</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25788688659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16029167175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88252782821655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52969169616699</t>
+    <t xml:space="preserve">8.25788593292236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16029357910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88252830505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52969264984131</t>
   </si>
   <si>
     <t xml:space="preserve">7.66482019424438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62728404998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61227035522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73989200592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75490713119507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76992225646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89754343032837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61977767944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79995012283325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72487735748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65731191635132</t>
+    <t xml:space="preserve">7.62728452682495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61227083206177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73989343643188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75490665435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76992082595825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89754199981689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61977624893188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79994964599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72487783432007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65731287002563</t>
   </si>
   <si>
     <t xml:space="preserve">7.50716972351074</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34201097488403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54470539093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39080810546875</t>
+    <t xml:space="preserve">7.34201049804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54470586776733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39080953598022</t>
   </si>
   <si>
     <t xml:space="preserve">7.58224201202393</t>
@@ -128,7 +128,7 @@
     <t xml:space="preserve">8.11525058746338</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95759963989258</t>
+    <t xml:space="preserve">7.95760107040405</t>
   </si>
   <si>
     <t xml:space="preserve">8.06270027160645</t>
@@ -137,37 +137,37 @@
     <t xml:space="preserve">8.03267097473145</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92006397247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77742671966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86751413345337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80745601654053</t>
+    <t xml:space="preserve">7.92006492614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77742767333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86751317977905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80745649337769</t>
   </si>
   <si>
     <t xml:space="preserve">7.98762893676758</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04018020629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99513483047485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96510744094849</t>
+    <t xml:space="preserve">8.0401782989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9951376914978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9651050567627</t>
   </si>
   <si>
     <t xml:space="preserve">7.90505027770996</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93507862091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89003562927246</t>
+    <t xml:space="preserve">7.9350790977478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89003610610962</t>
   </si>
   <si>
     <t xml:space="preserve">7.94258499145508</t>
@@ -176,7 +176,7 @@
     <t xml:space="preserve">7.82997941970825</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81496477127075</t>
+    <t xml:space="preserve">7.81496334075928</t>
   </si>
   <si>
     <t xml:space="preserve">7.73238468170166</t>
@@ -185,289 +185,289 @@
     <t xml:space="preserve">7.64980554580688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71737051010132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67232751846313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63479137420654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51467800140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64229965209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56722831726074</t>
+    <t xml:space="preserve">7.71737003326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6723256111145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63479232788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51467657089233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64229822158813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56722593307495</t>
   </si>
   <si>
     <t xml:space="preserve">7.70235776901245</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74739933013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46963357925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69484853744507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4921555519104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.473388671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43585157394409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50341701507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48089456558228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59725713729858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4283447265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38705444335938</t>
+    <t xml:space="preserve">7.747398853302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46963310241699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69484949111938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49215364456177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47338724136353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43585205078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50341606140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48089599609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59725522994995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42834424972534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38705492019653</t>
   </si>
   <si>
     <t xml:space="preserve">7.37204027175903</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31949043273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28195524215698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52122020721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80533838272095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75009393692017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75798606872559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81323194503784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8605842590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69879627227783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58435821533203</t>
+    <t xml:space="preserve">7.31949090957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28195381164551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52122116088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80533885955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75009441375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75798559188843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81323146820068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86058521270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69879579544067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58435916900635</t>
   </si>
   <si>
     <t xml:space="preserve">7.68695640563965</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57646608352661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53700542449951</t>
+    <t xml:space="preserve">7.57646703720093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53700637817383</t>
   </si>
   <si>
     <t xml:space="preserve">7.49754571914673</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28445720672607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92536401748657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07926082611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22921180725098</t>
+    <t xml:space="preserve">7.28445672988892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92536354064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07926225662231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22921133041382</t>
   </si>
   <si>
     <t xml:space="preserve">7.45808362960815</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26078081130981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37127208709717</t>
+    <t xml:space="preserve">7.26078033447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37127065658569</t>
   </si>
   <si>
     <t xml:space="preserve">7.26472663879395</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34759473800659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46992301940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36732482910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37916326522827</t>
+    <t xml:space="preserve">7.34759521484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46992206573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36732578277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37916278839111</t>
   </si>
   <si>
     <t xml:space="preserve">7.13450622558594</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18975067138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10293769836426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15029144287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10688352584839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20553541183472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18186044692993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22131872177124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19369649887085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24894237518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19764423370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18580484390259</t>
+    <t xml:space="preserve">7.18975162506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10293817520142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15029096603394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10688495635986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20553493499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18185901641846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22131967544556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19369697570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24894380569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19764375686646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18580436706543</t>
   </si>
   <si>
     <t xml:space="preserve">7.22526597976685</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20948266983032</t>
+    <t xml:space="preserve">7.20948219299316</t>
   </si>
   <si>
     <t xml:space="preserve">7.31602573394775</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21342945098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16607570648193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24499607086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13056039810181</t>
+    <t xml:space="preserve">7.21342802047729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16607475280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24499702453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13055992126465</t>
   </si>
   <si>
     <t xml:space="preserve">7.11082983016968</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17791271209717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23315811157227</t>
+    <t xml:space="preserve">7.17791366577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23315715789795</t>
   </si>
   <si>
     <t xml:space="preserve">7.27656507492065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30024099349976</t>
+    <t xml:space="preserve">7.30024242401123</t>
   </si>
   <si>
     <t xml:space="preserve">7.29234933853149</t>
   </si>
   <si>
-    <t xml:space="preserve">7.241051197052</t>
+    <t xml:space="preserve">7.24105024337769</t>
   </si>
   <si>
     <t xml:space="preserve">7.11872243881226</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09504556655884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00428533554077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94509506225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93325662612915</t>
+    <t xml:space="preserve">7.09504461288452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00428581237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94509410858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93325614929199</t>
   </si>
   <si>
     <t xml:space="preserve">7.09899139404297</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15423727035522</t>
+    <t xml:space="preserve">7.15423631668091</t>
   </si>
   <si>
     <t xml:space="preserve">7.13845300674438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1581826210022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0555853843689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07136917114258</t>
+    <t xml:space="preserve">7.15818119049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05558443069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07136821746826</t>
   </si>
   <si>
     <t xml:space="preserve">7.06742286682129</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0240159034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04769229888916</t>
+    <t xml:space="preserve">7.02401638031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04769277572632</t>
   </si>
   <si>
     <t xml:space="preserve">7.06347703933716</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08320713043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05163860321045</t>
+    <t xml:space="preserve">7.08320665359497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05164003372192</t>
   </si>
   <si>
     <t xml:space="preserve">7.04374647140503</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03190755844116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05953025817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03585386276245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17396688461304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9056339263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91352605819702</t>
+    <t xml:space="preserve">7.03190851211548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05953073501587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03585433959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17396783828735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90563297271729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91352701187134</t>
   </si>
   <si>
     <t xml:space="preserve">6.93720245361328</t>
@@ -476,31 +476,31 @@
     <t xml:space="preserve">6.9214186668396</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94114780426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9687705039978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14239835739136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45019149780273</t>
+    <t xml:space="preserve">6.94114875793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96877098083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14239883422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45019197463989</t>
   </si>
   <si>
     <t xml:space="preserve">7.79350137710571</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92372274398804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04999542236328</t>
+    <t xml:space="preserve">7.92372226715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0499963760376</t>
   </si>
   <si>
     <t xml:space="preserve">8.207839012146</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16837978363037</t>
+    <t xml:space="preserve">8.16837787628174</t>
   </si>
   <si>
     <t xml:space="preserve">8.08945751190186</t>
@@ -515,19 +515,19 @@
     <t xml:space="preserve">8.1289176940918</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17626953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32622146606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55509281158447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56298637390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42881965637207</t>
+    <t xml:space="preserve">8.17627048492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32622241973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55509376525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56298732757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42881870269775</t>
   </si>
   <si>
     <t xml:space="preserve">8.35779094696045</t>
@@ -536,88 +536,88 @@
     <t xml:space="preserve">8.39725112915039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42092704772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44460296630859</t>
+    <t xml:space="preserve">8.42092800140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44460391998291</t>
   </si>
   <si>
     <t xml:space="preserve">8.40514278411865</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26308441162109</t>
+    <t xml:space="preserve">8.26308345794678</t>
   </si>
   <si>
     <t xml:space="preserve">8.18416213989258</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30254459381104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22362422943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28676128387451</t>
+    <t xml:space="preserve">8.30254650115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22362232208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2867603302002</t>
   </si>
   <si>
     <t xml:space="preserve">8.25519275665283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34989643096924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31043720245361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36568164825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3341121673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34200572967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46038722991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62612342834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74450588226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88656425476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0049467086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23381900787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30484771728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26538562774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16278839111328</t>
+    <t xml:space="preserve">8.34989833831787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3104362487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36568260192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33411407470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34200477600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46038818359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62612247467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74450397491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88656520843506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00494575500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23381805419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30484867095947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2653865814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16279029846191</t>
   </si>
   <si>
     <t xml:space="preserve">9.19435787200928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24960231781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29695415496826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36798572540283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54950523376465</t>
+    <t xml:space="preserve">9.24960517883301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29695510864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36798667907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54950428009033</t>
   </si>
   <si>
     <t xml:space="preserve">9.67578125</t>
@@ -626,31 +626,31 @@
     <t xml:space="preserve">9.7468090057373</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2203378677368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4807796478271</t>
+    <t xml:space="preserve">10.2203388214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4807786941528</t>
   </si>
   <si>
     <t xml:space="preserve">10.4571027755737</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2913665771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2597990036011</t>
+    <t xml:space="preserve">10.2913675308228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2597980499268</t>
   </si>
   <si>
     <t xml:space="preserve">10.1493082046509</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0861711502075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0151405334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1019554138184</t>
+    <t xml:space="preserve">10.0861730575562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0151424407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1019563674927</t>
   </si>
   <si>
     <t xml:space="preserve">10.165093421936</t>
@@ -659,28 +659,28 @@
     <t xml:space="preserve">10.0546035766602</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1808776855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1177406311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1887693405151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.070387840271</t>
+    <t xml:space="preserve">10.1808767318726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1177387237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1887683868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0703859329224</t>
   </si>
   <si>
     <t xml:space="preserve">10.1098480224609</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0230331420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.496563911438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4176406860352</t>
+    <t xml:space="preserve">10.0230340957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4965629577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4176425933838</t>
   </si>
   <si>
     <t xml:space="preserve">10.3150434494019</t>
@@ -689,10 +689,10 @@
     <t xml:space="preserve">10.7333278656006</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4492101669312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5597009658813</t>
+    <t xml:space="preserve">10.4492111206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.559700012207</t>
   </si>
   <si>
     <t xml:space="preserve">10.6386222839355</t>
@@ -704,16 +704,16 @@
     <t xml:space="preserve">11.0095529556274</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8832807540894</t>
+    <t xml:space="preserve">10.8832788467407</t>
   </si>
   <si>
     <t xml:space="preserve">11.3410234451294</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0592088699341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9171514511108</t>
+    <t xml:space="preserve">12.0592098236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9171524047852</t>
   </si>
   <si>
     <t xml:space="preserve">12.0513181686401</t>
@@ -725,19 +725,19 @@
     <t xml:space="preserve">11.6803865432739</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2644052505493</t>
+    <t xml:space="preserve">12.2644062042236</t>
   </si>
   <si>
     <t xml:space="preserve">12.6274452209473</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5406312942505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6747970581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7379350662231</t>
+    <t xml:space="preserve">12.5406322479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6747980117798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7379341125488</t>
   </si>
   <si>
     <t xml:space="preserve">12.4728555679321</t>
@@ -746,7 +746,7 @@
     <t xml:space="preserve">12.6518526077271</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8471231460571</t>
+    <t xml:space="preserve">12.8471221923828</t>
   </si>
   <si>
     <t xml:space="preserve">12.8145780563354</t>
@@ -755,10 +755,10 @@
     <t xml:space="preserve">12.9203491210938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8715324401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9366216659546</t>
+    <t xml:space="preserve">12.8715305328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9366207122803</t>
   </si>
   <si>
     <t xml:space="preserve">12.8064422607422</t>
@@ -767,16 +767,16 @@
     <t xml:space="preserve">12.6437168121338</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8227157592773</t>
+    <t xml:space="preserve">12.822714805603</t>
   </si>
   <si>
     <t xml:space="preserve">11.5209150314331</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8463659286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7812747955322</t>
+    <t xml:space="preserve">11.8463640213013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7812757492065</t>
   </si>
   <si>
     <t xml:space="preserve">11.9114561080933</t>
@@ -791,10 +791,10 @@
     <t xml:space="preserve">11.8056840896606</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1311340332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.000955581665</t>
+    <t xml:space="preserve">12.1311330795288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0009536743164</t>
   </si>
   <si>
     <t xml:space="preserve">11.9846820831299</t>
@@ -812,16 +812,16 @@
     <t xml:space="preserve">11.8789100646973</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7161836624146</t>
+    <t xml:space="preserve">11.7161865234375</t>
   </si>
   <si>
     <t xml:space="preserve">11.4720983505249</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5534591674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5860052108765</t>
+    <t xml:space="preserve">11.5534601211548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5860061645508</t>
   </si>
   <si>
     <t xml:space="preserve">11.7975473403931</t>
@@ -833,19 +833,19 @@
     <t xml:space="preserve">12.0904521942139</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1636791229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0741806030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2287693023682</t>
+    <t xml:space="preserve">12.1636781692505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.074179649353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2287683486938</t>
   </si>
   <si>
     <t xml:space="preserve">12.1392707824707</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2043590545654</t>
+    <t xml:space="preserve">12.2043609619141</t>
   </si>
   <si>
     <t xml:space="preserve">12.1880855560303</t>
@@ -860,10 +860,10 @@
     <t xml:space="preserve">12.3670845031738</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4077653884888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4484462738037</t>
+    <t xml:space="preserve">12.4077663421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.448447227478</t>
   </si>
   <si>
     <t xml:space="preserve">12.9447584152222</t>
@@ -881,79 +881,79 @@
     <t xml:space="preserve">12.9528942108154</t>
   </si>
   <si>
-    <t xml:space="preserve">12.855260848999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7332153320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7738981246948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9854402542114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2620697021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6851558685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9292430877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9943332672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7502450942993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8153352737427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8316097259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0187397003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.026876449585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1814680099487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1570568084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2302827835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7754135131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3205404281616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2961301803589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4588565826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8249864578247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7924394607544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5076704025269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8493938446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8656663894653</t>
+    <t xml:space="preserve">12.8552598953247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7332143783569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7738962173462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9854383468628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2620706558228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.685154914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9292421340942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9943342208862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7502460479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8153343200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8316087722778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0187406539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0268774032593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1814651489258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.157057762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2302837371826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7754106521606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3205394744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2961311340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4588575363159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.824987411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7924404144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5076723098755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8493928909302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8656673431396</t>
   </si>
   <si>
     <t xml:space="preserve">15.5158100128174</t>
@@ -965,7 +965,7 @@
     <t xml:space="preserve">16.2643451690674</t>
   </si>
   <si>
-    <t xml:space="preserve">16.776927947998</t>
+    <t xml:space="preserve">16.7769298553467</t>
   </si>
   <si>
     <t xml:space="preserve">16.955924987793</t>
@@ -974,40 +974,40 @@
     <t xml:space="preserve">17.4115524291992</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0454235076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0787258148193</t>
+    <t xml:space="preserve">17.0454216003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0787220001221</t>
   </si>
   <si>
     <t xml:space="preserve">17.6475048065186</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0217704772949</t>
+    <t xml:space="preserve">18.0217723846436</t>
   </si>
   <si>
     <t xml:space="preserve">18.0543174743652</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1275444030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2984046936035</t>
+    <t xml:space="preserve">18.1275405883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2984027862549</t>
   </si>
   <si>
     <t xml:space="preserve">18.4123115539551</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1682262420654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1600856781006</t>
+    <t xml:space="preserve">18.1682243347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1600894927979</t>
   </si>
   <si>
     <t xml:space="preserve">17.9160003662109</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2651023864746</t>
+    <t xml:space="preserve">17.265100479126</t>
   </si>
   <si>
     <t xml:space="preserve">17.0861053466797</t>
@@ -1019,31 +1019,31 @@
     <t xml:space="preserve">17.0047416687012</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1267833709717</t>
+    <t xml:space="preserve">17.1267852783203</t>
   </si>
   <si>
     <t xml:space="preserve">16.8745613098145</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0779685974121</t>
+    <t xml:space="preserve">17.0779666900635</t>
   </si>
   <si>
     <t xml:space="preserve">16.8664245605469</t>
   </si>
   <si>
-    <t xml:space="preserve">16.785062789917</t>
+    <t xml:space="preserve">16.7850646972656</t>
   </si>
   <si>
     <t xml:space="preserve">16.988468170166</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5979290008545</t>
+    <t xml:space="preserve">16.5979309082031</t>
   </si>
   <si>
     <t xml:space="preserve">16.9152450561523</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8338775634766</t>
+    <t xml:space="preserve">16.8338813781738</t>
   </si>
   <si>
     <t xml:space="preserve">16.9640598297119</t>
@@ -1052,13 +1052,13 @@
     <t xml:space="preserve">16.882698059082</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9233779907227</t>
+    <t xml:space="preserve">16.923376083374</t>
   </si>
   <si>
     <t xml:space="preserve">17.1349220275879</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0698299407959</t>
+    <t xml:space="preserve">17.0698318481445</t>
   </si>
   <si>
     <t xml:space="preserve">17.1674671173096</t>
@@ -1067,7 +1067,7 @@
     <t xml:space="preserve">17.6637763977051</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2251777648926</t>
+    <t xml:space="preserve">18.2251796722412</t>
   </si>
   <si>
     <t xml:space="preserve">18.8598041534424</t>
@@ -1076,49 +1076,49 @@
     <t xml:space="preserve">19.0632095336914</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7052154541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6319904327393</t>
+    <t xml:space="preserve">18.7052135467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6319885253906</t>
   </si>
   <si>
     <t xml:space="preserve">18.7377624511719</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7133502960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5913105010986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3065414428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6157150268555</t>
+    <t xml:space="preserve">18.7133522033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.59130859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3065395355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6157169342041</t>
   </si>
   <si>
     <t xml:space="preserve">18.217041015625</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2089061737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4611301422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5417308807373</t>
+    <t xml:space="preserve">18.2089042663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4611282348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5417327880859</t>
   </si>
   <si>
     <t xml:space="preserve">16.9071083068848</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4758834838867</t>
+    <t xml:space="preserve">16.4758853912354</t>
   </si>
   <si>
     <t xml:space="preserve">16.3945236206055</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1097564697266</t>
+    <t xml:space="preserve">16.1097545623779</t>
   </si>
   <si>
     <t xml:space="preserve">16.3619785308838</t>
@@ -1127,10 +1127,10 @@
     <t xml:space="preserve">16.2806167602539</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3782501220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.199254989624</t>
+    <t xml:space="preserve">16.3782520294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1992530822754</t>
   </si>
   <si>
     <t xml:space="preserve">16.2236633300781</t>
@@ -1142,223 +1142,223 @@
     <t xml:space="preserve">16.679292678833</t>
   </si>
   <si>
-    <t xml:space="preserve">16.313159942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0934810638428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9470291137695</t>
+    <t xml:space="preserve">16.3131618499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0934829711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9470281600952</t>
   </si>
   <si>
     <t xml:space="preserve">16.1911163330078</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3538436889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0283908843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9144821166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.182222366333</t>
+    <t xml:space="preserve">16.3538417816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0283946990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9144840240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1822233200073</t>
   </si>
   <si>
     <t xml:space="preserve">14.9706811904907</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1008634567261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8730497360229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2221479415894</t>
+    <t xml:space="preserve">15.1008615493774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.873046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2221460342407</t>
   </si>
   <si>
     <t xml:space="preserve">13.8478803634644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8893165588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1984987258911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3937664031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5402173995972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.938136100769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5964136123657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4011449813843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2058725357056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1082391738892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0594234466553</t>
+    <t xml:space="preserve">14.8893175125122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1984958648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3937644958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5402193069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9381380081177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5964164733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4011468887329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2058753967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1082401275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.059422492981</t>
   </si>
   <si>
     <t xml:space="preserve">13.9129705429077</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0106058120728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3197832107544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6452322006226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7428684234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7265939712524</t>
+    <t xml:space="preserve">14.0106039047241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3197822570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6452312469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7428674697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7265949249268</t>
   </si>
   <si>
     <t xml:space="preserve">15.2147693634033</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8079595565796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8567733764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9544086456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7916841506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2709655761719</t>
+    <t xml:space="preserve">14.807954788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8567724227905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9544067382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7916870117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2709646224976</t>
   </si>
   <si>
     <t xml:space="preserve">15.0032262802124</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4825067520142</t>
+    <t xml:space="preserve">14.4825077056885</t>
   </si>
   <si>
     <t xml:space="preserve">14.9218635559082</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9055910110474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0194988250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0520429611206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2562084197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7354850769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8168506622314</t>
+    <t xml:space="preserve">14.9055919647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0194978713989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0520458221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2562046051025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7354869842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8168516159058</t>
   </si>
   <si>
     <t xml:space="preserve">15.6215791702271</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9307565689087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6866693496704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7192163467407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7029399871826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6703987121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6053085327148</t>
+    <t xml:space="preserve">15.9307584762573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6866722106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7192144393921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7029418945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6703996658325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6053066253662</t>
   </si>
   <si>
     <t xml:space="preserve">15.5653495788574</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9956817626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0291919708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0627031326294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2470102310181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2302522659302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5318412780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7161464691162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8669385910034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5821084976196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4983291625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4815759658813</t>
+    <t xml:space="preserve">14.9956827163696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0291957855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0627002716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2470054626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2302532196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5318403244019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7161445617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8669414520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.582106590271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4983320236206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4815740585327</t>
   </si>
   <si>
     <t xml:space="preserve">15.4145565032959</t>
   </si>
   <si>
-    <t xml:space="preserve">15.179988861084</t>
+    <t xml:space="preserve">15.1799879074097</t>
   </si>
   <si>
     <t xml:space="preserve">15.0794582366943</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1129684448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3589954376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.291974067688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2584648132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4595251083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4092597961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5600519180298</t>
+    <t xml:space="preserve">15.1129674911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3589944839478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2919750213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2584657669067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4595241546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4092607498169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5600538253784</t>
   </si>
   <si>
     <t xml:space="preserve">13.4039621353149</t>
@@ -1367,13 +1367,13 @@
     <t xml:space="preserve">13.4877376556396</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2364139556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5380020141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4374732971191</t>
+    <t xml:space="preserve">13.2364120483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5380029678345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4374723434448</t>
   </si>
   <si>
     <t xml:space="preserve">14.1914463043213</t>
@@ -1385,7 +1385,7 @@
     <t xml:space="preserve">13.6887969970703</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4207172393799</t>
+    <t xml:space="preserve">13.4207181930542</t>
   </si>
   <si>
     <t xml:space="preserve">13.5212469100952</t>
@@ -1394,34 +1394,34 @@
     <t xml:space="preserve">13.57151222229</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3201875686646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1526393890381</t>
+    <t xml:space="preserve">13.3201866149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1526384353638</t>
   </si>
   <si>
     <t xml:space="preserve">13.1861476898193</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2196588516235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3034324645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8510484695435</t>
+    <t xml:space="preserve">13.2196569442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3034334182739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8510494232178</t>
   </si>
   <si>
     <t xml:space="preserve">12.6834993362427</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5662136077881</t>
+    <t xml:space="preserve">12.5662145614624</t>
   </si>
   <si>
     <t xml:space="preserve">12.9013137817383</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8342933654785</t>
+    <t xml:space="preserve">12.8342943191528</t>
   </si>
   <si>
     <t xml:space="preserve">12.4824390411377</t>
@@ -1430,10 +1430,10 @@
     <t xml:space="preserve">12.1473407745361</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0803203582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0635643005371</t>
+    <t xml:space="preserve">12.0803213119507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0635671615601</t>
   </si>
   <si>
     <t xml:space="preserve">11.979790687561</t>
@@ -1442,7 +1442,7 @@
     <t xml:space="preserve">11.5609178543091</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1923093795776</t>
+    <t xml:space="preserve">11.192307472229</t>
   </si>
   <si>
     <t xml:space="preserve">11.2258176803589</t>
@@ -1451,10 +1451,10 @@
     <t xml:space="preserve">12.4321746826172</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1191282272339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2531681060791</t>
+    <t xml:space="preserve">13.1191272735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2531671524048</t>
   </si>
   <si>
     <t xml:space="preserve">13.2866773605347</t>
@@ -1463,16 +1463,16 @@
     <t xml:space="preserve">12.7672739028931</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3536977767944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9850883483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8007831573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6332340240479</t>
+    <t xml:space="preserve">13.3536968231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9850873947144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8007841110229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6332349777222</t>
   </si>
   <si>
     <t xml:space="preserve">12.8678035736084</t>
@@ -1481,55 +1481,55 @@
     <t xml:space="preserve">11.8122415542603</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6279373168945</t>
+    <t xml:space="preserve">11.6279382705688</t>
   </si>
   <si>
     <t xml:space="preserve">11.6111822128296</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7284660339355</t>
+    <t xml:space="preserve">11.7284669876099</t>
   </si>
   <si>
     <t xml:space="preserve">11.9630355834961</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8960151672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6614475250244</t>
+    <t xml:space="preserve">11.8960161209106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6614465713501</t>
   </si>
   <si>
     <t xml:space="preserve">11.075023651123</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0415134429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9577379226685</t>
+    <t xml:space="preserve">11.0415153503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9577388763428</t>
   </si>
   <si>
     <t xml:space="preserve">10.7566795349121</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9242286682129</t>
+    <t xml:space="preserve">10.9242296218872</t>
   </si>
   <si>
     <t xml:space="preserve">10.974494934082</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7117109298706</t>
+    <t xml:space="preserve">11.7117118835449</t>
   </si>
   <si>
     <t xml:space="preserve">12.3651552200317</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4603881835938</t>
+    <t xml:space="preserve">11.4603872299194</t>
   </si>
   <si>
     <t xml:space="preserve">11.1587982177734</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1252889633179</t>
+    <t xml:space="preserve">11.1252880096436</t>
   </si>
   <si>
     <t xml:space="preserve">11.1755542755127</t>
@@ -1553,7 +1553,7 @@
     <t xml:space="preserve">11.8792610168457</t>
   </si>
   <si>
-    <t xml:space="preserve">12.197606086731</t>
+    <t xml:space="preserve">12.1976051330566</t>
   </si>
   <si>
     <t xml:space="preserve">12.2478704452515</t>
@@ -1565,28 +1565,28 @@
     <t xml:space="preserve">12.1305856704712</t>
   </si>
   <si>
-    <t xml:space="preserve">12.180850982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3819093704224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3316450119019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4656848907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.599723815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7170076370239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8845596313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9515781402588</t>
+    <t xml:space="preserve">12.1808519363403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.381911277771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3316459655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4656839370728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5997247695923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7170095443726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8845586776733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9515800476074</t>
   </si>
   <si>
     <t xml:space="preserve">12.9683332443237</t>
@@ -1598,13 +1598,13 @@
     <t xml:space="preserve">12.7337636947632</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8175382614136</t>
+    <t xml:space="preserve">12.8175392150879</t>
   </si>
   <si>
     <t xml:space="preserve">12.6499900817871</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7002534866333</t>
+    <t xml:space="preserve">12.7002544403076</t>
   </si>
   <si>
     <t xml:space="preserve">12.5159492492676</t>
@@ -1613,7 +1613,7 @@
     <t xml:space="preserve">12.784029006958</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0018444061279</t>
+    <t xml:space="preserve">13.0018434524536</t>
   </si>
   <si>
     <t xml:space="preserve">13.0353536605835</t>
@@ -1628,16 +1628,16 @@
     <t xml:space="preserve">12.9180688858032</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3872079849243</t>
+    <t xml:space="preserve">13.38720703125</t>
   </si>
   <si>
     <t xml:space="preserve">13.6217775344849</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8228359222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5044937133789</t>
+    <t xml:space="preserve">13.8228349685669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5044927597046</t>
   </si>
   <si>
     <t xml:space="preserve">13.4542264938354</t>
@@ -1646,19 +1646,19 @@
     <t xml:space="preserve">13.6385326385498</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7223062515259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3704538345337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0521078109741</t>
+    <t xml:space="preserve">13.7223072052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3704519271851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0521087646484</t>
   </si>
   <si>
     <t xml:space="preserve">13.0185985565186</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1693935394287</t>
+    <t xml:space="preserve">13.1693925857544</t>
   </si>
   <si>
     <t xml:space="preserve">13.1023731231689</t>
@@ -1667,7 +1667,7 @@
     <t xml:space="preserve">12.499195098877</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7481775283813</t>
+    <t xml:space="preserve">12.7481784820557</t>
   </si>
   <si>
     <t xml:space="preserve">12.5740203857422</t>
@@ -1676,16 +1676,16 @@
     <t xml:space="preserve">12.3650341033936</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2257108688354</t>
+    <t xml:space="preserve">12.2257099151611</t>
   </si>
   <si>
     <t xml:space="preserve">12.2779569625854</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3127889633179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.295373916626</t>
+    <t xml:space="preserve">12.3127880096436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2953729629517</t>
   </si>
   <si>
     <t xml:space="preserve">12.3302030563354</t>
@@ -1697,13 +1697,13 @@
     <t xml:space="preserve">12.5217742919922</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4869441986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4521131515503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.138632774353</t>
+    <t xml:space="preserve">12.4869432449341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.452112197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1386337280273</t>
   </si>
   <si>
     <t xml:space="preserve">12.0515556335449</t>
@@ -1721,25 +1721,25 @@
     <t xml:space="preserve">12.7655925750732</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6436834335327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3998651504517</t>
+    <t xml:space="preserve">12.643684387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.399866104126</t>
   </si>
   <si>
     <t xml:space="preserve">12.6262683868408</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5391893386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8700847625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9745788574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.95716381073</t>
+    <t xml:space="preserve">12.5391912460327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8700866699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9745779037476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9571628570557</t>
   </si>
   <si>
     <t xml:space="preserve">12.9397468566895</t>
@@ -1748,13 +1748,13 @@
     <t xml:space="preserve">12.7830085754395</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6959295272827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.800422668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8875007629395</t>
+    <t xml:space="preserve">12.695930480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8004236221313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8875017166138</t>
   </si>
   <si>
     <t xml:space="preserve">12.1560487747192</t>
@@ -1766,28 +1766,28 @@
     <t xml:space="preserve">11.7206592559814</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2431268692017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7554912567139</t>
+    <t xml:space="preserve">12.2431259155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7554903030396</t>
   </si>
   <si>
     <t xml:space="preserve">11.6684122085571</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9993076324463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0689697265625</t>
+    <t xml:space="preserve">11.9993085861206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0689706802368</t>
   </si>
   <si>
     <t xml:space="preserve">12.1038017272949</t>
   </si>
   <si>
-    <t xml:space="preserve">11.790322303772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.842568397522</t>
+    <t xml:space="preserve">11.7903213500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8425693511963</t>
   </si>
   <si>
     <t xml:space="preserve">11.9470624923706</t>
@@ -1796,10 +1796,10 @@
     <t xml:space="preserve">11.8251523971558</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8599834442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7729072570801</t>
+    <t xml:space="preserve">11.8599843978882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7729063034058</t>
   </si>
   <si>
     <t xml:space="preserve">11.8773994445801</t>
@@ -1811,37 +1811,37 @@
     <t xml:space="preserve">11.5465040206909</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3201026916504</t>
+    <t xml:space="preserve">11.3201017379761</t>
   </si>
   <si>
     <t xml:space="preserve">11.2156095504761</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4071798324585</t>
+    <t xml:space="preserve">11.4071807861328</t>
   </si>
   <si>
     <t xml:space="preserve">11.3026857376099</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3549327850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3897638320923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1981925964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9369611740112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0414543151855</t>
+    <t xml:space="preserve">11.3549337387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3897647857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1981935501099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9369602203369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0414533615112</t>
   </si>
   <si>
     <t xml:space="preserve">10.8847141265869</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8672971725464</t>
+    <t xml:space="preserve">10.8672981262207</t>
   </si>
   <si>
     <t xml:space="preserve">10.9717922210693</t>
@@ -1850,13 +1850,13 @@
     <t xml:space="preserve">10.8324661254883</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6234798431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6060647964478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5886497497559</t>
+    <t xml:space="preserve">10.623480796814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6060657501221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5886487960815</t>
   </si>
   <si>
     <t xml:space="preserve">10.5189876556396</t>
@@ -1868,22 +1868,22 @@
     <t xml:space="preserve">10.6583108901978</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7802200317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1633625030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1111164093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0588693618774</t>
+    <t xml:space="preserve">10.7802209854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1633615493774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1111154556274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0588684082031</t>
   </si>
   <si>
     <t xml:space="preserve">10.9892063140869</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8498830795288</t>
+    <t xml:space="preserve">10.8498821258545</t>
   </si>
   <si>
     <t xml:space="preserve">11.0240383148193</t>
@@ -1892,25 +1892,25 @@
     <t xml:space="preserve">11.0066232681274</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7976360321045</t>
+    <t xml:space="preserve">10.7976369857788</t>
   </si>
   <si>
     <t xml:space="preserve">10.8150520324707</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9543762207031</t>
+    <t xml:space="preserve">10.9543752670288</t>
   </si>
   <si>
     <t xml:space="preserve">11.0937004089355</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7032442092896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.981894493103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9296474456787</t>
+    <t xml:space="preserve">11.7032432556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9818925857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9296464920044</t>
   </si>
   <si>
     <t xml:space="preserve">11.9122304916382</t>
@@ -1922,7 +1922,7 @@
     <t xml:space="preserve">12.2605419158936</t>
   </si>
   <si>
-    <t xml:space="preserve">12.086386680603</t>
+    <t xml:space="preserve">12.0863876342773</t>
   </si>
   <si>
     <t xml:space="preserve">11.9644775390625</t>
@@ -1931,58 +1931,58 @@
     <t xml:space="preserve">11.529088973999</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4942579269409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5813360214233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4768419265747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.685830116272</t>
+    <t xml:space="preserve">11.4942588806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.581335067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4768438339233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6858291625977</t>
   </si>
   <si>
     <t xml:space="preserve">12.1908798217773</t>
   </si>
   <si>
-    <t xml:space="preserve">12.347620010376</t>
+    <t xml:space="preserve">12.3476190567017</t>
   </si>
   <si>
     <t xml:space="preserve">11.5116729736328</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5987501144409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7105588912964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70045852661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49147033691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03866577148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98641967773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.429123878479</t>
+    <t xml:space="preserve">11.5987510681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7105579376221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7004566192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49146938323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03866672515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98641872406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42912292480469</t>
   </si>
   <si>
     <t xml:space="preserve">8.18530464172363</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22884368896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45524501800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.533616065979</t>
+    <t xml:space="preserve">8.22884273529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45524597167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53361511230469</t>
   </si>
   <si>
     <t xml:space="preserve">8.49007701873779</t>
@@ -1991,16 +1991,16 @@
     <t xml:space="preserve">8.31592178344727</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32462978363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16788959503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38558483123779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28979969024658</t>
+    <t xml:space="preserve">8.32462882995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16788864135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38558387756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28979873657227</t>
   </si>
   <si>
     <t xml:space="preserve">8.41170692443848</t>
@@ -2015,13 +2015,13 @@
     <t xml:space="preserve">8.69035625457764</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67293930053711</t>
+    <t xml:space="preserve">8.67294120788574</t>
   </si>
   <si>
     <t xml:space="preserve">8.79484939575195</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96900463104248</t>
+    <t xml:space="preserve">8.96900367736816</t>
   </si>
   <si>
     <t xml:space="preserve">8.75130939483643</t>
@@ -2030,25 +2030,25 @@
     <t xml:space="preserve">8.70777130126953</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83838844299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1866979598999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05608177185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14315891265869</t>
+    <t xml:space="preserve">8.83838748931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18669891357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05608081817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14315986633301</t>
   </si>
   <si>
     <t xml:space="preserve">9.23023796081543</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40439224243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66562652587891</t>
+    <t xml:space="preserve">9.40439319610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66562557220459</t>
   </si>
   <si>
     <t xml:space="preserve">9.57854747772217</t>
@@ -2057,31 +2057,31 @@
     <t xml:space="preserve">9.31731510162354</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88192462921143</t>
+    <t xml:space="preserve">8.88192653656006</t>
   </si>
   <si>
     <t xml:space="preserve">8.65552425384521</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51619911193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6032772064209</t>
+    <t xml:space="preserve">8.51620006561279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60327816009521</t>
   </si>
   <si>
     <t xml:space="preserve">8.56844711303711</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36085510253906</t>
+    <t xml:space="preserve">9.36085319519043</t>
   </si>
   <si>
     <t xml:space="preserve">9.83978176116943</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0139360427856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1010141372681</t>
+    <t xml:space="preserve">10.01393699646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1010150909424</t>
   </si>
   <si>
     <t xml:space="preserve">9.92685890197754</t>
@@ -2096,13 +2096,13 @@
     <t xml:space="preserve">9.97039794921875</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70916366577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75270366668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62208843231201</t>
+    <t xml:space="preserve">9.7091646194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75270462036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62208652496338</t>
   </si>
   <si>
     <t xml:space="preserve">9.53500938415527</t>
@@ -2111,25 +2111,25 @@
     <t xml:space="preserve">9.79624271392822</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1880931854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2751693725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5364027023315</t>
+    <t xml:space="preserve">10.1880912780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2751703262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5364036560059</t>
   </si>
   <si>
     <t xml:space="preserve">10.9282522201538</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0153303146362</t>
+    <t xml:space="preserve">11.0153293609619</t>
   </si>
   <si>
     <t xml:space="preserve">10.7540979385376</t>
   </si>
   <si>
-    <t xml:space="preserve">10.492865562439</t>
+    <t xml:space="preserve">10.4928646087646</t>
   </si>
   <si>
     <t xml:space="preserve">10.4057855606079</t>
@@ -2138,16 +2138,16 @@
     <t xml:space="preserve">10.362247467041</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3187093734741</t>
+    <t xml:space="preserve">10.3187084197998</t>
   </si>
   <si>
     <t xml:space="preserve">11.1894865036011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2765626907349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4507179260254</t>
+    <t xml:space="preserve">11.2765636444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4507188796997</t>
   </si>
   <si>
     <t xml:space="preserve">12.0167245864868</t>
@@ -2159,10 +2159,10 @@
     <t xml:space="preserve">12.5011930465698</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0100755691528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8314867019653</t>
+    <t xml:space="preserve">12.0100746154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.831485748291</t>
   </si>
   <si>
     <t xml:space="preserve">11.6975450515747</t>
@@ -2171,19 +2171,19 @@
     <t xml:space="preserve">11.4743099212646</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2064256668091</t>
+    <t xml:space="preserve">11.2064266204834</t>
   </si>
   <si>
     <t xml:space="preserve">11.4296627044678</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6082496643066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2510738372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5813674926758</t>
+    <t xml:space="preserve">11.608250617981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2510747909546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5813665390015</t>
   </si>
   <si>
     <t xml:space="preserve">10.5367202758789</t>
@@ -2192,16 +2192,16 @@
     <t xml:space="preserve">11.0278387069702</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8938970565796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1617784500122</t>
+    <t xml:space="preserve">10.8938961029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1617803573608</t>
   </si>
   <si>
     <t xml:space="preserve">11.0724849700928</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9207801818848</t>
+    <t xml:space="preserve">11.9207811355591</t>
   </si>
   <si>
     <t xml:space="preserve">12.1886625289917</t>
@@ -2216,28 +2216,28 @@
     <t xml:space="preserve">11.8761339187622</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1440162658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7868385314941</t>
+    <t xml:space="preserve">12.1440172195435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7868394851685</t>
   </si>
   <si>
     <t xml:space="preserve">12.0993690490723</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4387826919556</t>
+    <t xml:space="preserve">13.4387817382812</t>
   </si>
   <si>
     <t xml:space="preserve">13.4834308624268</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9299020767212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8406066894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0191946029663</t>
+    <t xml:space="preserve">13.9299011230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8406057357788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0191955566406</t>
   </si>
   <si>
     <t xml:space="preserve">12.9030170440674</t>
@@ -2249,25 +2249,25 @@
     <t xml:space="preserve">13.036958694458</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7513113021851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7959585189819</t>
+    <t xml:space="preserve">13.7513122558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7959594726562</t>
   </si>
   <si>
     <t xml:space="preserve">13.3941354751587</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9745483398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2601938247681</t>
+    <t xml:space="preserve">13.9745473861694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2601947784424</t>
   </si>
   <si>
     <t xml:space="preserve">13.6620178222656</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6173706054688</t>
+    <t xml:space="preserve">13.6173715591431</t>
   </si>
   <si>
     <t xml:space="preserve">13.88525390625</t>
@@ -2276,7 +2276,7 @@
     <t xml:space="preserve">14.6442546844482</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7781953811646</t>
+    <t xml:space="preserve">14.7781944274902</t>
   </si>
   <si>
     <t xml:space="preserve">14.9121379852295</t>
@@ -2285,10 +2285,10 @@
     <t xml:space="preserve">15.0907258987427</t>
   </si>
   <si>
-    <t xml:space="preserve">14.733549118042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4210195541382</t>
+    <t xml:space="preserve">14.7335481643677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4210186004639</t>
   </si>
   <si>
     <t xml:space="preserve">14.5103130340576</t>
@@ -2303,7 +2303,7 @@
     <t xml:space="preserve">15.8050813674927</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0729637145996</t>
+    <t xml:space="preserve">16.072961807251</t>
   </si>
   <si>
     <t xml:space="preserve">16.3854923248291</t>
@@ -2324,13 +2324,13 @@
     <t xml:space="preserve">17.769552230835</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8142032623291</t>
+    <t xml:space="preserve">17.8142013549805</t>
   </si>
   <si>
     <t xml:space="preserve">17.8588466644287</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0374355316162</t>
+    <t xml:space="preserve">18.0374374389648</t>
   </si>
   <si>
     <t xml:space="preserve">18.12672996521</t>
@@ -2342,13 +2342,13 @@
     <t xml:space="preserve">18.5732002258301</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6980247497559</t>
+    <t xml:space="preserve">16.6980228424072</t>
   </si>
   <si>
     <t xml:space="preserve">18.3053188323975</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5909652709961</t>
+    <t xml:space="preserve">17.5909671783447</t>
   </si>
   <si>
     <t xml:space="preserve">18.2160243988037</t>
@@ -2360,19 +2360,19 @@
     <t xml:space="preserve">19.0196723937988</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1804962158203</t>
+    <t xml:space="preserve">20.1804981231689</t>
   </si>
   <si>
     <t xml:space="preserve">20.5376739501953</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6269702911377</t>
+    <t xml:space="preserve">20.6269683837891</t>
   </si>
   <si>
     <t xml:space="preserve">20.9841461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8055553436279</t>
+    <t xml:space="preserve">20.8055572509766</t>
   </si>
   <si>
     <t xml:space="preserve">21.0734405517578</t>
@@ -2381,43 +2381,43 @@
     <t xml:space="preserve">20.0912036895752</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0019092559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8233222961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2697906494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1982612609863</t>
+    <t xml:space="preserve">20.0019111633301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8233203887939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2697925567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1982593536377</t>
   </si>
   <si>
     <t xml:space="preserve">19.9126129150391</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5554370880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6447334289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9303798675537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7162647247314</t>
+    <t xml:space="preserve">19.5554389953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6447315216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9303779602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7162628173828</t>
   </si>
   <si>
     <t xml:space="preserve">20.4483795166016</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4306163787842</t>
+    <t xml:space="preserve">21.4306182861328</t>
   </si>
   <si>
     <t xml:space="preserve">21.3413219451904</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3235569000244</t>
+    <t xml:space="preserve">22.3235607147217</t>
   </si>
   <si>
     <t xml:space="preserve">21.6092052459717</t>
@@ -2426,16 +2426,16 @@
     <t xml:space="preserve">22.0556774139404</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7877941131592</t>
+    <t xml:space="preserve">21.7877922058105</t>
   </si>
   <si>
     <t xml:space="preserve">22.7700309753418</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9147033691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4583892822266</t>
+    <t xml:space="preserve">24.914701461792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4583873748779</t>
   </si>
   <si>
     <t xml:space="preserve">24.0020771026611</t>
@@ -2444,22 +2444,22 @@
     <t xml:space="preserve">23.8195514678955</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5496520996094</t>
+    <t xml:space="preserve">24.549654006958</t>
   </si>
   <si>
     <t xml:space="preserve">25.4622783660889</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8234405517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0933380126953</t>
+    <t xml:space="preserve">24.8234424591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0933399200439</t>
   </si>
   <si>
     <t xml:space="preserve">24.732177734375</t>
   </si>
   <si>
-    <t xml:space="preserve">24.367130279541</t>
+    <t xml:space="preserve">24.3671283721924</t>
   </si>
   <si>
     <t xml:space="preserve">23.9108142852783</t>
@@ -2468,7 +2468,7 @@
     <t xml:space="preserve">23.2719764709473</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6370277404785</t>
+    <t xml:space="preserve">23.6370258331299</t>
   </si>
   <si>
     <t xml:space="preserve">23.5457630157471</t>
@@ -2480,22 +2480,22 @@
     <t xml:space="preserve">23.7282886505127</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1846027374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0059661865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3593482971191</t>
+    <t xml:space="preserve">24.1846008300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0059642791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3593502044678</t>
   </si>
   <si>
     <t xml:space="preserve">22.8156623840332</t>
   </si>
   <si>
-    <t xml:space="preserve">22.268087387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7243995666504</t>
+    <t xml:space="preserve">22.2680854797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7243976593018</t>
   </si>
   <si>
     <t xml:space="preserve">23.4545021057129</t>
@@ -2507,10 +2507,10 @@
     <t xml:space="preserve">23.1807117462158</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9069271087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1768245697021</t>
+    <t xml:space="preserve">22.906925201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1768226623535</t>
   </si>
   <si>
     <t xml:space="preserve">22.5418758392334</t>
@@ -2522,10 +2522,10 @@
     <t xml:space="preserve">22.0855617523193</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5379848480225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7205085754395</t>
+    <t xml:space="preserve">21.5379867553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7205104827881</t>
   </si>
   <si>
     <t xml:space="preserve">21.3554592132568</t>
@@ -2534,10 +2534,10 @@
     <t xml:space="preserve">21.8117733001709</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4467239379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8991470336914</t>
+    <t xml:space="preserve">21.4467220306396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8991451263428</t>
   </si>
   <si>
     <t xml:space="preserve">19.0738945007324</t>
@@ -2546,13 +2546,13 @@
     <t xml:space="preserve">19.8952560424805</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8039970397949</t>
+    <t xml:space="preserve">19.8039951324463</t>
   </si>
   <si>
     <t xml:space="preserve">19.6214694976807</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7127323150635</t>
+    <t xml:space="preserve">19.7127342224121</t>
   </si>
   <si>
     <t xml:space="preserve">21.081672668457</t>
@@ -2561,10 +2561,10 @@
     <t xml:space="preserve">24.6409149169922</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3710155487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.374906539917</t>
+    <t xml:space="preserve">25.3710174560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3749046325684</t>
   </si>
   <si>
     <t xml:space="preserve">25.6448059082031</t>
@@ -2591,22 +2591,22 @@
     <t xml:space="preserve">21.6292476654053</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9904079437256</t>
+    <t xml:space="preserve">20.9904098510742</t>
   </si>
   <si>
     <t xml:space="preserve">21.2641983032227</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1729354858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5340976715088</t>
+    <t xml:space="preserve">21.1729335784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5340957641602</t>
   </si>
   <si>
     <t xml:space="preserve">20.8078842163086</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4428329467773</t>
+    <t xml:space="preserve">20.442834854126</t>
   </si>
   <si>
     <t xml:space="preserve">21.9030361175537</t>
@@ -2621,19 +2621,19 @@
     <t xml:space="preserve">20.1690464019775</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3476810455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1651573181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2525291442871</t>
+    <t xml:space="preserve">19.3476829528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1651554107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2525310516357</t>
   </si>
   <si>
     <t xml:space="preserve">18.6175804138184</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1156349182129</t>
+    <t xml:space="preserve">18.1156368255615</t>
   </si>
   <si>
     <t xml:space="preserve">17.4311676025391</t>
@@ -2654,19 +2654,19 @@
     <t xml:space="preserve">16.7010650634766</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6593227386475</t>
+    <t xml:space="preserve">17.6593246459961</t>
   </si>
   <si>
     <t xml:space="preserve">17.2486400604248</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3437938690186</t>
+    <t xml:space="preserve">18.3437919616699</t>
   </si>
   <si>
     <t xml:space="preserve">18.800106048584</t>
   </si>
   <si>
-    <t xml:space="preserve">19.256420135498</t>
+    <t xml:space="preserve">19.2564182281494</t>
   </si>
   <si>
     <t xml:space="preserve">18.982629776001</t>
@@ -2687,7 +2687,7 @@
     <t xml:space="preserve">21.8574047088623</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3137168884277</t>
+    <t xml:space="preserve">22.3137187957764</t>
   </si>
   <si>
     <t xml:space="preserve">21.9486656188965</t>
@@ -2699,28 +2699,28 @@
     <t xml:space="preserve">21.4923534393311</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4049797058105</t>
+    <t xml:space="preserve">22.4049777984619</t>
   </si>
   <si>
     <t xml:space="preserve">22.678768157959</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5913944244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5001335144043</t>
+    <t xml:space="preserve">23.5913963317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5001316070557</t>
   </si>
   <si>
     <t xml:space="preserve">23.7337303161621</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8271713256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.387809753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2009315490723</t>
+    <t xml:space="preserve">23.827169418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3878116607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2009296417236</t>
   </si>
   <si>
     <t xml:space="preserve">24.6681289672852</t>
@@ -2729,28 +2729,28 @@
     <t xml:space="preserve">24.621410369873</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0607719421387</t>
+    <t xml:space="preserve">24.06077003479</t>
   </si>
   <si>
     <t xml:space="preserve">23.9673309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5001316070557</t>
+    <t xml:space="preserve">23.500129699707</t>
   </si>
   <si>
     <t xml:space="preserve">22.9394912719727</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7058925628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6591739654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5190124511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.425573348999</t>
+    <t xml:space="preserve">22.7058906555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6591720581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5190143585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4255714416504</t>
   </si>
   <si>
     <t xml:space="preserve">23.4534130096436</t>
@@ -2768,7 +2768,7 @@
     <t xml:space="preserve">22.0985317230225</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9116554260254</t>
+    <t xml:space="preserve">21.9116535186768</t>
   </si>
   <si>
     <t xml:space="preserve">21.6780548095703</t>
@@ -2780,7 +2780,7 @@
     <t xml:space="preserve">23.0329303741455</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9862117767334</t>
+    <t xml:space="preserve">22.986213684082</t>
   </si>
   <si>
     <t xml:space="preserve">21.8182144165039</t>
@@ -2789,7 +2789,7 @@
     <t xml:space="preserve">22.1919727325439</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7714939117432</t>
+    <t xml:space="preserve">21.7714920043945</t>
   </si>
   <si>
     <t xml:space="preserve">22.2386913299561</t>
@@ -2801,13 +2801,13 @@
     <t xml:space="preserve">23.31325340271</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7993335723877</t>
+    <t xml:space="preserve">22.7993316650391</t>
   </si>
   <si>
     <t xml:space="preserve">22.3321323394775</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5846138000488</t>
+    <t xml:space="preserve">21.5846157073975</t>
   </si>
   <si>
     <t xml:space="preserve">20.930534362793</t>
@@ -2819,7 +2819,7 @@
     <t xml:space="preserve">20.2764568328857</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9494152069092</t>
+    <t xml:space="preserve">19.9494171142578</t>
   </si>
   <si>
     <t xml:space="preserve">20.4166164398193</t>
@@ -2840,25 +2840,25 @@
     <t xml:space="preserve">19.9026947021484</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8092555999756</t>
+    <t xml:space="preserve">19.8092575073242</t>
   </si>
   <si>
     <t xml:space="preserve">19.5756568908691</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3420562744141</t>
+    <t xml:space="preserve">19.3420581817627</t>
   </si>
   <si>
     <t xml:space="preserve">19.2486171722412</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9215774536133</t>
+    <t xml:space="preserve">18.9215755462646</t>
   </si>
   <si>
     <t xml:space="preserve">18.8281364440918</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5758495330811</t>
+    <t xml:space="preserve">18.5758476257324</t>
   </si>
   <si>
     <t xml:space="preserve">18.5010967254639</t>
@@ -2870,7 +2870,7 @@
     <t xml:space="preserve">19.5289363861084</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5945377349854</t>
+    <t xml:space="preserve">18.5945358276367</t>
   </si>
   <si>
     <t xml:space="preserve">18.3702812194824</t>
@@ -2879,7 +2879,7 @@
     <t xml:space="preserve">18.0525856018066</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9217700958252</t>
+    <t xml:space="preserve">17.9217720031738</t>
   </si>
   <si>
     <t xml:space="preserve">17.7535781860352</t>
@@ -2891,10 +2891,10 @@
     <t xml:space="preserve">17.7348899841309</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4919452667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2303161621094</t>
+    <t xml:space="preserve">17.4919471740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2303142547607</t>
   </si>
   <si>
     <t xml:space="preserve">17.1742496490479</t>
@@ -2909,7 +2909,7 @@
     <t xml:space="preserve">16.4454212188721</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1277236938477</t>
+    <t xml:space="preserve">16.1277256011963</t>
   </si>
   <si>
     <t xml:space="preserve">16.5014839172363</t>
@@ -2921,13 +2921,13 @@
     <t xml:space="preserve">16.0342845916748</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8847808837891</t>
+    <t xml:space="preserve">15.8847818374634</t>
   </si>
   <si>
     <t xml:space="preserve">15.3241405487061</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6044616699219</t>
+    <t xml:space="preserve">15.6044607162476</t>
   </si>
   <si>
     <t xml:space="preserve">15.7352771759033</t>
@@ -2945,7 +2945,7 @@
     <t xml:space="preserve">16.7444267272949</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7257404327393</t>
+    <t xml:space="preserve">16.7257385253906</t>
   </si>
   <si>
     <t xml:space="preserve">16.9313087463379</t>
@@ -2957,7 +2957,7 @@
     <t xml:space="preserve">17.9965229034424</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2581558227539</t>
+    <t xml:space="preserve">18.2581539154053</t>
   </si>
   <si>
     <t xml:space="preserve">17.6601371765137</t>
@@ -2966,10 +2966,10 @@
     <t xml:space="preserve">17.5666980743408</t>
   </si>
   <si>
-    <t xml:space="preserve">17.641450881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3142166137695</t>
+    <t xml:space="preserve">17.6414489746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3142185211182</t>
   </si>
   <si>
     <t xml:space="preserve">18.0712738037109</t>
@@ -3008,7 +3008,7 @@
     <t xml:space="preserve">17.7162017822266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5293216705322</t>
+    <t xml:space="preserve">17.5293235778809</t>
   </si>
   <si>
     <t xml:space="preserve">16.9873714447021</t>
@@ -3020,10 +3020,10 @@
     <t xml:space="preserve">17.5480117797852</t>
   </si>
   <si>
-    <t xml:space="preserve">16.277229309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9221572875977</t>
+    <t xml:space="preserve">16.2772274017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.922158241272</t>
   </si>
   <si>
     <t xml:space="preserve">16.0155963897705</t>
@@ -3032,19 +3032,19 @@
     <t xml:space="preserve">15.9595327377319</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9782218933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0903472900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8287172317505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6231489181519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5857744216919</t>
+    <t xml:space="preserve">15.9782209396362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0903491973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8287162780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6231479644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5857725143433</t>
   </si>
   <si>
     <t xml:space="preserve">16.0716609954834</t>
@@ -3065,10 +3065,10 @@
     <t xml:space="preserve">16.6322994232178</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6136112213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5762348175049</t>
+    <t xml:space="preserve">16.6136131286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5762367248535</t>
   </si>
   <si>
     <t xml:space="preserve">16.3519802093506</t>
@@ -3077,13 +3077,13 @@
     <t xml:space="preserve">16.2024765014648</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7913408279419</t>
+    <t xml:space="preserve">15.7913398742676</t>
   </si>
   <si>
     <t xml:space="preserve">15.7726516723633</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6978998184204</t>
+    <t xml:space="preserve">15.6979007720947</t>
   </si>
   <si>
     <t xml:space="preserve">16.5201721191406</t>
@@ -3092,34 +3092,34 @@
     <t xml:space="preserve">16.1464138031006</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1650981903076</t>
+    <t xml:space="preserve">16.1651000976562</t>
   </si>
   <si>
     <t xml:space="preserve">16.109037399292</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8474044799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7539663314819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8660917282104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6792125701904</t>
+    <t xml:space="preserve">15.8474025726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7539653778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8660936355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6792144775391</t>
   </si>
   <si>
     <t xml:space="preserve">15.8100280761719</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5110206604004</t>
+    <t xml:space="preserve">15.5110216140747</t>
   </si>
   <si>
     <t xml:space="preserve">15.3802042007446</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0064449310303</t>
+    <t xml:space="preserve">15.0064458847046</t>
   </si>
   <si>
     <t xml:space="preserve">14.8008785247803</t>
@@ -3128,7 +3128,7 @@
     <t xml:space="preserve">14.6700620651245</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4271183013916</t>
+    <t xml:space="preserve">14.4271173477173</t>
   </si>
   <si>
     <t xml:space="preserve">14.5766229629517</t>
@@ -3158,13 +3158,13 @@
     <t xml:space="preserve">15.0811967849731</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5670852661133</t>
+    <t xml:space="preserve">15.567084312439</t>
   </si>
   <si>
     <t xml:space="preserve">15.716588973999</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6605253219604</t>
+    <t xml:space="preserve">15.6605262756348</t>
   </si>
   <si>
     <t xml:space="preserve">15.1933259963989</t>
@@ -3173,13 +3173,13 @@
     <t xml:space="preserve">15.3988933563232</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4175806045532</t>
+    <t xml:space="preserve">15.4175815582275</t>
   </si>
   <si>
     <t xml:space="preserve">15.4362697601318</t>
   </si>
   <si>
-    <t xml:space="preserve">15.137261390686</t>
+    <t xml:space="preserve">15.1372623443604</t>
   </si>
   <si>
     <t xml:space="preserve">15.0438222885132</t>
@@ -3191,7 +3191,7 @@
     <t xml:space="preserve">14.9877586364746</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7261257171631</t>
+    <t xml:space="preserve">14.7261266708374</t>
   </si>
   <si>
     <t xml:space="preserve">14.950382232666</t>
@@ -3206,22 +3206,22 @@
     <t xml:space="preserve">14.3149900436401</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5018701553345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4084310531616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1654872894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.202862739563</t>
+    <t xml:space="preserve">14.5018711090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4084300994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1654863357544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2028617858887</t>
   </si>
   <si>
     <t xml:space="preserve">14.2963027954102</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1281099319458</t>
+    <t xml:space="preserve">14.1281108856201</t>
   </si>
   <si>
     <t xml:space="preserve">13.8291034698486</t>
@@ -3236,19 +3236,19 @@
     <t xml:space="preserve">13.4179677963257</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5487833023071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6422233581543</t>
+    <t xml:space="preserve">13.5487842559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6422243118286</t>
   </si>
   <si>
     <t xml:space="preserve">13.45534324646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3992805480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3245277404785</t>
+    <t xml:space="preserve">13.3992795944214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3245286941528</t>
   </si>
   <si>
     <t xml:space="preserve">13.2497758865356</t>
@@ -3257,7 +3257,7 @@
     <t xml:space="preserve">13.0815839767456</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3432149887085</t>
+    <t xml:space="preserve">13.3432159423828</t>
   </si>
   <si>
     <t xml:space="preserve">13.1937122344971</t>
@@ -3266,7 +3266,7 @@
     <t xml:space="preserve">13.3058395385742</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2589263916016</t>
+    <t xml:space="preserve">14.2589273452759</t>
   </si>
   <si>
     <t xml:space="preserve">14.2776145935059</t>
@@ -3275,7 +3275,7 @@
     <t xml:space="preserve">14.7448139190674</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5575466156006</t>
+    <t xml:space="preserve">16.5575485229492</t>
   </si>
   <si>
     <t xml:space="preserve">16.4641094207764</t>
@@ -3284,13 +3284,13 @@
     <t xml:space="preserve">16.4267311096191</t>
   </si>
   <si>
-    <t xml:space="preserve">16.314603805542</t>
+    <t xml:space="preserve">16.3146018981934</t>
   </si>
   <si>
     <t xml:space="preserve">16.2585391998291</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2398529052734</t>
+    <t xml:space="preserve">16.2398509979248</t>
   </si>
   <si>
     <t xml:space="preserve">16.1837882995605</t>
@@ -3299,13 +3299,13 @@
     <t xml:space="preserve">14.8569412231445</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7074375152588</t>
+    <t xml:space="preserve">14.7074384689331</t>
   </si>
   <si>
     <t xml:space="preserve">14.6887502670288</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3897428512573</t>
+    <t xml:space="preserve">14.389741897583</t>
   </si>
   <si>
     <t xml:space="preserve">14.782190322876</t>
@@ -3326,19 +3326,19 @@
     <t xml:space="preserve">12.9881439208984</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5956964492798</t>
+    <t xml:space="preserve">12.5956954956055</t>
   </si>
   <si>
     <t xml:space="preserve">12.7078247070312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7452001571655</t>
+    <t xml:space="preserve">12.7452011108398</t>
   </si>
   <si>
     <t xml:space="preserve">12.4275054931641</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0442085266113</t>
+    <t xml:space="preserve">13.044207572937</t>
   </si>
   <si>
     <t xml:space="preserve">13.3805913925171</t>
@@ -3365,28 +3365,28 @@
     <t xml:space="preserve">13.9972944259644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0159826278687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6513748168945</t>
+    <t xml:space="preserve">14.015983581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6513738632202</t>
   </si>
   <si>
     <t xml:space="preserve">15.0251340866089</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4736442565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.903468132019</t>
+    <t xml:space="preserve">15.4736452102661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9034700393677</t>
   </si>
   <si>
     <t xml:space="preserve">16.482795715332</t>
   </si>
   <si>
-    <t xml:space="preserve">16.912618637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8565578460693</t>
+    <t xml:space="preserve">16.9126205444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8565559387207</t>
   </si>
   <si>
     <t xml:space="preserve">16.9499950408936</t>
@@ -3395,7 +3395,7 @@
     <t xml:space="preserve">16.8752422332764</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0434341430664</t>
+    <t xml:space="preserve">17.043436050415</t>
   </si>
   <si>
     <t xml:space="preserve">15.9969091415405</t>
@@ -3407,7 +3407,7 @@
     <t xml:space="preserve">15.5483961105347</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6418361663818</t>
+    <t xml:space="preserve">15.6418380737305</t>
   </si>
   <si>
     <t xml:space="preserve">16.4080429077148</t>
@@ -3419,13 +3419,13 @@
     <t xml:space="preserve">16.6790199279785</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5855808258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8002967834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7068576812744</t>
+    <t xml:space="preserve">16.585578918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8002986907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.706859588623</t>
   </si>
   <si>
     <t xml:space="preserve">16.211820602417</t>
@@ -3434,19 +3434,19 @@
     <t xml:space="preserve">15.3708620071411</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3052597045898</t>
+    <t xml:space="preserve">16.3052616119385</t>
   </si>
   <si>
     <t xml:space="preserve">16.0249404907227</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1273384094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9404582977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6134185791016</t>
+    <t xml:space="preserve">18.1273365020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9404602050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6134204864502</t>
   </si>
   <si>
     <t xml:space="preserve">17.7070121765137</t>
@@ -3843,9 +3843,6 @@
   </si>
   <si>
     <t xml:space="preserve">13</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
   </si>
   <si>
     <t xml:space="preserve">13.3500003814697</t>
@@ -71796,12 +71793,14 @@
         <v>13.6499996185303</v>
       </c>
       <c r="D2601" t="n">
-        <v>13.3999996185303</v>
+        <v>13.3500003814697</v>
       </c>
       <c r="E2601" t="n">
         <v>13.5500001907349</v>
       </c>
-      <c r="F2601"/>
+      <c r="F2601" t="n">
+        <v>13.3500003814697</v>
+      </c>
       <c r="G2601" t="s">
         <v>1277</v>
       </c>
@@ -71811,25 +71810,25 @@
     </row>
     <row r="2602">
       <c r="A2602" s="1" t="n">
-        <v>46107.6912384259</v>
+        <v>46108.3333333333</v>
       </c>
       <c r="B2602" t="n">
-        <v>6538</v>
+        <v>18408</v>
       </c>
       <c r="C2602" t="n">
-        <v>13.6499996185303</v>
+        <v>13.5500001907349</v>
       </c>
       <c r="D2602" t="n">
-        <v>13.3999996185303</v>
+        <v>13.1000003814697</v>
       </c>
       <c r="E2602" t="n">
-        <v>13.5500001907349</v>
+        <v>13.4499998092651</v>
       </c>
       <c r="F2602" t="n">
         <v>13.3500003814697</v>
       </c>
       <c r="G2602" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="H2602" t="s">
         <v>9</v>

--- a/data/SAB.MI.xlsx
+++ b/data/SAB.MI.xlsx
@@ -44,13 +44,13 @@
     <t xml:space="preserve">SAB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61823177337646</t>
+    <t xml:space="preserve">8.61823081970215</t>
   </si>
   <si>
     <t xml:space="preserve">8.48310089111328</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33295631408691</t>
+    <t xml:space="preserve">8.33295822143555</t>
   </si>
   <si>
     <t xml:space="preserve">8.37049388885498</t>
@@ -62,118 +62,118 @@
     <t xml:space="preserve">8.25788593292236</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16029357910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88252830505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52969264984131</t>
+    <t xml:space="preserve">8.16029453277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88252735137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52969169616699</t>
   </si>
   <si>
     <t xml:space="preserve">7.66482019424438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62728452682495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61227083206177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73989343643188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75490665435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76992082595825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89754199981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61977624893188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79994964599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72487783432007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65731287002563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50716972351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34201049804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54470586776733</t>
+    <t xml:space="preserve">7.62728404998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61226987838745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73989248275757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75490760803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76992130279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89754247665405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61977672576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79995012283325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72487878799438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65731191635132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5071702003479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34201240539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54470539093018</t>
   </si>
   <si>
     <t xml:space="preserve">7.39080953598022</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58224201202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82247066497803</t>
+    <t xml:space="preserve">7.58224153518677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82247114181519</t>
   </si>
   <si>
     <t xml:space="preserve">8.0852222442627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11525058746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95760107040405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06270027160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03267097473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92006492614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77742767333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86751317977905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80745649337769</t>
+    <t xml:space="preserve">8.1152515411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95759963989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06269931793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03267192840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92006397247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77742671966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86751413345337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80745553970337</t>
   </si>
   <si>
     <t xml:space="preserve">7.98762893676758</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0401782989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9951376914978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9651050567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90505027770996</t>
+    <t xml:space="preserve">8.04017925262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99513530731201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96510744094849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9050498008728</t>
   </si>
   <si>
     <t xml:space="preserve">7.9350790977478</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89003610610962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94258499145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82997941970825</t>
+    <t xml:space="preserve">7.89003658294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94258546829224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82997846603394</t>
   </si>
   <si>
     <t xml:space="preserve">7.81496334075928</t>
@@ -182,52 +182,52 @@
     <t xml:space="preserve">7.73238468170166</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64980554580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71737003326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6723256111145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63479232788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51467657089233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64229822158813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56722593307495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70235776901245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.747398853302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46963310241699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69484949111938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49215364456177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47338724136353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43585205078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50341606140137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48089599609375</t>
+    <t xml:space="preserve">7.64980506896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71737051010132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67232847213745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6347918510437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51467704772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64229869842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56722736358643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70235681533813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74739837646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46963453292847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69484853744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49215602874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47338771820068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43585109710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50341653823853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48089456558228</t>
   </si>
   <si>
     <t xml:space="preserve">7.59725522994995</t>
@@ -242,22 +242,22 @@
     <t xml:space="preserve">7.37204027175903</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31949090957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28195381164551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52122116088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80533885955811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75009441375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75798559188843</t>
+    <t xml:space="preserve">7.31949043273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28195285797119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52122163772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80534076690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75009346008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75798606872559</t>
   </si>
   <si>
     <t xml:space="preserve">7.81323146820068</t>
@@ -266,7 +266,7 @@
     <t xml:space="preserve">7.86058521270752</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69879579544067</t>
+    <t xml:space="preserve">7.69879531860352</t>
   </si>
   <si>
     <t xml:space="preserve">7.58435916900635</t>
@@ -275,67 +275,67 @@
     <t xml:space="preserve">7.68695640563965</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57646703720093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53700637817383</t>
+    <t xml:space="preserve">7.57646751403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53700542449951</t>
   </si>
   <si>
     <t xml:space="preserve">7.49754571914673</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28445672988892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92536354064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07926225662231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22921133041382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45808362960815</t>
+    <t xml:space="preserve">7.2844557762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92536401748657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.079261302948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22921228408813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45808458328247</t>
   </si>
   <si>
     <t xml:space="preserve">7.26078033447266</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37127065658569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26472663879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34759521484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46992206573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36732578277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37916278839111</t>
+    <t xml:space="preserve">7.37127113342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2647271156311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34759473800659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46992254257202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36732387542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37916421890259</t>
   </si>
   <si>
     <t xml:space="preserve">7.13450622558594</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18975162506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10293817520142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15029096603394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10688495635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20553493499756</t>
+    <t xml:space="preserve">7.18975067138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10293769836426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15029048919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10688304901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2055344581604</t>
   </si>
   <si>
     <t xml:space="preserve">7.18185901641846</t>
@@ -347,22 +347,22 @@
     <t xml:space="preserve">7.19369697570801</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24894380569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19764375686646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18580436706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22526597976685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20948219299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31602573394775</t>
+    <t xml:space="preserve">7.24894285202026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19764280319214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18580532073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22526693344116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20948171615601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31602668762207</t>
   </si>
   <si>
     <t xml:space="preserve">7.21342802047729</t>
@@ -371,88 +371,88 @@
     <t xml:space="preserve">7.16607475280762</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24499702453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13055992126465</t>
+    <t xml:space="preserve">7.24499654769897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13056135177612</t>
   </si>
   <si>
     <t xml:space="preserve">7.11082983016968</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17791366577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23315715789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27656507492065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30024242401123</t>
+    <t xml:space="preserve">7.17791318893433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23315811157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27656412124634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30024194717407</t>
   </si>
   <si>
     <t xml:space="preserve">7.29234933853149</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24105024337769</t>
+    <t xml:space="preserve">7.24105072021484</t>
   </si>
   <si>
     <t xml:space="preserve">7.11872243881226</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09504461288452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00428581237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94509410858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93325614929199</t>
+    <t xml:space="preserve">7.09504508972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00428533554077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94509506225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93325662612915</t>
   </si>
   <si>
     <t xml:space="preserve">7.09899139404297</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15423631668091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13845300674438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15818119049072</t>
+    <t xml:space="preserve">7.15423679351807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13845252990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15818309783936</t>
   </si>
   <si>
     <t xml:space="preserve">7.05558443069458</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07136821746826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06742286682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02401638031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04769277572632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06347703933716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08320665359497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05164003372192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04374647140503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03190851211548</t>
+    <t xml:space="preserve">7.07136869430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06742334365845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0240159034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04769325256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0634765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08320713043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05163908004761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04374742507935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03190946578979</t>
   </si>
   <si>
     <t xml:space="preserve">7.05953073501587</t>
@@ -461,100 +461,100 @@
     <t xml:space="preserve">7.03585433959961</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17396783828735</t>
+    <t xml:space="preserve">7.17396688461304</t>
   </si>
   <si>
     <t xml:space="preserve">6.90563297271729</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91352701187134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93720245361328</t>
+    <t xml:space="preserve">6.91352558135986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9372034072876</t>
   </si>
   <si>
     <t xml:space="preserve">6.9214186668396</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94114875793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96877098083496</t>
+    <t xml:space="preserve">6.94114828109741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9687705039978</t>
   </si>
   <si>
     <t xml:space="preserve">7.14239883422852</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45019197463989</t>
+    <t xml:space="preserve">7.45019245147705</t>
   </si>
   <si>
     <t xml:space="preserve">7.79350137710571</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92372226715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0499963760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.207839012146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16837787628174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08945751190186</t>
+    <t xml:space="preserve">7.9237208366394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04999542236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20783996582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16837882995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08945655822754</t>
   </si>
   <si>
     <t xml:space="preserve">8.19994735717773</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06578063964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1289176940918</t>
+    <t xml:space="preserve">8.06578159332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12891674041748</t>
   </si>
   <si>
     <t xml:space="preserve">8.17627048492432</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32622241973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55509376525879</t>
+    <t xml:space="preserve">8.32622146606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55509471893311</t>
   </si>
   <si>
     <t xml:space="preserve">8.56298732757568</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42881870269775</t>
+    <t xml:space="preserve">8.42882061004639</t>
   </si>
   <si>
     <t xml:space="preserve">8.35779094696045</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39725112915039</t>
+    <t xml:space="preserve">8.39725208282471</t>
   </si>
   <si>
     <t xml:space="preserve">8.42092800140381</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44460391998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40514278411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26308345794678</t>
+    <t xml:space="preserve">8.44460296630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40514183044434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26308441162109</t>
   </si>
   <si>
     <t xml:space="preserve">8.18416213989258</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30254650115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22362232208252</t>
+    <t xml:space="preserve">8.30254554748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22362327575684</t>
   </si>
   <si>
     <t xml:space="preserve">8.2867603302002</t>
@@ -563,7 +563,7 @@
     <t xml:space="preserve">8.25519275665283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34989833831787</t>
+    <t xml:space="preserve">8.34989738464355</t>
   </si>
   <si>
     <t xml:space="preserve">8.3104362487793</t>
@@ -572,28 +572,28 @@
     <t xml:space="preserve">8.36568260192871</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33411407470703</t>
+    <t xml:space="preserve">8.3341121673584</t>
   </si>
   <si>
     <t xml:space="preserve">8.34200477600098</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46038818359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62612247467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74450397491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88656520843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00494575500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23381805419922</t>
+    <t xml:space="preserve">8.46038722991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62612342834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74450588226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88656425476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00494766235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23381900787354</t>
   </si>
   <si>
     <t xml:space="preserve">9.30484867095947</t>
@@ -602,52 +602,52 @@
     <t xml:space="preserve">9.2653865814209</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16279029846191</t>
+    <t xml:space="preserve">9.16278839111328</t>
   </si>
   <si>
     <t xml:space="preserve">9.19435787200928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24960517883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29695510864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36798667907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54950428009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7468090057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2203388214111</t>
+    <t xml:space="preserve">9.24960327148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29695606231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36798477172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54950523376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67577934265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74680995941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2203378677368</t>
   </si>
   <si>
     <t xml:space="preserve">10.4807786941528</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4571027755737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2913675308228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2597980499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1493082046509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0861730575562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0151424407959</t>
+    <t xml:space="preserve">10.4571018218994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2913665771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2597990036011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1493091583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0861701965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0151414871216</t>
   </si>
   <si>
     <t xml:space="preserve">10.1019563674927</t>
@@ -656,31 +656,31 @@
     <t xml:space="preserve">10.165093421936</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0546035766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1808767318726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1177387237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1887683868408</t>
+    <t xml:space="preserve">10.0546026229858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1808776855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1177396774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1887702941895</t>
   </si>
   <si>
     <t xml:space="preserve">10.0703859329224</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1098480224609</t>
+    <t xml:space="preserve">10.1098489761353</t>
   </si>
   <si>
     <t xml:space="preserve">10.0230340957642</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4965629577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4176425933838</t>
+    <t xml:space="preserve">10.496563911438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4176406860352</t>
   </si>
   <si>
     <t xml:space="preserve">10.3150434494019</t>
@@ -689,31 +689,31 @@
     <t xml:space="preserve">10.7333278656006</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4492111206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.559700012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6386222839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.591269493103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0095529556274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8832788467407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3410234451294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0592098236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9171524047852</t>
+    <t xml:space="preserve">10.4492092132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5597019195557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6386203765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5912704467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0095520019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.883279800415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3410243988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0592088699341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9171514511108</t>
   </si>
   <si>
     <t xml:space="preserve">12.0513181686401</t>
@@ -722,28 +722,28 @@
     <t xml:space="preserve">11.6882791519165</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6803865432739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2644062042236</t>
+    <t xml:space="preserve">11.6803874969482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2644052505493</t>
   </si>
   <si>
     <t xml:space="preserve">12.6274452209473</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5406322479248</t>
+    <t xml:space="preserve">12.5406312942505</t>
   </si>
   <si>
     <t xml:space="preserve">12.6747980117798</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7379341125488</t>
+    <t xml:space="preserve">12.7379350662231</t>
   </si>
   <si>
     <t xml:space="preserve">12.4728555679321</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6518526077271</t>
+    <t xml:space="preserve">12.6518535614014</t>
   </si>
   <si>
     <t xml:space="preserve">12.8471221923828</t>
@@ -752,7 +752,7 @@
     <t xml:space="preserve">12.8145780563354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9203491210938</t>
+    <t xml:space="preserve">12.9203481674194</t>
   </si>
   <si>
     <t xml:space="preserve">12.8715305328369</t>
@@ -761,10 +761,10 @@
     <t xml:space="preserve">12.9366207122803</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8064422607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6437168121338</t>
+    <t xml:space="preserve">12.8064413070679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6437177658081</t>
   </si>
   <si>
     <t xml:space="preserve">12.822714805603</t>
@@ -773,37 +773,37 @@
     <t xml:space="preserve">11.5209150314331</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8463640213013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7812757492065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9114561080933</t>
+    <t xml:space="preserve">11.8463668823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7812747955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9114551544189</t>
   </si>
   <si>
     <t xml:space="preserve">11.9277276992798</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9602718353271</t>
+    <t xml:space="preserve">11.9602727890015</t>
   </si>
   <si>
     <t xml:space="preserve">11.8056840896606</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1311330795288</t>
+    <t xml:space="preserve">12.1311340332031</t>
   </si>
   <si>
     <t xml:space="preserve">12.0009536743164</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9846820831299</t>
+    <t xml:space="preserve">11.9846811294556</t>
   </si>
   <si>
     <t xml:space="preserve">12.0416355133057</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0823173522949</t>
+    <t xml:space="preserve">12.0823154449463</t>
   </si>
   <si>
     <t xml:space="preserve">11.9765453338623</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">11.8789100646973</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7161865234375</t>
+    <t xml:space="preserve">11.7161846160889</t>
   </si>
   <si>
     <t xml:space="preserve">11.4720983505249</t>
@@ -824,10 +824,10 @@
     <t xml:space="preserve">11.5860061645508</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7975473403931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8951826095581</t>
+    <t xml:space="preserve">11.7975482940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8951835632324</t>
   </si>
   <si>
     <t xml:space="preserve">12.0904521942139</t>
@@ -836,7 +836,7 @@
     <t xml:space="preserve">12.1636781692505</t>
   </si>
   <si>
-    <t xml:space="preserve">12.074179649353</t>
+    <t xml:space="preserve">12.0741806030273</t>
   </si>
   <si>
     <t xml:space="preserve">12.2287683486938</t>
@@ -845,10 +845,10 @@
     <t xml:space="preserve">12.1392707824707</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2043609619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1880855560303</t>
+    <t xml:space="preserve">12.2043600082397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1880865097046</t>
   </si>
   <si>
     <t xml:space="preserve">12.147406578064</t>
@@ -857,22 +857,22 @@
     <t xml:space="preserve">12.2531776428223</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3670845031738</t>
+    <t xml:space="preserve">12.3670854568481</t>
   </si>
   <si>
     <t xml:space="preserve">12.4077663421631</t>
   </si>
   <si>
-    <t xml:space="preserve">12.448447227478</t>
+    <t xml:space="preserve">12.4484462738037</t>
   </si>
   <si>
     <t xml:space="preserve">12.9447584152222</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7820329666138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8959407806396</t>
+    <t xml:space="preserve">12.7820320129395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8959398269653</t>
   </si>
   <si>
     <t xml:space="preserve">13.0098476409912</t>
@@ -884,31 +884,31 @@
     <t xml:space="preserve">12.8552598953247</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7332143783569</t>
+    <t xml:space="preserve">12.7332153320312</t>
   </si>
   <si>
     <t xml:space="preserve">12.7738962173462</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9854383468628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2620706558228</t>
+    <t xml:space="preserve">12.9854393005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2620716094971</t>
   </si>
   <si>
     <t xml:space="preserve">13.685154914856</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9292421340942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9943342208862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7502460479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8153343200684</t>
+    <t xml:space="preserve">13.9292430877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9943332672119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7502450942993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8153352737427</t>
   </si>
   <si>
     <t xml:space="preserve">13.8316087722778</t>
@@ -920,40 +920,40 @@
     <t xml:space="preserve">14.0268774032593</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1814651489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.157057762146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2302837371826</t>
+    <t xml:space="preserve">14.1814680099487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1570568084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2302827835083</t>
   </si>
   <si>
     <t xml:space="preserve">14.7754106521606</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3205394744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2961311340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4588575363159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.824987411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7924404144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5076723098755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8493928909302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8656673431396</t>
+    <t xml:space="preserve">15.3205404281616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2961301803589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4588556289673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8249864578247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.792441368103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5076713562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8493938446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.865668296814</t>
   </si>
   <si>
     <t xml:space="preserve">15.5158100128174</t>
@@ -965,52 +965,52 @@
     <t xml:space="preserve">16.2643451690674</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7769298553467</t>
+    <t xml:space="preserve">16.776927947998</t>
   </si>
   <si>
     <t xml:space="preserve">16.955924987793</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4115524291992</t>
+    <t xml:space="preserve">17.4115543365479</t>
   </si>
   <si>
     <t xml:space="preserve">17.0454216003418</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0787220001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6475048065186</t>
+    <t xml:space="preserve">18.0787258148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6475067138672</t>
   </si>
   <si>
     <t xml:space="preserve">18.0217723846436</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0543174743652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1275405883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2984027862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4123115539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1682243347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1600894927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9160003662109</t>
+    <t xml:space="preserve">18.0543193817139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1275424957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2983989715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4123096466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1682262420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1600856781006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9159984588623</t>
   </si>
   <si>
     <t xml:space="preserve">17.265100479126</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0861053466797</t>
+    <t xml:space="preserve">17.0861015319824</t>
   </si>
   <si>
     <t xml:space="preserve">17.2976474761963</t>
@@ -1031,10 +1031,10 @@
     <t xml:space="preserve">16.8664245605469</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7850646972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.988468170166</t>
+    <t xml:space="preserve">16.785062789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9884662628174</t>
   </si>
   <si>
     <t xml:space="preserve">16.5979309082031</t>
@@ -1043,7 +1043,7 @@
     <t xml:space="preserve">16.9152450561523</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8338813781738</t>
+    <t xml:space="preserve">16.8338794708252</t>
   </si>
   <si>
     <t xml:space="preserve">16.9640598297119</t>
@@ -1052,22 +1052,22 @@
     <t xml:space="preserve">16.882698059082</t>
   </si>
   <si>
-    <t xml:space="preserve">16.923376083374</t>
+    <t xml:space="preserve">16.9233798980713</t>
   </si>
   <si>
     <t xml:space="preserve">17.1349220275879</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0698318481445</t>
+    <t xml:space="preserve">17.0698299407959</t>
   </si>
   <si>
     <t xml:space="preserve">17.1674671173096</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6637763977051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2251796722412</t>
+    <t xml:space="preserve">17.6637744903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2251777648926</t>
   </si>
   <si>
     <t xml:space="preserve">18.8598041534424</t>
@@ -1076,22 +1076,22 @@
     <t xml:space="preserve">19.0632095336914</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7052135467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6319885253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7377624511719</t>
+    <t xml:space="preserve">18.7052154541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6319904327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7377605438232</t>
   </si>
   <si>
     <t xml:space="preserve">18.7133522033691</t>
   </si>
   <si>
-    <t xml:space="preserve">18.59130859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3065395355225</t>
+    <t xml:space="preserve">18.5913066864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3065376281738</t>
   </si>
   <si>
     <t xml:space="preserve">18.6157169342041</t>
@@ -1100,7 +1100,7 @@
     <t xml:space="preserve">18.217041015625</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2089042663574</t>
+    <t xml:space="preserve">18.2089023590088</t>
   </si>
   <si>
     <t xml:space="preserve">18.4611282348633</t>
@@ -1109,13 +1109,13 @@
     <t xml:space="preserve">17.5417327880859</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9071083068848</t>
+    <t xml:space="preserve">16.9071063995361</t>
   </si>
   <si>
     <t xml:space="preserve">16.4758853912354</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3945236206055</t>
+    <t xml:space="preserve">16.3945255279541</t>
   </si>
   <si>
     <t xml:space="preserve">16.1097545623779</t>
@@ -1124,43 +1124,43 @@
     <t xml:space="preserve">16.3619785308838</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2806167602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3782520294189</t>
+    <t xml:space="preserve">16.2806148529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3782501220703</t>
   </si>
   <si>
     <t xml:space="preserve">16.1992530822754</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2236633300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2724800109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.679292678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3131618499756</t>
+    <t xml:space="preserve">16.2236614227295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2724781036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6792907714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.313159942627</t>
   </si>
   <si>
     <t xml:space="preserve">16.0934829711914</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9470281600952</t>
+    <t xml:space="preserve">15.9470310211182</t>
   </si>
   <si>
     <t xml:space="preserve">16.1911163330078</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3538417816162</t>
+    <t xml:space="preserve">16.3538436889648</t>
   </si>
   <si>
     <t xml:space="preserve">16.0283946990967</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9144840240479</t>
+    <t xml:space="preserve">15.9144859313965</t>
   </si>
   <si>
     <t xml:space="preserve">15.1822233200073</t>
@@ -1169,52 +1169,52 @@
     <t xml:space="preserve">14.9706811904907</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1008615493774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.873046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2221460342407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8478803634644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8893175125122</t>
+    <t xml:space="preserve">15.1008605957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8730459213257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.222146987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8478813171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8893194198608</t>
   </si>
   <si>
     <t xml:space="preserve">15.1984958648682</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3937644958496</t>
+    <t xml:space="preserve">15.3937683105469</t>
   </si>
   <si>
     <t xml:space="preserve">15.5402193069458</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9381380081177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5964164733887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4011468887329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2058753967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1082401275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.059422492981</t>
+    <t xml:space="preserve">14.9381370544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5964136123657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4011459350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2058734893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1082410812378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0594234466553</t>
   </si>
   <si>
     <t xml:space="preserve">13.9129705429077</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0106039047241</t>
+    <t xml:space="preserve">14.0106048583984</t>
   </si>
   <si>
     <t xml:space="preserve">14.3197822570801</t>
@@ -1226,61 +1226,61 @@
     <t xml:space="preserve">14.7428674697876</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7265949249268</t>
+    <t xml:space="preserve">14.7265939712524</t>
   </si>
   <si>
     <t xml:space="preserve">15.2147693634033</t>
   </si>
   <si>
-    <t xml:space="preserve">14.807954788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8567724227905</t>
+    <t xml:space="preserve">14.8079586029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8567733764648</t>
   </si>
   <si>
     <t xml:space="preserve">14.9544067382812</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7916870117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2709646224976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0032262802124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4825077056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9218635559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9055919647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0194978713989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0520458221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2562046051025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7354869842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8168516159058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6215791702271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9307584762573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6866722106934</t>
+    <t xml:space="preserve">14.7916841506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2709665298462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.003228187561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4825086593628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9218645095825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.905590057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0194988250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0520448684692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2562084197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7354888916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8168487548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6215810775757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9307565689087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6866731643677</t>
   </si>
   <si>
     <t xml:space="preserve">15.7192144393921</t>
@@ -1289,124 +1289,124 @@
     <t xml:space="preserve">15.7029418945312</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6703996658325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6053066253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5653495788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9956827163696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0291957855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0627002716064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2470054626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2302532196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5318403244019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7161445617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8669414520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.582106590271</t>
+    <t xml:space="preserve">15.6703968048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6053113937378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5653505325317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9956817626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0291929244995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0627031326294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2470092773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2302522659302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5318422317505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7161464691162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8669404983521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5821056365967</t>
   </si>
   <si>
     <t xml:space="preserve">15.4983320236206</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4815740585327</t>
+    <t xml:space="preserve">15.481575012207</t>
   </si>
   <si>
     <t xml:space="preserve">15.4145565032959</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1799879074097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0794582366943</t>
+    <t xml:space="preserve">15.179988861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.07945728302</t>
   </si>
   <si>
     <t xml:space="preserve">15.1129674911499</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3589944839478</t>
+    <t xml:space="preserve">14.3589963912964</t>
   </si>
   <si>
     <t xml:space="preserve">14.2919750213623</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2584657669067</t>
+    <t xml:space="preserve">14.2584648132324</t>
   </si>
   <si>
     <t xml:space="preserve">14.4595241546631</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4092607498169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5600538253784</t>
+    <t xml:space="preserve">14.4092597961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5600547790527</t>
   </si>
   <si>
     <t xml:space="preserve">13.4039621353149</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4877376556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2364120483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5380029678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4374723434448</t>
+    <t xml:space="preserve">13.487738609314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2364130020142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5380010604858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4374713897705</t>
   </si>
   <si>
     <t xml:space="preserve">14.1914463043213</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5882663726807</t>
+    <t xml:space="preserve">13.5882654190063</t>
   </si>
   <si>
     <t xml:space="preserve">13.6887969970703</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4207181930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5212469100952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.57151222229</t>
+    <t xml:space="preserve">13.4207172393799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5212478637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5715112686157</t>
   </si>
   <si>
     <t xml:space="preserve">13.3201866149902</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1526384353638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1861476898193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2196569442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3034334182739</t>
+    <t xml:space="preserve">13.1526374816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.186146736145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2196578979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3034324645996</t>
   </si>
   <si>
     <t xml:space="preserve">12.8510494232178</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">12.5662145614624</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9013137817383</t>
+    <t xml:space="preserve">12.901312828064</t>
   </si>
   <si>
     <t xml:space="preserve">12.8342943191528</t>
@@ -1427,46 +1427,46 @@
     <t xml:space="preserve">12.4824390411377</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1473407745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0803213119507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0635671615601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.979790687561</t>
+    <t xml:space="preserve">12.1473417282104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0803194046021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0635643005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9797916412354</t>
   </si>
   <si>
     <t xml:space="preserve">11.5609178543091</t>
   </si>
   <si>
-    <t xml:space="preserve">11.192307472229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2258176803589</t>
+    <t xml:space="preserve">11.1923084259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2258167266846</t>
   </si>
   <si>
     <t xml:space="preserve">12.4321746826172</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1191272735596</t>
+    <t xml:space="preserve">13.1191282272339</t>
   </si>
   <si>
     <t xml:space="preserve">13.2531671524048</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2866773605347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7672739028931</t>
+    <t xml:space="preserve">13.286675453186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7672729492188</t>
   </si>
   <si>
     <t xml:space="preserve">13.3536968231201</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9850873947144</t>
+    <t xml:space="preserve">12.985089302063</t>
   </si>
   <si>
     <t xml:space="preserve">12.8007841110229</t>
@@ -1496,34 +1496,34 @@
     <t xml:space="preserve">11.8960161209106</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6614465713501</t>
+    <t xml:space="preserve">11.6614475250244</t>
   </si>
   <si>
     <t xml:space="preserve">11.075023651123</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0415153503418</t>
+    <t xml:space="preserve">11.0415143966675</t>
   </si>
   <si>
     <t xml:space="preserve">10.9577388763428</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7566795349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9242296218872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.974494934082</t>
+    <t xml:space="preserve">10.7566804885864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9242305755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9744930267334</t>
   </si>
   <si>
     <t xml:space="preserve">11.7117118835449</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3651552200317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4603872299194</t>
+    <t xml:space="preserve">12.3651542663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4603891372681</t>
   </si>
   <si>
     <t xml:space="preserve">11.1587982177734</t>
@@ -1535,7 +1535,7 @@
     <t xml:space="preserve">11.1755542755127</t>
   </si>
   <si>
-    <t xml:space="preserve">11.376612663269</t>
+    <t xml:space="preserve">11.3766117095947</t>
   </si>
   <si>
     <t xml:space="preserve">12.2311153411865</t>
@@ -1547,37 +1547,37 @@
     <t xml:space="preserve">11.9295263290405</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7954874038696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8792610168457</t>
+    <t xml:space="preserve">11.7954864501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.87926197052</t>
   </si>
   <si>
     <t xml:space="preserve">12.1976051330566</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2478704452515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0133008956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1305856704712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1808519363403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.381911277771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3316459655762</t>
+    <t xml:space="preserve">12.2478713989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0133018493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1305866241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1808500289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3819103240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3316450119019</t>
   </si>
   <si>
     <t xml:space="preserve">12.4656839370728</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5997247695923</t>
+    <t xml:space="preserve">12.599723815918</t>
   </si>
   <si>
     <t xml:space="preserve">12.7170095443726</t>
@@ -1586,7 +1586,7 @@
     <t xml:space="preserve">12.8845586776733</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9515800476074</t>
+    <t xml:space="preserve">12.9515781402588</t>
   </si>
   <si>
     <t xml:space="preserve">12.9683332443237</t>
@@ -1607,25 +1607,25 @@
     <t xml:space="preserve">12.7002544403076</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5159492492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.784029006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0018434524536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0353536605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5494575500488</t>
+    <t xml:space="preserve">12.5159502029419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7840299606323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0018444061279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0353527069092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5494585037231</t>
   </si>
   <si>
     <t xml:space="preserve">12.9348230361938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9180688858032</t>
+    <t xml:space="preserve">12.9180679321289</t>
   </si>
   <si>
     <t xml:space="preserve">13.38720703125</t>
@@ -1634,25 +1634,25 @@
     <t xml:space="preserve">13.6217775344849</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8228349685669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5044927597046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4542264938354</t>
+    <t xml:space="preserve">13.8228368759155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5044937133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4542255401611</t>
   </si>
   <si>
     <t xml:space="preserve">13.6385326385498</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7223072052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3704519271851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0521087646484</t>
+    <t xml:space="preserve">13.7223052978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3704528808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0521078109741</t>
   </si>
   <si>
     <t xml:space="preserve">13.0185985565186</t>
@@ -1664,13 +1664,13 @@
     <t xml:space="preserve">13.1023731231689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.499195098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7481784820557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5740203857422</t>
+    <t xml:space="preserve">12.4991941452026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7481756210327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5740222930908</t>
   </si>
   <si>
     <t xml:space="preserve">12.3650341033936</t>
@@ -1688,70 +1688,70 @@
     <t xml:space="preserve">12.2953729629517</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3302030563354</t>
+    <t xml:space="preserve">12.3302040100098</t>
   </si>
   <si>
     <t xml:space="preserve">12.1212167739868</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5217742919922</t>
+    <t xml:space="preserve">12.5217752456665</t>
   </si>
   <si>
     <t xml:space="preserve">12.4869432449341</t>
   </si>
   <si>
-    <t xml:space="preserve">12.452112197876</t>
+    <t xml:space="preserve">12.4521131515503</t>
   </si>
   <si>
     <t xml:space="preserve">12.1386337280273</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0515556335449</t>
+    <t xml:space="preserve">12.0515546798706</t>
   </si>
   <si>
     <t xml:space="preserve">11.8948154449463</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2082948684692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8178396224976</t>
+    <t xml:space="preserve">12.2082958221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8178405761719</t>
   </si>
   <si>
     <t xml:space="preserve">12.7655925750732</t>
   </si>
   <si>
-    <t xml:space="preserve">12.643684387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.399866104126</t>
+    <t xml:space="preserve">12.6436834335327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3998670578003</t>
   </si>
   <si>
     <t xml:space="preserve">12.6262683868408</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5391912460327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8700866699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9745779037476</t>
+    <t xml:space="preserve">12.5391893386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8700857162476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9745788574219</t>
   </si>
   <si>
     <t xml:space="preserve">12.9571628570557</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9397468566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7830085754395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.695930480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8004236221313</t>
+    <t xml:space="preserve">12.9397478103638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7830076217651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6959295272827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.800422668457</t>
   </si>
   <si>
     <t xml:space="preserve">12.8875017166138</t>
@@ -1763,22 +1763,22 @@
     <t xml:space="preserve">12.0341396331787</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7206592559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2431259155273</t>
+    <t xml:space="preserve">11.7206602096558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2431268692017</t>
   </si>
   <si>
     <t xml:space="preserve">11.7554903030396</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6684122085571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9993085861206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0689706802368</t>
+    <t xml:space="preserve">11.6684131622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9993076324463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0689697265625</t>
   </si>
   <si>
     <t xml:space="preserve">12.1038017272949</t>
@@ -1793,19 +1793,19 @@
     <t xml:space="preserve">11.9470624923706</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8251523971558</t>
+    <t xml:space="preserve">11.8251533508301</t>
   </si>
   <si>
     <t xml:space="preserve">11.8599843978882</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7729063034058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8773994445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6509971618652</t>
+    <t xml:space="preserve">11.7729072570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8774003982544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6509981155396</t>
   </si>
   <si>
     <t xml:space="preserve">11.5465040206909</t>
@@ -1817,19 +1817,19 @@
     <t xml:space="preserve">11.2156095504761</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4071807861328</t>
+    <t xml:space="preserve">11.4071798324585</t>
   </si>
   <si>
     <t xml:space="preserve">11.3026857376099</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3549337387085</t>
+    <t xml:space="preserve">11.3549327850342</t>
   </si>
   <si>
     <t xml:space="preserve">11.3897647857666</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1981935501099</t>
+    <t xml:space="preserve">11.1981925964355</t>
   </si>
   <si>
     <t xml:space="preserve">10.9369602203369</t>
@@ -1838,16 +1838,16 @@
     <t xml:space="preserve">11.0414533615112</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8847141265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8672981262207</t>
+    <t xml:space="preserve">10.8847131729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.867299079895</t>
   </si>
   <si>
     <t xml:space="preserve">10.9717922210693</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8324661254883</t>
+    <t xml:space="preserve">10.832465171814</t>
   </si>
   <si>
     <t xml:space="preserve">10.623480796814</t>
@@ -1856,34 +1856,34 @@
     <t xml:space="preserve">10.6060657501221</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5886487960815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5189876556396</t>
+    <t xml:space="preserve">10.5886497497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5189867019653</t>
   </si>
   <si>
     <t xml:space="preserve">10.4493255615234</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6583108901978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7802209854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1633615493774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1111154556274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0588684082031</t>
+    <t xml:space="preserve">10.6583127975464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7802200317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1633625030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1111164093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0588693618774</t>
   </si>
   <si>
     <t xml:space="preserve">10.9892063140869</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8498821258545</t>
+    <t xml:space="preserve">10.8498830795288</t>
   </si>
   <si>
     <t xml:space="preserve">11.0240383148193</t>
@@ -1892,34 +1892,34 @@
     <t xml:space="preserve">11.0066232681274</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7976369857788</t>
+    <t xml:space="preserve">10.7976360321045</t>
   </si>
   <si>
     <t xml:space="preserve">10.8150520324707</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9543752670288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0937004089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7032432556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9818925857544</t>
+    <t xml:space="preserve">10.9543762207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0936994552612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7032442092896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9818935394287</t>
   </si>
   <si>
     <t xml:space="preserve">11.9296464920044</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9122304916382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8077383041382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2605419158936</t>
+    <t xml:space="preserve">11.9122314453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8077373504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2605409622192</t>
   </si>
   <si>
     <t xml:space="preserve">12.0863876342773</t>
@@ -1931,22 +1931,22 @@
     <t xml:space="preserve">11.529088973999</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4942588806152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.581335067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4768438339233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6858291625977</t>
+    <t xml:space="preserve">11.4942569732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5813360214233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.476842880249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6858282089233</t>
   </si>
   <si>
     <t xml:space="preserve">12.1908798217773</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3476190567017</t>
+    <t xml:space="preserve">12.3476209640503</t>
   </si>
   <si>
     <t xml:space="preserve">11.5116729736328</t>
@@ -1955,34 +1955,34 @@
     <t xml:space="preserve">11.5987510681152</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7105579376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7004566192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49146938323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03866672515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98641872406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42912292480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18530464172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22884273529053</t>
+    <t xml:space="preserve">10.7105588912964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70045757293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49147033691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03866577148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98641967773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.429123878479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18530559539795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22884368896484</t>
   </si>
   <si>
     <t xml:space="preserve">8.45524597167969</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53361511230469</t>
+    <t xml:space="preserve">8.533616065979</t>
   </si>
   <si>
     <t xml:space="preserve">8.49007701873779</t>
@@ -1991,10 +1991,10 @@
     <t xml:space="preserve">8.31592178344727</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32462882995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16788864135742</t>
+    <t xml:space="preserve">8.32462978363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16788959503174</t>
   </si>
   <si>
     <t xml:space="preserve">8.38558387756348</t>
@@ -2003,7 +2003,7 @@
     <t xml:space="preserve">8.28979873657227</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41170692443848</t>
+    <t xml:space="preserve">8.41170597076416</t>
   </si>
   <si>
     <t xml:space="preserve">8.4987850189209</t>
@@ -2015,7 +2015,7 @@
     <t xml:space="preserve">8.69035625457764</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67294120788574</t>
+    <t xml:space="preserve">8.67294025421143</t>
   </si>
   <si>
     <t xml:space="preserve">8.79484939575195</t>
@@ -2024,7 +2024,7 @@
     <t xml:space="preserve">8.96900367736816</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75130939483643</t>
+    <t xml:space="preserve">8.75131034851074</t>
   </si>
   <si>
     <t xml:space="preserve">8.70777130126953</t>
@@ -2036,10 +2036,10 @@
     <t xml:space="preserve">9.18669891357422</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05608081817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14315986633301</t>
+    <t xml:space="preserve">9.05608177185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14315891265869</t>
   </si>
   <si>
     <t xml:space="preserve">9.23023796081543</t>
@@ -2048,16 +2048,16 @@
     <t xml:space="preserve">9.40439319610596</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66562557220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57854747772217</t>
+    <t xml:space="preserve">9.66562747955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57854843139648</t>
   </si>
   <si>
     <t xml:space="preserve">9.31731510162354</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88192653656006</t>
+    <t xml:space="preserve">8.88192558288574</t>
   </si>
   <si>
     <t xml:space="preserve">8.65552425384521</t>
@@ -2066,19 +2066,19 @@
     <t xml:space="preserve">8.51620006561279</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60327816009521</t>
+    <t xml:space="preserve">8.6032772064209</t>
   </si>
   <si>
     <t xml:space="preserve">8.56844711303711</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36085319519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83978176116943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.01393699646</t>
+    <t xml:space="preserve">9.36085414886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83978080749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0139360427856</t>
   </si>
   <si>
     <t xml:space="preserve">10.1010150909424</t>
@@ -2096,34 +2096,34 @@
     <t xml:space="preserve">9.97039794921875</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7091646194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75270462036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62208652496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53500938415527</t>
+    <t xml:space="preserve">9.70916366577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75270366668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6220874786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53500843048096</t>
   </si>
   <si>
     <t xml:space="preserve">9.79624271392822</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1880912780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2751703262329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5364036560059</t>
+    <t xml:space="preserve">10.1880922317505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2751693725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5364027023315</t>
   </si>
   <si>
     <t xml:space="preserve">10.9282522201538</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0153293609619</t>
+    <t xml:space="preserve">11.0153303146362</t>
   </si>
   <si>
     <t xml:space="preserve">10.7540979385376</t>
@@ -2132,7 +2132,7 @@
     <t xml:space="preserve">10.4928646087646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4057855606079</t>
+    <t xml:space="preserve">10.4057865142822</t>
   </si>
   <si>
     <t xml:space="preserve">10.362247467041</t>
@@ -2147,22 +2147,22 @@
     <t xml:space="preserve">11.2765636444092</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4507188796997</t>
+    <t xml:space="preserve">11.4507179260254</t>
   </si>
   <si>
     <t xml:space="preserve">12.0167245864868</t>
   </si>
   <si>
-    <t xml:space="preserve">12.060263633728</t>
+    <t xml:space="preserve">12.0602626800537</t>
   </si>
   <si>
     <t xml:space="preserve">12.5011930465698</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0100746154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.831485748291</t>
+    <t xml:space="preserve">12.0100755691528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8314867019653</t>
   </si>
   <si>
     <t xml:space="preserve">11.6975450515747</t>
@@ -2171,19 +2171,19 @@
     <t xml:space="preserve">11.4743099212646</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2064266204834</t>
+    <t xml:space="preserve">11.2064256668091</t>
   </si>
   <si>
     <t xml:space="preserve">11.4296627044678</t>
   </si>
   <si>
-    <t xml:space="preserve">11.608250617981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2510747909546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5813665390015</t>
+    <t xml:space="preserve">11.6082496643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2510738372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5813674926758</t>
   </si>
   <si>
     <t xml:space="preserve">10.5367202758789</t>
@@ -2192,16 +2192,16 @@
     <t xml:space="preserve">11.0278387069702</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8938961029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1617803573608</t>
+    <t xml:space="preserve">10.8938970565796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1617784500122</t>
   </si>
   <si>
     <t xml:space="preserve">11.0724849700928</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9207811355591</t>
+    <t xml:space="preserve">11.9207801818848</t>
   </si>
   <si>
     <t xml:space="preserve">12.1886625289917</t>
@@ -2216,28 +2216,28 @@
     <t xml:space="preserve">11.8761339187622</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1440172195435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7868394851685</t>
+    <t xml:space="preserve">12.1440162658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7868385314941</t>
   </si>
   <si>
     <t xml:space="preserve">12.0993690490723</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4387817382812</t>
+    <t xml:space="preserve">13.4387826919556</t>
   </si>
   <si>
     <t xml:space="preserve">13.4834308624268</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9299011230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8406057357788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0191955566406</t>
+    <t xml:space="preserve">13.9299020767212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8406066894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0191946029663</t>
   </si>
   <si>
     <t xml:space="preserve">12.9030170440674</t>
@@ -2249,25 +2249,25 @@
     <t xml:space="preserve">13.036958694458</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7513122558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7959594726562</t>
+    <t xml:space="preserve">13.7513113021851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7959585189819</t>
   </si>
   <si>
     <t xml:space="preserve">13.3941354751587</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9745473861694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2601947784424</t>
+    <t xml:space="preserve">13.9745483398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2601938247681</t>
   </si>
   <si>
     <t xml:space="preserve">13.6620178222656</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6173715591431</t>
+    <t xml:space="preserve">13.6173706054688</t>
   </si>
   <si>
     <t xml:space="preserve">13.88525390625</t>
@@ -2276,7 +2276,7 @@
     <t xml:space="preserve">14.6442546844482</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7781944274902</t>
+    <t xml:space="preserve">14.7781953811646</t>
   </si>
   <si>
     <t xml:space="preserve">14.9121379852295</t>
@@ -2285,10 +2285,10 @@
     <t xml:space="preserve">15.0907258987427</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7335481643677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4210186004639</t>
+    <t xml:space="preserve">14.733549118042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4210195541382</t>
   </si>
   <si>
     <t xml:space="preserve">14.5103130340576</t>
@@ -2303,7 +2303,7 @@
     <t xml:space="preserve">15.8050813674927</t>
   </si>
   <si>
-    <t xml:space="preserve">16.072961807251</t>
+    <t xml:space="preserve">16.0729637145996</t>
   </si>
   <si>
     <t xml:space="preserve">16.3854923248291</t>
@@ -2324,13 +2324,13 @@
     <t xml:space="preserve">17.769552230835</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8142013549805</t>
+    <t xml:space="preserve">17.8142032623291</t>
   </si>
   <si>
     <t xml:space="preserve">17.8588466644287</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0374374389648</t>
+    <t xml:space="preserve">18.0374355316162</t>
   </si>
   <si>
     <t xml:space="preserve">18.12672996521</t>
@@ -2342,13 +2342,13 @@
     <t xml:space="preserve">18.5732002258301</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6980228424072</t>
+    <t xml:space="preserve">16.6980247497559</t>
   </si>
   <si>
     <t xml:space="preserve">18.3053188323975</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5909671783447</t>
+    <t xml:space="preserve">17.5909652709961</t>
   </si>
   <si>
     <t xml:space="preserve">18.2160243988037</t>
@@ -2360,19 +2360,19 @@
     <t xml:space="preserve">19.0196723937988</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1804981231689</t>
+    <t xml:space="preserve">20.1804962158203</t>
   </si>
   <si>
     <t xml:space="preserve">20.5376739501953</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6269683837891</t>
+    <t xml:space="preserve">20.6269702911377</t>
   </si>
   <si>
     <t xml:space="preserve">20.9841461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8055572509766</t>
+    <t xml:space="preserve">20.8055553436279</t>
   </si>
   <si>
     <t xml:space="preserve">21.0734405517578</t>
@@ -2381,43 +2381,43 @@
     <t xml:space="preserve">20.0912036895752</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0019111633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8233203887939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2697925567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1982593536377</t>
+    <t xml:space="preserve">20.0019092559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8233222961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2697906494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1982612609863</t>
   </si>
   <si>
     <t xml:space="preserve">19.9126129150391</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5554389953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6447315216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9303779602051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7162628173828</t>
+    <t xml:space="preserve">19.5554370880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6447334289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9303798675537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7162647247314</t>
   </si>
   <si>
     <t xml:space="preserve">20.4483795166016</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4306182861328</t>
+    <t xml:space="preserve">21.4306163787842</t>
   </si>
   <si>
     <t xml:space="preserve">21.3413219451904</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3235607147217</t>
+    <t xml:space="preserve">22.3235569000244</t>
   </si>
   <si>
     <t xml:space="preserve">21.6092052459717</t>
@@ -2426,16 +2426,16 @@
     <t xml:space="preserve">22.0556774139404</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7877922058105</t>
+    <t xml:space="preserve">21.7877941131592</t>
   </si>
   <si>
     <t xml:space="preserve">22.7700309753418</t>
   </si>
   <si>
-    <t xml:space="preserve">24.914701461792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4583873748779</t>
+    <t xml:space="preserve">24.9147033691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4583892822266</t>
   </si>
   <si>
     <t xml:space="preserve">24.0020771026611</t>
@@ -2444,22 +2444,22 @@
     <t xml:space="preserve">23.8195514678955</t>
   </si>
   <si>
-    <t xml:space="preserve">24.549654006958</t>
+    <t xml:space="preserve">24.5496520996094</t>
   </si>
   <si>
     <t xml:space="preserve">25.4622783660889</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8234424591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0933399200439</t>
+    <t xml:space="preserve">24.8234405517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0933380126953</t>
   </si>
   <si>
     <t xml:space="preserve">24.732177734375</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3671283721924</t>
+    <t xml:space="preserve">24.367130279541</t>
   </si>
   <si>
     <t xml:space="preserve">23.9108142852783</t>
@@ -2468,7 +2468,7 @@
     <t xml:space="preserve">23.2719764709473</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6370258331299</t>
+    <t xml:space="preserve">23.6370277404785</t>
   </si>
   <si>
     <t xml:space="preserve">23.5457630157471</t>
@@ -2480,22 +2480,22 @@
     <t xml:space="preserve">23.7282886505127</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1846008300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0059642791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3593502044678</t>
+    <t xml:space="preserve">24.1846027374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0059661865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3593482971191</t>
   </si>
   <si>
     <t xml:space="preserve">22.8156623840332</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2680854797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7243976593018</t>
+    <t xml:space="preserve">22.268087387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7243995666504</t>
   </si>
   <si>
     <t xml:space="preserve">23.4545021057129</t>
@@ -2507,10 +2507,10 @@
     <t xml:space="preserve">23.1807117462158</t>
   </si>
   <si>
-    <t xml:space="preserve">22.906925201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1768226623535</t>
+    <t xml:space="preserve">22.9069271087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1768245697021</t>
   </si>
   <si>
     <t xml:space="preserve">22.5418758392334</t>
@@ -2522,10 +2522,10 @@
     <t xml:space="preserve">22.0855617523193</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5379867553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7205104827881</t>
+    <t xml:space="preserve">21.5379848480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7205085754395</t>
   </si>
   <si>
     <t xml:space="preserve">21.3554592132568</t>
@@ -2534,10 +2534,10 @@
     <t xml:space="preserve">21.8117733001709</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4467220306396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8991451263428</t>
+    <t xml:space="preserve">21.4467239379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8991470336914</t>
   </si>
   <si>
     <t xml:space="preserve">19.0738945007324</t>
@@ -2546,13 +2546,13 @@
     <t xml:space="preserve">19.8952560424805</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8039951324463</t>
+    <t xml:space="preserve">19.8039970397949</t>
   </si>
   <si>
     <t xml:space="preserve">19.6214694976807</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7127342224121</t>
+    <t xml:space="preserve">19.7127323150635</t>
   </si>
   <si>
     <t xml:space="preserve">21.081672668457</t>
@@ -2561,10 +2561,10 @@
     <t xml:space="preserve">24.6409149169922</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3710174560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3749046325684</t>
+    <t xml:space="preserve">25.3710155487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.374906539917</t>
   </si>
   <si>
     <t xml:space="preserve">25.6448059082031</t>
@@ -2591,22 +2591,22 @@
     <t xml:space="preserve">21.6292476654053</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9904098510742</t>
+    <t xml:space="preserve">20.9904079437256</t>
   </si>
   <si>
     <t xml:space="preserve">21.2641983032227</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1729335784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5340957641602</t>
+    <t xml:space="preserve">21.1729354858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5340976715088</t>
   </si>
   <si>
     <t xml:space="preserve">20.8078842163086</t>
   </si>
   <si>
-    <t xml:space="preserve">20.442834854126</t>
+    <t xml:space="preserve">20.4428329467773</t>
   </si>
   <si>
     <t xml:space="preserve">21.9030361175537</t>
@@ -2621,19 +2621,19 @@
     <t xml:space="preserve">20.1690464019775</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3476829528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1651554107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2525310516357</t>
+    <t xml:space="preserve">19.3476810455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1651573181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2525291442871</t>
   </si>
   <si>
     <t xml:space="preserve">18.6175804138184</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1156368255615</t>
+    <t xml:space="preserve">18.1156349182129</t>
   </si>
   <si>
     <t xml:space="preserve">17.4311676025391</t>
@@ -2654,19 +2654,19 @@
     <t xml:space="preserve">16.7010650634766</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6593246459961</t>
+    <t xml:space="preserve">17.6593227386475</t>
   </si>
   <si>
     <t xml:space="preserve">17.2486400604248</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3437919616699</t>
+    <t xml:space="preserve">18.3437938690186</t>
   </si>
   <si>
     <t xml:space="preserve">18.800106048584</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2564182281494</t>
+    <t xml:space="preserve">19.256420135498</t>
   </si>
   <si>
     <t xml:space="preserve">18.982629776001</t>
@@ -2687,7 +2687,7 @@
     <t xml:space="preserve">21.8574047088623</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3137187957764</t>
+    <t xml:space="preserve">22.3137168884277</t>
   </si>
   <si>
     <t xml:space="preserve">21.9486656188965</t>
@@ -2699,58 +2699,58 @@
     <t xml:space="preserve">21.4923534393311</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4049777984619</t>
+    <t xml:space="preserve">22.4049797058105</t>
   </si>
   <si>
     <t xml:space="preserve">22.678768157959</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5913963317871</t>
+    <t xml:space="preserve">23.5913944244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5001335144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7337303161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8271713256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.387809753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2009315490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6681289672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.621410369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0607719421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9673309326172</t>
   </si>
   <si>
     <t xml:space="preserve">23.5001316070557</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7337303161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.827169418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3878116607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2009296417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6681289672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.621410369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.06077003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9673309326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.500129699707</t>
-  </si>
-  <si>
     <t xml:space="preserve">22.9394912719727</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7058906555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6591720581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5190143585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4255714416504</t>
+    <t xml:space="preserve">22.7058925628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6591739654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5190124511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.425573348999</t>
   </si>
   <si>
     <t xml:space="preserve">23.4534130096436</t>
@@ -2768,7 +2768,7 @@
     <t xml:space="preserve">22.0985317230225</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9116535186768</t>
+    <t xml:space="preserve">21.9116554260254</t>
   </si>
   <si>
     <t xml:space="preserve">21.6780548095703</t>
@@ -2780,7 +2780,7 @@
     <t xml:space="preserve">23.0329303741455</t>
   </si>
   <si>
-    <t xml:space="preserve">22.986213684082</t>
+    <t xml:space="preserve">22.9862117767334</t>
   </si>
   <si>
     <t xml:space="preserve">21.8182144165039</t>
@@ -2789,7 +2789,7 @@
     <t xml:space="preserve">22.1919727325439</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7714920043945</t>
+    <t xml:space="preserve">21.7714939117432</t>
   </si>
   <si>
     <t xml:space="preserve">22.2386913299561</t>
@@ -2801,13 +2801,13 @@
     <t xml:space="preserve">23.31325340271</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7993316650391</t>
+    <t xml:space="preserve">22.7993335723877</t>
   </si>
   <si>
     <t xml:space="preserve">22.3321323394775</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5846157073975</t>
+    <t xml:space="preserve">21.5846138000488</t>
   </si>
   <si>
     <t xml:space="preserve">20.930534362793</t>
@@ -2819,7 +2819,7 @@
     <t xml:space="preserve">20.2764568328857</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9494171142578</t>
+    <t xml:space="preserve">19.9494152069092</t>
   </si>
   <si>
     <t xml:space="preserve">20.4166164398193</t>
@@ -2840,25 +2840,25 @@
     <t xml:space="preserve">19.9026947021484</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8092575073242</t>
+    <t xml:space="preserve">19.8092555999756</t>
   </si>
   <si>
     <t xml:space="preserve">19.5756568908691</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3420581817627</t>
+    <t xml:space="preserve">19.3420562744141</t>
   </si>
   <si>
     <t xml:space="preserve">19.2486171722412</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9215755462646</t>
+    <t xml:space="preserve">18.9215774536133</t>
   </si>
   <si>
     <t xml:space="preserve">18.8281364440918</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5758476257324</t>
+    <t xml:space="preserve">18.5758495330811</t>
   </si>
   <si>
     <t xml:space="preserve">18.5010967254639</t>
@@ -2870,7 +2870,7 @@
     <t xml:space="preserve">19.5289363861084</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5945358276367</t>
+    <t xml:space="preserve">18.5945377349854</t>
   </si>
   <si>
     <t xml:space="preserve">18.3702812194824</t>
@@ -2879,7 +2879,7 @@
     <t xml:space="preserve">18.0525856018066</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9217720031738</t>
+    <t xml:space="preserve">17.9217700958252</t>
   </si>
   <si>
     <t xml:space="preserve">17.7535781860352</t>
@@ -2891,10 +2891,10 @@
     <t xml:space="preserve">17.7348899841309</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4919471740723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2303142547607</t>
+    <t xml:space="preserve">17.4919452667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2303161621094</t>
   </si>
   <si>
     <t xml:space="preserve">17.1742496490479</t>
@@ -2909,7 +2909,7 @@
     <t xml:space="preserve">16.4454212188721</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1277256011963</t>
+    <t xml:space="preserve">16.1277236938477</t>
   </si>
   <si>
     <t xml:space="preserve">16.5014839172363</t>
@@ -2921,13 +2921,13 @@
     <t xml:space="preserve">16.0342845916748</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8847818374634</t>
+    <t xml:space="preserve">15.8847808837891</t>
   </si>
   <si>
     <t xml:space="preserve">15.3241405487061</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6044607162476</t>
+    <t xml:space="preserve">15.6044616699219</t>
   </si>
   <si>
     <t xml:space="preserve">15.7352771759033</t>
@@ -2945,7 +2945,7 @@
     <t xml:space="preserve">16.7444267272949</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7257385253906</t>
+    <t xml:space="preserve">16.7257404327393</t>
   </si>
   <si>
     <t xml:space="preserve">16.9313087463379</t>
@@ -2957,7 +2957,7 @@
     <t xml:space="preserve">17.9965229034424</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2581539154053</t>
+    <t xml:space="preserve">18.2581558227539</t>
   </si>
   <si>
     <t xml:space="preserve">17.6601371765137</t>
@@ -2966,10 +2966,10 @@
     <t xml:space="preserve">17.5666980743408</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6414489746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3142185211182</t>
+    <t xml:space="preserve">17.641450881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3142166137695</t>
   </si>
   <si>
     <t xml:space="preserve">18.0712738037109</t>
@@ -3008,7 +3008,7 @@
     <t xml:space="preserve">17.7162017822266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5293235778809</t>
+    <t xml:space="preserve">17.5293216705322</t>
   </si>
   <si>
     <t xml:space="preserve">16.9873714447021</t>
@@ -3020,10 +3020,10 @@
     <t xml:space="preserve">17.5480117797852</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2772274017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.922158241272</t>
+    <t xml:space="preserve">16.277229309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9221572875977</t>
   </si>
   <si>
     <t xml:space="preserve">16.0155963897705</t>
@@ -3032,19 +3032,19 @@
     <t xml:space="preserve">15.9595327377319</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9782209396362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0903491973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8287162780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6231479644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5857725143433</t>
+    <t xml:space="preserve">15.9782218933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0903472900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8287172317505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6231489181519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5857744216919</t>
   </si>
   <si>
     <t xml:space="preserve">16.0716609954834</t>
@@ -3065,10 +3065,10 @@
     <t xml:space="preserve">16.6322994232178</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6136131286621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5762367248535</t>
+    <t xml:space="preserve">16.6136112213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5762348175049</t>
   </si>
   <si>
     <t xml:space="preserve">16.3519802093506</t>
@@ -3077,13 +3077,13 @@
     <t xml:space="preserve">16.2024765014648</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7913398742676</t>
+    <t xml:space="preserve">15.7913408279419</t>
   </si>
   <si>
     <t xml:space="preserve">15.7726516723633</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6979007720947</t>
+    <t xml:space="preserve">15.6978998184204</t>
   </si>
   <si>
     <t xml:space="preserve">16.5201721191406</t>
@@ -3092,34 +3092,34 @@
     <t xml:space="preserve">16.1464138031006</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1651000976562</t>
+    <t xml:space="preserve">16.1650981903076</t>
   </si>
   <si>
     <t xml:space="preserve">16.109037399292</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8474025726318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7539653778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8660936355591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6792144775391</t>
+    <t xml:space="preserve">15.8474044799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7539663314819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8660917282104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6792125701904</t>
   </si>
   <si>
     <t xml:space="preserve">15.8100280761719</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5110216140747</t>
+    <t xml:space="preserve">15.5110206604004</t>
   </si>
   <si>
     <t xml:space="preserve">15.3802042007446</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0064458847046</t>
+    <t xml:space="preserve">15.0064449310303</t>
   </si>
   <si>
     <t xml:space="preserve">14.8008785247803</t>
@@ -3128,7 +3128,7 @@
     <t xml:space="preserve">14.6700620651245</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4271173477173</t>
+    <t xml:space="preserve">14.4271183013916</t>
   </si>
   <si>
     <t xml:space="preserve">14.5766229629517</t>
@@ -3158,13 +3158,13 @@
     <t xml:space="preserve">15.0811967849731</t>
   </si>
   <si>
-    <t xml:space="preserve">15.567084312439</t>
+    <t xml:space="preserve">15.5670852661133</t>
   </si>
   <si>
     <t xml:space="preserve">15.716588973999</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6605262756348</t>
+    <t xml:space="preserve">15.6605253219604</t>
   </si>
   <si>
     <t xml:space="preserve">15.1933259963989</t>
@@ -3173,13 +3173,13 @@
     <t xml:space="preserve">15.3988933563232</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4175815582275</t>
+    <t xml:space="preserve">15.4175806045532</t>
   </si>
   <si>
     <t xml:space="preserve">15.4362697601318</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1372623443604</t>
+    <t xml:space="preserve">15.137261390686</t>
   </si>
   <si>
     <t xml:space="preserve">15.0438222885132</t>
@@ -3191,7 +3191,7 @@
     <t xml:space="preserve">14.9877586364746</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7261266708374</t>
+    <t xml:space="preserve">14.7261257171631</t>
   </si>
   <si>
     <t xml:space="preserve">14.950382232666</t>
@@ -3206,22 +3206,22 @@
     <t xml:space="preserve">14.3149900436401</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5018711090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4084300994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1654863357544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2028617858887</t>
+    <t xml:space="preserve">14.5018701553345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4084310531616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1654872894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.202862739563</t>
   </si>
   <si>
     <t xml:space="preserve">14.2963027954102</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1281108856201</t>
+    <t xml:space="preserve">14.1281099319458</t>
   </si>
   <si>
     <t xml:space="preserve">13.8291034698486</t>
@@ -3236,19 +3236,19 @@
     <t xml:space="preserve">13.4179677963257</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5487842559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6422243118286</t>
+    <t xml:space="preserve">13.5487833023071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6422233581543</t>
   </si>
   <si>
     <t xml:space="preserve">13.45534324646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3992795944214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3245286941528</t>
+    <t xml:space="preserve">13.3992805480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3245277404785</t>
   </si>
   <si>
     <t xml:space="preserve">13.2497758865356</t>
@@ -3257,7 +3257,7 @@
     <t xml:space="preserve">13.0815839767456</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3432159423828</t>
+    <t xml:space="preserve">13.3432149887085</t>
   </si>
   <si>
     <t xml:space="preserve">13.1937122344971</t>
@@ -3266,7 +3266,7 @@
     <t xml:space="preserve">13.3058395385742</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2589273452759</t>
+    <t xml:space="preserve">14.2589263916016</t>
   </si>
   <si>
     <t xml:space="preserve">14.2776145935059</t>
@@ -3275,7 +3275,7 @@
     <t xml:space="preserve">14.7448139190674</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5575485229492</t>
+    <t xml:space="preserve">16.5575466156006</t>
   </si>
   <si>
     <t xml:space="preserve">16.4641094207764</t>
@@ -3284,13 +3284,13 @@
     <t xml:space="preserve">16.4267311096191</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3146018981934</t>
+    <t xml:space="preserve">16.314603805542</t>
   </si>
   <si>
     <t xml:space="preserve">16.2585391998291</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2398509979248</t>
+    <t xml:space="preserve">16.2398529052734</t>
   </si>
   <si>
     <t xml:space="preserve">16.1837882995605</t>
@@ -3299,13 +3299,13 @@
     <t xml:space="preserve">14.8569412231445</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7074384689331</t>
+    <t xml:space="preserve">14.7074375152588</t>
   </si>
   <si>
     <t xml:space="preserve">14.6887502670288</t>
   </si>
   <si>
-    <t xml:space="preserve">14.389741897583</t>
+    <t xml:space="preserve">14.3897428512573</t>
   </si>
   <si>
     <t xml:space="preserve">14.782190322876</t>
@@ -3326,19 +3326,19 @@
     <t xml:space="preserve">12.9881439208984</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5956954956055</t>
+    <t xml:space="preserve">12.5956964492798</t>
   </si>
   <si>
     <t xml:space="preserve">12.7078247070312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7452011108398</t>
+    <t xml:space="preserve">12.7452001571655</t>
   </si>
   <si>
     <t xml:space="preserve">12.4275054931641</t>
   </si>
   <si>
-    <t xml:space="preserve">13.044207572937</t>
+    <t xml:space="preserve">13.0442085266113</t>
   </si>
   <si>
     <t xml:space="preserve">13.3805913925171</t>
@@ -3365,28 +3365,28 @@
     <t xml:space="preserve">13.9972944259644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.015983581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6513738632202</t>
+    <t xml:space="preserve">14.0159826278687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6513748168945</t>
   </si>
   <si>
     <t xml:space="preserve">15.0251340866089</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4736452102661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9034700393677</t>
+    <t xml:space="preserve">15.4736442565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.903468132019</t>
   </si>
   <si>
     <t xml:space="preserve">16.482795715332</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9126205444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8565559387207</t>
+    <t xml:space="preserve">16.912618637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8565578460693</t>
   </si>
   <si>
     <t xml:space="preserve">16.9499950408936</t>
@@ -3395,7 +3395,7 @@
     <t xml:space="preserve">16.8752422332764</t>
   </si>
   <si>
-    <t xml:space="preserve">17.043436050415</t>
+    <t xml:space="preserve">17.0434341430664</t>
   </si>
   <si>
     <t xml:space="preserve">15.9969091415405</t>
@@ -3407,7 +3407,7 @@
     <t xml:space="preserve">15.5483961105347</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6418380737305</t>
+    <t xml:space="preserve">15.6418361663818</t>
   </si>
   <si>
     <t xml:space="preserve">16.4080429077148</t>
@@ -3419,13 +3419,13 @@
     <t xml:space="preserve">16.6790199279785</t>
   </si>
   <si>
-    <t xml:space="preserve">16.585578918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8002986907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.706859588623</t>
+    <t xml:space="preserve">16.5855808258057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8002967834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7068576812744</t>
   </si>
   <si>
     <t xml:space="preserve">16.211820602417</t>
@@ -3434,19 +3434,19 @@
     <t xml:space="preserve">15.3708620071411</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3052616119385</t>
+    <t xml:space="preserve">16.3052597045898</t>
   </si>
   <si>
     <t xml:space="preserve">16.0249404907227</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1273365020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9404602050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6134204864502</t>
+    <t xml:space="preserve">18.1273384094238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9404582977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6134185791016</t>
   </si>
   <si>
     <t xml:space="preserve">17.7070121765137</t>
@@ -71834,6 +71834,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2603">
+      <c r="A2603" s="1" t="n">
+        <v>46111.2916666667</v>
+      </c>
+      <c r="B2603" t="n">
+        <v>3609</v>
+      </c>
+      <c r="C2603" t="n">
+        <v>13.3999996185303</v>
+      </c>
+      <c r="D2603" t="n">
+        <v>13.1999998092651</v>
+      </c>
+      <c r="E2603" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="F2603" t="n">
+        <v>13.3000001907349</v>
+      </c>
+      <c r="G2603" t="s">
+        <v>1271</v>
+      </c>
+      <c r="H2603" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SAB.MI.xlsx
+++ b/data/SAB.MI.xlsx
@@ -50,10 +50,10 @@
     <t xml:space="preserve">8.4831018447876</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33295822143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37049579620361</t>
+    <t xml:space="preserve">8.33295917510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3704948425293</t>
   </si>
   <si>
     <t xml:space="preserve">8.31794357299805</t>
@@ -62,25 +62,25 @@
     <t xml:space="preserve">8.25788688659668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16029262542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88252830505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52969026565552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66482019424438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62728452682495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61227083206177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73989295959473</t>
+    <t xml:space="preserve">8.16029453277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88252735137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52969217300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66482210159302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62728548049927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61226987838745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73989248275757</t>
   </si>
   <si>
     <t xml:space="preserve">7.75490665435791</t>
@@ -89,97 +89,97 @@
     <t xml:space="preserve">7.76992130279541</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89754390716553</t>
+    <t xml:space="preserve">7.89754438400269</t>
   </si>
   <si>
     <t xml:space="preserve">7.6197772026062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79994916915894</t>
+    <t xml:space="preserve">7.79995012283325</t>
   </si>
   <si>
     <t xml:space="preserve">7.72487735748291</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65731382369995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5071702003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34201145172119</t>
+    <t xml:space="preserve">7.65731430053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50716972351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34201288223267</t>
   </si>
   <si>
     <t xml:space="preserve">7.54470586776733</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39081001281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58224248886108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82247161865234</t>
+    <t xml:space="preserve">7.39080858230591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58224153518677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82247114181519</t>
   </si>
   <si>
     <t xml:space="preserve">8.0852222442627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1152515411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95759916305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06269931793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03267097473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92006349563599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77742767333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86751461029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80745553970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98762941360474</t>
+    <t xml:space="preserve">8.11524963378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95759963989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06270122528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03267288208008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92006492614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77742719650269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86751222610474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80745649337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98762893676758</t>
   </si>
   <si>
     <t xml:space="preserve">8.04017925262451</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99513626098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96510601043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90504884719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93507766723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8900351524353</t>
+    <t xml:space="preserve">7.99513530731201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96510744094849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9050498008728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93507719039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89003467559814</t>
   </si>
   <si>
     <t xml:space="preserve">7.94258546829224</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82997941970825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81496429443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73238468170166</t>
+    <t xml:space="preserve">7.82997846603394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81496334075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73238515853882</t>
   </si>
   <si>
     <t xml:space="preserve">7.6498064994812</t>
@@ -191,88 +191,88 @@
     <t xml:space="preserve">7.67232847213745</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63479137420654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51467752456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64229965209961</t>
+    <t xml:space="preserve">7.63479280471802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51467704772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64229917526245</t>
   </si>
   <si>
     <t xml:space="preserve">7.56722640991211</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70235681533813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74739837646484</t>
+    <t xml:space="preserve">7.70235538482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74739789962769</t>
   </si>
   <si>
     <t xml:space="preserve">7.46963357925415</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69484853744507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49215507507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47338724136353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43585109710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50341558456421</t>
+    <t xml:space="preserve">7.69484806060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49215602874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47338771820068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43585157394409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50341701507568</t>
   </si>
   <si>
     <t xml:space="preserve">7.48089456558228</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59725570678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42834424972534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38705539703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37204027175903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31949090957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28195524215698</t>
+    <t xml:space="preserve">7.59725475311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4283447265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38705444335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37204074859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31949043273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28195476531982</t>
   </si>
   <si>
     <t xml:space="preserve">7.52122163772583</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80534029006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75009346008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75798559188843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81323003768921</t>
+    <t xml:space="preserve">7.80534076690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75009489059448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75798606872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81323099136353</t>
   </si>
   <si>
     <t xml:space="preserve">7.8605842590332</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69879627227783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58435821533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68695592880249</t>
+    <t xml:space="preserve">7.69879484176636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58435869216919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68695640563965</t>
   </si>
   <si>
     <t xml:space="preserve">7.57646703720093</t>
@@ -281,229 +281,229 @@
     <t xml:space="preserve">7.53700590133667</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49754476547241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28445672988892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92536401748657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.079261302948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22921276092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45808506011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26078081130981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37127065658569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26472616195679</t>
+    <t xml:space="preserve">7.49754571914673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28445720672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92536354064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07926225662231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22921133041382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45808458328247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26077938079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37126970291138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26472568511963</t>
   </si>
   <si>
     <t xml:space="preserve">7.34759473800659</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46992206573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36732530593872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37916326522827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13450574874878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18975067138672</t>
+    <t xml:space="preserve">7.46992349624634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36732387542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37916421890259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1345067024231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18975162506104</t>
   </si>
   <si>
     <t xml:space="preserve">7.10293769836426</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15029001235962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10688400268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20553588867188</t>
+    <t xml:space="preserve">7.15029144287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10688447952271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20553541183472</t>
   </si>
   <si>
     <t xml:space="preserve">7.18185949325562</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22131967544556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19369649887085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24894237518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19764280319214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18580389022827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22526597976685</t>
+    <t xml:space="preserve">7.22132015228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19369745254517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24894285202026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1976432800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18580532073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22526502609253</t>
   </si>
   <si>
     <t xml:space="preserve">7.20948219299316</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3160252571106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21342897415161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16607427597046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24499750137329</t>
+    <t xml:space="preserve">7.31602621078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21342849731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16607475280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24499654769897</t>
   </si>
   <si>
     <t xml:space="preserve">7.13056039810181</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11083030700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17791318893433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23315715789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27656507492065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30024003982544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29234886169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.241051197052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1187219619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09504556655884</t>
+    <t xml:space="preserve">7.11082935333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17791366577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23315811157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27656602859497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30024242401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29234981536865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24105024337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11872148513794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09504508972168</t>
   </si>
   <si>
     <t xml:space="preserve">7.00428581237793</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9450945854187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93325567245483</t>
+    <t xml:space="preserve">6.94509410858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93325614929199</t>
   </si>
   <si>
     <t xml:space="preserve">7.09899139404297</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15423631668091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13845252990723</t>
+    <t xml:space="preserve">7.15423679351807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13845157623291</t>
   </si>
   <si>
     <t xml:space="preserve">7.1581826210022</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05558395385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07136917114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06742238998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0240159034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04769325256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06347751617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08320665359497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05163812637329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04374694824219</t>
+    <t xml:space="preserve">7.05558347702026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07136964797974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06742334365845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02401685714722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04769229888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06347703933716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08320713043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05163860321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04374599456787</t>
   </si>
   <si>
     <t xml:space="preserve">7.03190803527832</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05953121185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03585433959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17396783828735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9056339263916</t>
+    <t xml:space="preserve">7.05953073501587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03585386276245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17396688461304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90563344955444</t>
   </si>
   <si>
     <t xml:space="preserve">6.91352653503418</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93720197677612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9214186668396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94114828109741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9687705039978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14239931106567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45019245147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69484949111938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7935004234314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9237208366394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0499963760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20783805847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16837787628174</t>
+    <t xml:space="preserve">6.93720293045044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92141771316528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94114923477173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96877145767212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14239883422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45019102096558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69484901428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79350090026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92372179031372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04999732971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.207839012146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16837882995605</t>
   </si>
   <si>
     <t xml:space="preserve">8.08945655822754</t>
@@ -512,196 +512,196 @@
     <t xml:space="preserve">8.19994735717773</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06578159332275</t>
+    <t xml:space="preserve">8.06578063964844</t>
   </si>
   <si>
     <t xml:space="preserve">8.1289176940918</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17626953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32622051239014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55509376525879</t>
+    <t xml:space="preserve">8.17627048492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32622146606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55509471893311</t>
   </si>
   <si>
     <t xml:space="preserve">8.56298637390137</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42882061004639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35778903961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39725112915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42092800140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44460391998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40514373779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26308536529541</t>
+    <t xml:space="preserve">8.42881870269775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35778999328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39725017547607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42092704772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44460487365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40514183044434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26308441162109</t>
   </si>
   <si>
     <t xml:space="preserve">8.18416213989258</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30254554748535</t>
+    <t xml:space="preserve">8.30254650115967</t>
   </si>
   <si>
     <t xml:space="preserve">8.22362327575684</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2867603302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25519275665283</t>
+    <t xml:space="preserve">8.28675937652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25519180297852</t>
   </si>
   <si>
     <t xml:space="preserve">8.34989738464355</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3104362487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36568260192871</t>
+    <t xml:space="preserve">8.31043815612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36568355560303</t>
   </si>
   <si>
     <t xml:space="preserve">8.33411407470703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34200477600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46038913726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62612438201904</t>
+    <t xml:space="preserve">8.34200572967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46038818359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62612342834473</t>
   </si>
   <si>
     <t xml:space="preserve">8.74450492858887</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88656425476074</t>
+    <t xml:space="preserve">8.88656520843506</t>
   </si>
   <si>
     <t xml:space="preserve">9.0049467086792</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23381996154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30484771728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26538753509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16279029846191</t>
+    <t xml:space="preserve">9.23381900787354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30484867095947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2653865814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16278839111328</t>
   </si>
   <si>
     <t xml:space="preserve">9.19435882568359</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24960422515869</t>
+    <t xml:space="preserve">9.24960327148438</t>
   </si>
   <si>
     <t xml:space="preserve">9.29695606231689</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36798572540283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54950428009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67577934265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74680995941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2203378677368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4807786941528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4571027755737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2913675308228</t>
+    <t xml:space="preserve">9.36798477172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54950523376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67578029632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7468090057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2203388214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4807796478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.457103729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2913684844971</t>
   </si>
   <si>
     <t xml:space="preserve">10.2597990036011</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1493072509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0861701965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0151424407959</t>
+    <t xml:space="preserve">10.1493091583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0861711502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0151414871216</t>
   </si>
   <si>
     <t xml:space="preserve">10.1019554138184</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1650943756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0546035766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1808757781982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1177387237549</t>
+    <t xml:space="preserve">10.1650924682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0546026229858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1808767318726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1177406311035</t>
   </si>
   <si>
     <t xml:space="preserve">10.1887693405151</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0703868865967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1098489761353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0230350494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.496563911438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4176416397095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3150424957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7333278656006</t>
+    <t xml:space="preserve">10.070387840271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1098480224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0230331420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4965629577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4176406860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3150434494019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7333288192749</t>
   </si>
   <si>
     <t xml:space="preserve">10.4492101669312</t>
   </si>
   <si>
-    <t xml:space="preserve">10.559700012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6386213302612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5912704467773</t>
+    <t xml:space="preserve">10.5597009658813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6386203765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.591269493103</t>
   </si>
   <si>
     <t xml:space="preserve">11.0095529556274</t>
@@ -710,91 +710,91 @@
     <t xml:space="preserve">10.8832788467407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3410224914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0592098236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9171524047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0513200759888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6882781982422</t>
+    <t xml:space="preserve">11.3410234451294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0592088699341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9171495437622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0513181686401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6882791519165</t>
   </si>
   <si>
     <t xml:space="preserve">11.6803865432739</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2644052505493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6274452209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5406303405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6747970581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7379341125488</t>
+    <t xml:space="preserve">12.2644062042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6274461746216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5406312942505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6747951507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7379350662231</t>
   </si>
   <si>
     <t xml:space="preserve">12.4728555679321</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6518526077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8471240997314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8145790100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9203491210938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8715295791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9366216659546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8064403533936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6437158584595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8227138519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5209150314331</t>
+    <t xml:space="preserve">12.6518535614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8471221923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8145780563354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9203481674194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8715314865112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9366207122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8064413070679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6437177658081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8227157592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5209159851074</t>
   </si>
   <si>
     <t xml:space="preserve">11.8463659286499</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7812747955322</t>
+    <t xml:space="preserve">11.7812757492065</t>
   </si>
   <si>
     <t xml:space="preserve">11.9114561080933</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9277267456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9602718353271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8056840896606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1311340332031</t>
+    <t xml:space="preserve">11.9277286529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9602727890015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.805685043335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1311330795288</t>
   </si>
   <si>
     <t xml:space="preserve">12.0009536743164</t>
@@ -803,40 +803,40 @@
     <t xml:space="preserve">11.9846811294556</t>
   </si>
   <si>
-    <t xml:space="preserve">12.041633605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0823173522949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.976544380188</t>
+    <t xml:space="preserve">12.0416355133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0823154449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9765453338623</t>
   </si>
   <si>
     <t xml:space="preserve">11.8789110183716</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7161855697632</t>
+    <t xml:space="preserve">11.7161836624146</t>
   </si>
   <si>
     <t xml:space="preserve">11.4720983505249</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5534610748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5860042572021</t>
+    <t xml:space="preserve">11.5534591674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5860061645508</t>
   </si>
   <si>
     <t xml:space="preserve">11.7975473403931</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8951826095581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0904512405396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1636781692505</t>
+    <t xml:space="preserve">11.8951835632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0904521942139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1636791229248</t>
   </si>
   <si>
     <t xml:space="preserve">12.0741806030273</t>
@@ -851,10 +851,10 @@
     <t xml:space="preserve">12.2043600082397</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1880865097046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.147406578064</t>
+    <t xml:space="preserve">12.1880874633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1474056243896</t>
   </si>
   <si>
     <t xml:space="preserve">12.2531785964966</t>
@@ -863,10 +863,10 @@
     <t xml:space="preserve">12.3670854568481</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4077644348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.448447227478</t>
+    <t xml:space="preserve">12.4077653884888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4484462738037</t>
   </si>
   <si>
     <t xml:space="preserve">12.9447584152222</t>
@@ -878,7 +878,7 @@
     <t xml:space="preserve">12.8959407806396</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0098466873169</t>
+    <t xml:space="preserve">13.0098476409912</t>
   </si>
   <si>
     <t xml:space="preserve">12.9528942108154</t>
@@ -890,13 +890,13 @@
     <t xml:space="preserve">12.7332153320312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7738962173462</t>
+    <t xml:space="preserve">12.7738971710205</t>
   </si>
   <si>
     <t xml:space="preserve">12.9854393005371</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2620697021484</t>
+    <t xml:space="preserve">13.2620716094971</t>
   </si>
   <si>
     <t xml:space="preserve">13.685154914856</t>
@@ -905,130 +905,130 @@
     <t xml:space="preserve">13.9292421340942</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9943342208862</t>
+    <t xml:space="preserve">13.9943332672119</t>
   </si>
   <si>
     <t xml:space="preserve">13.7502450942993</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8153343200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8316078186035</t>
+    <t xml:space="preserve">13.8153352737427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8316097259521</t>
   </si>
   <si>
     <t xml:space="preserve">14.0187406539917</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0268774032593</t>
+    <t xml:space="preserve">14.0268783569336</t>
   </si>
   <si>
     <t xml:space="preserve">14.1814680099487</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1570568084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2302837371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.775411605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3205404281616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2961301803589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4588556289673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8249864578247</t>
+    <t xml:space="preserve">14.157057762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2302827835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7754106521606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3205394744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2961320877075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4588575363159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8249883651733</t>
   </si>
   <si>
     <t xml:space="preserve">15.792441368103</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5076742172241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8493957519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8656673431396</t>
+    <t xml:space="preserve">15.5076732635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8493938446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.865668296814</t>
   </si>
   <si>
     <t xml:space="preserve">15.5158100128174</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0039844512939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2643413543701</t>
+    <t xml:space="preserve">16.0039863586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2643432617188</t>
   </si>
   <si>
     <t xml:space="preserve">16.7769260406494</t>
   </si>
   <si>
-    <t xml:space="preserve">16.955924987793</t>
+    <t xml:space="preserve">16.9559230804443</t>
   </si>
   <si>
     <t xml:space="preserve">17.4115562438965</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0454235076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0787258148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6475048065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0217704772949</t>
+    <t xml:space="preserve">17.0454216003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0787239074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6475067138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0217723846436</t>
   </si>
   <si>
     <t xml:space="preserve">18.0543174743652</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1275463104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2984027862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4123096466064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1682224273682</t>
+    <t xml:space="preserve">18.1275424957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2984008789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4123134613037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1682243347168</t>
   </si>
   <si>
     <t xml:space="preserve">18.1600856781006</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9159984588623</t>
+    <t xml:space="preserve">17.9160003662109</t>
   </si>
   <si>
     <t xml:space="preserve">17.265100479126</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0861053466797</t>
+    <t xml:space="preserve">17.0861034393311</t>
   </si>
   <si>
     <t xml:space="preserve">17.2976474761963</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0047397613525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1267833709717</t>
+    <t xml:space="preserve">17.0047416687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1267871856689</t>
   </si>
   <si>
     <t xml:space="preserve">16.8745613098145</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0779685974121</t>
+    <t xml:space="preserve">17.0779666900635</t>
   </si>
   <si>
     <t xml:space="preserve">16.8664245605469</t>
@@ -1037,10 +1037,10 @@
     <t xml:space="preserve">16.785062789917</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9884662628174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5979270935059</t>
+    <t xml:space="preserve">16.988468170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5979328155518</t>
   </si>
   <si>
     <t xml:space="preserve">16.9152450561523</t>
@@ -1052,37 +1052,37 @@
     <t xml:space="preserve">16.9640598297119</t>
   </si>
   <si>
-    <t xml:space="preserve">16.882698059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9233798980713</t>
+    <t xml:space="preserve">16.8826999664307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9233779907227</t>
   </si>
   <si>
     <t xml:space="preserve">17.1349220275879</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0698318481445</t>
+    <t xml:space="preserve">17.0698299407959</t>
   </si>
   <si>
     <t xml:space="preserve">17.1674671173096</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6637783050537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2251758575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.859806060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.06321144104</t>
+    <t xml:space="preserve">17.6637744903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2251777648926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8598022460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0632095336914</t>
   </si>
   <si>
     <t xml:space="preserve">18.7052173614502</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6319885253906</t>
+    <t xml:space="preserve">18.6319904327393</t>
   </si>
   <si>
     <t xml:space="preserve">18.7377624511719</t>
@@ -1094,28 +1094,28 @@
     <t xml:space="preserve">18.59130859375</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3065376281738</t>
+    <t xml:space="preserve">18.3065414428711</t>
   </si>
   <si>
     <t xml:space="preserve">18.6157169342041</t>
   </si>
   <si>
-    <t xml:space="preserve">18.217041015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2089042663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4611301422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5417346954346</t>
+    <t xml:space="preserve">18.2170391082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2089061737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4611263275146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5417327880859</t>
   </si>
   <si>
     <t xml:space="preserve">16.9071063995361</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4758834838867</t>
+    <t xml:space="preserve">16.4758853912354</t>
   </si>
   <si>
     <t xml:space="preserve">16.3945217132568</t>
@@ -1124,7 +1124,7 @@
     <t xml:space="preserve">16.1097545623779</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3619785308838</t>
+    <t xml:space="preserve">16.3619804382324</t>
   </si>
   <si>
     <t xml:space="preserve">16.2806148529053</t>
@@ -1133,13 +1133,13 @@
     <t xml:space="preserve">16.3782520294189</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1992530822754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2236652374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2724781036377</t>
+    <t xml:space="preserve">16.199254989624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2236633300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2724800109863</t>
   </si>
   <si>
     <t xml:space="preserve">16.679292678833</t>
@@ -1151,13 +1151,13 @@
     <t xml:space="preserve">16.09348487854</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9470300674438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1911182403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3538436889648</t>
+    <t xml:space="preserve">15.9470310211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1911163330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3538455963135</t>
   </si>
   <si>
     <t xml:space="preserve">16.028392791748</t>
@@ -1166,34 +1166,34 @@
     <t xml:space="preserve">15.9144859313965</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1822242736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9706811904907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1008615493774</t>
+    <t xml:space="preserve">15.182222366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9706802368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1008605957031</t>
   </si>
   <si>
     <t xml:space="preserve">14.873046875</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2221479415894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.84787940979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8893184661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1984958648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3937654495239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5402193069458</t>
+    <t xml:space="preserve">14.222146987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8478813171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8893194198608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1984968185425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3937673568726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5402183532715</t>
   </si>
   <si>
     <t xml:space="preserve">14.938136100769</t>
@@ -1202,7 +1202,7 @@
     <t xml:space="preserve">14.59641456604</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4011449813843</t>
+    <t xml:space="preserve">14.4011459350586</t>
   </si>
   <si>
     <t xml:space="preserve">14.2058734893799</t>
@@ -1211,103 +1211,103 @@
     <t xml:space="preserve">14.1082401275635</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0594244003296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9129695892334</t>
+    <t xml:space="preserve">14.059422492981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9129705429077</t>
   </si>
   <si>
     <t xml:space="preserve">14.0106048583984</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3197832107544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6452331542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7428674697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7265939712524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2147703170776</t>
+    <t xml:space="preserve">14.3197822570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6452312469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7428703308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7265958786011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.214768409729</t>
   </si>
   <si>
     <t xml:space="preserve">14.8079586029053</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8567752838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9544067382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7916841506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2709655761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.003228187561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4825057983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9218664169312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.905590057373</t>
+    <t xml:space="preserve">14.8567733764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9544076919556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7916831970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2709646224976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0032272338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4825067520142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9218626022339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9055919647217</t>
   </si>
   <si>
     <t xml:space="preserve">15.0194988250732</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0520448684692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2562065124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7354879379272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8168497085571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6215791702271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.930757522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6866703033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7192163467407</t>
+    <t xml:space="preserve">15.0520458221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2562084197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7354888916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8168487548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6215829849243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9307584762573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6866731643677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7192182540894</t>
   </si>
   <si>
     <t xml:space="preserve">15.7029418945312</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6704006195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6053085327148</t>
+    <t xml:space="preserve">15.6703987121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6053094863892</t>
   </si>
   <si>
     <t xml:space="preserve">15.5653514862061</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9956827163696</t>
+    <t xml:space="preserve">14.9956817626953</t>
   </si>
   <si>
     <t xml:space="preserve">15.0291919708252</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0627031326294</t>
+    <t xml:space="preserve">15.0627021789551</t>
   </si>
   <si>
     <t xml:space="preserve">15.2470083236694</t>
@@ -1322,31 +1322,31 @@
     <t xml:space="preserve">15.7161464691162</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8669404983521</t>
+    <t xml:space="preserve">15.8669385910034</t>
   </si>
   <si>
     <t xml:space="preserve">15.5821084976196</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4983320236206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.481575012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4145565032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1799879074097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0794591903687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1129693984985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3589944839478</t>
+    <t xml:space="preserve">15.4983339309692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4815740585327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4145555496216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1799898147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0794582366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1129674911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3589954376221</t>
   </si>
   <si>
     <t xml:space="preserve">14.291974067688</t>
@@ -1361,7 +1361,7 @@
     <t xml:space="preserve">14.4092607498169</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5600519180298</t>
+    <t xml:space="preserve">14.5600538253784</t>
   </si>
   <si>
     <t xml:space="preserve">13.4039621353149</t>
@@ -1373,7 +1373,7 @@
     <t xml:space="preserve">13.2364139556885</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5380020141602</t>
+    <t xml:space="preserve">13.5380010604858</t>
   </si>
   <si>
     <t xml:space="preserve">13.4374732971191</t>
@@ -1385,19 +1385,19 @@
     <t xml:space="preserve">13.5882663726807</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6887950897217</t>
+    <t xml:space="preserve">13.6887969970703</t>
   </si>
   <si>
     <t xml:space="preserve">13.4207172393799</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5212459564209</t>
+    <t xml:space="preserve">13.5212469100952</t>
   </si>
   <si>
     <t xml:space="preserve">13.5715112686157</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3201875686646</t>
+    <t xml:space="preserve">13.3201866149902</t>
   </si>
   <si>
     <t xml:space="preserve">13.1526384353638</t>
@@ -1409,28 +1409,28 @@
     <t xml:space="preserve">13.2196578979492</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3034324645996</t>
+    <t xml:space="preserve">13.3034334182739</t>
   </si>
   <si>
     <t xml:space="preserve">12.8510494232178</t>
   </si>
   <si>
-    <t xml:space="preserve">12.683500289917</t>
+    <t xml:space="preserve">12.6834983825684</t>
   </si>
   <si>
     <t xml:space="preserve">12.5662145614624</t>
   </si>
   <si>
-    <t xml:space="preserve">12.901312828064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8342933654785</t>
+    <t xml:space="preserve">12.9013137817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8342943191528</t>
   </si>
   <si>
     <t xml:space="preserve">12.4824390411377</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1473407745361</t>
+    <t xml:space="preserve">12.1473398208618</t>
   </si>
   <si>
     <t xml:space="preserve">12.0803213119507</t>
@@ -1439,49 +1439,49 @@
     <t xml:space="preserve">12.0635662078857</t>
   </si>
   <si>
-    <t xml:space="preserve">11.979790687561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5609169006348</t>
+    <t xml:space="preserve">11.9797916412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5609178543091</t>
   </si>
   <si>
     <t xml:space="preserve">11.1923084259033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2258186340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4321756362915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1191272735596</t>
+    <t xml:space="preserve">11.2258176803589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4321737289429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1191282272339</t>
   </si>
   <si>
     <t xml:space="preserve">13.2531661987305</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2866773605347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7672739028931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3536968231201</t>
+    <t xml:space="preserve">13.286675453186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7672748565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3536958694458</t>
   </si>
   <si>
     <t xml:space="preserve">12.9850883483887</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8007841110229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6332340240479</t>
+    <t xml:space="preserve">12.8007831573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6332349777222</t>
   </si>
   <si>
     <t xml:space="preserve">12.8678035736084</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8122425079346</t>
+    <t xml:space="preserve">11.8122415542603</t>
   </si>
   <si>
     <t xml:space="preserve">11.6279373168945</t>
@@ -1499,7 +1499,7 @@
     <t xml:space="preserve">11.8960161209106</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6614465713501</t>
+    <t xml:space="preserve">11.6614475250244</t>
   </si>
   <si>
     <t xml:space="preserve">11.075023651123</t>
@@ -1508,28 +1508,28 @@
     <t xml:space="preserve">11.0415143966675</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9577398300171</t>
+    <t xml:space="preserve">10.9577388763428</t>
   </si>
   <si>
     <t xml:space="preserve">10.7566795349121</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9242286682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.974494934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7117128372192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3651552200317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4603881835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1587972640991</t>
+    <t xml:space="preserve">10.9242296218872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9744939804077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7117118835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3651561737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4603872299194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1587982177734</t>
   </si>
   <si>
     <t xml:space="preserve">11.1252889633179</t>
@@ -1538,7 +1538,7 @@
     <t xml:space="preserve">11.1755542755127</t>
   </si>
   <si>
-    <t xml:space="preserve">11.376612663269</t>
+    <t xml:space="preserve">11.3766136169434</t>
   </si>
   <si>
     <t xml:space="preserve">12.2311162948608</t>
@@ -1550,7 +1550,7 @@
     <t xml:space="preserve">11.9295253753662</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7954864501953</t>
+    <t xml:space="preserve">11.7954874038696</t>
   </si>
   <si>
     <t xml:space="preserve">11.87926197052</t>
@@ -1562,13 +1562,13 @@
     <t xml:space="preserve">12.2478694915771</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0132999420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1305847167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1808500289917</t>
+    <t xml:space="preserve">12.0133008956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1305856704712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1808490753174</t>
   </si>
   <si>
     <t xml:space="preserve">12.3819103240967</t>
@@ -1577,10 +1577,10 @@
     <t xml:space="preserve">12.3316450119019</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4656858444214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.599723815918</t>
+    <t xml:space="preserve">12.4656848907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5997247695923</t>
   </si>
   <si>
     <t xml:space="preserve">12.7170076370239</t>
@@ -1589,10 +1589,10 @@
     <t xml:space="preserve">12.8845586776733</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9515771865845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9683332443237</t>
+    <t xml:space="preserve">12.9515781402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9683322906494</t>
   </si>
   <si>
     <t xml:space="preserve">13.2029027938843</t>
@@ -1601,10 +1601,10 @@
     <t xml:space="preserve">12.7337646484375</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8175382614136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6499891281128</t>
+    <t xml:space="preserve">12.8175373077393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6499900817871</t>
   </si>
   <si>
     <t xml:space="preserve">12.7002544403076</t>
@@ -1616,22 +1616,22 @@
     <t xml:space="preserve">12.7840280532837</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0018444061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0353546142578</t>
+    <t xml:space="preserve">13.0018434524536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0353527069092</t>
   </si>
   <si>
     <t xml:space="preserve">12.5494585037231</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9348230361938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9180698394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.38720703125</t>
+    <t xml:space="preserve">12.9348239898682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9180679321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3872060775757</t>
   </si>
   <si>
     <t xml:space="preserve">13.6217775344849</t>
@@ -1643,7 +1643,7 @@
     <t xml:space="preserve">13.5044937133789</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4542255401611</t>
+    <t xml:space="preserve">13.4542264938354</t>
   </si>
   <si>
     <t xml:space="preserve">13.6385316848755</t>
@@ -1658,16 +1658,16 @@
     <t xml:space="preserve">13.0521078109741</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0185976028442</t>
+    <t xml:space="preserve">13.0185985565186</t>
   </si>
   <si>
     <t xml:space="preserve">13.1693925857544</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1023740768433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.499195098877</t>
+    <t xml:space="preserve">13.1023721694946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4991941452026</t>
   </si>
   <si>
     <t xml:space="preserve">12.7481775283813</t>
@@ -1682,13 +1682,13 @@
     <t xml:space="preserve">12.2257108688354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2779579162598</t>
+    <t xml:space="preserve">12.2779569625854</t>
   </si>
   <si>
     <t xml:space="preserve">12.3127889633179</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2953729629517</t>
+    <t xml:space="preserve">12.295373916626</t>
   </si>
   <si>
     <t xml:space="preserve">12.3302030563354</t>
@@ -1703,7 +1703,7 @@
     <t xml:space="preserve">12.4869432449341</t>
   </si>
   <si>
-    <t xml:space="preserve">12.452112197876</t>
+    <t xml:space="preserve">12.4521131515503</t>
   </si>
   <si>
     <t xml:space="preserve">12.138632774353</t>
@@ -1712,7 +1712,7 @@
     <t xml:space="preserve">12.0515556335449</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8948154449463</t>
+    <t xml:space="preserve">11.8948163986206</t>
   </si>
   <si>
     <t xml:space="preserve">12.2082958221436</t>
@@ -1721,7 +1721,7 @@
     <t xml:space="preserve">12.8178396224976</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7655916213989</t>
+    <t xml:space="preserve">12.7655925750732</t>
   </si>
   <si>
     <t xml:space="preserve">12.6436834335327</t>
@@ -1739,22 +1739,22 @@
     <t xml:space="preserve">12.8700866699219</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9745779037476</t>
+    <t xml:space="preserve">12.9745788574219</t>
   </si>
   <si>
     <t xml:space="preserve">12.95716381073</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9397478103638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7830085754395</t>
+    <t xml:space="preserve">12.9397468566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7830076217651</t>
   </si>
   <si>
     <t xml:space="preserve">12.6959295272827</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8004236221313</t>
+    <t xml:space="preserve">12.800422668457</t>
   </si>
   <si>
     <t xml:space="preserve">12.8875007629395</t>
@@ -1766,13 +1766,13 @@
     <t xml:space="preserve">12.0341396331787</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7206592559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2431259155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7554922103882</t>
+    <t xml:space="preserve">11.7206583023071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2431268692017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7554912567139</t>
   </si>
   <si>
     <t xml:space="preserve">11.6684122085571</t>
@@ -1781,10 +1781,10 @@
     <t xml:space="preserve">11.9993076324463</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0689706802368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1038007736206</t>
+    <t xml:space="preserve">12.0689697265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1038017272949</t>
   </si>
   <si>
     <t xml:space="preserve">11.790322303772</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">11.9470624923706</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8251533508301</t>
+    <t xml:space="preserve">11.8251523971558</t>
   </si>
   <si>
     <t xml:space="preserve">11.8599834442139</t>
@@ -1820,10 +1820,10 @@
     <t xml:space="preserve">11.2156095504761</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4071807861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3026866912842</t>
+    <t xml:space="preserve">11.4071798324585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3026857376099</t>
   </si>
   <si>
     <t xml:space="preserve">11.3549337387085</t>
@@ -1832,7 +1832,7 @@
     <t xml:space="preserve">11.3897638320923</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1981925964355</t>
+    <t xml:space="preserve">11.1981916427612</t>
   </si>
   <si>
     <t xml:space="preserve">10.9369602203369</t>
@@ -1841,13 +1841,13 @@
     <t xml:space="preserve">11.0414543151855</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8847150802612</t>
+    <t xml:space="preserve">10.8847141265869</t>
   </si>
   <si>
     <t xml:space="preserve">10.8672971725464</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9717931747437</t>
+    <t xml:space="preserve">10.9717922210693</t>
   </si>
   <si>
     <t xml:space="preserve">10.8324670791626</t>
@@ -1859,13 +1859,13 @@
     <t xml:space="preserve">10.6060657501221</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5886487960815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5189867019653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4493265151978</t>
+    <t xml:space="preserve">10.5886497497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5189876556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4493255615234</t>
   </si>
   <si>
     <t xml:space="preserve">10.6583108901978</t>
@@ -1877,16 +1877,16 @@
     <t xml:space="preserve">11.1633634567261</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1111154556274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0588684082031</t>
+    <t xml:space="preserve">11.1111164093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0588693618774</t>
   </si>
   <si>
     <t xml:space="preserve">10.9892063140869</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8498830795288</t>
+    <t xml:space="preserve">10.8498840332031</t>
   </si>
   <si>
     <t xml:space="preserve">11.0240383148193</t>
@@ -1895,22 +1895,22 @@
     <t xml:space="preserve">11.0066232681274</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7976350784302</t>
+    <t xml:space="preserve">10.7976360321045</t>
   </si>
   <si>
     <t xml:space="preserve">10.8150520324707</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9543752670288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0937013626099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7032432556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9818925857544</t>
+    <t xml:space="preserve">10.9543762207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0937004089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7032442092896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9818935394287</t>
   </si>
   <si>
     <t xml:space="preserve">11.9296464920044</t>
@@ -1934,10 +1934,10 @@
     <t xml:space="preserve">11.529088973999</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4942588806152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.581335067749</t>
+    <t xml:space="preserve">11.4942579269409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5813360214233</t>
   </si>
   <si>
     <t xml:space="preserve">11.476842880249</t>
@@ -1961,19 +1961,19 @@
     <t xml:space="preserve">10.7105588912964</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70045852661133</t>
+    <t xml:space="preserve">9.70045757293701</t>
   </si>
   <si>
     <t xml:space="preserve">9.49146938323975</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03866672515869</t>
+    <t xml:space="preserve">9.03866577148438</t>
   </si>
   <si>
     <t xml:space="preserve">8.98641967773438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42912101745605</t>
+    <t xml:space="preserve">8.42912197113037</t>
   </si>
   <si>
     <t xml:space="preserve">8.18530464172363</t>
@@ -1988,10 +1988,10 @@
     <t xml:space="preserve">8.533616065979</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49007606506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31592273712158</t>
+    <t xml:space="preserve">8.49007701873779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31592178344727</t>
   </si>
   <si>
     <t xml:space="preserve">8.32463073730469</t>
@@ -2006,19 +2006,19 @@
     <t xml:space="preserve">8.28979778289795</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41170692443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49878406524658</t>
+    <t xml:space="preserve">8.41170597076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4987850189209</t>
   </si>
   <si>
     <t xml:space="preserve">8.63810920715332</t>
   </si>
   <si>
-    <t xml:space="preserve">8.690354347229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67294025421143</t>
+    <t xml:space="preserve">8.69035530090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67293930053711</t>
   </si>
   <si>
     <t xml:space="preserve">8.79484939575195</t>
@@ -2030,7 +2030,7 @@
     <t xml:space="preserve">8.75131034851074</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70777130126953</t>
+    <t xml:space="preserve">8.70777225494385</t>
   </si>
   <si>
     <t xml:space="preserve">8.83838844299316</t>
@@ -2048,13 +2048,13 @@
     <t xml:space="preserve">9.23023796081543</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40439224243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66562652587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57854843139648</t>
+    <t xml:space="preserve">9.40439319610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66562747955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57854747772217</t>
   </si>
   <si>
     <t xml:space="preserve">9.31731510162354</t>
@@ -2066,7 +2066,7 @@
     <t xml:space="preserve">8.65552425384521</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51620006561279</t>
+    <t xml:space="preserve">8.51619911193848</t>
   </si>
   <si>
     <t xml:space="preserve">8.60327816009521</t>
@@ -2081,7 +2081,7 @@
     <t xml:space="preserve">9.83978176116943</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0139360427856</t>
+    <t xml:space="preserve">10.0139350891113</t>
   </si>
   <si>
     <t xml:space="preserve">10.1010150909424</t>
@@ -2111,10 +2111,10 @@
     <t xml:space="preserve">9.53500938415527</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79624271392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1880922317505</t>
+    <t xml:space="preserve">9.79624176025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1880931854248</t>
   </si>
   <si>
     <t xml:space="preserve">10.2751693725586</t>
@@ -2126,13 +2126,13 @@
     <t xml:space="preserve">10.9282522201538</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0153293609619</t>
+    <t xml:space="preserve">11.0153303146362</t>
   </si>
   <si>
     <t xml:space="preserve">10.7540979385376</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4928646087646</t>
+    <t xml:space="preserve">10.492865562439</t>
   </si>
   <si>
     <t xml:space="preserve">10.4057855606079</t>
@@ -2141,13 +2141,13 @@
     <t xml:space="preserve">10.362247467041</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3187093734741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1894865036011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2765626907349</t>
+    <t xml:space="preserve">10.3187084197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1894855499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2765636444092</t>
   </si>
   <si>
     <t xml:space="preserve">11.4507179260254</t>
@@ -2174,7 +2174,7 @@
     <t xml:space="preserve">11.4743099212646</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2064275741577</t>
+    <t xml:space="preserve">11.2064266204834</t>
   </si>
   <si>
     <t xml:space="preserve">11.4296617507935</t>
@@ -2189,13 +2189,13 @@
     <t xml:space="preserve">10.5813665390015</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5367193222046</t>
+    <t xml:space="preserve">10.5367202758789</t>
   </si>
   <si>
     <t xml:space="preserve">11.0278387069702</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8938970565796</t>
+    <t xml:space="preserve">10.8938980102539</t>
   </si>
   <si>
     <t xml:space="preserve">11.1617794036865</t>
@@ -2204,10 +2204,10 @@
     <t xml:space="preserve">11.0724849700928</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9207820892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.188663482666</t>
+    <t xml:space="preserve">11.9207811355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1886625289917</t>
   </si>
   <si>
     <t xml:space="preserve">12.2333106994629</t>
@@ -2231,25 +2231,25 @@
     <t xml:space="preserve">13.4387826919556</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4834289550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9299011230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8406057357788</t>
+    <t xml:space="preserve">13.4834299087524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9299020767212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8406066894531</t>
   </si>
   <si>
     <t xml:space="preserve">14.0191946029663</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9030179977417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0816059112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.036958694458</t>
+    <t xml:space="preserve">12.9030170440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0816049575806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0369577407837</t>
   </si>
   <si>
     <t xml:space="preserve">13.7513122558594</t>
@@ -2294,19 +2294,19 @@
     <t xml:space="preserve">14.4210195541382</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5103130340576</t>
+    <t xml:space="preserve">14.5103120803833</t>
   </si>
   <si>
     <t xml:space="preserve">15.1800203323364</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8497285842896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8050813674927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.072961807251</t>
+    <t xml:space="preserve">15.8497276306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.805079460144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0729637145996</t>
   </si>
   <si>
     <t xml:space="preserve">16.3854923248291</t>
@@ -2315,16 +2315,16 @@
     <t xml:space="preserve">16.921257019043</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1891403198242</t>
+    <t xml:space="preserve">17.1891422271729</t>
   </si>
   <si>
     <t xml:space="preserve">16.7426700592041</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7249050140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7695541381836</t>
+    <t xml:space="preserve">17.7249069213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.769552230835</t>
   </si>
   <si>
     <t xml:space="preserve">17.8142013549805</t>
@@ -2357,13 +2357,13 @@
     <t xml:space="preserve">18.2160243988037</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9481430053711</t>
+    <t xml:space="preserve">17.9481410980225</t>
   </si>
   <si>
     <t xml:space="preserve">19.0196723937988</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1804981231689</t>
+    <t xml:space="preserve">20.1804962158203</t>
   </si>
   <si>
     <t xml:space="preserve">20.5376739501953</t>
@@ -2378,10 +2378,10 @@
     <t xml:space="preserve">20.8055572509766</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0734386444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0912055969238</t>
+    <t xml:space="preserve">21.0734405517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0912036895752</t>
   </si>
   <si>
     <t xml:space="preserve">20.0019092559814</t>
@@ -2390,16 +2390,16 @@
     <t xml:space="preserve">19.8233203887939</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2697944641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1982612609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9126148223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5554389953613</t>
+    <t xml:space="preserve">20.2697925567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1982593536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9126129150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5554370880127</t>
   </si>
   <si>
     <t xml:space="preserve">19.6447315216064</t>
@@ -2411,7 +2411,7 @@
     <t xml:space="preserve">20.7162628173828</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4483814239502</t>
+    <t xml:space="preserve">20.4483795166016</t>
   </si>
   <si>
     <t xml:space="preserve">21.4306163787842</t>
@@ -2429,7 +2429,7 @@
     <t xml:space="preserve">22.0556774139404</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7877941131592</t>
+    <t xml:space="preserve">21.7877960205078</t>
   </si>
   <si>
     <t xml:space="preserve">22.7700309753418</t>
@@ -71889,6 +71889,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2605">
+      <c r="A2605" s="1" t="n">
+        <v>46113.2916666667</v>
+      </c>
+      <c r="B2605" t="n">
+        <v>10269</v>
+      </c>
+      <c r="C2605" t="n">
+        <v>14.1499996185303</v>
+      </c>
+      <c r="D2605" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="E2605" t="n">
+        <v>14.1499996185303</v>
+      </c>
+      <c r="F2605" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="G2605" t="s">
+        <v>1260</v>
+      </c>
+      <c r="H2605" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SAB.MI.xlsx
+++ b/data/SAB.MI.xlsx
@@ -38,22 +38,22 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5656795501709</t>
+    <t xml:space="preserve">8.56568050384521</t>
   </si>
   <si>
     <t xml:space="preserve">SAB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61823081970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4831018447876</t>
+    <t xml:space="preserve">8.61822891235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48310279846191</t>
   </si>
   <si>
     <t xml:space="preserve">8.33295822143555</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37049388885498</t>
+    <t xml:space="preserve">8.3704948425293</t>
   </si>
   <si>
     <t xml:space="preserve">8.31794452667236</t>
@@ -62,40 +62,40 @@
     <t xml:space="preserve">8.25788688659668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16029453277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88252830505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52969169616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66482067108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62728452682495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61226987838745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73989200592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75490760803223</t>
+    <t xml:space="preserve">8.16029357910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88252735137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52969121932983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66481971740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62728548049927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61227130889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73989295959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75490665435791</t>
   </si>
   <si>
     <t xml:space="preserve">7.76992177963257</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89754390716553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6197772026062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79994869232178</t>
+    <t xml:space="preserve">7.89754199981689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61977624893188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79994964599609</t>
   </si>
   <si>
     <t xml:space="preserve">7.72487878799438</t>
@@ -107,70 +107,70 @@
     <t xml:space="preserve">7.50716972351074</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34201240539551</t>
+    <t xml:space="preserve">7.34201192855835</t>
   </si>
   <si>
     <t xml:space="preserve">7.54470539093018</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39080858230591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58224296569824</t>
+    <t xml:space="preserve">7.39080905914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58224201202393</t>
   </si>
   <si>
     <t xml:space="preserve">7.82247066497803</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08522129058838</t>
+    <t xml:space="preserve">8.0852222442627</t>
   </si>
   <si>
     <t xml:space="preserve">8.1152515411377</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95760107040405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06270027160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03267192840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92006397247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77742767333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86751317977905</t>
+    <t xml:space="preserve">7.95760011672974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06269931793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03267002105713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92006349563599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.777428150177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86751365661621</t>
   </si>
   <si>
     <t xml:space="preserve">7.80745553970337</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98762893676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0401782989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99513578414917</t>
+    <t xml:space="preserve">7.98762845993042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04018020629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99513626098633</t>
   </si>
   <si>
     <t xml:space="preserve">7.96510601043701</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90505027770996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9350790977478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89003419876099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94258499145508</t>
+    <t xml:space="preserve">7.9050498008728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93507766723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89003610610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94258451461792</t>
   </si>
   <si>
     <t xml:space="preserve">7.82997751235962</t>
@@ -179,31 +179,31 @@
     <t xml:space="preserve">7.81496334075928</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73238563537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64980459213257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71737098693848</t>
+    <t xml:space="preserve">7.73238468170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64980697631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71737194061279</t>
   </si>
   <si>
     <t xml:space="preserve">7.67232799530029</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63479280471802</t>
+    <t xml:space="preserve">7.63479232788086</t>
   </si>
   <si>
     <t xml:space="preserve">7.51467800140381</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64229869842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56722688674927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70235586166382</t>
+    <t xml:space="preserve">7.64229822158813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56722640991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70235681533813</t>
   </si>
   <si>
     <t xml:space="preserve">7.747398853302</t>
@@ -212,19 +212,19 @@
     <t xml:space="preserve">7.46963357925415</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69484901428223</t>
+    <t xml:space="preserve">7.69484996795654</t>
   </si>
   <si>
     <t xml:space="preserve">7.4921555519104</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47338676452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43585157394409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50341510772705</t>
+    <t xml:space="preserve">7.47338724136353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43585205078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50341558456421</t>
   </si>
   <si>
     <t xml:space="preserve">7.48089456558228</t>
@@ -233,70 +233,70 @@
     <t xml:space="preserve">7.59725522994995</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42834520339966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38705635070801</t>
+    <t xml:space="preserve">7.4283447265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38705539703369</t>
   </si>
   <si>
     <t xml:space="preserve">7.37204027175903</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31949043273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28195333480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52122211456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80533885955811</t>
+    <t xml:space="preserve">7.31949090957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28195428848267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52122163772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80533933639526</t>
   </si>
   <si>
     <t xml:space="preserve">7.75009346008301</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75798749923706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81323051452637</t>
+    <t xml:space="preserve">7.75798559188843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81323099136353</t>
   </si>
   <si>
     <t xml:space="preserve">7.8605842590332</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69879531860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58435916900635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68695640563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57646703720093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53700590133667</t>
+    <t xml:space="preserve">7.6987943649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58435869216919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68695735931396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57646799087524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53700685501099</t>
   </si>
   <si>
     <t xml:space="preserve">7.49754524230957</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28445672988892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92536306381226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07926177978516</t>
+    <t xml:space="preserve">7.28445768356323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92536354064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07926082611084</t>
   </si>
   <si>
     <t xml:space="preserve">7.22921180725098</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45808458328247</t>
+    <t xml:space="preserve">7.45808362960815</t>
   </si>
   <si>
     <t xml:space="preserve">7.26078033447266</t>
@@ -305,13 +305,13 @@
     <t xml:space="preserve">7.37127113342285</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2647271156311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34759569168091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46992254257202</t>
+    <t xml:space="preserve">7.26472663879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34759473800659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46992206573486</t>
   </si>
   <si>
     <t xml:space="preserve">7.36732482910156</t>
@@ -320,19 +320,19 @@
     <t xml:space="preserve">7.37916326522827</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13450622558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18975162506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10293912887573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15029096603394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10688447952271</t>
+    <t xml:space="preserve">7.1345067024231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18975210189819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10293769836426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15029144287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10688352584839</t>
   </si>
   <si>
     <t xml:space="preserve">7.20553588867188</t>
@@ -341,88 +341,88 @@
     <t xml:space="preserve">7.18185949325562</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22132062911987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19369697570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24894237518311</t>
+    <t xml:space="preserve">7.22132015228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19369745254517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24894332885742</t>
   </si>
   <si>
     <t xml:space="preserve">7.19764375686646</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18580484390259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22526597976685</t>
+    <t xml:space="preserve">7.18580436706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22526550292969</t>
   </si>
   <si>
     <t xml:space="preserve">7.20948123931885</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31602573394775</t>
+    <t xml:space="preserve">7.31602621078491</t>
   </si>
   <si>
     <t xml:space="preserve">7.21342754364014</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16607427597046</t>
+    <t xml:space="preserve">7.16607475280762</t>
   </si>
   <si>
     <t xml:space="preserve">7.24499607086182</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13056039810181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11082887649536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17791318893433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23315954208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27656507492065</t>
+    <t xml:space="preserve">7.13055992126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11083030700684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17791366577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23315906524658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27656555175781</t>
   </si>
   <si>
     <t xml:space="preserve">7.30024194717407</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29234933853149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24105024337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11872148513794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09504556655884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00428628921509</t>
+    <t xml:space="preserve">7.29234886169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24105072021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1187219619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.095046043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00428485870361</t>
   </si>
   <si>
     <t xml:space="preserve">6.9450945854187</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93325662612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09899139404297</t>
+    <t xml:space="preserve">6.93325614929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09899091720581</t>
   </si>
   <si>
     <t xml:space="preserve">7.15423631668091</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13845252990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1581826210022</t>
+    <t xml:space="preserve">7.13845205307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15818214416504</t>
   </si>
   <si>
     <t xml:space="preserve">7.05558490753174</t>
@@ -431,34 +431,34 @@
     <t xml:space="preserve">7.07136869430542</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06742238998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02401542663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04769325256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06347608566284</t>
+    <t xml:space="preserve">7.06742334365845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0240159034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04769229888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06347560882568</t>
   </si>
   <si>
     <t xml:space="preserve">7.08320713043213</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05163908004761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04374647140503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03190803527832</t>
+    <t xml:space="preserve">7.05163955688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04374694824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03190755844116</t>
   </si>
   <si>
     <t xml:space="preserve">7.05953073501587</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03585481643677</t>
+    <t xml:space="preserve">7.03585386276245</t>
   </si>
   <si>
     <t xml:space="preserve">7.17396640777588</t>
@@ -467,31 +467,31 @@
     <t xml:space="preserve">6.9056339263916</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91352653503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93720293045044</t>
+    <t xml:space="preserve">6.91352701187134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93720197677612</t>
   </si>
   <si>
     <t xml:space="preserve">6.9214186668396</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94114875793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96877002716064</t>
+    <t xml:space="preserve">6.94114923477173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96877145767212</t>
   </si>
   <si>
     <t xml:space="preserve">7.14239835739136</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45019102096558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79350137710571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92372226715088</t>
+    <t xml:space="preserve">7.45019197463989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79350090026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9237208366394</t>
   </si>
   <si>
     <t xml:space="preserve">8.0499963760376</t>
@@ -506,7 +506,7 @@
     <t xml:space="preserve">8.08945655822754</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1999454498291</t>
+    <t xml:space="preserve">8.19994640350342</t>
   </si>
   <si>
     <t xml:space="preserve">8.06578063964844</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">8.56298637390137</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42881965637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35779094696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39725017547607</t>
+    <t xml:space="preserve">8.42881870269775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35778999328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39725112915039</t>
   </si>
   <si>
     <t xml:space="preserve">8.42092704772949</t>
@@ -542,19 +542,19 @@
     <t xml:space="preserve">8.44460391998291</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40514278411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26308441162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18416309356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30254650115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22362232208252</t>
+    <t xml:space="preserve">8.40514183044434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26308536529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18416404724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30254554748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22362327575684</t>
   </si>
   <si>
     <t xml:space="preserve">8.2867603302002</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">8.34989738464355</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31043720245361</t>
+    <t xml:space="preserve">8.3104362487793</t>
   </si>
   <si>
     <t xml:space="preserve">8.36568260192871</t>
@@ -575,49 +575,49 @@
     <t xml:space="preserve">8.33411407470703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34200572967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46038722991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62612247467041</t>
+    <t xml:space="preserve">8.34200668334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46038913726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62612342834473</t>
   </si>
   <si>
     <t xml:space="preserve">8.74450588226318</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88656425476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00494480133057</t>
+    <t xml:space="preserve">8.88656330108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0049467086792</t>
   </si>
   <si>
     <t xml:space="preserve">9.23381805419922</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30484867095947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26538753509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1627893447876</t>
+    <t xml:space="preserve">9.30484771728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26538562774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16278839111328</t>
   </si>
   <si>
     <t xml:space="preserve">9.19435691833496</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24960422515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29695606231689</t>
+    <t xml:space="preserve">9.24960327148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29695510864258</t>
   </si>
   <si>
     <t xml:space="preserve">9.36798572540283</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54950523376465</t>
+    <t xml:space="preserve">9.54950428009033</t>
   </si>
   <si>
     <t xml:space="preserve">9.67578029632568</t>
@@ -629,25 +629,25 @@
     <t xml:space="preserve">10.2203388214111</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4807806015015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.457103729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2913675308228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2597990036011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1493072509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0861721038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0151414871216</t>
+    <t xml:space="preserve">10.4807786941528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4571018218994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2913684844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2597970962524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1493091583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0861711502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0151424407959</t>
   </si>
   <si>
     <t xml:space="preserve">10.1019563674927</t>
@@ -659,40 +659,40 @@
     <t xml:space="preserve">10.0546026229858</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1808767318726</t>
+    <t xml:space="preserve">10.1808786392212</t>
   </si>
   <si>
     <t xml:space="preserve">10.1177396774292</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1887702941895</t>
+    <t xml:space="preserve">10.1887693405151</t>
   </si>
   <si>
     <t xml:space="preserve">10.070387840271</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1098480224609</t>
+    <t xml:space="preserve">10.1098489761353</t>
   </si>
   <si>
     <t xml:space="preserve">10.0230340957642</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4965629577637</t>
+    <t xml:space="preserve">10.496563911438</t>
   </si>
   <si>
     <t xml:space="preserve">10.4176416397095</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3150453567505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7333288192749</t>
+    <t xml:space="preserve">10.3150424957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7333278656006</t>
   </si>
   <si>
     <t xml:space="preserve">10.4492092132568</t>
   </si>
   <si>
-    <t xml:space="preserve">10.559700012207</t>
+    <t xml:space="preserve">10.5597009658813</t>
   </si>
   <si>
     <t xml:space="preserve">10.6386213302612</t>
@@ -704,10 +704,10 @@
     <t xml:space="preserve">11.0095539093018</t>
   </si>
   <si>
-    <t xml:space="preserve">10.883279800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3410234451294</t>
+    <t xml:space="preserve">10.8832788467407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3410243988037</t>
   </si>
   <si>
     <t xml:space="preserve">12.0592098236084</t>
@@ -719,16 +719,16 @@
     <t xml:space="preserve">12.0513181686401</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6882791519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6803865432739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2644071578979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6274452209473</t>
+    <t xml:space="preserve">11.6882781982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6803855895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2644062042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6274442672729</t>
   </si>
   <si>
     <t xml:space="preserve">12.5406312942505</t>
@@ -737,13 +737,13 @@
     <t xml:space="preserve">12.6747970581055</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7379341125488</t>
+    <t xml:space="preserve">12.7379350662231</t>
   </si>
   <si>
     <t xml:space="preserve">12.4728565216064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6518526077271</t>
+    <t xml:space="preserve">12.6518535614014</t>
   </si>
   <si>
     <t xml:space="preserve">12.8471221923828</t>
@@ -752,22 +752,22 @@
     <t xml:space="preserve">12.8145780563354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9203500747681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8715314865112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9366216659546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8064413070679</t>
+    <t xml:space="preserve">12.9203481674194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8715324401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9366207122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8064422607422</t>
   </si>
   <si>
     <t xml:space="preserve">12.6437168121338</t>
   </si>
   <si>
-    <t xml:space="preserve">12.822714805603</t>
+    <t xml:space="preserve">12.8227138519287</t>
   </si>
   <si>
     <t xml:space="preserve">11.5209159851074</t>
@@ -776,13 +776,13 @@
     <t xml:space="preserve">11.8463659286499</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7812747955322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9114551544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9277286529541</t>
+    <t xml:space="preserve">11.7812757492065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9114561080933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9277267456055</t>
   </si>
   <si>
     <t xml:space="preserve">11.9602718353271</t>
@@ -794,19 +794,19 @@
     <t xml:space="preserve">12.1311340332031</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0009527206421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9846811294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0416355133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0823173522949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9765453338623</t>
+    <t xml:space="preserve">12.0009546279907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9846820831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.041633605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0823154449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9765462875366</t>
   </si>
   <si>
     <t xml:space="preserve">11.8789110183716</t>
@@ -815,43 +815,43 @@
     <t xml:space="preserve">11.7161855697632</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4720993041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5534591674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5860061645508</t>
+    <t xml:space="preserve">11.4720983505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5534610748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5860052108765</t>
   </si>
   <si>
     <t xml:space="preserve">11.7975473403931</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8951835632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0904521942139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1636791229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0741786956787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2287673950195</t>
+    <t xml:space="preserve">11.8951816558838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0904531478882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1636781692505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.074179649353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2287683486938</t>
   </si>
   <si>
     <t xml:space="preserve">12.1392707824707</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2043600082397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1880884170532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1474075317383</t>
+    <t xml:space="preserve">12.2043609619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1880874633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.147406578064</t>
   </si>
   <si>
     <t xml:space="preserve">12.2531776428223</t>
@@ -860,13 +860,13 @@
     <t xml:space="preserve">12.3670845031738</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4077653884888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.448447227478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9447584152222</t>
+    <t xml:space="preserve">12.4077644348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4484462738037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9447574615479</t>
   </si>
   <si>
     <t xml:space="preserve">12.7820320129395</t>
@@ -878,43 +878,43 @@
     <t xml:space="preserve">13.0098476409912</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9528932571411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8552589416504</t>
+    <t xml:space="preserve">12.9528942108154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8552598953247</t>
   </si>
   <si>
     <t xml:space="preserve">12.7332162857056</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7738952636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9854393005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2620706558228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.685154914856</t>
+    <t xml:space="preserve">12.7738962173462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9854383468628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2620697021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6851568222046</t>
   </si>
   <si>
     <t xml:space="preserve">13.9292421340942</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9943332672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7502460479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.815336227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8316078186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0187406539917</t>
+    <t xml:space="preserve">13.9943323135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7502450942993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8153352737427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8316087722778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.018741607666</t>
   </si>
   <si>
     <t xml:space="preserve">14.0268783569336</t>
@@ -926,40 +926,40 @@
     <t xml:space="preserve">14.1570568084717</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2302856445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7754106521606</t>
+    <t xml:space="preserve">14.2302837371826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.775411605835</t>
   </si>
   <si>
     <t xml:space="preserve">15.3205413818359</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2961311340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4588575363159</t>
+    <t xml:space="preserve">15.2961301803589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4588565826416</t>
   </si>
   <si>
     <t xml:space="preserve">15.824987411499</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7924423217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5076732635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8493947982788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8656673431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5158081054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0039825439453</t>
+    <t xml:space="preserve">15.7924451828003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5076723098755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8493957519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8656692504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5158090591431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0039844512939</t>
   </si>
   <si>
     <t xml:space="preserve">16.2643432617188</t>
@@ -971,16 +971,16 @@
     <t xml:space="preserve">16.9559230804443</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4115524291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0454216003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0787220001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6475028991699</t>
+    <t xml:space="preserve">17.4115543365479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0454235076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0787239074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6475048065186</t>
   </si>
   <si>
     <t xml:space="preserve">18.0217704772949</t>
@@ -989,19 +989,19 @@
     <t xml:space="preserve">18.0543174743652</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1275424957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2984046936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4123115539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1682205200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1600875854492</t>
+    <t xml:space="preserve">18.1275444030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2984027862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4123096466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1682224273682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1600856781006</t>
   </si>
   <si>
     <t xml:space="preserve">17.9160003662109</t>
@@ -1010,22 +1010,22 @@
     <t xml:space="preserve">17.265100479126</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0861053466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2976474761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0047397613525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1267833709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8745613098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0779666900635</t>
+    <t xml:space="preserve">17.0861034393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2976455688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0047416687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1267871856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8745632171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0779647827148</t>
   </si>
   <si>
     <t xml:space="preserve">16.8664245605469</t>
@@ -1034,7 +1034,7 @@
     <t xml:space="preserve">16.785062789917</t>
   </si>
   <si>
-    <t xml:space="preserve">16.988468170166</t>
+    <t xml:space="preserve">16.9884662628174</t>
   </si>
   <si>
     <t xml:space="preserve">16.5979309082031</t>
@@ -1043,43 +1043,43 @@
     <t xml:space="preserve">16.9152450561523</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8338813781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9640617370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8826961517334</t>
+    <t xml:space="preserve">16.8338794708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9640598297119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.882698059082</t>
   </si>
   <si>
     <t xml:space="preserve">16.9233779907227</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1349239349365</t>
+    <t xml:space="preserve">17.1349201202393</t>
   </si>
   <si>
     <t xml:space="preserve">17.0698318481445</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1674652099609</t>
+    <t xml:space="preserve">17.1674671173096</t>
   </si>
   <si>
     <t xml:space="preserve">17.6637763977051</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2251796722412</t>
+    <t xml:space="preserve">18.2251777648926</t>
   </si>
   <si>
     <t xml:space="preserve">18.8598041534424</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0632095336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7052135467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6319904327393</t>
+    <t xml:space="preserve">19.06321144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7052173614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.631986618042</t>
   </si>
   <si>
     <t xml:space="preserve">18.7377605438232</t>
@@ -1091,10 +1091,10 @@
     <t xml:space="preserve">18.59130859375</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3065395355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6157150268555</t>
+    <t xml:space="preserve">18.3065414428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6157169342041</t>
   </si>
   <si>
     <t xml:space="preserve">18.2170391082764</t>
@@ -1103,115 +1103,115 @@
     <t xml:space="preserve">18.2089042663574</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4611282348633</t>
+    <t xml:space="preserve">18.4611301422119</t>
   </si>
   <si>
     <t xml:space="preserve">17.5417327880859</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9071083068848</t>
+    <t xml:space="preserve">16.9071063995361</t>
   </si>
   <si>
     <t xml:space="preserve">16.4758853912354</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3945236206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1097526550293</t>
+    <t xml:space="preserve">16.3945217132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1097545623779</t>
   </si>
   <si>
     <t xml:space="preserve">16.3619785308838</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2806167602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3782501220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1992511749268</t>
+    <t xml:space="preserve">16.2806129455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3782520294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1992530822754</t>
   </si>
   <si>
     <t xml:space="preserve">16.2236633300781</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2724800109863</t>
+    <t xml:space="preserve">16.2724781036377</t>
   </si>
   <si>
     <t xml:space="preserve">16.6792907714844</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3131618499756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0934810638428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9470338821411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1911182403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3538398742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0283946990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9144859313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1822242736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9706802368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1008615493774</t>
+    <t xml:space="preserve">16.313159942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0934829711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9470300674438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1911163330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3538417816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.028392791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9144840240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1822214126587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9706811904907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1008605957031</t>
   </si>
   <si>
     <t xml:space="preserve">14.873046875</t>
   </si>
   <si>
-    <t xml:space="preserve">14.222146987915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8478803634644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8893184661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1984987258911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3937664031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5402173995972</t>
+    <t xml:space="preserve">14.2221479415894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8478813171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8893194198608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1984968185425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3937673568726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5402202606201</t>
   </si>
   <si>
     <t xml:space="preserve">14.9381351470947</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5964155197144</t>
+    <t xml:space="preserve">14.5964136123657</t>
   </si>
   <si>
     <t xml:space="preserve">14.4011449813843</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2058744430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1082382202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0594244003296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9129705429077</t>
+    <t xml:space="preserve">14.2058734893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1082401275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0594234466553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.912971496582</t>
   </si>
   <si>
     <t xml:space="preserve">14.0106058120728</t>
@@ -1220,31 +1220,31 @@
     <t xml:space="preserve">14.3197822570801</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6452350616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7428674697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7265949249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.214768409729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.807957649231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8567733764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9544086456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7916841506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2709646224976</t>
+    <t xml:space="preserve">14.6452312469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7428693771362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7265939712524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2147693634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8079566955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8567752838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9544076919556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7916822433472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2709665298462</t>
   </si>
   <si>
     <t xml:space="preserve">15.0032272338867</t>
@@ -1253,22 +1253,22 @@
     <t xml:space="preserve">14.4825067520142</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9218654632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9055919647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0194978713989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0520439147949</t>
+    <t xml:space="preserve">14.9218645095825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9055910110474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0194988250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0520448684692</t>
   </si>
   <si>
     <t xml:space="preserve">16.2562065124512</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7354888916016</t>
+    <t xml:space="preserve">15.7354879379272</t>
   </si>
   <si>
     <t xml:space="preserve">15.8168516159058</t>
@@ -1277,88 +1277,88 @@
     <t xml:space="preserve">15.6215829849243</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9307584762573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6866722106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7192182540894</t>
+    <t xml:space="preserve">15.9307594299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6866703033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7192144393921</t>
   </si>
   <si>
     <t xml:space="preserve">15.7029438018799</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6703977584839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6053066253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5653495788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.995680809021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0291948318481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0627012252808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2470083236694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2302522659302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5318422317505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7161445617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8669414520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5821084976196</t>
+    <t xml:space="preserve">15.6703987121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6053085327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5653505325317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9956817626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0291929244995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0627021789551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2470073699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2302532196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5318412780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7161464691162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8669424057007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5821075439453</t>
   </si>
   <si>
     <t xml:space="preserve">15.4983320236206</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4815759658813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4145545959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1799879074097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0794610977173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1129655838013</t>
+    <t xml:space="preserve">15.481575012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4145565032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1799898147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0794563293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1129684448242</t>
   </si>
   <si>
     <t xml:space="preserve">14.3589944839478</t>
   </si>
   <si>
-    <t xml:space="preserve">14.291974067688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2584648132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4595260620117</t>
+    <t xml:space="preserve">14.2919750213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2584667205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4595251083374</t>
   </si>
   <si>
     <t xml:space="preserve">14.4092597961426</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5600538253784</t>
+    <t xml:space="preserve">14.5600528717041</t>
   </si>
   <si>
     <t xml:space="preserve">13.4039621353149</t>
@@ -1373,10 +1373,10 @@
     <t xml:space="preserve">13.5380010604858</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4374723434448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1914463043213</t>
+    <t xml:space="preserve">13.4374732971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1914443969727</t>
   </si>
   <si>
     <t xml:space="preserve">13.5882654190063</t>
@@ -1388,10 +1388,10 @@
     <t xml:space="preserve">13.4207181930542</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5212478637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5715141296387</t>
+    <t xml:space="preserve">13.5212459564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.57151222229</t>
   </si>
   <si>
     <t xml:space="preserve">13.3201875686646</t>
@@ -1400,7 +1400,7 @@
     <t xml:space="preserve">13.1526374816895</t>
   </si>
   <si>
-    <t xml:space="preserve">13.186146736145</t>
+    <t xml:space="preserve">13.1861476898193</t>
   </si>
   <si>
     <t xml:space="preserve">13.2196578979492</t>
@@ -1412,25 +1412,25 @@
     <t xml:space="preserve">12.8510494232178</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6834993362427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5662145614624</t>
+    <t xml:space="preserve">12.683500289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5662155151367</t>
   </si>
   <si>
     <t xml:space="preserve">12.901312828064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8342943191528</t>
+    <t xml:space="preserve">12.8342924118042</t>
   </si>
   <si>
     <t xml:space="preserve">12.4824390411377</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1473398208618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0803213119507</t>
+    <t xml:space="preserve">12.1473407745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0803203582764</t>
   </si>
   <si>
     <t xml:space="preserve">12.0635662078857</t>
@@ -1445,61 +1445,61 @@
     <t xml:space="preserve">11.192307472229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2258195877075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4321737289429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1191282272339</t>
+    <t xml:space="preserve">11.2258186340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4321746826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1191272735596</t>
   </si>
   <si>
     <t xml:space="preserve">13.2531681060791</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2866764068604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7672739028931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3536977767944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9850883483887</t>
+    <t xml:space="preserve">13.2866773605347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7672729492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3536968231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.985089302063</t>
   </si>
   <si>
     <t xml:space="preserve">12.8007841110229</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6332349777222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8678026199341</t>
+    <t xml:space="preserve">12.6332340240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8678035736084</t>
   </si>
   <si>
     <t xml:space="preserve">11.8122425079346</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6279363632202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6111822128296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7284660339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9630365371704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8960161209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6614475250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0750246047974</t>
+    <t xml:space="preserve">11.6279373168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6111812591553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7284669876099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9630355834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8960151672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6614465713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.075023651123</t>
   </si>
   <si>
     <t xml:space="preserve">11.0415143966675</t>
@@ -1508,28 +1508,28 @@
     <t xml:space="preserve">10.9577388763428</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7566804885864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9242286682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.974494934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7117118835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3651552200317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4603872299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1587972640991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1252889633179</t>
+    <t xml:space="preserve">10.7566795349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9242296218872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9744939804077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7117109298706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3651561737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4603881835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1587982177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1252899169922</t>
   </si>
   <si>
     <t xml:space="preserve">11.1755542755127</t>
@@ -1550,13 +1550,13 @@
     <t xml:space="preserve">11.7954864501953</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8792610168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.197606086731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2478713989258</t>
+    <t xml:space="preserve">11.87926197052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1976051330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2478704452515</t>
   </si>
   <si>
     <t xml:space="preserve">12.0133008956909</t>
@@ -1568,25 +1568,25 @@
     <t xml:space="preserve">12.180850982666</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3819103240967</t>
+    <t xml:space="preserve">12.381911277771</t>
   </si>
   <si>
     <t xml:space="preserve">12.3316459655762</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4656839370728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5997247695923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7170095443726</t>
+    <t xml:space="preserve">12.4656858444214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.599723815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7170085906982</t>
   </si>
   <si>
     <t xml:space="preserve">12.8845586776733</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9515790939331</t>
+    <t xml:space="preserve">12.9515781402588</t>
   </si>
   <si>
     <t xml:space="preserve">12.9683332443237</t>
@@ -1601,7 +1601,7 @@
     <t xml:space="preserve">12.8175392150879</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6499891281128</t>
+    <t xml:space="preserve">12.6499900817871</t>
   </si>
   <si>
     <t xml:space="preserve">12.7002544403076</t>
@@ -1610,43 +1610,43 @@
     <t xml:space="preserve">12.5159482955933</t>
   </si>
   <si>
-    <t xml:space="preserve">12.784029006958</t>
+    <t xml:space="preserve">12.7840299606323</t>
   </si>
   <si>
     <t xml:space="preserve">13.0018444061279</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0353527069092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5494604110718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9348230361938</t>
+    <t xml:space="preserve">13.0353536605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5494585037231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9348220825195</t>
   </si>
   <si>
     <t xml:space="preserve">12.9180679321289</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3872060775757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6217775344849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8228368759155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5044918060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4542255401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6385316848755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7223062515259</t>
+    <t xml:space="preserve">13.38720703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6217784881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8228359222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5044927597046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4542274475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6385326385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7223052978516</t>
   </si>
   <si>
     <t xml:space="preserve">13.3704528808594</t>
@@ -1658,7 +1658,7 @@
     <t xml:space="preserve">13.0185985565186</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1693935394287</t>
+    <t xml:space="preserve">13.1693925857544</t>
   </si>
   <si>
     <t xml:space="preserve">13.1023740768433</t>
@@ -1667,25 +1667,25 @@
     <t xml:space="preserve">12.499195098877</t>
   </si>
   <si>
-    <t xml:space="preserve">12.748176574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5740213394165</t>
+    <t xml:space="preserve">12.7481775283813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5740203857422</t>
   </si>
   <si>
     <t xml:space="preserve">12.3650341033936</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2257099151611</t>
+    <t xml:space="preserve">12.2257108688354</t>
   </si>
   <si>
     <t xml:space="preserve">12.2779579162598</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3127880096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2953729629517</t>
+    <t xml:space="preserve">12.3127889633179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2953720092773</t>
   </si>
   <si>
     <t xml:space="preserve">12.3302040100098</t>
@@ -1694,7 +1694,7 @@
     <t xml:space="preserve">12.1212177276611</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5217742919922</t>
+    <t xml:space="preserve">12.5217752456665</t>
   </si>
   <si>
     <t xml:space="preserve">12.4869432449341</t>
@@ -1703,7 +1703,7 @@
     <t xml:space="preserve">12.4521131515503</t>
   </si>
   <si>
-    <t xml:space="preserve">12.138632774353</t>
+    <t xml:space="preserve">12.1386318206787</t>
   </si>
   <si>
     <t xml:space="preserve">12.0515546798706</t>
@@ -1712,58 +1712,58 @@
     <t xml:space="preserve">11.894814491272</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2082958221436</t>
+    <t xml:space="preserve">12.2082967758179</t>
   </si>
   <si>
     <t xml:space="preserve">12.8178396224976</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7655935287476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6436834335327</t>
+    <t xml:space="preserve">12.7655916213989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.643684387207</t>
   </si>
   <si>
     <t xml:space="preserve">12.399866104126</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6262674331665</t>
+    <t xml:space="preserve">12.6262683868408</t>
   </si>
   <si>
     <t xml:space="preserve">12.5391902923584</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8700857162476</t>
+    <t xml:space="preserve">12.8700866699219</t>
   </si>
   <si>
     <t xml:space="preserve">12.9745779037476</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9571628570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9397478103638</t>
+    <t xml:space="preserve">12.95716381073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9397487640381</t>
   </si>
   <si>
     <t xml:space="preserve">12.7830085754395</t>
   </si>
   <si>
-    <t xml:space="preserve">12.695930480957</t>
+    <t xml:space="preserve">12.6959295272827</t>
   </si>
   <si>
     <t xml:space="preserve">12.800422668457</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8875017166138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1560487747192</t>
+    <t xml:space="preserve">12.8875007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1560478210449</t>
   </si>
   <si>
     <t xml:space="preserve">12.0341396331787</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7206611633301</t>
+    <t xml:space="preserve">11.7206592559814</t>
   </si>
   <si>
     <t xml:space="preserve">12.2431268692017</t>
@@ -1772,22 +1772,22 @@
     <t xml:space="preserve">11.7554912567139</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6684141159058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9993085861206</t>
+    <t xml:space="preserve">11.6684131622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9993095397949</t>
   </si>
   <si>
     <t xml:space="preserve">12.0689706802368</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1038017272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7903213500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8425693511963</t>
+    <t xml:space="preserve">12.1038007736206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.790322303772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.842568397522</t>
   </si>
   <si>
     <t xml:space="preserve">11.9470615386963</t>
@@ -1796,22 +1796,22 @@
     <t xml:space="preserve">11.8251533508301</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8599834442139</t>
+    <t xml:space="preserve">11.8599843978882</t>
   </si>
   <si>
     <t xml:space="preserve">11.7729072570801</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8774003982544</t>
+    <t xml:space="preserve">11.8774013519287</t>
   </si>
   <si>
     <t xml:space="preserve">11.6509981155396</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5465059280396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3201026916504</t>
+    <t xml:space="preserve">11.5465049743652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3201017379761</t>
   </si>
   <si>
     <t xml:space="preserve">11.2156095504761</t>
@@ -1820,19 +1820,19 @@
     <t xml:space="preserve">11.4071807861328</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3026847839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3549327850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3897647857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1981925964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9369602203369</t>
+    <t xml:space="preserve">11.3026857376099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3549337387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3897638320923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1981935501099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9369611740112</t>
   </si>
   <si>
     <t xml:space="preserve">11.0414543151855</t>
@@ -1841,16 +1841,16 @@
     <t xml:space="preserve">10.8847141265869</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8672981262207</t>
+    <t xml:space="preserve">10.8672971725464</t>
   </si>
   <si>
     <t xml:space="preserve">10.9717922210693</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8324661254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6234798431396</t>
+    <t xml:space="preserve">10.8324670791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.623480796814</t>
   </si>
   <si>
     <t xml:space="preserve">10.6060657501221</t>
@@ -1859,25 +1859,25 @@
     <t xml:space="preserve">10.5886497497559</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5189876556396</t>
+    <t xml:space="preserve">10.5189867019653</t>
   </si>
   <si>
     <t xml:space="preserve">10.4493255615234</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6583127975464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7802209854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1633615493774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1111164093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0588693618774</t>
+    <t xml:space="preserve">10.6583108901978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7802200317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1633634567261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1111145019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0588684082031</t>
   </si>
   <si>
     <t xml:space="preserve">10.9892063140869</t>
@@ -1886,7 +1886,7 @@
     <t xml:space="preserve">10.8498821258545</t>
   </si>
   <si>
-    <t xml:space="preserve">11.024037361145</t>
+    <t xml:space="preserve">11.0240383148193</t>
   </si>
   <si>
     <t xml:space="preserve">11.0066232681274</t>
@@ -1895,25 +1895,25 @@
     <t xml:space="preserve">10.7976360321045</t>
   </si>
   <si>
-    <t xml:space="preserve">10.815052986145</t>
+    <t xml:space="preserve">10.8150520324707</t>
   </si>
   <si>
     <t xml:space="preserve">10.9543762207031</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0937004089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7032451629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.981894493103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9296464920044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9122304916382</t>
+    <t xml:space="preserve">11.0936994552612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7032432556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9818935394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9296455383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9122314453125</t>
   </si>
   <si>
     <t xml:space="preserve">11.8077383041382</t>
@@ -1922,7 +1922,7 @@
     <t xml:space="preserve">12.2605409622192</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0863857269287</t>
+    <t xml:space="preserve">12.086386680603</t>
   </si>
   <si>
     <t xml:space="preserve">11.9644765853882</t>
@@ -1934,43 +1934,43 @@
     <t xml:space="preserve">11.4942579269409</t>
   </si>
   <si>
-    <t xml:space="preserve">11.581335067749</t>
+    <t xml:space="preserve">11.5813360214233</t>
   </si>
   <si>
     <t xml:space="preserve">11.476842880249</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6858282089233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.190878868103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3476190567017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5116739273071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5987501144409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7105588912964</t>
+    <t xml:space="preserve">11.6858291625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1908798217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.347620010376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5116720199585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5987510681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7105598449707</t>
   </si>
   <si>
     <t xml:space="preserve">9.70045757293701</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49147033691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03866577148438</t>
+    <t xml:space="preserve">9.49146938323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03866672515869</t>
   </si>
   <si>
     <t xml:space="preserve">8.98641967773438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42912292480469</t>
+    <t xml:space="preserve">8.42912197113037</t>
   </si>
   <si>
     <t xml:space="preserve">8.18530464172363</t>
@@ -1982,52 +1982,52 @@
     <t xml:space="preserve">8.45524501800537</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53361701965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49007701873779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31592082977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32462882995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16788864135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38558387756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28979682922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41170787811279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4987850189209</t>
+    <t xml:space="preserve">8.533616065979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49007606506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31592178344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32462978363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16788959503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38558483123779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28979778289795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41170692443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49878406524658</t>
   </si>
   <si>
     <t xml:space="preserve">8.63810920715332</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69035625457764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67294025421143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79484939575195</t>
+    <t xml:space="preserve">8.690354347229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67294120788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79485034942627</t>
   </si>
   <si>
     <t xml:space="preserve">8.96900463104248</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75130844116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70777130126953</t>
+    <t xml:space="preserve">8.75131034851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70777034759521</t>
   </si>
   <si>
     <t xml:space="preserve">8.83838748931885</t>
@@ -2039,16 +2039,16 @@
     <t xml:space="preserve">9.05608177185059</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14315986633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23023700714111</t>
+    <t xml:space="preserve">9.14315891265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23023796081543</t>
   </si>
   <si>
     <t xml:space="preserve">9.40439224243164</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66562557220459</t>
+    <t xml:space="preserve">9.66562652587891</t>
   </si>
   <si>
     <t xml:space="preserve">9.57854843139648</t>
@@ -2060,37 +2060,37 @@
     <t xml:space="preserve">8.88192653656006</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65552425384521</t>
+    <t xml:space="preserve">8.6555233001709</t>
   </si>
   <si>
     <t xml:space="preserve">8.51620006561279</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6032772064209</t>
+    <t xml:space="preserve">8.60327911376953</t>
   </si>
   <si>
     <t xml:space="preserve">8.56844711303711</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36085414886475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83978080749512</t>
+    <t xml:space="preserve">9.36085319519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83978271484375</t>
   </si>
   <si>
     <t xml:space="preserve">10.01393699646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1010141372681</t>
+    <t xml:space="preserve">10.1010150909424</t>
   </si>
   <si>
     <t xml:space="preserve">9.92685890197754</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88332080841064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0574769973755</t>
+    <t xml:space="preserve">9.88332176208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0574760437012</t>
   </si>
   <si>
     <t xml:space="preserve">9.97039794921875</t>
@@ -2099,10 +2099,10 @@
     <t xml:space="preserve">9.70916366577148</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75270462036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62208843231201</t>
+    <t xml:space="preserve">9.75270366668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6220874786377</t>
   </si>
   <si>
     <t xml:space="preserve">9.53500938415527</t>
@@ -2111,19 +2111,19 @@
     <t xml:space="preserve">9.79624271392822</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1880912780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2751693725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5364027023315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9282522201538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0153303146362</t>
+    <t xml:space="preserve">10.1880922317505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2751703262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5364036560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9282531738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0153293609619</t>
   </si>
   <si>
     <t xml:space="preserve">10.7540979385376</t>
@@ -2132,10 +2132,10 @@
     <t xml:space="preserve">10.4928646087646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4057855606079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.362247467041</t>
+    <t xml:space="preserve">10.4057865142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3622465133667</t>
   </si>
   <si>
     <t xml:space="preserve">10.3187093734741</t>
@@ -2144,7 +2144,7 @@
     <t xml:space="preserve">11.1894865036011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2765636444092</t>
+    <t xml:space="preserve">11.2765626907349</t>
   </si>
   <si>
     <t xml:space="preserve">11.4507188796997</t>
@@ -2153,16 +2153,16 @@
     <t xml:space="preserve">12.0167245864868</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0602617263794</t>
+    <t xml:space="preserve">12.0602626800537</t>
   </si>
   <si>
     <t xml:space="preserve">12.5011930465698</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0100755691528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8314867019653</t>
+    <t xml:space="preserve">12.0100746154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.831485748291</t>
   </si>
   <si>
     <t xml:space="preserve">11.6975450515747</t>
@@ -2171,19 +2171,19 @@
     <t xml:space="preserve">11.4743099212646</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2064266204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4296617507935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.608250617981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2510747909546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5813665390015</t>
+    <t xml:space="preserve">11.2064275741577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4296627044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6082496643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2510738372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5813674926758</t>
   </si>
   <si>
     <t xml:space="preserve">10.5367202758789</t>
@@ -2195,25 +2195,25 @@
     <t xml:space="preserve">10.8938961029053</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1617794036865</t>
+    <t xml:space="preserve">11.1617784500122</t>
   </si>
   <si>
     <t xml:space="preserve">11.0724849700928</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9207801818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1886615753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2333106994629</t>
+    <t xml:space="preserve">11.9207811355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.188663482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2333097457886</t>
   </si>
   <si>
     <t xml:space="preserve">12.3226051330566</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8761329650879</t>
+    <t xml:space="preserve">11.8761339187622</t>
   </si>
   <si>
     <t xml:space="preserve">12.1440162658691</t>
@@ -2222,10 +2222,10 @@
     <t xml:space="preserve">11.7868385314941</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0993690490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4387836456299</t>
+    <t xml:space="preserve">12.0993700027466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4387826919556</t>
   </si>
   <si>
     <t xml:space="preserve">13.4834299087524</t>
@@ -2243,10 +2243,10 @@
     <t xml:space="preserve">12.9030170440674</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0816049575806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.036958694458</t>
+    <t xml:space="preserve">13.0816059112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0369596481323</t>
   </si>
   <si>
     <t xml:space="preserve">13.7513113021851</t>
@@ -2261,52 +2261,52 @@
     <t xml:space="preserve">13.9745473861694</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2601938247681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6620187759399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6173706054688</t>
+    <t xml:space="preserve">13.2601947784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6620178222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6173715591431</t>
   </si>
   <si>
     <t xml:space="preserve">13.88525390625</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6442546844482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7781972885132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9121379852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.090726852417</t>
+    <t xml:space="preserve">14.6442537307739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7781963348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9121370315552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0907249450684</t>
   </si>
   <si>
     <t xml:space="preserve">14.733549118042</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4210195541382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5103130340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1800193786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8497285842896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.805079460144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0729637145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3854923248291</t>
+    <t xml:space="preserve">14.4210186004639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5103139877319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1800212860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8497266769409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8050813674927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.072961807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3854942321777</t>
   </si>
   <si>
     <t xml:space="preserve">16.9212589263916</t>
@@ -2318,7 +2318,7 @@
     <t xml:space="preserve">16.7426681518555</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7249050140381</t>
+    <t xml:space="preserve">17.7249069213867</t>
   </si>
   <si>
     <t xml:space="preserve">17.769552230835</t>
@@ -2330,7 +2330,7 @@
     <t xml:space="preserve">17.8588466644287</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0374355316162</t>
+    <t xml:space="preserve">18.0374374389648</t>
   </si>
   <si>
     <t xml:space="preserve">18.12672996521</t>
@@ -2342,34 +2342,34 @@
     <t xml:space="preserve">18.5732002258301</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6980228424072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3053169250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5909652709961</t>
+    <t xml:space="preserve">16.6980247497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3053188323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5909671783447</t>
   </si>
   <si>
     <t xml:space="preserve">18.2160243988037</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9481410980225</t>
+    <t xml:space="preserve">17.9481430053711</t>
   </si>
   <si>
     <t xml:space="preserve">19.0196723937988</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1804981231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5376758575439</t>
+    <t xml:space="preserve">20.1805000305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5376739501953</t>
   </si>
   <si>
     <t xml:space="preserve">20.6269702911377</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9841461181641</t>
+    <t xml:space="preserve">20.9841442108154</t>
   </si>
   <si>
     <t xml:space="preserve">20.8055553436279</t>
@@ -2384,40 +2384,40 @@
     <t xml:space="preserve">20.0019092559814</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8233184814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2697906494141</t>
+    <t xml:space="preserve">19.8233222961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2697944641113</t>
   </si>
   <si>
     <t xml:space="preserve">19.1982612609863</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9126129150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5554370880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6447334289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9303779602051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7162609100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4483795166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4306182861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3413200378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.323558807373</t>
+    <t xml:space="preserve">19.9126148223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5554389953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6447315216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9303798675537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7162628173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4483814239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4306144714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3413219451904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3235569000244</t>
   </si>
   <si>
     <t xml:space="preserve">21.6092052459717</t>
@@ -2429,10 +2429,10 @@
     <t xml:space="preserve">21.7877922058105</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7700309753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.914701461792</t>
+    <t xml:space="preserve">22.7700290679932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9147033691406</t>
   </si>
   <si>
     <t xml:space="preserve">24.4583892822266</t>
@@ -2441,22 +2441,22 @@
     <t xml:space="preserve">24.0020771026611</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8195514678955</t>
+    <t xml:space="preserve">23.8195533752441</t>
   </si>
   <si>
     <t xml:space="preserve">24.5496520996094</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4622764587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8234424591064</t>
+    <t xml:space="preserve">25.4622783660889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8234405517578</t>
   </si>
   <si>
     <t xml:space="preserve">24.0933380126953</t>
   </si>
   <si>
-    <t xml:space="preserve">24.732177734375</t>
+    <t xml:space="preserve">24.7321796417236</t>
   </si>
   <si>
     <t xml:space="preserve">24.3671283721924</t>
@@ -2465,7 +2465,7 @@
     <t xml:space="preserve">23.9108142852783</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2719764709473</t>
+    <t xml:space="preserve">23.2719745635986</t>
   </si>
   <si>
     <t xml:space="preserve">23.6370258331299</t>
@@ -2477,10 +2477,10 @@
     <t xml:space="preserve">24.2758655548096</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7282886505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1846027374268</t>
+    <t xml:space="preserve">23.7282867431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1846008300781</t>
   </si>
   <si>
     <t xml:space="preserve">25.0059642791748</t>
@@ -2489,16 +2489,16 @@
     <t xml:space="preserve">22.3593482971191</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8156623840332</t>
+    <t xml:space="preserve">22.8156604766846</t>
   </si>
   <si>
     <t xml:space="preserve">22.2680854797363</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7243976593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4545001983643</t>
+    <t xml:space="preserve">22.7243995666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4545021057129</t>
   </si>
   <si>
     <t xml:space="preserve">23.0894508361816</t>
@@ -2507,16 +2507,16 @@
     <t xml:space="preserve">23.1807117462158</t>
   </si>
   <si>
-    <t xml:space="preserve">22.906925201416</t>
+    <t xml:space="preserve">22.9069271087646</t>
   </si>
   <si>
     <t xml:space="preserve">22.1768226623535</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5418739318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9942989349365</t>
+    <t xml:space="preserve">22.5418758392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9943008422852</t>
   </si>
   <si>
     <t xml:space="preserve">22.0855617523193</t>
@@ -2525,7 +2525,7 @@
     <t xml:space="preserve">21.5379867553711</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7205104827881</t>
+    <t xml:space="preserve">21.7205085754395</t>
   </si>
   <si>
     <t xml:space="preserve">21.3554592132568</t>
@@ -2534,28 +2534,28 @@
     <t xml:space="preserve">21.8117733001709</t>
   </si>
   <si>
-    <t xml:space="preserve">21.446720123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8991451263428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0738925933838</t>
+    <t xml:space="preserve">21.4467220306396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8991470336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0738945007324</t>
   </si>
   <si>
     <t xml:space="preserve">19.8952560424805</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8039951324463</t>
+    <t xml:space="preserve">19.8039970397949</t>
   </si>
   <si>
     <t xml:space="preserve">19.6214694976807</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7127342224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.081672668457</t>
+    <t xml:space="preserve">19.7127323150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0816745758057</t>
   </si>
   <si>
     <t xml:space="preserve">24.6409149169922</t>
@@ -2564,49 +2564,49 @@
     <t xml:space="preserve">25.3710155487061</t>
   </si>
   <si>
-    <t xml:space="preserve">26.374906539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6448040008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9185924530029</t>
+    <t xml:space="preserve">26.3749046325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6448059082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9185905456543</t>
   </si>
   <si>
     <t xml:space="preserve">25.8273296356201</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5535430908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2797565460205</t>
+    <t xml:space="preserve">25.5535411834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2797546386719</t>
   </si>
   <si>
     <t xml:space="preserve">23.3632392883301</t>
   </si>
   <si>
-    <t xml:space="preserve">22.450611114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6292476654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9904098510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2641983032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1729335784912</t>
+    <t xml:space="preserve">22.4506130218506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6292495727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9904079437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.264196395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1729354858398</t>
   </si>
   <si>
     <t xml:space="preserve">20.5340957641602</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8078842163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.442834854126</t>
+    <t xml:space="preserve">20.80788230896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4428329467773</t>
   </si>
   <si>
     <t xml:space="preserve">21.9030342102051</t>
@@ -2621,7 +2621,7 @@
     <t xml:space="preserve">20.1690464019775</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3476810455322</t>
+    <t xml:space="preserve">19.3476829528809</t>
   </si>
   <si>
     <t xml:space="preserve">19.1651554107666</t>
@@ -2633,10 +2633,10 @@
     <t xml:space="preserve">18.6175804138184</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1156349182129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4311656951904</t>
+    <t xml:space="preserve">18.1156368255615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4311676025391</t>
   </si>
   <si>
     <t xml:space="preserve">17.5224304199219</t>
@@ -2645,7 +2645,7 @@
     <t xml:space="preserve">16.2447509765625</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5185394287109</t>
+    <t xml:space="preserve">16.5185413360596</t>
   </si>
   <si>
     <t xml:space="preserve">16.6098022460938</t>
@@ -2657,10 +2657,10 @@
     <t xml:space="preserve">17.6593246459961</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2486419677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3437919616699</t>
+    <t xml:space="preserve">17.2486400604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3437938690186</t>
   </si>
   <si>
     <t xml:space="preserve">18.800106048584</t>
@@ -2672,7 +2672,7 @@
     <t xml:space="preserve">18.982629776001</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5263156890869</t>
+    <t xml:space="preserve">18.5263175964355</t>
   </si>
   <si>
     <t xml:space="preserve">18.4350566864014</t>
@@ -2684,7 +2684,7 @@
     <t xml:space="preserve">21.7661418914795</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8574047088623</t>
+    <t xml:space="preserve">21.8574066162109</t>
   </si>
   <si>
     <t xml:space="preserve">22.3137187957764</t>
@@ -2693,34 +2693,34 @@
     <t xml:space="preserve">21.9486656188965</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0399303436279</t>
+    <t xml:space="preserve">22.0399284362793</t>
   </si>
   <si>
     <t xml:space="preserve">21.4923534393311</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4049777984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6787662506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5913963317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5001335144043</t>
+    <t xml:space="preserve">22.4049797058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.678768157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5913944244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5001316070557</t>
   </si>
   <si>
     <t xml:space="preserve">23.7337303161621</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8271713256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.387809753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2009315490723</t>
+    <t xml:space="preserve">23.827169418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3878116607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2009296417236</t>
   </si>
   <si>
     <t xml:space="preserve">24.6681289672852</t>
@@ -2729,28 +2729,28 @@
     <t xml:space="preserve">24.621410369873</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0607719421387</t>
+    <t xml:space="preserve">24.06077003479</t>
   </si>
   <si>
     <t xml:space="preserve">23.9673309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5001316070557</t>
+    <t xml:space="preserve">23.500129699707</t>
   </si>
   <si>
     <t xml:space="preserve">22.9394912719727</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7058925628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6591739654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5190124511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.425573348999</t>
+    <t xml:space="preserve">22.7058906555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6591720581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5190143585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4255714416504</t>
   </si>
   <si>
     <t xml:space="preserve">23.4534130096436</t>
@@ -2768,7 +2768,7 @@
     <t xml:space="preserve">22.0985317230225</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9116554260254</t>
+    <t xml:space="preserve">21.9116535186768</t>
   </si>
   <si>
     <t xml:space="preserve">21.6780548095703</t>
@@ -2780,7 +2780,7 @@
     <t xml:space="preserve">23.0329303741455</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9862117767334</t>
+    <t xml:space="preserve">22.986213684082</t>
   </si>
   <si>
     <t xml:space="preserve">21.8182144165039</t>
@@ -2789,7 +2789,7 @@
     <t xml:space="preserve">22.1919727325439</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7714939117432</t>
+    <t xml:space="preserve">21.7714920043945</t>
   </si>
   <si>
     <t xml:space="preserve">22.2386913299561</t>
@@ -2801,13 +2801,13 @@
     <t xml:space="preserve">23.31325340271</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7993335723877</t>
+    <t xml:space="preserve">22.7993316650391</t>
   </si>
   <si>
     <t xml:space="preserve">22.3321323394775</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5846138000488</t>
+    <t xml:space="preserve">21.5846157073975</t>
   </si>
   <si>
     <t xml:space="preserve">20.930534362793</t>
@@ -2819,7 +2819,7 @@
     <t xml:space="preserve">20.2764568328857</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9494152069092</t>
+    <t xml:space="preserve">19.9494171142578</t>
   </si>
   <si>
     <t xml:space="preserve">20.4166164398193</t>
@@ -2840,25 +2840,25 @@
     <t xml:space="preserve">19.9026947021484</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8092555999756</t>
+    <t xml:space="preserve">19.8092575073242</t>
   </si>
   <si>
     <t xml:space="preserve">19.5756568908691</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3420562744141</t>
+    <t xml:space="preserve">19.3420581817627</t>
   </si>
   <si>
     <t xml:space="preserve">19.2486171722412</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9215774536133</t>
+    <t xml:space="preserve">18.9215755462646</t>
   </si>
   <si>
     <t xml:space="preserve">18.8281364440918</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5758495330811</t>
+    <t xml:space="preserve">18.5758476257324</t>
   </si>
   <si>
     <t xml:space="preserve">18.5010967254639</t>
@@ -2870,7 +2870,7 @@
     <t xml:space="preserve">19.5289363861084</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5945377349854</t>
+    <t xml:space="preserve">18.5945358276367</t>
   </si>
   <si>
     <t xml:space="preserve">18.3702812194824</t>
@@ -2879,7 +2879,7 @@
     <t xml:space="preserve">18.0525856018066</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9217700958252</t>
+    <t xml:space="preserve">17.9217720031738</t>
   </si>
   <si>
     <t xml:space="preserve">17.7535781860352</t>
@@ -2891,10 +2891,10 @@
     <t xml:space="preserve">17.7348899841309</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4919452667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2303161621094</t>
+    <t xml:space="preserve">17.4919471740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2303142547607</t>
   </si>
   <si>
     <t xml:space="preserve">17.1742496490479</t>
@@ -2909,7 +2909,7 @@
     <t xml:space="preserve">16.4454212188721</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1277236938477</t>
+    <t xml:space="preserve">16.1277256011963</t>
   </si>
   <si>
     <t xml:space="preserve">16.5014839172363</t>
@@ -2921,13 +2921,13 @@
     <t xml:space="preserve">16.0342845916748</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8847808837891</t>
+    <t xml:space="preserve">15.8847818374634</t>
   </si>
   <si>
     <t xml:space="preserve">15.3241405487061</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6044616699219</t>
+    <t xml:space="preserve">15.6044607162476</t>
   </si>
   <si>
     <t xml:space="preserve">15.7352771759033</t>
@@ -2945,7 +2945,7 @@
     <t xml:space="preserve">16.7444267272949</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7257404327393</t>
+    <t xml:space="preserve">16.7257385253906</t>
   </si>
   <si>
     <t xml:space="preserve">16.9313087463379</t>
@@ -2957,7 +2957,7 @@
     <t xml:space="preserve">17.9965229034424</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2581558227539</t>
+    <t xml:space="preserve">18.2581539154053</t>
   </si>
   <si>
     <t xml:space="preserve">17.6601371765137</t>
@@ -2966,10 +2966,10 @@
     <t xml:space="preserve">17.5666980743408</t>
   </si>
   <si>
-    <t xml:space="preserve">17.641450881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3142166137695</t>
+    <t xml:space="preserve">17.6414489746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3142185211182</t>
   </si>
   <si>
     <t xml:space="preserve">18.0712738037109</t>
@@ -3008,7 +3008,7 @@
     <t xml:space="preserve">17.7162017822266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5293216705322</t>
+    <t xml:space="preserve">17.5293235778809</t>
   </si>
   <si>
     <t xml:space="preserve">16.9873714447021</t>
@@ -3020,10 +3020,10 @@
     <t xml:space="preserve">17.5480117797852</t>
   </si>
   <si>
-    <t xml:space="preserve">16.277229309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9221572875977</t>
+    <t xml:space="preserve">16.2772274017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.922158241272</t>
   </si>
   <si>
     <t xml:space="preserve">16.0155963897705</t>
@@ -3032,19 +3032,19 @@
     <t xml:space="preserve">15.9595327377319</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9782218933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0903472900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8287172317505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6231489181519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5857744216919</t>
+    <t xml:space="preserve">15.9782209396362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0903491973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8287162780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6231479644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5857725143433</t>
   </si>
   <si>
     <t xml:space="preserve">16.0716609954834</t>
@@ -3065,10 +3065,10 @@
     <t xml:space="preserve">16.6322994232178</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6136112213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5762348175049</t>
+    <t xml:space="preserve">16.6136131286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5762367248535</t>
   </si>
   <si>
     <t xml:space="preserve">16.3519802093506</t>
@@ -3077,13 +3077,13 @@
     <t xml:space="preserve">16.2024765014648</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7913408279419</t>
+    <t xml:space="preserve">15.7913398742676</t>
   </si>
   <si>
     <t xml:space="preserve">15.7726516723633</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6978998184204</t>
+    <t xml:space="preserve">15.6979007720947</t>
   </si>
   <si>
     <t xml:space="preserve">16.5201721191406</t>
@@ -3092,34 +3092,34 @@
     <t xml:space="preserve">16.1464138031006</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1650981903076</t>
+    <t xml:space="preserve">16.1651000976562</t>
   </si>
   <si>
     <t xml:space="preserve">16.109037399292</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8474044799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7539663314819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8660917282104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6792125701904</t>
+    <t xml:space="preserve">15.8474025726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7539653778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8660936355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6792144775391</t>
   </si>
   <si>
     <t xml:space="preserve">15.8100280761719</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5110206604004</t>
+    <t xml:space="preserve">15.5110216140747</t>
   </si>
   <si>
     <t xml:space="preserve">15.3802042007446</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0064449310303</t>
+    <t xml:space="preserve">15.0064458847046</t>
   </si>
   <si>
     <t xml:space="preserve">14.8008785247803</t>
@@ -3128,7 +3128,7 @@
     <t xml:space="preserve">14.6700620651245</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4271183013916</t>
+    <t xml:space="preserve">14.4271173477173</t>
   </si>
   <si>
     <t xml:space="preserve">14.5766229629517</t>
@@ -3158,13 +3158,13 @@
     <t xml:space="preserve">15.0811967849731</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5670852661133</t>
+    <t xml:space="preserve">15.567084312439</t>
   </si>
   <si>
     <t xml:space="preserve">15.716588973999</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6605253219604</t>
+    <t xml:space="preserve">15.6605262756348</t>
   </si>
   <si>
     <t xml:space="preserve">15.1933259963989</t>
@@ -3173,13 +3173,13 @@
     <t xml:space="preserve">15.3988933563232</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4175806045532</t>
+    <t xml:space="preserve">15.4175815582275</t>
   </si>
   <si>
     <t xml:space="preserve">15.4362697601318</t>
   </si>
   <si>
-    <t xml:space="preserve">15.137261390686</t>
+    <t xml:space="preserve">15.1372623443604</t>
   </si>
   <si>
     <t xml:space="preserve">15.0438222885132</t>
@@ -3191,7 +3191,7 @@
     <t xml:space="preserve">14.9877586364746</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7261257171631</t>
+    <t xml:space="preserve">14.7261266708374</t>
   </si>
   <si>
     <t xml:space="preserve">14.950382232666</t>
@@ -3206,22 +3206,22 @@
     <t xml:space="preserve">14.3149900436401</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5018701553345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4084310531616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1654872894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.202862739563</t>
+    <t xml:space="preserve">14.5018711090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4084300994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1654863357544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2028617858887</t>
   </si>
   <si>
     <t xml:space="preserve">14.2963027954102</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1281099319458</t>
+    <t xml:space="preserve">14.1281108856201</t>
   </si>
   <si>
     <t xml:space="preserve">13.8291034698486</t>
@@ -3236,19 +3236,19 @@
     <t xml:space="preserve">13.4179677963257</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5487833023071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6422233581543</t>
+    <t xml:space="preserve">13.5487842559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6422243118286</t>
   </si>
   <si>
     <t xml:space="preserve">13.45534324646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3992805480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3245277404785</t>
+    <t xml:space="preserve">13.3992795944214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3245286941528</t>
   </si>
   <si>
     <t xml:space="preserve">13.2497758865356</t>
@@ -3257,7 +3257,7 @@
     <t xml:space="preserve">13.0815839767456</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3432149887085</t>
+    <t xml:space="preserve">13.3432159423828</t>
   </si>
   <si>
     <t xml:space="preserve">13.1937122344971</t>
@@ -3266,7 +3266,7 @@
     <t xml:space="preserve">13.3058395385742</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2589263916016</t>
+    <t xml:space="preserve">14.2589273452759</t>
   </si>
   <si>
     <t xml:space="preserve">14.2776145935059</t>
@@ -3275,7 +3275,7 @@
     <t xml:space="preserve">14.7448139190674</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5575466156006</t>
+    <t xml:space="preserve">16.5575485229492</t>
   </si>
   <si>
     <t xml:space="preserve">16.4641094207764</t>
@@ -3284,13 +3284,13 @@
     <t xml:space="preserve">16.4267311096191</t>
   </si>
   <si>
-    <t xml:space="preserve">16.314603805542</t>
+    <t xml:space="preserve">16.3146018981934</t>
   </si>
   <si>
     <t xml:space="preserve">16.2585391998291</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2398529052734</t>
+    <t xml:space="preserve">16.2398509979248</t>
   </si>
   <si>
     <t xml:space="preserve">16.1837882995605</t>
@@ -3299,13 +3299,13 @@
     <t xml:space="preserve">14.8569412231445</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7074375152588</t>
+    <t xml:space="preserve">14.7074384689331</t>
   </si>
   <si>
     <t xml:space="preserve">14.6887502670288</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3897428512573</t>
+    <t xml:space="preserve">14.389741897583</t>
   </si>
   <si>
     <t xml:space="preserve">14.782190322876</t>
@@ -3326,19 +3326,19 @@
     <t xml:space="preserve">12.9881439208984</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5956964492798</t>
+    <t xml:space="preserve">12.5956954956055</t>
   </si>
   <si>
     <t xml:space="preserve">12.7078247070312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7452001571655</t>
+    <t xml:space="preserve">12.7452011108398</t>
   </si>
   <si>
     <t xml:space="preserve">12.4275054931641</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0442085266113</t>
+    <t xml:space="preserve">13.044207572937</t>
   </si>
   <si>
     <t xml:space="preserve">13.3805913925171</t>
@@ -3365,28 +3365,28 @@
     <t xml:space="preserve">13.9972944259644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0159826278687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6513748168945</t>
+    <t xml:space="preserve">14.015983581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6513738632202</t>
   </si>
   <si>
     <t xml:space="preserve">15.0251340866089</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4736442565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.903468132019</t>
+    <t xml:space="preserve">15.4736452102661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9034700393677</t>
   </si>
   <si>
     <t xml:space="preserve">16.482795715332</t>
   </si>
   <si>
-    <t xml:space="preserve">16.912618637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8565578460693</t>
+    <t xml:space="preserve">16.9126205444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8565559387207</t>
   </si>
   <si>
     <t xml:space="preserve">16.9499950408936</t>
@@ -3395,7 +3395,7 @@
     <t xml:space="preserve">16.8752422332764</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0434341430664</t>
+    <t xml:space="preserve">17.043436050415</t>
   </si>
   <si>
     <t xml:space="preserve">15.9969091415405</t>
@@ -3407,7 +3407,7 @@
     <t xml:space="preserve">15.5483961105347</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6418361663818</t>
+    <t xml:space="preserve">15.6418380737305</t>
   </si>
   <si>
     <t xml:space="preserve">16.4080429077148</t>
@@ -3419,13 +3419,13 @@
     <t xml:space="preserve">16.6790199279785</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5855808258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8002967834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7068576812744</t>
+    <t xml:space="preserve">16.585578918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8002986907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.706859588623</t>
   </si>
   <si>
     <t xml:space="preserve">16.211820602417</t>
@@ -3434,19 +3434,19 @@
     <t xml:space="preserve">15.3708620071411</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3052597045898</t>
+    <t xml:space="preserve">16.3052616119385</t>
   </si>
   <si>
     <t xml:space="preserve">16.0249404907227</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1273384094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9404582977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6134185791016</t>
+    <t xml:space="preserve">18.1273365020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9404602050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6134204864502</t>
   </si>
   <si>
     <t xml:space="preserve">17.7070121765137</t>
@@ -72417,7 +72417,7 @@
         <v>13.75</v>
       </c>
       <c r="D2625" t="n">
-        <v>13.5500001907349</v>
+        <v>13.5</v>
       </c>
       <c r="E2625" t="n">
         <v>13.6999998092651</v>
@@ -72429,6 +72429,32 @@
         <v>1268</v>
       </c>
       <c r="H2625" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2626">
+      <c r="A2626" s="1" t="n">
+        <v>46147.2916666667</v>
+      </c>
+      <c r="B2626" t="n">
+        <v>2316</v>
+      </c>
+      <c r="C2626" t="n">
+        <v>13.6499996185303</v>
+      </c>
+      <c r="D2626" t="n">
+        <v>13.4499998092651</v>
+      </c>
+      <c r="E2626" t="n">
+        <v>13.6000003814697</v>
+      </c>
+      <c r="F2626" t="n">
+        <v>13.6499996185303</v>
+      </c>
+      <c r="G2626" t="s">
+        <v>1257</v>
+      </c>
+      <c r="H2626" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SAB.MI.xlsx
+++ b/data/SAB.MI.xlsx
@@ -50,46 +50,46 @@
     <t xml:space="preserve">8.48310279846191</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33295822143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37049388885498</t>
+    <t xml:space="preserve">8.33295917510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37049293518066</t>
   </si>
   <si>
     <t xml:space="preserve">8.31794452667236</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25788688659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16029453277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88252830505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52969074249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6648211479187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62728357315063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61226940155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73989200592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75490617752075</t>
+    <t xml:space="preserve">8.25788593292236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16029357910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88252925872803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52969169616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66481971740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62728500366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61226987838745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73989248275757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75490665435791</t>
   </si>
   <si>
     <t xml:space="preserve">7.76992130279541</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89754343032837</t>
+    <t xml:space="preserve">7.89754247665405</t>
   </si>
   <si>
     <t xml:space="preserve">7.6197772026062</t>
@@ -98,127 +98,127 @@
     <t xml:space="preserve">7.79994964599609</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72487831115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65731287002563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50716924667358</t>
+    <t xml:space="preserve">7.72487783432007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65731191635132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5071702003479</t>
   </si>
   <si>
     <t xml:space="preserve">7.34201145172119</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54470491409302</t>
+    <t xml:space="preserve">7.54470586776733</t>
   </si>
   <si>
     <t xml:space="preserve">7.39080905914307</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58224201202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82247114181519</t>
+    <t xml:space="preserve">7.58224058151245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82247018814087</t>
   </si>
   <si>
     <t xml:space="preserve">8.0852222442627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1152515411377</t>
+    <t xml:space="preserve">8.11525058746338</t>
   </si>
   <si>
     <t xml:space="preserve">7.95760059356689</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06269931793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03267097473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92006492614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77742767333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86751317977905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80745649337769</t>
+    <t xml:space="preserve">8.06270027160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03267192840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92006397247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.777428150177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86751222610474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80745601654053</t>
   </si>
   <si>
     <t xml:space="preserve">7.98762989044189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04017734527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99513530731201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96510744094849</t>
+    <t xml:space="preserve">8.04017925262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9951343536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96510648727417</t>
   </si>
   <si>
     <t xml:space="preserve">7.9050498008728</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93507814407349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89003562927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94258642196655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82997941970825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81496429443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73238563537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64980602264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71737241744995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67232704162598</t>
+    <t xml:space="preserve">7.9350790977478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89003467559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94258451461792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82997846603394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81496334075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73238372802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64980506896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71737146377563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67232894897461</t>
   </si>
   <si>
     <t xml:space="preserve">7.63479137420654</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51467609405518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64229965209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56722640991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70235633850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74739980697632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46963310241699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69484853744507</t>
+    <t xml:space="preserve">7.51467704772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64229917526245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56722736358643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70235681533813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.747398853302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46963405609131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69484901428223</t>
   </si>
   <si>
     <t xml:space="preserve">7.4921555519104</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47338771820068</t>
+    <t xml:space="preserve">7.47338676452637</t>
   </si>
   <si>
     <t xml:space="preserve">7.43585109710693</t>
@@ -227,55 +227,55 @@
     <t xml:space="preserve">7.50341558456421</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48089361190796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59725570678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4283447265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38705539703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37203979492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31948947906494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28195571899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52122068405151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80533933639526</t>
+    <t xml:space="preserve">7.48089504241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59725666046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42834424972534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38705492019653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37204074859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31949138641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28195524215698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52122116088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80533885955811</t>
   </si>
   <si>
     <t xml:space="preserve">7.75009346008301</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75798749923706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.813232421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8605842590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69879531860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58435916900635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68695688247681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57646656036377</t>
+    <t xml:space="preserve">7.75798606872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81323099136353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86058521270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69879579544067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58435869216919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68695735931396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57646703720093</t>
   </si>
   <si>
     <t xml:space="preserve">7.53700685501099</t>
@@ -284,79 +284,79 @@
     <t xml:space="preserve">7.49754476547241</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28445625305176</t>
+    <t xml:space="preserve">7.28445672988892</t>
   </si>
   <si>
     <t xml:space="preserve">6.92536354064941</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07926177978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22921133041382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45808362960815</t>
+    <t xml:space="preserve">7.079261302948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22921180725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45808506011963</t>
   </si>
   <si>
     <t xml:space="preserve">7.26078081130981</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37127113342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26472663879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34759473800659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46992206573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36732578277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37916469573975</t>
+    <t xml:space="preserve">7.37127065658569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2647271156311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34759521484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46992301940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36732482910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37916421890259</t>
   </si>
   <si>
     <t xml:space="preserve">7.13450622558594</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18975114822388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10293769836426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15029191970825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10688447952271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20553588867188</t>
+    <t xml:space="preserve">7.18975067138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.102937221